--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>40</v>
+        <v>172</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>40</v>
+        <v>172</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
@@ -2555,12 +2555,12 @@
       <c r="G45" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H45" s="9" t="n">
-        <v>6</v>
+      <c r="H45" s="5" t="n">
+        <v>28</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>2:40</t>
+          <t>2:172</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>40</v>
+        <v>176</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>40</v>
+        <v>176</v>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
@@ -2599,12 +2599,12 @@
       <c r="G46" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H46" s="11" t="n">
-        <v>5</v>
+      <c r="H46" s="5" t="n">
+        <v>22</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>2:40</t>
+          <t>2:176</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
@@ -2643,12 +2643,12 @@
       <c r="G47" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H47" s="11" t="n">
-        <v>4</v>
+      <c r="H47" s="9" t="n">
+        <v>11</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>2:40</t>
+          <t>2:100</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -2814,13 +2814,13 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14259</v>
+        <v>14587</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2892,8 +2892,6 @@
           <t>辞書にある全単語数（問題化の母数）</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
@@ -2248,11 +2248,11 @@
         <v>6</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>3:80</t>
+          <t>3:100</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
@@ -2292,11 +2292,11 @@
         <v>7</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>3:80</t>
+          <t>3:100</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
@@ -2336,11 +2336,11 @@
         <v>6</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>3:80</t>
+          <t>3:100</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
@@ -2556,11 +2556,11 @@
         <v>6</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>2:172</t>
+          <t>2:200</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
@@ -2600,11 +2600,11 @@
         <v>8</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>2:176</t>
+          <t>2:200</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
@@ -2644,11 +2644,11 @@
         <v>9</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>2:100</t>
+          <t>2:200</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14587</v>
+        <v>14799</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大問別まとめ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模試ストック換算" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解攻略耐性分析" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大問別まとめ'!$A$1:$J$1</definedName>
@@ -99,7 +100,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6C9C4"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -161,9 +162,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -172,11 +170,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2247,7 +2245,7 @@
       <c r="G38" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H38" s="9" t="n">
+      <c r="H38" s="5" t="n">
         <v>16</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -2335,7 +2333,7 @@
       <c r="G40" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H40" s="9" t="n">
+      <c r="H40" s="5" t="n">
         <v>16</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -2410,10 +2408,10 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
@@ -2423,12 +2421,12 @@
       <c r="G42" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H42" s="9" t="n">
-        <v>8</v>
+      <c r="H42" s="5" t="n">
+        <v>40</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>2:40</t>
+          <t>2:200</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2454,10 +2452,10 @@
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
@@ -2467,12 +2465,12 @@
       <c r="G43" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H43" s="9" t="n">
-        <v>8</v>
+      <c r="H43" s="5" t="n">
+        <v>40</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>2:40</t>
+          <t>2:200</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2498,10 +2496,10 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
@@ -2511,12 +2509,12 @@
       <c r="G44" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H44" s="9" t="n">
-        <v>10</v>
+      <c r="H44" s="5" t="n">
+        <v>50</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>2:40</t>
+          <t>2:200</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -2542,10 +2540,10 @@
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
@@ -2556,11 +2554,11 @@
         <v>6</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>2:200</t>
+          <t>2:240</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -2586,10 +2584,10 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
@@ -2600,11 +2598,11 @@
         <v>8</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>2:200</t>
+          <t>2:240</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -2630,10 +2628,10 @@
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
@@ -2643,12 +2641,12 @@
       <c r="G47" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H47" s="9" t="n">
-        <v>22</v>
+      <c r="H47" s="5" t="n">
+        <v>26</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>2:200</t>
+          <t>2:240</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -2679,14 +2677,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>◆ 模試換算 = 在庫 ÷ 本番出題数 = その大問だけで組めるフル模試の回数（floor）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>セクション別 律速（そのセクションで最も少ない大問の回数＝そのセクションを何回組めるか）</t>
         </is>
@@ -2720,13 +2718,13 @@
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="13" t="n">
         <v>49</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="13" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2736,13 +2734,13 @@
           <t>文法</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="13" t="n">
         <v>34</v>
       </c>
     </row>
@@ -2752,13 +2750,13 @@
           <t>読解</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="14" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2768,18 +2766,18 @@
           <t>聴解</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="C8" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>10</v>
+      <c r="B8" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>級ごとの「フル模試」完成可能回数（全大問の最小＝律速大問で決まる）</t>
         </is>
@@ -2814,17 +2812,17 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>凡例：赤=5回以下(不足) / 橙=15回以下(要増産) / 緑=16回以上(十分)</t>
         </is>
@@ -2850,20 +2848,20 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>◆ 参考データ</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>在庫 合計</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14799</v>
+        <v>15399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2887,7 +2885,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>辞書にある全単語数（問題化の母数）</t>
         </is>
@@ -2909,6 +2907,1207 @@
           <t>内訳</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="18" max="18"/>
+    <col width="5" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>聴解 攻略耐性・モーラ・ワンパターン 分析（2026-08-16 自動集計｜daimon_solvability.py）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>本質3観点→ ①答えが本文/設問から予測できる ②誤答が弱い ③大問×レベル内でワンパターン/重複。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>語彙マッチ的中%=「本文と最も語が重なる選択肢」を選ぶと正解になる割合(基準=1/選択肢数)。高い=正解だけ本文語→聞かず語マッチで解ける(①②)。良い設計は正解を言い換え本文語は誤答へ罠として置く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>正解−誤答 本文一致差=正解の本文一致語数−誤答平均。+大=正解だけ本文語(①②)。最長を選ぶ的中=正解が最長選択肢の割合(②)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>選択肢方式「表示時ランダム」(課題/ポイント/概要=テキスト4択)はアプリが並べ替え→正解位置は無関係(正本①固定でOK)。「音声焼込み」(発話/即時)は位置固定→位置偏りが有効。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>台本重複/選択肢セット重複=同一大問×レベル内の近似(③)。設問テンプレ最大=同一設問文の最大シェア(③)。設計帯:課題/ポイント/概要/発話=公式中央値±20%、即時=公式実測再センタリング。既存問の帯外は帯導入前の据え置き。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>大問</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>問題数</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>選択肢数</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>選択肢方式</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>台本モーラ min/中/max</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>設計帯</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>帯外 短/長</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>最長を選ぶ的中%</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>基準%</t>
+        </is>
+      </c>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>語彙マッチ的中%</t>
+        </is>
+      </c>
+      <c r="L7" s="17" t="inlineStr">
+        <is>
+          <t>正解−誤答 本文一致差</t>
+        </is>
+      </c>
+      <c r="M7" s="17" t="inlineStr">
+        <is>
+          <t>設問テンプレ最大%</t>
+        </is>
+      </c>
+      <c r="N7" s="17" t="inlineStr">
+        <is>
+          <t>台本重複(≥.60)</t>
+        </is>
+      </c>
+      <c r="O7" s="17" t="inlineStr">
+        <is>
+          <t>選択肢セット重複(≥.70)</t>
+        </is>
+      </c>
+      <c r="P7" s="17" t="inlineStr">
+        <is>
+          <t>正解位置(正本)</t>
+        </is>
+      </c>
+      <c r="Q7" s="17" t="inlineStr">
+        <is>
+          <t>位置最大%(有効時)</t>
+        </is>
+      </c>
+      <c r="R7" s="17" t="inlineStr">
+        <is>
+          <t>係</t>
+        </is>
+      </c>
+      <c r="S7" s="17" t="inlineStr">
+        <is>
+          <t>留守</t>
+        </is>
+      </c>
+      <c r="T7" s="17" t="inlineStr">
+        <is>
+          <t>依頼形%</t>
+        </is>
+      </c>
+      <c r="U7" s="17" t="inlineStr">
+        <is>
+          <t>形分離%</t>
+        </is>
+      </c>
+      <c r="V7" s="17" t="inlineStr">
+        <is>
+          <t>機能max%</t>
+        </is>
+      </c>
+      <c r="W7" s="17" t="inlineStr">
+        <is>
+          <t>弁別軸max%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>課題理解</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>表示時ランダム</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>183/306/360</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>258-386</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>19/0</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>59</v>
+      </c>
+      <c r="J8" t="n">
+        <v>25</v>
+      </c>
+      <c r="K8" t="n">
+        <v>42</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>12</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>100/0/0/0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>課題理解</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>表示時ランダム</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>163/228/280</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>209-313</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>20/0</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>58</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25</v>
+      </c>
+      <c r="K9" t="n">
+        <v>36</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>100/0/0/0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>課題理解</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>表示時ランダム</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>73/116/154</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>105-157</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>13/0</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>57</v>
+      </c>
+      <c r="J10" t="n">
+        <v>25</v>
+      </c>
+      <c r="K10" t="n">
+        <v>18</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>100/0/0/0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ポイント理解</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>表示時ランダム</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>183/234/268</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>179-269</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>63</v>
+      </c>
+      <c r="J11" t="n">
+        <v>25</v>
+      </c>
+      <c r="K11" t="n">
+        <v>23</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>100/0/0/0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ポイント理解</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>表示時ランダム</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>124/192/256</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>175-263</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>16/0</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>63</v>
+      </c>
+      <c r="J12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>100/0/0/0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ポイント理解</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>表示時ランダム</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>84/162/216</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>149-223</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>20/0</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>60</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>100/0/0/0</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>概要理解</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>40</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>表示時ランダム</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>157/215/258</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>190-284</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>12/0</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>78</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K14" t="n">
+        <v>50</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>25/5/5/5</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>発話表現</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>200</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>音声焼込み(位置固定)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>29/40/47</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>27-41</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0/70</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>28</v>
+      </c>
+      <c r="J15" t="n">
+        <v>33</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>60/74/66</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>37</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>12</v>
+      </c>
+      <c r="U15" t="n">
+        <v>56</v>
+      </c>
+      <c r="V15" t="n">
+        <v>33</v>
+      </c>
+      <c r="W15" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>発話表現</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>200</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>音声焼込み(位置固定)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>24/38/47</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>20-30</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0/184</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>26</v>
+      </c>
+      <c r="J16" t="n">
+        <v>33</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>54/77/69</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>38</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>54</v>
+      </c>
+      <c r="V16" t="n">
+        <v>28</v>
+      </c>
+      <c r="W16" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>発話表現</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>200</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>音声焼込み(位置固定)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>24/36/47</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>20-30</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0/166</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>29</v>
+      </c>
+      <c r="J17" t="n">
+        <v>33</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>24</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>53/80/67</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>40</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>49</v>
+      </c>
+      <c r="V17" t="n">
+        <v>26</v>
+      </c>
+      <c r="W17" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>240</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>音声焼込み(位置固定)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>13/26/46</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>18-32</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>5/2</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>46</v>
+      </c>
+      <c r="J18" t="n">
+        <v>33</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>94/74/72</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>39</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>240</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>音声焼込み(位置固定)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>12/25/33</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>18-33</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>9/0</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>52</v>
+      </c>
+      <c r="J19" t="n">
+        <v>33</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>94/74/72</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>39</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>240</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>音声焼込み(位置固定)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8/24/30</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>14-27</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>13/21</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>38</v>
+      </c>
+      <c r="J20" t="n">
+        <v>33</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>94/74/72</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>39</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
@@ -2377,12 +2377,12 @@
       <c r="G41" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H41" s="9" t="n">
-        <v>13</v>
+      <c r="H41" s="5" t="n">
+        <v>26</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>3:40</t>
+          <t>3:80</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2772,8 +2772,8 @@
       <c r="C8" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>13</v>
+      <c r="D8" s="13" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15399</v>
+        <v>15439</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3144,16 +3144,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="J8" t="n">
         <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M8" t="n">
         <v>12</v>
@@ -3223,16 +3223,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="J9" t="n">
         <v>25</v>
       </c>
       <c r="K9" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="M9" t="n">
         <v>9</v>
@@ -3302,16 +3302,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="J10" t="n">
         <v>25</v>
       </c>
       <c r="K10" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="M10" t="n">
         <v>20</v>
@@ -3381,16 +3381,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="J11" t="n">
         <v>25</v>
       </c>
       <c r="K11" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="M11" t="n">
         <v>8</v>
@@ -3460,16 +3460,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>25</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="M12" t="n">
         <v>5</v>
@@ -3539,16 +3539,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
         <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M13" t="n">
         <v>9</v>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
         <v>4</v>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>157/215/258</t>
+          <t>203/234/272</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3614,23 +3614,23 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12/0</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
         <v>25</v>
       </c>
       <c r="K14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>-0.4</v>
       </c>
       <c r="M14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>25/5/5/5</t>
+          <t>20/20/20/20</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
@@ -2114,11 +2114,11 @@
         <v>7</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>3:100</t>
+          <t>3:96</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
@@ -2246,11 +2246,11 @@
         <v>6</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>3:100</t>
+          <t>3:104</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="14" t="n">
         <v>12</v>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>12</v>
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>73/116/154</t>
+          <t>73/115/154</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3314,7 +3314,7 @@
         <v>0.2</v>
       </c>
       <c r="M10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>100/0/0/0</t>
+          <t>96/0/0/0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>84/162/216</t>
+          <t>84/160/216</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3535,11 +3535,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>20/0</t>
+          <t>24/0</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
         <v>25</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>100/0/0/0</t>
+          <t>104/0/0/0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模試ストック換算" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解攻略耐性分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解 骨組みパラメータ分布" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大問別まとめ'!$A$1:$J$1</definedName>
@@ -2100,10 +2101,10 @@
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
@@ -2113,12 +2114,12 @@
       <c r="G35" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H35" s="9" t="n">
-        <v>13</v>
+      <c r="H35" s="5" t="n">
+        <v>21</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>3:96</t>
+          <t>3:150</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2144,10 +2145,10 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
@@ -2157,12 +2158,12 @@
       <c r="G36" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H36" s="9" t="n">
-        <v>12</v>
+      <c r="H36" s="5" t="n">
+        <v>18</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>3:100</t>
+          <t>3:150</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2188,10 +2189,10 @@
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
@@ -2202,11 +2203,11 @@
         <v>6</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>3:100</t>
+          <t>3:150</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2766,11 +2767,11 @@
           <t>聴解</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
-        <v>13</v>
+      <c r="B8" s="13" t="n">
+        <v>17</v>
       </c>
       <c r="C8" s="14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>16</v>
@@ -2811,11 +2812,11 @@
           <t>フル模試</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C12" s="9" t="n">
         <v>13</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>12</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>13</v>
@@ -2861,7 +2862,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15439</v>
+        <v>15593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3118,7 +3119,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -3130,7 +3131,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>183/306/360</t>
+          <t>183/306/384</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3144,19 +3145,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J8" t="n">
         <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3166,7 +3167,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>100/0/0/0</t>
+          <t>150/0/0/0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -3180,10 +3181,6 @@
       <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3197,7 +3194,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
@@ -3209,7 +3206,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>163/228/280</t>
+          <t>163/241/311</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3223,19 +3220,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J9" t="n">
         <v>25</v>
       </c>
       <c r="K9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -3245,7 +3242,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>100/0/0/0</t>
+          <t>150/0/0/0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -3259,10 +3256,6 @@
       <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3276,7 +3269,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -3298,23 +3291,23 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13/0</t>
+          <t>18/0</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J10" t="n">
         <v>25</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M10" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
@@ -3324,7 +3317,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>96/0/0/0</t>
+          <t>150/0/0/0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -3338,10 +3331,6 @@
       <c r="S10" t="n">
         <v>0</v>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3367,7 +3356,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>183/234/268</t>
+          <t>183/236/290</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3377,7 +3366,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -3417,10 +3406,6 @@
       <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3446,7 +3431,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>124/192/256</t>
+          <t>124/190/256</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3456,7 +3441,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>16/0</t>
+          <t>21/0</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -3469,7 +3454,7 @@
         <v>17</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="M12" t="n">
         <v>5</v>
@@ -3496,10 +3481,6 @@
       <c r="S12" t="n">
         <v>0</v>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3525,7 +3506,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>84/160/216</t>
+          <t>84/162/216</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3535,7 +3516,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>24/0</t>
+          <t>29/0</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -3575,10 +3556,6 @@
       <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3654,10 +3631,6 @@
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3702,9 +3675,6 @@
       <c r="J15" t="n">
         <v>33</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
         <v>4</v>
       </c>
@@ -3781,9 +3751,6 @@
       <c r="J16" t="n">
         <v>33</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
         <v>8</v>
       </c>
@@ -3860,9 +3827,6 @@
       <c r="J17" t="n">
         <v>33</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
         <v>24</v>
       </c>
@@ -3939,9 +3903,6 @@
       <c r="J18" t="n">
         <v>33</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
         <v>0</v>
       </c>
@@ -3962,10 +3923,6 @@
       <c r="S18" t="n">
         <v>0</v>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4010,9 +3967,6 @@
       <c r="J19" t="n">
         <v>33</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
         <v>0</v>
       </c>
@@ -4033,10 +3987,6 @@
       <c r="S19" t="n">
         <v>0</v>
       </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4081,9 +4031,6 @@
       <c r="J20" t="n">
         <v>33</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -4104,10 +4051,526 @@
       <c r="S20" t="n">
         <v>0</v>
       </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>聴解 骨組みパラメータ分布（2026-08-18 自動集計｜skeleton_tag.py）＝ワンパターン化を止めるための型バランス。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>偏り＝聞かず解ける/飽きるの芽。直し方＝既存はいじらず『薄い型』を新しく足して薄める（既存音声の焼き直し不要・新規追加分だけTTS）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>番人：1つの型が過半(50%)を占めたらビルド失格。作問前の目安＝35%以下（skeleton_tag.py check）。『薄い型』列＝ここを増やせば偏りが下がる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>kanten(観点)は全レベル良好。q_type(概要の聞き方)は質問が音声焼込み＝既存の付け替えは有料、薄めは新規追加で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>大問</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>パラメータ</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>問題数</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>型の数</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>目安/型</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>最も多い型</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>最大%</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>薄い型＝ここを増やして薄める</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>全分布</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>①課題理解</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>develop</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>150</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>条件順序</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>✅良好</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>上書き15 条件順序33 消去30 まず次13 追加14 二者択一14 断って代案14 勘違い訂正17</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>①課題理解</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>develop</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>消去</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>✅良好</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>上書き18 条件順序18 消去33 まず次23 追加16 二者択一14 断って代案14 勘違い訂正14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>①課題理解</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>develop</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>150</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>消去</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>✅良好</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>上書き12 条件順序34 消去46 まず次11 追加12 二者択一11 断って代案11 勘違い訂正13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>②ポイント理解</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>kanten</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>104</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>21</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>いつ</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>✅良好</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>なぜ20 いつ24 いくつ19 気持ち18 どれ23</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>②ポイント理解</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>kanten</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>どれ</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>✅良好</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>なぜ20 いつ20 いくつ19 気持ち20 どれ21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>②ポイント理解</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>kanten</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>20</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>なぜ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>✅良好</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>なぜ21 いつ20 いくつ20 気持ち19 どれ20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>③概要理解</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>genre</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>80</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>社会自然</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>✅良好</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>モノサービス(1) 文化行事(2)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>健康体10 生活くらし14 社会自然24 仕事7 学び12 モノサービス1 文化行事2 趣味旅食10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>③概要理解</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q_type</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>27</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>主張</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>❌過半(音声固定)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>何について(20) タイトル(0)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>何について20 主張60</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大問別まとめ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模試ストック換算" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解攻略耐性分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解 骨組みパラメータ分布" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="習得の仕組み(ID×面)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大問別まとめ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模試ストック換算" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解攻略耐性分析" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解 骨組みパラメータ分布" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大問別まとめ'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大問別まとめ'!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,8 +57,25 @@
       <i val="1"/>
       <color rgb="007A756C"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -104,8 +122,38 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF2FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -127,11 +175,25 @@
         <color rgb="00C9D3DE"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00AAB4C8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00AAB4C8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAB4C8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAB4C8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -175,6 +237,53 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -541,6 +650,374 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>習得の仕組み ― 「ID × 面(かたち)」で覚え具合を測る</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>IDは『あなたが何をどれだけ覚えたか』を記録する“貯金箱”。大問を1問解くたびに、その問題が紐づくIDへ習得が貯まり、その貯金がアプリの成長表示(予想得点・カバー率・リング・復習)をすべて動かしている。弱点ドリルはその使い道の一つにすぎない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>■ 流れ（1問解くと何が起きるか）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>① 大問を1問解く</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>② その問題が「どのID」の「どの面」かを判定  ← facetMap.ts が正本</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>③ そのID×面に習得が加算/減点  ← state.mastery（面別マスタリー）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>④ 貯まった習得が、予想得点・カバー率・合格リング・復習の出題・弱点ドリルを動かす</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>■ 5つの面(かたち)＝1つのIDを、この5方向で別々に追う</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>面</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>意味</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>read（読み）</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>漢字が読めるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>write（書き）</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>漢字が書けるか・正しい表記が選べるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>mean（意味）</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>語の意味・使い方が分かるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>listen（聞き取り）</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>聞いて分かるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>grammar（文法）</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>文法の形・組み立てが分かるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>■ 3種のID × 貯まる面 × どの大問で貯まるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>種類</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>貯まる面</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>どの大問を解くと貯まるか</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="n"/>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>語彙単語（vocab id）</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>read・write・mean・listen</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>漢字読み→read ／ 表記→write ／ 文脈規定・言い換え・用法→mean ／ 聞き取り→listen</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="n"/>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>漢字単語（kanji字）</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>read・write</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>漢字読み→read ／ 書き取り→write</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="n"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>文法単語（文法点 pointId）</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>grammar</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>穴埋め(文法形式)・並べ替え(組み立て)・文章の文法 → すべて grammar 面へ合流</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>■ 例：語彙「食べる」</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>「読める(read)」「書ける(write)」「意味が分かる(mean)」「聞いて分かる(listen)」を別々に持つ。だから『覚えた／覚えてない』の○×ではなく、面ごとの“濃淡”で測れる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>■ IDが実際に動かしているもの（弱点ドリルは氷山の一角）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>動かすもの</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>中身</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>予想得点（合格ラインにどれだけ届いたか）</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>各文法点／語の習得を正答確率に変換し、本番の出題数で重み付けして180点満点で計算（selectors.ts・CLAUDE.md §4）</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="n"/>
+      <c r="D29" s="33" t="n"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>カバー率</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>レベル内の文法点のうち、grammar面が0.6以上の点の割合＝『文法をどれだけ広く覚えたか』</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="n"/>
+      <c r="D30" s="33" t="n"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>合格リングの中央％</t>
+        </is>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>予想得点と同じ配点で合格の可能性を示す</t>
+        </is>
+      </c>
+      <c r="C31" s="33" t="n"/>
+      <c r="D31" s="33" t="n"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>復習の出題選び</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>弱い／期限が来たIDを選び、そのID×面に合う“検証済みバンク問題”を出す（おすすめ・ホーム・書斎・AIコーチ・カード）</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="n"/>
+      <c r="D32" s="33" t="n"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>模試あとの弱点ドリル</t>
+        </is>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>間違えた問題のIDを、上と同じ検証済みバンク経路で復習（今回、復習と同じプールに統一）</t>
+        </is>
+      </c>
+      <c r="C33" s="33" t="n"/>
+      <c r="D33" s="33" t="n"/>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="34" t="inlineStr">
+        <is>
+          <t>だから CLAUDE.md §4 は「pointId の貼り直し(正解=pointID)は予想得点・カバー率を正確化する」と言う。IDが習得の受け皿だから、紐づけを間違えると別の場所に習得が貯まって数字が狂う、という意味。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B12:D12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2662,7 +3139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2834,7 +3311,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2914,7 +3391,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4057,7 +4534,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -7,15 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="習得の仕組み(ID×面)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大問別まとめ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模試ストック換算" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解攻略耐性分析" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解 骨組みパラメータ分布" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大問別まとめ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模試ストック換算" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="読解 品質パラメータ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="習得の仕組み(ID×面)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="単語数と紐づけ大問" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="単語×大問カバー率" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解攻略耐性分析" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解 骨組みパラメータ分布" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大問別まとめ'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大問別まとめ'!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,8 +77,33 @@
       <i val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F7A1F"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C55A11"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -152,8 +180,23 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C55A11"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -189,11 +232,69 @@
         <color rgb="00AAB4C8"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAB4C8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00AAB4C8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAB4C8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAB4C8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAB4C8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00AAB4C8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAB4C8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAB4C8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -285,6 +386,75 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -650,6 +820,3740 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>セクション</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>大問</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>在庫問題数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>セット数</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>未検証</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>本番出題数</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>模試換算(何回分)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>誤答数の内訳</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>シャッフル</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>漢字読み</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>463</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>3:463</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>漢字読み</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>3:448</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>漢字読み</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>1398</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>174</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>3:1398</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>527</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>3:527</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>492</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>3:492</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1527</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>254</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>3:1527</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>文脈規定</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>655</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>3:165 / 4:222 / 5:268</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>文脈規定</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>651</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>3:239 / 4:230 / 5:182</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>文脈規定</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>2090</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1318</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>3:1382 / 4:450 / 5:258</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>言い換え類義</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>3:72 / 4:23 / 5:53</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>言い換え類義</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>3:1 / 4:8 / 5:45 / 6:131</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>言い換え類義</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>3:3 / 4:16 / 5:106 / 6:875</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>用法</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>3:42 / 4:37 / 5:40 / 6:34</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>用法</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>3:46 / 4:44 / 5:39 / 6:21</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>文法形式</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>3:203 / 4:1</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>文法形式</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>357</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>3:357</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>文法形式</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>443</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>3:441 / 4:2</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>組み立て</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>3:137</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>組み立て</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>214</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>3:214</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>組み立て</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>308</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>3:308</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>文章の文法</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>3:400</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>文章の文法</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>3:400</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>文章の文法</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>3:200</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>内容理解(短文)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D25" s="60" t="n">
+        <v>90</v>
+      </c>
+      <c r="E25" s="60" t="n">
+        <v>90</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="61" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="62" t="inlineStr">
+        <is>
+          <t>3:90</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>内容理解(短文)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D26" s="60" t="n">
+        <v>120</v>
+      </c>
+      <c r="E26" s="60" t="n">
+        <v>120</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="61" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="62" t="inlineStr">
+        <is>
+          <t>3:120</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>内容理解(短文)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D27" s="60" t="n">
+        <v>120</v>
+      </c>
+      <c r="E27" s="60" t="n">
+        <v>120</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" s="61" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="62" t="inlineStr">
+        <is>
+          <t>3:120</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>内容理解(中文)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D28" s="60" t="n">
+        <v>80</v>
+      </c>
+      <c r="E28" s="60" t="n">
+        <v>40</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="61" t="n">
+        <v>40</v>
+      </c>
+      <c r="I28" s="62" t="inlineStr">
+        <is>
+          <t>3:80</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>内容理解(中文)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D29" s="60" t="n">
+        <v>160</v>
+      </c>
+      <c r="E29" s="60" t="n">
+        <v>40</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="61" t="n">
+        <v>40</v>
+      </c>
+      <c r="I29" s="62" t="inlineStr">
+        <is>
+          <t>3:160</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>内容理解(中文)</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D30" s="60" t="n">
+        <v>240</v>
+      </c>
+      <c r="E30" s="60" t="n">
+        <v>80</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" s="61" t="n">
+        <v>40</v>
+      </c>
+      <c r="I30" s="62" t="inlineStr">
+        <is>
+          <t>3:240</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>内容理解(長文)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D31" s="60" t="n">
+        <v>160</v>
+      </c>
+      <c r="E31" s="60" t="n">
+        <v>40</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" s="61" t="n">
+        <v>40</v>
+      </c>
+      <c r="I31" s="62" t="inlineStr">
+        <is>
+          <t>3:160</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>情報検索</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>3:110</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>情報検索</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>3:140</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>情報検索</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>3:155</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>課題理解</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>課題理解</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>課題理解</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>ポイント理解</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>ポイント理解</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>ポイント理解</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>概要理解</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>3:80</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>発話表現</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>2:200</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>発話表現</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>2:200</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>発話表現</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>2:200</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>2:240</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>2:240</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>2:240</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="63" t="inlineStr">
+        <is>
+          <t>※2026-08-20 読解の新規217本(短N4+65/短N3+65/中N4+15/中N3+53/長N3+19)を在庫に反映(黄セル)。本体JSONへはネパール語訳後に適用予定(番人green)。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>◆ 模試換算 = 在庫 ÷ 本番出題数 = その大問だけで組めるフル模試の回数（floor）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>セクション別 律速（そのセクションで最も少ない大問の回数＝そのセクションを何回組めるか）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>セクション</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="n">
+        <v>30</v>
+      </c>
+      <c r="C7" s="60" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" s="60" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>級ごとの「フル模試」完成可能回数（全大問の最小＝律速大問で決まる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>セクション</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>フル模試</t>
+        </is>
+      </c>
+      <c r="B12" s="61" t="n">
+        <v>21</v>
+      </c>
+      <c r="C12" s="61" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="61" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>凡例：赤=5回以下(不足) / 橙=15回以下(要増産) / 緑=16回以上(十分)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>◆ 参考データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>在庫 合計</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>15739</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>問</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>在庫外（監査に落ちた分・在庫に数えない）</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>問</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>辞書にある全単語数（問題化の母数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>辞書</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>内訳</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>読解 品質パラメータ（更新 2026-08-20・番人と同基準／字数はルビ除去）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="53" t="inlineStr">
+        <is>
+          <t>①内容理解（短/中/長）　現行＝本体JSON／適用後見込み＝新規217本を合流した姿（黄・番人green・ne訳後に適用予定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>大問</t>
+        </is>
+      </c>
+      <c r="B4" s="54" t="inlineStr">
+        <is>
+          <t>級</t>
+        </is>
+      </c>
+      <c r="C4" s="54" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="E4" s="54" t="inlineStr">
+        <is>
+          <t>設問</t>
+        </is>
+      </c>
+      <c r="F4" s="54" t="inlineStr">
+        <is>
+          <t>設問/本文(公式)</t>
+        </is>
+      </c>
+      <c r="G4" s="54" t="inlineStr">
+        <is>
+          <t>字数中央(最小/最大)</t>
+        </is>
+      </c>
+      <c r="H4" s="54" t="inlineStr">
+        <is>
+          <t>目標[許容]</t>
+        </is>
+      </c>
+      <c r="I4" s="54" t="inlineStr">
+        <is>
+          <t>帯外短/長</t>
+        </is>
+      </c>
+      <c r="J4" s="54" t="inlineStr">
+        <is>
+          <t>最長%(≤35)</t>
+        </is>
+      </c>
+      <c r="K4" s="54" t="inlineStr">
+        <is>
+          <t>丸写%</t>
+        </is>
+      </c>
+      <c r="L4" s="54" t="inlineStr">
+        <is>
+          <t>語彙%(≤45)</t>
+        </is>
+      </c>
+      <c r="M4" s="54" t="inlineStr">
+        <is>
+          <t>指示語本</t>
+        </is>
+      </c>
+      <c r="N4" s="54" t="inlineStr">
+        <is>
+          <t>指示語率</t>
+        </is>
+      </c>
+      <c r="O4" s="54" t="inlineStr">
+        <is>
+          <t>設問型</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>内容理解短</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>現行</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="n">
+        <v>55</v>
+      </c>
+      <c r="E5" s="55" t="n">
+        <v>55</v>
+      </c>
+      <c r="F5" s="55" t="inlineStr">
+        <is>
+          <t>1.0(1)</t>
+        </is>
+      </c>
+      <c r="G5" s="55" t="inlineStr">
+        <is>
+          <t>70(60/80)</t>
+        </is>
+      </c>
+      <c r="H5" s="55" t="inlineStr">
+        <is>
+          <t>80[48-120]</t>
+        </is>
+      </c>
+      <c r="I5" s="55" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J5" s="55" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="K5" s="55" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L5" s="55" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="M5" s="55" t="inlineStr">
+        <is>
+          <t>0/55</t>
+        </is>
+      </c>
+      <c r="N5" s="55" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="O5" s="55" t="inlineStr">
+        <is>
+          <t>その他27 条件照合24 理由4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="56" t="inlineStr">
+        <is>
+          <t>内容理解短</t>
+        </is>
+      </c>
+      <c r="B6" s="56" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C6" s="56" t="inlineStr">
+        <is>
+          <t>適用後(+35)</t>
+        </is>
+      </c>
+      <c r="D6" s="56" t="n">
+        <v>90</v>
+      </c>
+      <c r="E6" s="56" t="n">
+        <v>90</v>
+      </c>
+      <c r="F6" s="56" t="inlineStr">
+        <is>
+          <t>1.0(1)</t>
+        </is>
+      </c>
+      <c r="G6" s="56" t="inlineStr">
+        <is>
+          <t>70(53/80)</t>
+        </is>
+      </c>
+      <c r="H6" s="56" t="inlineStr">
+        <is>
+          <t>80[48-120]</t>
+        </is>
+      </c>
+      <c r="I6" s="56" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J6" s="56" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="K6" s="56" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="L6" s="56" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="M6" s="56" t="inlineStr">
+        <is>
+          <t>0/90</t>
+        </is>
+      </c>
+      <c r="N6" s="56" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="O6" s="56" t="inlineStr">
+        <is>
+          <t>その他49 条件照合31 理由7 行動2 主張主旨1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t>内容理解短</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>現行</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="n">
+        <v>55</v>
+      </c>
+      <c r="E7" s="55" t="n">
+        <v>55</v>
+      </c>
+      <c r="F7" s="55" t="inlineStr">
+        <is>
+          <t>1.0(1)</t>
+        </is>
+      </c>
+      <c r="G7" s="55" t="inlineStr">
+        <is>
+          <t>101(87/114)</t>
+        </is>
+      </c>
+      <c r="H7" s="55" t="inlineStr">
+        <is>
+          <t>150[90-225]</t>
+        </is>
+      </c>
+      <c r="I7" s="55" t="inlineStr">
+        <is>
+          <t>2/0</t>
+        </is>
+      </c>
+      <c r="J7" s="55" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="K7" s="55" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="L7" s="55" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="M7" s="55" t="inlineStr">
+        <is>
+          <t>0/55</t>
+        </is>
+      </c>
+      <c r="N7" s="55" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="O7" s="55" t="inlineStr">
+        <is>
+          <t>その他21 条件照合14 行動10 理由6 主張主旨4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="56" t="inlineStr">
+        <is>
+          <t>内容理解短</t>
+        </is>
+      </c>
+      <c r="B8" s="56" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C8" s="56" t="inlineStr">
+        <is>
+          <t>適用後(+65)</t>
+        </is>
+      </c>
+      <c r="D8" s="56" t="n">
+        <v>120</v>
+      </c>
+      <c r="E8" s="56" t="n">
+        <v>120</v>
+      </c>
+      <c r="F8" s="56" t="inlineStr">
+        <is>
+          <t>1.0(1)</t>
+        </is>
+      </c>
+      <c r="G8" s="56" t="inlineStr">
+        <is>
+          <t>113(87/138)</t>
+        </is>
+      </c>
+      <c r="H8" s="56" t="inlineStr">
+        <is>
+          <t>150[90-225]</t>
+        </is>
+      </c>
+      <c r="I8" s="56" t="inlineStr">
+        <is>
+          <t>2/0</t>
+        </is>
+      </c>
+      <c r="J8" s="56" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K8" s="56" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="L8" s="56" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M8" s="56" t="inlineStr">
+        <is>
+          <t>0/120</t>
+        </is>
+      </c>
+      <c r="N8" s="56" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="O8" s="56" t="inlineStr">
+        <is>
+          <t>その他62 条件照合26 行動17 理由9 主張主旨6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="55" t="inlineStr">
+        <is>
+          <t>内容理解短</t>
+        </is>
+      </c>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>現行</t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="n">
+        <v>55</v>
+      </c>
+      <c r="E9" s="55" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" s="55" t="inlineStr">
+        <is>
+          <t>1.0(1)</t>
+        </is>
+      </c>
+      <c r="G9" s="55" t="inlineStr">
+        <is>
+          <t>133(118/151)</t>
+        </is>
+      </c>
+      <c r="H9" s="55" t="inlineStr">
+        <is>
+          <t>175[105-262]</t>
+        </is>
+      </c>
+      <c r="I9" s="55" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J9" s="55" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K9" s="55" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="L9" s="55" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="M9" s="55" t="inlineStr">
+        <is>
+          <t>0/55</t>
+        </is>
+      </c>
+      <c r="N9" s="55" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="O9" s="55" t="inlineStr">
+        <is>
+          <t>主張主旨17 その他15 理由14 条件照合6 行動3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="56" t="inlineStr">
+        <is>
+          <t>内容理解短</t>
+        </is>
+      </c>
+      <c r="B10" s="56" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C10" s="56" t="inlineStr">
+        <is>
+          <t>適用後(+65)</t>
+        </is>
+      </c>
+      <c r="D10" s="56" t="n">
+        <v>120</v>
+      </c>
+      <c r="E10" s="56" t="n">
+        <v>120</v>
+      </c>
+      <c r="F10" s="56" t="inlineStr">
+        <is>
+          <t>1.0(1)</t>
+        </is>
+      </c>
+      <c r="G10" s="56" t="inlineStr">
+        <is>
+          <t>152(118/191)</t>
+        </is>
+      </c>
+      <c r="H10" s="56" t="inlineStr">
+        <is>
+          <t>175[105-262]</t>
+        </is>
+      </c>
+      <c r="I10" s="56" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J10" s="56" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K10" s="56" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="L10" s="56" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="M10" s="56" t="inlineStr">
+        <is>
+          <t>7/120</t>
+        </is>
+      </c>
+      <c r="N10" s="56" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="O10" s="56" t="inlineStr">
+        <is>
+          <t>その他43 主張主旨25 理由20 条件照合17 行動8 指示語7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
+          <t>内容理解中</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>現行</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="n">
+        <v>27</v>
+      </c>
+      <c r="E11" s="55" t="n">
+        <v>54</v>
+      </c>
+      <c r="F11" s="55" t="inlineStr">
+        <is>
+          <t>2.0(2)</t>
+        </is>
+      </c>
+      <c r="G11" s="55" t="inlineStr">
+        <is>
+          <t>221(172/235)</t>
+        </is>
+      </c>
+      <c r="H11" s="55" t="inlineStr">
+        <is>
+          <t>250[150-375]</t>
+        </is>
+      </c>
+      <c r="I11" s="55" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J11" s="55" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K11" s="55" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L11" s="55" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="M11" s="55" t="inlineStr">
+        <is>
+          <t>27/27</t>
+        </is>
+      </c>
+      <c r="N11" s="57" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O11" s="55" t="inlineStr">
+        <is>
+          <t>指示語27 その他20 理由5 条件照合2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="56" t="inlineStr">
+        <is>
+          <t>内容理解中</t>
+        </is>
+      </c>
+      <c r="B12" s="56" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C12" s="56" t="inlineStr">
+        <is>
+          <t>適用後(+13)</t>
+        </is>
+      </c>
+      <c r="D12" s="56" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" s="56" t="n">
+        <v>80</v>
+      </c>
+      <c r="F12" s="56" t="inlineStr">
+        <is>
+          <t>2.0(2)</t>
+        </is>
+      </c>
+      <c r="G12" s="56" t="inlineStr">
+        <is>
+          <t>215(163/235)</t>
+        </is>
+      </c>
+      <c r="H12" s="56" t="inlineStr">
+        <is>
+          <t>250[150-375]</t>
+        </is>
+      </c>
+      <c r="I12" s="56" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J12" s="56" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K12" s="56" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="L12" s="56" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M12" s="56" t="inlineStr">
+        <is>
+          <t>40/40</t>
+        </is>
+      </c>
+      <c r="N12" s="58" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O12" s="56" t="inlineStr">
+        <is>
+          <t>指示語40 その他31 理由6 条件照合3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>内容理解中</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>現行</t>
+        </is>
+      </c>
+      <c r="D13" s="55" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="55" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" s="55" t="inlineStr">
+        <is>
+          <t>4.0(4)</t>
+        </is>
+      </c>
+      <c r="G13" s="55" t="inlineStr">
+        <is>
+          <t>339(322/370)</t>
+        </is>
+      </c>
+      <c r="H13" s="55" t="inlineStr">
+        <is>
+          <t>450[270-675]</t>
+        </is>
+      </c>
+      <c r="I13" s="55" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J13" s="55" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K13" s="55" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="L13" s="55" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="M13" s="55" t="inlineStr">
+        <is>
+          <t>25/25</t>
+        </is>
+      </c>
+      <c r="N13" s="57" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O13" s="55" t="inlineStr">
+        <is>
+          <t>その他46 指示語25 理由17 条件照合8 主張主旨4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="56" t="inlineStr">
+        <is>
+          <t>内容理解中</t>
+        </is>
+      </c>
+      <c r="B14" s="56" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C14" s="56" t="inlineStr">
+        <is>
+          <t>適用後(+15)</t>
+        </is>
+      </c>
+      <c r="D14" s="56" t="n">
+        <v>40</v>
+      </c>
+      <c r="E14" s="56" t="n">
+        <v>160</v>
+      </c>
+      <c r="F14" s="56" t="inlineStr">
+        <is>
+          <t>4.0(4)</t>
+        </is>
+      </c>
+      <c r="G14" s="56" t="inlineStr">
+        <is>
+          <t>348(322/476)</t>
+        </is>
+      </c>
+      <c r="H14" s="56" t="inlineStr">
+        <is>
+          <t>450[270-675]</t>
+        </is>
+      </c>
+      <c r="I14" s="56" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J14" s="56" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K14" s="56" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L14" s="56" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="M14" s="56" t="inlineStr">
+        <is>
+          <t>40/40</t>
+        </is>
+      </c>
+      <c r="N14" s="58" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O14" s="56" t="inlineStr">
+        <is>
+          <t>その他71 指示語40 理由26 条件照合14 主張主旨5 行動4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t>内容理解中</t>
+        </is>
+      </c>
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C15" s="55" t="inlineStr">
+        <is>
+          <t>現行</t>
+        </is>
+      </c>
+      <c r="D15" s="55" t="n">
+        <v>27</v>
+      </c>
+      <c r="E15" s="55" t="n">
+        <v>81</v>
+      </c>
+      <c r="F15" s="55" t="inlineStr">
+        <is>
+          <t>3.0(3)</t>
+        </is>
+      </c>
+      <c r="G15" s="55" t="inlineStr">
+        <is>
+          <t>409(322/436)</t>
+        </is>
+      </c>
+      <c r="H15" s="55" t="inlineStr">
+        <is>
+          <t>350[210-525]</t>
+        </is>
+      </c>
+      <c r="I15" s="55" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J15" s="55" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="K15" s="55" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="L15" s="55" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="M15" s="55" t="inlineStr">
+        <is>
+          <t>27/27</t>
+        </is>
+      </c>
+      <c r="N15" s="57" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O15" s="55" t="inlineStr">
+        <is>
+          <t>主張主旨38 指示語27 理由7 その他6 条件照合3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="56" t="inlineStr">
+        <is>
+          <t>内容理解中</t>
+        </is>
+      </c>
+      <c r="B16" s="56" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C16" s="56" t="inlineStr">
+        <is>
+          <t>適用後(+53)</t>
+        </is>
+      </c>
+      <c r="D16" s="56" t="n">
+        <v>80</v>
+      </c>
+      <c r="E16" s="56" t="n">
+        <v>240</v>
+      </c>
+      <c r="F16" s="56" t="inlineStr">
+        <is>
+          <t>3.0(3)</t>
+        </is>
+      </c>
+      <c r="G16" s="56" t="inlineStr">
+        <is>
+          <t>312(277/436)</t>
+        </is>
+      </c>
+      <c r="H16" s="56" t="inlineStr">
+        <is>
+          <t>350[210-525]</t>
+        </is>
+      </c>
+      <c r="I16" s="56" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J16" s="56" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="K16" s="56" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="L16" s="56" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="M16" s="56" t="inlineStr">
+        <is>
+          <t>80/80</t>
+        </is>
+      </c>
+      <c r="N16" s="58" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O16" s="56" t="inlineStr">
+        <is>
+          <t>指示語80 主張主旨62 条件照合62 理由26 その他10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="55" t="inlineStr">
+        <is>
+          <t>内容理解長</t>
+        </is>
+      </c>
+      <c r="B17" s="55" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C17" s="55" t="inlineStr">
+        <is>
+          <t>現行</t>
+        </is>
+      </c>
+      <c r="D17" s="55" t="n">
+        <v>21</v>
+      </c>
+      <c r="E17" s="55" t="n">
+        <v>84</v>
+      </c>
+      <c r="F17" s="55" t="inlineStr">
+        <is>
+          <t>4.0(4)</t>
+        </is>
+      </c>
+      <c r="G17" s="55" t="inlineStr">
+        <is>
+          <t>552(542/579)</t>
+        </is>
+      </c>
+      <c r="H17" s="55" t="inlineStr">
+        <is>
+          <t>550[330-825]</t>
+        </is>
+      </c>
+      <c r="I17" s="55" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J17" s="55" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K17" s="55" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="L17" s="55" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="M17" s="55" t="inlineStr">
+        <is>
+          <t>21/21</t>
+        </is>
+      </c>
+      <c r="N17" s="57" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O17" s="55" t="inlineStr">
+        <is>
+          <t>主張主旨34 指示語21 理由11 条件照合10 その他8</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="56" t="inlineStr">
+        <is>
+          <t>内容理解長</t>
+        </is>
+      </c>
+      <c r="B18" s="56" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C18" s="56" t="inlineStr">
+        <is>
+          <t>適用後(+19)</t>
+        </is>
+      </c>
+      <c r="D18" s="56" t="n">
+        <v>40</v>
+      </c>
+      <c r="E18" s="56" t="n">
+        <v>160</v>
+      </c>
+      <c r="F18" s="56" t="inlineStr">
+        <is>
+          <t>4.0(4)</t>
+        </is>
+      </c>
+      <c r="G18" s="56" t="inlineStr">
+        <is>
+          <t>543(441/579)</t>
+        </is>
+      </c>
+      <c r="H18" s="56" t="inlineStr">
+        <is>
+          <t>550[330-825]</t>
+        </is>
+      </c>
+      <c r="I18" s="56" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J18" s="56" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K18" s="56" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="L18" s="56" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="M18" s="56" t="inlineStr">
+        <is>
+          <t>40/40</t>
+        </is>
+      </c>
+      <c r="N18" s="58" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O18" s="56" t="inlineStr">
+        <is>
+          <t>主張主旨54 指示語40 条件照合34 理由23 その他9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="53" t="inlineStr">
+        <is>
+          <t>②情報検索（図版込み・新規なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="54" t="inlineStr">
+        <is>
+          <t>級</t>
+        </is>
+      </c>
+      <c r="B21" s="54" t="inlineStr">
+        <is>
+          <t>掲示</t>
+        </is>
+      </c>
+      <c r="C21" s="54" t="inlineStr">
+        <is>
+          <t>設問</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>実効字数中央(最小/最大)</t>
+        </is>
+      </c>
+      <c r="E21" s="54" t="inlineStr">
+        <is>
+          <t>目標[許容]</t>
+        </is>
+      </c>
+      <c r="F21" s="54" t="inlineStr">
+        <is>
+          <t>帯外短/長</t>
+        </is>
+      </c>
+      <c r="G21" s="54" t="inlineStr">
+        <is>
+          <t>figure比率</t>
+        </is>
+      </c>
+      <c r="H21" s="54" t="inlineStr">
+        <is>
+          <t>図版依存%</t>
+        </is>
+      </c>
+      <c r="I21" s="54" t="inlineStr">
+        <is>
+          <t>本文自足%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="55" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="B22" s="55" t="n">
+        <v>110</v>
+      </c>
+      <c r="C22" s="55" t="n">
+        <v>110</v>
+      </c>
+      <c r="D22" s="55" t="inlineStr">
+        <is>
+          <t>292(196/420)</t>
+        </is>
+      </c>
+      <c r="E22" s="55" t="inlineStr">
+        <is>
+          <t>250[150-375]</t>
+        </is>
+      </c>
+      <c r="F22" s="55" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="G22" s="55" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="H22" s="55" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="I22" s="55" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="B23" s="55" t="n">
+        <v>140</v>
+      </c>
+      <c r="C23" s="55" t="n">
+        <v>140</v>
+      </c>
+      <c r="D23" s="55" t="inlineStr">
+        <is>
+          <t>430(330/587)</t>
+        </is>
+      </c>
+      <c r="E23" s="55" t="inlineStr">
+        <is>
+          <t>400[240-600]</t>
+        </is>
+      </c>
+      <c r="F23" s="55" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="G23" s="55" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="H23" s="55" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="I23" s="55" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="55" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="B24" s="55" t="n">
+        <v>155</v>
+      </c>
+      <c r="C24" s="55" t="n">
+        <v>155</v>
+      </c>
+      <c r="D24" s="55" t="inlineStr">
+        <is>
+          <t>607(495/988)</t>
+        </is>
+      </c>
+      <c r="E24" s="55" t="inlineStr">
+        <is>
+          <t>600[360-900]</t>
+        </is>
+      </c>
+      <c r="F24" s="55" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G24" s="55" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="H24" s="55" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="I24" s="55" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="59" t="inlineStr">
+        <is>
+          <t>番人：tools/dokkai_solvability.py --check（最長≤35/語彙≤45/設問数固定/指示語必須 中N4中N3長N3）＋ joho_figure_check.py（図版込み字数）。現状ハード全合格。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="59" t="inlineStr">
+        <is>
+          <t>更新点(2026-08-20)：中N4/中N3/長N3を全問題に指示語（現行本体＝100%）。新規217本(短N4 65/短N3 65/中N4 15/中N3 53/長N3 19)は番人green・ne訳→適用待ち。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="59" t="inlineStr">
+        <is>
+          <t>WARN(非致命)：短N4の2本が字数下限割れ／中N5は指示語0（公式もんだい5の指示内容問が要補充・別件）。丸写%は指標であり番人ゲートではない。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -726,6 +4630,8 @@
           <t>意味</t>
         </is>
       </c>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="36" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
@@ -738,6 +4644,8 @@
           <t>漢字が読めるか</t>
         </is>
       </c>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="36" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
@@ -750,6 +4658,8 @@
           <t>漢字が書けるか・正しい表記が選べるか</t>
         </is>
       </c>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="36" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
@@ -762,6 +4672,8 @@
           <t>語の意味・使い方が分かるか</t>
         </is>
       </c>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="36" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="25" t="inlineStr">
@@ -774,6 +4686,8 @@
           <t>聞いて分かるか</t>
         </is>
       </c>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="36" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="23" t="inlineStr">
@@ -786,6 +4700,8 @@
           <t>文法の形・組み立てが分かるか</t>
         </is>
       </c>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="36" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="20" t="inlineStr">
@@ -810,7 +4726,7 @@
           <t>どの大問を解くと貯まるか</t>
         </is>
       </c>
-      <c r="D19" s="27" t="n"/>
+      <c r="D19" s="36" t="n"/>
     </row>
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
@@ -828,7 +4744,7 @@
           <t>漢字読み→read ／ 表記→write ／ 文脈規定・言い換え・用法→mean ／ 聞き取り→listen</t>
         </is>
       </c>
-      <c r="D20" s="26" t="n"/>
+      <c r="D20" s="36" t="n"/>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="29" t="inlineStr">
@@ -846,7 +4762,7 @@
           <t>漢字読み→read ／ 書き取り→write</t>
         </is>
       </c>
-      <c r="D21" s="24" t="n"/>
+      <c r="D21" s="36" t="n"/>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
@@ -864,7 +4780,7 @@
           <t>穴埋め(文法形式)・並べ替え(組み立て)・文章の文法 → すべて grammar 面へ合流</t>
         </is>
       </c>
-      <c r="D22" s="26" t="n"/>
+      <c r="D22" s="36" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
@@ -898,6 +4814,8 @@
           <t>中身</t>
         </is>
       </c>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="36" t="n"/>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="31" t="inlineStr">
@@ -910,8 +4828,8 @@
           <t>各文法点／語の習得を正答確率に変換し、本番の出題数で重み付けして180点満点で計算（selectors.ts・CLAUDE.md §4）</t>
         </is>
       </c>
-      <c r="C29" s="33" t="n"/>
-      <c r="D29" s="33" t="n"/>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="36" t="n"/>
     </row>
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="29" t="inlineStr">
@@ -924,8 +4842,8 @@
           <t>レベル内の文法点のうち、grammar面が0.6以上の点の割合＝『文法をどれだけ広く覚えたか』</t>
         </is>
       </c>
-      <c r="C30" s="33" t="n"/>
-      <c r="D30" s="33" t="n"/>
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="36" t="n"/>
     </row>
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="31" t="inlineStr">
@@ -938,8 +4856,8 @@
           <t>予想得点と同じ配点で合格の可能性を示す</t>
         </is>
       </c>
-      <c r="C31" s="33" t="n"/>
-      <c r="D31" s="33" t="n"/>
+      <c r="C31" s="35" t="n"/>
+      <c r="D31" s="36" t="n"/>
     </row>
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="29" t="inlineStr">
@@ -952,8 +4870,8 @@
           <t>弱い／期限が来たIDを選び、そのID×面に合う“検証済みバンク問題”を出す（おすすめ・ホーム・書斎・AIコーチ・カード）</t>
         </is>
       </c>
-      <c r="C32" s="33" t="n"/>
-      <c r="D32" s="33" t="n"/>
+      <c r="C32" s="35" t="n"/>
+      <c r="D32" s="36" t="n"/>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="31" t="inlineStr">
@@ -966,8 +4884,8 @@
           <t>間違えた問題のIDを、上と同じ検証済みバンク経路で復習（今回、復習と同じプールに統一）</t>
         </is>
       </c>
-      <c r="C33" s="33" t="n"/>
-      <c r="D33" s="33" t="n"/>
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="36" t="n"/>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="34" t="inlineStr">
@@ -1012,2386 +4930,1413 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>セクション</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>単語マスタと紐づけ大問（2026-08-19 集計）</t>
+        </is>
+      </c>
+      <c r="I1" s="38" t="n"/>
+    </row>
+    <row r="2">
+      <c r="I2" s="38" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>①単語マスタ数（学習項目）</t>
+        </is>
+      </c>
+      <c r="I3" s="38" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="39" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C4" s="39" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D4" s="39" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="E4" s="39" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="I4" s="38" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>語彙単語</t>
+        </is>
+      </c>
+      <c r="B5" s="40" t="n">
+        <v>723</v>
+      </c>
+      <c r="C5" s="40" t="n">
+        <v>673</v>
+      </c>
+      <c r="D5" s="40" t="n">
+        <v>2145</v>
+      </c>
+      <c r="E5" s="40" t="n">
+        <v>3541</v>
+      </c>
+      <c r="I5" s="38" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>漢字単語</t>
+        </is>
+      </c>
+      <c r="B6" s="40" t="n">
+        <v>79</v>
+      </c>
+      <c r="C6" s="40" t="n">
+        <v>166</v>
+      </c>
+      <c r="D6" s="40" t="n">
+        <v>367</v>
+      </c>
+      <c r="E6" s="40" t="n">
+        <v>612</v>
+      </c>
+      <c r="I6" s="38" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>文法単語</t>
+        </is>
+      </c>
+      <c r="B7" s="40" t="n">
+        <v>92</v>
+      </c>
+      <c r="C7" s="40" t="n">
+        <v>131</v>
+      </c>
+      <c r="D7" s="40" t="n">
+        <v>186</v>
+      </c>
+      <c r="E7" s="40" t="n">
+        <v>409</v>
+      </c>
+      <c r="I7" s="38" t="n"/>
+    </row>
+    <row r="8">
+      <c r="I8" s="38" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>②紐づく大問と問題数　総数 ／ verified在庫</t>
+        </is>
+      </c>
+      <c r="I9" s="38" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>グループ</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>大問</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>レベル</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>在庫問題数</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>セット数</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>未検証</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>本番出題数</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>模試換算(何回分)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>誤答数の内訳</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>シャッフル</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="C10" s="39" t="inlineStr">
+        <is>
+          <t>N5 総数</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="inlineStr">
+        <is>
+          <t>N5 在庫</t>
+        </is>
+      </c>
+      <c r="E10" s="39" t="inlineStr">
+        <is>
+          <t>N4 総数</t>
+        </is>
+      </c>
+      <c r="F10" s="39" t="inlineStr">
+        <is>
+          <t>N4 在庫</t>
+        </is>
+      </c>
+      <c r="G10" s="39" t="inlineStr">
+        <is>
+          <t>N3 総数</t>
+        </is>
+      </c>
+      <c r="H10" s="39" t="inlineStr">
+        <is>
+          <t>N3 在庫</t>
+        </is>
+      </c>
+      <c r="I10" s="41" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>漢字（文字）</t>
+        </is>
+      </c>
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>漢字読み</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
+      <c r="C11" s="40" t="n">
         <v>463</v>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>3:463</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>漢字読み</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
+      <c r="D11" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="40" t="n">
         <v>448</v>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>3:448</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>漢字読み</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="n">
         <v>1398</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>174</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>3:1398</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="H11" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="43" t="inlineStr">
+        <is>
+          <t>辞書から機械生成（公式作問でない＝在庫に数えない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="40" t="inlineStr"/>
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>表記</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="C12" s="40" t="n">
         <v>527</v>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>105</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>3:527</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>表記</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="D12" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="40" t="n">
         <v>492</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>3:492</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>表記</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="n">
         <v>1527</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>254</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>3:1527</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="H12" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="43" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>文脈規定</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
+      <c r="C13" s="40" t="n">
+        <v>672</v>
+      </c>
+      <c r="D13" s="40" t="n">
         <v>655</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
+      <c r="E13" s="40" t="n">
+        <v>651</v>
+      </c>
+      <c r="F13" s="40" t="n">
+        <v>651</v>
+      </c>
+      <c r="G13" s="40" t="n">
+        <v>2090</v>
+      </c>
+      <c r="H13" s="40" t="n">
+        <v>772</v>
+      </c>
+      <c r="I13" s="43" t="inlineStr">
+        <is>
+          <t>公式作問。在庫＝verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr"/>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>言い換え類義</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="n">
+        <v>148</v>
+      </c>
+      <c r="D14" s="40" t="n">
+        <v>148</v>
+      </c>
+      <c r="E14" s="40" t="n">
+        <v>185</v>
+      </c>
+      <c r="F14" s="40" t="n">
+        <v>185</v>
+      </c>
+      <c r="G14" s="40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H14" s="40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I14" s="43" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="inlineStr"/>
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t>用法</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>109</v>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>3:165 / 4:222 / 5:268</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>文脈規定</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>651</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>3:239 / 4:230 / 5:182</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>文脈規定</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>2090</v>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>1318</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>3:1382 / 4:450 / 5:258</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>言い換え類義</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>148</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>3:72 / 4:23 / 5:53</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>言い換え類義</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>185</v>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>3:1 / 4:8 / 5:45 / 6:131</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>言い換え類義</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" s="5" t="n">
+      <c r="D15" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="40" t="n">
+        <v>153</v>
+      </c>
+      <c r="F15" s="40" t="n">
+        <v>153</v>
+      </c>
+      <c r="G15" s="40" t="n">
+        <v>150</v>
+      </c>
+      <c r="H15" s="40" t="n">
+        <v>150</v>
+      </c>
+      <c r="I15" s="43" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B16" s="40" t="inlineStr">
+        <is>
+          <t>文法形式(穴埋め)</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="n">
+        <v>204</v>
+      </c>
+      <c r="D16" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="40" t="n">
+        <v>357</v>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="40" t="n">
+        <v>443</v>
+      </c>
+      <c r="H16" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="43" t="inlineStr">
+        <is>
+          <t>穴埋め/並べ替えは在庫を文法点×cloze可で管理。文章の文法は全数在庫</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="inlineStr"/>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>語の並べ替え</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="n">
+        <v>137</v>
+      </c>
+      <c r="D17" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="40" t="n">
+        <v>214</v>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="n">
+        <v>308</v>
+      </c>
+      <c r="H17" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="43" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="inlineStr"/>
+      <c r="B18" s="40" t="inlineStr">
+        <is>
+          <t>文章の文法</t>
+        </is>
+      </c>
+      <c r="C18" s="40" t="n">
+        <v>400</v>
+      </c>
+      <c r="D18" s="40" t="n">
+        <v>400</v>
+      </c>
+      <c r="E18" s="40" t="n">
+        <v>400</v>
+      </c>
+      <c r="F18" s="40" t="n">
+        <v>400</v>
+      </c>
+      <c r="G18" s="40" t="n">
         <v>200</v>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>3:3 / 4:16 / 5:106 / 6:875</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>用法</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>153</v>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>3:42 / 4:37 / 5:40 / 6:34</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>用法</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>3:46 / 4:44 / 5:39 / 6:21</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>文法形式</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>204</v>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>3:203 / 4:1</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>文法形式</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>357</v>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>3:357</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>文法形式</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>443</v>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>3:441 / 4:2</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>組み立て</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>137</v>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>3:137</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>組み立て</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>214</v>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>3:214</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>組み立て</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>308</v>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>3:308</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>文章の文法</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>3:400</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>文章の文法</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>3:400</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>文章の文法</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n">
+      <c r="H18" s="40" t="n">
         <v>200</v>
       </c>
-      <c r="E24" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>3:200</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>内容理解(短文)</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>3:55</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>内容理解(短文)</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H26" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>3:55</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>内容理解(短文)</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>3:55</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>内容理解(中文)</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>3:54</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>内容理解(中文)</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>3:100</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>内容理解(中文)</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H30" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>3:81</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>内容理解(長文)</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>3:84</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>情報検索</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>3:110</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>情報検索</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>3:140</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>情報検索</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>155</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>155</v>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>3:155</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>課題理解</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>3:150</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>課題理解</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>3:150</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>課題理解</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>3:150</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>ポイント理解</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>3:104</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>ポイント理解</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H39" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>3:100</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>ポイント理解</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>3:100</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>概要理解</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>3:80</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>発話表現</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>2:200</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>発話表現</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>2:200</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>発話表現</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>2:200</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>即時応答</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>2:240</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>即時応答</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>2:240</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>即時応答</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>2:240</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
+      <c r="I18" s="43" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>◆ 模試換算 = 在庫 ÷ 本番出題数 = その大問だけで組めるフル模試の回数（floor）</t>
-        </is>
-      </c>
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>単語×大問 カバー率（2026-08-19・vocabId/pointId実リンク集計）</t>
+        </is>
+      </c>
+      <c r="G1" s="38" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>※用法は場面/例文単位でvocabId無し＝語カバー測定不可。漢字カバーは語(vocabId)の漢字から導出。</t>
+        </is>
+      </c>
+      <c r="G2" s="38" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>セクション別 律速（そのセクションで最も少ない大問の回数＝そのセクションを何回組めるか）</t>
-        </is>
-      </c>
+      <c r="G3" s="38" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>セクション</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
+      <c r="A4" s="45" t="inlineStr">
+        <is>
+          <t>■ N5</t>
+        </is>
+      </c>
+      <c r="G4" s="38" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>49</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>30</v>
+      <c r="A5" s="46" t="inlineStr">
+        <is>
+          <t>単語種別</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="inlineStr">
+        <is>
+          <t>大問</t>
+        </is>
+      </c>
+      <c r="C5" s="46" t="inlineStr">
+        <is>
+          <t>問題数</t>
+        </is>
+      </c>
+      <c r="D5" s="46" t="inlineStr">
+        <is>
+          <t>カバー数</t>
+        </is>
+      </c>
+      <c r="E5" s="46" t="inlineStr">
+        <is>
+          <t>母数</t>
+        </is>
+      </c>
+      <c r="F5" s="46" t="inlineStr">
+        <is>
+          <t>カバー率</t>
+        </is>
+      </c>
+      <c r="G5" s="47" t="inlineStr">
+        <is>
+          <t>1単語が紐づく大問数の分布</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>23</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>34</v>
+      <c r="A6" s="48" t="inlineStr">
+        <is>
+          <t>語彙単語(723)</t>
+        </is>
+      </c>
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>漢字読み</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="n">
+        <v>463</v>
+      </c>
+      <c r="D6" s="40" t="n">
+        <v>463</v>
+      </c>
+      <c r="E6" s="40" t="n">
+        <v>563</v>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="G6" s="43" t="inlineStr">
+        <is>
+          <t>0:46／1:121／2:90／3:355／4:111</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>13</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>13</v>
-      </c>
+      <c r="A7" s="40" t="inlineStr"/>
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="n">
+        <v>527</v>
+      </c>
+      <c r="D7" s="40" t="n">
+        <v>527</v>
+      </c>
+      <c r="E7" s="40" t="n">
+        <v>563</v>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="G7" s="43" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>14</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <v>16</v>
-      </c>
+      <c r="A8" s="40" t="inlineStr"/>
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t>文脈規定</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="n">
+        <v>672</v>
+      </c>
+      <c r="D8" s="40" t="n">
+        <v>672</v>
+      </c>
+      <c r="E8" s="40" t="n">
+        <v>723</v>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="G8" s="43" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="40" t="inlineStr"/>
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>言い換え類義</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="n">
+        <v>148</v>
+      </c>
+      <c r="D9" s="40" t="n">
+        <v>148</v>
+      </c>
+      <c r="E9" s="40" t="n">
+        <v>723</v>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G9" s="43" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>級ごとの「フル模試」完成可能回数（全大問の最小＝律速大問で決まる）</t>
-        </is>
-      </c>
+      <c r="A10" s="40" t="inlineStr"/>
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>用法</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="D10" s="40" t="inlineStr"/>
+      <c r="E10" s="40" t="inlineStr"/>
+      <c r="F10" s="40" t="inlineStr"/>
+      <c r="G10" s="43" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>セクション</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>N3</t>
+      <c r="A11" s="48" t="inlineStr">
+        <is>
+          <t>漢字単語(79)</t>
+        </is>
+      </c>
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>漢字読み</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="n">
+        <v>463</v>
+      </c>
+      <c r="D11" s="40" t="n">
+        <v>77</v>
+      </c>
+      <c r="E11" s="40" t="n">
+        <v>79</v>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="G11" s="43" t="inlineStr">
+        <is>
+          <t>0:2／1:0／2:77</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>フル模試</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>13</v>
+      <c r="A12" s="40" t="inlineStr"/>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="n">
+        <v>527</v>
+      </c>
+      <c r="D12" s="40" t="n">
+        <v>77</v>
+      </c>
+      <c r="E12" s="40" t="n">
+        <v>79</v>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="G12" s="43" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="48" t="inlineStr">
+        <is>
+          <t>文法単語(92)</t>
+        </is>
+      </c>
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>文法形式(穴埋め)</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="n">
+        <v>204</v>
+      </c>
+      <c r="D13" s="40" t="n">
+        <v>82</v>
+      </c>
+      <c r="E13" s="40" t="n">
+        <v>92</v>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="G13" s="43" t="inlineStr">
+        <is>
+          <t>0:2／1:14／2:41／3:35</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>凡例：赤=5回以下(不足) / 橙=15回以下(要増産) / 緑=16回以上(十分)</t>
-        </is>
-      </c>
+      <c r="A14" s="40" t="inlineStr"/>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>語の並べ替え</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="n">
+        <v>137</v>
+      </c>
+      <c r="D14" s="40" t="n">
+        <v>66</v>
+      </c>
+      <c r="E14" s="40" t="n">
+        <v>92</v>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="G14" s="43" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="inlineStr"/>
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t>文章の文法</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="n">
+        <v>400</v>
+      </c>
+      <c r="D15" s="40" t="n">
+        <v>53</v>
+      </c>
+      <c r="E15" s="40" t="n">
+        <v>92</v>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="G15" s="43" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="G16" s="38" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="45" t="inlineStr">
+        <is>
+          <t>■ N4</t>
+        </is>
+      </c>
+      <c r="G17" s="38" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="46" t="inlineStr">
+        <is>
+          <t>単語種別</t>
+        </is>
+      </c>
+      <c r="B18" s="46" t="inlineStr">
+        <is>
+          <t>大問</t>
+        </is>
+      </c>
+      <c r="C18" s="46" t="inlineStr">
+        <is>
+          <t>問題数</t>
+        </is>
+      </c>
+      <c r="D18" s="46" t="inlineStr">
+        <is>
+          <t>カバー数</t>
+        </is>
+      </c>
+      <c r="E18" s="46" t="inlineStr">
+        <is>
+          <t>母数</t>
+        </is>
+      </c>
+      <c r="F18" s="46" t="inlineStr">
+        <is>
+          <t>カバー率</t>
+        </is>
+      </c>
+      <c r="G18" s="47" t="inlineStr">
+        <is>
+          <t>1単語が紐づく大問数の分布</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t>語彙単語(673)</t>
+        </is>
+      </c>
+      <c r="B19" s="40" t="inlineStr">
+        <is>
+          <t>漢字読み</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="n">
+        <v>448</v>
+      </c>
+      <c r="D19" s="40" t="n">
+        <v>448</v>
+      </c>
+      <c r="E19" s="40" t="n">
+        <v>542</v>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="G19" s="43" t="inlineStr">
+        <is>
+          <t>0:16／1:113／2:95／3:323／4:126</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="inlineStr"/>
+      <c r="B20" s="40" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="C20" s="40" t="n">
+        <v>492</v>
+      </c>
+      <c r="D20" s="40" t="n">
+        <v>492</v>
+      </c>
+      <c r="E20" s="40" t="n">
+        <v>542</v>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="G20" s="43" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="40" t="inlineStr"/>
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t>文脈規定</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="n">
+        <v>651</v>
+      </c>
+      <c r="D21" s="40" t="n">
+        <v>651</v>
+      </c>
+      <c r="E21" s="40" t="n">
+        <v>673</v>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="G21" s="43" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="40" t="inlineStr"/>
+      <c r="B22" s="40" t="inlineStr">
+        <is>
+          <t>言い換え類義</t>
+        </is>
+      </c>
+      <c r="C22" s="40" t="n">
+        <v>185</v>
+      </c>
+      <c r="D22" s="40" t="n">
+        <v>185</v>
+      </c>
+      <c r="E22" s="40" t="n">
+        <v>673</v>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="G22" s="43" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="inlineStr"/>
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <t>用法</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="n">
+        <v>153</v>
+      </c>
+      <c r="D23" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="43" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>漢字単語(166)</t>
+        </is>
+      </c>
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t>漢字読み</t>
+        </is>
+      </c>
+      <c r="C24" s="40" t="n">
+        <v>448</v>
+      </c>
+      <c r="D24" s="40" t="n">
+        <v>103</v>
+      </c>
+      <c r="E24" s="40" t="n">
+        <v>166</v>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="G24" s="43" t="inlineStr">
+        <is>
+          <t>0:63／1:0／2:103</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="40" t="inlineStr"/>
+      <c r="B25" s="40" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="C25" s="40" t="n">
+        <v>492</v>
+      </c>
+      <c r="D25" s="40" t="n">
+        <v>103</v>
+      </c>
+      <c r="E25" s="40" t="n">
+        <v>166</v>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="G25" s="43" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="48" t="inlineStr">
+        <is>
+          <t>文法単語(131)</t>
+        </is>
+      </c>
+      <c r="B26" s="40" t="inlineStr">
+        <is>
+          <t>文法形式(穴埋め)</t>
+        </is>
+      </c>
+      <c r="C26" s="40" t="n">
+        <v>357</v>
+      </c>
+      <c r="D26" s="40" t="n">
+        <v>125</v>
+      </c>
+      <c r="E26" s="40" t="n">
+        <v>131</v>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="G26" s="43" t="inlineStr">
+        <is>
+          <t>0:0／1:16／2:75／3:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="40" t="inlineStr"/>
+      <c r="B27" s="40" t="inlineStr">
+        <is>
+          <t>語の並べ替え</t>
+        </is>
+      </c>
+      <c r="C27" s="40" t="n">
+        <v>214</v>
+      </c>
+      <c r="D27" s="40" t="n">
+        <v>111</v>
+      </c>
+      <c r="E27" s="40" t="n">
+        <v>131</v>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="G27" s="43" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="40" t="inlineStr"/>
+      <c r="B28" s="40" t="inlineStr">
+        <is>
+          <t>文章の文法</t>
+        </is>
+      </c>
+      <c r="C28" s="40" t="n">
+        <v>400</v>
+      </c>
+      <c r="D28" s="40" t="n">
+        <v>50</v>
+      </c>
+      <c r="E28" s="40" t="n">
+        <v>131</v>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="G28" s="43" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="G29" s="38" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="inlineStr">
+        <is>
+          <t>■ N3</t>
+        </is>
+      </c>
+      <c r="G30" s="38" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="46" t="inlineStr">
+        <is>
+          <t>単語種別</t>
+        </is>
+      </c>
+      <c r="B31" s="46" t="inlineStr">
+        <is>
+          <t>大問</t>
+        </is>
+      </c>
+      <c r="C31" s="46" t="inlineStr">
+        <is>
+          <t>問題数</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="inlineStr">
+        <is>
+          <t>カバー数</t>
+        </is>
+      </c>
+      <c r="E31" s="46" t="inlineStr">
+        <is>
+          <t>母数</t>
+        </is>
+      </c>
+      <c r="F31" s="46" t="inlineStr">
+        <is>
+          <t>カバー率</t>
+        </is>
+      </c>
+      <c r="G31" s="47" t="inlineStr">
+        <is>
+          <t>1単語が紐づく大問数の分布</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="48" t="inlineStr">
+        <is>
+          <t>語彙単語(2145)</t>
+        </is>
+      </c>
+      <c r="B32" s="40" t="inlineStr">
+        <is>
+          <t>漢字読み</t>
+        </is>
+      </c>
+      <c r="C32" s="40" t="n">
+        <v>1398</v>
+      </c>
+      <c r="D32" s="40" t="n">
+        <v>1398</v>
+      </c>
+      <c r="E32" s="40" t="n">
+        <v>1896</v>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="G32" s="43" t="inlineStr">
+        <is>
+          <t>0:42／1:321／2:357／3:720／4:705</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="40" t="inlineStr"/>
+      <c r="B33" s="40" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="C33" s="40" t="n">
+        <v>1527</v>
+      </c>
+      <c r="D33" s="40" t="n">
+        <v>1527</v>
+      </c>
+      <c r="E33" s="40" t="n">
+        <v>1896</v>
+      </c>
+      <c r="F33" s="40" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G33" s="43" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="40" t="inlineStr"/>
+      <c r="B34" s="40" t="inlineStr">
+        <is>
+          <t>文脈規定</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="n">
+        <v>2090</v>
+      </c>
+      <c r="D34" s="40" t="n">
+        <v>2090</v>
+      </c>
+      <c r="E34" s="40" t="n">
+        <v>2145</v>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="G34" s="43" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="40" t="inlineStr"/>
+      <c r="B35" s="40" t="inlineStr">
+        <is>
+          <t>言い換え類義</t>
+        </is>
+      </c>
+      <c r="C35" s="40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D35" s="40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E35" s="40" t="n">
+        <v>2145</v>
+      </c>
+      <c r="F35" s="40" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="G35" s="43" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="40" t="inlineStr"/>
+      <c r="B36" s="40" t="inlineStr">
+        <is>
+          <t>用法</t>
+        </is>
+      </c>
+      <c r="C36" s="40" t="n">
+        <v>150</v>
+      </c>
+      <c r="D36" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="43" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="48" t="inlineStr">
+        <is>
+          <t>漢字単語(367)</t>
+        </is>
+      </c>
+      <c r="B37" s="40" t="inlineStr">
+        <is>
+          <t>漢字読み</t>
+        </is>
+      </c>
+      <c r="C37" s="40" t="n">
+        <v>1398</v>
+      </c>
+      <c r="D37" s="40" t="n">
+        <v>312</v>
+      </c>
+      <c r="E37" s="40" t="n">
+        <v>367</v>
+      </c>
+      <c r="F37" s="40" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="G37" s="43" t="inlineStr">
+        <is>
+          <t>0:55／1:0／2:312</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="40" t="inlineStr"/>
+      <c r="B38" s="40" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="C38" s="40" t="n">
+        <v>1527</v>
+      </c>
+      <c r="D38" s="40" t="n">
+        <v>312</v>
+      </c>
+      <c r="E38" s="40" t="n">
+        <v>367</v>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="G38" s="43" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="48" t="inlineStr">
+        <is>
+          <t>文法単語(186)</t>
+        </is>
+      </c>
+      <c r="B39" s="40" t="inlineStr">
+        <is>
+          <t>文法形式(穴埋め)</t>
+        </is>
+      </c>
+      <c r="C39" s="40" t="n">
+        <v>443</v>
+      </c>
+      <c r="D39" s="40" t="n">
+        <v>177</v>
+      </c>
+      <c r="E39" s="40" t="n">
+        <v>186</v>
+      </c>
+      <c r="F39" s="40" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="G39" s="43" t="inlineStr">
+        <is>
+          <t>0:1／1:36／2:142／3:7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="40" t="inlineStr"/>
+      <c r="B40" s="40" t="inlineStr">
+        <is>
+          <t>語の並べ替え</t>
+        </is>
+      </c>
+      <c r="C40" s="40" t="n">
+        <v>308</v>
+      </c>
+      <c r="D40" s="40" t="n">
+        <v>157</v>
+      </c>
+      <c r="E40" s="40" t="n">
+        <v>186</v>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="G40" s="43" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="40" t="inlineStr"/>
+      <c r="B41" s="40" t="inlineStr">
+        <is>
+          <t>文章の文法</t>
+        </is>
+      </c>
+      <c r="C41" s="40" t="n">
+        <v>200</v>
+      </c>
+      <c r="D41" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" s="40" t="n">
+        <v>186</v>
+      </c>
+      <c r="F41" s="40" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G41" s="43" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="G42" s="38" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>◆ 参考データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>在庫 合計</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>15593</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>問</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>在庫外（監査に落ちた分・在庫に数えない）</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>問</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>辞書にある全単語数（問題化の母数）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>辞書</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>内訳</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4534,7 +7479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -103,7 +103,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -193,6 +193,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C55A11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6C9C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -294,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -455,6 +460,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -820,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1939,10 +1950,10 @@
           <t>N5</t>
         </is>
       </c>
-      <c r="D25" s="60" t="n">
+      <c r="D25" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="E25" s="60" t="n">
+      <c r="E25" s="4" t="n">
         <v>90</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1953,10 +1964,10 @@
       <c r="G25" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="61" t="n">
+      <c r="H25" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="I25" s="62" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>3:90</t>
         </is>
@@ -1983,10 +1994,10 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="D26" s="60" t="n">
+      <c r="D26" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="E26" s="60" t="n">
+      <c r="E26" s="4" t="n">
         <v>120</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1997,10 +2008,10 @@
       <c r="G26" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H26" s="61" t="n">
+      <c r="H26" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="I26" s="62" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>3:120</t>
         </is>
@@ -2027,10 +2038,10 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="D27" s="60" t="n">
+      <c r="D27" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="E27" s="60" t="n">
+      <c r="E27" s="4" t="n">
         <v>120</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2041,10 +2052,10 @@
       <c r="G27" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H27" s="61" t="n">
+      <c r="H27" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="I27" s="62" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>3:120</t>
         </is>
@@ -2071,10 +2082,10 @@
           <t>N5</t>
         </is>
       </c>
-      <c r="D28" s="60" t="n">
+      <c r="D28" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="E28" s="60" t="n">
+      <c r="E28" s="4" t="n">
         <v>40</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -2085,10 +2096,10 @@
       <c r="G28" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="61" t="n">
+      <c r="H28" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="I28" s="62" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>3:80</t>
         </is>
@@ -2115,10 +2126,10 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="D29" s="60" t="n">
+      <c r="D29" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="E29" s="60" t="n">
+      <c r="E29" s="4" t="n">
         <v>40</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2129,10 +2140,10 @@
       <c r="G29" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H29" s="61" t="n">
+      <c r="H29" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="I29" s="62" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>3:160</t>
         </is>
@@ -2159,10 +2170,10 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="D30" s="60" t="n">
+      <c r="D30" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="E30" s="60" t="n">
+      <c r="E30" s="4" t="n">
         <v>80</v>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2173,10 +2184,10 @@
       <c r="G30" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H30" s="61" t="n">
+      <c r="H30" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="I30" s="62" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>3:240</t>
         </is>
@@ -2203,10 +2214,10 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="D31" s="60" t="n">
+      <c r="D31" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="E31" s="60" t="n">
+      <c r="E31" s="4" t="n">
         <v>40</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2217,10 +2228,10 @@
       <c r="G31" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H31" s="61" t="n">
+      <c r="H31" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="I31" s="62" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>3:160</t>
         </is>
@@ -2248,10 +2259,10 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
@@ -2262,11 +2273,11 @@
         <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>3:110</t>
+          <t>3:60</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2292,10 +2303,10 @@
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
@@ -2306,11 +2317,11 @@
         <v>2</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>3:140</t>
+          <t>3:60</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2336,10 +2347,10 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
@@ -2350,11 +2361,11 @@
         <v>2</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>3:155</t>
+          <t>3:60</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2932,13 +2943,6 @@
       <c r="J47" s="4" t="inlineStr">
         <is>
           <t>なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="63" t="inlineStr">
-        <is>
-          <t>※2026-08-20 読解の新規217本(短N4+65/短N3+65/中N4+15/中N3+53/長N3+19)を在庫に反映(黄セル)。本体JSONへはネパール語訳後に適用予定(番人green)。</t>
         </is>
       </c>
     </row>
@@ -3037,13 +3041,13 @@
           <t>読解</t>
         </is>
       </c>
-      <c r="B7" s="60" t="n">
+      <c r="B7" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="C7" s="60" t="n">
+      <c r="C7" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="D7" s="60" t="n">
+      <c r="D7" s="13" t="n">
         <v>30</v>
       </c>
     </row>
@@ -3098,13 +3102,13 @@
           <t>フル模試</t>
         </is>
       </c>
-      <c r="B12" s="61" t="n">
+      <c r="B12" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="C12" s="61" t="n">
+      <c r="C12" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D12" s="61" t="n">
+      <c r="D12" s="5" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3148,7 +3152,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15739</v>
+        <v>16000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3177,6 +3181,8 @@
           <t>辞書にある全単語数（問題化の母数）</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -103,7 +103,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -198,6 +198,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F6C9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -299,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -466,6 +471,32 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3181,8 +3212,6 @@
           <t>辞書にある全単語数（問題化の母数）</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -3212,7 +3241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3239,10 +3268,11 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="53" t="inlineStr">
         <is>
-          <t>①内容理解（短/中/長）　現行＝本体JSON／適用後見込み＝新規217本を合流した姿（黄・番人green・ne訳後に適用予定）</t>
+          <t>①内容理解（短/中/長）　本体JSONの現在値（旧「現行」比較行は削除済み）</t>
         </is>
       </c>
     </row>
@@ -3324,75 +3354,75 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="55" t="inlineStr">
+      <c r="A5" s="56" t="inlineStr">
         <is>
           <t>内容理解短</t>
         </is>
       </c>
-      <c r="B5" s="55" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="C5" s="55" t="inlineStr">
-        <is>
-          <t>現行</t>
-        </is>
-      </c>
-      <c r="D5" s="55" t="n">
-        <v>55</v>
-      </c>
-      <c r="E5" s="55" t="n">
-        <v>55</v>
-      </c>
-      <c r="F5" s="55" t="inlineStr">
+      <c r="C5" s="56" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="D5" s="56" t="n">
+        <v>90</v>
+      </c>
+      <c r="E5" s="56" t="n">
+        <v>90</v>
+      </c>
+      <c r="F5" s="56" t="inlineStr">
         <is>
           <t>1.0(1)</t>
         </is>
       </c>
-      <c r="G5" s="55" t="inlineStr">
-        <is>
-          <t>70(60/80)</t>
-        </is>
-      </c>
-      <c r="H5" s="55" t="inlineStr">
+      <c r="G5" s="56" t="inlineStr">
+        <is>
+          <t>70(53/80)</t>
+        </is>
+      </c>
+      <c r="H5" s="56" t="inlineStr">
         <is>
           <t>80[48-120]</t>
         </is>
       </c>
-      <c r="I5" s="55" t="inlineStr">
+      <c r="I5" s="67" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="J5" s="55" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="K5" s="55" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L5" s="55" t="inlineStr">
-        <is>
-          <t>29%</t>
-        </is>
-      </c>
-      <c r="M5" s="55" t="inlineStr">
-        <is>
-          <t>0/55</t>
-        </is>
-      </c>
-      <c r="N5" s="55" t="inlineStr">
+      <c r="J5" s="67" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K5" s="67" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="L5" s="67" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="M5" s="56" t="inlineStr">
+        <is>
+          <t>0/90</t>
+        </is>
+      </c>
+      <c r="N5" s="56" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="O5" s="55" t="inlineStr">
-        <is>
-          <t>その他27 条件照合24 理由4</t>
+      <c r="O5" s="56" t="inlineStr">
+        <is>
+          <t>その他49 条件照合31 理由7 行動2 主張主旨1</t>
         </is>
       </c>
     </row>
@@ -3404,19 +3434,19 @@
       </c>
       <c r="B6" s="56" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N4</t>
         </is>
       </c>
       <c r="C6" s="56" t="inlineStr">
         <is>
-          <t>適用後(+35)</t>
+          <t>最新</t>
         </is>
       </c>
       <c r="D6" s="56" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E6" s="56" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="F6" s="56" t="inlineStr">
         <is>
@@ -3425,273 +3455,273 @@
       </c>
       <c r="G6" s="56" t="inlineStr">
         <is>
-          <t>70(53/80)</t>
+          <t>113(87/138)</t>
         </is>
       </c>
       <c r="H6" s="56" t="inlineStr">
         <is>
-          <t>80[48-120]</t>
-        </is>
-      </c>
-      <c r="I6" s="56" t="inlineStr">
+          <t>150[90-225]</t>
+        </is>
+      </c>
+      <c r="I6" s="68" t="inlineStr">
+        <is>
+          <t>2/0</t>
+        </is>
+      </c>
+      <c r="J6" s="67" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K6" s="67" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="L6" s="67" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="M6" s="56" t="inlineStr">
+        <is>
+          <t>0/120</t>
+        </is>
+      </c>
+      <c r="N6" s="56" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="O6" s="56" t="inlineStr">
+        <is>
+          <t>その他62 条件照合26 行動17 理由9 主張主旨6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="56" t="inlineStr">
+        <is>
+          <t>内容理解短</t>
+        </is>
+      </c>
+      <c r="B7" s="56" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C7" s="56" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="D7" s="56" t="n">
+        <v>120</v>
+      </c>
+      <c r="E7" s="56" t="n">
+        <v>120</v>
+      </c>
+      <c r="F7" s="56" t="inlineStr">
+        <is>
+          <t>1.0(1)</t>
+        </is>
+      </c>
+      <c r="G7" s="56" t="inlineStr">
+        <is>
+          <t>152(118/191)</t>
+        </is>
+      </c>
+      <c r="H7" s="56" t="inlineStr">
+        <is>
+          <t>175[105-262]</t>
+        </is>
+      </c>
+      <c r="I7" s="67" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="J6" s="56" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="K6" s="56" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
-      </c>
-      <c r="L6" s="56" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="M6" s="56" t="inlineStr">
-        <is>
-          <t>0/90</t>
-        </is>
-      </c>
-      <c r="N6" s="56" t="inlineStr">
+      <c r="J7" s="67" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="O6" s="56" t="inlineStr">
-        <is>
-          <t>その他49 条件照合31 理由7 行動2 主張主旨1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="55" t="inlineStr">
-        <is>
-          <t>内容理解短</t>
-        </is>
-      </c>
-      <c r="B7" s="55" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="C7" s="55" t="inlineStr">
-        <is>
-          <t>現行</t>
-        </is>
-      </c>
-      <c r="D7" s="55" t="n">
-        <v>55</v>
-      </c>
-      <c r="E7" s="55" t="n">
-        <v>55</v>
-      </c>
-      <c r="F7" s="55" t="inlineStr">
-        <is>
-          <t>1.0(1)</t>
-        </is>
-      </c>
-      <c r="G7" s="55" t="inlineStr">
-        <is>
-          <t>101(87/114)</t>
-        </is>
-      </c>
-      <c r="H7" s="55" t="inlineStr">
-        <is>
-          <t>150[90-225]</t>
-        </is>
-      </c>
-      <c r="I7" s="55" t="inlineStr">
-        <is>
-          <t>2/0</t>
-        </is>
-      </c>
-      <c r="J7" s="55" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="K7" s="55" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="L7" s="55" t="inlineStr">
-        <is>
-          <t>34%</t>
-        </is>
-      </c>
-      <c r="M7" s="55" t="inlineStr">
-        <is>
-          <t>0/55</t>
-        </is>
-      </c>
-      <c r="N7" s="55" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="O7" s="55" t="inlineStr">
-        <is>
-          <t>その他21 条件照合14 行動10 理由6 主張主旨4</t>
+      <c r="K7" s="67" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="L7" s="67" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="M7" s="56" t="inlineStr">
+        <is>
+          <t>6/120</t>
+        </is>
+      </c>
+      <c r="N7" s="56" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="O7" s="56" t="inlineStr">
+        <is>
+          <t>その他43 主張主旨25 理由20 条件照合17 行動8 指示語7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="56" t="inlineStr">
         <is>
-          <t>内容理解短</t>
+          <t>内容理解中</t>
         </is>
       </c>
       <c r="B8" s="56" t="inlineStr">
         <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C8" s="56" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="D8" s="56" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" s="56" t="n">
+        <v>80</v>
+      </c>
+      <c r="F8" s="56" t="inlineStr">
+        <is>
+          <t>2.0(2)</t>
+        </is>
+      </c>
+      <c r="G8" s="56" t="inlineStr">
+        <is>
+          <t>215(163/235)</t>
+        </is>
+      </c>
+      <c r="H8" s="56" t="inlineStr">
+        <is>
+          <t>250[150-375]</t>
+        </is>
+      </c>
+      <c r="I8" s="67" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J8" s="67" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K8" s="67" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="L8" s="67" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M8" s="56" t="inlineStr">
+        <is>
+          <t>17/40</t>
+        </is>
+      </c>
+      <c r="N8" s="58" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="O8" s="56" t="inlineStr">
+        <is>
+          <t>指示語40 その他31 理由6 条件照合3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="56" t="inlineStr">
+        <is>
+          <t>内容理解中</t>
+        </is>
+      </c>
+      <c r="B9" s="56" t="inlineStr">
+        <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="C8" s="56" t="inlineStr">
-        <is>
-          <t>適用後(+65)</t>
-        </is>
-      </c>
-      <c r="D8" s="56" t="n">
-        <v>120</v>
-      </c>
-      <c r="E8" s="56" t="n">
-        <v>120</v>
-      </c>
-      <c r="F8" s="56" t="inlineStr">
-        <is>
-          <t>1.0(1)</t>
-        </is>
-      </c>
-      <c r="G8" s="56" t="inlineStr">
-        <is>
-          <t>113(87/138)</t>
-        </is>
-      </c>
-      <c r="H8" s="56" t="inlineStr">
-        <is>
-          <t>150[90-225]</t>
-        </is>
-      </c>
-      <c r="I8" s="56" t="inlineStr">
-        <is>
-          <t>2/0</t>
-        </is>
-      </c>
-      <c r="J8" s="56" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="K8" s="56" t="inlineStr">
-        <is>
-          <t>21%</t>
-        </is>
-      </c>
-      <c r="L8" s="56" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="M8" s="56" t="inlineStr">
-        <is>
-          <t>0/120</t>
-        </is>
-      </c>
-      <c r="N8" s="56" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="O8" s="56" t="inlineStr">
-        <is>
-          <t>その他62 条件照合26 行動17 理由9 主張主旨6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="55" t="inlineStr">
-        <is>
-          <t>内容理解短</t>
-        </is>
-      </c>
-      <c r="B9" s="55" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="C9" s="55" t="inlineStr">
-        <is>
-          <t>現行</t>
-        </is>
-      </c>
-      <c r="D9" s="55" t="n">
-        <v>55</v>
-      </c>
-      <c r="E9" s="55" t="n">
-        <v>55</v>
-      </c>
-      <c r="F9" s="55" t="inlineStr">
-        <is>
-          <t>1.0(1)</t>
-        </is>
-      </c>
-      <c r="G9" s="55" t="inlineStr">
-        <is>
-          <t>133(118/151)</t>
-        </is>
-      </c>
-      <c r="H9" s="55" t="inlineStr">
-        <is>
-          <t>175[105-262]</t>
-        </is>
-      </c>
-      <c r="I9" s="55" t="inlineStr">
+      <c r="C9" s="56" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="D9" s="56" t="n">
+        <v>40</v>
+      </c>
+      <c r="E9" s="56" t="n">
+        <v>160</v>
+      </c>
+      <c r="F9" s="56" t="inlineStr">
+        <is>
+          <t>4.0(4)</t>
+        </is>
+      </c>
+      <c r="G9" s="56" t="inlineStr">
+        <is>
+          <t>348(322/476)</t>
+        </is>
+      </c>
+      <c r="H9" s="56" t="inlineStr">
+        <is>
+          <t>450[270-675]</t>
+        </is>
+      </c>
+      <c r="I9" s="67" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="J9" s="55" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K9" s="55" t="inlineStr">
+      <c r="J9" s="67" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K9" s="67" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="L9" s="67" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="M9" s="56" t="inlineStr">
+        <is>
+          <t>7/40</t>
+        </is>
+      </c>
+      <c r="N9" s="58" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
       </c>
-      <c r="L9" s="55" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="M9" s="55" t="inlineStr">
-        <is>
-          <t>0/55</t>
-        </is>
-      </c>
-      <c r="N9" s="55" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="O9" s="55" t="inlineStr">
-        <is>
-          <t>主張主旨17 その他15 理由14 条件照合6 行動3</t>
+      <c r="O9" s="56" t="inlineStr">
+        <is>
+          <t>その他71 指示語40 理由26 条件照合14 主張主旨5 行動4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="56" t="inlineStr">
         <is>
-          <t>内容理解短</t>
+          <t>内容理解中</t>
         </is>
       </c>
       <c r="B10" s="56" t="inlineStr">
@@ -3701,851 +3731,353 @@
       </c>
       <c r="C10" s="56" t="inlineStr">
         <is>
-          <t>適用後(+65)</t>
+          <t>最新</t>
         </is>
       </c>
       <c r="D10" s="56" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="E10" s="56" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="F10" s="56" t="inlineStr">
         <is>
-          <t>1.0(1)</t>
+          <t>3.0(3)</t>
         </is>
       </c>
       <c r="G10" s="56" t="inlineStr">
         <is>
-          <t>152(118/191)</t>
+          <t>312(277/436)</t>
         </is>
       </c>
       <c r="H10" s="56" t="inlineStr">
         <is>
-          <t>175[105-262]</t>
-        </is>
-      </c>
-      <c r="I10" s="56" t="inlineStr">
+          <t>350[210-525]</t>
+        </is>
+      </c>
+      <c r="I10" s="67" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="J10" s="56" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K10" s="56" t="inlineStr">
+      <c r="J10" s="67" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="K10" s="67" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="L10" s="67" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="M10" s="56" t="inlineStr">
+        <is>
+          <t>23/80</t>
+        </is>
+      </c>
+      <c r="N10" s="58" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="O10" s="56" t="inlineStr">
+        <is>
+          <t>指示語80 主張主旨62 条件照合62 理由26 その他10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="56" t="inlineStr">
+        <is>
+          <t>内容理解長</t>
+        </is>
+      </c>
+      <c r="B11" s="56" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C11" s="56" t="inlineStr">
+        <is>
+          <t>最新</t>
+        </is>
+      </c>
+      <c r="D11" s="56" t="n">
+        <v>40</v>
+      </c>
+      <c r="E11" s="56" t="n">
+        <v>160</v>
+      </c>
+      <c r="F11" s="56" t="inlineStr">
+        <is>
+          <t>4.0(4)</t>
+        </is>
+      </c>
+      <c r="G11" s="56" t="inlineStr">
+        <is>
+          <t>543(441/579)</t>
+        </is>
+      </c>
+      <c r="H11" s="56" t="inlineStr">
+        <is>
+          <t>550[330-825]</t>
+        </is>
+      </c>
+      <c r="I11" s="67" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J11" s="67" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K11" s="67" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="L10" s="56" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="M10" s="56" t="inlineStr">
-        <is>
-          <t>7/120</t>
-        </is>
-      </c>
-      <c r="N10" s="56" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="O10" s="56" t="inlineStr">
-        <is>
-          <t>その他43 主張主旨25 理由20 条件照合17 行動8 指示語7</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="55" t="inlineStr">
-        <is>
-          <t>内容理解中</t>
-        </is>
-      </c>
-      <c r="B11" s="55" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="C11" s="55" t="inlineStr">
-        <is>
-          <t>現行</t>
-        </is>
-      </c>
-      <c r="D11" s="55" t="n">
-        <v>27</v>
-      </c>
-      <c r="E11" s="55" t="n">
-        <v>54</v>
-      </c>
-      <c r="F11" s="55" t="inlineStr">
-        <is>
-          <t>2.0(2)</t>
-        </is>
-      </c>
-      <c r="G11" s="55" t="inlineStr">
-        <is>
-          <t>221(172/235)</t>
-        </is>
-      </c>
-      <c r="H11" s="55" t="inlineStr">
-        <is>
-          <t>250[150-375]</t>
-        </is>
-      </c>
-      <c r="I11" s="55" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="J11" s="55" t="inlineStr">
-        <is>
-          <t>16%</t>
-        </is>
-      </c>
-      <c r="K11" s="55" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="L11" s="55" t="inlineStr">
-        <is>
-          <t>24%</t>
-        </is>
-      </c>
-      <c r="M11" s="55" t="inlineStr">
-        <is>
-          <t>27/27</t>
-        </is>
-      </c>
-      <c r="N11" s="57" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O11" s="55" t="inlineStr">
-        <is>
-          <t>指示語27 その他20 理由5 条件照合2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="56" t="inlineStr">
-        <is>
-          <t>内容理解中</t>
-        </is>
-      </c>
-      <c r="B12" s="56" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="C12" s="56" t="inlineStr">
-        <is>
-          <t>適用後(+13)</t>
-        </is>
-      </c>
-      <c r="D12" s="56" t="n">
-        <v>40</v>
-      </c>
-      <c r="E12" s="56" t="n">
-        <v>80</v>
-      </c>
-      <c r="F12" s="56" t="inlineStr">
-        <is>
-          <t>2.0(2)</t>
-        </is>
-      </c>
-      <c r="G12" s="56" t="inlineStr">
-        <is>
-          <t>215(163/235)</t>
-        </is>
-      </c>
-      <c r="H12" s="56" t="inlineStr">
-        <is>
-          <t>250[150-375]</t>
-        </is>
-      </c>
-      <c r="I12" s="56" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="J12" s="56" t="inlineStr">
-        <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="K12" s="56" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="L12" s="56" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="M12" s="56" t="inlineStr">
-        <is>
-          <t>40/40</t>
-        </is>
-      </c>
-      <c r="N12" s="58" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O12" s="56" t="inlineStr">
-        <is>
-          <t>指示語40 その他31 理由6 条件照合3</t>
-        </is>
-      </c>
-    </row>
+      <c r="L11" s="67" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="M11" s="56" t="inlineStr">
+        <is>
+          <t>11/40</t>
+        </is>
+      </c>
+      <c r="N11" s="58" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="O11" s="56" t="inlineStr">
+        <is>
+          <t>主張主旨54 指示語40 条件照合34 理由23 その他9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="55" t="inlineStr">
-        <is>
-          <t>内容理解中</t>
-        </is>
-      </c>
-      <c r="B13" s="55" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="C13" s="55" t="inlineStr">
-        <is>
-          <t>現行</t>
-        </is>
-      </c>
-      <c r="D13" s="55" t="n">
-        <v>25</v>
-      </c>
-      <c r="E13" s="55" t="n">
-        <v>100</v>
-      </c>
-      <c r="F13" s="55" t="inlineStr">
-        <is>
-          <t>4.0(4)</t>
-        </is>
-      </c>
-      <c r="G13" s="55" t="inlineStr">
-        <is>
-          <t>339(322/370)</t>
-        </is>
-      </c>
-      <c r="H13" s="55" t="inlineStr">
-        <is>
-          <t>450[270-675]</t>
-        </is>
-      </c>
-      <c r="I13" s="55" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="J13" s="55" t="inlineStr">
-        <is>
-          <t>24%</t>
-        </is>
-      </c>
-      <c r="K13" s="55" t="inlineStr">
-        <is>
-          <t>39%</t>
-        </is>
-      </c>
-      <c r="L13" s="55" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="M13" s="55" t="inlineStr">
-        <is>
-          <t>25/25</t>
-        </is>
-      </c>
-      <c r="N13" s="57" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O13" s="55" t="inlineStr">
-        <is>
-          <t>その他46 指示語25 理由17 条件照合8 主張主旨4</t>
+      <c r="A13" s="53" t="inlineStr">
+        <is>
+          <t>②情報検索（図版込み・新規なし）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="56" t="inlineStr">
-        <is>
-          <t>内容理解中</t>
-        </is>
-      </c>
-      <c r="B14" s="56" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="C14" s="56" t="inlineStr">
-        <is>
-          <t>適用後(+15)</t>
-        </is>
-      </c>
-      <c r="D14" s="56" t="n">
-        <v>40</v>
-      </c>
-      <c r="E14" s="56" t="n">
-        <v>160</v>
-      </c>
-      <c r="F14" s="56" t="inlineStr">
-        <is>
-          <t>4.0(4)</t>
-        </is>
-      </c>
-      <c r="G14" s="56" t="inlineStr">
-        <is>
-          <t>348(322/476)</t>
-        </is>
-      </c>
-      <c r="H14" s="56" t="inlineStr">
-        <is>
-          <t>450[270-675]</t>
-        </is>
-      </c>
-      <c r="I14" s="56" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="J14" s="56" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="K14" s="56" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L14" s="56" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="M14" s="56" t="inlineStr">
-        <is>
-          <t>40/40</t>
-        </is>
-      </c>
-      <c r="N14" s="58" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O14" s="56" t="inlineStr">
-        <is>
-          <t>その他71 指示語40 理由26 条件照合14 主張主旨5 行動4</t>
+      <c r="A14" s="54" t="inlineStr">
+        <is>
+          <t>級</t>
+        </is>
+      </c>
+      <c r="B14" s="54" t="inlineStr">
+        <is>
+          <t>掲示</t>
+        </is>
+      </c>
+      <c r="C14" s="54" t="inlineStr">
+        <is>
+          <t>設問</t>
+        </is>
+      </c>
+      <c r="D14" s="54" t="inlineStr">
+        <is>
+          <t>実効字数中央(最小/最大)</t>
+        </is>
+      </c>
+      <c r="E14" s="54" t="inlineStr">
+        <is>
+          <t>目標[許容]</t>
+        </is>
+      </c>
+      <c r="F14" s="54" t="inlineStr">
+        <is>
+          <t>帯外短/長</t>
+        </is>
+      </c>
+      <c r="G14" s="54" t="inlineStr">
+        <is>
+          <t>figure比率</t>
+        </is>
+      </c>
+      <c r="H14" s="54" t="inlineStr">
+        <is>
+          <t>図版依存%</t>
+        </is>
+      </c>
+      <c r="I14" s="54" t="inlineStr">
+        <is>
+          <t>本文自足%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="55" t="inlineStr">
         <is>
-          <t>内容理解中</t>
-        </is>
-      </c>
-      <c r="B15" s="55" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="C15" s="55" t="inlineStr">
-        <is>
-          <t>現行</t>
-        </is>
-      </c>
-      <c r="D15" s="55" t="n">
-        <v>27</v>
-      </c>
-      <c r="E15" s="55" t="n">
-        <v>81</v>
-      </c>
-      <c r="F15" s="55" t="inlineStr">
-        <is>
-          <t>3.0(3)</t>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="B15" s="55" t="n">
+        <v>60</v>
+      </c>
+      <c r="C15" s="55" t="n">
+        <v>60</v>
+      </c>
+      <c r="D15" s="67" t="inlineStr">
+        <is>
+          <t>271(204/313)</t>
+        </is>
+      </c>
+      <c r="E15" s="55" t="inlineStr">
+        <is>
+          <t>250[200-375]</t>
+        </is>
+      </c>
+      <c r="F15" s="67" t="inlineStr">
+        <is>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G15" s="55" t="inlineStr">
         <is>
-          <t>409(322/436)</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="H15" s="55" t="inlineStr">
         <is>
-          <t>350[210-525]</t>
-        </is>
-      </c>
-      <c r="I15" s="55" t="inlineStr">
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="I15" s="67" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="B16" s="55" t="n">
+        <v>60</v>
+      </c>
+      <c r="C16" s="55" t="n">
+        <v>60</v>
+      </c>
+      <c r="D16" s="67" t="inlineStr">
+        <is>
+          <t>420(349/541)</t>
+        </is>
+      </c>
+      <c r="E16" s="55" t="inlineStr">
+        <is>
+          <t>400[320-600]</t>
+        </is>
+      </c>
+      <c r="F16" s="67" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="J15" s="55" t="inlineStr">
-        <is>
-          <t>23%</t>
-        </is>
-      </c>
-      <c r="K15" s="55" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="L15" s="55" t="inlineStr">
-        <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="M15" s="55" t="inlineStr">
-        <is>
-          <t>27/27</t>
-        </is>
-      </c>
-      <c r="N15" s="57" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="55" t="inlineStr">
-        <is>
-          <t>主張主旨38 指示語27 理由7 その他6 条件照合3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="56" t="inlineStr">
-        <is>
-          <t>内容理解中</t>
-        </is>
-      </c>
-      <c r="B16" s="56" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="C16" s="56" t="inlineStr">
-        <is>
-          <t>適用後(+53)</t>
-        </is>
-      </c>
-      <c r="D16" s="56" t="n">
-        <v>80</v>
-      </c>
-      <c r="E16" s="56" t="n">
-        <v>240</v>
-      </c>
-      <c r="F16" s="56" t="inlineStr">
-        <is>
-          <t>3.0(3)</t>
-        </is>
-      </c>
-      <c r="G16" s="56" t="inlineStr">
-        <is>
-          <t>312(277/436)</t>
-        </is>
-      </c>
-      <c r="H16" s="56" t="inlineStr">
-        <is>
-          <t>350[210-525]</t>
-        </is>
-      </c>
-      <c r="I16" s="56" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="J16" s="56" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="K16" s="56" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="L16" s="56" t="inlineStr">
-        <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="M16" s="56" t="inlineStr">
-        <is>
-          <t>80/80</t>
-        </is>
-      </c>
-      <c r="N16" s="58" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O16" s="56" t="inlineStr">
-        <is>
-          <t>指示語80 主張主旨62 条件照合62 理由26 その他10</t>
+      <c r="G16" s="55" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="H16" s="55" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="I16" s="67" t="inlineStr">
+        <is>
+          <t>10%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="55" t="inlineStr">
         <is>
-          <t>内容理解長</t>
-        </is>
-      </c>
-      <c r="B17" s="55" t="inlineStr">
-        <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="C17" s="55" t="inlineStr">
-        <is>
-          <t>現行</t>
-        </is>
-      </c>
-      <c r="D17" s="55" t="n">
-        <v>21</v>
-      </c>
-      <c r="E17" s="55" t="n">
-        <v>84</v>
-      </c>
-      <c r="F17" s="55" t="inlineStr">
-        <is>
-          <t>4.0(4)</t>
+      <c r="B17" s="55" t="n">
+        <v>60</v>
+      </c>
+      <c r="C17" s="55" t="n">
+        <v>60</v>
+      </c>
+      <c r="D17" s="67" t="inlineStr">
+        <is>
+          <t>525(481/719)</t>
+        </is>
+      </c>
+      <c r="E17" s="55" t="inlineStr">
+        <is>
+          <t>600[480-900]</t>
+        </is>
+      </c>
+      <c r="F17" s="67" t="inlineStr">
+        <is>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G17" s="55" t="inlineStr">
         <is>
-          <t>552(542/579)</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="H17" s="55" t="inlineStr">
         <is>
-          <t>550[330-825]</t>
-        </is>
-      </c>
-      <c r="I17" s="55" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="J17" s="55" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="K17" s="55" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="L17" s="55" t="inlineStr">
-        <is>
-          <t>21%</t>
-        </is>
-      </c>
-      <c r="M17" s="55" t="inlineStr">
-        <is>
-          <t>21/21</t>
-        </is>
-      </c>
-      <c r="N17" s="57" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="55" t="inlineStr">
-        <is>
-          <t>主張主旨34 指示語21 理由11 条件照合10 その他8</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="56" t="inlineStr">
-        <is>
-          <t>内容理解長</t>
-        </is>
-      </c>
-      <c r="B18" s="56" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="C18" s="56" t="inlineStr">
-        <is>
-          <t>適用後(+19)</t>
-        </is>
-      </c>
-      <c r="D18" s="56" t="n">
-        <v>40</v>
-      </c>
-      <c r="E18" s="56" t="n">
-        <v>160</v>
-      </c>
-      <c r="F18" s="56" t="inlineStr">
-        <is>
-          <t>4.0(4)</t>
-        </is>
-      </c>
-      <c r="G18" s="56" t="inlineStr">
-        <is>
-          <t>543(441/579)</t>
-        </is>
-      </c>
-      <c r="H18" s="56" t="inlineStr">
-        <is>
-          <t>550[330-825]</t>
-        </is>
-      </c>
-      <c r="I18" s="56" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="J18" s="56" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K18" s="56" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="L18" s="56" t="inlineStr">
-        <is>
-          <t>21%</t>
-        </is>
-      </c>
-      <c r="M18" s="56" t="inlineStr">
-        <is>
-          <t>40/40</t>
-        </is>
-      </c>
-      <c r="N18" s="58" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O18" s="56" t="inlineStr">
-        <is>
-          <t>主張主旨54 指示語40 条件照合34 理由23 その他9</t>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="I17" s="67" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="59" t="inlineStr">
+        <is>
+          <t>番人：tools/dokkai_solvability.py --check（最長≤35/語彙≤45/設問数固定/指示語必須 中N4中N3長N3）＋ joho_figure_check.py（図版込み字数）。現状ハード全合格。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="53" t="inlineStr">
-        <is>
-          <t>②情報検索（図版込み・新規なし）</t>
+      <c r="A20" s="59" t="inlineStr">
+        <is>
+          <t>更新点(2026-08-20)：中N4/中N3/長N3を全問題に指示語（現行本体＝100%）。新規217本(短N4 65/短N3 65/中N4 15/中N3 53/長N3 19)は番人green・ne訳→適用待ち。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="54" t="inlineStr">
-        <is>
-          <t>級</t>
-        </is>
-      </c>
-      <c r="B21" s="54" t="inlineStr">
-        <is>
-          <t>掲示</t>
-        </is>
-      </c>
-      <c r="C21" s="54" t="inlineStr">
-        <is>
-          <t>設問</t>
-        </is>
-      </c>
-      <c r="D21" s="54" t="inlineStr">
-        <is>
-          <t>実効字数中央(最小/最大)</t>
-        </is>
-      </c>
-      <c r="E21" s="54" t="inlineStr">
-        <is>
-          <t>目標[許容]</t>
-        </is>
-      </c>
-      <c r="F21" s="54" t="inlineStr">
-        <is>
-          <t>帯外短/長</t>
-        </is>
-      </c>
-      <c r="G21" s="54" t="inlineStr">
-        <is>
-          <t>figure比率</t>
-        </is>
-      </c>
-      <c r="H21" s="54" t="inlineStr">
-        <is>
-          <t>図版依存%</t>
-        </is>
-      </c>
-      <c r="I21" s="54" t="inlineStr">
-        <is>
-          <t>本文自足%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="55" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="B22" s="55" t="n">
-        <v>110</v>
-      </c>
-      <c r="C22" s="55" t="n">
-        <v>110</v>
-      </c>
-      <c r="D22" s="55" t="inlineStr">
-        <is>
-          <t>292(196/420)</t>
-        </is>
-      </c>
-      <c r="E22" s="55" t="inlineStr">
-        <is>
-          <t>250[150-375]</t>
-        </is>
-      </c>
-      <c r="F22" s="55" t="inlineStr">
-        <is>
-          <t>0/3</t>
-        </is>
-      </c>
-      <c r="G22" s="55" t="inlineStr">
-        <is>
-          <t>79%</t>
-        </is>
-      </c>
-      <c r="H22" s="55" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="I22" s="55" t="inlineStr">
-        <is>
-          <t>66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="55" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="B23" s="55" t="n">
-        <v>140</v>
-      </c>
-      <c r="C23" s="55" t="n">
-        <v>140</v>
-      </c>
-      <c r="D23" s="55" t="inlineStr">
-        <is>
-          <t>430(330/587)</t>
-        </is>
-      </c>
-      <c r="E23" s="55" t="inlineStr">
-        <is>
-          <t>400[240-600]</t>
-        </is>
-      </c>
-      <c r="F23" s="55" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G23" s="55" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="H23" s="55" t="inlineStr">
-        <is>
-          <t>37%</t>
-        </is>
-      </c>
-      <c r="I23" s="55" t="inlineStr">
-        <is>
-          <t>62%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="55" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="B24" s="55" t="n">
-        <v>155</v>
-      </c>
-      <c r="C24" s="55" t="n">
-        <v>155</v>
-      </c>
-      <c r="D24" s="55" t="inlineStr">
-        <is>
-          <t>607(495/988)</t>
-        </is>
-      </c>
-      <c r="E24" s="55" t="inlineStr">
-        <is>
-          <t>600[360-900]</t>
-        </is>
-      </c>
-      <c r="F24" s="55" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G24" s="55" t="inlineStr">
-        <is>
-          <t>79%</t>
-        </is>
-      </c>
-      <c r="H24" s="55" t="inlineStr">
-        <is>
-          <t>52%</t>
-        </is>
-      </c>
-      <c r="I24" s="55" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="59" t="inlineStr">
-        <is>
-          <t>番人：tools/dokkai_solvability.py --check（最長≤35/語彙≤45/設問数固定/指示語必須 中N4中N3長N3）＋ joho_figure_check.py（図版込み字数）。現状ハード全合格。</t>
-        </is>
-      </c>
-    </row>
+      <c r="A21" s="59" t="inlineStr">
+        <is>
+          <t>WARN(非致命)：短N4の2本が字数下限割れ／中N5は指示語0（公式もんだい5の指示内容問が要補充・別件）。丸写%は指標であり番人ゲートではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
     <row r="27">
-      <c r="A27" s="59" t="inlineStr">
-        <is>
-          <t>更新点(2026-08-20)：中N4/中N3/長N3を全問題に指示語（現行本体＝100%）。新規217本(短N4 65/短N3 65/中N4 15/中N3 53/長N3 19)は番人green・ne訳→適用待ち。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="59" t="inlineStr">
-        <is>
-          <t>WARN(非致命)：短N4の2本が字数下限割れ／中N5は指示語0（公式もんだい5の指示内容問が要補充・別件）。丸写%は指標であり番人ゲートではない。</t>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
       </c>
     </row>
@@ -5398,7 +4930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5408,6 +4940,7 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5473,6 +5006,11 @@
           <t>1単語が紐づく大問数の分布</t>
         </is>
       </c>
+      <c r="H5" s="69" t="inlineStr">
+        <is>
+          <t>点検メモ</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="48" t="inlineStr">
@@ -5494,7 +5032,7 @@
       <c r="E6" s="40" t="n">
         <v>563</v>
       </c>
-      <c r="F6" s="40" t="inlineStr">
+      <c r="F6" s="70" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -5504,6 +5042,7 @@
           <t>0:46／1:121／2:90／3:355／4:111</t>
         </is>
       </c>
+      <c r="H6" s="71" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="40" t="inlineStr"/>
@@ -5521,12 +5060,13 @@
       <c r="E7" s="40" t="n">
         <v>563</v>
       </c>
-      <c r="F7" s="40" t="inlineStr">
+      <c r="F7" s="70" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
       </c>
       <c r="G7" s="43" t="inlineStr"/>
+      <c r="H7" s="71" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="40" t="inlineStr"/>
@@ -5544,12 +5084,13 @@
       <c r="E8" s="40" t="n">
         <v>723</v>
       </c>
-      <c r="F8" s="40" t="inlineStr">
+      <c r="F8" s="70" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
       <c r="G8" s="43" t="inlineStr"/>
+      <c r="H8" s="71" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="40" t="inlineStr"/>
@@ -5567,12 +5108,17 @@
       <c r="E9" s="40" t="n">
         <v>723</v>
       </c>
-      <c r="F9" s="40" t="inlineStr">
+      <c r="F9" s="72" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
       <c r="G9" s="43" t="inlineStr"/>
+      <c r="H9" s="71" t="inlineStr">
+        <is>
+          <t>母数723中148問＝20%。語彙単語(723)の約80%が「言い換え類義」で一度も出題されない。増産か別大問で補完を。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="40" t="inlineStr"/>
@@ -5611,7 +5157,7 @@
       <c r="E11" s="40" t="n">
         <v>79</v>
       </c>
-      <c r="F11" s="40" t="inlineStr">
+      <c r="F11" s="70" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -5621,6 +5167,7 @@
           <t>0:2／1:0／2:77</t>
         </is>
       </c>
+      <c r="H11" s="71" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="40" t="inlineStr"/>
@@ -5638,12 +5185,13 @@
       <c r="E12" s="40" t="n">
         <v>79</v>
       </c>
-      <c r="F12" s="40" t="inlineStr">
+      <c r="F12" s="70" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
       </c>
       <c r="G12" s="43" t="inlineStr"/>
+      <c r="H12" s="71" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="48" t="inlineStr">
@@ -5665,7 +5213,7 @@
       <c r="E13" s="40" t="n">
         <v>92</v>
       </c>
-      <c r="F13" s="40" t="inlineStr">
+      <c r="F13" s="70" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -5675,6 +5223,7 @@
           <t>0:2／1:14／2:41／3:35</t>
         </is>
       </c>
+      <c r="H13" s="71" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="40" t="inlineStr"/>
@@ -5692,12 +5241,17 @@
       <c r="E14" s="40" t="n">
         <v>92</v>
       </c>
-      <c r="F14" s="40" t="inlineStr">
+      <c r="F14" s="73" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
       </c>
       <c r="G14" s="43" t="inlineStr"/>
+      <c r="H14" s="71" t="inlineStr">
+        <is>
+          <t>カバー率71%。文法単語(92)の約29%が「語の並べ替え」で一度も出題されない。余裕を持って補いたい。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="40" t="inlineStr"/>
@@ -5715,12 +5269,17 @@
       <c r="E15" s="40" t="n">
         <v>92</v>
       </c>
-      <c r="F15" s="40" t="inlineStr">
+      <c r="F15" s="72" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
       </c>
       <c r="G15" s="43" t="inlineStr"/>
+      <c r="H15" s="71" t="inlineStr">
+        <is>
+          <t>母数92中53問＝57%。文法単語(92)の約43%が「文章の文法」で一度も出題されない。増産か別大問で補完を。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="G16" s="38" t="n"/>
@@ -5769,6 +5328,11 @@
           <t>1単語が紐づく大問数の分布</t>
         </is>
       </c>
+      <c r="H18" s="69" t="inlineStr">
+        <is>
+          <t>点検メモ</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="48" t="inlineStr">
@@ -5790,7 +5354,7 @@
       <c r="E19" s="40" t="n">
         <v>542</v>
       </c>
-      <c r="F19" s="40" t="inlineStr">
+      <c r="F19" s="70" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -5800,6 +5364,7 @@
           <t>0:16／1:113／2:95／3:323／4:126</t>
         </is>
       </c>
+      <c r="H19" s="71" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="40" t="inlineStr"/>
@@ -5817,12 +5382,13 @@
       <c r="E20" s="40" t="n">
         <v>542</v>
       </c>
-      <c r="F20" s="40" t="inlineStr">
+      <c r="F20" s="70" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
       <c r="G20" s="43" t="inlineStr"/>
+      <c r="H20" s="71" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="40" t="inlineStr"/>
@@ -5840,12 +5406,13 @@
       <c r="E21" s="40" t="n">
         <v>673</v>
       </c>
-      <c r="F21" s="40" t="inlineStr">
+      <c r="F21" s="70" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
       </c>
       <c r="G21" s="43" t="inlineStr"/>
+      <c r="H21" s="71" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="40" t="inlineStr"/>
@@ -5863,12 +5430,17 @@
       <c r="E22" s="40" t="n">
         <v>673</v>
       </c>
-      <c r="F22" s="40" t="inlineStr">
+      <c r="F22" s="72" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
       <c r="G22" s="43" t="inlineStr"/>
+      <c r="H22" s="71" t="inlineStr">
+        <is>
+          <t>母数673中185問＝27%。語彙単語(673)の約73%が「言い換え類義」で一度も出題されない。増産か別大問で補完を。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="40" t="inlineStr"/>
@@ -5890,12 +5462,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F23" s="40" t="inlineStr">
+      <c r="F23" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="G23" s="43" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>用法は場面/例文単位で単語IDを持たない＝カバー率の対象外（欠落ではない）</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="48" t="inlineStr">
@@ -5917,7 +5494,7 @@
       <c r="E24" s="40" t="n">
         <v>166</v>
       </c>
-      <c r="F24" s="40" t="inlineStr">
+      <c r="F24" s="73" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -5925,6 +5502,11 @@
       <c r="G24" s="43" t="inlineStr">
         <is>
           <t>0:63／1:0／2:103</t>
+        </is>
+      </c>
+      <c r="H24" s="71" t="inlineStr">
+        <is>
+          <t>カバー率62%。漢字単語(166)の約38%が「漢字読み」で一度も出題されない。余裕を持って補いたい。</t>
         </is>
       </c>
     </row>
@@ -5944,12 +5526,17 @@
       <c r="E25" s="40" t="n">
         <v>166</v>
       </c>
-      <c r="F25" s="40" t="inlineStr">
+      <c r="F25" s="73" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
       </c>
       <c r="G25" s="43" t="inlineStr"/>
+      <c r="H25" s="71" t="inlineStr">
+        <is>
+          <t>カバー率62%。漢字単語(166)の約38%が「表記」で一度も出題されない。余裕を持って補いたい。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="48" t="inlineStr">
@@ -5971,7 +5558,7 @@
       <c r="E26" s="40" t="n">
         <v>131</v>
       </c>
-      <c r="F26" s="40" t="inlineStr">
+      <c r="F26" s="70" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -5981,6 +5568,7 @@
           <t>0:0／1:16／2:75／3:40</t>
         </is>
       </c>
+      <c r="H26" s="71" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="40" t="inlineStr"/>
@@ -5998,12 +5586,13 @@
       <c r="E27" s="40" t="n">
         <v>131</v>
       </c>
-      <c r="F27" s="40" t="inlineStr">
+      <c r="F27" s="70" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
       </c>
       <c r="G27" s="43" t="inlineStr"/>
+      <c r="H27" s="71" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="40" t="inlineStr"/>
@@ -6021,12 +5610,17 @@
       <c r="E28" s="40" t="n">
         <v>131</v>
       </c>
-      <c r="F28" s="40" t="inlineStr">
+      <c r="F28" s="72" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
       <c r="G28" s="43" t="inlineStr"/>
+      <c r="H28" s="71" t="inlineStr">
+        <is>
+          <t>母数131中50問＝38%。文法単語(131)の約62%が「文章の文法」で一度も出題されない。増産か別大問で補完を。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="G29" s="38" t="n"/>
@@ -6075,6 +5669,11 @@
           <t>1単語が紐づく大問数の分布</t>
         </is>
       </c>
+      <c r="H31" s="69" t="inlineStr">
+        <is>
+          <t>点検メモ</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="48" t="inlineStr">
@@ -6096,7 +5695,7 @@
       <c r="E32" s="40" t="n">
         <v>1896</v>
       </c>
-      <c r="F32" s="40" t="inlineStr">
+      <c r="F32" s="73" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -6104,6 +5703,11 @@
       <c r="G32" s="43" t="inlineStr">
         <is>
           <t>0:42／1:321／2:357／3:720／4:705</t>
+        </is>
+      </c>
+      <c r="H32" s="71" t="inlineStr">
+        <is>
+          <t>カバー率73%。語彙単語(2145)の約27%が「漢字読み」で一度も出題されない。余裕を持って補いたい。</t>
         </is>
       </c>
     </row>
@@ -6123,12 +5727,13 @@
       <c r="E33" s="40" t="n">
         <v>1896</v>
       </c>
-      <c r="F33" s="40" t="inlineStr">
+      <c r="F33" s="70" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
       <c r="G33" s="43" t="inlineStr"/>
+      <c r="H33" s="71" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="40" t="inlineStr"/>
@@ -6146,12 +5751,13 @@
       <c r="E34" s="40" t="n">
         <v>2145</v>
       </c>
-      <c r="F34" s="40" t="inlineStr">
+      <c r="F34" s="70" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
       </c>
       <c r="G34" s="43" t="inlineStr"/>
+      <c r="H34" s="71" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="40" t="inlineStr"/>
@@ -6169,12 +5775,17 @@
       <c r="E35" s="40" t="n">
         <v>2145</v>
       </c>
-      <c r="F35" s="40" t="inlineStr">
+      <c r="F35" s="72" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
       </c>
       <c r="G35" s="43" t="inlineStr"/>
+      <c r="H35" s="71" t="inlineStr">
+        <is>
+          <t>母数2145中1000問＝46%。語彙単語(2145)の約54%が「言い換え類義」で一度も出題されない。増産か別大問で補完を。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="40" t="inlineStr"/>
@@ -6196,12 +5807,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="40" t="inlineStr">
+      <c r="F36" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="G36" s="43" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>用法は場面/例文単位で単語IDを持たない＝カバー率の対象外（欠落ではない）</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="48" t="inlineStr">
@@ -6223,7 +5839,7 @@
       <c r="E37" s="40" t="n">
         <v>367</v>
       </c>
-      <c r="F37" s="40" t="inlineStr">
+      <c r="F37" s="70" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -6233,6 +5849,7 @@
           <t>0:55／1:0／2:312</t>
         </is>
       </c>
+      <c r="H37" s="71" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="40" t="inlineStr"/>
@@ -6250,12 +5867,13 @@
       <c r="E38" s="40" t="n">
         <v>367</v>
       </c>
-      <c r="F38" s="40" t="inlineStr">
+      <c r="F38" s="70" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
       <c r="G38" s="43" t="inlineStr"/>
+      <c r="H38" s="71" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="48" t="inlineStr">
@@ -6277,7 +5895,7 @@
       <c r="E39" s="40" t="n">
         <v>186</v>
       </c>
-      <c r="F39" s="40" t="inlineStr">
+      <c r="F39" s="70" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -6287,6 +5905,7 @@
           <t>0:1／1:36／2:142／3:7</t>
         </is>
       </c>
+      <c r="H39" s="71" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="40" t="inlineStr"/>
@@ -6304,12 +5923,13 @@
       <c r="E40" s="40" t="n">
         <v>186</v>
       </c>
-      <c r="F40" s="40" t="inlineStr">
+      <c r="F40" s="70" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
       </c>
       <c r="G40" s="43" t="inlineStr"/>
+      <c r="H40" s="71" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="40" t="inlineStr"/>
@@ -6327,15 +5947,31 @@
       <c r="E41" s="40" t="n">
         <v>186</v>
       </c>
-      <c r="F41" s="40" t="inlineStr">
+      <c r="F41" s="72" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
       <c r="G41" s="43" t="inlineStr"/>
+      <c r="H41" s="71" t="inlineStr">
+        <is>
+          <t>母数186中7問＝3%。文法単語(186)の約97%が「文章の文法」で一度も出題されない。増産か別大問で補完を。 ※極端に低い＝データ欠落の疑いあり・要確認。</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="G42" s="38" t="n"/>
+    </row>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6348,7 +5984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6567,12 +6203,12 @@
           <t>258-386</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="79" t="inlineStr">
         <is>
           <t>19/0</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="75" t="n">
         <v>36</v>
       </c>
       <c r="J8" t="n">
@@ -6587,10 +6223,10 @@
       <c r="M8" t="n">
         <v>9</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="76" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="inlineStr">
@@ -6642,12 +6278,12 @@
           <t>209-313</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="79" t="inlineStr">
         <is>
           <t>20/0</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="75" t="n">
         <v>34</v>
       </c>
       <c r="J9" t="n">
@@ -6662,10 +6298,10 @@
       <c r="M9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="75" t="n">
         <v>2</v>
       </c>
       <c r="P9" t="inlineStr">
@@ -6717,12 +6353,12 @@
           <t>105-157</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="79" t="inlineStr">
         <is>
           <t>18/0</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="75" t="n">
         <v>38</v>
       </c>
       <c r="J10" t="n">
@@ -6737,10 +6373,10 @@
       <c r="M10" t="n">
         <v>16</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="75" t="n">
         <v>2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="76" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="inlineStr">
@@ -6792,12 +6428,12 @@
           <t>179-269</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="79" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="75" t="n">
         <v>38</v>
       </c>
       <c r="J11" t="n">
@@ -6812,10 +6448,10 @@
       <c r="M11" t="n">
         <v>8</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="76" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="inlineStr">
@@ -6867,12 +6503,12 @@
           <t>175-263</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="79" t="inlineStr">
         <is>
           <t>21/0</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="76" t="n">
         <v>4</v>
       </c>
       <c r="J12" t="n">
@@ -6887,10 +6523,10 @@
       <c r="M12" t="n">
         <v>5</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12" s="76" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="inlineStr">
@@ -6942,12 +6578,12 @@
           <t>149-223</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="79" t="inlineStr">
         <is>
           <t>29/0</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="76" t="n">
         <v>6</v>
       </c>
       <c r="J13" t="n">
@@ -6962,10 +6598,10 @@
       <c r="M13" t="n">
         <v>9</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13" s="76" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="inlineStr">
@@ -7017,12 +6653,12 @@
           <t>190-284</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="76" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="76" t="n">
         <v>18</v>
       </c>
       <c r="J14" t="n">
@@ -7037,10 +6673,10 @@
       <c r="M14" t="n">
         <v>12</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14" s="76" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="inlineStr">
@@ -7092,21 +6728,21 @@
           <t>27-41</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="79" t="inlineStr">
         <is>
           <t>0/70</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="76" t="n">
         <v>28</v>
       </c>
       <c r="J15" t="n">
         <v>33</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15" s="76" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="inlineStr">
@@ -7168,21 +6804,21 @@
           <t>20-30</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="79" t="inlineStr">
         <is>
           <t>0/184</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="76" t="n">
         <v>26</v>
       </c>
       <c r="J16" t="n">
         <v>33</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16" s="76" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="inlineStr">
@@ -7244,21 +6880,21 @@
           <t>20-30</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="79" t="inlineStr">
         <is>
           <t>0/166</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="76" t="n">
         <v>29</v>
       </c>
       <c r="J17" t="n">
         <v>33</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="77" t="n">
         <v>24</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17" s="76" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="inlineStr">
@@ -7320,21 +6956,21 @@
           <t>18-32</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="79" t="inlineStr">
         <is>
           <t>5/2</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="75" t="n">
         <v>46</v>
       </c>
       <c r="J18" t="n">
         <v>33</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" s="75" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="inlineStr">
@@ -7384,21 +7020,21 @@
           <t>18-33</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="79" t="inlineStr">
         <is>
           <t>9/0</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="77" t="n">
         <v>52</v>
       </c>
       <c r="J19" t="n">
         <v>33</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19" s="76" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="inlineStr">
@@ -7448,21 +7084,21 @@
           <t>14-27</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="79" t="inlineStr">
         <is>
           <t>13/21</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="76" t="n">
         <v>38</v>
       </c>
       <c r="J20" t="n">
         <v>33</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" s="75" t="n">
         <v>2</v>
       </c>
       <c r="P20" t="inlineStr">
@@ -7478,6 +7114,17 @@
       </c>
       <c r="S20" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7491,7 +7138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7622,12 +7269,12 @@
           <t>条件順序</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="76" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="76" t="inlineStr">
         <is>
           <t>✅良好</t>
         </is>
@@ -7673,12 +7320,12 @@
           <t>消去</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="76" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="76" t="inlineStr">
         <is>
           <t>✅良好</t>
         </is>
@@ -7724,12 +7371,12 @@
           <t>消去</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="76" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="76" t="inlineStr">
         <is>
           <t>✅良好</t>
         </is>
@@ -7775,12 +7422,12 @@
           <t>いつ</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="76" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="76" t="inlineStr">
         <is>
           <t>✅良好</t>
         </is>
@@ -7826,12 +7473,12 @@
           <t>どれ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="76" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="76" t="inlineStr">
         <is>
           <t>✅良好</t>
         </is>
@@ -7877,12 +7524,12 @@
           <t>なぜ</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="76" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="76" t="inlineStr">
         <is>
           <t>✅良好</t>
         </is>
@@ -7928,12 +7575,12 @@
           <t>社会自然</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="76" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="76" t="inlineStr">
         <is>
           <t>✅良好</t>
         </is>
@@ -7979,12 +7626,12 @@
           <t>主張</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="77" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="77" t="inlineStr">
         <is>
           <t>❌過半(音声固定)</t>
         </is>
@@ -7997,6 +7644,17 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>何について20 主張60</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
       </c>
     </row>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -3241,7 +3241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3918,6 +3918,21 @@
           <t>本文自足%</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>多様性(種類/最頻)</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>走査S 情報源≥2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>走査C 誘惑肢(選ぶ)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="55" t="inlineStr">
@@ -3961,6 +3976,21 @@
           <t>16%</t>
         </is>
       </c>
+      <c r="J15" s="76" t="inlineStr">
+        <is>
+          <t>8種/最頻15%</t>
+        </is>
+      </c>
+      <c r="K15" s="76" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="L15" s="76" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="55" t="inlineStr">
@@ -3976,12 +4006,12 @@
       </c>
       <c r="D16" s="67" t="inlineStr">
         <is>
-          <t>420(349/541)</t>
+          <t>391(340/459)</t>
         </is>
       </c>
       <c r="E16" s="55" t="inlineStr">
         <is>
-          <t>400[320-600]</t>
+          <t>400[340-460]</t>
         </is>
       </c>
       <c r="F16" s="67" t="inlineStr">
@@ -3991,17 +4021,32 @@
       </c>
       <c r="G16" s="55" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="H16" s="55" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="I16" s="67" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="J16" s="76" t="inlineStr">
+        <is>
+          <t>8種/最頻13%</t>
+        </is>
+      </c>
+      <c r="K16" s="76" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L16" s="76" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4064,12 @@
       </c>
       <c r="D17" s="67" t="inlineStr">
         <is>
-          <t>525(481/719)</t>
+          <t>563(510/679)</t>
         </is>
       </c>
       <c r="E17" s="55" t="inlineStr">
         <is>
-          <t>600[480-900]</t>
+          <t>600[510-690]</t>
         </is>
       </c>
       <c r="F17" s="67" t="inlineStr">
@@ -4034,17 +4079,32 @@
       </c>
       <c r="G17" s="55" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="H17" s="55" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="I17" s="67" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="J17" s="76" t="inlineStr">
+        <is>
+          <t>8種/最頻15%</t>
+        </is>
+      </c>
+      <c r="K17" s="76" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L17" s="76" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -4074,8 +4134,10 @@
     <row r="23"/>
     <row r="24"/>
     <row r="25"/>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+    <row r="26"/>
+    <row r="27"/>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
@@ -4930,7 +4992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5966,8 +6028,10 @@
     <row r="44"/>
     <row r="45"/>
     <row r="46"/>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+    <row r="47"/>
+    <row r="48"/>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
@@ -5984,7 +6048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7120,8 +7184,10 @@
     <row r="22"/>
     <row r="23"/>
     <row r="24"/>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+    <row r="25"/>
+    <row r="26"/>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
@@ -7138,7 +7204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7651,8 +7717,10 @@
     <row r="15"/>
     <row r="16"/>
     <row r="17"/>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="18"/>
+    <row r="19"/>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -304,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -497,6 +497,15 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3241,7 +3250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3253,10 +3262,10 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="34" customWidth="1" min="15" max="15"/>
   </cols>
@@ -3866,9 +3875,9 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="53" t="inlineStr">
-        <is>
-          <t>②情報検索（図版込み・新規なし）</t>
+      <c r="A13" s="80" t="inlineStr">
+        <is>
+          <t>②情報検索（図版込み・掲示物1枚＝1問）　実効字数＝ルビ除き本文＋図版の全文字（目標±15%）。figure比率＝全文字に占める図版の割合／図版依存%＝答えの根拠が図版側にある設問の割合／本文自足%＝本文だけで解ける設問の割合（低いほど図版を走査させる＝良い）。J列＝場面（全8種）の出題内訳%。走査S＝正解に必要な参照箇所（表/注記/カード）が何か所か＝多いほど掲示物全体を見る必要。走査C＝誘惑肢＝図版に実在して正解に見える紛らわしい選択肢（「選ぶ」型で必須。金額/時刻等は計算や言い換えの誘惑肢のため別枠）。全体走査＝表の最有力行が罠で決め手が注記/条件にあり、図版全体を突き合わせないと解けない問題数。N5は走査S/Cのハード判定は対象外（易しく）だが数値は参考表示。</t>
         </is>
       </c>
     </row>
@@ -3918,19 +3927,24 @@
           <t>本文自足%</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>多様性(種類/最頻)</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>走査S 情報源≥2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>走査C 誘惑肢(選ぶ)</t>
+      <c r="J14" s="71" t="inlineStr">
+        <is>
+          <t>場面内訳（全8種：習い事／ツアー見学／施設案内／カタログ／カレンダー回覧／イベント／窓口受付／募集）</t>
+        </is>
+      </c>
+      <c r="K14" s="71" t="inlineStr">
+        <is>
+          <t>走査S 情報源数の分布（参照＝表/注記/カード。多いほど掲示物全体を見る必要）</t>
+        </is>
+      </c>
+      <c r="L14" s="71" t="inlineStr">
+        <is>
+          <t>走査C 誘惑肢（図版に実在する紛らわしい肢＝「選ぶ」型で必須）</t>
+        </is>
+      </c>
+      <c r="M14" s="71" t="inlineStr">
+        <is>
+          <t>全体走査（正解に図版全体の突合が要る問題数＝情報源≥2かつ条件≥2）</t>
         </is>
       </c>
     </row>
@@ -3976,19 +3990,24 @@
           <t>16%</t>
         </is>
       </c>
-      <c r="J15" s="76" t="inlineStr">
-        <is>
-          <t>8種/最頻15%</t>
-        </is>
-      </c>
-      <c r="K15" s="76" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="L15" s="76" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="J15" s="81" t="inlineStr">
+        <is>
+          <t>習い事13% ／ ツアー見学15% ／ 施設案内13% ／ カタログ12% ／ カレンダー回覧12% ／ イベント12% ／ 窓口受付12% ／ 募集12%</t>
+        </is>
+      </c>
+      <c r="K15" s="81" t="inlineStr">
+        <is>
+          <t>4源:9問／3源:1問／2源:24問／1源(密):26問（N5は走査ハード対象外＝参考値）</t>
+        </is>
+      </c>
+      <c r="L15" s="81" t="inlineStr">
+        <is>
+          <t>「選ぶ」型12問中 図版に実在する誘惑肢≥3＝8問（全型では24問が図版由来の紛らわしい肢）（N5は対象外）</t>
+        </is>
+      </c>
+      <c r="M15" s="81" t="inlineStr">
+        <is>
+          <t>19/60問（32%）＝表の最有力行が罠・決め手は注記/条件＝図版全体の突き合わせが必要</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4025,7 @@
       </c>
       <c r="D16" s="67" t="inlineStr">
         <is>
-          <t>391(340/459)</t>
+          <t>386(341/459)</t>
         </is>
       </c>
       <c r="E16" s="55" t="inlineStr">
@@ -4021,32 +4040,37 @@
       </c>
       <c r="G16" s="55" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="H16" s="55" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="I16" s="67" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="J16" s="76" t="inlineStr">
-        <is>
-          <t>8種/最頻13%</t>
-        </is>
-      </c>
-      <c r="K16" s="76" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="L16" s="76" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J16" s="81" t="inlineStr">
+        <is>
+          <t>習い事13% ／ ツアー見学13% ／ 施設案内13% ／ カタログ13% ／ カレンダー回覧12% ／ イベント12% ／ 窓口受付12% ／ 募集12%</t>
+        </is>
+      </c>
+      <c r="K16" s="81" t="inlineStr">
+        <is>
+          <t>3源:22問／2源:38問／全60問が「表1行だけでは解けない」基準クリア</t>
+        </is>
+      </c>
+      <c r="L16" s="81" t="inlineStr">
+        <is>
+          <t>「選ぶ」型11問中 図版に実在する誘惑肢≥3＝11問（全型では24問が図版由来の紛らわしい肢）</t>
+        </is>
+      </c>
+      <c r="M16" s="81" t="inlineStr">
+        <is>
+          <t>27/60問（45%）＝表の最有力行が罠・決め手は注記/条件＝図版全体の突き合わせが必要</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4088,7 @@
       </c>
       <c r="D17" s="67" t="inlineStr">
         <is>
-          <t>563(510/679)</t>
+          <t>550(516/679)</t>
         </is>
       </c>
       <c r="E17" s="55" t="inlineStr">
@@ -4079,12 +4103,12 @@
       </c>
       <c r="G17" s="55" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="H17" s="55" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="I17" s="67" t="inlineStr">
@@ -4092,19 +4116,24 @@
           <t>8%</t>
         </is>
       </c>
-      <c r="J17" s="76" t="inlineStr">
-        <is>
-          <t>8種/最頻15%</t>
-        </is>
-      </c>
-      <c r="K17" s="76" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="L17" s="76" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="J17" s="81" t="inlineStr">
+        <is>
+          <t>習い事15% ／ ツアー見学12% ／ 施設案内13% ／ カタログ13% ／ カレンダー回覧12% ／ イベント12% ／ 窓口受付12% ／ 募集12%</t>
+        </is>
+      </c>
+      <c r="K17" s="81" t="inlineStr">
+        <is>
+          <t>4源:16問／3源:18問／2源:26問／全60問が「表1行だけでは解けない」基準クリア</t>
+        </is>
+      </c>
+      <c r="L17" s="81" t="inlineStr">
+        <is>
+          <t>「選ぶ」型11問中 図版に実在する誘惑肢≥3＝11問（全型では30問が図版由来の紛らわしい肢）</t>
+        </is>
+      </c>
+      <c r="M17" s="81" t="inlineStr">
+        <is>
+          <t>48/60問（80%）＝表の最有力行が罠・決め手は注記/条件＝図版全体の突き合わせが必要</t>
         </is>
       </c>
     </row>
@@ -4136,8 +4165,12 @@
     <row r="25"/>
     <row r="26"/>
     <row r="27"/>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
@@ -4992,7 +5025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6030,8 +6063,12 @@
     <row r="46"/>
     <row r="47"/>
     <row r="48"/>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
@@ -6048,7 +6085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7186,8 +7223,12 @@
     <row r="24"/>
     <row r="25"/>
     <row r="26"/>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
@@ -7204,7 +7245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7719,8 +7760,12 @@
     <row r="17"/>
     <row r="18"/>
     <row r="19"/>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
@@ -1917,11 +1917,11 @@
         <v>5</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>3:400</t>
+          <t>3:250</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
@@ -1961,11 +1961,11 @@
         <v>5</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>3:200</t>
+          <t>3:100</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -3072,7 +3072,7 @@
         <v>23</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -3149,7 +3149,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16000</v>
+        <v>15750</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3221,6 +3221,8 @@
           <t>辞書にある全単語数（問題化の母数）</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -3250,7 +3252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3277,7 +3279,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="53" t="inlineStr">
         <is>
@@ -3873,11 +3874,10 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="80" t="inlineStr">
         <is>
-          <t>②情報検索（図版込み・掲示物1枚＝1問）　実効字数＝ルビ除き本文＋図版の全文字（目標±15%）。figure比率＝全文字に占める図版の割合／図版依存%＝答えの根拠が図版側にある設問の割合／本文自足%＝本文だけで解ける設問の割合（低いほど図版を走査させる＝良い）。J列＝場面（全8種）の出題内訳%。走査S＝正解に必要な参照箇所（表/注記/カード）が何か所か＝多いほど掲示物全体を見る必要。走査C＝誘惑肢＝図版に実在して正解に見える紛らわしい選択肢（「選ぶ」型で必須。金額/時刻等は計算や言い換えの誘惑肢のため別枠）。全体走査＝表の最有力行が罠で決め手が注記/条件にあり、図版全体を突き合わせないと解けない問題数。N5は走査S/Cのハード判定は対象外（易しく）だが数値は参考表示。</t>
+          <t>②情報検索（図版込み・掲示物1枚＝1問）　実効字数＝ルビ除き本文＋図版の全文字（目標±15%）。figure比率＝全文字に占める図版の割合／図版依存%＝答えの根拠が図版側にある設問の割合／本文自足%＝本文だけで解ける設問の割合（低いほど図版を走査させる＝良い）。J列＝場面（全8種）の出題内訳%。走査S＝正解に必要な参照箇所（表/注記/カード）が何か所か＝多いほど掲示物全体を見る必要。走査C＝誘惑肢＝図版に実在して正解に見える紛らわしい選択肢（「選ぶ」型で必須。金額/時刻等は計算や言い換えの誘惑肢のため別枠）。全体走査＝正解に必要な情報源数(answer_sources)の分布（1源/2源/3源の問題数）。表の最有力行が罠で決め手が注記/別表/条件にあり、源数が多いほど掲示物の複数箇所を突き合わせないと解けない＝走査が重い。N5は走査S/Cのハード判定は対象外（易しく）だが数値は参考表示。</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="M14" s="71" t="inlineStr">
         <is>
-          <t>全体走査（正解に図版全体の突合が要る問題数＝情報源≥2かつ条件≥2）</t>
+          <t>全体走査（正解に必要な情報源数 answer_sources の分布＝「1源=◯問／2源=◯問／3源=◯問」。源数が多いほど掲示物の複数箇所を突き合わせる必要）</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4007,7 @@
       </c>
       <c r="M15" s="81" t="inlineStr">
         <is>
-          <t>19/60問（32%）＝表の最有力行が罠・決め手は注記/条件＝図版全体の突き合わせが必要</t>
+          <t>1源=41問　2源=18問　3源=1問（正解に必要な情報源数。2源以上=19/60問=32%）</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M16" s="81" t="inlineStr">
         <is>
-          <t>27/60問（45%）＝表の最有力行が罠・決め手は注記/条件＝図版全体の突き合わせが必要</t>
+          <t>1源=20問　2源=39問　3源=1問（正解に必要な情報源数。2源以上=40/60問=67%）</t>
         </is>
       </c>
     </row>
@@ -4133,11 +4133,10 @@
       </c>
       <c r="M17" s="81" t="inlineStr">
         <is>
-          <t>48/60問（80%）＝表の最有力行が罠・決め手は注記/条件＝図版全体の突き合わせが必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
+          <t>2源=30問　3源=30問（正解に必要な情報源数。2源以上=60/60問=100%）</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
       <c r="A19" s="59" t="inlineStr">
         <is>
@@ -4159,18 +4158,8 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
@@ -5025,7 +5014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6057,18 +6046,8 @@
     <row r="42">
       <c r="G42" s="38" t="n"/>
     </row>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="54">
-      <c r="A54" s="15" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
@@ -6085,7 +6064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7217,18 +7196,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
@@ -7245,7 +7214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7754,18 +7723,8 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="習得の仕組み(ID×面)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="単語数と紐づけ大問" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="単語×大問カバー率" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解攻略耐性分析" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解 骨組みパラメータ分布" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解 骨組みパラメータ分布" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解攻略耐性分析" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大問別まとめ'!$A$1:$J$1</definedName>
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,8 +102,17 @@
       <color rgb="00C55A11"/>
       <sz val="9"/>
     </font>
+    <font>
+      <color rgb="009C6500"/>
+    </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <color rgb="009C0006"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -205,6 +214,21 @@
         <fgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -304,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -506,6 +530,9 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1947,10 +1974,10 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
@@ -1961,11 +1988,11 @@
         <v>5</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>3:100</t>
+          <t>3:250</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -3072,7 +3099,7 @@
         <v>23</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -3149,7 +3176,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -3192,7 +3219,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15750</v>
+        <v>15900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3221,8 +3248,6 @@
           <t>辞書にある全単語数（問題化の母数）</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -3252,7 +3277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4158,8 +4183,8 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
@@ -5014,7 +5039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5280,7 +5305,7 @@
     <row r="13">
       <c r="A13" s="48" t="inlineStr">
         <is>
-          <t>文法単語(92)</t>
+          <t>文法単語(91)</t>
         </is>
       </c>
       <c r="B13" s="40" t="inlineStr">
@@ -5295,11 +5320,11 @@
         <v>82</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F13" s="70" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="G13" s="43" t="inlineStr">
@@ -5323,17 +5348,17 @@
         <v>66</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F14" s="73" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="G14" s="43" t="inlineStr"/>
       <c r="H14" s="71" t="inlineStr">
         <is>
-          <t>カバー率71%。文法単語(92)の約29%が「語の並べ替え」で一度も出題されない。余裕を持って補いたい。</t>
+          <t>カバー率73%。文法単語(91)の約27%が「語の並べ替え」で一度も出題されない。余裕を持って補いたい。</t>
         </is>
       </c>
     </row>
@@ -5348,20 +5373,20 @@
         <v>400</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F15" s="72" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G15" s="43" t="inlineStr"/>
       <c r="H15" s="71" t="inlineStr">
         <is>
-          <t>母数92中53問＝57%。文法単語(92)の約43%が「文章の文法」で一度も出題されない。増産か別大問で補完を。</t>
+          <t>母数91中52問＝57%。文法単語(91)の約43%が「文章の文法」で一度も出題されない。増産か別大問で補完を。</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5697,7 @@
       </c>
       <c r="F27" s="70" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="G27" s="43" t="inlineStr"/>
@@ -5686,23 +5711,23 @@
         </is>
       </c>
       <c r="C28" s="40" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="D28" s="40" t="n">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="E28" s="40" t="n">
         <v>131</v>
       </c>
-      <c r="F28" s="72" t="inlineStr">
-        <is>
-          <t>38%</t>
+      <c r="F28" s="73" t="inlineStr">
+        <is>
+          <t>77%</t>
         </is>
       </c>
       <c r="G28" s="43" t="inlineStr"/>
       <c r="H28" s="71" t="inlineStr">
         <is>
-          <t>母数131中50問＝38%。文法単語(131)の約62%が「文章の文法」で一度も出題されない。増産か別大問で補完を。</t>
+          <t>カバー率77%。文法単語(131)の約23%が「文章の文法」で一度も出題されない。余裕を持って補いたい。</t>
         </is>
       </c>
     </row>
@@ -6023,31 +6048,44 @@
         </is>
       </c>
       <c r="C41" s="40" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D41" s="40" t="n">
-        <v>7</v>
+        <v>126</v>
       </c>
       <c r="E41" s="40" t="n">
         <v>186</v>
       </c>
-      <c r="F41" s="72" t="inlineStr">
-        <is>
-          <t>3%</t>
+      <c r="F41" s="73" t="inlineStr">
+        <is>
+          <t>68%</t>
         </is>
       </c>
       <c r="G41" s="43" t="inlineStr"/>
       <c r="H41" s="71" t="inlineStr">
         <is>
-          <t>母数186中7問＝3%。文法単語(186)の約97%が「文章の文法」で一度も出題されない。増産か別大問で補完を。 ※極端に低い＝データ欠落の疑いあり・要確認。</t>
+          <t>カバー率68%。文法単語(186)の約32%が「文章の文法」で一度も出題されない。余裕を持って補いたい。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="G42" s="38" t="n"/>
     </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
@@ -6064,7 +6102,534 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W33"/>
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>聴解 骨組みパラメータ分布（2026-08-18 自動集計｜skeleton_tag.py）＝ワンパターン化を止めるための型バランス。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>偏り＝聞かず解ける/飽きるの芽。直し方＝既存はいじらず『薄い型』を新しく足して薄める（既存音声の焼き直し不要・新規追加分だけTTS）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>番人：1つの型が過半(50%)を占めたらビルド失格。作問前の目安＝35%以下（skeleton_tag.py check）。『薄い型』列＝ここを増やせば偏りが下がる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>kanten(観点)は全レベル良好。q_type(概要の聞き方)は質問が音声焼込み＝既存の付け替えは有料、薄めは新規追加で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>大問</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>パラメータ</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>問題数</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>型の数</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>目安/型</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>最も多い型</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>最大%</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>薄い型＝ここを増やして薄める</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>全分布</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>①課題理解</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>develop</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>150</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>条件順序</t>
+        </is>
+      </c>
+      <c r="H6" s="76" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="I6" s="76" t="inlineStr">
+        <is>
+          <t>✅良好</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>上書き15 条件順序33 消去30 まず次13 追加14 二者択一14 断って代案14 勘違い訂正17</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>①課題理解</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>develop</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>消去</t>
+        </is>
+      </c>
+      <c r="H7" s="76" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="I7" s="76" t="inlineStr">
+        <is>
+          <t>✅良好</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>上書き18 条件順序18 消去33 まず次23 追加16 二者択一14 断って代案14 勘違い訂正14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>①課題理解</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>develop</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>150</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>消去</t>
+        </is>
+      </c>
+      <c r="H8" s="76" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="I8" s="76" t="inlineStr">
+        <is>
+          <t>✅良好</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>上書き12 条件順序34 消去46 まず次11 追加12 二者択一11 断って代案11 勘違い訂正13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>②ポイント理解</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>kanten</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>104</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>21</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>いつ</t>
+        </is>
+      </c>
+      <c r="H9" s="76" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="I9" s="76" t="inlineStr">
+        <is>
+          <t>✅良好</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>なぜ20 いつ24 いくつ19 気持ち18 どれ23</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>②ポイント理解</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>kanten</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>どれ</t>
+        </is>
+      </c>
+      <c r="H10" s="76" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="I10" s="76" t="inlineStr">
+        <is>
+          <t>✅良好</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>なぜ20 いつ20 いくつ19 気持ち20 どれ21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>②ポイント理解</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>kanten</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>20</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>なぜ</t>
+        </is>
+      </c>
+      <c r="H11" s="76" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="I11" s="76" t="inlineStr">
+        <is>
+          <t>✅良好</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>なぜ21 いつ20 いくつ20 気持ち19 どれ20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>③概要理解</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>genre</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>80</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>社会自然</t>
+        </is>
+      </c>
+      <c r="H12" s="76" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="I12" s="76" t="inlineStr">
+        <is>
+          <t>✅良好</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>モノサービス(1) 文化行事(2)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>健康体10 生活くらし14 社会自然24 仕事7 学び12 モノサービス1 文化行事2 趣味旅食10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>③概要理解</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q_type</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>27</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>主張</t>
+        </is>
+      </c>
+      <c r="H13" s="77" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="I13" s="77" t="inlineStr">
+        <is>
+          <t>❌過半(音声固定)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>何について(20) タイトル(0)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>何について20 主張60</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6102,228 +6667,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>本質3観点→ ①答えが本文/設問から予測できる ②誤答が弱い ③大問×レベル内でワンパターン/重複。</t>
+          <t>★セル色＝信号：緑=合格／黄=境界・注意／赤=要改善。しきい値＝最長≤基準+15・語彙マッチ≤基準+10・正誤差≤+1.0・設問テンプレ≤30%・台本/選択肢重複=0・帯外=0が理想・係/留守=0・(発話)依頼形≤35%/形分離≤65%・位置最大≤基準+7。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>語彙マッチ的中%=「本文と最も語が重なる選択肢」を選ぶと正解になる割合(基準=1/選択肢数)。高い=正解だけ本文語→聞かず語マッチで解ける(①②)。良い設計は正解を言い換え本文語は誤答へ罠として置く。</t>
+          <t>本質3観点→ ①答えが本文/設問から予測できる ②誤答が弱い ③大問×レベル内でワンパターン/重複。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>正解−誤答 本文一致差=正解の本文一致語数−誤答平均。+大=正解だけ本文語(①②)。最長を選ぶ的中=正解が最長選択肢の割合(②)。</t>
+          <t>語彙マッチ的中%=「本文と最も語が重なる選択肢」を選ぶと正解になる割合(基準=1/選択肢数)。高い=正解だけ本文語→聞かず語マッチで解ける(①②)。良い設計は正解を言い換え本文語は誤答へ罠として置く。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>選択肢方式「表示時ランダム」(課題/ポイント/概要=テキスト4択)はアプリが並べ替え→正解位置は無関係(正本①固定でOK)。「音声焼込み」(発話/即時)は位置固定→位置偏りが有効。</t>
+          <t>正解−誤答 本文一致差=正解の本文一致語数−誤答平均。+大=正解だけ本文語(①②)。最長を選ぶ的中=正解が最長選択肢の割合(②)。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>選択肢方式「表示時ランダム」(課題/ポイント/概要=テキスト4択)はアプリが並べ替え→正解位置は無関係(正本①固定でOK)。「音声焼込み」(発話/即時)は位置固定→位置偏りが有効。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>台本重複/選択肢セット重複=同一大問×レベル内の近似(③)。設問テンプレ最大=同一設問文の最大シェア(③)。設計帯:課題/ポイント/概要/発話=公式中央値±20%、即時=公式実測再センタリング。既存問の帯外は帯導入前の据え置き。</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>大問</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>レベル</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>問題数</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>選択肢数</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>選択肢方式</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>台本モーラ min/中/max</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>設計帯</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>帯外 短/長</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>最長を選ぶ的中%</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>基準%</t>
         </is>
       </c>
-      <c r="K7" s="17" t="inlineStr">
+      <c r="K8" s="17" t="inlineStr">
         <is>
           <t>語彙マッチ的中%</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L8" s="17" t="inlineStr">
         <is>
           <t>正解−誤答 本文一致差</t>
         </is>
       </c>
-      <c r="M7" s="17" t="inlineStr">
+      <c r="M8" s="17" t="inlineStr">
         <is>
           <t>設問テンプレ最大%</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N8" s="17" t="inlineStr">
         <is>
           <t>台本重複(≥.60)</t>
         </is>
       </c>
-      <c r="O7" s="17" t="inlineStr">
+      <c r="O8" s="17" t="inlineStr">
         <is>
           <t>選択肢セット重複(≥.70)</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P8" s="17" t="inlineStr">
         <is>
           <t>正解位置(正本)</t>
         </is>
       </c>
-      <c r="Q7" s="17" t="inlineStr">
+      <c r="Q8" s="17" t="inlineStr">
         <is>
           <t>位置最大%(有効時)</t>
         </is>
       </c>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="R8" s="17" t="inlineStr">
         <is>
           <t>係</t>
         </is>
       </c>
-      <c r="S7" s="17" t="inlineStr">
+      <c r="S8" s="17" t="inlineStr">
         <is>
           <t>留守</t>
         </is>
       </c>
-      <c r="T7" s="17" t="inlineStr">
+      <c r="T8" s="17" t="inlineStr">
         <is>
           <t>依頼形%</t>
         </is>
       </c>
-      <c r="U7" s="17" t="inlineStr">
+      <c r="U8" s="17" t="inlineStr">
         <is>
           <t>形分離%</t>
         </is>
       </c>
-      <c r="V7" s="17" t="inlineStr">
+      <c r="V8" s="17" t="inlineStr">
         <is>
           <t>機能max%</t>
         </is>
       </c>
-      <c r="W7" s="17" t="inlineStr">
+      <c r="W8" s="17" t="inlineStr">
         <is>
           <t>弁別軸max%</t>
         </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>課題理解</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>150</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>表示時ランダム</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>183/306/384</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>258-386</t>
-        </is>
-      </c>
-      <c r="H8" s="79" t="inlineStr">
-        <is>
-          <t>19/0</t>
-        </is>
-      </c>
-      <c r="I8" s="75" t="n">
-        <v>36</v>
-      </c>
-      <c r="J8" t="n">
-        <v>25</v>
-      </c>
-      <c r="K8" t="n">
-        <v>29</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>9</v>
-      </c>
-      <c r="N8" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>150/0/0/0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6334,7 +6831,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>N4</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6350,39 +6847,39 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>163/241/311</t>
+          <t>183/306/384</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>209-313</t>
-        </is>
-      </c>
-      <c r="H9" s="79" t="inlineStr">
-        <is>
-          <t>20/0</t>
-        </is>
-      </c>
-      <c r="I9" s="75" t="n">
-        <v>34</v>
+          <t>258-386</t>
+        </is>
+      </c>
+      <c r="H9" s="83" t="inlineStr">
+        <is>
+          <t>19/0</t>
+        </is>
+      </c>
+      <c r="I9" s="84" t="n">
+        <v>36</v>
       </c>
       <c r="J9" t="n">
         <v>25</v>
       </c>
-      <c r="K9" t="n">
-        <v>19</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>8</v>
-      </c>
-      <c r="N9" s="76" t="n">
+      <c r="K9" s="84" t="n">
+        <v>29</v>
+      </c>
+      <c r="L9" s="84" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" s="84" t="n">
+        <v>9</v>
+      </c>
+      <c r="N9" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="75" t="n">
-        <v>2</v>
+      <c r="O9" s="84" t="n">
+        <v>0</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -6394,10 +6891,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="R9" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S9" s="84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6409,7 +6906,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N4</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6425,70 +6922,70 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>73/115/154</t>
+          <t>163/241/311</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>105-157</t>
-        </is>
-      </c>
-      <c r="H10" s="79" t="inlineStr">
-        <is>
-          <t>18/0</t>
-        </is>
-      </c>
-      <c r="I10" s="75" t="n">
-        <v>38</v>
+          <t>209-313</t>
+        </is>
+      </c>
+      <c r="H10" s="83" t="inlineStr">
+        <is>
+          <t>20/0</t>
+        </is>
+      </c>
+      <c r="I10" s="84" t="n">
+        <v>34</v>
       </c>
       <c r="J10" t="n">
         <v>25</v>
       </c>
-      <c r="K10" t="n">
-        <v>13</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K10" s="84" t="n">
+        <v>19</v>
+      </c>
+      <c r="L10" s="84" t="n">
         <v>0.3</v>
       </c>
-      <c r="M10" t="n">
-        <v>16</v>
-      </c>
-      <c r="N10" s="75" t="n">
+      <c r="M10" s="84" t="n">
+        <v>8</v>
+      </c>
+      <c r="N10" s="84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="O10" s="76" t="n">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>150/0/0/0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R10" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>150/0/0/0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="S10" s="84" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ポイント理解</t>
+          <t>課題理解</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
@@ -6500,54 +6997,54 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>183/236/290</t>
+          <t>73/115/154</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>179-269</t>
-        </is>
-      </c>
-      <c r="H11" s="79" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="I11" s="75" t="n">
+          <t>105-157</t>
+        </is>
+      </c>
+      <c r="H11" s="83" t="inlineStr">
+        <is>
+          <t>18/0</t>
+        </is>
+      </c>
+      <c r="I11" s="84" t="n">
         <v>38</v>
       </c>
       <c r="J11" t="n">
         <v>25</v>
       </c>
-      <c r="K11" t="n">
-        <v>14</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N11" s="76" t="n">
+      <c r="K11" s="84" t="n">
+        <v>13</v>
+      </c>
+      <c r="L11" s="84" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M11" s="84" t="n">
+        <v>16</v>
+      </c>
+      <c r="N11" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="76" t="n">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>150/0/0/0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R11" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>100/0/0/0</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="S11" s="84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6559,11 +7056,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>N4</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
@@ -6575,54 +7072,54 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>124/190/256</t>
+          <t>183/239/290</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>175-263</t>
-        </is>
-      </c>
-      <c r="H12" s="79" t="inlineStr">
-        <is>
-          <t>21/0</t>
-        </is>
-      </c>
-      <c r="I12" s="76" t="n">
-        <v>4</v>
+          <t>179-269</t>
+        </is>
+      </c>
+      <c r="H12" s="83" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="I12" s="83" t="n">
+        <v>45</v>
       </c>
       <c r="J12" t="n">
         <v>25</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="84" t="n">
         <v>17</v>
       </c>
-      <c r="L12" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N12" s="76" t="n">
+      <c r="L12" s="84" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M12" s="84" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="76" t="n">
+      <c r="O12" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>150/0/0/0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R12" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>100/0/0/0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="S12" s="84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6634,11 +7131,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N4</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
@@ -6650,43 +7147,43 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>84/162/216</t>
+          <t>124/196/263</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>149-223</t>
-        </is>
-      </c>
-      <c r="H13" s="79" t="inlineStr">
-        <is>
-          <t>29/0</t>
-        </is>
-      </c>
-      <c r="I13" s="76" t="n">
-        <v>6</v>
+          <t>175-263</t>
+        </is>
+      </c>
+      <c r="H13" s="83" t="inlineStr">
+        <is>
+          <t>21/0</t>
+        </is>
+      </c>
+      <c r="I13" s="84" t="n">
+        <v>20</v>
       </c>
       <c r="J13" t="n">
         <v>25</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="84" t="n">
+        <v>19</v>
+      </c>
+      <c r="L13" s="84" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M13" s="84" t="n">
         <v>6</v>
       </c>
-      <c r="L13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>9</v>
-      </c>
-      <c r="N13" s="76" t="n">
+      <c r="N13" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="76" t="n">
+      <c r="O13" s="84" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>104/0/0/0</t>
+          <t>150/0/0/0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -6694,26 +7191,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="R13" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S13" s="84" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>概要理解</t>
+          <t>ポイント理解</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="D14" t="n">
         <v>4</v>
@@ -6725,43 +7222,43 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>203/234/272</t>
+          <t>84/168/216</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>190-284</t>
-        </is>
-      </c>
-      <c r="H14" s="76" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I14" s="76" t="n">
-        <v>18</v>
+          <t>149-223</t>
+        </is>
+      </c>
+      <c r="H14" s="83" t="inlineStr">
+        <is>
+          <t>29/0</t>
+        </is>
+      </c>
+      <c r="I14" s="84" t="n">
+        <v>23</v>
       </c>
       <c r="J14" t="n">
         <v>25</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="84" t="n">
         <v>10</v>
       </c>
-      <c r="L14" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="M14" t="n">
-        <v>12</v>
-      </c>
-      <c r="N14" s="76" t="n">
+      <c r="L14" s="84" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M14" s="84" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="76" t="n">
+      <c r="O14" s="84" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20/20/20/20</t>
+          <t>150/0/0/0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -6769,17 +7266,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="R14" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S14" s="84" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>発話表現</t>
+          <t>概要理解</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6788,68 +7285,67 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>音声焼込み(位置固定)</t>
+          <t>表示時ランダム</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>29/40/47</t>
+          <t>203/234/272</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>27-41</t>
-        </is>
-      </c>
-      <c r="H15" s="79" t="inlineStr">
-        <is>
-          <t>0/70</t>
-        </is>
-      </c>
-      <c r="I15" s="76" t="n">
-        <v>28</v>
+          <t>190-284</t>
+        </is>
+      </c>
+      <c r="H15" s="84" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I15" s="84" t="n">
+        <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>33</v>
-      </c>
-      <c r="N15" s="77" t="n">
-        <v>4</v>
-      </c>
-      <c r="O15" s="76" t="n">
+        <v>25</v>
+      </c>
+      <c r="K15" s="84" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" s="84" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="M15" s="84" t="n">
+        <v>12</v>
+      </c>
+      <c r="N15" s="84" t="n">
         <v>0</v>
       </c>
+      <c r="O15" s="84" t="n">
+        <v>0</v>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>60/74/66</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>37</v>
-      </c>
-      <c r="R15" t="n">
+          <t>20/20/20/20</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R15" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S15" s="84" t="n">
         <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>12</v>
-      </c>
-      <c r="U15" t="n">
-        <v>56</v>
-      </c>
-      <c r="V15" t="n">
-        <v>33</v>
-      </c>
-      <c r="W15" t="n">
-        <v>67</v>
       </c>
     </row>
     <row r="16">
@@ -6860,7 +7356,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>N4</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -6876,56 +7372,56 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24/38/47</t>
+          <t>29/40/47</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20-30</t>
-        </is>
-      </c>
-      <c r="H16" s="79" t="inlineStr">
-        <is>
-          <t>0/184</t>
-        </is>
-      </c>
-      <c r="I16" s="76" t="n">
-        <v>26</v>
+          <t>27-41</t>
+        </is>
+      </c>
+      <c r="H16" s="83" t="inlineStr">
+        <is>
+          <t>0/71</t>
+        </is>
+      </c>
+      <c r="I16" s="84" t="n">
+        <v>28</v>
       </c>
       <c r="J16" t="n">
         <v>33</v>
       </c>
-      <c r="N16" s="77" t="n">
-        <v>8</v>
-      </c>
-      <c r="O16" s="76" t="n">
+      <c r="N16" s="84" t="n">
         <v>0</v>
       </c>
+      <c r="O16" s="84" t="n">
+        <v>0</v>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>54/77/69</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>38</v>
-      </c>
-      <c r="R16" t="n">
+          <t>60/74/66</t>
+        </is>
+      </c>
+      <c r="Q16" s="84" t="n">
+        <v>37</v>
+      </c>
+      <c r="R16" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S16" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="T16" t="n">
-        <v>7</v>
-      </c>
-      <c r="U16" t="n">
-        <v>54</v>
+      <c r="T16" s="84" t="n">
+        <v>12</v>
+      </c>
+      <c r="U16" s="84" t="n">
+        <v>56</v>
       </c>
       <c r="V16" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="W16" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -6936,7 +7432,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N4</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -6952,7 +7448,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24/36/47</t>
+          <t>24/38/47</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6960,45 +7456,45 @@
           <t>20-30</t>
         </is>
       </c>
-      <c r="H17" s="79" t="inlineStr">
-        <is>
-          <t>0/166</t>
-        </is>
-      </c>
-      <c r="I17" s="76" t="n">
-        <v>29</v>
+      <c r="H17" s="83" t="inlineStr">
+        <is>
+          <t>0/183</t>
+        </is>
+      </c>
+      <c r="I17" s="84" t="n">
+        <v>28</v>
       </c>
       <c r="J17" t="n">
         <v>33</v>
       </c>
-      <c r="N17" s="77" t="n">
-        <v>24</v>
-      </c>
-      <c r="O17" s="76" t="n">
+      <c r="N17" s="84" t="n">
         <v>0</v>
       </c>
+      <c r="O17" s="84" t="n">
+        <v>0</v>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>53/80/67</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>40</v>
-      </c>
-      <c r="R17" t="n">
+          <t>58/74/68</t>
+        </is>
+      </c>
+      <c r="Q17" s="84" t="n">
+        <v>37</v>
+      </c>
+      <c r="R17" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S17" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="T17" t="n">
-        <v>6</v>
-      </c>
-      <c r="U17" t="n">
-        <v>49</v>
+      <c r="T17" s="84" t="n">
+        <v>7</v>
+      </c>
+      <c r="U17" s="84" t="n">
+        <v>54</v>
       </c>
       <c r="V17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="W17" t="n">
         <v>62</v>
@@ -7007,16 +7503,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>即時応答</t>
+          <t>発話表現</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
@@ -7028,44 +7524,56 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13/26/46</t>
+          <t>24/36/47</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>18-32</t>
-        </is>
-      </c>
-      <c r="H18" s="79" t="inlineStr">
-        <is>
-          <t>5/2</t>
-        </is>
-      </c>
-      <c r="I18" s="75" t="n">
-        <v>46</v>
+          <t>20-30</t>
+        </is>
+      </c>
+      <c r="H18" s="83" t="inlineStr">
+        <is>
+          <t>0/168</t>
+        </is>
+      </c>
+      <c r="I18" s="84" t="n">
+        <v>32</v>
       </c>
       <c r="J18" t="n">
         <v>33</v>
       </c>
-      <c r="N18" s="76" t="n">
+      <c r="N18" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="75" t="n">
-        <v>2</v>
+      <c r="O18" s="84" t="n">
+        <v>0</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>94/74/72</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>39</v>
-      </c>
-      <c r="R18" t="n">
+          <t>59/77/64</t>
+        </is>
+      </c>
+      <c r="Q18" s="84" t="n">
+        <v>38</v>
+      </c>
+      <c r="R18" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S18" s="84" t="n">
         <v>0</v>
+      </c>
+      <c r="T18" s="84" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" s="84" t="n">
+        <v>50</v>
+      </c>
+      <c r="V18" t="n">
+        <v>26</v>
+      </c>
+      <c r="W18" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -7076,7 +7584,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>N4</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -7092,43 +7600,43 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>12/25/33</t>
+          <t>13/26/46</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18-33</t>
-        </is>
-      </c>
-      <c r="H19" s="79" t="inlineStr">
-        <is>
-          <t>9/0</t>
-        </is>
-      </c>
-      <c r="I19" s="77" t="n">
-        <v>52</v>
+          <t>18-32</t>
+        </is>
+      </c>
+      <c r="H19" s="83" t="inlineStr">
+        <is>
+          <t>5/2</t>
+        </is>
+      </c>
+      <c r="I19" s="84" t="n">
+        <v>46</v>
       </c>
       <c r="J19" t="n">
         <v>33</v>
       </c>
-      <c r="N19" s="76" t="n">
+      <c r="N19" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="O19" s="76" t="n">
+      <c r="O19" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>94/74/72</t>
+        </is>
+      </c>
+      <c r="Q19" s="84" t="n">
+        <v>39</v>
+      </c>
+      <c r="R19" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>94/74/72</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>39</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="S19" s="84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7140,7 +7648,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N4</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -7156,578 +7664,108 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>8/24/30</t>
+          <t>12/25/33</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>14-27</t>
-        </is>
-      </c>
-      <c r="H20" s="79" t="inlineStr">
-        <is>
-          <t>13/21</t>
-        </is>
-      </c>
-      <c r="I20" s="76" t="n">
-        <v>38</v>
+          <t>18-33</t>
+        </is>
+      </c>
+      <c r="H20" s="83" t="inlineStr">
+        <is>
+          <t>9/0</t>
+        </is>
+      </c>
+      <c r="I20" s="84" t="n">
+        <v>40</v>
       </c>
       <c r="J20" t="n">
         <v>33</v>
       </c>
-      <c r="N20" s="76" t="n">
+      <c r="N20" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="75" t="n">
+      <c r="O20" s="84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>94/74/72</t>
+        </is>
+      </c>
+      <c r="Q20" s="84" t="n">
+        <v>39</v>
+      </c>
+      <c r="R20" s="84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>240</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>音声焼込み(位置固定)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8/24/30</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>14-27</t>
+        </is>
+      </c>
+      <c r="H21" s="83" t="inlineStr">
+        <is>
+          <t>13/21</t>
+        </is>
+      </c>
+      <c r="I21" s="84" t="n">
+        <v>38</v>
+      </c>
+      <c r="J21" t="n">
+        <v>33</v>
+      </c>
+      <c r="N21" s="84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>94/74/72</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" s="84" t="n">
         <v>39</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" s="84" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>聴解 骨組みパラメータ分布（2026-08-18 自動集計｜skeleton_tag.py）＝ワンパターン化を止めるための型バランス。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>偏り＝聞かず解ける/飽きるの芽。直し方＝既存はいじらず『薄い型』を新しく足して薄める（既存音声の焼き直し不要・新規追加分だけTTS）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>番人：1つの型が過半(50%)を占めたらビルド失格。作問前の目安＝35%以下（skeleton_tag.py check）。『薄い型』列＝ここを増やせば偏りが下がる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>kanten(観点)は全レベル良好。q_type(概要の聞き方)は質問が音声焼込み＝既存の付け替えは有料、薄めは新規追加で。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>大問</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>レベル</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>パラメータ</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>問題数</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>型の数</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>目安/型</t>
-        </is>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>最も多い型</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>最大%</t>
-        </is>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t>薄い型＝ここを増やして薄める</t>
-        </is>
-      </c>
-      <c r="K5" s="17" t="inlineStr">
-        <is>
-          <t>全分布</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>①課題理解</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>develop</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>150</v>
-      </c>
-      <c r="E6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" t="n">
-        <v>19</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>条件順序</t>
-        </is>
-      </c>
-      <c r="H6" s="76" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
-      </c>
-      <c r="I6" s="76" t="inlineStr">
-        <is>
-          <t>✅良好</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>上書き15 条件順序33 消去30 まず次13 追加14 二者択一14 断って代案14 勘違い訂正17</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>①課題理解</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>develop</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>150</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" t="n">
-        <v>19</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>消去</t>
-        </is>
-      </c>
-      <c r="H7" s="76" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
-      </c>
-      <c r="I7" s="76" t="inlineStr">
-        <is>
-          <t>✅良好</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>上書き18 条件順序18 消去33 まず次23 追加16 二者択一14 断って代案14 勘違い訂正14</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>①課題理解</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>develop</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>150</v>
-      </c>
-      <c r="E8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" t="n">
-        <v>19</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>消去</t>
-        </is>
-      </c>
-      <c r="H8" s="76" t="inlineStr">
-        <is>
-          <t>31%</t>
-        </is>
-      </c>
-      <c r="I8" s="76" t="inlineStr">
-        <is>
-          <t>✅良好</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>上書き12 条件順序34 消去46 まず次11 追加12 二者択一11 断って代案11 勘違い訂正13</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>②ポイント理解</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>kanten</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>104</v>
-      </c>
-      <c r="E9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>21</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>いつ</t>
-        </is>
-      </c>
-      <c r="H9" s="76" t="inlineStr">
-        <is>
-          <t>23%</t>
-        </is>
-      </c>
-      <c r="I9" s="76" t="inlineStr">
-        <is>
-          <t>✅良好</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>なぜ20 いつ24 いくつ19 気持ち18 どれ23</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>②ポイント理解</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>kanten</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>100</v>
-      </c>
-      <c r="E10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" t="n">
-        <v>20</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>どれ</t>
-        </is>
-      </c>
-      <c r="H10" s="76" t="inlineStr">
-        <is>
-          <t>21%</t>
-        </is>
-      </c>
-      <c r="I10" s="76" t="inlineStr">
-        <is>
-          <t>✅良好</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>なぜ20 いつ20 いくつ19 気持ち20 どれ21</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>②ポイント理解</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>kanten</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>100</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>なぜ</t>
-        </is>
-      </c>
-      <c r="H11" s="76" t="inlineStr">
-        <is>
-          <t>21%</t>
-        </is>
-      </c>
-      <c r="I11" s="76" t="inlineStr">
-        <is>
-          <t>✅良好</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>なぜ21 いつ20 いくつ20 気持ち19 どれ20</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>③概要理解</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>genre</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>80</v>
-      </c>
-      <c r="E12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>社会自然</t>
-        </is>
-      </c>
-      <c r="H12" s="76" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="I12" s="76" t="inlineStr">
-        <is>
-          <t>✅良好</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>モノサービス(1) 文化行事(2)</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>健康体10 生活くらし14 社会自然24 仕事7 学び12 モノサービス1 文化行事2 趣味旅食10</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>③概要理解</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>q_type</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>80</v>
-      </c>
-      <c r="E13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" t="n">
-        <v>27</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>主張</t>
-        </is>
-      </c>
-      <c r="H13" s="77" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="I13" s="77" t="inlineStr">
-        <is>
-          <t>❌過半(音声固定)</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>何について(20) タイトル(0)</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>何について20 主張60</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -5378,7 +5378,7 @@
       <c r="E15" s="40" t="n">
         <v>91</v>
       </c>
-      <c r="F15" s="72" t="inlineStr">
+      <c r="F15" s="70" t="inlineStr">
         <is>
           <t>100%</t>
         </is>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -4583,7 +4583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4667,151 +4667,152 @@
     <row r="6">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>漢字単語</t>
+          <t>文法単語</t>
         </is>
       </c>
       <c r="B6" s="40" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C6" s="40" t="n">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="D6" s="40" t="n">
-        <v>367</v>
+        <v>186</v>
       </c>
       <c r="E6" s="40" t="n">
-        <v>612</v>
+        <v>409</v>
       </c>
       <c r="I6" s="38" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
-        <is>
-          <t>文法単語</t>
-        </is>
-      </c>
-      <c r="B7" s="40" t="n">
-        <v>92</v>
-      </c>
-      <c r="C7" s="40" t="n">
-        <v>131</v>
-      </c>
-      <c r="D7" s="40" t="n">
-        <v>186</v>
-      </c>
-      <c r="E7" s="40" t="n">
-        <v>409</v>
-      </c>
       <c r="I7" s="38" t="n"/>
     </row>
     <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>②紐づく大問と問題数　総数 ／ verified在庫</t>
+        </is>
+      </c>
       <c r="I8" s="38" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>②紐づく大問と問題数　総数 ／ verified在庫</t>
-        </is>
-      </c>
-      <c r="I9" s="38" t="n"/>
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t>グループ</t>
+        </is>
+      </c>
+      <c r="B9" s="39" t="inlineStr">
+        <is>
+          <t>大問</t>
+        </is>
+      </c>
+      <c r="C9" s="39" t="inlineStr">
+        <is>
+          <t>N5 総数</t>
+        </is>
+      </c>
+      <c r="D9" s="39" t="inlineStr">
+        <is>
+          <t>N5 在庫</t>
+        </is>
+      </c>
+      <c r="E9" s="39" t="inlineStr">
+        <is>
+          <t>N4 総数</t>
+        </is>
+      </c>
+      <c r="F9" s="39" t="inlineStr">
+        <is>
+          <t>N4 在庫</t>
+        </is>
+      </c>
+      <c r="G9" s="39" t="inlineStr">
+        <is>
+          <t>N3 総数</t>
+        </is>
+      </c>
+      <c r="H9" s="39" t="inlineStr">
+        <is>
+          <t>N3 在庫</t>
+        </is>
+      </c>
+      <c r="I9" s="41" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
-        <is>
-          <t>グループ</t>
-        </is>
-      </c>
-      <c r="B10" s="39" t="inlineStr">
-        <is>
-          <t>大問</t>
-        </is>
-      </c>
-      <c r="C10" s="39" t="inlineStr">
-        <is>
-          <t>N5 総数</t>
-        </is>
-      </c>
-      <c r="D10" s="39" t="inlineStr">
-        <is>
-          <t>N5 在庫</t>
-        </is>
-      </c>
-      <c r="E10" s="39" t="inlineStr">
-        <is>
-          <t>N4 総数</t>
-        </is>
-      </c>
-      <c r="F10" s="39" t="inlineStr">
-        <is>
-          <t>N4 在庫</t>
-        </is>
-      </c>
-      <c r="G10" s="39" t="inlineStr">
-        <is>
-          <t>N3 総数</t>
-        </is>
-      </c>
-      <c r="H10" s="39" t="inlineStr">
-        <is>
-          <t>N3 在庫</t>
-        </is>
-      </c>
-      <c r="I10" s="41" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>文脈規定</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="n">
+        <v>672</v>
+      </c>
+      <c r="D10" s="40" t="n">
+        <v>655</v>
+      </c>
+      <c r="E10" s="40" t="n">
+        <v>651</v>
+      </c>
+      <c r="F10" s="40" t="n">
+        <v>651</v>
+      </c>
+      <c r="G10" s="40" t="n">
+        <v>2090</v>
+      </c>
+      <c r="H10" s="40" t="n">
+        <v>772</v>
+      </c>
+      <c r="I10" s="43" t="inlineStr">
+        <is>
+          <t>公式作問。在庫＝verified</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="42" t="inlineStr">
-        <is>
-          <t>漢字（文字）</t>
-        </is>
-      </c>
+      <c r="A11" s="40" t="inlineStr"/>
       <c r="B11" s="40" t="inlineStr">
         <is>
-          <t>漢字読み</t>
+          <t>言い換え類義</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>463</v>
-      </c>
-      <c r="D11" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>148</v>
+      </c>
+      <c r="D11" s="40" t="n">
+        <v>148</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>448</v>
-      </c>
-      <c r="F11" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>185</v>
+      </c>
+      <c r="F11" s="40" t="n">
+        <v>185</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>1398</v>
-      </c>
-      <c r="H11" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="43" t="inlineStr">
-        <is>
-          <t>辞書から機械生成（公式作問でない＝在庫に数えない）</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="H11" s="40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I11" s="43" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="40" t="inlineStr"/>
       <c r="B12" s="40" t="inlineStr">
         <is>
-          <t>表記</t>
+          <t>用法</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>527</v>
+        <v>0</v>
       </c>
       <c r="D12" s="40" t="inlineStr">
         <is>
@@ -4819,55 +4820,57 @@
         </is>
       </c>
       <c r="E12" s="40" t="n">
-        <v>492</v>
-      </c>
-      <c r="F12" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>153</v>
+      </c>
+      <c r="F12" s="40" t="n">
+        <v>153</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>1527</v>
-      </c>
-      <c r="H12" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>150</v>
+      </c>
+      <c r="H12" s="40" t="n">
+        <v>150</v>
       </c>
       <c r="I12" s="43" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="42" t="inlineStr">
         <is>
-          <t>語彙</t>
+          <t>文法</t>
         </is>
       </c>
       <c r="B13" s="40" t="inlineStr">
         <is>
-          <t>文脈規定</t>
+          <t>文法形式(穴埋め)</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>672</v>
-      </c>
-      <c r="D13" s="40" t="n">
-        <v>655</v>
+        <v>204</v>
+      </c>
+      <c r="D13" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E13" s="40" t="n">
-        <v>651</v>
-      </c>
-      <c r="F13" s="40" t="n">
-        <v>651</v>
+        <v>357</v>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G13" s="40" t="n">
-        <v>2090</v>
-      </c>
-      <c r="H13" s="40" t="n">
-        <v>772</v>
+        <v>443</v>
+      </c>
+      <c r="H13" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" s="43" t="inlineStr">
         <is>
-          <t>公式作問。在庫＝verified</t>
+          <t>穴埋め/並べ替えは在庫を文法点×cloze可で管理。文章の文法は全数在庫</t>
         </is>
       </c>
     </row>
@@ -4875,26 +4878,32 @@
       <c r="A14" s="40" t="inlineStr"/>
       <c r="B14" s="40" t="inlineStr">
         <is>
-          <t>言い換え類義</t>
+          <t>語の並べ替え</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>148</v>
-      </c>
-      <c r="D14" s="40" t="n">
-        <v>148</v>
+        <v>137</v>
+      </c>
+      <c r="D14" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E14" s="40" t="n">
-        <v>185</v>
-      </c>
-      <c r="F14" s="40" t="n">
-        <v>185</v>
+        <v>214</v>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G14" s="40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H14" s="40" t="n">
-        <v>1000</v>
+        <v>308</v>
+      </c>
+      <c r="H14" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" s="43" t="inlineStr"/>
     </row>
@@ -4902,131 +4911,28 @@
       <c r="A15" s="40" t="inlineStr"/>
       <c r="B15" s="40" t="inlineStr">
         <is>
-          <t>用法</t>
+          <t>文章の文法</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>400</v>
+      </c>
+      <c r="D15" s="40" t="n">
+        <v>400</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>153</v>
+        <v>400</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>153</v>
+        <v>400</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I15" s="43" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="42" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B16" s="40" t="inlineStr">
-        <is>
-          <t>文法形式(穴埋め)</t>
-        </is>
-      </c>
-      <c r="C16" s="40" t="n">
-        <v>204</v>
-      </c>
-      <c r="D16" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="40" t="n">
-        <v>357</v>
-      </c>
-      <c r="F16" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="40" t="n">
-        <v>443</v>
-      </c>
-      <c r="H16" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" s="43" t="inlineStr">
-        <is>
-          <t>穴埋め/並べ替えは在庫を文法点×cloze可で管理。文章の文法は全数在庫</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="40" t="inlineStr"/>
-      <c r="B17" s="40" t="inlineStr">
-        <is>
-          <t>語の並べ替え</t>
-        </is>
-      </c>
-      <c r="C17" s="40" t="n">
-        <v>137</v>
-      </c>
-      <c r="D17" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="40" t="n">
-        <v>214</v>
-      </c>
-      <c r="F17" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="40" t="n">
-        <v>308</v>
-      </c>
-      <c r="H17" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" s="43" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="40" t="inlineStr"/>
-      <c r="B18" s="40" t="inlineStr">
-        <is>
-          <t>文章の文法</t>
-        </is>
-      </c>
-      <c r="C18" s="40" t="n">
-        <v>400</v>
-      </c>
-      <c r="D18" s="40" t="n">
-        <v>400</v>
-      </c>
-      <c r="E18" s="40" t="n">
-        <v>400</v>
-      </c>
-      <c r="F18" s="40" t="n">
-        <v>400</v>
-      </c>
-      <c r="G18" s="40" t="n">
-        <v>200</v>
-      </c>
-      <c r="H18" s="40" t="n">
-        <v>200</v>
-      </c>
-      <c r="I18" s="43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5039,7 +4945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5063,7 +4969,7 @@
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>※用法は場面/例文単位でvocabId無し＝語カバー測定不可。漢字カバーは語(vocabId)の漢字から導出。</t>
+          <t>※用法は場面/例文単位でvocabId無し＝語カバー測定不可。漢字は語彙に統合済(漢字カバー行は廃止・2026-08-22)。</t>
         </is>
       </c>
       <c r="G2" s="38" t="n"/>
@@ -5249,31 +5155,31 @@
     <row r="11">
       <c r="A11" s="48" t="inlineStr">
         <is>
-          <t>漢字単語(79)</t>
+          <t>文法単語(91)</t>
         </is>
       </c>
       <c r="B11" s="40" t="inlineStr">
         <is>
-          <t>漢字読み</t>
+          <t>文法形式(穴埋め)</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>463</v>
+        <v>204</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F11" s="70" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>0:2／1:0／2:77</t>
+          <t>0:2／1:14／2:41／3:35</t>
         </is>
       </c>
       <c r="H11" s="71" t="n"/>
@@ -5282,587 +5188,583 @@
       <c r="A12" s="40" t="inlineStr"/>
       <c r="B12" s="40" t="inlineStr">
         <is>
-          <t>表記</t>
+          <t>語の並べ替え</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>527</v>
+        <v>137</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>79</v>
-      </c>
-      <c r="F12" s="70" t="inlineStr">
-        <is>
-          <t>97%</t>
+        <v>91</v>
+      </c>
+      <c r="F12" s="73" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
       <c r="G12" s="43" t="inlineStr"/>
-      <c r="H12" s="71" t="n"/>
+      <c r="H12" s="71" t="inlineStr">
+        <is>
+          <t>カバー率73%。文法単語(91)の約27%が「語の並べ替え」で一度も出題されない。余裕を持って補いたい。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="inlineStr">
-        <is>
-          <t>文法単語(91)</t>
-        </is>
-      </c>
+      <c r="A13" s="40" t="inlineStr"/>
       <c r="B13" s="40" t="inlineStr">
         <is>
-          <t>文法形式(穴埋め)</t>
+          <t>文章の文法</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>204</v>
+        <v>400</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E13" s="40" t="n">
         <v>91</v>
       </c>
       <c r="F13" s="70" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G13" s="43" t="inlineStr"/>
+      <c r="H13" s="71" t="inlineStr">
+        <is>
+          <t>母数91中52問＝57%。文法単語(91)の約43%が「文章の文法」で一度も出題されない。増産か別大問で補完を。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="G14" s="38" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>■ N4</t>
+        </is>
+      </c>
+      <c r="G15" s="38" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="46" t="inlineStr">
+        <is>
+          <t>単語種別</t>
+        </is>
+      </c>
+      <c r="B16" s="46" t="inlineStr">
+        <is>
+          <t>大問</t>
+        </is>
+      </c>
+      <c r="C16" s="46" t="inlineStr">
+        <is>
+          <t>問題数</t>
+        </is>
+      </c>
+      <c r="D16" s="46" t="inlineStr">
+        <is>
+          <t>カバー数</t>
+        </is>
+      </c>
+      <c r="E16" s="46" t="inlineStr">
+        <is>
+          <t>母数</t>
+        </is>
+      </c>
+      <c r="F16" s="46" t="inlineStr">
+        <is>
+          <t>カバー率</t>
+        </is>
+      </c>
+      <c r="G16" s="47" t="inlineStr">
+        <is>
+          <t>1単語が紐づく大問数の分布</t>
+        </is>
+      </c>
+      <c r="H16" s="69" t="inlineStr">
+        <is>
+          <t>点検メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="48" t="inlineStr">
+        <is>
+          <t>語彙単語(673)</t>
+        </is>
+      </c>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>漢字読み</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="n">
+        <v>448</v>
+      </c>
+      <c r="D17" s="40" t="n">
+        <v>448</v>
+      </c>
+      <c r="E17" s="40" t="n">
+        <v>542</v>
+      </c>
+      <c r="F17" s="70" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="G17" s="43" t="inlineStr">
+        <is>
+          <t>0:16／1:113／2:95／3:323／4:126</t>
+        </is>
+      </c>
+      <c r="H17" s="71" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="inlineStr"/>
+      <c r="B18" s="40" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="C18" s="40" t="n">
+        <v>492</v>
+      </c>
+      <c r="D18" s="40" t="n">
+        <v>492</v>
+      </c>
+      <c r="E18" s="40" t="n">
+        <v>542</v>
+      </c>
+      <c r="F18" s="70" t="inlineStr">
+        <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="G13" s="43" t="inlineStr">
-        <is>
-          <t>0:2／1:14／2:41／3:35</t>
-        </is>
-      </c>
-      <c r="H13" s="71" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="40" t="inlineStr"/>
-      <c r="B14" s="40" t="inlineStr">
-        <is>
-          <t>語の並べ替え</t>
-        </is>
-      </c>
-      <c r="C14" s="40" t="n">
-        <v>137</v>
-      </c>
-      <c r="D14" s="40" t="n">
-        <v>66</v>
-      </c>
-      <c r="E14" s="40" t="n">
-        <v>91</v>
-      </c>
-      <c r="F14" s="73" t="inlineStr">
-        <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="G14" s="43" t="inlineStr"/>
-      <c r="H14" s="71" t="inlineStr">
-        <is>
-          <t>カバー率73%。文法単語(91)の約27%が「語の並べ替え」で一度も出題されない。余裕を持って補いたい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="40" t="inlineStr"/>
-      <c r="B15" s="40" t="inlineStr">
-        <is>
-          <t>文章の文法</t>
-        </is>
-      </c>
-      <c r="C15" s="40" t="n">
-        <v>400</v>
-      </c>
-      <c r="D15" s="40" t="n">
-        <v>91</v>
-      </c>
-      <c r="E15" s="40" t="n">
-        <v>91</v>
-      </c>
-      <c r="F15" s="70" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G15" s="43" t="inlineStr"/>
-      <c r="H15" s="71" t="inlineStr">
-        <is>
-          <t>母数91中52問＝57%。文法単語(91)の約43%が「文章の文法」で一度も出題されない。増産か別大問で補完を。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="G16" s="38" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="45" t="inlineStr">
-        <is>
-          <t>■ N4</t>
-        </is>
-      </c>
-      <c r="G17" s="38" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="46" t="inlineStr">
-        <is>
-          <t>単語種別</t>
-        </is>
-      </c>
-      <c r="B18" s="46" t="inlineStr">
-        <is>
-          <t>大問</t>
-        </is>
-      </c>
-      <c r="C18" s="46" t="inlineStr">
-        <is>
-          <t>問題数</t>
-        </is>
-      </c>
-      <c r="D18" s="46" t="inlineStr">
-        <is>
-          <t>カバー数</t>
-        </is>
-      </c>
-      <c r="E18" s="46" t="inlineStr">
-        <is>
-          <t>母数</t>
-        </is>
-      </c>
-      <c r="F18" s="46" t="inlineStr">
-        <is>
-          <t>カバー率</t>
-        </is>
-      </c>
-      <c r="G18" s="47" t="inlineStr">
-        <is>
-          <t>1単語が紐づく大問数の分布</t>
-        </is>
-      </c>
-      <c r="H18" s="69" t="inlineStr">
-        <is>
-          <t>点検メモ</t>
-        </is>
-      </c>
+      <c r="G18" s="43" t="inlineStr"/>
+      <c r="H18" s="71" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="48" t="inlineStr">
-        <is>
-          <t>語彙単語(673)</t>
-        </is>
-      </c>
+      <c r="A19" s="40" t="inlineStr"/>
       <c r="B19" s="40" t="inlineStr">
         <is>
-          <t>漢字読み</t>
+          <t>文脈規定</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>448</v>
+        <v>651</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>448</v>
+        <v>651</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>542</v>
+        <v>673</v>
       </c>
       <c r="F19" s="70" t="inlineStr">
         <is>
-          <t>82%</t>
-        </is>
-      </c>
-      <c r="G19" s="43" t="inlineStr">
-        <is>
-          <t>0:16／1:113／2:95／3:323／4:126</t>
-        </is>
-      </c>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="G19" s="43" t="inlineStr"/>
       <c r="H19" s="71" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="40" t="inlineStr"/>
       <c r="B20" s="40" t="inlineStr">
         <is>
-          <t>表記</t>
+          <t>言い換え類義</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>492</v>
+        <v>185</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>492</v>
+        <v>185</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>542</v>
-      </c>
-      <c r="F20" s="70" t="inlineStr">
-        <is>
-          <t>90%</t>
+        <v>673</v>
+      </c>
+      <c r="F20" s="72" t="inlineStr">
+        <is>
+          <t>27%</t>
         </is>
       </c>
       <c r="G20" s="43" t="inlineStr"/>
-      <c r="H20" s="71" t="n"/>
+      <c r="H20" s="71" t="inlineStr">
+        <is>
+          <t>母数673中185問＝27%。語彙単語(673)の約73%が「言い換え類義」で一度も出題されない。増産か別大問で補完を。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="40" t="inlineStr"/>
       <c r="B21" s="40" t="inlineStr">
         <is>
-          <t>文脈規定</t>
+          <t>用法</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
-        <v>651</v>
-      </c>
-      <c r="D21" s="40" t="n">
-        <v>651</v>
-      </c>
-      <c r="E21" s="40" t="n">
-        <v>673</v>
-      </c>
-      <c r="F21" s="70" t="inlineStr">
-        <is>
-          <t>96%</t>
+        <v>153</v>
+      </c>
+      <c r="D21" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="43" t="inlineStr"/>
-      <c r="H21" s="71" t="n"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>用法は場面/例文単位で単語IDを持たない＝カバー率の対象外（欠落ではない）</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="inlineStr"/>
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>文法単語(131)</t>
+        </is>
+      </c>
       <c r="B22" s="40" t="inlineStr">
         <is>
-          <t>言い換え類義</t>
+          <t>文法形式(穴埋め)</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>185</v>
+        <v>357</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>673</v>
-      </c>
-      <c r="F22" s="72" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="G22" s="43" t="inlineStr"/>
-      <c r="H22" s="71" t="inlineStr">
-        <is>
-          <t>母数673中185問＝27%。語彙単語(673)の約73%が「言い換え類義」で一度も出題されない。増産か別大問で補完を。</t>
-        </is>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="F22" s="70" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="G22" s="43" t="inlineStr">
+        <is>
+          <t>0:0／1:16／2:75／3:40</t>
+        </is>
+      </c>
+      <c r="H22" s="71" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="40" t="inlineStr"/>
       <c r="B23" s="40" t="inlineStr">
         <is>
+          <t>語の並べ替え</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="n">
+        <v>214</v>
+      </c>
+      <c r="D23" s="40" t="n">
+        <v>111</v>
+      </c>
+      <c r="E23" s="40" t="n">
+        <v>131</v>
+      </c>
+      <c r="F23" s="70" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="G23" s="43" t="inlineStr"/>
+      <c r="H23" s="71" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="40" t="inlineStr"/>
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t>文章の文法</t>
+        </is>
+      </c>
+      <c r="C24" s="40" t="n">
+        <v>250</v>
+      </c>
+      <c r="D24" s="40" t="n">
+        <v>101</v>
+      </c>
+      <c r="E24" s="40" t="n">
+        <v>131</v>
+      </c>
+      <c r="F24" s="73" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="G24" s="43" t="inlineStr"/>
+      <c r="H24" s="71" t="inlineStr">
+        <is>
+          <t>カバー率77%。文法単語(131)の約23%が「文章の文法」で一度も出題されない。余裕を持って補いたい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="G25" s="38" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="45" t="inlineStr">
+        <is>
+          <t>■ N3</t>
+        </is>
+      </c>
+      <c r="G26" s="38" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="46" t="inlineStr">
+        <is>
+          <t>単語種別</t>
+        </is>
+      </c>
+      <c r="B27" s="46" t="inlineStr">
+        <is>
+          <t>大問</t>
+        </is>
+      </c>
+      <c r="C27" s="46" t="inlineStr">
+        <is>
+          <t>問題数</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="inlineStr">
+        <is>
+          <t>カバー数</t>
+        </is>
+      </c>
+      <c r="E27" s="46" t="inlineStr">
+        <is>
+          <t>母数</t>
+        </is>
+      </c>
+      <c r="F27" s="46" t="inlineStr">
+        <is>
+          <t>カバー率</t>
+        </is>
+      </c>
+      <c r="G27" s="47" t="inlineStr">
+        <is>
+          <t>1単語が紐づく大問数の分布</t>
+        </is>
+      </c>
+      <c r="H27" s="69" t="inlineStr">
+        <is>
+          <t>点検メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t>語彙単語(2145)</t>
+        </is>
+      </c>
+      <c r="B28" s="40" t="inlineStr">
+        <is>
+          <t>漢字読み</t>
+        </is>
+      </c>
+      <c r="C28" s="40" t="n">
+        <v>1398</v>
+      </c>
+      <c r="D28" s="40" t="n">
+        <v>1398</v>
+      </c>
+      <c r="E28" s="40" t="n">
+        <v>1896</v>
+      </c>
+      <c r="F28" s="73" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="G28" s="43" t="inlineStr">
+        <is>
+          <t>0:42／1:321／2:357／3:720／4:705</t>
+        </is>
+      </c>
+      <c r="H28" s="71" t="inlineStr">
+        <is>
+          <t>カバー率73%。語彙単語(2145)の約27%が「漢字読み」で一度も出題されない。余裕を持って補いたい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="40" t="inlineStr"/>
+      <c r="B29" s="40" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="C29" s="40" t="n">
+        <v>1527</v>
+      </c>
+      <c r="D29" s="40" t="n">
+        <v>1527</v>
+      </c>
+      <c r="E29" s="40" t="n">
+        <v>1896</v>
+      </c>
+      <c r="F29" s="70" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G29" s="43" t="inlineStr"/>
+      <c r="H29" s="71" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="40" t="inlineStr"/>
+      <c r="B30" s="40" t="inlineStr">
+        <is>
+          <t>文脈規定</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="n">
+        <v>2090</v>
+      </c>
+      <c r="D30" s="40" t="n">
+        <v>2090</v>
+      </c>
+      <c r="E30" s="40" t="n">
+        <v>2145</v>
+      </c>
+      <c r="F30" s="70" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="G30" s="43" t="inlineStr"/>
+      <c r="H30" s="71" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="40" t="inlineStr"/>
+      <c r="B31" s="40" t="inlineStr">
+        <is>
+          <t>言い換え類義</t>
+        </is>
+      </c>
+      <c r="C31" s="40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D31" s="40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E31" s="40" t="n">
+        <v>2145</v>
+      </c>
+      <c r="F31" s="72" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="G31" s="43" t="inlineStr"/>
+      <c r="H31" s="71" t="inlineStr">
+        <is>
+          <t>母数2145中1000問＝46%。語彙単語(2145)の約54%が「言い換え類義」で一度も出題されない。増産か別大問で補完を。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="40" t="inlineStr"/>
+      <c r="B32" s="40" t="inlineStr">
+        <is>
           <t>用法</t>
         </is>
       </c>
-      <c r="C23" s="40" t="n">
-        <v>153</v>
-      </c>
-      <c r="D23" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="43" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
+      <c r="C32" s="40" t="n">
+        <v>150</v>
+      </c>
+      <c r="D32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="43" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
         <is>
           <t>用法は場面/例文単位で単語IDを持たない＝カバー率の対象外（欠落ではない）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="48" t="inlineStr">
-        <is>
-          <t>漢字単語(166)</t>
-        </is>
-      </c>
-      <c r="B24" s="40" t="inlineStr">
-        <is>
-          <t>漢字読み</t>
-        </is>
-      </c>
-      <c r="C24" s="40" t="n">
-        <v>448</v>
-      </c>
-      <c r="D24" s="40" t="n">
-        <v>103</v>
-      </c>
-      <c r="E24" s="40" t="n">
-        <v>166</v>
-      </c>
-      <c r="F24" s="73" t="inlineStr">
-        <is>
-          <t>62%</t>
-        </is>
-      </c>
-      <c r="G24" s="43" t="inlineStr">
-        <is>
-          <t>0:63／1:0／2:103</t>
-        </is>
-      </c>
-      <c r="H24" s="71" t="inlineStr">
-        <is>
-          <t>カバー率62%。漢字単語(166)の約38%が「漢字読み」で一度も出題されない。余裕を持って補いたい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="40" t="inlineStr"/>
-      <c r="B25" s="40" t="inlineStr">
-        <is>
-          <t>表記</t>
-        </is>
-      </c>
-      <c r="C25" s="40" t="n">
-        <v>492</v>
-      </c>
-      <c r="D25" s="40" t="n">
-        <v>103</v>
-      </c>
-      <c r="E25" s="40" t="n">
-        <v>166</v>
-      </c>
-      <c r="F25" s="73" t="inlineStr">
-        <is>
-          <t>62%</t>
-        </is>
-      </c>
-      <c r="G25" s="43" t="inlineStr"/>
-      <c r="H25" s="71" t="inlineStr">
-        <is>
-          <t>カバー率62%。漢字単語(166)の約38%が「表記」で一度も出題されない。余裕を持って補いたい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="48" t="inlineStr">
-        <is>
-          <t>文法単語(131)</t>
-        </is>
-      </c>
-      <c r="B26" s="40" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="48" t="inlineStr">
+        <is>
+          <t>文法単語(186)</t>
+        </is>
+      </c>
+      <c r="B33" s="40" t="inlineStr">
         <is>
           <t>文法形式(穴埋め)</t>
         </is>
       </c>
-      <c r="C26" s="40" t="n">
-        <v>357</v>
-      </c>
-      <c r="D26" s="40" t="n">
-        <v>125</v>
-      </c>
-      <c r="E26" s="40" t="n">
-        <v>131</v>
-      </c>
-      <c r="F26" s="70" t="inlineStr">
+      <c r="C33" s="40" t="n">
+        <v>443</v>
+      </c>
+      <c r="D33" s="40" t="n">
+        <v>177</v>
+      </c>
+      <c r="E33" s="40" t="n">
+        <v>186</v>
+      </c>
+      <c r="F33" s="70" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="G26" s="43" t="inlineStr">
-        <is>
-          <t>0:0／1:16／2:75／3:40</t>
-        </is>
-      </c>
-      <c r="H26" s="71" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="40" t="inlineStr"/>
-      <c r="B27" s="40" t="inlineStr">
-        <is>
-          <t>語の並べ替え</t>
-        </is>
-      </c>
-      <c r="C27" s="40" t="n">
-        <v>214</v>
-      </c>
-      <c r="D27" s="40" t="n">
-        <v>111</v>
-      </c>
-      <c r="E27" s="40" t="n">
-        <v>131</v>
-      </c>
-      <c r="F27" s="70" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="G27" s="43" t="inlineStr"/>
-      <c r="H27" s="71" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="40" t="inlineStr"/>
-      <c r="B28" s="40" t="inlineStr">
-        <is>
-          <t>文章の文法</t>
-        </is>
-      </c>
-      <c r="C28" s="40" t="n">
-        <v>250</v>
-      </c>
-      <c r="D28" s="40" t="n">
-        <v>101</v>
-      </c>
-      <c r="E28" s="40" t="n">
-        <v>131</v>
-      </c>
-      <c r="F28" s="73" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="G28" s="43" t="inlineStr"/>
-      <c r="H28" s="71" t="inlineStr">
-        <is>
-          <t>カバー率77%。文法単語(131)の約23%が「文章の文法」で一度も出題されない。余裕を持って補いたい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="G29" s="38" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="45" t="inlineStr">
-        <is>
-          <t>■ N3</t>
-        </is>
-      </c>
-      <c r="G30" s="38" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="46" t="inlineStr">
-        <is>
-          <t>単語種別</t>
-        </is>
-      </c>
-      <c r="B31" s="46" t="inlineStr">
-        <is>
-          <t>大問</t>
-        </is>
-      </c>
-      <c r="C31" s="46" t="inlineStr">
-        <is>
-          <t>問題数</t>
-        </is>
-      </c>
-      <c r="D31" s="46" t="inlineStr">
-        <is>
-          <t>カバー数</t>
-        </is>
-      </c>
-      <c r="E31" s="46" t="inlineStr">
-        <is>
-          <t>母数</t>
-        </is>
-      </c>
-      <c r="F31" s="46" t="inlineStr">
-        <is>
-          <t>カバー率</t>
-        </is>
-      </c>
-      <c r="G31" s="47" t="inlineStr">
-        <is>
-          <t>1単語が紐づく大問数の分布</t>
-        </is>
-      </c>
-      <c r="H31" s="69" t="inlineStr">
-        <is>
-          <t>点検メモ</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="48" t="inlineStr">
-        <is>
-          <t>語彙単語(2145)</t>
-        </is>
-      </c>
-      <c r="B32" s="40" t="inlineStr">
-        <is>
-          <t>漢字読み</t>
-        </is>
-      </c>
-      <c r="C32" s="40" t="n">
-        <v>1398</v>
-      </c>
-      <c r="D32" s="40" t="n">
-        <v>1398</v>
-      </c>
-      <c r="E32" s="40" t="n">
-        <v>1896</v>
-      </c>
-      <c r="F32" s="73" t="inlineStr">
-        <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="G32" s="43" t="inlineStr">
-        <is>
-          <t>0:42／1:321／2:357／3:720／4:705</t>
-        </is>
-      </c>
-      <c r="H32" s="71" t="inlineStr">
-        <is>
-          <t>カバー率73%。語彙単語(2145)の約27%が「漢字読み」で一度も出題されない。余裕を持って補いたい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="40" t="inlineStr"/>
-      <c r="B33" s="40" t="inlineStr">
-        <is>
-          <t>表記</t>
-        </is>
-      </c>
-      <c r="C33" s="40" t="n">
-        <v>1527</v>
-      </c>
-      <c r="D33" s="40" t="n">
-        <v>1527</v>
-      </c>
-      <c r="E33" s="40" t="n">
-        <v>1896</v>
-      </c>
-      <c r="F33" s="70" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="G33" s="43" t="inlineStr"/>
+      <c r="G33" s="43" t="inlineStr">
+        <is>
+          <t>0:1／1:36／2:142／3:7</t>
+        </is>
+      </c>
       <c r="H33" s="71" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="40" t="inlineStr"/>
       <c r="B34" s="40" t="inlineStr">
         <is>
-          <t>文脈規定</t>
+          <t>語の並べ替え</t>
         </is>
       </c>
       <c r="C34" s="40" t="n">
-        <v>2090</v>
+        <v>308</v>
       </c>
       <c r="D34" s="40" t="n">
-        <v>2090</v>
+        <v>157</v>
       </c>
       <c r="E34" s="40" t="n">
-        <v>2145</v>
+        <v>186</v>
       </c>
       <c r="F34" s="70" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="G34" s="43" t="inlineStr"/>
@@ -5872,220 +5774,35 @@
       <c r="A35" s="40" t="inlineStr"/>
       <c r="B35" s="40" t="inlineStr">
         <is>
-          <t>言い換え類義</t>
+          <t>文章の文法</t>
         </is>
       </c>
       <c r="C35" s="40" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="D35" s="40" t="n">
-        <v>1000</v>
+        <v>126</v>
       </c>
       <c r="E35" s="40" t="n">
-        <v>2145</v>
-      </c>
-      <c r="F35" s="72" t="inlineStr">
-        <is>
-          <t>46%</t>
+        <v>186</v>
+      </c>
+      <c r="F35" s="73" t="inlineStr">
+        <is>
+          <t>68%</t>
         </is>
       </c>
       <c r="G35" s="43" t="inlineStr"/>
       <c r="H35" s="71" t="inlineStr">
         <is>
-          <t>母数2145中1000問＝46%。語彙単語(2145)の約54%が「言い換え類義」で一度も出題されない。増産か別大問で補完を。</t>
+          <t>カバー率68%。文法単語(186)の約32%が「文章の文法」で一度も出題されない。余裕を持って補いたい。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="40" t="inlineStr"/>
-      <c r="B36" s="40" t="inlineStr">
-        <is>
-          <t>用法</t>
-        </is>
-      </c>
-      <c r="C36" s="40" t="n">
-        <v>150</v>
-      </c>
-      <c r="D36" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="43" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>用法は場面/例文単位で単語IDを持たない＝カバー率の対象外（欠落ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="48" t="inlineStr">
-        <is>
-          <t>漢字単語(367)</t>
-        </is>
-      </c>
-      <c r="B37" s="40" t="inlineStr">
-        <is>
-          <t>漢字読み</t>
-        </is>
-      </c>
-      <c r="C37" s="40" t="n">
-        <v>1398</v>
-      </c>
-      <c r="D37" s="40" t="n">
-        <v>312</v>
-      </c>
-      <c r="E37" s="40" t="n">
-        <v>367</v>
-      </c>
-      <c r="F37" s="70" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="G37" s="43" t="inlineStr">
-        <is>
-          <t>0:55／1:0／2:312</t>
-        </is>
-      </c>
-      <c r="H37" s="71" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="40" t="inlineStr"/>
-      <c r="B38" s="40" t="inlineStr">
-        <is>
-          <t>表記</t>
-        </is>
-      </c>
-      <c r="C38" s="40" t="n">
-        <v>1527</v>
-      </c>
-      <c r="D38" s="40" t="n">
-        <v>312</v>
-      </c>
-      <c r="E38" s="40" t="n">
-        <v>367</v>
-      </c>
-      <c r="F38" s="70" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="G38" s="43" t="inlineStr"/>
-      <c r="H38" s="71" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="48" t="inlineStr">
-        <is>
-          <t>文法単語(186)</t>
-        </is>
-      </c>
-      <c r="B39" s="40" t="inlineStr">
-        <is>
-          <t>文法形式(穴埋め)</t>
-        </is>
-      </c>
-      <c r="C39" s="40" t="n">
-        <v>443</v>
-      </c>
-      <c r="D39" s="40" t="n">
-        <v>177</v>
-      </c>
-      <c r="E39" s="40" t="n">
-        <v>186</v>
-      </c>
-      <c r="F39" s="70" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="G39" s="43" t="inlineStr">
-        <is>
-          <t>0:1／1:36／2:142／3:7</t>
-        </is>
-      </c>
-      <c r="H39" s="71" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="40" t="inlineStr"/>
-      <c r="B40" s="40" t="inlineStr">
-        <is>
-          <t>語の並べ替え</t>
-        </is>
-      </c>
-      <c r="C40" s="40" t="n">
-        <v>308</v>
-      </c>
-      <c r="D40" s="40" t="n">
-        <v>157</v>
-      </c>
-      <c r="E40" s="40" t="n">
-        <v>186</v>
-      </c>
-      <c r="F40" s="70" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="G40" s="43" t="inlineStr"/>
-      <c r="H40" s="71" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="40" t="inlineStr"/>
-      <c r="B41" s="40" t="inlineStr">
-        <is>
-          <t>文章の文法</t>
-        </is>
-      </c>
-      <c r="C41" s="40" t="n">
-        <v>250</v>
-      </c>
-      <c r="D41" s="40" t="n">
-        <v>126</v>
-      </c>
-      <c r="E41" s="40" t="n">
-        <v>186</v>
-      </c>
-      <c r="F41" s="73" t="inlineStr">
-        <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="G41" s="43" t="inlineStr"/>
-      <c r="H41" s="71" t="inlineStr">
-        <is>
-          <t>カバー率68%。文法単語(186)の約32%が「文章の文法」で一度も出題されない。余裕を持って補いたい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="G42" s="38" t="n"/>
-    </row>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" s="15" t="inlineStr">
+      <c r="G36" s="38" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="単語×大問カバー率" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解 骨組みパラメータ分布" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解攻略耐性分析" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学習ドリル×カバー率" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大問別まとめ'!$A$1:$J$1</definedName>
@@ -3019,6 +3020,738 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>学習ドリル×カバー率（学習タブ・各ドリルがID紐づけで対象にできる項目の広さ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>※全ID母数=レベル内の全項目(語彙数/文法点数[n5-g-92除外]/漢字数)。真の母数=そのドリルで「そもそも作れる」項目数(カタカナ語・分離型文法など"永久に不可能"を除く)＝真のカバー率が実力。試験タブの大問は別シート「単語×大問カバー率」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>■ N5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="69" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="69" t="inlineStr">
+        <is>
+          <t>ドリル</t>
+        </is>
+      </c>
+      <c r="C5" s="69" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="D5" s="69" t="inlineStr">
+        <is>
+          <t>全ID母数</t>
+        </is>
+      </c>
+      <c r="E5" s="69" t="inlineStr">
+        <is>
+          <t>全IDカバー率</t>
+        </is>
+      </c>
+      <c r="F5" s="69" t="inlineStr">
+        <is>
+          <t>真の母数</t>
+        </is>
+      </c>
+      <c r="G5" s="69" t="inlineStr">
+        <is>
+          <t>真のカバー率</t>
+        </is>
+      </c>
+      <c r="H5" s="69" t="inlineStr">
+        <is>
+          <t>点検メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>語彙パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>606</v>
+      </c>
+      <c r="D6" t="n">
+        <v>723</v>
+      </c>
+      <c r="E6" s="76" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>606</v>
+      </c>
+      <c r="G6" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="71" t="inlineStr">
+        <is>
+          <t>見かけ84%だが真の100%＝差16ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>聞き取り(語彙)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>681</v>
+      </c>
+      <c r="D7" t="n">
+        <v>723</v>
+      </c>
+      <c r="E7" s="76" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>681</v>
+      </c>
+      <c r="G7" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="71" t="inlineStr">
+        <is>
+          <t>見かけ94%だが真の100%＝差6ptは"作れない天井"。読みを聞いて単語を選ぶ。非自立語(接辞/助詞)・波ダッシュ語のみ対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>意味を選ぶ(受容)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>91</v>
+      </c>
+      <c r="D8" t="n">
+        <v>91</v>
+      </c>
+      <c r="E8" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>91</v>
+      </c>
+      <c r="G8" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="71" t="inlineStr">
+        <is>
+          <t>文法点の意味を4択。意味を持つ全点が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>文法パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>67</v>
+      </c>
+      <c r="D9" t="n">
+        <v>91</v>
+      </c>
+      <c r="E9" s="75" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>67</v>
+      </c>
+      <c r="G9" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="71" t="inlineStr">
+        <is>
+          <t>見かけ74%だが真の100%＝差26ptは"作れない天井"。例文の空所に文法語をタイルで作る。例文に表層形が一意に1回出る点のみ対象(0回/複数回は空所位置が曖昧で除外)＝構造的に低い。上げたい場合は例文を「表層形が1回だけ出る」形に整えるか、対象点の例文を追加する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>聞き取り(漢字)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>79</v>
+      </c>
+      <c r="D10" t="n">
+        <v>79</v>
+      </c>
+      <c r="E10" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>79</v>
+      </c>
+      <c r="G10" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="71" t="inlineStr">
+        <is>
+          <t>読みを聞いて漢字を選ぶ。drillレップを持つ当該級の漢字が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>■ N4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="69" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B13" s="69" t="inlineStr">
+        <is>
+          <t>ドリル</t>
+        </is>
+      </c>
+      <c r="C13" s="69" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="D13" s="69" t="inlineStr">
+        <is>
+          <t>全ID母数</t>
+        </is>
+      </c>
+      <c r="E13" s="69" t="inlineStr">
+        <is>
+          <t>全IDカバー率</t>
+        </is>
+      </c>
+      <c r="F13" s="69" t="inlineStr">
+        <is>
+          <t>真の母数</t>
+        </is>
+      </c>
+      <c r="G13" s="69" t="inlineStr">
+        <is>
+          <t>真のカバー率</t>
+        </is>
+      </c>
+      <c r="H13" s="69" t="inlineStr">
+        <is>
+          <t>点検メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>語彙パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>576</v>
+      </c>
+      <c r="D14" t="n">
+        <v>673</v>
+      </c>
+      <c r="E14" s="76" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>576</v>
+      </c>
+      <c r="G14" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H14" s="71" t="inlineStr">
+        <is>
+          <t>見かけ86%だが真の100%＝差14ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>聞き取り(語彙)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>643</v>
+      </c>
+      <c r="D15" t="n">
+        <v>673</v>
+      </c>
+      <c r="E15" s="76" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>643</v>
+      </c>
+      <c r="G15" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="71" t="inlineStr">
+        <is>
+          <t>見かけ96%だが真の100%＝差4ptは"作れない天井"。読みを聞いて単語を選ぶ。非自立語(接辞/助詞)・波ダッシュ語のみ対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>意味を選ぶ(受容)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>131</v>
+      </c>
+      <c r="D16" t="n">
+        <v>131</v>
+      </c>
+      <c r="E16" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>131</v>
+      </c>
+      <c r="G16" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H16" s="71" t="inlineStr">
+        <is>
+          <t>文法点の意味を4択。意味を持つ全点が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>文法パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>113</v>
+      </c>
+      <c r="D17" t="n">
+        <v>131</v>
+      </c>
+      <c r="E17" s="76" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>114</v>
+      </c>
+      <c r="G17" s="76" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="H17" s="71" t="inlineStr">
+        <is>
+          <t>見かけ86%だが真の99%＝差13ptは"作れない天井"。例文の空所に文法語をタイルで作る。例文に表層形が一意に1回出る点のみ対象(0回/複数回は空所位置が曖昧で除外)＝構造的に低い。上げたい場合は例文を「表層形が1回だけ出る」形に整えるか、対象点の例文を追加する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聞き取り(漢字)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>166</v>
+      </c>
+      <c r="D18" t="n">
+        <v>166</v>
+      </c>
+      <c r="E18" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>166</v>
+      </c>
+      <c r="G18" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="71" t="inlineStr">
+        <is>
+          <t>読みを聞いて漢字を選ぶ。drillレップを持つ当該級の漢字が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>■ N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="69" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B21" s="69" t="inlineStr">
+        <is>
+          <t>ドリル</t>
+        </is>
+      </c>
+      <c r="C21" s="69" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="D21" s="69" t="inlineStr">
+        <is>
+          <t>全ID母数</t>
+        </is>
+      </c>
+      <c r="E21" s="69" t="inlineStr">
+        <is>
+          <t>全IDカバー率</t>
+        </is>
+      </c>
+      <c r="F21" s="69" t="inlineStr">
+        <is>
+          <t>真の母数</t>
+        </is>
+      </c>
+      <c r="G21" s="69" t="inlineStr">
+        <is>
+          <t>真のカバー率</t>
+        </is>
+      </c>
+      <c r="H21" s="69" t="inlineStr">
+        <is>
+          <t>点検メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>語彙パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1963</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2145</v>
+      </c>
+      <c r="E22" s="76" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1963</v>
+      </c>
+      <c r="G22" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H22" s="71" t="inlineStr">
+        <is>
+          <t>見かけ92%だが真の100%＝差8ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>聞き取り(語彙)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2143</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2145</v>
+      </c>
+      <c r="E23" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2143</v>
+      </c>
+      <c r="G23" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="71" t="inlineStr">
+        <is>
+          <t>読みを聞いて単語を選ぶ。非自立語(接辞/助詞)・波ダッシュ語のみ対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>意味を選ぶ(受容)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>186</v>
+      </c>
+      <c r="D24" t="n">
+        <v>186</v>
+      </c>
+      <c r="E24" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>186</v>
+      </c>
+      <c r="G24" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="71" t="inlineStr">
+        <is>
+          <t>文法点の意味を4択。意味を持つ全点が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>文法パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>167</v>
+      </c>
+      <c r="D25" t="n">
+        <v>186</v>
+      </c>
+      <c r="E25" s="76" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>169</v>
+      </c>
+      <c r="G25" s="76" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="H25" s="71" t="inlineStr">
+        <is>
+          <t>見かけ90%だが真の99%＝差9ptは"作れない天井"。例文の空所に文法語をタイルで作る。例文に表層形が一意に1回出る点のみ対象(0回/複数回は空所位置が曖昧で除外)＝構造的に低い。上げたい場合は例文を「表層形が1回だけ出る」形に整えるか、対象点の例文を追加する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>聞き取り(漢字)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>367</v>
+      </c>
+      <c r="D26" t="n">
+        <v>367</v>
+      </c>
+      <c r="E26" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>367</v>
+      </c>
+      <c r="G26" s="76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H26" s="71" t="inlineStr">
+        <is>
+          <t>読みを聞いて漢字を選ぶ。drillレップを持つ当該級の漢字が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>凡例：緑=問題なし(≥80%) ／ 黄=気になる(60-79%) ／ 赤=危険(&lt;60%)。カバー率が2つあるのは"天井"のあるドリル＝真のカバー率で判断。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5142,15 +5875,26 @@
           <t>用法</t>
         </is>
       </c>
-      <c r="C10" s="40" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="D10" s="40" t="inlineStr"/>
-      <c r="E10" s="40" t="inlineStr"/>
-      <c r="F10" s="40" t="inlineStr"/>
+      <c r="C10" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="40" t="n">
+        <v>723</v>
+      </c>
+      <c r="F10" s="72" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="G10" s="43" t="inlineStr"/>
+      <c r="H10" s="71" t="inlineStr">
+        <is>
+          <t>vocabId紐づけ済で測定可能に。用法は語を選ばず作れる(天井なし)＝真のカバー率≒全ID。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="48" t="inlineStr">
@@ -5409,27 +6153,23 @@
         </is>
       </c>
       <c r="C21" s="40" t="n">
-        <v>153</v>
-      </c>
-      <c r="D21" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>166</v>
+      </c>
+      <c r="D21" s="40" t="n">
+        <v>155</v>
+      </c>
+      <c r="E21" s="40" t="n">
+        <v>673</v>
+      </c>
+      <c r="F21" s="72" t="inlineStr">
+        <is>
+          <t>23%</t>
         </is>
       </c>
       <c r="G21" s="43" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>用法は場面/例文単位で単語IDを持たない＝カバー率の対象外（欠落ではない）</t>
+      <c r="H21" s="71" t="inlineStr">
+        <is>
+          <t>vocabId紐づけ済で測定可能に。用法は語を選ばず作れる(天井なし)＝真のカバー率≒全ID。</t>
         </is>
       </c>
     </row>
@@ -5690,27 +6430,23 @@
         </is>
       </c>
       <c r="C32" s="40" t="n">
-        <v>150</v>
-      </c>
-      <c r="D32" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F32" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>94</v>
+      </c>
+      <c r="D32" s="40" t="n">
+        <v>94</v>
+      </c>
+      <c r="E32" s="40" t="n">
+        <v>2145</v>
+      </c>
+      <c r="F32" s="72" t="inlineStr">
+        <is>
+          <t>4%</t>
         </is>
       </c>
       <c r="G32" s="43" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>用法は場面/例文単位で単語IDを持たない＝カバー率の対象外（欠落ではない）</t>
+      <c r="H32" s="71" t="inlineStr">
+        <is>
+          <t>vocabId紐づけ済で測定可能に。用法は語を選ばず作れる(天井なし)＝真のカバー率≒全ID。 ※N3は約40語がvocabマスタ未収録で測定外。</t>
         </is>
       </c>
     </row>
@@ -5801,6 +6537,19 @@
     <row r="36">
       <c r="G36" s="38" t="n"/>
     </row>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="15" t="inlineStr">
         <is>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -112,8 +112,11 @@
     <font>
       <color rgb="009C0006"/>
     </font>
+    <font>
+      <color rgb="00808080"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -230,6 +233,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -329,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -534,6 +542,17 @@
     <xf numFmtId="0" fontId="17" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5678,7 +5697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5702,7 +5721,7 @@
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>※用法は場面/例文単位でvocabId無し＝語カバー測定不可。漢字は語彙に統合済(漢字カバー行は廃止・2026-08-22)。</t>
+          <t>※用法は場面/例文単位でvocabId無し＝語カバー測定不可。漢字は語彙に統合済(漢字カバー行は廃止・2026-08-22)。言い換え類義は真の母数(言い換え可能語)列を追加(2026-08-23)＝真のカバー率で判断。</t>
         </is>
       </c>
       <c r="G2" s="38" t="n"/>
@@ -5759,6 +5778,16 @@
           <t>点検メモ</t>
         </is>
       </c>
+      <c r="I5" s="86" t="inlineStr">
+        <is>
+          <t>真の母数</t>
+        </is>
+      </c>
+      <c r="J5" s="86" t="inlineStr">
+        <is>
+          <t>真のカバー率</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="48" t="inlineStr">
@@ -5790,7 +5819,11 @@
           <t>0:46／1:121／2:90／3:355／4:111</t>
         </is>
       </c>
-      <c r="H6" s="71" t="n"/>
+      <c r="H6" s="71" t="inlineStr">
+        <is>
+          <t>漢字読み・表記＝「その漢字をどう読む／どう書く」を問う大問。漢字を含む語でしか作れません。N5の723語のうち、かな・カタカナだけの語（例：あります・きれい・テレビ・ゆっくり）約160語には漢字形が無いので、この2大問の母数から自動で外れ、563語になります。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="40" t="inlineStr"/>
@@ -5810,11 +5843,15 @@
       </c>
       <c r="F7" s="70" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="G7" s="43" t="inlineStr"/>
-      <c r="H7" s="71" t="n"/>
+      <c r="H7" s="71" t="inlineStr">
+        <is>
+          <t>漢字読み・表記＝「その漢字をどう読む／どう書く」を問う大問。漢字を含む語でしか作れません。N5の723語のうち、かな・カタカナだけの語（例：あります・きれい・テレビ・ゆっくり）約160語には漢字形が無いので、この2大問の母数から自動で外れ、563語になります。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="40" t="inlineStr"/>
@@ -5834,7 +5871,7 @@
       </c>
       <c r="F8" s="70" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="G8" s="43" t="inlineStr"/>
@@ -5848,51 +5885,59 @@
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>148</v>
+        <v>245</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>148</v>
+        <v>245</v>
       </c>
       <c r="E9" s="40" t="n">
         <v>723</v>
       </c>
       <c r="F9" s="72" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="G9" s="43" t="inlineStr"/>
       <c r="H9" s="71" t="inlineStr">
         <is>
-          <t>母数723中148問＝20%。語彙単語(723)の約80%が「言い換え類義」で一度も出題されない。増産か別大問で補完を。</t>
+          <t>全ID 245/723=34%。真の母数=392語(言い換え可能=近い類義語がある語)中 245語=62%。全ID母数には数詞/あいさつ/固有名/類義語のない具体名詞(カメラ等)が含まれ言い換え不可のため、真のカバー率が実力。カタカナ語は類義語がある語のみ計上(ルール→規則等)。分類正本=iikaePossible.json。</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>392</v>
+      </c>
+      <c r="J9" s="75" t="inlineStr">
+        <is>
+          <t>62%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr"/>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="A10" s="87" t="inlineStr"/>
+      <c r="B10" s="87" t="inlineStr">
         <is>
           <t>用法</t>
         </is>
       </c>
-      <c r="C10" s="40" t="n">
+      <c r="C10" s="87" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="40" t="n">
+      <c r="D10" s="87" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="40" t="n">
+      <c r="E10" s="87" t="n">
         <v>723</v>
       </c>
-      <c r="F10" s="72" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G10" s="43" t="inlineStr"/>
-      <c r="H10" s="71" t="inlineStr">
-        <is>
-          <t>vocabId紐づけ済で測定可能に。用法は語を選ばず作れる(天井なし)＝真のカバー率≒全ID。</t>
+      <c r="F10" s="88" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="G10" s="89" t="inlineStr"/>
+      <c r="H10" s="90" t="inlineStr">
+        <is>
+          <t>N5の文字・語彙に「用法」大問は無い(公式試験対象外)。アプリ予想得点も既にN5用法を除外済み。</t>
         </is>
       </c>
     </row>
@@ -6036,6 +6081,16 @@
           <t>点検メモ</t>
         </is>
       </c>
+      <c r="I16" s="86" t="inlineStr">
+        <is>
+          <t>真の母数</t>
+        </is>
+      </c>
+      <c r="J16" s="86" t="inlineStr">
+        <is>
+          <t>真のカバー率</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="48" t="inlineStr">
@@ -6059,7 +6114,7 @@
       </c>
       <c r="F17" s="70" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="G17" s="43" t="inlineStr">
@@ -6077,17 +6132,17 @@
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>492</v>
+        <v>450</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>492</v>
+        <v>450</v>
       </c>
       <c r="E18" s="40" t="n">
         <v>542</v>
       </c>
       <c r="F18" s="70" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="G18" s="43" t="inlineStr"/>
@@ -6111,7 +6166,7 @@
       </c>
       <c r="F19" s="70" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="G19" s="43" t="inlineStr"/>
@@ -6125,23 +6180,31 @@
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>185</v>
+        <v>285</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>185</v>
+        <v>285</v>
       </c>
       <c r="E20" s="40" t="n">
         <v>673</v>
       </c>
       <c r="F20" s="72" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="G20" s="43" t="inlineStr"/>
       <c r="H20" s="71" t="inlineStr">
         <is>
-          <t>母数673中185問＝27%。語彙単語(673)の約73%が「言い換え類義」で一度も出題されない。増産か別大問で補完を。</t>
+          <t>全ID 285/673=42%。真の母数=484語(言い換え可能=近い類義語がある語)中 285語=59%。全ID母数には数詞/あいさつ/固有名/類義語のない具体名詞(カメラ等)が含まれ言い換え不可のため、真のカバー率が実力。カタカナ語は類義語がある語のみ計上(ルール→規則等)。分類正本=iikaePossible.json。</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>484</v>
+      </c>
+      <c r="J20" s="77" t="inlineStr">
+        <is>
+          <t>59%</t>
         </is>
       </c>
     </row>
@@ -6237,17 +6300,17 @@
         </is>
       </c>
       <c r="C24" s="40" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D24" s="40" t="n">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="E24" s="40" t="n">
         <v>131</v>
       </c>
-      <c r="F24" s="73" t="inlineStr">
-        <is>
-          <t>77%</t>
+      <c r="F24" s="70" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="G24" s="43" t="inlineStr"/>
@@ -6309,6 +6372,16 @@
           <t>点検メモ</t>
         </is>
       </c>
+      <c r="I27" s="86" t="inlineStr">
+        <is>
+          <t>真の母数</t>
+        </is>
+      </c>
+      <c r="J27" s="86" t="inlineStr">
+        <is>
+          <t>真のカバー率</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="48" t="inlineStr">
@@ -6332,7 +6405,7 @@
       </c>
       <c r="F28" s="73" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="G28" s="43" t="inlineStr">
@@ -6354,17 +6427,17 @@
         </is>
       </c>
       <c r="C29" s="40" t="n">
-        <v>1527</v>
+        <v>1400</v>
       </c>
       <c r="D29" s="40" t="n">
-        <v>1527</v>
+        <v>1400</v>
       </c>
       <c r="E29" s="40" t="n">
         <v>1896</v>
       </c>
-      <c r="F29" s="70" t="inlineStr">
-        <is>
-          <t>80%</t>
+      <c r="F29" s="73" t="inlineStr">
+        <is>
+          <t>74%</t>
         </is>
       </c>
       <c r="G29" s="43" t="inlineStr"/>
@@ -6402,23 +6475,31 @@
         </is>
       </c>
       <c r="C31" s="40" t="n">
-        <v>1000</v>
+        <v>1099</v>
       </c>
       <c r="D31" s="40" t="n">
-        <v>1000</v>
+        <v>1099</v>
       </c>
       <c r="E31" s="40" t="n">
         <v>2145</v>
       </c>
       <c r="F31" s="72" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="G31" s="43" t="inlineStr"/>
       <c r="H31" s="71" t="inlineStr">
         <is>
-          <t>母数2145中1000問＝46%。語彙単語(2145)の約54%が「言い換え類義」で一度も出題されない。増産か別大問で補完を。</t>
+          <t>全ID 1099/2145=51%。真の母数=1776語(言い換え可能=近い類義語がある語)中 1099語=62%。全ID母数には数詞/あいさつ/固有名/類義語のない具体名詞(カメラ等)が含まれ言い換え不可のため、真のカバー率が実力。カタカナ語は類義語がある語のみ計上(ルール→規則等)。分類正本=iikaePossible.json。</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1776</v>
+      </c>
+      <c r="J31" s="75" t="inlineStr">
+        <is>
+          <t>62%</t>
         </is>
       </c>
     </row>
@@ -6514,17 +6595,17 @@
         </is>
       </c>
       <c r="C35" s="40" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="D35" s="40" t="n">
-        <v>126</v>
+        <v>186</v>
       </c>
       <c r="E35" s="40" t="n">
         <v>186</v>
       </c>
-      <c r="F35" s="73" t="inlineStr">
-        <is>
-          <t>68%</t>
+      <c r="F35" s="70" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="G35" s="43" t="inlineStr"/>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="D3" s="13" t="n">
-        <v>463</v>
+        <v>146</v>
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
@@ -1155,11 +1155,11 @@
         <v>7</v>
       </c>
       <c r="H3" s="14" t="n">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>3:463</t>
+          <t>3:146</t>
         </is>
       </c>
       <c r="J3" s="13" t="inlineStr">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="D4" s="13" t="n">
-        <v>448</v>
+        <v>331</v>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
@@ -1201,11 +1201,11 @@
         <v>9</v>
       </c>
       <c r="H4" s="14" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>3:448</t>
+          <t>3:331</t>
         </is>
       </c>
       <c r="J4" s="13" t="inlineStr">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>1398</v>
+        <v>1944</v>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
@@ -1247,11 +1247,11 @@
         <v>8</v>
       </c>
       <c r="H5" s="14" t="n">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>3:1398</t>
+          <t>3:1944</t>
         </is>
       </c>
       <c r="J5" s="13" t="inlineStr">
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>527</v>
+        <v>210</v>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -1293,11 +1293,11 @@
         <v>5</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>3:527</t>
+          <t>3:210</t>
         </is>
       </c>
       <c r="J6" s="13" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>492</v>
+        <v>332</v>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -1339,11 +1339,11 @@
         <v>6</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>3:492</t>
+          <t>3:332</t>
         </is>
       </c>
       <c r="J7" s="13" t="inlineStr">
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="D8" s="13" t="n">
-        <v>1527</v>
+        <v>1944</v>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
@@ -1385,11 +1385,11 @@
         <v>6</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>254</v>
+        <v>324</v>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>3:1527</t>
+          <t>3:1944</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
@@ -3170,8 +3170,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50"/>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
@@ -3186,7 +3184,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
@@ -3223,7 +3220,7 @@
         </is>
       </c>
       <c r="B56" s="21" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C56" s="21" t="n">
         <v>30</v>
@@ -3280,7 +3277,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="20" t="inlineStr">
         <is>
@@ -3317,7 +3313,7 @@
         </is>
       </c>
       <c r="B63" s="14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C63" s="14" t="n">
         <v>18</v>
@@ -3326,7 +3322,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="22" t="inlineStr">
         <is>
@@ -3334,8 +3329,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
-    <row r="67"/>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
@@ -3350,7 +3343,6 @@
         </is>
       </c>
     </row>
-    <row r="70"/>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
@@ -3381,7 +3373,6 @@
         </is>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="20" t="inlineStr">
         <is>
@@ -3777,8 +3768,6 @@
       </c>
       <c r="I16" s="29" t="n"/>
     </row>
-    <row r="17"/>
-    <row r="18"/>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
@@ -3877,37 +3866,18 @@
         </is>
       </c>
       <c r="C25" s="26" t="n">
-        <v>521</v>
-      </c>
-      <c r="D25" s="26" t="n">
-        <v>521</v>
-      </c>
-      <c r="E25" s="26" t="n">
-        <v>719</v>
-      </c>
-      <c r="F25" s="36" t="inlineStr">
-        <is>
-          <t>72%</t>
-        </is>
-      </c>
-      <c r="G25" s="29" t="inlineStr">
-        <is>
-          <t>0:46／1:121／2:90／3:355／4:111</t>
-        </is>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="D25" s="26" t="n"/>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="29" t="n"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>真の母数=出題級N5の漢字語彙(vocabKanjiClass)。2026-08-24 助数詞・熟字訓を丁寧に増作し真99%。残りは読み非一意でスキップ(四/何〜/御〜/〜君/〜様/〜月/〜町/〜観/〜敗)。</t>
-        </is>
-      </c>
-      <c r="I25" s="34" t="n">
-        <v>148</v>
-      </c>
-      <c r="J25" s="37" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
+          <t>例外カウント：漢字級(testLevel=MAX)で出題。語彙母数の概念なし＝問題数のみ。</t>
+        </is>
+      </c>
+      <c r="I25" s="34" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="26" t="n"/>
@@ -3917,33 +3887,18 @@
         </is>
       </c>
       <c r="C26" s="26" t="n">
-        <v>585</v>
-      </c>
-      <c r="D26" s="26" t="n">
-        <v>585</v>
-      </c>
-      <c r="E26" s="26" t="n">
-        <v>719</v>
-      </c>
-      <c r="F26" s="36" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="26" t="n"/>
+      <c r="F26" s="26" t="n"/>
       <c r="G26" s="29" t="n"/>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>真の母数=表記も同じ出題級基準。カタカナ語は別枠(表記可)。詳細=vocabKanjiClass.json/kanjiJlptLevel.json。</t>
-        </is>
-      </c>
-      <c r="I26" s="34" t="n">
-        <v>148</v>
-      </c>
-      <c r="J26" s="37" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
+          <t>例外カウント：漢字級(testLevel=MAX)で出題。語彙母数の概念なし＝問題数のみ。</t>
+        </is>
+      </c>
+      <c r="I26" s="34" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="26" t="n"/>
@@ -4212,37 +4167,18 @@
         </is>
       </c>
       <c r="C36" s="26" t="n">
-        <v>537</v>
-      </c>
-      <c r="D36" s="26" t="n">
-        <v>537</v>
-      </c>
-      <c r="E36" s="26" t="n">
-        <v>668</v>
-      </c>
-      <c r="F36" s="36" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="G36" s="29" t="inlineStr">
-        <is>
-          <t>0:16／1:113／2:95／3:323／4:126</t>
-        </is>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="D36" s="26" t="n"/>
+      <c r="E36" s="26" t="n"/>
+      <c r="F36" s="26" t="n"/>
+      <c r="G36" s="29" t="n"/>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>真の母数=出題級N4の漢字語彙(vocabKanjiClass)。2026-08-24 助数詞・熟字訓を丁寧に増作し真99%。残りは読み非一意でスキップ(四/何〜/御〜/〜君/〜様/〜月/〜町/〜観/〜敗)。</t>
-        </is>
-      </c>
-      <c r="I36" s="34" t="n">
-        <v>333</v>
-      </c>
-      <c r="J36" s="37" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
+          <t>例外カウント：漢字級(testLevel=MAX)で出題。語彙母数の概念なし＝問題数のみ。</t>
+        </is>
+      </c>
+      <c r="I36" s="34" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="26" t="n"/>
@@ -4252,33 +4188,18 @@
         </is>
       </c>
       <c r="C37" s="26" t="n">
-        <v>538</v>
-      </c>
-      <c r="D37" s="26" t="n">
-        <v>538</v>
-      </c>
-      <c r="E37" s="26" t="n">
-        <v>668</v>
-      </c>
-      <c r="F37" s="36" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="D37" s="26" t="n"/>
+      <c r="E37" s="26" t="n"/>
+      <c r="F37" s="26" t="n"/>
       <c r="G37" s="29" t="n"/>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>真の母数=表記も同じ出題級基準。カタカナ語は別枠(表記可)。詳細=vocabKanjiClass.json/kanjiJlptLevel.json。</t>
-        </is>
-      </c>
-      <c r="I37" s="34" t="n">
-        <v>333</v>
-      </c>
-      <c r="J37" s="37" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
+          <t>例外カウント：漢字級(testLevel=MAX)で出題。語彙母数の概念なし＝問題数のみ。</t>
+        </is>
+      </c>
+      <c r="I37" s="34" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="26" t="n"/>
@@ -4543,37 +4464,18 @@
         </is>
       </c>
       <c r="C47" s="26" t="n">
-        <v>1882</v>
-      </c>
-      <c r="D47" s="26" t="n">
-        <v>1882</v>
-      </c>
-      <c r="E47" s="26" t="n">
-        <v>2145</v>
-      </c>
-      <c r="F47" s="38" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="G47" s="29" t="inlineStr">
-        <is>
-          <t>0:42／1:321／2:357／3:720／4:705</t>
-        </is>
-      </c>
+        <v>1944</v>
+      </c>
+      <c r="D47" s="26" t="n"/>
+      <c r="E47" s="26" t="n"/>
+      <c r="F47" s="26" t="n"/>
+      <c r="G47" s="29" t="n"/>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>真の母数=出題級N3の漢字語彙(vocabKanjiClass)。2026-08-24 助数詞・熟字訓を丁寧に増作し真100%。残りは読み非一意でスキップ(四/何〜/御〜/〜君/〜様/〜月/〜町/〜観/〜敗)。</t>
-        </is>
-      </c>
-      <c r="I47" s="34" t="n">
-        <v>1949</v>
-      </c>
-      <c r="J47" s="37" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
+          <t>例外カウント：漢字級(testLevel=MAX)で出題。語彙母数の概念なし＝問題数のみ。</t>
+        </is>
+      </c>
+      <c r="I47" s="34" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="26" t="n"/>
@@ -4583,33 +4485,18 @@
         </is>
       </c>
       <c r="C48" s="26" t="n">
-        <v>1882</v>
-      </c>
-      <c r="D48" s="26" t="n">
-        <v>1882</v>
-      </c>
-      <c r="E48" s="26" t="n">
-        <v>2145</v>
-      </c>
-      <c r="F48" s="38" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
+        <v>1944</v>
+      </c>
+      <c r="D48" s="26" t="n"/>
+      <c r="E48" s="26" t="n"/>
+      <c r="F48" s="26" t="n"/>
       <c r="G48" s="29" t="n"/>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>真の母数=表記も同じ出題級基準。カタカナ語は別枠(表記可)。詳細=vocabKanjiClass.json/kanjiJlptLevel.json。</t>
-        </is>
-      </c>
-      <c r="I48" s="34" t="n">
-        <v>1949</v>
-      </c>
-      <c r="J48" s="37" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
+          <t>例外カウント：漢字級(testLevel=MAX)で出題。語彙母数の概念なし＝問題数のみ。</t>
+        </is>
+      </c>
+      <c r="I48" s="34" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="26" t="n"/>
@@ -4802,19 +4689,6 @@
     <row r="55">
       <c r="G55" s="24" t="n"/>
     </row>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
     <row r="69">
       <c r="A69" s="22" t="inlineStr">
         <is>
@@ -4822,8 +4696,6 @@
         </is>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
@@ -4845,7 +4717,6 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
@@ -5075,7 +4946,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
@@ -5305,7 +5175,6 @@
         </is>
       </c>
     </row>
-    <row r="91"/>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
@@ -5535,7 +5404,6 @@
         </is>
       </c>
     </row>
-    <row r="99"/>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
@@ -5543,8 +5411,6 @@
         </is>
       </c>
     </row>
-    <row r="101"/>
-    <row r="102"/>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="9" t="inlineStr">
         <is>
@@ -5559,7 +5425,6 @@
         </is>
       </c>
     </row>
-    <row r="105"/>
     <row r="106">
       <c r="A106" s="46" t="inlineStr">
         <is>
@@ -5876,7 +5741,6 @@
         </is>
       </c>
     </row>
-    <row r="116"/>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
@@ -5941,7 +5805,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="49" t="inlineStr">
         <is>
@@ -6537,7 +6400,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="55" t="inlineStr">
         <is>
@@ -6801,7 +6663,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="58" t="inlineStr">
         <is>
@@ -6823,19 +6684,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
         <is>
@@ -6843,8 +6691,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
@@ -7345,19 +7191,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
     <row r="66">
       <c r="A66" s="22" t="inlineStr">
         <is>
@@ -7365,8 +7198,6 @@
         </is>
       </c>
     </row>
-    <row r="67"/>
-    <row r="68"/>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
@@ -8526,7 +8357,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="65" t="inlineStr">
         <is>
@@ -8562,7 +8392,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="65" t="inlineStr">
         <is>
@@ -8654,7 +8483,6 @@
       <c r="C17" s="68" t="n"/>
       <c r="D17" s="69" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="65" t="inlineStr">
         <is>
@@ -8734,7 +8562,6 @@
       </c>
       <c r="D23" s="69" t="n"/>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="65" t="inlineStr">
         <is>
@@ -8749,7 +8576,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="65" t="inlineStr">
         <is>
@@ -8841,7 +8667,6 @@
       <c r="C34" s="68" t="n"/>
       <c r="D34" s="69" t="n"/>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="79" t="inlineStr">
         <is>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -3940,31 +3940,31 @@
         </is>
       </c>
       <c r="C28" s="26" t="n">
-        <v>345</v>
+        <v>231</v>
       </c>
       <c r="D28" s="26" t="n">
-        <v>345</v>
+        <v>231</v>
       </c>
       <c r="E28" s="26" t="n">
         <v>719</v>
       </c>
       <c r="F28" s="39" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="G28" s="29" t="n"/>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>全ID 345/723=48%。真の母数=387語中 296語=76%。新規EXCEL問題(N5+100/N4+159/N3+300・未マージ)を含む。2026-08-24 言い換えEXCEL青セル削除語(N5 5/N4 16=元p=1)を真の母数から除外(iikaePossible p=0・N3は削除なし)。全ID母数には数詞/あいさつ/固有名/類義語のない具体名詞が含まれ言い換え不可。</t>
+          <t>2026-08-25 級以下監査で確定＝全問N5語彙で解ける231問。真の母数=級内で作れる語=231(=天井)。上級語のみの語はp=0へ降格。真カバー率100%。</t>
         </is>
       </c>
       <c r="I28" s="34" t="n">
-        <v>387</v>
+        <v>231</v>
       </c>
       <c r="J28" s="40" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -4241,31 +4241,31 @@
         </is>
       </c>
       <c r="C39" s="26" t="n">
-        <v>444</v>
+        <v>406</v>
       </c>
       <c r="D39" s="26" t="n">
-        <v>444</v>
+        <v>406</v>
       </c>
       <c r="E39" s="26" t="n">
         <v>668</v>
       </c>
       <c r="F39" s="36" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="G39" s="29" t="n"/>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>全ID 444/673=66%。真の母数=468語中 402語=86%。新規EXCEL問題(N5+100/N4+159/N3+300・未マージ)を含む。2026-08-24 言い換えEXCEL青セル削除語(N5 5/N4 16=元p=1)を真の母数から除外(iikaePossible p=0・N3は削除なし)。全ID母数には数詞/あいさつ/固有名/類義語のない具体名詞が含まれ言い換え不可。</t>
+          <t>2026-08-25 級以下監査で確定＝全問N4語彙で解ける406問。真の母数=級内で作れる語=406(=天井)。上級語のみの語はp=0へ降格。真カバー率100%。</t>
         </is>
       </c>
       <c r="I39" s="34" t="n">
-        <v>467</v>
+        <v>406</v>
       </c>
       <c r="J39" s="37" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -4538,23 +4538,23 @@
         </is>
       </c>
       <c r="C50" s="26" t="n">
-        <v>1399</v>
+        <v>1653</v>
       </c>
       <c r="D50" s="26" t="n">
-        <v>1399</v>
+        <v>1653</v>
       </c>
       <c r="E50" s="26" t="n">
         <v>2145</v>
       </c>
       <c r="F50" s="36" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="G50" s="29" t="n"/>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>全ID 1399/2145=65%。真の母数=1776語中 1376語=77%。新規EXCEL問題(N5+100/N4+159/N3+300・未マージ)を含む。2026-08-24 言い換えEXCEL青セル削除語(N5 5/N4 16=元p=1)を真の母数から除外(iikaePossible p=0・N3は削除なし)。全ID母数には数詞/あいさつ/固有名/類義語のない具体名詞が含まれ言い換え不可。</t>
+          <t>全ID 1399/2145=65%。真の母数=1776語中 1376語=77%。新規EXCEL問題(N5+100/N4+159/N3+300・未マージ)を含む。2026-08-24 言い換えEXCEL青セル削除語(N5 5/N4 16=元p=1)を真の母数から除外(iikaePossible p=0・N3は削除なし)。全ID母数には数詞/あいさつ/固有名/類義語のない具体名詞が含まれ言い換え不可。 2026-08-24 増作2で未カバー全語を追加(N5+36/N4+44/N3+272=352問)＋N3の不適語5件除外・20件正解修正。iikaePossible未改変(真の分子は実カバー)。 2026-08-25 QA訂正+青セル除外13を反映。</t>
         </is>
       </c>
       <c r="I50" s="34" t="n">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="J50" s="40" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>92%</t>
         </is>
       </c>
     </row>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② カバー率" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 品質・攻略耐性" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ 習得の仕組み(説明)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ 用法カバー×バランス" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -335,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -525,6 +526,12 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8708,4 +8715,169 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="66" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>用法(語の使い方) × 語彙idカバー×バランス</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="80" t="inlineStr">
+        <is>
+          <t>最終目標＝可能な限り語彙をカバー(breadth%を100%へ)。番人=src/data/usageCoverage.test.ts が「①未紐づけ0(測定可能) ②大問内で1語1問まで(集中させず広く) ③カバー数は後退させない(ラチェット)」を担保。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="80" t="inlineStr">
+        <is>
+          <t>級跨ぎ重複(同語をN4とN3の両大問で出題=冗長)＝0語。冗長は禁止せず記録のみ(復習として妥当な場合あり)＝新規作問は未カバー語を優先すると breadth が伸びる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>■ 級別サマリ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="81" t="inlineStr">
+        <is>
+          <t>級</t>
+        </is>
+      </c>
+      <c r="B7" s="81" t="inlineStr">
+        <is>
+          <t>問題数</t>
+        </is>
+      </c>
+      <c r="C7" s="81" t="inlineStr">
+        <is>
+          <t>リンク</t>
+        </is>
+      </c>
+      <c r="D7" s="81" t="inlineStr">
+        <is>
+          <t>未紐づけ</t>
+        </is>
+      </c>
+      <c r="E7" s="81" t="inlineStr">
+        <is>
+          <t>カバー語</t>
+        </is>
+      </c>
+      <c r="F7" s="81" t="inlineStr">
+        <is>
+          <t>母数</t>
+        </is>
+      </c>
+      <c r="G7" s="81" t="inlineStr">
+        <is>
+          <t>breadth%</t>
+        </is>
+      </c>
+      <c r="H7" s="81" t="inlineStr">
+        <is>
+          <t>未カバー(backlog)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>153</v>
+      </c>
+      <c r="C8" t="n">
+        <v>153</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>155</v>
+      </c>
+      <c r="F8" t="n">
+        <v>673</v>
+      </c>
+      <c r="G8" s="45" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>518</v>
+      </c>
+      <c r="I8" s="80" t="inlineStr">
+        <is>
+          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=153</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>99</v>
+      </c>
+      <c r="C9" t="n">
+        <v>99</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>94</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2145</v>
+      </c>
+      <c r="G9" s="45" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2051</v>
+      </c>
+      <c r="I9" s="80" t="inlineStr">
+        <is>
+          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=94 / 下級流出=N5:3, N4:2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -7,14 +7,19 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目次・凡例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="① 在庫・模試換算" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② カバー率" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 品質・攻略耐性" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ 習得の仕組み(説明)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ 用法カバー×バランス" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大問別まとめ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模試ストック換算" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目次・凡例" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="① 在庫・模試換算" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② カバー率" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 品質・攻略耐性" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ 習得の仕組み(説明)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ 用法カバー×バランス" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大問別まとめ'!$A$1:$J$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -895,6 +900,2385 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>セクション</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>大問</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>在庫問題数</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>セット数</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>未検証</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>本番出題数</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>模試換算(何回分)</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>誤答数の内訳</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>シャッフル</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>漢字読み</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>3:521</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>漢字読み</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>537</v>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>3:537</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>漢字読み</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>1882</v>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>235</v>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>3:1882</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>585</v>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>117</v>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>3:585</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>538</v>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>89</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>3:538</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>1882</v>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>313</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>3:1882</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>文脈規定</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>655</v>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>109</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>3:165 / 4:222 / 5:268</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>文脈規定</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>651</v>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>3:239 / 4:231 / 5:181</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>文脈規定</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>2090</v>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>1318</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>190</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>3:1382 / 4:450 / 5:258</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>言い換え類義</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>131</v>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>3:100 / 4:13 / 5:18</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>言い換え類義</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>225</v>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>3:1 / 4:8 / 5:40 / 6:176</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>言い換え類義</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>1057</v>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>211</v>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>3:46 / 4:14 / 5:100 / 6:897</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>用法</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>173</v>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>3:62 / 4:37 / 5:40 / 6:34</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>用法</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>3:30 / 4:28 / 5:27 / 6:14</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>文法形式</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>204</v>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>3:203 / 4:1</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>文法形式</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>357</v>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>3:357</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>文法形式</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>443</v>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>3:441 / 4:2</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>組み立て</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>137</v>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>3:137</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>組み立て</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>214</v>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>3:214</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>組み立て</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>308</v>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>3:308</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>文章の文法</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>3:400</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>文章の文法</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>3:300</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>文章の文法</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>350</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>3:350</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>内容理解(短文)</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>3:90</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>内容理解(短文)</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>3:120</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>内容理解(短文)</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>3:120</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>内容理解(中文)</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>3:80</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>内容理解(中文)</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>160</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>3:160</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>内容理解(中文)</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>3:240</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>内容理解(長文)</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>160</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>3:160</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>情報検索</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>3:60</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>情報検索</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>3:60</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>情報検索</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>3:60</t>
+        </is>
+      </c>
+      <c r="J34" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>課題理解</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>課題理解</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>課題理解</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>ポイント理解</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>ポイント理解</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>ポイント理解</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>概要理解</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>3:80</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>発話表現</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>2:200</t>
+        </is>
+      </c>
+      <c r="J42" s="13" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>発話表現</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>2:200</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>発話表現</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>2:200</t>
+        </is>
+      </c>
+      <c r="J44" s="13" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>2:240</t>
+        </is>
+      </c>
+      <c r="J45" s="13" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>2:240</t>
+        </is>
+      </c>
+      <c r="J46" s="13" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>2:240</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>◆ 模試換算 = 在庫 ÷ 本番出題数 = その大問だけで組めるフル模試の回数（floor）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>セクション別 律速（そのセクションで最も少ない大問の回数＝そのセクションを何回組めるか）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>セクション</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>文字・語彙</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>43</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="C8" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>級ごとの「フル模試」完成可能回数（全大問の最小＝律速大問で決まる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>セクション</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>フル模試</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>凡例：赤=5回以下(不足) / 橙=15回以下(要増産) / 緑=16回以上(十分)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>◆ 参考データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>在庫 合計</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>17189</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>問</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>在庫外（監査に落ちた分・在庫に数えない）</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>問</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>辞書にある全単語数（問題化の母数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>辞書</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>内訳</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1048,7 +3432,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E5DA8"/>
@@ -3409,7 +5793,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E7D32"/>
@@ -5763,7 +8147,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C25E00"/>
@@ -8328,7 +10712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006A3D9A"/>
@@ -8717,7 +11101,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8814,31 +11198,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="C8" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="F8" t="n">
         <v>673</v>
       </c>
       <c r="G8" s="45" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="I8" s="80" t="inlineStr">
         <is>
-          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=153</t>
+          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=173</t>
         </is>
       </c>
     </row>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>153</v>
+        <v>565</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
@@ -4084,11 +4084,11 @@
         <v>5</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>3:42 / 4:37 / 5:40 / 6:34</t>
+          <t>3:565</t>
         </is>
       </c>
       <c r="J15" s="13" t="inlineStr">
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="E13" s="26" t="n">
-        <v>153</v>
+        <v>565</v>
       </c>
       <c r="F13" s="26" t="n">
-        <v>153</v>
+        <v>565</v>
       </c>
       <c r="G13" s="26" t="n">
         <v>150</v>
@@ -6668,17 +6668,17 @@
         </is>
       </c>
       <c r="C40" s="26" t="n">
-        <v>166</v>
+        <v>565</v>
       </c>
       <c r="D40" s="26" t="n">
-        <v>155</v>
+        <v>567</v>
       </c>
       <c r="E40" s="26" t="n">
         <v>668</v>
       </c>
       <c r="F40" s="39" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="G40" s="29" t="n"/>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="J40" s="45" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>85%</t>
         </is>
       </c>
     </row>
@@ -11198,31 +11198,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>173</v>
+        <v>565</v>
       </c>
       <c r="C8" t="n">
-        <v>173</v>
+        <v>565</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>175</v>
+        <v>567</v>
       </c>
       <c r="F8" t="n">
         <v>673</v>
       </c>
-      <c r="G8" s="45" t="inlineStr">
-        <is>
-          <t>26%</t>
+      <c r="G8" s="37" t="inlineStr">
+        <is>
+          <t>84%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>498</v>
+        <v>106</v>
       </c>
       <c r="I8" s="80" t="inlineStr">
         <is>
-          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=173</t>
+          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=565</t>
         </is>
       </c>
     </row>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D11" s="94" t="n">
-        <v>131</v>
+        <v>231</v>
       </c>
       <c r="E11" s="94" t="inlineStr">
         <is>
@@ -1617,11 +1617,11 @@
         <v>3</v>
       </c>
       <c r="H11" s="95" t="n">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="I11" s="93" t="inlineStr">
         <is>
-          <t>3:100 / 4:13 / 5:18</t>
+          <t>3:200 / 4:13 / 5:18</t>
         </is>
       </c>
       <c r="J11" s="94" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D12" s="94" t="n">
-        <v>225</v>
+        <v>406</v>
       </c>
       <c r="E12" s="94" t="inlineStr">
         <is>
@@ -1661,11 +1661,11 @@
         <v>5</v>
       </c>
       <c r="H12" s="95" t="n">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="I12" s="93" t="inlineStr">
         <is>
-          <t>3:1 / 4:8 / 5:40 / 6:176</t>
+          <t>3:182 / 4:8 / 5:40 / 6:176</t>
         </is>
       </c>
       <c r="J12" s="94" t="inlineStr">
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="D13" s="94" t="n">
-        <v>1057</v>
+        <v>1611</v>
       </c>
       <c r="E13" s="94" t="inlineStr">
         <is>
@@ -1705,11 +1705,11 @@
         <v>5</v>
       </c>
       <c r="H13" s="95" t="n">
-        <v>211</v>
+        <v>322</v>
       </c>
       <c r="I13" s="93" t="inlineStr">
         <is>
-          <t>3:46 / 4:14 / 5:100 / 6:897</t>
+          <t>3:600 / 4:14 / 5:100 / 6:897</t>
         </is>
       </c>
       <c r="J13" s="94" t="inlineStr">
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="B5" s="102" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="C5" s="102" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D5" s="102" t="n">
         <v>59</v>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17781</v>
+        <v>18616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -6216,22 +6216,22 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>148</v>
+        <v>231</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>148</v>
+        <v>231</v>
       </c>
       <c r="E12" s="25" t="n">
-        <v>185</v>
+        <v>406</v>
       </c>
       <c r="F12" s="25" t="n">
-        <v>185</v>
+        <v>406</v>
       </c>
       <c r="G12" s="25" t="n">
-        <v>1000</v>
+        <v>1611</v>
       </c>
       <c r="H12" s="25" t="n">
-        <v>1000</v>
+        <v>1611</v>
       </c>
       <c r="I12" s="28" t="n"/>
     </row>
@@ -7129,27 +7129,27 @@
         </is>
       </c>
       <c r="C50" s="25" t="n">
-        <v>1653</v>
+        <v>1611</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>1653</v>
+        <v>1611</v>
       </c>
       <c r="E50" s="25" t="n">
         <v>2145</v>
       </c>
       <c r="F50" s="35" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="G50" s="28" t="n"/>
       <c r="H50" s="72" t="inlineStr">
         <is>
-          <t>全ID 1399/2145=65%。真の母数=1776語中 1376語=77%。新規EXCEL問題(N5+100/N4+159/N3+300・未マージ)を含む。2026-08-24 言い換えEXCEL青セル削除語(N5 5/N4 16=元p=1)を真の母数から除外(iikaePossible p=0・N3は削除なし)。全ID母数には数詞/あいさつ/固有名/類義語のない具体名詞が含まれ言い換え不可。 2026-08-24 増作2で未カバー全語を追加(N5+36/N4+44/N3+272=352問)＋N3の不適語5件除外・20件正解修正。iikaePossible未改変(真の分子は実カバー)。 2026-08-25 QA訂正+青セル除外13を反映。</t>
+          <t>全ID 1611/2145=75%。真の母数(iikaePossible p=1)=1755, 真カバー率=1611/1755=92%。2026-08-26 未マージEXCEL新問を content へマージ完了(N5+100/N4+181/N3+554=835)→全マージ済。大問別まとめD(231/406/1611)と一致。N3新規554語をiikaePossible p=1へ更新。全ID母数には数詞/あいさつ/固有名/類義語のない具体名詞(言い換え不可)を含む。</t>
         </is>
       </c>
       <c r="I50" s="33" t="n">
-        <v>1776</v>
+        <v>1755</v>
       </c>
       <c r="J50" s="69" t="inlineStr">
         <is>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -7165,27 +7165,27 @@
         </is>
       </c>
       <c r="C51" s="25" t="n">
-        <v>99</v>
+        <v>299</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>99</v>
+        <v>299</v>
       </c>
       <c r="E51" s="25" t="n">
         <v>2145</v>
       </c>
       <c r="F51" s="38" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G51" s="28" t="n"/>
       <c r="H51" s="72" t="inlineStr">
         <is>
-          <t>真の母数=用法作問済み語数(＝問題数99)。用法は語を選ばず作れるため天井は作問した語自体＝真カバー率100%。漢字読み/表記と同じ例外カウント。※旧94は古い集計、実99へ更新。</t>
+          <t>真の母数=用法作問済み語数(＝問題数299)。用法は語を選ばず作れるため天井は作問した語自体＝真カバー率100%。漢字読み/表記と同じ例外カウント。2026-08-26 新規N3用法200問(N3-V-Y-0151〜0350)追加で99→299。大問別まとめD=299と一致。</t>
         </is>
       </c>
       <c r="I51" s="33" t="n">
-        <v>99</v>
+        <v>299</v>
       </c>
       <c r="J51" s="69" t="inlineStr">
         <is>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 品質・攻略耐性" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ 習得の仕組み(説明)" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ 用法カバー×バランス" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学習ドリル×カバー率" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大問別まとめ'!$A$1:$J$1</definedName>
@@ -26,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -199,8 +200,12 @@
       <b val="1"/>
       <sz val="13"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill/>
     </fill>
@@ -374,6 +379,11 @@
         <fgColor rgb="00F6C9C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE7C0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -490,7 +500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -746,6 +756,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3232,6 +3246,1062 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="71" min="1" max="1"/>
+    <col width="20" customWidth="1" style="71" min="2" max="2"/>
+    <col width="11" customWidth="1" style="71" min="3" max="3"/>
+    <col width="11" customWidth="1" style="71" min="4" max="4"/>
+    <col width="11" customWidth="1" style="71" min="5" max="5"/>
+    <col width="11" customWidth="1" style="71" min="6" max="6"/>
+    <col width="11" customWidth="1" style="71" min="7" max="7"/>
+    <col width="60" customWidth="1" style="71" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="104" t="inlineStr">
+        <is>
+          <t>学習ドリル×カバー率（学習タブ・各ドリルがID紐づけで対象にできる項目の広さ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>※全ID母数=レベル内の全項目(語彙数/文法点数[n5-g-92除外]/漢字数)。真の母数=そのドリルで「そもそも作れる」項目数(カタカナ語・分離型文法など"永久に不可能"を除く)＝真のカバー率が実力。試験タブの大問は別シート「単語×大問カバー率」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="104" t="inlineStr">
+        <is>
+          <t>■ N5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="109" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="109" t="inlineStr">
+        <is>
+          <t>ドリル</t>
+        </is>
+      </c>
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="D5" s="109" t="inlineStr">
+        <is>
+          <t>全ID母数</t>
+        </is>
+      </c>
+      <c r="E5" s="109" t="inlineStr">
+        <is>
+          <t>全IDカバー率</t>
+        </is>
+      </c>
+      <c r="F5" s="109" t="inlineStr">
+        <is>
+          <t>真の母数</t>
+        </is>
+      </c>
+      <c r="G5" s="109" t="inlineStr">
+        <is>
+          <t>真のカバー率</t>
+        </is>
+      </c>
+      <c r="H5" s="109" t="inlineStr">
+        <is>
+          <t>点検メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>語彙パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>606</v>
+      </c>
+      <c r="D6" t="n">
+        <v>723</v>
+      </c>
+      <c r="E6" s="107" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>606</v>
+      </c>
+      <c r="G6" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="72" t="inlineStr">
+        <is>
+          <t>見かけ84%だが真の100%＝差16ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>聞き取り(語彙)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>681</v>
+      </c>
+      <c r="D7" t="n">
+        <v>723</v>
+      </c>
+      <c r="E7" s="107" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>681</v>
+      </c>
+      <c r="G7" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="72" t="inlineStr">
+        <is>
+          <t>見かけ94%だが真の100%＝差6ptは"作れない天井"。読みを聞いて単語を選ぶ。非自立語(接辞/助詞)・波ダッシュ語のみ対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>意味を選ぶ(受容)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>91</v>
+      </c>
+      <c r="D8" t="n">
+        <v>91</v>
+      </c>
+      <c r="E8" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>91</v>
+      </c>
+      <c r="G8" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="72" t="inlineStr">
+        <is>
+          <t>文法点の意味を4択。意味を持つ全点が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>文法パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>67</v>
+      </c>
+      <c r="D9" t="n">
+        <v>91</v>
+      </c>
+      <c r="E9" s="110" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>67</v>
+      </c>
+      <c r="G9" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="72" t="inlineStr">
+        <is>
+          <t>見かけ74%だが真の100%＝差26ptは"作れない天井"。例文の空所に文法語をタイルで作る。例文に表層形が一意に1回出る点のみ対象(0回/複数回は空所位置が曖昧で除外)＝構造的に低い。上げたい場合は例文を「表層形が1回だけ出る」形に整えるか、対象点の例文を追加する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>意味を選ぶ(漢字)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>77</v>
+      </c>
+      <c r="D10" t="n">
+        <v>79</v>
+      </c>
+      <c r="E10" s="107" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>77</v>
+      </c>
+      <c r="G10" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="72" t="inlineStr">
+        <is>
+          <t>見かけ97%だが真の100%＝差3ptは"作れない天井"。字→意味を4択(認識テスト)。意味が立つ字(訓読みあり or 単独語=meaningClear)だけが対象。校のような字は意味面を作れず対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>読み(漢字)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>79</v>
+      </c>
+      <c r="D11" t="n">
+        <v>79</v>
+      </c>
+      <c r="E11" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>79</v>
+      </c>
+      <c r="G11" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="72" t="inlineStr">
+        <is>
+          <t>字→読みを4択(認識テスト)。全字が対象。訓読みを優先し送り仮名を補って提示(強→つよ（い）)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>形の弁別(漢字)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>62</v>
+      </c>
+      <c r="D12" t="n">
+        <v>79</v>
+      </c>
+      <c r="E12" s="110" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>62</v>
+      </c>
+      <c r="G12" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="72" t="inlineStr">
+        <is>
+          <t>見かけ78%だが真の100%＝差22ptは"作れない天井"。似た字4択→正しい字を選ぶ(形の弁別)。見た目が紛らわしい字が3つ揃う字(formMakeable)だけが対象。※書き取り(手書き産出)は練習ゆえ面に非計上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>聞き取り(漢字)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>79</v>
+      </c>
+      <c r="D13" t="n">
+        <v>79</v>
+      </c>
+      <c r="E13" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>79</v>
+      </c>
+      <c r="G13" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="72" t="inlineStr">
+        <is>
+          <t>読みを聞いて漢字を選ぶ。drillレップを持つ当該級の漢字が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="104" t="inlineStr">
+        <is>
+          <t>■ N4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="109" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B16" s="109" t="inlineStr">
+        <is>
+          <t>ドリル</t>
+        </is>
+      </c>
+      <c r="C16" s="109" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="D16" s="109" t="inlineStr">
+        <is>
+          <t>全ID母数</t>
+        </is>
+      </c>
+      <c r="E16" s="109" t="inlineStr">
+        <is>
+          <t>全IDカバー率</t>
+        </is>
+      </c>
+      <c r="F16" s="109" t="inlineStr">
+        <is>
+          <t>真の母数</t>
+        </is>
+      </c>
+      <c r="G16" s="109" t="inlineStr">
+        <is>
+          <t>真のカバー率</t>
+        </is>
+      </c>
+      <c r="H16" s="109" t="inlineStr">
+        <is>
+          <t>点検メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>語彙パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>576</v>
+      </c>
+      <c r="D17" t="n">
+        <v>673</v>
+      </c>
+      <c r="E17" s="107" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>576</v>
+      </c>
+      <c r="G17" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="72" t="inlineStr">
+        <is>
+          <t>見かけ86%だが真の100%＝差14ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聞き取り(語彙)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>643</v>
+      </c>
+      <c r="D18" t="n">
+        <v>673</v>
+      </c>
+      <c r="E18" s="107" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>643</v>
+      </c>
+      <c r="G18" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="72" t="inlineStr">
+        <is>
+          <t>見かけ96%だが真の100%＝差4ptは"作れない天井"。読みを聞いて単語を選ぶ。非自立語(接辞/助詞)・波ダッシュ語のみ対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>意味を選ぶ(受容)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>131</v>
+      </c>
+      <c r="D19" t="n">
+        <v>131</v>
+      </c>
+      <c r="E19" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>131</v>
+      </c>
+      <c r="G19" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="72" t="inlineStr">
+        <is>
+          <t>文法点の意味を4択。意味を持つ全点が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>文法パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>113</v>
+      </c>
+      <c r="D20" t="n">
+        <v>131</v>
+      </c>
+      <c r="E20" s="107" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>114</v>
+      </c>
+      <c r="G20" s="107" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="H20" s="72" t="inlineStr">
+        <is>
+          <t>見かけ86%だが真の99%＝差13ptは"作れない天井"。例文の空所に文法語をタイルで作る。例文に表層形が一意に1回出る点のみ対象(0回/複数回は空所位置が曖昧で除外)＝構造的に低い。上げたい場合は例文を「表層形が1回だけ出る」形に整えるか、対象点の例文を追加する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>意味を選ぶ(漢字)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>141</v>
+      </c>
+      <c r="D21" t="n">
+        <v>166</v>
+      </c>
+      <c r="E21" s="107" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>141</v>
+      </c>
+      <c r="G21" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="72" t="inlineStr">
+        <is>
+          <t>見かけ85%だが真の100%＝差15ptは"作れない天井"。字→意味を4択(認識テスト)。意味が立つ字(訓読みあり or 単独語=meaningClear)だけが対象。校のような字は意味面を作れず対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>読み(漢字)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>166</v>
+      </c>
+      <c r="D22" t="n">
+        <v>166</v>
+      </c>
+      <c r="E22" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>166</v>
+      </c>
+      <c r="G22" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H22" s="72" t="inlineStr">
+        <is>
+          <t>字→読みを4択(認識テスト)。全字が対象。訓読みを優先し送り仮名を補って提示(強→つよ（い）)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>形の弁別(漢字)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>159</v>
+      </c>
+      <c r="D23" t="n">
+        <v>166</v>
+      </c>
+      <c r="E23" s="107" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>159</v>
+      </c>
+      <c r="G23" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="72" t="inlineStr">
+        <is>
+          <t>見かけ96%だが真の100%＝差4ptは"作れない天井"。似た字4択→正しい字を選ぶ(形の弁別)。見た目が紛らわしい字が3つ揃う字(formMakeable)だけが対象。※書き取り(手書き産出)は練習ゆえ面に非計上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>聞き取り(漢字)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>166</v>
+      </c>
+      <c r="D24" t="n">
+        <v>166</v>
+      </c>
+      <c r="E24" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>166</v>
+      </c>
+      <c r="G24" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="72" t="inlineStr">
+        <is>
+          <t>読みを聞いて漢字を選ぶ。drillレップを持つ当該級の漢字が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="104" t="inlineStr">
+        <is>
+          <t>■ N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="109" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B27" s="109" t="inlineStr">
+        <is>
+          <t>ドリル</t>
+        </is>
+      </c>
+      <c r="C27" s="109" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="D27" s="109" t="inlineStr">
+        <is>
+          <t>全ID母数</t>
+        </is>
+      </c>
+      <c r="E27" s="109" t="inlineStr">
+        <is>
+          <t>全IDカバー率</t>
+        </is>
+      </c>
+      <c r="F27" s="109" t="inlineStr">
+        <is>
+          <t>真の母数</t>
+        </is>
+      </c>
+      <c r="G27" s="109" t="inlineStr">
+        <is>
+          <t>真のカバー率</t>
+        </is>
+      </c>
+      <c r="H27" s="109" t="inlineStr">
+        <is>
+          <t>点検メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>語彙パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1963</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2145</v>
+      </c>
+      <c r="E28" s="107" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1963</v>
+      </c>
+      <c r="G28" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="72" t="inlineStr">
+        <is>
+          <t>見かけ92%だが真の100%＝差8ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>聞き取り(語彙)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2143</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2145</v>
+      </c>
+      <c r="E29" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2143</v>
+      </c>
+      <c r="G29" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H29" s="72" t="inlineStr">
+        <is>
+          <t>読みを聞いて単語を選ぶ。非自立語(接辞/助詞)・波ダッシュ語のみ対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>意味を選ぶ(受容)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>186</v>
+      </c>
+      <c r="D30" t="n">
+        <v>186</v>
+      </c>
+      <c r="E30" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>186</v>
+      </c>
+      <c r="G30" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="72" t="inlineStr">
+        <is>
+          <t>文法点の意味を4択。意味を持つ全点が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>文法パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>167</v>
+      </c>
+      <c r="D31" t="n">
+        <v>186</v>
+      </c>
+      <c r="E31" s="107" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>169</v>
+      </c>
+      <c r="G31" s="107" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="H31" s="72" t="inlineStr">
+        <is>
+          <t>見かけ90%だが真の99%＝差9ptは"作れない天井"。例文の空所に文法語をタイルで作る。例文に表層形が一意に1回出る点のみ対象(0回/複数回は空所位置が曖昧で除外)＝構造的に低い。上げたい場合は例文を「表層形が1回だけ出る」形に整えるか、対象点の例文を追加する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>意味を選ぶ(漢字)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>311</v>
+      </c>
+      <c r="D32" t="n">
+        <v>367</v>
+      </c>
+      <c r="E32" s="107" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>311</v>
+      </c>
+      <c r="G32" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H32" s="72" t="inlineStr">
+        <is>
+          <t>見かけ85%だが真の100%＝差15ptは"作れない天井"。字→意味を4択(認識テスト)。意味が立つ字(訓読みあり or 単独語=meaningClear)だけが対象。校のような字は意味面を作れず対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>読み(漢字)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>367</v>
+      </c>
+      <c r="D33" t="n">
+        <v>367</v>
+      </c>
+      <c r="E33" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>367</v>
+      </c>
+      <c r="G33" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="72" t="inlineStr">
+        <is>
+          <t>字→読みを4択(認識テスト)。全字が対象。訓読みを優先し送り仮名を補って提示(強→つよ（い）)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>形の弁別(漢字)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>336</v>
+      </c>
+      <c r="D34" t="n">
+        <v>367</v>
+      </c>
+      <c r="E34" s="107" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>336</v>
+      </c>
+      <c r="G34" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H34" s="72" t="inlineStr">
+        <is>
+          <t>見かけ92%だが真の100%＝差8ptは"作れない天井"。似た字4択→正しい字を選ぶ(形の弁別)。見た目が紛らわしい字が3つ揃う字(formMakeable)だけが対象。※書き取り(手書き産出)は練習ゆえ面に非計上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>聞き取り(漢字)</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>367</v>
+      </c>
+      <c r="D35" t="n">
+        <v>367</v>
+      </c>
+      <c r="E35" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>367</v>
+      </c>
+      <c r="G35" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H35" s="72" t="inlineStr">
+        <is>
+          <t>読みを聞いて漢字を選ぶ。drillレップを持つ当該級の漢字が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>凡例：緑=問題なし(≥80%) ／ 黄=気になる(60-79%) ／ 赤=危険(&lt;60%)。カバー率が2つあるのは"天井"のあるドリル＝真のカバー率で判断。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6007,7 +7077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="46" customWidth="1" style="71" min="1" max="1"/>
@@ -6116,6 +7186,23 @@
       <c r="I7" s="23" t="n"/>
     </row>
     <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>漢字（字）</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="n">
+        <v>79</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>166</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>367</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>612</v>
+      </c>
       <c r="I8" s="23" t="n"/>
     </row>
     <row r="9">
@@ -6364,6 +7451,32 @@
         <v>200</v>
       </c>
       <c r="I16" s="28" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>読み/意味/聞き取り/形＋書き(練習)</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>79</v>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>166</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>367</v>
+      </c>
+      <c r="I17" s="27" t="inlineStr">
+        <is>
+          <t>漢字ID=字。面の内訳・字数は下の◆漢字面数分布を参照。書き取りは練習(面外)。</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="22.05" customHeight="1" s="71">
       <c r="A19" s="8" t="inlineStr">
@@ -8012,7 +9125,7 @@
     <row r="104" ht="15.6" customHeight="1" s="71">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>語彙 面数分布 — 1語が何面(大問/ドリル)に問題を持つか（2026-08-24）</t>
+          <t>語彙 面数分布 — 1語が何面(大問/ドリル)に問題を持つか（2026-08-26 更新）</t>
         </is>
       </c>
     </row>
@@ -8063,10 +9176,10 @@
         <v>0</v>
       </c>
       <c r="C107" s="43" t="n">
-        <v>69</v>
+        <v>319</v>
       </c>
       <c r="D107" s="43" t="n">
-        <v>42</v>
+        <v>223</v>
       </c>
       <c r="E107" s="43" t="inlineStr">
         <is>
@@ -8075,12 +9188,12 @@
       </c>
       <c r="F107" s="43" t="inlineStr">
         <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G107" s="43" t="inlineStr">
+        <is>
           <t>10%</t>
-        </is>
-      </c>
-      <c r="G107" s="43" t="inlineStr">
-        <is>
-          <t>2%</t>
         </is>
       </c>
     </row>
@@ -8091,27 +9204,27 @@
         </is>
       </c>
       <c r="B108" s="43" t="n">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="C108" s="43" t="n">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="D108" s="43" t="n">
-        <v>982</v>
+        <v>1212</v>
       </c>
       <c r="E108" s="43" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="F108" s="43" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G108" s="43" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>57%</t>
         </is>
       </c>
     </row>
@@ -8122,27 +9235,27 @@
         </is>
       </c>
       <c r="B109" s="43" t="n">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C109" s="43" t="n">
-        <v>232</v>
+        <v>60</v>
       </c>
       <c r="D109" s="43" t="n">
-        <v>819</v>
+        <v>438</v>
       </c>
       <c r="E109" s="43" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="F109" s="43" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G109" s="43" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -8153,22 +9266,22 @@
         </is>
       </c>
       <c r="B110" s="43" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C110" s="43" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D110" s="43" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E110" s="43" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="F110" s="43" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G110" s="43" t="inlineStr">
@@ -8184,17 +9297,17 @@
         </is>
       </c>
       <c r="B111" s="43" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C111" s="43" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D111" s="43" t="n">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="E111" s="43" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="F111" s="43" t="inlineStr">
@@ -8204,7 +9317,7 @@
       </c>
       <c r="G111" s="43" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
@@ -8215,13 +9328,13 @@
         </is>
       </c>
       <c r="B112" s="43" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C112" s="43" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D112" s="43" t="n">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="E112" s="43" t="inlineStr">
         <is>
@@ -8235,7 +9348,7 @@
       </c>
       <c r="G112" s="43" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>3%</t>
         </is>
       </c>
     </row>
@@ -8246,10 +9359,10 @@
         </is>
       </c>
       <c r="B113" s="43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C113" s="43" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D113" s="43" t="n">
         <v>2</v>
@@ -8261,7 +9374,7 @@
       </c>
       <c r="F113" s="43" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G113" s="43" t="inlineStr">
@@ -8277,7 +9390,7 @@
         </is>
       </c>
       <c r="B114" s="43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C114" s="43" t="n">
         <v>1</v>
@@ -8292,7 +9405,7 @@
       </c>
       <c r="F114" s="43" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G114" s="43" t="inlineStr">
@@ -8335,12 +9448,687 @@
     <row r="117">
       <c r="A117" s="72" t="inlineStr">
         <is>
-          <t>※面(=大問/ドリル)は最大7つ：①漢字読み ②表記 ③文脈規定 ④言い換え類義 ⑤用法（＝試験の5大問）＋⑥語彙パズル(産出) ⑦聞き取り（＝学習ドリル2つ）。数字は「その語が現時点で問題を持つ面の数」＝深さ。N5で7面が0なのは用法がまだ3語しか無いため（用法が増えれば7面へ上がる）。点の総数(語数)は合計行＝N5 723/N4 673/N3 2145。 ／ 2026-08-24: 束縛形態素9語(助詞/接尾辞・vocabMetricExcluded.json)を語彙点から除外(全て0面)→合計 N5 723→719・N4 673→668。理由=単独の語彙問題が作れず、機能は文法点として文法側で練習・カバーされるため(二重計上/紛らわしさ回避)。辞書表示は残す(可逆)。</t>
+          <t>※面(=大問/ドリル)は最大7つ：①漢字読み ②表記 ③文脈規定 ④言い換え類義 ⑤用法（＝試験の5大問）＋⑥語彙パズル(産出) ⑦聞き取り（＝学習ドリル2つ）。数字は「その語が現時点で問題を持つ面の数」＝深さ。N5の7面が0なのは用法大問がN5には存在しない（用法はN4/N3のみ）ためで、N5の上限は6面（構造的）。0面はいずれも接頭・接尾辞（何～/～君/～観）＝単独問題が作れない語。母数(合計行)は束縛形態素9語(vocabMetricExcluded.json・全て0面)を除いた N5 719/N4 668/N3 2145。 ／ 2026-08-26 更新: 言い換え835問＋用法(N3 200/N4 252)のcontent反映を再集計。N4は7面が 69→319語(48%)・N3は7面が 42→223語(10%)へ大幅増（言い換え・用法の追加で深さが増した）。集計=scratchpad/facet_hist.ts。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>◆ 文法 面数分布（1文法点が何面に問題を持つか）</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>文法 面数分布 — 1文法点が何面(試験3大問＋学習ドリル2)に問題を持つか（2026-08-26）</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="42" t="inlineStr">
+        <is>
+          <t>面数</t>
+        </is>
+      </c>
+      <c r="B122" s="42" t="inlineStr">
+        <is>
+          <t>N5 点数</t>
+        </is>
+      </c>
+      <c r="C122" s="42" t="inlineStr">
+        <is>
+          <t>N4 点数</t>
+        </is>
+      </c>
+      <c r="D122" s="42" t="inlineStr">
+        <is>
+          <t>N3 点数</t>
+        </is>
+      </c>
+      <c r="E122" s="42" t="inlineStr">
+        <is>
+          <t>（参考）N5%</t>
+        </is>
+      </c>
+      <c r="F122" s="42" t="inlineStr">
+        <is>
+          <t>N4%</t>
+        </is>
+      </c>
+      <c r="G122" s="42" t="inlineStr">
+        <is>
+          <t>N3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="43" t="inlineStr">
+        <is>
+          <t>5面</t>
+        </is>
+      </c>
+      <c r="B123" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="C123" s="43" t="n">
+        <v>93</v>
+      </c>
+      <c r="D123" s="43" t="n">
+        <v>136</v>
+      </c>
+      <c r="E123" s="43" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="F123" s="43" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="G123" s="43" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="43" t="inlineStr">
+        <is>
+          <t>4面</t>
+        </is>
+      </c>
+      <c r="B124" s="43" t="n">
+        <v>28</v>
+      </c>
+      <c r="C124" s="43" t="n">
+        <v>32</v>
+      </c>
+      <c r="D124" s="43" t="n">
+        <v>43</v>
+      </c>
+      <c r="E124" s="43" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="F124" s="43" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="G124" s="43" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="43" t="inlineStr">
+        <is>
+          <t>3面</t>
+        </is>
+      </c>
+      <c r="B125" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="C125" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="D125" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E125" s="43" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="F125" s="43" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G125" s="43" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="43" t="inlineStr">
+        <is>
+          <t>2面</t>
+        </is>
+      </c>
+      <c r="B126" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C126" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="43" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F126" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G126" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="43" t="inlineStr">
+        <is>
+          <t>1面</t>
+        </is>
+      </c>
+      <c r="B127" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F127" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G127" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="43" t="inlineStr">
+        <is>
+          <t>0面</t>
+        </is>
+      </c>
+      <c r="B128" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F128" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G128" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="44" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B129" s="44" t="n">
+        <v>91</v>
+      </c>
+      <c r="C129" s="44" t="n">
+        <v>131</v>
+      </c>
+      <c r="D129" s="44" t="n">
+        <v>186</v>
+      </c>
+      <c r="E129" s="44" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F129" s="44" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G129" s="44" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="72" t="inlineStr">
+        <is>
+          <t>※面(最大5)：①文法形式判断(穴埋め) ②文の組み立て ③文章の文法（＝試験の文法3大問）＋④意味を選ぶ(受容) ⑤文法パズル(産出)（＝学習ドリル2つ）。数字は「その文法点が現時点で問題を持つ面の数」＝深さ。単位=文法点(pointId)。母数は指標対象外の n5-g-92（本文非依存の活用ドリル）を除いた N5 91/N4 131/N3 186点。0～1面が0なのは、意味ドリルが全点対象＋少なくとも1大問には必ず出るため下限が実質2面だから。（2026-08-26 新規作成・集計=scratchpad/facet_hist_gk.ts）</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>◆ 漢字 面数分布（1漢字が何面を作れるか・新4面モデル）</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>漢字 面数分布 — 1漢字が何面(読み/意味/聞き取り/形)を作れるか（2026-08-26 改訂・新モデル）</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="42" t="inlineStr">
+        <is>
+          <t>面数</t>
+        </is>
+      </c>
+      <c r="B136" s="42" t="inlineStr">
+        <is>
+          <t>N5 字数</t>
+        </is>
+      </c>
+      <c r="C136" s="42" t="inlineStr">
+        <is>
+          <t>N4 字数</t>
+        </is>
+      </c>
+      <c r="D136" s="42" t="inlineStr">
+        <is>
+          <t>N3 字数</t>
+        </is>
+      </c>
+      <c r="E136" s="42" t="inlineStr">
+        <is>
+          <t>（参考）N5%</t>
+        </is>
+      </c>
+      <c r="F136" s="42" t="inlineStr">
+        <is>
+          <t>N4%</t>
+        </is>
+      </c>
+      <c r="G136" s="42" t="inlineStr">
+        <is>
+          <t>N3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="43" t="inlineStr">
+        <is>
+          <t>4面</t>
+        </is>
+      </c>
+      <c r="B137" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="C137" s="43" t="n">
+        <v>136</v>
+      </c>
+      <c r="D137" s="43" t="n">
+        <v>283</v>
+      </c>
+      <c r="E137" s="43" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="F137" s="43" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="G137" s="43" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="43" t="inlineStr">
+        <is>
+          <t>3面</t>
+        </is>
+      </c>
+      <c r="B138" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="C138" s="43" t="n">
+        <v>28</v>
+      </c>
+      <c r="D138" s="43" t="n">
+        <v>81</v>
+      </c>
+      <c r="E138" s="43" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="F138" s="43" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="G138" s="43" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="43" t="inlineStr">
+        <is>
+          <t>2面</t>
+        </is>
+      </c>
+      <c r="B139" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D139" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E139" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F139" s="43" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G139" s="43" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="43" t="inlineStr">
+        <is>
+          <t>1面</t>
+        </is>
+      </c>
+      <c r="B140" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F140" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G140" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="43" t="inlineStr">
+        <is>
+          <t>0面</t>
+        </is>
+      </c>
+      <c r="B141" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F141" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G141" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="44" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B142" s="44" t="n">
+        <v>79</v>
+      </c>
+      <c r="C142" s="44" t="n">
+        <v>166</v>
+      </c>
+      <c r="D142" s="44" t="n">
+        <v>367</v>
+      </c>
+      <c r="E142" s="44" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F142" s="44" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G142" s="44" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="72" t="inlineStr">
+        <is>
+          <t>※漢字の面=4面: 読み(read・認識テスト)／意味(mean・認識テスト・意味が立つ字のみ)／聞き取り(listen・全字)／形(form・似た字の弁別・類似字が3つ揃う字のみ)。数字は「その字で作れる面の数」＝深さ。読み・聞き取りは全字で作れるので下限は2面。意味が立つ字(meaningClear)= N5 77/N4 141/N3 311、形が作れる字(似た字3つ揃い)= N5 62/N4 159/N3 336。※書き取り(手書き産出)は「練習」＝面に非計上(ユーザー方針2026-08-26)。母数=当該級の漢字字数 N5 79/N4 166/N3 367。アプリのカバー率(coverageBars)は作れる面の加重平均≥0.6で「覚えた」と判定。集計=kanjiFacets.json＋kanjiSimilar.json。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t>◆ 漢字ID×面 詳細（1漢字IDが紐づく面・対象字数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>漢字ID＝字。面=読み/意味/聞き取り/形の4面＋書き(練習・面外)。字数=当該級の対象字数（2026-08-26）</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="42" t="inlineStr">
+        <is>
+          <t>面（ドリル）</t>
+        </is>
+      </c>
+      <c r="B149" s="42" t="inlineStr">
+        <is>
+          <t>N5 字数</t>
+        </is>
+      </c>
+      <c r="C149" s="42" t="inlineStr">
+        <is>
+          <t>N4 字数</t>
+        </is>
+      </c>
+      <c r="D149" s="42" t="inlineStr">
+        <is>
+          <t>N3 字数</t>
+        </is>
+      </c>
+      <c r="E149" s="42" t="inlineStr">
+        <is>
+          <t>扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="43" t="inlineStr">
+        <is>
+          <t>読み（認識）</t>
+        </is>
+      </c>
+      <c r="B150" s="43" t="n">
+        <v>79</v>
+      </c>
+      <c r="C150" s="43" t="n">
+        <v>166</v>
+      </c>
+      <c r="D150" s="43" t="n">
+        <v>367</v>
+      </c>
+      <c r="E150" s="43" t="inlineStr">
+        <is>
+          <t>面(read)・全字</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="43" t="inlineStr">
+        <is>
+          <t>意味（認識）</t>
+        </is>
+      </c>
+      <c r="B151" s="43" t="n">
+        <v>77</v>
+      </c>
+      <c r="C151" s="43" t="n">
+        <v>141</v>
+      </c>
+      <c r="D151" s="43" t="n">
+        <v>311</v>
+      </c>
+      <c r="E151" s="43" t="inlineStr">
+        <is>
+          <t>面(mean)・意味が立つ字</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="43" t="inlineStr">
+        <is>
+          <t>聞き取り</t>
+        </is>
+      </c>
+      <c r="B152" s="43" t="n">
+        <v>79</v>
+      </c>
+      <c r="C152" s="43" t="n">
+        <v>166</v>
+      </c>
+      <c r="D152" s="43" t="n">
+        <v>367</v>
+      </c>
+      <c r="E152" s="43" t="inlineStr">
+        <is>
+          <t>面(listen)・全字</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="43" t="inlineStr">
+        <is>
+          <t>形の弁別</t>
+        </is>
+      </c>
+      <c r="B153" s="43" t="n">
+        <v>62</v>
+      </c>
+      <c r="C153" s="43" t="n">
+        <v>159</v>
+      </c>
+      <c r="D153" s="43" t="n">
+        <v>336</v>
+      </c>
+      <c r="E153" s="43" t="inlineStr">
+        <is>
+          <t>面(form)・似た字3つ揃う字</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="43" t="inlineStr">
+        <is>
+          <t>書き取り</t>
+        </is>
+      </c>
+      <c r="B154" s="43" t="n">
+        <v>79</v>
+      </c>
+      <c r="C154" s="43" t="n">
+        <v>166</v>
+      </c>
+      <c r="D154" s="43" t="n">
+        <v>367</v>
+      </c>
+      <c r="E154" s="43" t="inlineStr">
+        <is>
+          <t>練習（面に非計上）</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="72" t="inlineStr">
+        <is>
+          <t>※漢字の「覚えた」=作れる面(読み/意味/聞き取り/形)の加重平均≥0.6。書き取りは手書き産出の練習で面には数えない。アプリの結線=KanjiRecognition(意味/読み)・KanjiForm(形)・ListeningQuiz(聞き取り)・Kakitori(書き取り=練習)。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
+    <mergeCell ref="A144:G144"/>
+    <mergeCell ref="A156:E156"/>
+    <mergeCell ref="A131:G131"/>
     <mergeCell ref="A117:G117"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -9462,7 +9462,7 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>文法 面数分布 — 1文法点が何面(試験3大問＋学習ドリル2)に問題を持つか（2026-08-26）</t>
+          <t>文法 面数分布 — 1文法点が何面(試験3大問＋学習ドリル2)に問題を持つか（2026-08-28 更新）</t>
         </is>
       </c>
     </row>
@@ -9510,27 +9510,27 @@
         </is>
       </c>
       <c r="B123" s="43" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C123" s="43" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D123" s="43" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E123" s="43" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="F123" s="43" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="G123" s="43" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>76%</t>
         </is>
       </c>
     </row>
@@ -9541,27 +9541,27 @@
         </is>
       </c>
       <c r="B124" s="43" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C124" s="43" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D124" s="43" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E124" s="43" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="F124" s="43" t="inlineStr">
         <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="G124" s="43" t="inlineStr">
+        <is>
           <t>24%</t>
-        </is>
-      </c>
-      <c r="G124" s="43" t="inlineStr">
-        <is>
-          <t>23%</t>
         </is>
       </c>
     </row>
@@ -9572,27 +9572,27 @@
         </is>
       </c>
       <c r="B125" s="43" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C125" s="43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D125" s="43" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E125" s="43" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F125" s="43" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G125" s="43" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="B126" s="43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C126" s="43" t="n">
         <v>0</v>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="E126" s="43" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F126" s="43" t="inlineStr">
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B129" s="44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C129" s="44" t="n">
         <v>131</v>
@@ -9723,7 +9723,7 @@
     <row r="131">
       <c r="A131" s="72" t="inlineStr">
         <is>
-          <t>※面(最大5)：①文法形式判断(穴埋め) ②文の組み立て ③文章の文法（＝試験の文法3大問）＋④意味を選ぶ(受容) ⑤文法パズル(産出)（＝学習ドリル2つ）。数字は「その文法点が現時点で問題を持つ面の数」＝深さ。単位=文法点(pointId)。母数は指標対象外の n5-g-92（本文非依存の活用ドリル）を除いた N5 91/N4 131/N3 186点。0～1面が0なのは、意味ドリルが全点対象＋少なくとも1大問には必ず出るため下限が実質2面だから。（2026-08-26 新規作成・集計=scratchpad/facet_hist_gk.ts）</t>
+          <t>※面(最大5)：①文法形式判断 ②文の組み立て ③文章の文法（試験3大問）＋④意味を選ぶ ⑤文法パズル(産出)（学習ドリル2）。単位=文法点(pointId・n5-g-92除外)。母数 N5 90/N4 131/N3 186。2026-08-28: 薄い点を作問で全面手当て→3面も消滅、全点4面以上（パズル不可の型は4面止まり）。集計=scratchpad/facet_emit.ts。</t>
         </is>
       </c>
     </row>
@@ -9737,7 +9737,7 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>漢字 面数分布 — 1漢字が何面(読み/意味/聞き取り/形)を作れるか（2026-08-26 改訂・新モデル）</t>
+          <t>漢字 面数分布 — 1漢字が何面(読み/意味/聞き取り/形)を作れるか（2026-08-28 全4面化）</t>
         </is>
       </c>
     </row>
@@ -9785,27 +9785,27 @@
         </is>
       </c>
       <c r="B137" s="43" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C137" s="43" t="n">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="D137" s="43" t="n">
-        <v>283</v>
+        <v>367</v>
       </c>
       <c r="E137" s="43" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F137" s="43" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G137" s="43" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -9816,27 +9816,27 @@
         </is>
       </c>
       <c r="B138" s="43" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C138" s="43" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D138" s="43" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="E138" s="43" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F138" s="43" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G138" s="43" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -9850,10 +9850,10 @@
         <v>0</v>
       </c>
       <c r="C139" s="43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D139" s="43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E139" s="43" t="inlineStr">
         <is>
@@ -9862,12 +9862,12 @@
       </c>
       <c r="F139" s="43" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G139" s="43" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9967,7 @@
     <row r="144">
       <c r="A144" s="72" t="inlineStr">
         <is>
-          <t>※漢字の面=4面: 読み(read・認識テスト)／意味(mean・認識テスト・意味が立つ字のみ)／聞き取り(listen・全字)／形(form・似た字の弁別・類似字が3つ揃う字のみ)。数字は「その字で作れる面の数」＝深さ。読み・聞き取りは全字で作れるので下限は2面。意味が立つ字(meaningClear)= N5 77/N4 141/N3 311、形が作れる字(似た字3つ揃い)= N5 62/N4 159/N3 336。※書き取り(手書き産出)は「練習」＝面に非計上(ユーザー方針2026-08-26)。母数=当該級の漢字字数 N5 79/N4 166/N3 367。アプリのカバー率(coverageBars)は作れる面の加重平均≥0.6で「覚えた」と判定。集計=kanjiFacets.json＋kanjiSimilar.json。</t>
+          <t>※漢字の面=4面: 読み(全字)／意味(全字・辞書glossで判定＝方針A 2026-08-28)／聞き取り(全字)／形(似た字4択・級内の似字3つを55字へ追加し全字化)。→全612字が4面。母数 N5 79/N4 166/N3 367。書き取りは練習(面外)。集計=kanjiFacets.json＋kanjiSimilar.json。</t>
         </is>
       </c>
     </row>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -9125,7 +9125,7 @@
     <row r="104" ht="15.6" customHeight="1" s="71">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>語彙 面数分布 — 1語が何面(大問/ドリル)に問題を持つか（2026-08-26 更新）</t>
+          <t>語彙 面数分布 — 1語が何面(大問/ドリル)に問題を持つか（2026-08-28 更新: カタカナ表記83問を反映）</t>
         </is>
       </c>
     </row>
@@ -9297,13 +9297,13 @@
         </is>
       </c>
       <c r="B111" s="43" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C111" s="43" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D111" s="43" t="n">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="E111" s="43" t="inlineStr">
         <is>
@@ -9312,12 +9312,12 @@
       </c>
       <c r="F111" s="43" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G111" s="43" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>8%</t>
         </is>
       </c>
     </row>
@@ -9328,13 +9328,13 @@
         </is>
       </c>
       <c r="B112" s="43" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C112" s="43" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="D112" s="43" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E112" s="43" t="inlineStr">
         <is>
@@ -9343,12 +9343,12 @@
       </c>
       <c r="F112" s="43" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G112" s="43" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1%</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
     <row r="117">
       <c r="A117" s="72" t="inlineStr">
         <is>
-          <t>※面(=大問/ドリル)は最大7つ：①漢字読み ②表記 ③文脈規定 ④言い換え類義 ⑤用法（＝試験の5大問）＋⑥語彙パズル(産出) ⑦聞き取り（＝学習ドリル2つ）。数字は「その語が現時点で問題を持つ面の数」＝深さ。N5の7面が0なのは用法大問がN5には存在しない（用法はN4/N3のみ）ためで、N5の上限は6面（構造的）。0面はいずれも接頭・接尾辞（何～/～君/～観）＝単独問題が作れない語。母数(合計行)は束縛形態素9語(vocabMetricExcluded.json・全て0面)を除いた N5 719/N4 668/N3 2145。 ／ 2026-08-26 更新: 言い換え835問＋用法(N3 200/N4 252)のcontent反映を再集計。N4は7面が 69→319語(48%)・N3は7面が 42→223語(10%)へ大幅増（言い換え・用法の追加で深さが増した）。集計=scratchpad/facet_hist.ts。</t>
+          <t>※面(最大7)：①漢字読み ②表記(漢字/カタカナ) ③文脈規定 ④言い換え ⑤用法（試験5大問）＋⑥語彙パズル(産出) ⑦聞き取り。2026-08-28: カタカナ外来語83語に表記(カタカナ)を作問(公式に実在・N4/N3はほぼ空)→2面が N5 35→33/N4 37→4/N3 60→12 に減。母数 N5 719/N4 668/N3 2145。</t>
         </is>
       </c>
     </row>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -7077,7 +7077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J156"/>
+  <dimension ref="A1:J159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="46" customWidth="1" style="71" min="1" max="1"/>
@@ -7496,7 +7496,7 @@
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
         <is>
-          <t>※全ID母数=級内の全語彙数。真の母数=その大問が本当に作れる語だけ＝【漢字読み/表記】漢字を含む語 【文脈規定/用法】どの語でも作れる=全ID 【言い換え類義】言い換え可能語(iikaePossible p=1)。真のカバー率=covered/真の母数(2026-08-24 全大問更新)。漢字読み/表記のN3は今回498語追加で74→99%(真)。言い換え類義は新規EXCEL問題(未マージ)を含む。 ※2026-08-24: 束縛形態素(助詞/接尾辞)で単独の語彙問題が作れず文法点として文法側でカバーされる9語(〜ずつ/〜だけ/〜時とき/〜など/〜しまう/〜ばかり/〜まま/〜よると/〜ついて=vocabMetricExcluded.json)を全語彙数から除外→N5 723→719・N4 673→668(N3据置)。二重計上/紛らわしさ回避。</t>
+          <t>※全ID母数=級内の全語彙数。真の母数=その大問が本当に作れる語だけ＝【漢字読み/表記】漢字を含む語 【文脈規定/用法】どの語でも作れる=全ID 【言い換え類義】言い換え可能語(iikaePossible p=1)。真のカバー率=covered/真の母数(2026-08-24 全大問更新)。漢字読み/表記のN3は今回498語追加で74→99%(真)。言い換え類義は新規EXCEL問題(未マージ)を含む。 ※2026-08-24: 束縛形態素(助詞/接尾辞)で単独の語彙問題が作れず文法点として文法側でカバーされる9語(〜ずつ/〜だけ/〜時とき/〜など/〜しまう/〜ばかり/〜まま/〜よると/〜ついて=vocabMetricExcluded.json)を全語彙数から除外→N5 723→719・N4 673→668(N3据置)。二重計上/紛らわしさ回避。　※2026-08-28追加: 感動詞 あ・ああ の2語も母数除外→N5 719→718・N4 668→667(計11語)。</t>
         </is>
       </c>
       <c r="G21" s="23" t="n"/>
@@ -7567,7 +7567,7 @@
     <row r="25" ht="28.8" customHeight="1" s="71">
       <c r="A25" s="34" t="inlineStr">
         <is>
-          <t>語彙単語(719)</t>
+          <t>語彙単語(718)</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
@@ -7624,7 +7624,7 @@
         <v>672</v>
       </c>
       <c r="E27" s="25" t="n">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F27" s="37" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
       <c r="G27" s="28" t="n"/>
       <c r="H27" s="72" t="n"/>
       <c r="I27" s="33" t="n">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J27" s="69" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>231</v>
       </c>
       <c r="E28" s="25" t="n">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F28" s="38" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>3</v>
       </c>
       <c r="E29" s="85" t="n">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F29" s="86" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
     <row r="36" ht="28.8" customHeight="1" s="71">
       <c r="A36" s="34" t="inlineStr">
         <is>
-          <t>語彙単語(668)</t>
+          <t>語彙単語(667)</t>
         </is>
       </c>
       <c r="B36" s="25" t="inlineStr">
@@ -7919,7 +7919,7 @@
         <v>651</v>
       </c>
       <c r="E38" s="25" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F38" s="37" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
       <c r="G38" s="28" t="n"/>
       <c r="H38" s="72" t="n"/>
       <c r="I38" s="33" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="J38" s="69" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>406</v>
       </c>
       <c r="E39" s="25" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>565</v>
       </c>
       <c r="E40" s="25" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F40" s="38" t="inlineStr">
         <is>
@@ -8482,18 +8482,18 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>606</v>
+        <v>705</v>
       </c>
       <c r="D78" t="n">
         <v>723</v>
       </c>
       <c r="E78" s="36" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>606</v>
+        <v>705</v>
       </c>
       <c r="G78" s="36" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="H78" s="72" t="inlineStr">
         <is>
-          <t>見かけ84%だが真の100%＝差16ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
+          <t>産出可705/723=98%(真100%＝残りは"作れない天井")。かなタイルで単語を作る。2026-08-28拡大: カタカナ語(カタカナタイル)・2〜8モーラ・接辞(～を外し例文の空所)も対象化。残る対象外=1モーラ語・例文で空所化できない接辞のみ。</t>
         </is>
       </c>
     </row>
@@ -8711,18 +8711,18 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>576</v>
+        <v>646</v>
       </c>
       <c r="D86" t="n">
         <v>673</v>
       </c>
       <c r="E86" s="36" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>576</v>
+        <v>646</v>
       </c>
       <c r="G86" s="36" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="H86" s="72" t="inlineStr">
         <is>
-          <t>見かけ86%だが真の100%＝差14ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
+          <t>産出可646/673=96%(真100%＝残りは"作れない天井")。かなタイルで単語を作る。2026-08-28拡大: カタカナ語(カタカナタイル)・2〜8モーラ・接辞(～を外し例文の空所)も対象化。残る対象外=1モーラ語・例文で空所化できない接辞のみ。</t>
         </is>
       </c>
     </row>
@@ -8940,18 +8940,18 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1963</v>
+        <v>2092</v>
       </c>
       <c r="D94" t="n">
         <v>2145</v>
       </c>
       <c r="E94" s="36" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1963</v>
+        <v>2092</v>
       </c>
       <c r="G94" s="36" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="H94" s="72" t="inlineStr">
         <is>
-          <t>見かけ92%だが真の100%＝差8ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
+          <t>産出可2092/2145=98%(真100%＝残りは"作れない天井")。かなタイルで単語を作る。2026-08-28拡大: カタカナ語(カタカナタイル)・2〜8モーラ・接辞(～を外し例文の空所)も対象化。残る対象外=1モーラ語・例文で空所化できない接辞のみ。</t>
         </is>
       </c>
     </row>
@@ -9125,7 +9125,7 @@
     <row r="104" ht="15.6" customHeight="1" s="71">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>語彙 面数分布 — 1語が何面(大問/ドリル)に問題を持つか（2026-08-28 更新: カタカナ表記83問を反映）</t>
+          <t>語彙 面数分布 — 1語が何面(大問/ドリル)に問題を持つか（2026-08-28 受容3面 いみ/よみ/かたち＋産出拡大[カタカナ/8モーラ/接辞]反映＝最大10面）</t>
         </is>
       </c>
     </row>
@@ -9169,14 +9169,14 @@
     <row r="107">
       <c r="A107" s="43" t="inlineStr">
         <is>
-          <t>7面</t>
+          <t>10面</t>
         </is>
       </c>
       <c r="B107" s="43" t="n">
         <v>0</v>
       </c>
       <c r="C107" s="43" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D107" s="43" t="n">
         <v>223</v>
@@ -9200,17 +9200,17 @@
     <row r="108">
       <c r="A108" s="43" t="inlineStr">
         <is>
-          <t>6面</t>
+          <t>9面</t>
         </is>
       </c>
       <c r="B108" s="43" t="n">
         <v>164</v>
       </c>
       <c r="C108" s="43" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D108" s="43" t="n">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="E108" s="43" t="inlineStr">
         <is>
@@ -9224,24 +9224,24 @@
       </c>
       <c r="G108" s="43" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>56%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="43" t="inlineStr">
         <is>
-          <t>5面</t>
+          <t>8面</t>
         </is>
       </c>
       <c r="B109" s="43" t="n">
         <v>316</v>
       </c>
       <c r="C109" s="43" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="D109" s="43" t="n">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="E109" s="43" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="F109" s="43" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G109" s="43" t="inlineStr">
@@ -9262,406 +9262,406 @@
     <row r="110">
       <c r="A110" s="43" t="inlineStr">
         <is>
-          <t>4面</t>
+          <t>7面</t>
         </is>
       </c>
       <c r="B110" s="43" t="n">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C110" s="43" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D110" s="43" t="n">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="E110" s="43" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F110" s="43" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G110" s="43" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>1%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="43" t="inlineStr">
         <is>
-          <t>3面</t>
+          <t>6面</t>
         </is>
       </c>
       <c r="B111" s="43" t="n">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="C111" s="43" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D111" s="43" t="n">
-        <v>164</v>
+        <v>35</v>
       </c>
       <c r="E111" s="43" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="F111" s="43" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="G111" s="43" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="43" t="inlineStr">
         <is>
-          <t>2面</t>
+          <t>5面</t>
         </is>
       </c>
       <c r="B112" s="43" t="n">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="C112" s="43" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="D112" s="43" t="n">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="E112" s="43" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="F112" s="43" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G112" s="43" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>8%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="43" t="inlineStr">
         <is>
-          <t>1面</t>
+          <t>4面</t>
         </is>
       </c>
       <c r="B113" s="43" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="C113" s="43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D113" s="43" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="E113" s="43" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="F113" s="43" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G113" s="43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="43" t="inlineStr">
         <is>
-          <t>0面</t>
+          <t>3面</t>
         </is>
       </c>
       <c r="B114" s="43" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C114" s="43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D114" s="43" t="n">
         <v>1</v>
       </c>
       <c r="E114" s="43" t="inlineStr">
         <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="F114" s="43" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G114" s="43" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="F114" s="43" t="inlineStr">
+    </row>
+    <row r="115">
+      <c r="A115" s="43" t="inlineStr">
+        <is>
+          <t>2面</t>
+        </is>
+      </c>
+      <c r="B115" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D115" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="43" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G114" s="43" t="inlineStr">
+      <c r="F115" s="43" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="44" t="inlineStr">
+      <c r="G115" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="43" t="inlineStr">
+        <is>
+          <t>1面</t>
+        </is>
+      </c>
+      <c r="B116" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F116" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G116" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="43" t="inlineStr">
+        <is>
+          <t>0面</t>
+        </is>
+      </c>
+      <c r="B117" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F117" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G117" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="44" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B115" s="44" t="n">
-        <v>719</v>
-      </c>
-      <c r="C115" s="44" t="n">
-        <v>668</v>
-      </c>
-      <c r="D115" s="44" t="n">
+      <c r="B118" s="44" t="n">
+        <v>718</v>
+      </c>
+      <c r="C118" s="44" t="n">
+        <v>667</v>
+      </c>
+      <c r="D118" s="44" t="n">
         <v>2145</v>
       </c>
-      <c r="E115" s="44" t="inlineStr">
+      <c r="E118" s="44" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F115" s="44" t="inlineStr">
+      <c r="F118" s="44" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G115" s="44" t="inlineStr">
+      <c r="G118" s="44" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="72" t="inlineStr">
-        <is>
-          <t>※面(最大7)：①漢字読み ②表記(漢字/カタカナ) ③文脈規定 ④言い換え ⑤用法（試験5大問）＋⑥語彙パズル(産出) ⑦聞き取り。2026-08-28: カタカナ外来語83語に表記(カタカナ)を作問(公式に実在・N4/N3はほぼ空)→2面が N5 35→33/N4 37→4/N3 60→12 に減。母数 N5 719/N4 668/N3 2145。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="8" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="72" t="inlineStr">
+        <is>
+          <t>※面(最大10)：①漢字読み ②表記 ③文脈規定 ④言い換え ⑤用法（試験5大問）＋⑥語彙パズル(産出) ⑦聞き取り＋⑧いみ ⑨よみ ⑩かたち（受容3ドリル・文脈なし4択）。産出はカタカナ語(カタカナタイル)・2〜8モーラへ拡大(2026-08-28)＝産出カバー N5 671/N4 626/N3 2090。いみは全語100%。母数 N5 718/N4 667/N3 2145。集計=scratchpad/facet_emit.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="inlineStr">
         <is>
           <t>◆ 文法 面数分布（1文法点が何面に問題を持つか）</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="1" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
         <is>
           <t>文法 面数分布 — 1文法点が何面(試験3大問＋学習ドリル2)に問題を持つか（2026-08-28 更新）</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="42" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="42" t="inlineStr">
         <is>
           <t>面数</t>
         </is>
       </c>
-      <c r="B122" s="42" t="inlineStr">
+      <c r="B125" s="42" t="inlineStr">
         <is>
           <t>N5 点数</t>
         </is>
       </c>
-      <c r="C122" s="42" t="inlineStr">
+      <c r="C125" s="42" t="inlineStr">
         <is>
           <t>N4 点数</t>
         </is>
       </c>
-      <c r="D122" s="42" t="inlineStr">
+      <c r="D125" s="42" t="inlineStr">
         <is>
           <t>N3 点数</t>
         </is>
       </c>
-      <c r="E122" s="42" t="inlineStr">
+      <c r="E125" s="42" t="inlineStr">
         <is>
           <t>（参考）N5%</t>
         </is>
       </c>
-      <c r="F122" s="42" t="inlineStr">
+      <c r="F125" s="42" t="inlineStr">
         <is>
           <t>N4%</t>
         </is>
       </c>
-      <c r="G122" s="42" t="inlineStr">
+      <c r="G125" s="42" t="inlineStr">
         <is>
           <t>N3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="43" t="inlineStr">
-        <is>
-          <t>5面</t>
-        </is>
-      </c>
-      <c r="B123" s="43" t="n">
-        <v>56</v>
-      </c>
-      <c r="C123" s="43" t="n">
-        <v>96</v>
-      </c>
-      <c r="D123" s="43" t="n">
-        <v>142</v>
-      </c>
-      <c r="E123" s="43" t="inlineStr">
-        <is>
-          <t>62%</t>
-        </is>
-      </c>
-      <c r="F123" s="43" t="inlineStr">
-        <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="G123" s="43" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="43" t="inlineStr">
-        <is>
-          <t>4面</t>
-        </is>
-      </c>
-      <c r="B124" s="43" t="n">
-        <v>34</v>
-      </c>
-      <c r="C124" s="43" t="n">
-        <v>35</v>
-      </c>
-      <c r="D124" s="43" t="n">
-        <v>44</v>
-      </c>
-      <c r="E124" s="43" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="F124" s="43" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="G124" s="43" t="inlineStr">
-        <is>
-          <t>24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="43" t="inlineStr">
-        <is>
-          <t>3面</t>
-        </is>
-      </c>
-      <c r="B125" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C125" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" s="43" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F125" s="43" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G125" s="43" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="43" t="inlineStr">
         <is>
-          <t>2面</t>
+          <t>5面</t>
         </is>
       </c>
       <c r="B126" s="43" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="C126" s="43" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D126" s="43" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="E126" s="43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="F126" s="43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="G126" s="43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>76%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="43" t="inlineStr">
         <is>
-          <t>1面</t>
+          <t>4面</t>
         </is>
       </c>
       <c r="B127" s="43" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C127" s="43" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D127" s="43" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E127" s="43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="F127" s="43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G127" s="43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>24%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="43" t="inlineStr">
         <is>
-          <t>0面</t>
+          <t>3面</t>
         </is>
       </c>
       <c r="B128" s="43" t="n">
@@ -9690,222 +9690,222 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="44" t="inlineStr">
+      <c r="A129" s="43" t="inlineStr">
+        <is>
+          <t>2面</t>
+        </is>
+      </c>
+      <c r="B129" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F129" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G129" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="43" t="inlineStr">
+        <is>
+          <t>1面</t>
+        </is>
+      </c>
+      <c r="B130" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F130" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G130" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="43" t="inlineStr">
+        <is>
+          <t>0面</t>
+        </is>
+      </c>
+      <c r="B131" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F131" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G131" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="44" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B129" s="44" t="n">
+      <c r="B132" s="44" t="n">
         <v>90</v>
       </c>
-      <c r="C129" s="44" t="n">
+      <c r="C132" s="44" t="n">
         <v>131</v>
       </c>
-      <c r="D129" s="44" t="n">
+      <c r="D132" s="44" t="n">
         <v>186</v>
       </c>
-      <c r="E129" s="44" t="inlineStr">
+      <c r="E132" s="44" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F129" s="44" t="inlineStr">
+      <c r="F132" s="44" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G129" s="44" t="inlineStr">
+      <c r="G132" s="44" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="72" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="72" t="inlineStr">
         <is>
           <t>※面(最大5)：①文法形式判断 ②文の組み立て ③文章の文法（試験3大問）＋④意味を選ぶ ⑤文法パズル(産出)（学習ドリル2）。単位=文法点(pointId・n5-g-92除外)。母数 N5 90/N4 131/N3 186。2026-08-28: 薄い点を作問で全面手当て→3面も消滅、全点4面以上（パズル不可の型は4面止まり）。集計=scratchpad/facet_emit.ts。</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="8" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="8" t="inlineStr">
         <is>
           <t>◆ 漢字 面数分布（1漢字が何面を作れるか・新4面モデル）</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="1" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
         <is>
           <t>漢字 面数分布 — 1漢字が何面(読み/意味/聞き取り/形)を作れるか（2026-08-28 全4面化）</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="42" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="42" t="inlineStr">
         <is>
           <t>面数</t>
         </is>
       </c>
-      <c r="B136" s="42" t="inlineStr">
+      <c r="B139" s="42" t="inlineStr">
         <is>
           <t>N5 字数</t>
         </is>
       </c>
-      <c r="C136" s="42" t="inlineStr">
+      <c r="C139" s="42" t="inlineStr">
         <is>
           <t>N4 字数</t>
         </is>
       </c>
-      <c r="D136" s="42" t="inlineStr">
+      <c r="D139" s="42" t="inlineStr">
         <is>
           <t>N3 字数</t>
         </is>
       </c>
-      <c r="E136" s="42" t="inlineStr">
+      <c r="E139" s="42" t="inlineStr">
         <is>
           <t>（参考）N5%</t>
         </is>
       </c>
-      <c r="F136" s="42" t="inlineStr">
+      <c r="F139" s="42" t="inlineStr">
         <is>
           <t>N4%</t>
         </is>
       </c>
-      <c r="G136" s="42" t="inlineStr">
+      <c r="G139" s="42" t="inlineStr">
         <is>
           <t>N3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="43" t="inlineStr">
-        <is>
-          <t>4面</t>
-        </is>
-      </c>
-      <c r="B137" s="43" t="n">
-        <v>79</v>
-      </c>
-      <c r="C137" s="43" t="n">
-        <v>166</v>
-      </c>
-      <c r="D137" s="43" t="n">
-        <v>367</v>
-      </c>
-      <c r="E137" s="43" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F137" s="43" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G137" s="43" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="43" t="inlineStr">
-        <is>
-          <t>3面</t>
-        </is>
-      </c>
-      <c r="B138" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C138" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E138" s="43" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F138" s="43" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G138" s="43" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="43" t="inlineStr">
-        <is>
-          <t>2面</t>
-        </is>
-      </c>
-      <c r="B139" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C139" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" s="43" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F139" s="43" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G139" s="43" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="43" t="inlineStr">
         <is>
-          <t>1面</t>
+          <t>4面</t>
         </is>
       </c>
       <c r="B140" s="43" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="C140" s="43" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="D140" s="43" t="n">
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="E140" s="43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F140" s="43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G140" s="43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="43" t="inlineStr">
         <is>
-          <t>0面</t>
+          <t>3面</t>
         </is>
       </c>
       <c r="B141" s="43" t="n">
@@ -9934,191 +9934,284 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="44" t="inlineStr">
+      <c r="A142" s="43" t="inlineStr">
+        <is>
+          <t>2面</t>
+        </is>
+      </c>
+      <c r="B142" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C142" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F142" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G142" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="43" t="inlineStr">
+        <is>
+          <t>1面</t>
+        </is>
+      </c>
+      <c r="B143" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C143" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F143" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G143" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="43" t="inlineStr">
+        <is>
+          <t>0面</t>
+        </is>
+      </c>
+      <c r="B144" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F144" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G144" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="44" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B142" s="44" t="n">
+      <c r="B145" s="44" t="n">
         <v>79</v>
       </c>
-      <c r="C142" s="44" t="n">
+      <c r="C145" s="44" t="n">
         <v>166</v>
       </c>
-      <c r="D142" s="44" t="n">
+      <c r="D145" s="44" t="n">
         <v>367</v>
       </c>
-      <c r="E142" s="44" t="inlineStr">
+      <c r="E145" s="44" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F142" s="44" t="inlineStr">
+      <c r="F145" s="44" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G142" s="44" t="inlineStr">
+      <c r="G145" s="44" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="72" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="72" t="inlineStr">
         <is>
           <t>※漢字の面=4面: 読み(全字)／意味(全字・辞書glossで判定＝方針A 2026-08-28)／聞き取り(全字)／形(似た字4択・級内の似字3つを55字へ追加し全字化)。→全612字が4面。母数 N5 79/N4 166/N3 367。書き取りは練習(面外)。集計=kanjiFacets.json＋kanjiSimilar.json。</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="8" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="8" t="inlineStr">
         <is>
           <t>◆ 漢字ID×面 詳細（1漢字IDが紐づく面・対象字数）</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="1" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
         <is>
           <t>漢字ID＝字。面=読み/意味/聞き取り/形の4面＋書き(練習・面外)。字数=当該級の対象字数（2026-08-26）</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="42" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="42" t="inlineStr">
         <is>
           <t>面（ドリル）</t>
         </is>
       </c>
-      <c r="B149" s="42" t="inlineStr">
+      <c r="B152" s="42" t="inlineStr">
         <is>
           <t>N5 字数</t>
         </is>
       </c>
-      <c r="C149" s="42" t="inlineStr">
+      <c r="C152" s="42" t="inlineStr">
         <is>
           <t>N4 字数</t>
         </is>
       </c>
-      <c r="D149" s="42" t="inlineStr">
+      <c r="D152" s="42" t="inlineStr">
         <is>
           <t>N3 字数</t>
         </is>
       </c>
-      <c r="E149" s="42" t="inlineStr">
+      <c r="E152" s="42" t="inlineStr">
         <is>
           <t>扱い</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="43" t="inlineStr">
-        <is>
-          <t>読み（認識）</t>
-        </is>
-      </c>
-      <c r="B150" s="43" t="n">
-        <v>79</v>
-      </c>
-      <c r="C150" s="43" t="n">
-        <v>166</v>
-      </c>
-      <c r="D150" s="43" t="n">
-        <v>367</v>
-      </c>
-      <c r="E150" s="43" t="inlineStr">
-        <is>
-          <t>面(read)・全字</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="43" t="inlineStr">
-        <is>
-          <t>意味（認識）</t>
-        </is>
-      </c>
-      <c r="B151" s="43" t="n">
-        <v>77</v>
-      </c>
-      <c r="C151" s="43" t="n">
-        <v>141</v>
-      </c>
-      <c r="D151" s="43" t="n">
-        <v>311</v>
-      </c>
-      <c r="E151" s="43" t="inlineStr">
-        <is>
-          <t>面(mean)・意味が立つ字</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="43" t="inlineStr">
-        <is>
-          <t>聞き取り</t>
-        </is>
-      </c>
-      <c r="B152" s="43" t="n">
-        <v>79</v>
-      </c>
-      <c r="C152" s="43" t="n">
-        <v>166</v>
-      </c>
-      <c r="D152" s="43" t="n">
-        <v>367</v>
-      </c>
-      <c r="E152" s="43" t="inlineStr">
-        <is>
-          <t>面(listen)・全字</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="43" t="inlineStr">
         <is>
-          <t>形の弁別</t>
+          <t>読み（認識）</t>
         </is>
       </c>
       <c r="B153" s="43" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C153" s="43" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D153" s="43" t="n">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="E153" s="43" t="inlineStr">
         <is>
-          <t>面(form)・似た字3つ揃う字</t>
+          <t>面(read)・全字</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="43" t="inlineStr">
         <is>
+          <t>意味（認識）</t>
+        </is>
+      </c>
+      <c r="B154" s="43" t="n">
+        <v>77</v>
+      </c>
+      <c r="C154" s="43" t="n">
+        <v>141</v>
+      </c>
+      <c r="D154" s="43" t="n">
+        <v>311</v>
+      </c>
+      <c r="E154" s="43" t="inlineStr">
+        <is>
+          <t>面(mean)・意味が立つ字</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="43" t="inlineStr">
+        <is>
+          <t>聞き取り</t>
+        </is>
+      </c>
+      <c r="B155" s="43" t="n">
+        <v>79</v>
+      </c>
+      <c r="C155" s="43" t="n">
+        <v>166</v>
+      </c>
+      <c r="D155" s="43" t="n">
+        <v>367</v>
+      </c>
+      <c r="E155" s="43" t="inlineStr">
+        <is>
+          <t>面(listen)・全字</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="43" t="inlineStr">
+        <is>
+          <t>形の弁別</t>
+        </is>
+      </c>
+      <c r="B156" s="43" t="n">
+        <v>62</v>
+      </c>
+      <c r="C156" s="43" t="n">
+        <v>159</v>
+      </c>
+      <c r="D156" s="43" t="n">
+        <v>336</v>
+      </c>
+      <c r="E156" s="43" t="inlineStr">
+        <is>
+          <t>面(form)・似た字3つ揃う字</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="43" t="inlineStr">
+        <is>
           <t>書き取り</t>
         </is>
       </c>
-      <c r="B154" s="43" t="n">
+      <c r="B157" s="43" t="n">
         <v>79</v>
       </c>
-      <c r="C154" s="43" t="n">
+      <c r="C157" s="43" t="n">
         <v>166</v>
       </c>
-      <c r="D154" s="43" t="n">
+      <c r="D157" s="43" t="n">
         <v>367</v>
       </c>
-      <c r="E154" s="43" t="inlineStr">
+      <c r="E157" s="43" t="inlineStr">
         <is>
           <t>練習（面に非計上）</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="72" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="72" t="inlineStr">
         <is>
           <t>※漢字の「覚えた」=作れる面(読み/意味/聞き取り/形)の加重平均≥0.6。書き取りは手書き産出の練習で面には数えない。アプリの結線=KanjiRecognition(意味/読み)・KanjiForm(形)・ListeningQuiz(聞き取り)・Kakitori(書き取り=練習)。</t>
         </is>
@@ -10126,10 +10219,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A144:G144"/>
-    <mergeCell ref="A156:E156"/>
-    <mergeCell ref="A131:G131"/>
-    <mergeCell ref="A117:G117"/>
+    <mergeCell ref="A159:E159"/>
+    <mergeCell ref="A120:G120"/>
+    <mergeCell ref="A147:G147"/>
+    <mergeCell ref="A134:G134"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -7077,7 +7077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J159"/>
+  <dimension ref="A1:K159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="46" customWidth="1" style="71" min="1" max="1"/>
@@ -7158,7 +7158,7 @@
         <v>673</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="E6" s="25" t="n">
         <v>3541</v>
@@ -7478,6 +7478,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="22.05" customHeight="1" s="71">
       <c r="A19" s="8" t="inlineStr">
         <is>
@@ -7567,7 +7568,7 @@
     <row r="25" ht="28.8" customHeight="1" s="71">
       <c r="A25" s="34" t="inlineStr">
         <is>
-          <t>語彙単語(718)</t>
+          <t>語彙単語(717)</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
@@ -7624,7 +7625,7 @@
         <v>672</v>
       </c>
       <c r="E27" s="25" t="n">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F27" s="37" t="inlineStr">
         <is>
@@ -7634,7 +7635,7 @@
       <c r="G27" s="28" t="n"/>
       <c r="H27" s="72" t="n"/>
       <c r="I27" s="33" t="n">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="J27" s="69" t="inlineStr">
         <is>
@@ -7656,7 +7657,7 @@
         <v>231</v>
       </c>
       <c r="E28" s="25" t="n">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F28" s="38" t="inlineStr">
         <is>
@@ -7692,7 +7693,7 @@
         <v>3</v>
       </c>
       <c r="E29" s="85" t="n">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F29" s="86" t="inlineStr">
         <is>
@@ -8216,7 +8217,7 @@
         <v>2090</v>
       </c>
       <c r="E49" s="25" t="n">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="F49" s="37" t="inlineStr">
         <is>
@@ -8226,7 +8227,7 @@
       <c r="G49" s="28" t="n"/>
       <c r="H49" s="72" t="n"/>
       <c r="I49" s="33" t="n">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="J49" s="69" t="inlineStr">
         <is>
@@ -8248,7 +8249,7 @@
         <v>1611</v>
       </c>
       <c r="E50" s="25" t="n">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="F50" s="35" t="inlineStr">
         <is>
@@ -8284,7 +8285,7 @@
         <v>299</v>
       </c>
       <c r="E51" s="25" t="n">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="F51" s="38" t="inlineStr">
         <is>
@@ -8393,6 +8394,19 @@
     <row r="55">
       <c r="G55" s="23" t="n"/>
     </row>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
     <row r="69">
       <c r="A69" s="21" t="inlineStr">
         <is>
@@ -8400,6 +8414,8 @@
         </is>
       </c>
     </row>
+    <row r="70"/>
+    <row r="71"/>
     <row r="72" ht="22.05" customHeight="1" s="71">
       <c r="A72" s="8" t="inlineStr">
         <is>
@@ -8421,6 +8437,7 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
@@ -8650,6 +8667,7 @@
         </is>
       </c>
     </row>
+    <row r="83"/>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
@@ -8879,6 +8897,7 @@
         </is>
       </c>
     </row>
+    <row r="91"/>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
@@ -8943,7 +8962,7 @@
         <v>2092</v>
       </c>
       <c r="D94" t="n">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="E94" s="36" t="inlineStr">
         <is>
@@ -8979,7 +8998,7 @@
         <v>2143</v>
       </c>
       <c r="D95" t="n">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="E95" s="36" t="inlineStr">
         <is>
@@ -9108,6 +9127,7 @@
         </is>
       </c>
     </row>
+    <row r="99"/>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
@@ -9115,6 +9135,8 @@
         </is>
       </c>
     </row>
+    <row r="101"/>
+    <row r="102"/>
     <row r="103" ht="22.05" customHeight="1" s="71">
       <c r="A103" s="8" t="inlineStr">
         <is>
@@ -9129,6 +9151,7 @@
         </is>
       </c>
     </row>
+    <row r="105"/>
     <row r="106">
       <c r="A106" s="42" t="inlineStr">
         <is>
@@ -9303,7 +9326,7 @@
         <v>53</v>
       </c>
       <c r="D111" s="43" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E111" s="43" t="inlineStr">
         <is>
@@ -9365,7 +9388,7 @@
         <v>11</v>
       </c>
       <c r="D113" s="43" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E113" s="43" t="inlineStr">
         <is>
@@ -9393,7 +9416,7 @@
         <v>7</v>
       </c>
       <c r="C114" s="43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D114" s="43" t="n">
         <v>1</v>
@@ -9421,13 +9444,13 @@
         </is>
       </c>
       <c r="B115" s="43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C115" s="43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D115" s="43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115" s="43" t="inlineStr">
         <is>
@@ -9514,13 +9537,13 @@
         </is>
       </c>
       <c r="B118" s="44" t="n">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C118" s="44" t="n">
         <v>667</v>
       </c>
       <c r="D118" s="44" t="n">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="E118" s="44" t="inlineStr">
         <is>
@@ -9538,6 +9561,7 @@
         </is>
       </c>
     </row>
+    <row r="119"/>
     <row r="120">
       <c r="A120" s="72" t="inlineStr">
         <is>
@@ -9545,6 +9569,7 @@
         </is>
       </c>
     </row>
+    <row r="121"/>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
@@ -9559,6 +9584,7 @@
         </is>
       </c>
     </row>
+    <row r="124"/>
     <row r="125">
       <c r="A125" s="42" t="inlineStr">
         <is>
@@ -9813,6 +9839,7 @@
         </is>
       </c>
     </row>
+    <row r="133"/>
     <row r="134">
       <c r="A134" s="72" t="inlineStr">
         <is>
@@ -9820,6 +9847,7 @@
         </is>
       </c>
     </row>
+    <row r="135"/>
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
@@ -9834,6 +9862,7 @@
         </is>
       </c>
     </row>
+    <row r="138"/>
     <row r="139">
       <c r="A139" s="42" t="inlineStr">
         <is>
@@ -10057,6 +10086,7 @@
         </is>
       </c>
     </row>
+    <row r="146"/>
     <row r="147">
       <c r="A147" s="72" t="inlineStr">
         <is>
@@ -10064,6 +10094,7 @@
         </is>
       </c>
     </row>
+    <row r="148"/>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
@@ -10078,6 +10109,7 @@
         </is>
       </c>
     </row>
+    <row r="151"/>
     <row r="152">
       <c r="A152" s="42" t="inlineStr">
         <is>
@@ -10210,6 +10242,7 @@
         </is>
       </c>
     </row>
+    <row r="158"/>
     <row r="159">
       <c r="A159" s="72" t="inlineStr">
         <is>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② カバー率" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 品質・攻略耐性" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ 習得の仕組み(説明)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ 用法カバー×バランス" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学習ドリル×カバー率" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学習ドリル×カバー率" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ 用法カバー×バランス" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大問別まとめ'!$A$1:$J$1</definedName>
@@ -3252,1048 +3252,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="71" min="1" max="1"/>
-    <col width="20" customWidth="1" style="71" min="2" max="2"/>
-    <col width="11" customWidth="1" style="71" min="3" max="3"/>
-    <col width="11" customWidth="1" style="71" min="4" max="4"/>
-    <col width="11" customWidth="1" style="71" min="5" max="5"/>
-    <col width="11" customWidth="1" style="71" min="6" max="6"/>
-    <col width="11" customWidth="1" style="71" min="7" max="7"/>
-    <col width="60" customWidth="1" style="71" min="8" max="8"/>
+    <col width="16" customWidth="1" style="71" min="1" max="1"/>
+    <col width="12" customWidth="1" style="71" min="2" max="2"/>
+    <col width="12" customWidth="1" style="71" min="3" max="3"/>
+    <col width="12" customWidth="1" style="71" min="4" max="4"/>
+    <col width="12" customWidth="1" style="71" min="5" max="5"/>
+    <col width="12" customWidth="1" style="71" min="6" max="6"/>
+    <col width="12" customWidth="1" style="71" min="7" max="7"/>
+    <col width="12" customWidth="1" style="71" min="8" max="8"/>
+    <col width="66" customWidth="1" style="71" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="104" t="inlineStr">
-        <is>
-          <t>学習ドリル×カバー率（学習タブ・各ドリルがID紐づけで対象にできる項目の広さ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>※全ID母数=レベル内の全項目(語彙数/文法点数[n5-g-92除外]/漢字数)。真の母数=そのドリルで「そもそも作れる」項目数(カタカナ語・分離型文法など"永久に不可能"を除く)＝真のカバー率が実力。試験タブの大問は別シート「単語×大問カバー率」。</t>
+      <c r="A1" s="105" t="inlineStr">
+        <is>
+          <t>用法(語の使い方) × 語彙idカバー×バランス</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="67" t="inlineStr">
+        <is>
+          <t>最終目標＝可能な限り語彙をカバー(breadth%を100%へ)。番人=src/data/usageCoverage.test.ts が「①未紐づけ0(測定可能) ②大問内で1語1問まで(集中させず広く) ③カバー数は後退させない(ラチェット)」を担保。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="104" t="inlineStr">
-        <is>
-          <t>■ N5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="109" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B5" s="109" t="inlineStr">
-        <is>
-          <t>ドリル</t>
-        </is>
-      </c>
-      <c r="C5" s="109" t="inlineStr">
-        <is>
-          <t>対象</t>
-        </is>
-      </c>
-      <c r="D5" s="109" t="inlineStr">
-        <is>
-          <t>全ID母数</t>
-        </is>
-      </c>
-      <c r="E5" s="109" t="inlineStr">
-        <is>
-          <t>全IDカバー率</t>
-        </is>
-      </c>
-      <c r="F5" s="109" t="inlineStr">
-        <is>
-          <t>真の母数</t>
-        </is>
-      </c>
-      <c r="G5" s="109" t="inlineStr">
-        <is>
-          <t>真のカバー率</t>
-        </is>
-      </c>
-      <c r="H5" s="109" t="inlineStr">
-        <is>
-          <t>点検メモ</t>
+      <c r="A4" s="67" t="inlineStr">
+        <is>
+          <t>級跨ぎ重複(同語をN4とN3の両大問で出題=冗長)＝0語。冗長は禁止せず記録のみ(復習として妥当な場合あり)＝新規作問は未カバー語を優先すると breadth が伸びる。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>語彙</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>語彙パズル(産出)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>606</v>
-      </c>
-      <c r="D6" t="n">
-        <v>723</v>
-      </c>
-      <c r="E6" s="107" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>606</v>
-      </c>
-      <c r="G6" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="72" t="inlineStr">
-        <is>
-          <t>見かけ84%だが真の100%＝差16ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
+      <c r="A6" s="104" t="inlineStr">
+        <is>
+          <t>■ 級別サマリ</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>語彙</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>聞き取り(語彙)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>681</v>
-      </c>
-      <c r="D7" t="n">
-        <v>723</v>
-      </c>
-      <c r="E7" s="107" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>681</v>
-      </c>
-      <c r="G7" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="72" t="inlineStr">
-        <is>
-          <t>見かけ94%だが真の100%＝差6ptは"作れない天井"。読みを聞いて単語を選ぶ。非自立語(接辞/助詞)・波ダッシュ語のみ対象外。</t>
+      <c r="A7" s="106" t="inlineStr">
+        <is>
+          <t>級</t>
+        </is>
+      </c>
+      <c r="B7" s="106" t="inlineStr">
+        <is>
+          <t>問題数</t>
+        </is>
+      </c>
+      <c r="C7" s="106" t="inlineStr">
+        <is>
+          <t>リンク</t>
+        </is>
+      </c>
+      <c r="D7" s="106" t="inlineStr">
+        <is>
+          <t>未紐づけ</t>
+        </is>
+      </c>
+      <c r="E7" s="106" t="inlineStr">
+        <is>
+          <t>カバー語</t>
+        </is>
+      </c>
+      <c r="F7" s="106" t="inlineStr">
+        <is>
+          <t>母数</t>
+        </is>
+      </c>
+      <c r="G7" s="106" t="inlineStr">
+        <is>
+          <t>breadth%</t>
+        </is>
+      </c>
+      <c r="H7" s="106" t="inlineStr">
+        <is>
+          <t>未カバー(backlog)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>意味を選ぶ(受容)</t>
-        </is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>571</v>
       </c>
       <c r="C8" t="n">
-        <v>91</v>
+        <v>571</v>
       </c>
       <c r="D8" t="n">
-        <v>91</v>
-      </c>
-      <c r="E8" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>573</v>
       </c>
       <c r="F8" t="n">
-        <v>91</v>
+        <v>673</v>
       </c>
       <c r="G8" s="107" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="72" t="inlineStr">
-        <is>
-          <t>文法点の意味を4択。意味を持つ全点が対象。</t>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>100</v>
+      </c>
+      <c r="I8" s="67" t="inlineStr">
+        <is>
+          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=571</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>文法パズル(産出)</t>
-        </is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>300</v>
       </c>
       <c r="C9" t="n">
-        <v>67</v>
+        <v>300</v>
       </c>
       <c r="D9" t="n">
-        <v>91</v>
-      </c>
-      <c r="E9" s="110" t="inlineStr">
-        <is>
-          <t>74%</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>295</v>
       </c>
       <c r="F9" t="n">
-        <v>67</v>
-      </c>
-      <c r="G9" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="72" t="inlineStr">
-        <is>
-          <t>見かけ74%だが真の100%＝差26ptは"作れない天井"。例文の空所に文法語をタイルで作る。例文に表層形が一意に1回出る点のみ対象(0回/複数回は空所位置が曖昧で除外)＝構造的に低い。上げたい場合は例文を「表層形が1回だけ出る」形に整えるか、対象点の例文を追加する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>意味を選ぶ(漢字)</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>77</v>
-      </c>
-      <c r="D10" t="n">
-        <v>79</v>
-      </c>
-      <c r="E10" s="107" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>77</v>
-      </c>
-      <c r="G10" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H10" s="72" t="inlineStr">
-        <is>
-          <t>見かけ97%だが真の100%＝差3ptは"作れない天井"。字→意味を4択(認識テスト)。意味が立つ字(訓読みあり or 単独語=meaningClear)だけが対象。校のような字は意味面を作れず対象外。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>読み(漢字)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>79</v>
-      </c>
-      <c r="D11" t="n">
-        <v>79</v>
-      </c>
-      <c r="E11" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>79</v>
-      </c>
-      <c r="G11" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="72" t="inlineStr">
-        <is>
-          <t>字→読みを4択(認識テスト)。全字が対象。訓読みを優先し送り仮名を補って提示(強→つよ（い）)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>形の弁別(漢字)</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>62</v>
-      </c>
-      <c r="D12" t="n">
-        <v>79</v>
-      </c>
-      <c r="E12" s="110" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>62</v>
-      </c>
-      <c r="G12" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="72" t="inlineStr">
-        <is>
-          <t>見かけ78%だが真の100%＝差22ptは"作れない天井"。似た字4択→正しい字を選ぶ(形の弁別)。見た目が紛らわしい字が3つ揃う字(formMakeable)だけが対象。※書き取り(手書き産出)は練習ゆえ面に非計上。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>聞き取り(漢字)</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>79</v>
-      </c>
-      <c r="D13" t="n">
-        <v>79</v>
-      </c>
-      <c r="E13" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>79</v>
-      </c>
-      <c r="G13" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="72" t="inlineStr">
-        <is>
-          <t>読みを聞いて漢字を選ぶ。drillレップを持つ当該級の漢字が対象。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="104" t="inlineStr">
-        <is>
-          <t>■ N4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="109" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B16" s="109" t="inlineStr">
-        <is>
-          <t>ドリル</t>
-        </is>
-      </c>
-      <c r="C16" s="109" t="inlineStr">
-        <is>
-          <t>対象</t>
-        </is>
-      </c>
-      <c r="D16" s="109" t="inlineStr">
-        <is>
-          <t>全ID母数</t>
-        </is>
-      </c>
-      <c r="E16" s="109" t="inlineStr">
-        <is>
-          <t>全IDカバー率</t>
-        </is>
-      </c>
-      <c r="F16" s="109" t="inlineStr">
-        <is>
-          <t>真の母数</t>
-        </is>
-      </c>
-      <c r="G16" s="109" t="inlineStr">
-        <is>
-          <t>真のカバー率</t>
-        </is>
-      </c>
-      <c r="H16" s="109" t="inlineStr">
-        <is>
-          <t>点検メモ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>語彙</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>語彙パズル(産出)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>576</v>
-      </c>
-      <c r="D17" t="n">
-        <v>673</v>
-      </c>
-      <c r="E17" s="107" t="inlineStr">
-        <is>
-          <t>86%</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>576</v>
-      </c>
-      <c r="G17" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="72" t="inlineStr">
-        <is>
-          <t>見かけ86%だが真の100%＝差14ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>語彙</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>聞き取り(語彙)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>643</v>
-      </c>
-      <c r="D18" t="n">
-        <v>673</v>
-      </c>
-      <c r="E18" s="107" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>643</v>
-      </c>
-      <c r="G18" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="72" t="inlineStr">
-        <is>
-          <t>見かけ96%だが真の100%＝差4ptは"作れない天井"。読みを聞いて単語を選ぶ。非自立語(接辞/助詞)・波ダッシュ語のみ対象外。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>意味を選ぶ(受容)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>131</v>
-      </c>
-      <c r="D19" t="n">
-        <v>131</v>
-      </c>
-      <c r="E19" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>131</v>
-      </c>
-      <c r="G19" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="72" t="inlineStr">
-        <is>
-          <t>文法点の意味を4択。意味を持つ全点が対象。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>文法パズル(産出)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>113</v>
-      </c>
-      <c r="D20" t="n">
-        <v>131</v>
-      </c>
-      <c r="E20" s="107" t="inlineStr">
-        <is>
-          <t>86%</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>114</v>
-      </c>
-      <c r="G20" s="107" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="H20" s="72" t="inlineStr">
-        <is>
-          <t>見かけ86%だが真の99%＝差13ptは"作れない天井"。例文の空所に文法語をタイルで作る。例文に表層形が一意に1回出る点のみ対象(0回/複数回は空所位置が曖昧で除外)＝構造的に低い。上げたい場合は例文を「表層形が1回だけ出る」形に整えるか、対象点の例文を追加する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>意味を選ぶ(漢字)</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>141</v>
-      </c>
-      <c r="D21" t="n">
-        <v>166</v>
-      </c>
-      <c r="E21" s="107" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>141</v>
-      </c>
-      <c r="G21" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="72" t="inlineStr">
-        <is>
-          <t>見かけ85%だが真の100%＝差15ptは"作れない天井"。字→意味を4択(認識テスト)。意味が立つ字(訓読みあり or 単独語=meaningClear)だけが対象。校のような字は意味面を作れず対象外。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>読み(漢字)</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>166</v>
-      </c>
-      <c r="D22" t="n">
-        <v>166</v>
-      </c>
-      <c r="E22" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>166</v>
-      </c>
-      <c r="G22" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H22" s="72" t="inlineStr">
-        <is>
-          <t>字→読みを4択(認識テスト)。全字が対象。訓読みを優先し送り仮名を補って提示(強→つよ（い）)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>形の弁別(漢字)</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>159</v>
-      </c>
-      <c r="D23" t="n">
-        <v>166</v>
-      </c>
-      <c r="E23" s="107" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>159</v>
-      </c>
-      <c r="G23" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="72" t="inlineStr">
-        <is>
-          <t>見かけ96%だが真の100%＝差4ptは"作れない天井"。似た字4択→正しい字を選ぶ(形の弁別)。見た目が紛らわしい字が3つ揃う字(formMakeable)だけが対象。※書き取り(手書き産出)は練習ゆえ面に非計上。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>聞き取り(漢字)</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>166</v>
-      </c>
-      <c r="D24" t="n">
-        <v>166</v>
-      </c>
-      <c r="E24" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>166</v>
-      </c>
-      <c r="G24" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="72" t="inlineStr">
-        <is>
-          <t>読みを聞いて漢字を選ぶ。drillレップを持つ当該級の漢字が対象。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="104" t="inlineStr">
-        <is>
-          <t>■ N3</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="109" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B27" s="109" t="inlineStr">
-        <is>
-          <t>ドリル</t>
-        </is>
-      </c>
-      <c r="C27" s="109" t="inlineStr">
-        <is>
-          <t>対象</t>
-        </is>
-      </c>
-      <c r="D27" s="109" t="inlineStr">
-        <is>
-          <t>全ID母数</t>
-        </is>
-      </c>
-      <c r="E27" s="109" t="inlineStr">
-        <is>
-          <t>全IDカバー率</t>
-        </is>
-      </c>
-      <c r="F27" s="109" t="inlineStr">
-        <is>
-          <t>真の母数</t>
-        </is>
-      </c>
-      <c r="G27" s="109" t="inlineStr">
-        <is>
-          <t>真のカバー率</t>
-        </is>
-      </c>
-      <c r="H27" s="109" t="inlineStr">
-        <is>
-          <t>点検メモ</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>語彙</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>語彙パズル(産出)</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1963</v>
-      </c>
-      <c r="D28" t="n">
         <v>2145</v>
       </c>
-      <c r="E28" s="107" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>1963</v>
-      </c>
-      <c r="G28" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="72" t="inlineStr">
-        <is>
-          <t>見かけ92%だが真の100%＝差8ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>語彙</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>聞き取り(語彙)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>2143</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2145</v>
-      </c>
-      <c r="E29" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>2143</v>
-      </c>
-      <c r="G29" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H29" s="72" t="inlineStr">
-        <is>
-          <t>読みを聞いて単語を選ぶ。非自立語(接辞/助詞)・波ダッシュ語のみ対象外。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>意味を選ぶ(受容)</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>186</v>
-      </c>
-      <c r="D30" t="n">
-        <v>186</v>
-      </c>
-      <c r="E30" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>186</v>
-      </c>
-      <c r="G30" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="72" t="inlineStr">
-        <is>
-          <t>文法点の意味を4択。意味を持つ全点が対象。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>文法パズル(産出)</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>167</v>
-      </c>
-      <c r="D31" t="n">
-        <v>186</v>
-      </c>
-      <c r="E31" s="107" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>169</v>
-      </c>
-      <c r="G31" s="107" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="H31" s="72" t="inlineStr">
-        <is>
-          <t>見かけ90%だが真の99%＝差9ptは"作れない天井"。例文の空所に文法語をタイルで作る。例文に表層形が一意に1回出る点のみ対象(0回/複数回は空所位置が曖昧で除外)＝構造的に低い。上げたい場合は例文を「表層形が1回だけ出る」形に整えるか、対象点の例文を追加する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>意味を選ぶ(漢字)</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>311</v>
-      </c>
-      <c r="D32" t="n">
-        <v>367</v>
-      </c>
-      <c r="E32" s="107" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>311</v>
-      </c>
-      <c r="G32" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H32" s="72" t="inlineStr">
-        <is>
-          <t>見かけ85%だが真の100%＝差15ptは"作れない天井"。字→意味を4択(認識テスト)。意味が立つ字(訓読みあり or 単独語=meaningClear)だけが対象。校のような字は意味面を作れず対象外。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>読み(漢字)</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>367</v>
-      </c>
-      <c r="D33" t="n">
-        <v>367</v>
-      </c>
-      <c r="E33" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>367</v>
-      </c>
-      <c r="G33" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="72" t="inlineStr">
-        <is>
-          <t>字→読みを4択(認識テスト)。全字が対象。訓読みを優先し送り仮名を補って提示(強→つよ（い）)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>形の弁別(漢字)</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>336</v>
-      </c>
-      <c r="D34" t="n">
-        <v>367</v>
-      </c>
-      <c r="E34" s="107" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>336</v>
-      </c>
-      <c r="G34" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H34" s="72" t="inlineStr">
-        <is>
-          <t>見かけ92%だが真の100%＝差8ptは"作れない天井"。似た字4択→正しい字を選ぶ(形の弁別)。見た目が紛らわしい字が3つ揃う字(formMakeable)だけが対象。※書き取り(手書き産出)は練習ゆえ面に非計上。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>聞き取り(漢字)</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>367</v>
-      </c>
-      <c r="D35" t="n">
-        <v>367</v>
-      </c>
-      <c r="E35" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>367</v>
-      </c>
-      <c r="G35" s="107" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H35" s="72" t="inlineStr">
-        <is>
-          <t>読みを聞いて漢字を選ぶ。drillレップを持つ当該級の漢字が対象。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>凡例：緑=問題なし(≥80%) ／ 黄=気になる(60-79%) ／ 赤=危険(&lt;60%)。カバー率が2つあるのは"天井"のあるドリル＝真のカバー率で判断。</t>
+      <c r="G9" s="108" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1850</v>
+      </c>
+      <c r="I9" s="67" t="inlineStr">
+        <is>
+          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=295 / 下級流出=N5:3, N4:2</t>
         </is>
       </c>
     </row>
@@ -7077,7 +6186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K159"/>
+  <dimension ref="A1:J159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="46" customWidth="1" style="71" min="1" max="1"/>
@@ -7478,7 +6587,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19" ht="22.05" customHeight="1" s="71">
       <c r="A19" s="8" t="inlineStr">
         <is>
@@ -7497,7 +6605,7 @@
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
         <is>
-          <t>※全ID母数=級内の全語彙数。真の母数=その大問が本当に作れる語だけ＝【漢字読み/表記】漢字を含む語 【文脈規定/用法】どの語でも作れる=全ID 【言い換え類義】言い換え可能語(iikaePossible p=1)。真のカバー率=covered/真の母数(2026-08-24 全大問更新)。漢字読み/表記のN3は今回498語追加で74→99%(真)。言い換え類義は新規EXCEL問題(未マージ)を含む。 ※2026-08-24: 束縛形態素(助詞/接尾辞)で単独の語彙問題が作れず文法点として文法側でカバーされる9語(〜ずつ/〜だけ/〜時とき/〜など/〜しまう/〜ばかり/〜まま/〜よると/〜ついて=vocabMetricExcluded.json)を全語彙数から除外→N5 723→719・N4 673→668(N3据置)。二重計上/紛らわしさ回避。　※2026-08-28追加: 感動詞 あ・ああ の2語も母数除外→N5 719→718・N4 668→667(計11語)。</t>
+          <t>※全ID母数=級内の全語彙数。真の母数=その大問が本当に作れる語だけ＝【漢字読み/表記】漢字を含む語 【文脈規定/用法】どの語でも作れる=全ID 【言い換え類義】言い換え可能語(iikaePossible p=1)。真のカバー率=covered/真の母数(2026-08-24 全大問更新)。漢字読み/表記のN3は今回498語追加で74→99%(真)。言い換え類義は新規EXCEL問題(未マージ)を含む。 ※2026-08-24: 束縛形態素(助詞/接尾辞)で単独の語彙問題が作れず文法点として文法側でカバーされる9語(〜ずつ/〜だけ/〜時とき/〜など/〜しまう/〜ばかり/〜まま/〜よると/〜ついて=vocabMetricExcluded.json)を全語彙数から除外→N5 723→719・N4 673→668(N3据置)。二重計上/紛らわしさ回避。　※2026-08-28追加: 感動詞 あ・ああ の2語も母数除外→N5 719→718・N4 668→667(計11語)。 ※2026-08-28追加: 御～(n4-v-530)も文法n5-g-59そのものゆえ母数除外→N4 667→666(計14語・お～/と含む)。</t>
         </is>
       </c>
       <c r="G21" s="23" t="n"/>
@@ -7863,7 +6971,7 @@
     <row r="36" ht="28.8" customHeight="1" s="71">
       <c r="A36" s="34" t="inlineStr">
         <is>
-          <t>語彙単語(667)</t>
+          <t>語彙単語(666)</t>
         </is>
       </c>
       <c r="B36" s="25" t="inlineStr">
@@ -7914,13 +7022,13 @@
         </is>
       </c>
       <c r="C38" s="25" t="n">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E38" s="25" t="n">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F38" s="37" t="inlineStr">
         <is>
@@ -7930,7 +7038,7 @@
       <c r="G38" s="28" t="n"/>
       <c r="H38" s="72" t="n"/>
       <c r="I38" s="33" t="n">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J38" s="69" t="inlineStr">
         <is>
@@ -7952,7 +7060,7 @@
         <v>406</v>
       </c>
       <c r="E39" s="25" t="n">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
@@ -7988,7 +7096,7 @@
         <v>565</v>
       </c>
       <c r="E40" s="25" t="n">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F40" s="38" t="inlineStr">
         <is>
@@ -8394,19 +7502,6 @@
     <row r="55">
       <c r="G55" s="23" t="n"/>
     </row>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
     <row r="69">
       <c r="A69" s="21" t="inlineStr">
         <is>
@@ -8414,8 +7509,6 @@
         </is>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72" ht="22.05" customHeight="1" s="71">
       <c r="A72" s="8" t="inlineStr">
         <is>
@@ -8437,7 +7530,6 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
@@ -8667,7 +7759,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
@@ -8897,7 +7988,6 @@
         </is>
       </c>
     </row>
-    <row r="91"/>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
@@ -9127,7 +8217,6 @@
         </is>
       </c>
     </row>
-    <row r="99"/>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
@@ -9135,8 +8224,6 @@
         </is>
       </c>
     </row>
-    <row r="101"/>
-    <row r="102"/>
     <row r="103" ht="22.05" customHeight="1" s="71">
       <c r="A103" s="8" t="inlineStr">
         <is>
@@ -9151,7 +8238,6 @@
         </is>
       </c>
     </row>
-    <row r="105"/>
     <row r="106">
       <c r="A106" s="42" t="inlineStr">
         <is>
@@ -9354,10 +8440,10 @@
         <v>79</v>
       </c>
       <c r="C112" s="43" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D112" s="43" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E112" s="43" t="inlineStr">
         <is>
@@ -9382,10 +8468,10 @@
         </is>
       </c>
       <c r="B113" s="43" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C113" s="43" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D113" s="43" t="n">
         <v>44</v>
@@ -9413,13 +8499,13 @@
         </is>
       </c>
       <c r="B114" s="43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C114" s="43" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D114" s="43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" s="43" t="inlineStr">
         <is>
@@ -9428,7 +8514,7 @@
       </c>
       <c r="F114" s="43" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G114" s="43" t="inlineStr">
@@ -9540,7 +8626,7 @@
         <v>717</v>
       </c>
       <c r="C118" s="44" t="n">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D118" s="44" t="n">
         <v>2144</v>
@@ -9561,15 +8647,13 @@
         </is>
       </c>
     </row>
-    <row r="119"/>
     <row r="120">
       <c r="A120" s="72" t="inlineStr">
         <is>
-          <t>※面(最大10)：①漢字読み ②表記 ③文脈規定 ④言い換え ⑤用法（試験5大問）＋⑥語彙パズル(産出) ⑦聞き取り＋⑧いみ ⑨よみ ⑩かたち（受容3ドリル・文脈なし4択）。産出はカタカナ語(カタカナタイル)・2〜8モーラへ拡大(2026-08-28)＝産出カバー N5 671/N4 626/N3 2090。いみは全語100%。母数 N5 718/N4 667/N3 2145。集計=scratchpad/facet_emit.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="121"/>
+          <t>※面(最大10)：①漢字読み ②表記 ③文脈規定 ④言い換え ⑤用法（試験5大問）＋⑥語彙パズル(産出) ⑦聞き取り＋⑧いみ ⑨よみ ⑩かたち（受容3ドリル・文脈なし4択）。産出はカタカナ語(カタカナタイル)・2〜8モーラへ拡大(2026-08-28)＝産出カバー N5 671/N4 626/N3 2090。いみは全語100%。母数 N5 717/N4 666/N3 2144。集計=scratchpad/facet_emit.ts 2026-08-28: 3面語の面数底上げ(B案)＝いくら～ても/やすい/おき/ちゃん/おわる/君に用法、何～/君/はあに言い換えを追加→N4 3面7→1・N5 3面7→6・N3 3面1→0。 御～(n4-v-530)は文法n5-g-59(お/ご)そのものゆえ母数除外(お～と同扱い)→N4 667→666・N4 3面1→0。</t>
+        </is>
+      </c>
+    </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
@@ -9584,7 +8668,6 @@
         </is>
       </c>
     </row>
-    <row r="124"/>
     <row r="125">
       <c r="A125" s="42" t="inlineStr">
         <is>
@@ -9839,7 +8922,6 @@
         </is>
       </c>
     </row>
-    <row r="133"/>
     <row r="134">
       <c r="A134" s="72" t="inlineStr">
         <is>
@@ -9847,7 +8929,6 @@
         </is>
       </c>
     </row>
-    <row r="135"/>
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
@@ -9862,7 +8943,6 @@
         </is>
       </c>
     </row>
-    <row r="138"/>
     <row r="139">
       <c r="A139" s="42" t="inlineStr">
         <is>
@@ -10086,7 +9166,6 @@
         </is>
       </c>
     </row>
-    <row r="146"/>
     <row r="147">
       <c r="A147" s="72" t="inlineStr">
         <is>
@@ -10094,7 +9173,6 @@
         </is>
       </c>
     </row>
-    <row r="148"/>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
@@ -10109,7 +9187,6 @@
         </is>
       </c>
     </row>
-    <row r="151"/>
     <row r="152">
       <c r="A152" s="42" t="inlineStr">
         <is>
@@ -10242,7 +9319,6 @@
         </is>
       </c>
     </row>
-    <row r="158"/>
     <row r="159">
       <c r="A159" s="72" t="inlineStr">
         <is>
@@ -13213,157 +12289,1048 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="71" min="1" max="1"/>
-    <col width="12" customWidth="1" style="71" min="2" max="2"/>
-    <col width="12" customWidth="1" style="71" min="3" max="3"/>
-    <col width="12" customWidth="1" style="71" min="4" max="4"/>
-    <col width="12" customWidth="1" style="71" min="5" max="5"/>
-    <col width="12" customWidth="1" style="71" min="6" max="6"/>
-    <col width="12" customWidth="1" style="71" min="7" max="7"/>
-    <col width="12" customWidth="1" style="71" min="8" max="8"/>
-    <col width="66" customWidth="1" style="71" min="9" max="9"/>
+    <col width="8" customWidth="1" style="71" min="1" max="1"/>
+    <col width="20" customWidth="1" style="71" min="2" max="2"/>
+    <col width="11" customWidth="1" style="71" min="3" max="3"/>
+    <col width="11" customWidth="1" style="71" min="4" max="4"/>
+    <col width="11" customWidth="1" style="71" min="5" max="5"/>
+    <col width="11" customWidth="1" style="71" min="6" max="6"/>
+    <col width="11" customWidth="1" style="71" min="7" max="7"/>
+    <col width="60" customWidth="1" style="71" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="105" t="inlineStr">
-        <is>
-          <t>用法(語の使い方) × 語彙idカバー×バランス</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="67" t="inlineStr">
-        <is>
-          <t>最終目標＝可能な限り語彙をカバー(breadth%を100%へ)。番人=src/data/usageCoverage.test.ts が「①未紐づけ0(測定可能) ②大問内で1語1問まで(集中させず広く) ③カバー数は後退させない(ラチェット)」を担保。</t>
+      <c r="A1" s="104" t="inlineStr">
+        <is>
+          <t>学習ドリル×カバー率（学習タブ・各ドリルがID紐づけで対象にできる項目の広さ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>※全ID母数=レベル内の全項目(語彙数/文法点数[n5-g-92除外]/漢字数)。真の母数=そのドリルで「そもそも作れる」項目数(カタカナ語・分離型文法など"永久に不可能"を除く)＝真のカバー率が実力。試験タブの大問は別シート「単語×大問カバー率」。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="67" t="inlineStr">
-        <is>
-          <t>級跨ぎ重複(同語をN4とN3の両大問で出題=冗長)＝0語。冗長は禁止せず記録のみ(復習として妥当な場合あり)＝新規作問は未カバー語を優先すると breadth が伸びる。</t>
+      <c r="A4" s="104" t="inlineStr">
+        <is>
+          <t>■ N5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="109" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="109" t="inlineStr">
+        <is>
+          <t>ドリル</t>
+        </is>
+      </c>
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="D5" s="109" t="inlineStr">
+        <is>
+          <t>全ID母数</t>
+        </is>
+      </c>
+      <c r="E5" s="109" t="inlineStr">
+        <is>
+          <t>全IDカバー率</t>
+        </is>
+      </c>
+      <c r="F5" s="109" t="inlineStr">
+        <is>
+          <t>真の母数</t>
+        </is>
+      </c>
+      <c r="G5" s="109" t="inlineStr">
+        <is>
+          <t>真のカバー率</t>
+        </is>
+      </c>
+      <c r="H5" s="109" t="inlineStr">
+        <is>
+          <t>点検メモ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="104" t="inlineStr">
-        <is>
-          <t>■ 級別サマリ</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>語彙パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>606</v>
+      </c>
+      <c r="D6" t="n">
+        <v>723</v>
+      </c>
+      <c r="E6" s="107" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>606</v>
+      </c>
+      <c r="G6" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="72" t="inlineStr">
+        <is>
+          <t>見かけ84%だが真の100%＝差16ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="106" t="inlineStr">
-        <is>
-          <t>級</t>
-        </is>
-      </c>
-      <c r="B7" s="106" t="inlineStr">
-        <is>
-          <t>問題数</t>
-        </is>
-      </c>
-      <c r="C7" s="106" t="inlineStr">
-        <is>
-          <t>リンク</t>
-        </is>
-      </c>
-      <c r="D7" s="106" t="inlineStr">
-        <is>
-          <t>未紐づけ</t>
-        </is>
-      </c>
-      <c r="E7" s="106" t="inlineStr">
-        <is>
-          <t>カバー語</t>
-        </is>
-      </c>
-      <c r="F7" s="106" t="inlineStr">
-        <is>
-          <t>母数</t>
-        </is>
-      </c>
-      <c r="G7" s="106" t="inlineStr">
-        <is>
-          <t>breadth%</t>
-        </is>
-      </c>
-      <c r="H7" s="106" t="inlineStr">
-        <is>
-          <t>未カバー(backlog)</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>聞き取り(語彙)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>681</v>
+      </c>
+      <c r="D7" t="n">
+        <v>723</v>
+      </c>
+      <c r="E7" s="107" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>681</v>
+      </c>
+      <c r="G7" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="72" t="inlineStr">
+        <is>
+          <t>見かけ94%だが真の100%＝差6ptは"作れない天井"。読みを聞いて単語を選ぶ。非自立語(接辞/助詞)・波ダッシュ語のみ対象外。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>565</v>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>意味を選ぶ(受容)</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>565</v>
+        <v>91</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>567</v>
+        <v>91</v>
+      </c>
+      <c r="E8" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>673</v>
+        <v>91</v>
       </c>
       <c r="G8" s="107" t="inlineStr">
         <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>106</v>
-      </c>
-      <c r="I8" s="67" t="inlineStr">
-        <is>
-          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=565</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="72" t="inlineStr">
+        <is>
+          <t>文法点の意味を4択。意味を持つ全点が対象。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>299</v>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>文法パズル(産出)</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>67</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>294</v>
+        <v>91</v>
+      </c>
+      <c r="E9" s="110" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
       </c>
       <c r="F9" t="n">
+        <v>67</v>
+      </c>
+      <c r="G9" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="72" t="inlineStr">
+        <is>
+          <t>見かけ74%だが真の100%＝差26ptは"作れない天井"。例文の空所に文法語をタイルで作る。例文に表層形が一意に1回出る点のみ対象(0回/複数回は空所位置が曖昧で除外)＝構造的に低い。上げたい場合は例文を「表層形が1回だけ出る」形に整えるか、対象点の例文を追加する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>意味を選ぶ(漢字)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>77</v>
+      </c>
+      <c r="D10" t="n">
+        <v>79</v>
+      </c>
+      <c r="E10" s="107" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>77</v>
+      </c>
+      <c r="G10" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="72" t="inlineStr">
+        <is>
+          <t>見かけ97%だが真の100%＝差3ptは"作れない天井"。字→意味を4択(認識テスト)。意味が立つ字(訓読みあり or 単独語=meaningClear)だけが対象。校のような字は意味面を作れず対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>読み(漢字)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>79</v>
+      </c>
+      <c r="D11" t="n">
+        <v>79</v>
+      </c>
+      <c r="E11" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>79</v>
+      </c>
+      <c r="G11" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="72" t="inlineStr">
+        <is>
+          <t>字→読みを4択(認識テスト)。全字が対象。訓読みを優先し送り仮名を補って提示(強→つよ（い）)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>形の弁別(漢字)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>62</v>
+      </c>
+      <c r="D12" t="n">
+        <v>79</v>
+      </c>
+      <c r="E12" s="110" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>62</v>
+      </c>
+      <c r="G12" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="72" t="inlineStr">
+        <is>
+          <t>見かけ78%だが真の100%＝差22ptは"作れない天井"。似た字4択→正しい字を選ぶ(形の弁別)。見た目が紛らわしい字が3つ揃う字(formMakeable)だけが対象。※書き取り(手書き産出)は練習ゆえ面に非計上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>聞き取り(漢字)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>79</v>
+      </c>
+      <c r="D13" t="n">
+        <v>79</v>
+      </c>
+      <c r="E13" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>79</v>
+      </c>
+      <c r="G13" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="72" t="inlineStr">
+        <is>
+          <t>読みを聞いて漢字を選ぶ。drillレップを持つ当該級の漢字が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="104" t="inlineStr">
+        <is>
+          <t>■ N4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="109" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B16" s="109" t="inlineStr">
+        <is>
+          <t>ドリル</t>
+        </is>
+      </c>
+      <c r="C16" s="109" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="D16" s="109" t="inlineStr">
+        <is>
+          <t>全ID母数</t>
+        </is>
+      </c>
+      <c r="E16" s="109" t="inlineStr">
+        <is>
+          <t>全IDカバー率</t>
+        </is>
+      </c>
+      <c r="F16" s="109" t="inlineStr">
+        <is>
+          <t>真の母数</t>
+        </is>
+      </c>
+      <c r="G16" s="109" t="inlineStr">
+        <is>
+          <t>真のカバー率</t>
+        </is>
+      </c>
+      <c r="H16" s="109" t="inlineStr">
+        <is>
+          <t>点検メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>語彙パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>576</v>
+      </c>
+      <c r="D17" t="n">
+        <v>673</v>
+      </c>
+      <c r="E17" s="107" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>576</v>
+      </c>
+      <c r="G17" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="72" t="inlineStr">
+        <is>
+          <t>見かけ86%だが真の100%＝差14ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聞き取り(語彙)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>643</v>
+      </c>
+      <c r="D18" t="n">
+        <v>673</v>
+      </c>
+      <c r="E18" s="107" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>643</v>
+      </c>
+      <c r="G18" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="72" t="inlineStr">
+        <is>
+          <t>見かけ96%だが真の100%＝差4ptは"作れない天井"。読みを聞いて単語を選ぶ。非自立語(接辞/助詞)・波ダッシュ語のみ対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>意味を選ぶ(受容)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>131</v>
+      </c>
+      <c r="D19" t="n">
+        <v>131</v>
+      </c>
+      <c r="E19" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>131</v>
+      </c>
+      <c r="G19" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="72" t="inlineStr">
+        <is>
+          <t>文法点の意味を4択。意味を持つ全点が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>文法パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>113</v>
+      </c>
+      <c r="D20" t="n">
+        <v>131</v>
+      </c>
+      <c r="E20" s="107" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>114</v>
+      </c>
+      <c r="G20" s="107" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="H20" s="72" t="inlineStr">
+        <is>
+          <t>見かけ86%だが真の99%＝差13ptは"作れない天井"。例文の空所に文法語をタイルで作る。例文に表層形が一意に1回出る点のみ対象(0回/複数回は空所位置が曖昧で除外)＝構造的に低い。上げたい場合は例文を「表層形が1回だけ出る」形に整えるか、対象点の例文を追加する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>意味を選ぶ(漢字)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>141</v>
+      </c>
+      <c r="D21" t="n">
+        <v>166</v>
+      </c>
+      <c r="E21" s="107" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>141</v>
+      </c>
+      <c r="G21" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="72" t="inlineStr">
+        <is>
+          <t>見かけ85%だが真の100%＝差15ptは"作れない天井"。字→意味を4択(認識テスト)。意味が立つ字(訓読みあり or 単独語=meaningClear)だけが対象。校のような字は意味面を作れず対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>読み(漢字)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>166</v>
+      </c>
+      <c r="D22" t="n">
+        <v>166</v>
+      </c>
+      <c r="E22" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>166</v>
+      </c>
+      <c r="G22" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H22" s="72" t="inlineStr">
+        <is>
+          <t>字→読みを4択(認識テスト)。全字が対象。訓読みを優先し送り仮名を補って提示(強→つよ（い）)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>形の弁別(漢字)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>159</v>
+      </c>
+      <c r="D23" t="n">
+        <v>166</v>
+      </c>
+      <c r="E23" s="107" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>159</v>
+      </c>
+      <c r="G23" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="72" t="inlineStr">
+        <is>
+          <t>見かけ96%だが真の100%＝差4ptは"作れない天井"。似た字4択→正しい字を選ぶ(形の弁別)。見た目が紛らわしい字が3つ揃う字(formMakeable)だけが対象。※書き取り(手書き産出)は練習ゆえ面に非計上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>聞き取り(漢字)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>166</v>
+      </c>
+      <c r="D24" t="n">
+        <v>166</v>
+      </c>
+      <c r="E24" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>166</v>
+      </c>
+      <c r="G24" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="72" t="inlineStr">
+        <is>
+          <t>読みを聞いて漢字を選ぶ。drillレップを持つ当該級の漢字が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="104" t="inlineStr">
+        <is>
+          <t>■ N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="109" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B27" s="109" t="inlineStr">
+        <is>
+          <t>ドリル</t>
+        </is>
+      </c>
+      <c r="C27" s="109" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="D27" s="109" t="inlineStr">
+        <is>
+          <t>全ID母数</t>
+        </is>
+      </c>
+      <c r="E27" s="109" t="inlineStr">
+        <is>
+          <t>全IDカバー率</t>
+        </is>
+      </c>
+      <c r="F27" s="109" t="inlineStr">
+        <is>
+          <t>真の母数</t>
+        </is>
+      </c>
+      <c r="G27" s="109" t="inlineStr">
+        <is>
+          <t>真のカバー率</t>
+        </is>
+      </c>
+      <c r="H27" s="109" t="inlineStr">
+        <is>
+          <t>点検メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>語彙パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1963</v>
+      </c>
+      <c r="D28" t="n">
         <v>2145</v>
       </c>
-      <c r="G9" s="108" t="inlineStr">
-        <is>
-          <t>14%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1851</v>
-      </c>
-      <c r="I9" s="67" t="inlineStr">
-        <is>
-          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=294 / 下級流出=N5:3, N4:2</t>
+      <c r="E28" s="107" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1963</v>
+      </c>
+      <c r="G28" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="72" t="inlineStr">
+        <is>
+          <t>見かけ92%だが真の100%＝差8ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>語彙</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>聞き取り(語彙)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2143</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2145</v>
+      </c>
+      <c r="E29" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2143</v>
+      </c>
+      <c r="G29" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H29" s="72" t="inlineStr">
+        <is>
+          <t>読みを聞いて単語を選ぶ。非自立語(接辞/助詞)・波ダッシュ語のみ対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>意味を選ぶ(受容)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>186</v>
+      </c>
+      <c r="D30" t="n">
+        <v>186</v>
+      </c>
+      <c r="E30" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>186</v>
+      </c>
+      <c r="G30" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="72" t="inlineStr">
+        <is>
+          <t>文法点の意味を4択。意味を持つ全点が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>文法パズル(産出)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>167</v>
+      </c>
+      <c r="D31" t="n">
+        <v>186</v>
+      </c>
+      <c r="E31" s="107" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>169</v>
+      </c>
+      <c r="G31" s="107" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="H31" s="72" t="inlineStr">
+        <is>
+          <t>見かけ90%だが真の99%＝差9ptは"作れない天井"。例文の空所に文法語をタイルで作る。例文に表層形が一意に1回出る点のみ対象(0回/複数回は空所位置が曖昧で除外)＝構造的に低い。上げたい場合は例文を「表層形が1回だけ出る」形に整えるか、対象点の例文を追加する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>意味を選ぶ(漢字)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>311</v>
+      </c>
+      <c r="D32" t="n">
+        <v>367</v>
+      </c>
+      <c r="E32" s="107" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>311</v>
+      </c>
+      <c r="G32" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H32" s="72" t="inlineStr">
+        <is>
+          <t>見かけ85%だが真の100%＝差15ptは"作れない天井"。字→意味を4択(認識テスト)。意味が立つ字(訓読みあり or 単独語=meaningClear)だけが対象。校のような字は意味面を作れず対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>読み(漢字)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>367</v>
+      </c>
+      <c r="D33" t="n">
+        <v>367</v>
+      </c>
+      <c r="E33" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>367</v>
+      </c>
+      <c r="G33" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="72" t="inlineStr">
+        <is>
+          <t>字→読みを4択(認識テスト)。全字が対象。訓読みを優先し送り仮名を補って提示(強→つよ（い）)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>形の弁別(漢字)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>336</v>
+      </c>
+      <c r="D34" t="n">
+        <v>367</v>
+      </c>
+      <c r="E34" s="107" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>336</v>
+      </c>
+      <c r="G34" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H34" s="72" t="inlineStr">
+        <is>
+          <t>見かけ92%だが真の100%＝差8ptは"作れない天井"。似た字4択→正しい字を選ぶ(形の弁別)。見た目が紛らわしい字が3つ揃う字(formMakeable)だけが対象。※書き取り(手書き産出)は練習ゆえ面に非計上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>漢字</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>聞き取り(漢字)</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>367</v>
+      </c>
+      <c r="D35" t="n">
+        <v>367</v>
+      </c>
+      <c r="E35" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>367</v>
+      </c>
+      <c r="G35" s="107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H35" s="72" t="inlineStr">
+        <is>
+          <t>読みを聞いて漢字を選ぶ。drillレップを持つ当該級の漢字が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>凡例：緑=問題なし(≥80%) ／ 黄=気になる(60-79%) ／ 赤=危険(&lt;60%)。カバー率が2つあるのは"天井"のあるドリル＝真のカバー率で判断。</t>
         </is>
       </c>
     </row>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -6676,7 +6676,7 @@
     <row r="25" ht="28.8" customHeight="1" s="71">
       <c r="A25" s="34" t="inlineStr">
         <is>
-          <t>語彙単語(717)</t>
+          <t>語彙単語(716)</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
@@ -6733,7 +6733,7 @@
         <v>672</v>
       </c>
       <c r="E27" s="25" t="n">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F27" s="37" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
       <c r="G27" s="28" t="n"/>
       <c r="H27" s="72" t="n"/>
       <c r="I27" s="33" t="n">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="J27" s="69" t="inlineStr">
         <is>
@@ -6759,17 +6759,17 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E28" s="25" t="n">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F28" s="38" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="G28" s="28" t="n"/>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="I28" s="33" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="J28" s="69" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>3</v>
       </c>
       <c r="E29" s="85" t="n">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F29" s="86" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         </is>
       </c>
       <c r="B113" s="43" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C113" s="43" t="n">
         <v>16</v>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="B114" s="43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C114" s="43" t="n">
         <v>0</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="B118" s="44" t="n">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C118" s="44" t="n">
         <v>666</v>
@@ -8650,7 +8650,7 @@
     <row r="120">
       <c r="A120" s="72" t="inlineStr">
         <is>
-          <t>※面(最大10)：①漢字読み ②表記 ③文脈規定 ④言い換え ⑤用法（試験5大問）＋⑥語彙パズル(産出) ⑦聞き取り＋⑧いみ ⑨よみ ⑩かたち（受容3ドリル・文脈なし4択）。産出はカタカナ語(カタカナタイル)・2〜8モーラへ拡大(2026-08-28)＝産出カバー N5 671/N4 626/N3 2090。いみは全語100%。母数 N5 717/N4 666/N3 2144。集計=scratchpad/facet_emit.ts 2026-08-28: 3面語の面数底上げ(B案)＝いくら～ても/やすい/おき/ちゃん/おわる/君に用法、何～/君/はあに言い換えを追加→N4 3面7→1・N5 3面7→6・N3 3面1→0。 御～(n4-v-530)は文法n5-g-59(お/ご)そのものゆえ母数除外(お～と同扱い)→N4 667→666・N4 3面1→0。</t>
+          <t>※面(最大10)：①漢字読み ②表記 ③文脈規定 ④言い換え ⑤用法（試験5大問）＋⑥語彙パズル(産出) ⑦聞き取り＋⑧いみ ⑨よみ ⑩かたち（受容3ドリル・文脈なし4択）。産出はカタカナ語(カタカナタイル)・2〜8モーラへ拡大(2026-08-28)＝産出カバー N5 671/N4 626/N3 2090。いみは全語100%。母数 N5 716/N4 666/N3 2144。集計=scratchpad/facet_emit.ts 2026-08-28: 3面語の面数底上げ(B案)＝いくら～ても/やすい/おき/ちゃん/おわる/君に用法、何～/君/はあに言い換えを追加→N4 3面7→1・N5 3面7→6・N3 3面1→0。 御～(n4-v-530)は文法n5-g-59(お/ご)そのものゆえ母数除外(お～と同扱い)→N4 667→666・N4 3面1→0。 2026-08-29: さん(n5-v-287)を語彙削除→N5 717→716。くらいに文脈規定+言い換え(級修正)で3→4面→N5の3面ゼロ・全語彙≥4面。</t>
         </is>
       </c>
     </row>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -3378,31 +3378,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="C9" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>295</v>
+        <v>595</v>
       </c>
       <c r="F9" t="n">
         <v>2145</v>
       </c>
       <c r="G9" s="108" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1850</v>
+        <v>1550</v>
       </c>
       <c r="I9" s="67" t="inlineStr">
         <is>
-          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=295 / 下級流出=N5:3, N4:2</t>
+          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=595 / 下級流出=N5:3, N4:2</t>
         </is>
       </c>
     </row>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -8,17 +8,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大問別まとめ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模試ストック換算" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="①大問別まとめ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② カバー率" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 品質・攻略耐性" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ 習得の仕組み(説明)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学習ドリル×カバー率" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ 用法カバー×バランス" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② カバー率" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 品質・攻略耐性" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥ 翻訳状況" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大問別まとめ'!$A$1:$M$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'①大問別まとめ'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大問別まとめ'!$A$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="33">
+  <fonts count="37">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -225,8 +220,27 @@
       <i val="1"/>
       <color rgb="007A756C"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="42">
+  <fills count="47">
     <fill>
       <patternFill/>
     </fill>
@@ -435,8 +449,33 @@
         <fgColor rgb="00F3EAF3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6DCE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -547,11 +586,25 @@
         <color rgb="00C9D3DE"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -812,6 +865,28 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="42" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1177,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="82" min="1" max="1"/>
@@ -1188,11 +1263,10 @@
     <col width="10" customWidth="1" style="82" min="6" max="6"/>
     <col width="46" customWidth="1" style="82" min="7" max="7"/>
     <col width="9" customWidth="1" style="82" min="8" max="8"/>
-    <col width="8" customWidth="1" style="82" min="9" max="9"/>
-    <col width="11" customWidth="1" style="82" min="10" max="10"/>
-    <col width="15" customWidth="1" style="82" min="11" max="11"/>
-    <col width="26" customWidth="1" style="82" min="12" max="12"/>
-    <col width="12" customWidth="1" style="82" min="13" max="13"/>
+    <col width="11" customWidth="1" style="82" min="9" max="9"/>
+    <col width="15" customWidth="1" style="82" min="10" max="10"/>
+    <col width="26" customWidth="1" style="82" min="11" max="11"/>
+    <col width="12" customWidth="1" style="82" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1238,25 +1312,20 @@
       </c>
       <c r="I1" s="95" t="inlineStr">
         <is>
-          <t>未検証</t>
+          <t>本番出題数</t>
         </is>
       </c>
       <c r="J1" s="95" t="inlineStr">
         <is>
-          <t>本番出題数</t>
+          <t>模試換算(何回分)</t>
         </is>
       </c>
       <c r="K1" s="95" t="inlineStr">
         <is>
-          <t>模試換算(何回分)</t>
+          <t>誤答数の内訳</t>
         </is>
       </c>
       <c r="L1" s="95" t="inlineStr">
-        <is>
-          <t>誤答数の内訳</t>
-        </is>
-      </c>
-      <c r="M1" s="95" t="inlineStr">
         <is>
           <t>シャッフル</t>
         </is>
@@ -1299,23 +1368,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I2" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J2" s="98" t="n">
+      <c r="I2" s="98" t="n">
         <v>12</v>
       </c>
-      <c r="K2" s="100" t="n">
+      <c r="J2" s="100" t="n">
         <v>34</v>
       </c>
-      <c r="L2" s="97" t="inlineStr">
+      <c r="K2" s="97" t="inlineStr">
         <is>
           <t>3:785</t>
         </is>
       </c>
-      <c r="M2" s="98" t="inlineStr">
+      <c r="L2" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -1354,23 +1418,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I3" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" s="98" t="n">
+      <c r="I3" s="98" t="n">
         <v>9</v>
       </c>
-      <c r="K3" s="100" t="n">
+      <c r="J3" s="100" t="n">
         <v>36</v>
       </c>
-      <c r="L3" s="97" t="inlineStr">
+      <c r="K3" s="97" t="inlineStr">
         <is>
           <t>3:537</t>
         </is>
       </c>
-      <c r="M3" s="98" t="inlineStr">
+      <c r="L3" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -1409,23 +1468,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I4" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="98" t="n">
+      <c r="I4" s="98" t="n">
         <v>8</v>
       </c>
-      <c r="K4" s="100" t="n">
+      <c r="J4" s="100" t="n">
         <v>243</v>
       </c>
-      <c r="L4" s="97" t="inlineStr">
+      <c r="K4" s="97" t="inlineStr">
         <is>
           <t>3:1882</t>
         </is>
       </c>
-      <c r="M4" s="98" t="inlineStr">
+      <c r="L4" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -1448,41 +1502,38 @@
         </is>
       </c>
       <c r="D5" s="98" t="n">
-        <v>212</v>
+        <v>474</v>
       </c>
       <c r="E5" s="98" t="inlineStr">
         <is>
           <t>×1</t>
         </is>
       </c>
-      <c r="F5" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="97" t="inlineStr"/>
+      <c r="F5" s="98" t="n">
+        <v>80</v>
+      </c>
+      <c r="G5" s="97" t="inlineStr">
+        <is>
+          <t>漢字読みN5の104×2の例題を流用</t>
+        </is>
+      </c>
       <c r="H5" s="98" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="98" t="n">
+      <c r="I5" s="98" t="n">
         <v>8</v>
       </c>
-      <c r="K5" s="100" t="n">
-        <v>26</v>
-      </c>
-      <c r="L5" s="97" t="inlineStr">
-        <is>
-          <t>3:587</t>
-        </is>
-      </c>
-      <c r="M5" s="98" t="inlineStr">
+      <c r="J5" s="100" t="n">
+        <v>59</v>
+      </c>
+      <c r="K5" s="97" t="inlineStr">
+        <is>
+          <t>3:849</t>
+        </is>
+      </c>
+      <c r="L5" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -1512,10 +1563,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F6" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F6" s="98" t="n">
+        <v>60</v>
       </c>
       <c r="G6" s="97" t="inlineStr"/>
       <c r="H6" s="98" t="inlineStr">
@@ -1523,23 +1572,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="98" t="n">
+      <c r="I6" s="98" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="100" t="n">
+      <c r="J6" s="100" t="n">
         <v>60</v>
       </c>
-      <c r="L6" s="97" t="inlineStr">
+      <c r="K6" s="97" t="inlineStr">
         <is>
           <t>3:571</t>
         </is>
       </c>
-      <c r="M6" s="98" t="inlineStr">
+      <c r="L6" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -1569,10 +1613,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F7" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F7" s="98" t="n">
+        <v>60</v>
       </c>
       <c r="G7" s="97" t="inlineStr"/>
       <c r="H7" s="98" t="inlineStr">
@@ -1580,23 +1622,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I7" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="98" t="n">
+      <c r="I7" s="98" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="100" t="n">
+      <c r="J7" s="100" t="n">
         <v>332</v>
       </c>
-      <c r="L7" s="97" t="inlineStr">
+      <c r="K7" s="97" t="inlineStr">
         <is>
           <t>3:1930</t>
         </is>
       </c>
-      <c r="M7" s="98" t="inlineStr">
+      <c r="L7" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -1626,10 +1663,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F8" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F8" s="98" t="n">
+        <v>100</v>
       </c>
       <c r="G8" s="97" t="inlineStr"/>
       <c r="H8" s="98" t="inlineStr">
@@ -1638,20 +1673,17 @@
         </is>
       </c>
       <c r="I8" s="98" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="98" t="n">
         <v>10</v>
       </c>
-      <c r="K8" s="100" t="n">
+      <c r="J8" s="100" t="n">
         <v>68</v>
       </c>
-      <c r="L8" s="97" t="inlineStr">
+      <c r="K8" s="97" t="inlineStr">
         <is>
           <t>3:197 / 4:222 / 5:268</t>
         </is>
       </c>
-      <c r="M8" s="98" t="inlineStr">
+      <c r="L8" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -1681,10 +1713,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F9" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F9" s="98" t="n">
+        <v>100</v>
       </c>
       <c r="G9" s="97" t="inlineStr"/>
       <c r="H9" s="98" t="inlineStr">
@@ -1693,20 +1723,17 @@
         </is>
       </c>
       <c r="I9" s="98" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="98" t="n">
         <v>10</v>
       </c>
-      <c r="K9" s="100" t="n">
+      <c r="J9" s="100" t="n">
         <v>65</v>
       </c>
-      <c r="L9" s="97" t="inlineStr">
+      <c r="K9" s="97" t="inlineStr">
         <is>
           <t>3:243 / 4:231 / 5:181</t>
         </is>
       </c>
-      <c r="M9" s="98" t="inlineStr">
+      <c r="L9" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -1736,10 +1763,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F10" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F10" s="98" t="n">
+        <v>110</v>
       </c>
       <c r="G10" s="97" t="inlineStr"/>
       <c r="H10" s="98" t="inlineStr">
@@ -1747,21 +1772,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I10" s="101" t="n">
-        <v>1318</v>
-      </c>
-      <c r="J10" s="98" t="n">
+      <c r="I10" s="98" t="n">
         <v>11</v>
       </c>
-      <c r="K10" s="100" t="n">
+      <c r="J10" s="100" t="n">
         <v>191</v>
       </c>
-      <c r="L10" s="97" t="inlineStr">
+      <c r="K10" s="97" t="inlineStr">
         <is>
           <t>3:1397 / 4:450 / 5:258</t>
         </is>
       </c>
-      <c r="M10" s="98" t="inlineStr">
+      <c r="L10" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -1791,10 +1813,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F11" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F11" s="98" t="n">
+        <v>50</v>
       </c>
       <c r="G11" s="97" t="inlineStr"/>
       <c r="H11" s="98" t="inlineStr">
@@ -1803,20 +1823,17 @@
         </is>
       </c>
       <c r="I11" s="98" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="98" t="n">
         <v>5</v>
       </c>
-      <c r="K11" s="100" t="n">
+      <c r="J11" s="100" t="n">
         <v>47</v>
       </c>
-      <c r="L11" s="97" t="inlineStr">
+      <c r="K11" s="97" t="inlineStr">
         <is>
           <t>3:205 / 4:13 / 5:18</t>
         </is>
       </c>
-      <c r="M11" s="98" t="inlineStr">
+      <c r="L11" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -1846,10 +1863,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F12" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F12" s="98" t="n">
+        <v>50</v>
       </c>
       <c r="G12" s="97" t="inlineStr"/>
       <c r="H12" s="98" t="inlineStr">
@@ -1858,20 +1873,17 @@
         </is>
       </c>
       <c r="I12" s="98" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="98" t="n">
         <v>5</v>
       </c>
-      <c r="K12" s="100" t="n">
+      <c r="J12" s="100" t="n">
         <v>81</v>
       </c>
-      <c r="L12" s="97" t="inlineStr">
+      <c r="K12" s="97" t="inlineStr">
         <is>
           <t>3:183 / 4:8 / 5:40 / 6:176</t>
         </is>
       </c>
-      <c r="M12" s="98" t="inlineStr">
+      <c r="L12" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -1901,10 +1913,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F13" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F13" s="98" t="n">
+        <v>50</v>
       </c>
       <c r="G13" s="97" t="inlineStr"/>
       <c r="H13" s="98" t="inlineStr">
@@ -1913,20 +1923,17 @@
         </is>
       </c>
       <c r="I13" s="98" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="98" t="n">
         <v>5</v>
       </c>
-      <c r="K13" s="100" t="n">
+      <c r="J13" s="100" t="n">
         <v>322</v>
       </c>
-      <c r="L13" s="97" t="inlineStr">
+      <c r="K13" s="97" t="inlineStr">
         <is>
           <t>3:601 / 4:14 / 5:100 / 6:897</t>
         </is>
       </c>
-      <c r="M13" s="98" t="inlineStr">
+      <c r="L13" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -1956,10 +1963,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F14" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F14" s="98" t="n">
+        <v>50</v>
       </c>
       <c r="G14" s="97" t="inlineStr"/>
       <c r="H14" s="98" t="inlineStr">
@@ -1968,20 +1973,17 @@
         </is>
       </c>
       <c r="I14" s="98" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="98" t="n">
         <v>5</v>
       </c>
-      <c r="K14" s="100" t="n">
+      <c r="J14" s="100" t="n">
         <v>114</v>
       </c>
-      <c r="L14" s="97" t="inlineStr">
+      <c r="K14" s="97" t="inlineStr">
         <is>
           <t>3:571</t>
         </is>
       </c>
-      <c r="M14" s="98" t="inlineStr">
+      <c r="L14" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2011,10 +2013,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F15" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F15" s="98" t="n">
+        <v>50</v>
       </c>
       <c r="G15" s="97" t="inlineStr"/>
       <c r="H15" s="98" t="inlineStr">
@@ -2023,20 +2023,17 @@
         </is>
       </c>
       <c r="I15" s="98" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="98" t="n">
         <v>5</v>
       </c>
-      <c r="K15" s="100" t="n">
+      <c r="J15" s="100" t="n">
         <v>120</v>
       </c>
-      <c r="L15" s="97" t="inlineStr">
+      <c r="K15" s="97" t="inlineStr">
         <is>
           <t>3:531 / 4:28 / 5:27 / 6:14</t>
         </is>
       </c>
-      <c r="M15" s="98" t="inlineStr">
+      <c r="L15" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2077,23 +2074,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I16" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" s="98" t="n">
+      <c r="I16" s="98" t="n">
         <v>16</v>
       </c>
-      <c r="K16" s="103" t="n">
+      <c r="J16" s="103" t="n">
         <v>13</v>
       </c>
-      <c r="L16" s="97" t="inlineStr">
+      <c r="K16" s="97" t="inlineStr">
         <is>
           <t>3:210 / 4:1</t>
         </is>
       </c>
-      <c r="M16" s="98" t="inlineStr">
+      <c r="L16" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2134,23 +2126,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I17" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="98" t="n">
+      <c r="I17" s="98" t="n">
         <v>15</v>
       </c>
-      <c r="K17" s="100" t="n">
+      <c r="J17" s="100" t="n">
         <v>24</v>
       </c>
-      <c r="L17" s="97" t="inlineStr">
+      <c r="K17" s="97" t="inlineStr">
         <is>
           <t>3:361</t>
         </is>
       </c>
-      <c r="M17" s="98" t="inlineStr">
+      <c r="L17" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2191,23 +2178,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I18" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J18" s="98" t="n">
+      <c r="I18" s="98" t="n">
         <v>13</v>
       </c>
-      <c r="K18" s="100" t="n">
+      <c r="J18" s="100" t="n">
         <v>34</v>
       </c>
-      <c r="L18" s="97" t="inlineStr">
+      <c r="K18" s="97" t="inlineStr">
         <is>
           <t>3:446 / 4:2</t>
         </is>
       </c>
-      <c r="M18" s="98" t="inlineStr">
+      <c r="L18" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2248,23 +2230,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I19" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" s="98" t="n">
+      <c r="I19" s="98" t="n">
         <v>5</v>
       </c>
-      <c r="K19" s="100" t="n">
+      <c r="J19" s="100" t="n">
         <v>29</v>
       </c>
-      <c r="L19" s="97" t="inlineStr">
+      <c r="K19" s="97" t="inlineStr">
         <is>
           <t>3:146</t>
         </is>
       </c>
-      <c r="M19" s="98" t="inlineStr">
+      <c r="L19" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2305,23 +2282,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I20" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J20" s="98" t="n">
+      <c r="I20" s="98" t="n">
         <v>5</v>
       </c>
-      <c r="K20" s="100" t="n">
+      <c r="J20" s="100" t="n">
         <v>43</v>
       </c>
-      <c r="L20" s="97" t="inlineStr">
+      <c r="K20" s="97" t="inlineStr">
         <is>
           <t>3:216</t>
         </is>
       </c>
-      <c r="M20" s="98" t="inlineStr">
+      <c r="L20" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2362,23 +2334,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I21" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J21" s="98" t="n">
+      <c r="I21" s="98" t="n">
         <v>5</v>
       </c>
-      <c r="K21" s="100" t="n">
+      <c r="J21" s="100" t="n">
         <v>62</v>
       </c>
-      <c r="L21" s="97" t="inlineStr">
+      <c r="K21" s="97" t="inlineStr">
         <is>
           <t>3:311</t>
         </is>
       </c>
-      <c r="M21" s="98" t="inlineStr">
+      <c r="L21" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2417,23 +2384,18 @@
       <c r="H22" s="98" t="n">
         <v>80</v>
       </c>
-      <c r="I22" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J22" s="98" t="n">
+      <c r="I22" s="98" t="n">
         <v>5</v>
       </c>
-      <c r="K22" s="100" t="n">
+      <c r="J22" s="100" t="n">
         <v>80</v>
       </c>
-      <c r="L22" s="97" t="inlineStr">
+      <c r="K22" s="97" t="inlineStr">
         <is>
           <t>3:400</t>
         </is>
       </c>
-      <c r="M22" s="98" t="inlineStr">
+      <c r="L22" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2472,23 +2434,18 @@
       <c r="H23" s="98" t="n">
         <v>60</v>
       </c>
-      <c r="I23" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" s="98" t="n">
+      <c r="I23" s="98" t="n">
         <v>5</v>
       </c>
-      <c r="K23" s="100" t="n">
+      <c r="J23" s="100" t="n">
         <v>60</v>
       </c>
-      <c r="L23" s="97" t="inlineStr">
+      <c r="K23" s="97" t="inlineStr">
         <is>
           <t>3:300</t>
         </is>
       </c>
-      <c r="M23" s="98" t="inlineStr">
+      <c r="L23" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2527,23 +2484,18 @@
       <c r="H24" s="98" t="n">
         <v>70</v>
       </c>
-      <c r="I24" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J24" s="98" t="n">
+      <c r="I24" s="98" t="n">
         <v>5</v>
       </c>
-      <c r="K24" s="100" t="n">
+      <c r="J24" s="100" t="n">
         <v>70</v>
       </c>
-      <c r="L24" s="97" t="inlineStr">
+      <c r="K24" s="97" t="inlineStr">
         <is>
           <t>3:350</t>
         </is>
       </c>
-      <c r="M24" s="98" t="inlineStr">
+      <c r="L24" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2582,23 +2534,18 @@
       <c r="H25" s="98" t="n">
         <v>90</v>
       </c>
-      <c r="I25" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J25" s="98" t="n">
+      <c r="I25" s="98" t="n">
         <v>3</v>
       </c>
-      <c r="K25" s="100" t="n">
+      <c r="J25" s="100" t="n">
         <v>30</v>
       </c>
-      <c r="L25" s="97" t="inlineStr">
+      <c r="K25" s="97" t="inlineStr">
         <is>
           <t>3:90</t>
         </is>
       </c>
-      <c r="M25" s="98" t="inlineStr">
+      <c r="L25" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2637,23 +2584,18 @@
       <c r="H26" s="98" t="n">
         <v>120</v>
       </c>
-      <c r="I26" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J26" s="98" t="n">
+      <c r="I26" s="98" t="n">
         <v>4</v>
       </c>
-      <c r="K26" s="100" t="n">
+      <c r="J26" s="100" t="n">
         <v>30</v>
       </c>
-      <c r="L26" s="97" t="inlineStr">
+      <c r="K26" s="97" t="inlineStr">
         <is>
           <t>3:120</t>
         </is>
       </c>
-      <c r="M26" s="98" t="inlineStr">
+      <c r="L26" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2692,23 +2634,18 @@
       <c r="H27" s="98" t="n">
         <v>120</v>
       </c>
-      <c r="I27" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J27" s="98" t="n">
+      <c r="I27" s="98" t="n">
         <v>4</v>
       </c>
-      <c r="K27" s="100" t="n">
+      <c r="J27" s="100" t="n">
         <v>30</v>
       </c>
-      <c r="L27" s="97" t="inlineStr">
+      <c r="K27" s="97" t="inlineStr">
         <is>
           <t>3:120</t>
         </is>
       </c>
-      <c r="M27" s="98" t="inlineStr">
+      <c r="L27" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2747,23 +2684,18 @@
       <c r="H28" s="98" t="n">
         <v>40</v>
       </c>
-      <c r="I28" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J28" s="98" t="n">
+      <c r="I28" s="98" t="n">
         <v>2</v>
       </c>
-      <c r="K28" s="100" t="n">
+      <c r="J28" s="100" t="n">
         <v>40</v>
       </c>
-      <c r="L28" s="97" t="inlineStr">
+      <c r="K28" s="97" t="inlineStr">
         <is>
           <t>3:80</t>
         </is>
       </c>
-      <c r="M28" s="98" t="inlineStr">
+      <c r="L28" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2802,23 +2734,18 @@
       <c r="H29" s="98" t="n">
         <v>40</v>
       </c>
-      <c r="I29" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J29" s="98" t="n">
+      <c r="I29" s="98" t="n">
         <v>4</v>
       </c>
-      <c r="K29" s="100" t="n">
+      <c r="J29" s="100" t="n">
         <v>40</v>
       </c>
-      <c r="L29" s="97" t="inlineStr">
+      <c r="K29" s="97" t="inlineStr">
         <is>
           <t>3:160</t>
         </is>
       </c>
-      <c r="M29" s="98" t="inlineStr">
+      <c r="L29" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2857,23 +2784,18 @@
       <c r="H30" s="98" t="n">
         <v>80</v>
       </c>
-      <c r="I30" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" s="98" t="n">
+      <c r="I30" s="98" t="n">
         <v>6</v>
       </c>
-      <c r="K30" s="100" t="n">
+      <c r="J30" s="100" t="n">
         <v>40</v>
       </c>
-      <c r="L30" s="97" t="inlineStr">
+      <c r="K30" s="97" t="inlineStr">
         <is>
           <t>3:240</t>
         </is>
       </c>
-      <c r="M30" s="98" t="inlineStr">
+      <c r="L30" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2912,23 +2834,18 @@
       <c r="H31" s="98" t="n">
         <v>40</v>
       </c>
-      <c r="I31" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J31" s="98" t="n">
+      <c r="I31" s="98" t="n">
         <v>4</v>
       </c>
-      <c r="K31" s="100" t="n">
+      <c r="J31" s="100" t="n">
         <v>40</v>
       </c>
-      <c r="L31" s="97" t="inlineStr">
+      <c r="K31" s="97" t="inlineStr">
         <is>
           <t>3:160</t>
         </is>
       </c>
-      <c r="M31" s="98" t="inlineStr">
+      <c r="L31" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -2967,23 +2884,18 @@
       <c r="H32" s="98" t="n">
         <v>60</v>
       </c>
-      <c r="I32" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J32" s="98" t="n">
+      <c r="I32" s="98" t="n">
         <v>1</v>
       </c>
-      <c r="K32" s="100" t="n">
+      <c r="J32" s="100" t="n">
         <v>60</v>
       </c>
-      <c r="L32" s="97" t="inlineStr">
+      <c r="K32" s="97" t="inlineStr">
         <is>
           <t>3:60</t>
         </is>
       </c>
-      <c r="M32" s="98" t="inlineStr">
+      <c r="L32" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3022,23 +2934,18 @@
       <c r="H33" s="98" t="n">
         <v>60</v>
       </c>
-      <c r="I33" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J33" s="98" t="n">
+      <c r="I33" s="98" t="n">
         <v>2</v>
       </c>
-      <c r="K33" s="100" t="n">
+      <c r="J33" s="100" t="n">
         <v>30</v>
       </c>
-      <c r="L33" s="97" t="inlineStr">
+      <c r="K33" s="97" t="inlineStr">
         <is>
           <t>3:60</t>
         </is>
       </c>
-      <c r="M33" s="98" t="inlineStr">
+      <c r="L33" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3077,23 +2984,18 @@
       <c r="H34" s="98" t="n">
         <v>60</v>
       </c>
-      <c r="I34" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J34" s="98" t="n">
+      <c r="I34" s="98" t="n">
         <v>2</v>
       </c>
-      <c r="K34" s="100" t="n">
+      <c r="J34" s="100" t="n">
         <v>30</v>
       </c>
-      <c r="L34" s="97" t="inlineStr">
+      <c r="K34" s="97" t="inlineStr">
         <is>
           <t>3:60</t>
         </is>
       </c>
-      <c r="M34" s="98" t="inlineStr">
+      <c r="L34" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3132,23 +3034,18 @@
       <c r="H35" s="98" t="n">
         <v>150</v>
       </c>
-      <c r="I35" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J35" s="98" t="n">
+      <c r="I35" s="98" t="n">
         <v>7</v>
       </c>
-      <c r="K35" s="100" t="n">
+      <c r="J35" s="100" t="n">
         <v>21</v>
       </c>
-      <c r="L35" s="97" t="inlineStr">
+      <c r="K35" s="97" t="inlineStr">
         <is>
           <t>3:150</t>
         </is>
       </c>
-      <c r="M35" s="98" t="inlineStr">
+      <c r="L35" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3187,23 +3084,18 @@
       <c r="H36" s="98" t="n">
         <v>150</v>
       </c>
-      <c r="I36" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J36" s="98" t="n">
+      <c r="I36" s="98" t="n">
         <v>8</v>
       </c>
-      <c r="K36" s="100" t="n">
+      <c r="J36" s="100" t="n">
         <v>18</v>
       </c>
-      <c r="L36" s="97" t="inlineStr">
+      <c r="K36" s="97" t="inlineStr">
         <is>
           <t>3:150</t>
         </is>
       </c>
-      <c r="M36" s="98" t="inlineStr">
+      <c r="L36" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3242,23 +3134,18 @@
       <c r="H37" s="98" t="n">
         <v>150</v>
       </c>
-      <c r="I37" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J37" s="98" t="n">
+      <c r="I37" s="98" t="n">
         <v>6</v>
       </c>
-      <c r="K37" s="100" t="n">
+      <c r="J37" s="100" t="n">
         <v>25</v>
       </c>
-      <c r="L37" s="97" t="inlineStr">
+      <c r="K37" s="97" t="inlineStr">
         <is>
           <t>3:150</t>
         </is>
       </c>
-      <c r="M37" s="98" t="inlineStr">
+      <c r="L37" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3297,23 +3184,18 @@
       <c r="H38" s="98" t="n">
         <v>150</v>
       </c>
-      <c r="I38" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J38" s="98" t="n">
+      <c r="I38" s="98" t="n">
         <v>6</v>
       </c>
-      <c r="K38" s="100" t="n">
+      <c r="J38" s="100" t="n">
         <v>25</v>
       </c>
-      <c r="L38" s="97" t="inlineStr">
+      <c r="K38" s="97" t="inlineStr">
         <is>
           <t>3:150</t>
         </is>
       </c>
-      <c r="M38" s="98" t="inlineStr">
+      <c r="L38" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3352,23 +3234,18 @@
       <c r="H39" s="98" t="n">
         <v>150</v>
       </c>
-      <c r="I39" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J39" s="98" t="n">
+      <c r="I39" s="98" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="100" t="n">
+      <c r="J39" s="100" t="n">
         <v>21</v>
       </c>
-      <c r="L39" s="97" t="inlineStr">
+      <c r="K39" s="97" t="inlineStr">
         <is>
           <t>3:150</t>
         </is>
       </c>
-      <c r="M39" s="98" t="inlineStr">
+      <c r="L39" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3407,23 +3284,18 @@
       <c r="H40" s="98" t="n">
         <v>150</v>
       </c>
-      <c r="I40" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J40" s="98" t="n">
+      <c r="I40" s="98" t="n">
         <v>6</v>
       </c>
-      <c r="K40" s="100" t="n">
+      <c r="J40" s="100" t="n">
         <v>25</v>
       </c>
-      <c r="L40" s="97" t="inlineStr">
+      <c r="K40" s="97" t="inlineStr">
         <is>
           <t>3:150</t>
         </is>
       </c>
-      <c r="M40" s="98" t="inlineStr">
+      <c r="L40" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3462,23 +3334,18 @@
       <c r="H41" s="98" t="n">
         <v>80</v>
       </c>
-      <c r="I41" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J41" s="98" t="n">
+      <c r="I41" s="98" t="n">
         <v>3</v>
       </c>
-      <c r="K41" s="100" t="n">
+      <c r="J41" s="100" t="n">
         <v>26</v>
       </c>
-      <c r="L41" s="97" t="inlineStr">
+      <c r="K41" s="97" t="inlineStr">
         <is>
           <t>3:80</t>
         </is>
       </c>
-      <c r="M41" s="98" t="inlineStr">
+      <c r="L41" s="98" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3517,23 +3384,18 @@
       <c r="H42" s="98" t="n">
         <v>200</v>
       </c>
-      <c r="I42" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J42" s="98" t="n">
+      <c r="I42" s="98" t="n">
         <v>5</v>
       </c>
-      <c r="K42" s="100" t="n">
+      <c r="J42" s="100" t="n">
         <v>40</v>
       </c>
-      <c r="L42" s="97" t="inlineStr">
+      <c r="K42" s="97" t="inlineStr">
         <is>
           <t>2:200</t>
         </is>
       </c>
-      <c r="M42" s="98" t="inlineStr">
+      <c r="L42" s="98" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
@@ -3572,23 +3434,18 @@
       <c r="H43" s="98" t="n">
         <v>200</v>
       </c>
-      <c r="I43" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J43" s="98" t="n">
+      <c r="I43" s="98" t="n">
         <v>5</v>
       </c>
-      <c r="K43" s="100" t="n">
+      <c r="J43" s="100" t="n">
         <v>40</v>
       </c>
-      <c r="L43" s="97" t="inlineStr">
+      <c r="K43" s="97" t="inlineStr">
         <is>
           <t>2:200</t>
         </is>
       </c>
-      <c r="M43" s="98" t="inlineStr">
+      <c r="L43" s="98" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
@@ -3627,23 +3484,18 @@
       <c r="H44" s="98" t="n">
         <v>200</v>
       </c>
-      <c r="I44" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J44" s="98" t="n">
+      <c r="I44" s="98" t="n">
         <v>4</v>
       </c>
-      <c r="K44" s="100" t="n">
+      <c r="J44" s="100" t="n">
         <v>50</v>
       </c>
-      <c r="L44" s="97" t="inlineStr">
+      <c r="K44" s="97" t="inlineStr">
         <is>
           <t>2:200</t>
         </is>
       </c>
-      <c r="M44" s="98" t="inlineStr">
+      <c r="L44" s="98" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
@@ -3682,23 +3534,18 @@
       <c r="H45" s="98" t="n">
         <v>240</v>
       </c>
-      <c r="I45" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J45" s="98" t="n">
+      <c r="I45" s="98" t="n">
         <v>6</v>
       </c>
-      <c r="K45" s="100" t="n">
+      <c r="J45" s="100" t="n">
         <v>40</v>
       </c>
-      <c r="L45" s="97" t="inlineStr">
+      <c r="K45" s="97" t="inlineStr">
         <is>
           <t>2:240</t>
         </is>
       </c>
-      <c r="M45" s="98" t="inlineStr">
+      <c r="L45" s="98" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
@@ -3737,23 +3584,18 @@
       <c r="H46" s="98" t="n">
         <v>240</v>
       </c>
-      <c r="I46" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J46" s="98" t="n">
+      <c r="I46" s="98" t="n">
         <v>8</v>
       </c>
-      <c r="K46" s="100" t="n">
+      <c r="J46" s="100" t="n">
         <v>30</v>
       </c>
-      <c r="L46" s="97" t="inlineStr">
+      <c r="K46" s="97" t="inlineStr">
         <is>
           <t>2:240</t>
         </is>
       </c>
-      <c r="M46" s="98" t="inlineStr">
+      <c r="L46" s="98" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
@@ -3792,30 +3634,25 @@
       <c r="H47" s="98" t="n">
         <v>240</v>
       </c>
-      <c r="I47" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J47" s="98" t="n">
+      <c r="I47" s="98" t="n">
         <v>9</v>
       </c>
-      <c r="K47" s="100" t="n">
+      <c r="J47" s="100" t="n">
         <v>26</v>
       </c>
-      <c r="L47" s="97" t="inlineStr">
+      <c r="K47" s="97" t="inlineStr">
         <is>
           <t>2:240</t>
         </is>
       </c>
-      <c r="M47" s="98" t="inlineStr">
+      <c r="L47" s="98" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:L1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3878,7 +3715,7 @@
         </is>
       </c>
       <c r="B5" s="108" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C5" s="108" t="n">
         <v>36</v>
@@ -3993,2516 +3830,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" style="82" min="1" max="1"/>
-    <col width="10" customWidth="1" style="82" min="2" max="2"/>
-    <col width="30" customWidth="1" style="82" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="106" t="inlineStr">
-        <is>
-          <t>◆ 参考データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="111" t="inlineStr">
-        <is>
-          <t>在庫 合計</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>18320</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>問</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>在庫外（監査に落ちた分・在庫に数えない）</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>問</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="107" t="inlineStr">
-        <is>
-          <t>辞書にある全単語数（問題化の母数）</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="95" t="inlineStr">
-        <is>
-          <t>辞書</t>
-        </is>
-      </c>
-      <c r="B7" s="95" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="C7" s="95" t="inlineStr">
-        <is>
-          <t>内訳</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="12" customWidth="1" style="82" min="1" max="1"/>
-    <col width="16" customWidth="1" style="82" min="2" max="2"/>
-    <col width="7" customWidth="1" style="82" min="3" max="3"/>
-    <col width="12" customWidth="1" style="82" min="4" max="4"/>
-    <col width="9" customWidth="1" style="82" min="5" max="6"/>
-    <col width="11" customWidth="1" style="82" min="7" max="7"/>
-    <col width="15" customWidth="1" style="82" min="8" max="8"/>
-    <col width="26" customWidth="1" style="82" min="9" max="9"/>
-    <col width="12" customWidth="1" style="82" min="10" max="10"/>
-    <col width="10" customWidth="1" style="82" min="11" max="11"/>
-    <col width="46" customWidth="1" style="82" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="66" t="inlineStr">
-        <is>
-          <t>セクション</t>
-        </is>
-      </c>
-      <c r="B1" s="66" t="inlineStr">
-        <is>
-          <t>大問</t>
-        </is>
-      </c>
-      <c r="C1" s="66" t="inlineStr">
-        <is>
-          <t>レベル</t>
-        </is>
-      </c>
-      <c r="D1" s="66" t="inlineStr">
-        <is>
-          <t>在庫問題数</t>
-        </is>
-      </c>
-      <c r="E1" s="66" t="inlineStr">
-        <is>
-          <t>セット数</t>
-        </is>
-      </c>
-      <c r="F1" s="66" t="inlineStr">
-        <is>
-          <t>割増し倍数</t>
-        </is>
-      </c>
-      <c r="G1" s="66" t="inlineStr">
-        <is>
-          <t>本番出題数</t>
-        </is>
-      </c>
-      <c r="H1" s="66" t="inlineStr">
-        <is>
-          <t>模試換算(何回分)</t>
-        </is>
-      </c>
-      <c r="I1" s="66" t="inlineStr">
-        <is>
-          <t>誤答数の内訳</t>
-        </is>
-      </c>
-      <c r="J1" s="66" t="inlineStr">
-        <is>
-          <t>シャッフル</t>
-        </is>
-      </c>
-      <c r="K1" s="66" t="inlineStr">
-        <is>
-          <t>模試問題数</t>
-        </is>
-      </c>
-      <c r="L1" s="66" t="inlineStr">
-        <is>
-          <t>メモ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="67" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B2" s="68" t="inlineStr">
-        <is>
-          <t>漢字読み</t>
-        </is>
-      </c>
-      <c r="C2" s="69" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D2" s="69" t="n">
-        <v>146</v>
-      </c>
-      <c r="E2" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F2" s="70" t="inlineStr">
-        <is>
-          <t>×3</t>
-        </is>
-      </c>
-      <c r="G2" s="69" t="n">
-        <v>12</v>
-      </c>
-      <c r="H2" s="71" t="n">
-        <v>12</v>
-      </c>
-      <c r="I2" s="68" t="inlineStr">
-        <is>
-          <t>3:785</t>
-        </is>
-      </c>
-      <c r="J2" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K2" s="69" t="n">
-        <v>104</v>
-      </c>
-      <c r="L2" s="68" t="inlineStr">
-        <is>
-          <t>N5の質の高い漢字語（数字・接尾辞を除く）は実質104語＝N5は漢字自体が少ないため上限。模試プールは120でなく104問が自然な上限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="67" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B3" s="68" t="inlineStr">
-        <is>
-          <t>漢字読み</t>
-        </is>
-      </c>
-      <c r="C3" s="69" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D3" s="69" t="n">
-        <v>331</v>
-      </c>
-      <c r="E3" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F3" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G3" s="69" t="n">
-        <v>9</v>
-      </c>
-      <c r="H3" s="72" t="n">
-        <v>36</v>
-      </c>
-      <c r="I3" s="68" t="inlineStr">
-        <is>
-          <t>3:537</t>
-        </is>
-      </c>
-      <c r="J3" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K3" s="69" t="n">
-        <v>90</v>
-      </c>
-      <c r="L3" s="68" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="67" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B4" s="68" t="inlineStr">
-        <is>
-          <t>漢字読み</t>
-        </is>
-      </c>
-      <c r="C4" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D4" s="69" t="n">
-        <v>1944</v>
-      </c>
-      <c r="E4" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G4" s="69" t="n">
-        <v>8</v>
-      </c>
-      <c r="H4" s="72" t="n">
-        <v>243</v>
-      </c>
-      <c r="I4" s="68" t="inlineStr">
-        <is>
-          <t>3:1882</t>
-        </is>
-      </c>
-      <c r="J4" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K4" s="69" t="n">
-        <v>80</v>
-      </c>
-      <c r="L4" s="68" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="67" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B5" s="68" t="inlineStr">
-        <is>
-          <t>表記</t>
-        </is>
-      </c>
-      <c r="C5" s="69" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D5" s="69" t="n">
-        <v>212</v>
-      </c>
-      <c r="E5" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G5" s="69" t="n">
-        <v>8</v>
-      </c>
-      <c r="H5" s="72" t="n">
-        <v>26</v>
-      </c>
-      <c r="I5" s="68" t="inlineStr">
-        <is>
-          <t>3:587</t>
-        </is>
-      </c>
-      <c r="J5" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K5" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="68" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="67" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B6" s="68" t="inlineStr">
-        <is>
-          <t>表記</t>
-        </is>
-      </c>
-      <c r="C6" s="69" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D6" s="69" t="n">
-        <v>365</v>
-      </c>
-      <c r="E6" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G6" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" s="72" t="n">
-        <v>60</v>
-      </c>
-      <c r="I6" s="68" t="inlineStr">
-        <is>
-          <t>3:571</t>
-        </is>
-      </c>
-      <c r="J6" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K6" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="68" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="67" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B7" s="68" t="inlineStr">
-        <is>
-          <t>表記</t>
-        </is>
-      </c>
-      <c r="C7" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D7" s="69" t="n">
-        <v>1992</v>
-      </c>
-      <c r="E7" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G7" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" s="72" t="n">
-        <v>332</v>
-      </c>
-      <c r="I7" s="68" t="inlineStr">
-        <is>
-          <t>3:1930</t>
-        </is>
-      </c>
-      <c r="J7" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K7" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="68" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="67" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B8" s="68" t="inlineStr">
-        <is>
-          <t>文脈規定</t>
-        </is>
-      </c>
-      <c r="C8" s="69" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D8" s="69" t="n">
-        <v>687</v>
-      </c>
-      <c r="E8" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G8" s="69" t="n">
-        <v>10</v>
-      </c>
-      <c r="H8" s="72" t="n">
-        <v>68</v>
-      </c>
-      <c r="I8" s="68" t="inlineStr">
-        <is>
-          <t>3:197 / 4:222 / 5:268</t>
-        </is>
-      </c>
-      <c r="J8" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K8" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L8" s="68" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="67" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B9" s="68" t="inlineStr">
-        <is>
-          <t>文脈規定</t>
-        </is>
-      </c>
-      <c r="C9" s="69" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D9" s="69" t="n">
-        <v>655</v>
-      </c>
-      <c r="E9" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G9" s="69" t="n">
-        <v>10</v>
-      </c>
-      <c r="H9" s="72" t="n">
-        <v>65</v>
-      </c>
-      <c r="I9" s="68" t="inlineStr">
-        <is>
-          <t>3:243 / 4:231 / 5:181</t>
-        </is>
-      </c>
-      <c r="J9" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K9" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L9" s="68" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="67" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B10" s="68" t="inlineStr">
-        <is>
-          <t>文脈規定</t>
-        </is>
-      </c>
-      <c r="C10" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D10" s="69" t="n">
-        <v>2105</v>
-      </c>
-      <c r="E10" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G10" s="69" t="n">
-        <v>11</v>
-      </c>
-      <c r="H10" s="72" t="n">
-        <v>191</v>
-      </c>
-      <c r="I10" s="68" t="inlineStr">
-        <is>
-          <t>3:1397 / 4:450 / 5:258</t>
-        </is>
-      </c>
-      <c r="J10" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K10" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="68" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="67" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B11" s="68" t="inlineStr">
-        <is>
-          <t>言い換え類義</t>
-        </is>
-      </c>
-      <c r="C11" s="69" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D11" s="69" t="n">
-        <v>236</v>
-      </c>
-      <c r="E11" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G11" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="72" t="n">
-        <v>47</v>
-      </c>
-      <c r="I11" s="68" t="inlineStr">
-        <is>
-          <t>3:205 / 4:13 / 5:18</t>
-        </is>
-      </c>
-      <c r="J11" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K11" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L11" s="68" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="67" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B12" s="68" t="inlineStr">
-        <is>
-          <t>言い換え類義</t>
-        </is>
-      </c>
-      <c r="C12" s="69" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D12" s="69" t="n">
-        <v>407</v>
-      </c>
-      <c r="E12" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G12" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="H12" s="72" t="n">
-        <v>81</v>
-      </c>
-      <c r="I12" s="68" t="inlineStr">
-        <is>
-          <t>3:183 / 4:8 / 5:40 / 6:176</t>
-        </is>
-      </c>
-      <c r="J12" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K12" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" s="68" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="67" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B13" s="68" t="inlineStr">
-        <is>
-          <t>言い換え類義</t>
-        </is>
-      </c>
-      <c r="C13" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D13" s="69" t="n">
-        <v>1612</v>
-      </c>
-      <c r="E13" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G13" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" s="72" t="n">
-        <v>322</v>
-      </c>
-      <c r="I13" s="68" t="inlineStr">
-        <is>
-          <t>3:601 / 4:14 / 5:100 / 6:897</t>
-        </is>
-      </c>
-      <c r="J13" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K13" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L13" s="68" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="67" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B14" s="68" t="inlineStr">
-        <is>
-          <t>用法</t>
-        </is>
-      </c>
-      <c r="C14" s="69" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D14" s="69" t="n">
-        <v>571</v>
-      </c>
-      <c r="E14" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G14" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" s="72" t="n">
-        <v>114</v>
-      </c>
-      <c r="I14" s="68" t="inlineStr">
-        <is>
-          <t>3:571</t>
-        </is>
-      </c>
-      <c r="J14" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K14" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L14" s="68" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="67" t="inlineStr">
-        <is>
-          <t>文字・語彙</t>
-        </is>
-      </c>
-      <c r="B15" s="68" t="inlineStr">
-        <is>
-          <t>用法</t>
-        </is>
-      </c>
-      <c r="C15" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D15" s="69" t="n">
-        <v>600</v>
-      </c>
-      <c r="E15" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G15" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" s="72" t="n">
-        <v>120</v>
-      </c>
-      <c r="I15" s="68" t="inlineStr">
-        <is>
-          <t>3:531 / 4:28 / 5:27 / 6:14</t>
-        </is>
-      </c>
-      <c r="J15" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K15" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L15" s="68" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="73" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B16" s="68" t="inlineStr">
-        <is>
-          <t>文法形式</t>
-        </is>
-      </c>
-      <c r="C16" s="69" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D16" s="69" t="n">
-        <v>211</v>
-      </c>
-      <c r="E16" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G16" s="69" t="n">
-        <v>16</v>
-      </c>
-      <c r="H16" s="71" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" s="68" t="inlineStr">
-        <is>
-          <t>3:210 / 4:1</t>
-        </is>
-      </c>
-      <c r="J16" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K16" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L16" s="68" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="73" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B17" s="68" t="inlineStr">
-        <is>
-          <t>文法形式</t>
-        </is>
-      </c>
-      <c r="C17" s="69" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D17" s="69" t="n">
-        <v>361</v>
-      </c>
-      <c r="E17" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G17" s="69" t="n">
-        <v>15</v>
-      </c>
-      <c r="H17" s="72" t="n">
-        <v>24</v>
-      </c>
-      <c r="I17" s="68" t="inlineStr">
-        <is>
-          <t>3:361</t>
-        </is>
-      </c>
-      <c r="J17" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K17" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L17" s="68" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="73" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B18" s="68" t="inlineStr">
-        <is>
-          <t>文法形式</t>
-        </is>
-      </c>
-      <c r="C18" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D18" s="69" t="n">
-        <v>448</v>
-      </c>
-      <c r="E18" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G18" s="69" t="n">
-        <v>13</v>
-      </c>
-      <c r="H18" s="72" t="n">
-        <v>34</v>
-      </c>
-      <c r="I18" s="68" t="inlineStr">
-        <is>
-          <t>3:446 / 4:2</t>
-        </is>
-      </c>
-      <c r="J18" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K18" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L18" s="68" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="73" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B19" s="68" t="inlineStr">
-        <is>
-          <t>組み立て</t>
-        </is>
-      </c>
-      <c r="C19" s="69" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D19" s="69" t="n">
-        <v>146</v>
-      </c>
-      <c r="E19" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G19" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" s="72" t="n">
-        <v>29</v>
-      </c>
-      <c r="I19" s="68" t="inlineStr">
-        <is>
-          <t>3:146</t>
-        </is>
-      </c>
-      <c r="J19" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K19" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="68" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="73" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B20" s="68" t="inlineStr">
-        <is>
-          <t>組み立て</t>
-        </is>
-      </c>
-      <c r="C20" s="69" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D20" s="69" t="n">
-        <v>216</v>
-      </c>
-      <c r="E20" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G20" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" s="72" t="n">
-        <v>43</v>
-      </c>
-      <c r="I20" s="68" t="inlineStr">
-        <is>
-          <t>3:216</t>
-        </is>
-      </c>
-      <c r="J20" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K20" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L20" s="68" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="73" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B21" s="68" t="inlineStr">
-        <is>
-          <t>組み立て</t>
-        </is>
-      </c>
-      <c r="C21" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D21" s="69" t="n">
-        <v>311</v>
-      </c>
-      <c r="E21" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G21" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" s="72" t="n">
-        <v>62</v>
-      </c>
-      <c r="I21" s="68" t="inlineStr">
-        <is>
-          <t>3:311</t>
-        </is>
-      </c>
-      <c r="J21" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K21" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L21" s="68" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="73" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B22" s="68" t="inlineStr">
-        <is>
-          <t>文章の文法</t>
-        </is>
-      </c>
-      <c r="C22" s="69" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D22" s="69" t="n">
-        <v>400</v>
-      </c>
-      <c r="E22" s="69" t="n">
-        <v>80</v>
-      </c>
-      <c r="F22" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G22" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" s="72" t="n">
-        <v>80</v>
-      </c>
-      <c r="I22" s="68" t="inlineStr">
-        <is>
-          <t>3:400</t>
-        </is>
-      </c>
-      <c r="J22" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K22" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="68" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="73" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B23" s="68" t="inlineStr">
-        <is>
-          <t>文章の文法</t>
-        </is>
-      </c>
-      <c r="C23" s="69" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D23" s="69" t="n">
-        <v>300</v>
-      </c>
-      <c r="E23" s="69" t="n">
-        <v>60</v>
-      </c>
-      <c r="F23" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G23" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="H23" s="72" t="n">
-        <v>60</v>
-      </c>
-      <c r="I23" s="68" t="inlineStr">
-        <is>
-          <t>3:300</t>
-        </is>
-      </c>
-      <c r="J23" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K23" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="68" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="73" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B24" s="68" t="inlineStr">
-        <is>
-          <t>文章の文法</t>
-        </is>
-      </c>
-      <c r="C24" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D24" s="69" t="n">
-        <v>350</v>
-      </c>
-      <c r="E24" s="69" t="n">
-        <v>70</v>
-      </c>
-      <c r="F24" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G24" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="H24" s="72" t="n">
-        <v>70</v>
-      </c>
-      <c r="I24" s="68" t="inlineStr">
-        <is>
-          <t>3:350</t>
-        </is>
-      </c>
-      <c r="J24" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K24" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L24" s="68" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="74" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B25" s="68" t="inlineStr">
-        <is>
-          <t>内容理解(短文)</t>
-        </is>
-      </c>
-      <c r="C25" s="69" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D25" s="69" t="n">
-        <v>90</v>
-      </c>
-      <c r="E25" s="69" t="n">
-        <v>90</v>
-      </c>
-      <c r="F25" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G25" s="69" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="72" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="68" t="inlineStr">
-        <is>
-          <t>3:90</t>
-        </is>
-      </c>
-      <c r="J25" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K25" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L25" s="68" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="74" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B26" s="68" t="inlineStr">
-        <is>
-          <t>内容理解(短文)</t>
-        </is>
-      </c>
-      <c r="C26" s="69" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D26" s="69" t="n">
-        <v>120</v>
-      </c>
-      <c r="E26" s="69" t="n">
-        <v>120</v>
-      </c>
-      <c r="F26" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G26" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="H26" s="72" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="68" t="inlineStr">
-        <is>
-          <t>3:120</t>
-        </is>
-      </c>
-      <c r="J26" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K26" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L26" s="68" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="74" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B27" s="68" t="inlineStr">
-        <is>
-          <t>内容理解(短文)</t>
-        </is>
-      </c>
-      <c r="C27" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D27" s="69" t="n">
-        <v>120</v>
-      </c>
-      <c r="E27" s="69" t="n">
-        <v>120</v>
-      </c>
-      <c r="F27" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G27" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="H27" s="72" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="68" t="inlineStr">
-        <is>
-          <t>3:120</t>
-        </is>
-      </c>
-      <c r="J27" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K27" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L27" s="68" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="74" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B28" s="68" t="inlineStr">
-        <is>
-          <t>内容理解(中文)</t>
-        </is>
-      </c>
-      <c r="C28" s="69" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D28" s="69" t="n">
-        <v>80</v>
-      </c>
-      <c r="E28" s="69" t="n">
-        <v>40</v>
-      </c>
-      <c r="F28" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G28" s="69" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" s="72" t="n">
-        <v>40</v>
-      </c>
-      <c r="I28" s="68" t="inlineStr">
-        <is>
-          <t>3:80</t>
-        </is>
-      </c>
-      <c r="J28" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K28" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L28" s="68" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="74" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B29" s="68" t="inlineStr">
-        <is>
-          <t>内容理解(中文)</t>
-        </is>
-      </c>
-      <c r="C29" s="69" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D29" s="69" t="n">
-        <v>160</v>
-      </c>
-      <c r="E29" s="69" t="n">
-        <v>40</v>
-      </c>
-      <c r="F29" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G29" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="H29" s="72" t="n">
-        <v>40</v>
-      </c>
-      <c r="I29" s="68" t="inlineStr">
-        <is>
-          <t>3:160</t>
-        </is>
-      </c>
-      <c r="J29" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K29" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L29" s="68" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="74" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B30" s="68" t="inlineStr">
-        <is>
-          <t>内容理解(中文)</t>
-        </is>
-      </c>
-      <c r="C30" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D30" s="69" t="n">
-        <v>240</v>
-      </c>
-      <c r="E30" s="69" t="n">
-        <v>80</v>
-      </c>
-      <c r="F30" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G30" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="H30" s="72" t="n">
-        <v>40</v>
-      </c>
-      <c r="I30" s="68" t="inlineStr">
-        <is>
-          <t>3:240</t>
-        </is>
-      </c>
-      <c r="J30" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K30" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L30" s="68" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="74" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B31" s="68" t="inlineStr">
-        <is>
-          <t>内容理解(長文)</t>
-        </is>
-      </c>
-      <c r="C31" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D31" s="69" t="n">
-        <v>160</v>
-      </c>
-      <c r="E31" s="69" t="n">
-        <v>40</v>
-      </c>
-      <c r="F31" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G31" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="H31" s="72" t="n">
-        <v>40</v>
-      </c>
-      <c r="I31" s="68" t="inlineStr">
-        <is>
-          <t>3:160</t>
-        </is>
-      </c>
-      <c r="J31" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K31" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L31" s="68" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="74" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B32" s="68" t="inlineStr">
-        <is>
-          <t>情報検索</t>
-        </is>
-      </c>
-      <c r="C32" s="69" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D32" s="69" t="n">
-        <v>60</v>
-      </c>
-      <c r="E32" s="69" t="n">
-        <v>60</v>
-      </c>
-      <c r="F32" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G32" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="72" t="n">
-        <v>60</v>
-      </c>
-      <c r="I32" s="68" t="inlineStr">
-        <is>
-          <t>3:60</t>
-        </is>
-      </c>
-      <c r="J32" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K32" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L32" s="68" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="74" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B33" s="68" t="inlineStr">
-        <is>
-          <t>情報検索</t>
-        </is>
-      </c>
-      <c r="C33" s="69" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D33" s="69" t="n">
-        <v>60</v>
-      </c>
-      <c r="E33" s="69" t="n">
-        <v>60</v>
-      </c>
-      <c r="F33" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G33" s="69" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" s="72" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" s="68" t="inlineStr">
-        <is>
-          <t>3:60</t>
-        </is>
-      </c>
-      <c r="J33" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K33" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L33" s="68" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="74" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B34" s="68" t="inlineStr">
-        <is>
-          <t>情報検索</t>
-        </is>
-      </c>
-      <c r="C34" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D34" s="69" t="n">
-        <v>60</v>
-      </c>
-      <c r="E34" s="69" t="n">
-        <v>60</v>
-      </c>
-      <c r="F34" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G34" s="69" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="72" t="n">
-        <v>30</v>
-      </c>
-      <c r="I34" s="68" t="inlineStr">
-        <is>
-          <t>3:60</t>
-        </is>
-      </c>
-      <c r="J34" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K34" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L34" s="68" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="75" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B35" s="68" t="inlineStr">
-        <is>
-          <t>課題理解</t>
-        </is>
-      </c>
-      <c r="C35" s="69" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D35" s="69" t="n">
-        <v>150</v>
-      </c>
-      <c r="E35" s="69" t="n">
-        <v>150</v>
-      </c>
-      <c r="F35" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G35" s="69" t="n">
-        <v>7</v>
-      </c>
-      <c r="H35" s="72" t="n">
-        <v>21</v>
-      </c>
-      <c r="I35" s="68" t="inlineStr">
-        <is>
-          <t>3:150</t>
-        </is>
-      </c>
-      <c r="J35" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K35" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L35" s="68" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="75" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B36" s="68" t="inlineStr">
-        <is>
-          <t>課題理解</t>
-        </is>
-      </c>
-      <c r="C36" s="69" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D36" s="69" t="n">
-        <v>150</v>
-      </c>
-      <c r="E36" s="69" t="n">
-        <v>150</v>
-      </c>
-      <c r="F36" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G36" s="69" t="n">
-        <v>8</v>
-      </c>
-      <c r="H36" s="72" t="n">
-        <v>18</v>
-      </c>
-      <c r="I36" s="68" t="inlineStr">
-        <is>
-          <t>3:150</t>
-        </is>
-      </c>
-      <c r="J36" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K36" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L36" s="68" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="75" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B37" s="68" t="inlineStr">
-        <is>
-          <t>課題理解</t>
-        </is>
-      </c>
-      <c r="C37" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D37" s="69" t="n">
-        <v>150</v>
-      </c>
-      <c r="E37" s="69" t="n">
-        <v>150</v>
-      </c>
-      <c r="F37" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G37" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="H37" s="72" t="n">
-        <v>25</v>
-      </c>
-      <c r="I37" s="68" t="inlineStr">
-        <is>
-          <t>3:150</t>
-        </is>
-      </c>
-      <c r="J37" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K37" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L37" s="68" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="75" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B38" s="68" t="inlineStr">
-        <is>
-          <t>ポイント理解</t>
-        </is>
-      </c>
-      <c r="C38" s="69" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D38" s="69" t="n">
-        <v>150</v>
-      </c>
-      <c r="E38" s="69" t="n">
-        <v>150</v>
-      </c>
-      <c r="F38" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G38" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="H38" s="72" t="n">
-        <v>25</v>
-      </c>
-      <c r="I38" s="68" t="inlineStr">
-        <is>
-          <t>3:150</t>
-        </is>
-      </c>
-      <c r="J38" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K38" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L38" s="68" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="75" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B39" s="68" t="inlineStr">
-        <is>
-          <t>ポイント理解</t>
-        </is>
-      </c>
-      <c r="C39" s="69" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D39" s="69" t="n">
-        <v>150</v>
-      </c>
-      <c r="E39" s="69" t="n">
-        <v>150</v>
-      </c>
-      <c r="F39" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G39" s="69" t="n">
-        <v>7</v>
-      </c>
-      <c r="H39" s="72" t="n">
-        <v>21</v>
-      </c>
-      <c r="I39" s="68" t="inlineStr">
-        <is>
-          <t>3:150</t>
-        </is>
-      </c>
-      <c r="J39" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K39" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L39" s="68" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="75" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B40" s="68" t="inlineStr">
-        <is>
-          <t>ポイント理解</t>
-        </is>
-      </c>
-      <c r="C40" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D40" s="69" t="n">
-        <v>150</v>
-      </c>
-      <c r="E40" s="69" t="n">
-        <v>150</v>
-      </c>
-      <c r="F40" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G40" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="H40" s="72" t="n">
-        <v>25</v>
-      </c>
-      <c r="I40" s="68" t="inlineStr">
-        <is>
-          <t>3:150</t>
-        </is>
-      </c>
-      <c r="J40" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K40" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L40" s="68" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="75" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B41" s="68" t="inlineStr">
-        <is>
-          <t>概要理解</t>
-        </is>
-      </c>
-      <c r="C41" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D41" s="69" t="n">
-        <v>80</v>
-      </c>
-      <c r="E41" s="69" t="n">
-        <v>80</v>
-      </c>
-      <c r="F41" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G41" s="69" t="n">
-        <v>3</v>
-      </c>
-      <c r="H41" s="72" t="n">
-        <v>26</v>
-      </c>
-      <c r="I41" s="68" t="inlineStr">
-        <is>
-          <t>3:80</t>
-        </is>
-      </c>
-      <c r="J41" s="69" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="K41" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L41" s="68" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="75" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B42" s="68" t="inlineStr">
-        <is>
-          <t>発話表現</t>
-        </is>
-      </c>
-      <c r="C42" s="69" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D42" s="69" t="n">
-        <v>200</v>
-      </c>
-      <c r="E42" s="69" t="n">
-        <v>200</v>
-      </c>
-      <c r="F42" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G42" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="H42" s="72" t="n">
-        <v>40</v>
-      </c>
-      <c r="I42" s="68" t="inlineStr">
-        <is>
-          <t>2:200</t>
-        </is>
-      </c>
-      <c r="J42" s="69" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="K42" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L42" s="68" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="75" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B43" s="68" t="inlineStr">
-        <is>
-          <t>発話表現</t>
-        </is>
-      </c>
-      <c r="C43" s="69" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D43" s="69" t="n">
-        <v>200</v>
-      </c>
-      <c r="E43" s="69" t="n">
-        <v>200</v>
-      </c>
-      <c r="F43" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G43" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="H43" s="72" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" s="68" t="inlineStr">
-        <is>
-          <t>2:200</t>
-        </is>
-      </c>
-      <c r="J43" s="69" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="K43" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L43" s="68" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="75" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B44" s="68" t="inlineStr">
-        <is>
-          <t>発話表現</t>
-        </is>
-      </c>
-      <c r="C44" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D44" s="69" t="n">
-        <v>200</v>
-      </c>
-      <c r="E44" s="69" t="n">
-        <v>200</v>
-      </c>
-      <c r="F44" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G44" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="H44" s="72" t="n">
-        <v>50</v>
-      </c>
-      <c r="I44" s="68" t="inlineStr">
-        <is>
-          <t>2:200</t>
-        </is>
-      </c>
-      <c r="J44" s="69" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="K44" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L44" s="68" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="75" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B45" s="68" t="inlineStr">
-        <is>
-          <t>即時応答</t>
-        </is>
-      </c>
-      <c r="C45" s="69" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D45" s="69" t="n">
-        <v>240</v>
-      </c>
-      <c r="E45" s="69" t="n">
-        <v>240</v>
-      </c>
-      <c r="F45" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G45" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="H45" s="72" t="n">
-        <v>40</v>
-      </c>
-      <c r="I45" s="68" t="inlineStr">
-        <is>
-          <t>2:240</t>
-        </is>
-      </c>
-      <c r="J45" s="69" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="K45" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L45" s="68" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="75" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B46" s="68" t="inlineStr">
-        <is>
-          <t>即時応答</t>
-        </is>
-      </c>
-      <c r="C46" s="69" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D46" s="69" t="n">
-        <v>240</v>
-      </c>
-      <c r="E46" s="69" t="n">
-        <v>240</v>
-      </c>
-      <c r="F46" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G46" s="69" t="n">
-        <v>8</v>
-      </c>
-      <c r="H46" s="72" t="n">
-        <v>30</v>
-      </c>
-      <c r="I46" s="68" t="inlineStr">
-        <is>
-          <t>2:240</t>
-        </is>
-      </c>
-      <c r="J46" s="69" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="K46" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L46" s="68" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="75" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B47" s="68" t="inlineStr">
-        <is>
-          <t>即時応答</t>
-        </is>
-      </c>
-      <c r="C47" s="69" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D47" s="69" t="n">
-        <v>240</v>
-      </c>
-      <c r="E47" s="69" t="n">
-        <v>240</v>
-      </c>
-      <c r="F47" s="69" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="G47" s="69" t="n">
-        <v>9</v>
-      </c>
-      <c r="H47" s="72" t="n">
-        <v>26</v>
-      </c>
-      <c r="I47" s="68" t="inlineStr">
-        <is>
-          <t>2:240</t>
-        </is>
-      </c>
-      <c r="J47" s="69" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="K47" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L47" s="68" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:L1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
@@ -9660,7 +6987,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFC25E00"/>
@@ -12219,1600 +9546,1712 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF6A3D9A"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="46" customWidth="1" style="82" min="1" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22.05" customHeight="1" s="82">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>◆ 習得の仕組み ― ID×面 で覚え具合を測る</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="94" t="inlineStr">
-        <is>
-          <t>習得の仕組み ― 「ID × 面(かたち)」で覚え具合を測る</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="87" t="inlineStr">
-        <is>
-          <t>IDは『あなたが何をどれだけ覚えたか』を記録する“貯金箱”。大問を1問解くたびに、その問題が紐づくIDへ習得が貯まり、その貯金がアプリの成長表示(予想得点・カバー率・リング・復習)をすべて動かしている。弱点ドリルはその使い道の一つにすぎない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="83" t="inlineStr">
-        <is>
-          <t>■ 流れ（1問解くと何が起きるか）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="87" t="inlineStr">
-        <is>
-          <t>① 大問を1問解く</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="91" t="inlineStr">
-        <is>
-          <t>② その問題が「どのID」の「どの面」かを判定  ← facetMap.ts が正本</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="87" t="inlineStr">
-        <is>
-          <t>③ そのID×面に習得が加算/減点  ← state.mastery（面別マスタリー）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="91" t="inlineStr">
-        <is>
-          <t>④ 貯まった習得が、予想得点・カバー率・合格リング・復習の出題・弱点ドリルを動かす</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="83" t="inlineStr">
-        <is>
-          <t>■ 5つの面(かたち)＝1つのIDを、この5方向で別々に追う</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="89" t="inlineStr">
-        <is>
-          <t>面</t>
-        </is>
-      </c>
-      <c r="B12" s="89" t="inlineStr">
-        <is>
-          <t>意味</t>
-        </is>
-      </c>
-      <c r="C12" s="85" t="n"/>
-      <c r="D12" s="86" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="44" t="inlineStr">
-        <is>
-          <t>read（読み）</t>
-        </is>
-      </c>
-      <c r="B13" s="88" t="inlineStr">
-        <is>
-          <t>漢字が読めるか</t>
-        </is>
-      </c>
-      <c r="C13" s="85" t="n"/>
-      <c r="D13" s="86" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="46" t="inlineStr">
-        <is>
-          <t>write（書き）</t>
-        </is>
-      </c>
-      <c r="B14" s="84" t="inlineStr">
-        <is>
-          <t>漢字が書けるか・正しい表記が選べるか</t>
-        </is>
-      </c>
-      <c r="C14" s="85" t="n"/>
-      <c r="D14" s="86" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="44" t="inlineStr">
-        <is>
-          <t>mean（意味）</t>
-        </is>
-      </c>
-      <c r="B15" s="88" t="inlineStr">
-        <is>
-          <t>語の意味・使い方が分かるか</t>
-        </is>
-      </c>
-      <c r="C15" s="85" t="n"/>
-      <c r="D15" s="86" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="46" t="inlineStr">
-        <is>
-          <t>listen（聞き取り）</t>
-        </is>
-      </c>
-      <c r="B16" s="84" t="inlineStr">
-        <is>
-          <t>聞いて分かるか</t>
-        </is>
-      </c>
-      <c r="C16" s="85" t="n"/>
-      <c r="D16" s="86" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="44" t="inlineStr">
-        <is>
-          <t>grammar（文法）</t>
-        </is>
-      </c>
-      <c r="B17" s="88" t="inlineStr">
-        <is>
-          <t>文法の形・組み立てが分かるか</t>
-        </is>
-      </c>
-      <c r="C17" s="85" t="n"/>
-      <c r="D17" s="86" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="83" t="inlineStr">
-        <is>
-          <t>■ 3種のID × 貯まる面 × どの大問で貯まるか</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="89" t="inlineStr">
-        <is>
-          <t>種類</t>
-        </is>
-      </c>
-      <c r="B20" s="89" t="inlineStr">
-        <is>
-          <t>貯まる面</t>
-        </is>
-      </c>
-      <c r="C20" s="89" t="inlineStr">
-        <is>
-          <t>どの大問を解くと貯まるか</t>
-        </is>
-      </c>
-      <c r="D20" s="86" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="48" t="inlineStr">
-        <is>
-          <t>語彙単語（vocab id）</t>
-        </is>
-      </c>
-      <c r="B21" s="84" t="inlineStr">
-        <is>
-          <t>read・write・mean・listen</t>
-        </is>
-      </c>
-      <c r="C21" s="84" t="inlineStr">
-        <is>
-          <t>漢字読み→read ／ 表記→write ／ 文脈規定・言い換え・用法→mean ／ 聞き取り→listen</t>
-        </is>
-      </c>
-      <c r="D21" s="86" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="49" t="inlineStr">
-        <is>
-          <t>漢字単語（kanji字）</t>
-        </is>
-      </c>
-      <c r="B22" s="88" t="inlineStr">
-        <is>
-          <t>read・write</t>
-        </is>
-      </c>
-      <c r="C22" s="88" t="inlineStr">
-        <is>
-          <t>漢字読み→read ／ 書き取り→write</t>
-        </is>
-      </c>
-      <c r="D22" s="86" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="48" t="inlineStr">
-        <is>
-          <t>文法単語（文法点 pointId）</t>
-        </is>
-      </c>
-      <c r="B23" s="84" t="inlineStr">
-        <is>
-          <t>grammar</t>
-        </is>
-      </c>
-      <c r="C23" s="84" t="inlineStr">
-        <is>
-          <t>穴埋め(文法形式)・並べ替え(組み立て)・文章の文法 → すべて grammar 面へ合流</t>
-        </is>
-      </c>
-      <c r="D23" s="86" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="83" t="inlineStr">
-        <is>
-          <t>■ 例：語彙「食べる」</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="93" t="inlineStr">
-        <is>
-          <t>「読める(read)」「書ける(write)」「意味が分かる(mean)」「聞いて分かる(listen)」を別々に持つ。だから『覚えた／覚えてない』の○×ではなく、面ごとの“濃淡”で測れる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="83" t="inlineStr">
-        <is>
-          <t>■ IDが実際に動かしているもの（弱点ドリルは氷山の一角）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="89" t="inlineStr">
-        <is>
-          <t>動かすもの</t>
-        </is>
-      </c>
-      <c r="B29" s="89" t="inlineStr">
-        <is>
-          <t>中身</t>
-        </is>
-      </c>
-      <c r="C29" s="85" t="n"/>
-      <c r="D29" s="86" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="50" t="inlineStr">
-        <is>
-          <t>予想得点（合格ラインにどれだけ届いたか）</t>
-        </is>
-      </c>
-      <c r="B30" s="90" t="inlineStr">
-        <is>
-          <t>各文法点／語の習得を正答確率に変換し、本番の出題数で重み付けして180点満点で計算（selectors.ts・CLAUDE.md §4）</t>
-        </is>
-      </c>
-      <c r="C30" s="85" t="n"/>
-      <c r="D30" s="86" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="49" t="inlineStr">
-        <is>
-          <t>カバー率</t>
-        </is>
-      </c>
-      <c r="B31" s="88" t="inlineStr">
-        <is>
-          <t>レベル内の文法点のうち、grammar面が0.6以上の点の割合＝『文法をどれだけ広く覚えたか』</t>
-        </is>
-      </c>
-      <c r="C31" s="85" t="n"/>
-      <c r="D31" s="86" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="50" t="inlineStr">
-        <is>
-          <t>合格リングの中央％</t>
-        </is>
-      </c>
-      <c r="B32" s="90" t="inlineStr">
-        <is>
-          <t>予想得点と同じ配点で合格の可能性を示す</t>
-        </is>
-      </c>
-      <c r="C32" s="85" t="n"/>
-      <c r="D32" s="86" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="49" t="inlineStr">
-        <is>
-          <t>復習の出題選び</t>
-        </is>
-      </c>
-      <c r="B33" s="88" t="inlineStr">
-        <is>
-          <t>弱い／期限が来たIDを選び、そのID×面に合う“検証済みバンク問題”を出す（おすすめ・ホーム・書斎・AIコーチ・カード）</t>
-        </is>
-      </c>
-      <c r="C33" s="85" t="n"/>
-      <c r="D33" s="86" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="50" t="inlineStr">
-        <is>
-          <t>模試あとの弱点ドリル</t>
-        </is>
-      </c>
-      <c r="B34" s="90" t="inlineStr">
-        <is>
-          <t>間違えた問題のIDを、上と同じ検証済みバンク経路で復習（今回、復習と同じプールに統一）</t>
-        </is>
-      </c>
-      <c r="C34" s="85" t="n"/>
-      <c r="D34" s="86" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="92" t="inlineStr">
-        <is>
-          <t>だから CLAUDE.md §4 は「pointId の貼り直し(正解=pointID)は予想得点・カバー率を正確化する」と言う。IDが習得の受け皿だから、紐づけを間違えると別の場所に習得が貯まって数字が狂う、という意味。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B12:D12"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:I74"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="82" min="1" max="1"/>
+    <col width="26" customWidth="1" style="82" min="1" max="1"/>
     <col width="20" customWidth="1" style="82" min="2" max="2"/>
-    <col width="11" customWidth="1" style="82" min="3" max="7"/>
-    <col width="60" customWidth="1" style="82" min="8" max="8"/>
+    <col width="20" customWidth="1" style="82" min="3" max="3"/>
+    <col width="16" customWidth="1" style="82" min="4" max="4"/>
+    <col width="22" customWidth="1" style="82" min="5" max="5"/>
+    <col width="16" customWidth="1" style="82" min="6" max="6"/>
+    <col width="14" customWidth="1" style="82" min="7" max="7"/>
+    <col width="12" customWidth="1" style="82" min="8" max="8"/>
+    <col width="10" customWidth="1" style="82" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="59" t="inlineStr">
-        <is>
-          <t>学習ドリル×カバー率（学習タブ・各ドリルがID紐づけで対象にできる項目の広さ）</t>
+      <c r="A1" s="112" t="inlineStr">
+        <is>
+          <t>アプリ全体の翻訳状況  (2026-08-29 / v1.1.24 build2884 時点)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>※全ID母数=レベル内の全項目(語彙数/文法点数[n5-g-92除外]/漢字数)。真の母数=そのドリルで「そもそも作れる」項目数(カタカナ語・分離型文法など"永久に不可能"を除く)＝真のカバー率が実力。試験タブの大問は別シート「単語×大問カバー率」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="59" t="inlineStr">
-        <is>
-          <t>■ N5</t>
+      <c r="A2" s="113" t="inlineStr">
+        <is>
+          <t>フル対応＝日本語(ja)・英語(en)・ネパール語(ne) の3言語。残り7言語(bn/id/ko/my/th/vi/zh)はUIの約1/4のみで、辞書・問題は未着手（＝指示が来たら一括翻訳する『バックログ』運用）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="113" t="inlineStr">
+        <is>
+          <t>問題文そのものは日本語（JLPTは日本語の試験のため）。翻訳されるのは①読解の本文 ②一部の文字・語彙問題の解説 ③辞書の意味・例文。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="64" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B5" s="64" t="inlineStr">
+      <c r="A5" s="114" t="inlineStr">
+        <is>
+          <t>① 表示言語 10種の対応ぐあい（ざっくり）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="116" t="inlineStr">
+        <is>
+          <t>言語</t>
+        </is>
+      </c>
+      <c r="B6" s="116" t="inlineStr">
+        <is>
+          <t>役割</t>
+        </is>
+      </c>
+      <c r="C6" s="116" t="inlineStr">
+        <is>
+          <t>UI(画面文字)</t>
+        </is>
+      </c>
+      <c r="D6" s="116" t="inlineStr">
+        <is>
+          <t>辞書の意味</t>
+        </is>
+      </c>
+      <c r="E6" s="116" t="inlineStr">
+        <is>
+          <t>例文</t>
+        </is>
+      </c>
+      <c r="F6" s="116" t="inlineStr">
+        <is>
+          <t>問題の翻訳</t>
+        </is>
+      </c>
+      <c r="G6" s="116" t="inlineStr">
+        <is>
+          <t>総合</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="117" t="inlineStr">
+        <is>
+          <t>ja（日本語）</t>
+        </is>
+      </c>
+      <c r="B7" s="118" t="inlineStr">
+        <is>
+          <t>元(すべての元)</t>
+        </is>
+      </c>
+      <c r="C7" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D7" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E7" s="120" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="F7" s="118" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G7" s="119" t="inlineStr">
+        <is>
+          <t>フル</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="117" t="inlineStr">
+        <is>
+          <t>en（英語）</t>
+        </is>
+      </c>
+      <c r="B8" s="118" t="inlineStr">
+        <is>
+          <t>表示言語(常時)</t>
+        </is>
+      </c>
+      <c r="C8" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D8" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E8" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F8" s="118" t="inlineStr">
+        <is>
+          <t>読解本文＋α</t>
+        </is>
+      </c>
+      <c r="G8" s="119" t="inlineStr">
+        <is>
+          <t>フル</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="117" t="inlineStr">
+        <is>
+          <t>ne（ネパール語）</t>
+        </is>
+      </c>
+      <c r="B9" s="118" t="inlineStr">
+        <is>
+          <t>母語＋表示言語</t>
+        </is>
+      </c>
+      <c r="C9" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D9" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E9" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F9" s="118" t="inlineStr">
+        <is>
+          <t>読解本文＋解説一部</t>
+        </is>
+      </c>
+      <c r="G9" s="119" t="inlineStr">
+        <is>
+          <t>フル</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="117" t="inlineStr">
+        <is>
+          <t>bn（ベンガル語）</t>
+        </is>
+      </c>
+      <c r="B10" s="118" t="inlineStr">
+        <is>
+          <t>母語</t>
+        </is>
+      </c>
+      <c r="C10" s="121" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="D10" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="120" t="inlineStr">
+        <is>
+          <t>UIの一部のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="117" t="inlineStr">
+        <is>
+          <t>id（インドネシア語）</t>
+        </is>
+      </c>
+      <c r="B11" s="118" t="inlineStr">
+        <is>
+          <t>母語</t>
+        </is>
+      </c>
+      <c r="C11" s="121" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="D11" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="120" t="inlineStr">
+        <is>
+          <t>UIの一部のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="117" t="inlineStr">
+        <is>
+          <t>ko（韓国語）</t>
+        </is>
+      </c>
+      <c r="B12" s="118" t="inlineStr">
+        <is>
+          <t>母語</t>
+        </is>
+      </c>
+      <c r="C12" s="121" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="D12" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="120" t="inlineStr">
+        <is>
+          <t>UIの一部のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="117" t="inlineStr">
+        <is>
+          <t>my（ミャンマー語）</t>
+        </is>
+      </c>
+      <c r="B13" s="118" t="inlineStr">
+        <is>
+          <t>母語</t>
+        </is>
+      </c>
+      <c r="C13" s="121" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="D13" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="120" t="inlineStr">
+        <is>
+          <t>UIの一部のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="117" t="inlineStr">
+        <is>
+          <t>th（タイ語）</t>
+        </is>
+      </c>
+      <c r="B14" s="118" t="inlineStr">
+        <is>
+          <t>母語</t>
+        </is>
+      </c>
+      <c r="C14" s="121" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="D14" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="120" t="inlineStr">
+        <is>
+          <t>UIの一部のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="117" t="inlineStr">
+        <is>
+          <t>vi（ベトナム語）</t>
+        </is>
+      </c>
+      <c r="B15" s="118" t="inlineStr">
+        <is>
+          <t>母語</t>
+        </is>
+      </c>
+      <c r="C15" s="121" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="D15" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="120" t="inlineStr">
+        <is>
+          <t>UIの一部のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="117" t="inlineStr">
+        <is>
+          <t>zh（中国語）</t>
+        </is>
+      </c>
+      <c r="B16" s="118" t="inlineStr">
+        <is>
+          <t>母語</t>
+        </is>
+      </c>
+      <c r="C16" s="121" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="D16" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="120" t="inlineStr">
+        <is>
+          <t>UIの一部のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="114" t="inlineStr">
+        <is>
+          <t>② UI（画面の文字）　ja=1396 キーが元</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="116" t="inlineStr">
+        <is>
+          <t>言語</t>
+        </is>
+      </c>
+      <c r="B19" s="116" t="inlineStr">
+        <is>
+          <t>訳済みキー数</t>
+        </is>
+      </c>
+      <c r="C19" s="116" t="inlineStr">
+        <is>
+          <t>総キー</t>
+        </is>
+      </c>
+      <c r="D19" s="116" t="inlineStr">
+        <is>
+          <t>カバー率</t>
+        </is>
+      </c>
+      <c r="E19" s="116" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="117" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="B20" s="119" t="n">
+        <v>1396</v>
+      </c>
+      <c r="C20" s="118" t="n">
+        <v>1396</v>
+      </c>
+      <c r="D20" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E20" s="118" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="117" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B21" s="119" t="n">
+        <v>1396</v>
+      </c>
+      <c r="C21" s="118" t="n">
+        <v>1396</v>
+      </c>
+      <c r="D21" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E21" s="118" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="117" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="B22" s="119" t="n">
+        <v>1396</v>
+      </c>
+      <c r="C22" s="118" t="n">
+        <v>1396</v>
+      </c>
+      <c r="D22" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E22" s="118" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="117" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="B23" s="121" t="n">
+        <v>315</v>
+      </c>
+      <c r="C23" s="118" t="n">
+        <v>1396</v>
+      </c>
+      <c r="D23" s="121" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="E23" s="118" t="inlineStr">
+        <is>
+          <t>バックログ(未訳はjaで表示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="117" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B24" s="121" t="n">
+        <v>315</v>
+      </c>
+      <c r="C24" s="118" t="n">
+        <v>1396</v>
+      </c>
+      <c r="D24" s="121" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="E24" s="118" t="inlineStr">
+        <is>
+          <t>バックログ(未訳はjaで表示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="117" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="B25" s="121" t="n">
+        <v>315</v>
+      </c>
+      <c r="C25" s="118" t="n">
+        <v>1396</v>
+      </c>
+      <c r="D25" s="121" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="E25" s="118" t="inlineStr">
+        <is>
+          <t>バックログ(未訳はjaで表示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="117" t="inlineStr">
+        <is>
+          <t>my</t>
+        </is>
+      </c>
+      <c r="B26" s="121" t="n">
+        <v>315</v>
+      </c>
+      <c r="C26" s="118" t="n">
+        <v>1396</v>
+      </c>
+      <c r="D26" s="121" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="E26" s="118" t="inlineStr">
+        <is>
+          <t>バックログ(未訳はjaで表示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="117" t="inlineStr">
+        <is>
+          <t>th</t>
+        </is>
+      </c>
+      <c r="B27" s="121" t="n">
+        <v>315</v>
+      </c>
+      <c r="C27" s="118" t="n">
+        <v>1396</v>
+      </c>
+      <c r="D27" s="121" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="E27" s="118" t="inlineStr">
+        <is>
+          <t>バックログ(未訳はjaで表示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="117" t="inlineStr">
+        <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="B28" s="121" t="n">
+        <v>315</v>
+      </c>
+      <c r="C28" s="118" t="n">
+        <v>1396</v>
+      </c>
+      <c r="D28" s="121" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="E28" s="118" t="inlineStr">
+        <is>
+          <t>バックログ(未訳はjaで表示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="117" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="B29" s="121" t="n">
+        <v>315</v>
+      </c>
+      <c r="C29" s="118" t="n">
+        <v>1396</v>
+      </c>
+      <c r="D29" s="121" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="E29" s="118" t="inlineStr">
+        <is>
+          <t>バックログ(未訳はjaで表示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="113" t="inlineStr">
+        <is>
+          <t>※ en/ne は新規UIを作るたび必ず同時に訳す運用（番人テスト parity.test.ts が欠落でビルドを止める）。他7言語は指示時のみ一括翻訳。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="114" t="inlineStr">
+        <is>
+          <t>③ 辞書（語彙・漢字・文法・例文）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="116" t="inlineStr">
+        <is>
+          <t>種類</t>
+        </is>
+      </c>
+      <c r="B33" s="116" t="inlineStr">
+        <is>
+          <t>総数</t>
+        </is>
+      </c>
+      <c r="C33" s="116" t="inlineStr">
+        <is>
+          <t>日本語(語/読み)</t>
+        </is>
+      </c>
+      <c r="D33" s="116" t="inlineStr">
+        <is>
+          <t>英語(意味)</t>
+        </is>
+      </c>
+      <c r="E33" s="116" t="inlineStr">
+        <is>
+          <t>ネパール語(意味)</t>
+        </is>
+      </c>
+      <c r="F33" s="116" t="inlineStr">
+        <is>
+          <t>他7言語</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="117" t="inlineStr">
+        <is>
+          <t>語彙（意味）</t>
+        </is>
+      </c>
+      <c r="B34" s="118" t="n">
+        <v>3540</v>
+      </c>
+      <c r="C34" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D34" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E34" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F34" s="120" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="117" t="inlineStr">
+        <is>
+          <t>漢字（意味・音訓）</t>
+        </is>
+      </c>
+      <c r="B35" s="118" t="n">
+        <v>612</v>
+      </c>
+      <c r="C35" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D35" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E35" s="119" t="inlineStr">
+        <is>
+          <t>100%（語義1182）</t>
+        </is>
+      </c>
+      <c r="F35" s="120" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="117" t="inlineStr">
+        <is>
+          <t>文法（意味・例文）</t>
+        </is>
+      </c>
+      <c r="B36" s="118" t="n">
+        <v>408</v>
+      </c>
+      <c r="C36" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D36" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E36" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F36" s="120" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="117" t="inlineStr">
+        <is>
+          <t>例文（辞書タブ）</t>
+        </is>
+      </c>
+      <c r="B37" s="118" t="n">
+        <v>3524</v>
+      </c>
+      <c r="C37" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D37" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E37" s="119" t="inlineStr">
+        <is>
+          <t>100%（3844）</t>
+        </is>
+      </c>
+      <c r="F37" s="120" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="113" t="inlineStr">
+        <is>
+          <t>※ 英語＝同梱データに最初から入っている意味。ネパール語＝配信(OTA)の上書き層 content/lexicon で全件対応済（meaning=4561件＝語彙+漢字+文法の全意味）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="114" t="inlineStr">
+        <is>
+          <t>④ 各大問（問題）の翻訳　※問題文は日本語。ここは『解説』や『読解本文』の翻訳の話</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="116" t="inlineStr">
+        <is>
+          <t>大問</t>
+        </is>
+      </c>
+      <c r="B41" s="116" t="inlineStr">
+        <is>
+          <t>問題数</t>
+        </is>
+      </c>
+      <c r="C41" s="116" t="inlineStr">
+        <is>
+          <t>翻訳の種類</t>
+        </is>
+      </c>
+      <c r="D41" s="116" t="inlineStr">
+        <is>
+          <t>英語(en)</t>
+        </is>
+      </c>
+      <c r="E41" s="116" t="inlineStr">
+        <is>
+          <t>ネパール語(ne)</t>
+        </is>
+      </c>
+      <c r="F41" s="116" t="inlineStr">
+        <is>
+          <t>他7言語</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="117" t="inlineStr">
+        <is>
+          <t>文字語彙・文脈規定</t>
+        </is>
+      </c>
+      <c r="B42" s="118" t="n">
+        <v>3464</v>
+      </c>
+      <c r="C42" s="118" t="inlineStr">
+        <is>
+          <t>解説の翻訳</t>
+        </is>
+      </c>
+      <c r="D42" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="121" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="F42" s="120" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="117" t="inlineStr">
+        <is>
+          <t>文字語彙・漢字読み</t>
+        </is>
+      </c>
+      <c r="B43" s="118" t="n">
+        <v>3204</v>
+      </c>
+      <c r="C43" s="118" t="inlineStr">
+        <is>
+          <t>翻訳なし（機械式・不要）</t>
+        </is>
+      </c>
+      <c r="D43" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　└ 漢字読み(模試プール)</t>
+        </is>
+      </c>
+      <c r="B44" s="118" t="n">
+        <v>274</v>
+      </c>
+      <c r="C44" s="118" t="inlineStr">
+        <is>
+          <t>翻訳なし（機械式・不要）</t>
+        </is>
+      </c>
+      <c r="D44" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="117" t="inlineStr">
+        <is>
+          <t>文字語彙・表記</t>
+        </is>
+      </c>
+      <c r="B45" s="118" t="n">
+        <v>3088</v>
+      </c>
+      <c r="C45" s="118" t="inlineStr">
+        <is>
+          <t>解説の翻訳</t>
+        </is>
+      </c>
+      <c r="D45" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="121" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="F45" s="120" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="117" t="inlineStr">
+        <is>
+          <t>文字語彙・言い換え</t>
+        </is>
+      </c>
+      <c r="B46" s="118" t="n">
+        <v>2255</v>
+      </c>
+      <c r="C46" s="118" t="inlineStr">
+        <is>
+          <t>解説の翻訳</t>
+        </is>
+      </c>
+      <c r="D46" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="121" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="F46" s="120" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="117" t="inlineStr">
+        <is>
+          <t>文字語彙・用法</t>
+        </is>
+      </c>
+      <c r="B47" s="118" t="n">
+        <v>1171</v>
+      </c>
+      <c r="C47" s="118" t="inlineStr">
+        <is>
+          <t>翻訳なし（機械式・不要）</t>
+        </is>
+      </c>
+      <c r="D47" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="117" t="inlineStr">
+        <is>
+          <t>文法・穴埋め</t>
+        </is>
+      </c>
+      <c r="B48" s="118" t="n">
+        <v>1020</v>
+      </c>
+      <c r="C48" s="118" t="inlineStr">
+        <is>
+          <t>翻訳なし（機械式・不要）</t>
+        </is>
+      </c>
+      <c r="D48" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="117" t="inlineStr">
+        <is>
+          <t>文法・並べ替え</t>
+        </is>
+      </c>
+      <c r="B49" s="118" t="n">
+        <v>673</v>
+      </c>
+      <c r="C49" s="118" t="inlineStr">
+        <is>
+          <t>解説の翻訳</t>
+        </is>
+      </c>
+      <c r="D49" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="121" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F49" s="120" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="117" t="inlineStr">
+        <is>
+          <t>文法・文章の文法</t>
+        </is>
+      </c>
+      <c r="B50" s="118" t="n">
+        <v>210</v>
+      </c>
+      <c r="C50" s="118" t="inlineStr">
+        <is>
+          <t>本文の対訳</t>
+        </is>
+      </c>
+      <c r="D50" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E50" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F50" s="120" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="117" t="inlineStr">
+        <is>
+          <t>読解・内容理解(短)</t>
+        </is>
+      </c>
+      <c r="B51" s="118" t="n">
+        <v>330</v>
+      </c>
+      <c r="C51" s="118" t="inlineStr">
+        <is>
+          <t>本文の対訳</t>
+        </is>
+      </c>
+      <c r="D51" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E51" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F51" s="120" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="117" t="inlineStr">
+        <is>
+          <t>読解・内容理解(中)</t>
+        </is>
+      </c>
+      <c r="B52" s="118" t="n">
+        <v>160</v>
+      </c>
+      <c r="C52" s="118" t="inlineStr">
+        <is>
+          <t>本文の対訳</t>
+        </is>
+      </c>
+      <c r="D52" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E52" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F52" s="120" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="117" t="inlineStr">
+        <is>
+          <t>読解・長文</t>
+        </is>
+      </c>
+      <c r="B53" s="118" t="n">
+        <v>40</v>
+      </c>
+      <c r="C53" s="118" t="inlineStr">
+        <is>
+          <t>本文の対訳</t>
+        </is>
+      </c>
+      <c r="D53" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E53" s="119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F53" s="120" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="117" t="inlineStr">
+        <is>
+          <t>読解・情報検索</t>
+        </is>
+      </c>
+      <c r="B54" s="118" t="n">
+        <v>180</v>
+      </c>
+      <c r="C54" s="118" t="inlineStr">
+        <is>
+          <t>翻訳なし（機械式・不要）</t>
+        </is>
+      </c>
+      <c r="D54" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="117" t="inlineStr">
+        <is>
+          <t>聴解・課題理解</t>
+        </is>
+      </c>
+      <c r="B55" s="118" t="n">
+        <v>450</v>
+      </c>
+      <c r="C55" s="118" t="inlineStr">
+        <is>
+          <t>音声台本(スクリプト)の訳</t>
+        </is>
+      </c>
+      <c r="D55" s="120" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E55" s="120" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="F55" s="120" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="117" t="inlineStr">
+        <is>
+          <t>聴解・ポイント理解</t>
+        </is>
+      </c>
+      <c r="B56" s="118" t="n">
+        <v>450</v>
+      </c>
+      <c r="C56" s="118" t="inlineStr">
+        <is>
+          <t>音声台本(スクリプト)の訳</t>
+        </is>
+      </c>
+      <c r="D56" s="120" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E56" s="120" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="F56" s="120" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="117" t="inlineStr">
+        <is>
+          <t>聴解・概要理解</t>
+        </is>
+      </c>
+      <c r="B57" s="118" t="n">
+        <v>80</v>
+      </c>
+      <c r="C57" s="118" t="inlineStr">
+        <is>
+          <t>音声台本(スクリプト)の訳</t>
+        </is>
+      </c>
+      <c r="D57" s="120" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E57" s="120" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="F57" s="120" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="117" t="inlineStr">
+        <is>
+          <t>聴解・発話表現</t>
+        </is>
+      </c>
+      <c r="B58" s="118" t="n">
+        <v>600</v>
+      </c>
+      <c r="C58" s="118" t="inlineStr">
+        <is>
+          <t>音声台本(スクリプト)の訳</t>
+        </is>
+      </c>
+      <c r="D58" s="120" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E58" s="120" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="F58" s="120" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="117" t="inlineStr">
+        <is>
+          <t>聴解・即時応答</t>
+        </is>
+      </c>
+      <c r="B59" s="118" t="n">
+        <v>720</v>
+      </c>
+      <c r="C59" s="118" t="inlineStr">
+        <is>
+          <t>音声台本(スクリプト)の訳</t>
+        </is>
+      </c>
+      <c r="D59" s="120" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E59" s="120" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="F59" s="120" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="113" t="inlineStr">
+        <is>
+          <t>※ 漢字読み・表記・言い換え・用法・穴埋めは、下線や選択肢だけで解けるため解説翻訳を付けていない。読解と一部の文脈問題だけ本文・解説を en/ne 化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="113" t="inlineStr">
+        <is>
+          <t>※ 聴解は「解説」ではなく『音声台本(スクリプト)の訳があるか』を記載。全大問=台本は日本語のみで、en/ne の対訳は0件（＝現状なし）。将来スクリプト対訳を付ける余地はデータ上あり。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="114" t="inlineStr">
+        <is>
+          <t>⑤ 各ドリル（単語タブの受容ドリル）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="116" t="inlineStr">
         <is>
           <t>ドリル</t>
         </is>
       </c>
-      <c r="C5" s="64" t="inlineStr">
-        <is>
-          <t>対象</t>
-        </is>
-      </c>
-      <c r="D5" s="64" t="inlineStr">
-        <is>
-          <t>全ID母数</t>
-        </is>
-      </c>
-      <c r="E5" s="64" t="inlineStr">
-        <is>
-          <t>全IDカバー率</t>
-        </is>
-      </c>
-      <c r="F5" s="64" t="inlineStr">
-        <is>
-          <t>真の母数</t>
-        </is>
-      </c>
-      <c r="G5" s="64" t="inlineStr">
-        <is>
-          <t>真のカバー率</t>
-        </is>
-      </c>
-      <c r="H5" s="64" t="inlineStr">
-        <is>
-          <t>点検メモ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="43.2" customHeight="1" s="82">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>語彙</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>語彙パズル(産出)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>606</v>
-      </c>
-      <c r="D6" t="n">
-        <v>723</v>
-      </c>
-      <c r="E6" s="62" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>606</v>
-      </c>
-      <c r="G6" s="62" t="inlineStr">
+      <c r="B64" s="116" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C64" s="116" t="inlineStr">
+        <is>
+          <t>翻訳の出どころ</t>
+        </is>
+      </c>
+      <c r="D64" s="116" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E64" s="116" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F64" s="116" t="inlineStr">
+        <is>
+          <t>他7言語</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="117" t="inlineStr">
+        <is>
+          <t>いみ(意味認識)</t>
+        </is>
+      </c>
+      <c r="B65" s="118" t="inlineStr">
+        <is>
+          <t>語→意味を4択</t>
+        </is>
+      </c>
+      <c r="C65" s="118" t="inlineStr">
+        <is>
+          <t>辞書の意味を流用</t>
+        </is>
+      </c>
+      <c r="D65" s="119" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H6" s="81" t="inlineStr">
-        <is>
-          <t>見かけ84%だが真の100%＝差16ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="43.2" customHeight="1" s="82">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>語彙</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>聞き取り(語彙)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>681</v>
-      </c>
-      <c r="D7" t="n">
-        <v>723</v>
-      </c>
-      <c r="E7" s="62" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>681</v>
-      </c>
-      <c r="G7" s="62" t="inlineStr">
+      <c r="E65" s="119" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H7" s="81" t="inlineStr">
-        <is>
-          <t>見かけ94%だが真の100%＝差6ptは"作れない天井"。読みを聞いて単語を選ぶ。非自立語(接辞/助詞)・波ダッシュ語のみ対象外。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>意味を選ぶ(受容)</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>91</v>
-      </c>
-      <c r="D8" t="n">
-        <v>91</v>
-      </c>
-      <c r="E8" s="62" t="inlineStr">
+      <c r="F65" s="120" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="117" t="inlineStr">
+        <is>
+          <t>よみ(読み認識)</t>
+        </is>
+      </c>
+      <c r="B66" s="118" t="inlineStr">
+        <is>
+          <t>語→読みを4択</t>
+        </is>
+      </c>
+      <c r="C66" s="118" t="inlineStr">
+        <is>
+          <t>日本語のみ(翻訳不要)</t>
+        </is>
+      </c>
+      <c r="D66" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="117" t="inlineStr">
+        <is>
+          <t>かたち(表記認識)</t>
+        </is>
+      </c>
+      <c r="B67" s="118" t="inlineStr">
+        <is>
+          <t>意味→漢字表記を4択</t>
+        </is>
+      </c>
+      <c r="C67" s="118" t="inlineStr">
+        <is>
+          <t>辞書の意味を流用</t>
+        </is>
+      </c>
+      <c r="D67" s="119" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>91</v>
-      </c>
-      <c r="G8" s="62" t="inlineStr">
+      <c r="E67" s="119" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H8" s="81" t="inlineStr">
-        <is>
-          <t>文法点の意味を4択。意味を持つ全点が対象。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="72" customHeight="1" s="82">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>文法パズル(産出)</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>67</v>
-      </c>
-      <c r="D9" t="n">
-        <v>91</v>
-      </c>
-      <c r="E9" s="65" t="inlineStr">
-        <is>
-          <t>74%</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>67</v>
-      </c>
-      <c r="G9" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="81" t="inlineStr">
-        <is>
-          <t>見かけ74%だが真の100%＝差26ptは"作れない天井"。例文の空所に文法語をタイルで作る。例文に表層形が一意に1回出る点のみ対象(0回/複数回は空所位置が曖昧で除外)＝構造的に低い。上げたい場合は例文を「表層形が1回だけ出る」形に整えるか、対象点の例文を追加する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="57.6" customHeight="1" s="82">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>意味を選ぶ(漢字)</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>77</v>
-      </c>
-      <c r="D10" t="n">
-        <v>79</v>
-      </c>
-      <c r="E10" s="62" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>77</v>
-      </c>
-      <c r="G10" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H10" s="81" t="inlineStr">
-        <is>
-          <t>見かけ97%だが真の100%＝差3ptは"作れない天井"。字→意味を4択(認識テスト)。意味が立つ字(訓読みあり or 単独語=meaningClear)だけが対象。校のような字は意味面を作れず対象外。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28.8" customHeight="1" s="82">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>読み(漢字)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>79</v>
-      </c>
-      <c r="D11" t="n">
-        <v>79</v>
-      </c>
-      <c r="E11" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>79</v>
-      </c>
-      <c r="G11" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="81" t="inlineStr">
-        <is>
-          <t>字→読みを4択(認識テスト)。全字が対象。訓読みを優先し送り仮名を補って提示(強→つよ（い）)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="57.6" customHeight="1" s="82">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>形の弁別(漢字)</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>62</v>
-      </c>
-      <c r="D12" t="n">
-        <v>79</v>
-      </c>
-      <c r="E12" s="65" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>62</v>
-      </c>
-      <c r="G12" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="81" t="inlineStr">
-        <is>
-          <t>見かけ78%だが真の100%＝差22ptは"作れない天井"。似た字4択→正しい字を選ぶ(形の弁別)。見た目が紛らわしい字が3つ揃う字(formMakeable)だけが対象。※書き取り(手書き産出)は練習ゆえ面に非計上。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28.8" customHeight="1" s="82">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>聞き取り(漢字)</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>79</v>
-      </c>
-      <c r="D13" t="n">
-        <v>79</v>
-      </c>
-      <c r="E13" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>79</v>
-      </c>
-      <c r="G13" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="81" t="inlineStr">
-        <is>
-          <t>読みを聞いて漢字を選ぶ。drillレップを持つ当該級の漢字が対象。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="59" t="inlineStr">
-        <is>
-          <t>■ N4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="64" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B16" s="64" t="inlineStr">
-        <is>
-          <t>ドリル</t>
-        </is>
-      </c>
-      <c r="C16" s="64" t="inlineStr">
-        <is>
-          <t>対象</t>
-        </is>
-      </c>
-      <c r="D16" s="64" t="inlineStr">
-        <is>
-          <t>全ID母数</t>
-        </is>
-      </c>
-      <c r="E16" s="64" t="inlineStr">
-        <is>
-          <t>全IDカバー率</t>
-        </is>
-      </c>
-      <c r="F16" s="64" t="inlineStr">
-        <is>
-          <t>真の母数</t>
-        </is>
-      </c>
-      <c r="G16" s="64" t="inlineStr">
-        <is>
-          <t>真のカバー率</t>
-        </is>
-      </c>
-      <c r="H16" s="64" t="inlineStr">
-        <is>
-          <t>点検メモ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="43.2" customHeight="1" s="82">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>語彙</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>語彙パズル(産出)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>576</v>
-      </c>
-      <c r="D17" t="n">
-        <v>673</v>
-      </c>
-      <c r="E17" s="62" t="inlineStr">
-        <is>
-          <t>86%</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>576</v>
-      </c>
-      <c r="G17" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="81" t="inlineStr">
-        <is>
-          <t>見かけ86%だが真の100%＝差14ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="43.2" customHeight="1" s="82">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>語彙</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>聞き取り(語彙)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>643</v>
-      </c>
-      <c r="D18" t="n">
-        <v>673</v>
-      </c>
-      <c r="E18" s="62" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>643</v>
-      </c>
-      <c r="G18" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="81" t="inlineStr">
-        <is>
-          <t>見かけ96%だが真の100%＝差4ptは"作れない天井"。読みを聞いて単語を選ぶ。非自立語(接辞/助詞)・波ダッシュ語のみ対象外。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>意味を選ぶ(受容)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>131</v>
-      </c>
-      <c r="D19" t="n">
-        <v>131</v>
-      </c>
-      <c r="E19" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>131</v>
-      </c>
-      <c r="G19" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="81" t="inlineStr">
-        <is>
-          <t>文法点の意味を4択。意味を持つ全点が対象。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="72" customHeight="1" s="82">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>文法パズル(産出)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>113</v>
-      </c>
-      <c r="D20" t="n">
-        <v>131</v>
-      </c>
-      <c r="E20" s="62" t="inlineStr">
-        <is>
-          <t>86%</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>114</v>
-      </c>
-      <c r="G20" s="62" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="H20" s="81" t="inlineStr">
-        <is>
-          <t>見かけ86%だが真の99%＝差13ptは"作れない天井"。例文の空所に文法語をタイルで作る。例文に表層形が一意に1回出る点のみ対象(0回/複数回は空所位置が曖昧で除外)＝構造的に低い。上げたい場合は例文を「表層形が1回だけ出る」形に整えるか、対象点の例文を追加する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="57.6" customHeight="1" s="82">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>意味を選ぶ(漢字)</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>141</v>
-      </c>
-      <c r="D21" t="n">
-        <v>166</v>
-      </c>
-      <c r="E21" s="62" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>141</v>
-      </c>
-      <c r="G21" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="81" t="inlineStr">
-        <is>
-          <t>見かけ85%だが真の100%＝差15ptは"作れない天井"。字→意味を4択(認識テスト)。意味が立つ字(訓読みあり or 単独語=meaningClear)だけが対象。校のような字は意味面を作れず対象外。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28.8" customHeight="1" s="82">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>読み(漢字)</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>166</v>
-      </c>
-      <c r="D22" t="n">
-        <v>166</v>
-      </c>
-      <c r="E22" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>166</v>
-      </c>
-      <c r="G22" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H22" s="81" t="inlineStr">
-        <is>
-          <t>字→読みを4択(認識テスト)。全字が対象。訓読みを優先し送り仮名を補って提示(強→つよ（い）)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="57.6" customHeight="1" s="82">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>形の弁別(漢字)</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>159</v>
-      </c>
-      <c r="D23" t="n">
-        <v>166</v>
-      </c>
-      <c r="E23" s="62" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>159</v>
-      </c>
-      <c r="G23" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="81" t="inlineStr">
-        <is>
-          <t>見かけ96%だが真の100%＝差4ptは"作れない天井"。似た字4択→正しい字を選ぶ(形の弁別)。見た目が紛らわしい字が3つ揃う字(formMakeable)だけが対象。※書き取り(手書き産出)は練習ゆえ面に非計上。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28.8" customHeight="1" s="82">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>聞き取り(漢字)</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>166</v>
-      </c>
-      <c r="D24" t="n">
-        <v>166</v>
-      </c>
-      <c r="E24" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>166</v>
-      </c>
-      <c r="G24" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="81" t="inlineStr">
-        <is>
-          <t>読みを聞いて漢字を選ぶ。drillレップを持つ当該級の漢字が対象。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="59" t="inlineStr">
-        <is>
-          <t>■ N3</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="64" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B27" s="64" t="inlineStr">
-        <is>
-          <t>ドリル</t>
-        </is>
-      </c>
-      <c r="C27" s="64" t="inlineStr">
-        <is>
-          <t>対象</t>
-        </is>
-      </c>
-      <c r="D27" s="64" t="inlineStr">
-        <is>
-          <t>全ID母数</t>
-        </is>
-      </c>
-      <c r="E27" s="64" t="inlineStr">
-        <is>
-          <t>全IDカバー率</t>
-        </is>
-      </c>
-      <c r="F27" s="64" t="inlineStr">
-        <is>
-          <t>真の母数</t>
-        </is>
-      </c>
-      <c r="G27" s="64" t="inlineStr">
-        <is>
-          <t>真のカバー率</t>
-        </is>
-      </c>
-      <c r="H27" s="64" t="inlineStr">
-        <is>
-          <t>点検メモ</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="43.2" customHeight="1" s="82">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>語彙</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>語彙パズル(産出)</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1963</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2145</v>
-      </c>
-      <c r="E28" s="62" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>1963</v>
-      </c>
-      <c r="G28" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="81" t="inlineStr">
-        <is>
-          <t>見かけ92%だが真の100%＝差8ptは"作れない天井"。かなタイルで単語を作る産出ドリル。カタカナ語・波ダッシュ語(～)・2〜6モーラ外の語は対象外ゆえ100%未満(欠落ではなく仕様)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28.8" customHeight="1" s="82">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>語彙</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>聞き取り(語彙)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>2143</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2145</v>
-      </c>
-      <c r="E29" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>2143</v>
-      </c>
-      <c r="G29" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H29" s="81" t="inlineStr">
-        <is>
-          <t>読みを聞いて単語を選ぶ。非自立語(接辞/助詞)・波ダッシュ語のみ対象外。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>意味を選ぶ(受容)</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>186</v>
-      </c>
-      <c r="D30" t="n">
-        <v>186</v>
-      </c>
-      <c r="E30" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>186</v>
-      </c>
-      <c r="G30" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="81" t="inlineStr">
-        <is>
-          <t>文法点の意味を4択。意味を持つ全点が対象。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="72" customHeight="1" s="82">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>文法パズル(産出)</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>167</v>
-      </c>
-      <c r="D31" t="n">
-        <v>186</v>
-      </c>
-      <c r="E31" s="62" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>169</v>
-      </c>
-      <c r="G31" s="62" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="H31" s="81" t="inlineStr">
-        <is>
-          <t>見かけ90%だが真の99%＝差9ptは"作れない天井"。例文の空所に文法語をタイルで作る。例文に表層形が一意に1回出る点のみ対象(0回/複数回は空所位置が曖昧で除外)＝構造的に低い。上げたい場合は例文を「表層形が1回だけ出る」形に整えるか、対象点の例文を追加する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="57.6" customHeight="1" s="82">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>意味を選ぶ(漢字)</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>311</v>
-      </c>
-      <c r="D32" t="n">
-        <v>367</v>
-      </c>
-      <c r="E32" s="62" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>311</v>
-      </c>
-      <c r="G32" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H32" s="81" t="inlineStr">
-        <is>
-          <t>見かけ85%だが真の100%＝差15ptは"作れない天井"。字→意味を4択(認識テスト)。意味が立つ字(訓読みあり or 単独語=meaningClear)だけが対象。校のような字は意味面を作れず対象外。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28.8" customHeight="1" s="82">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>読み(漢字)</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>367</v>
-      </c>
-      <c r="D33" t="n">
-        <v>367</v>
-      </c>
-      <c r="E33" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>367</v>
-      </c>
-      <c r="G33" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="81" t="inlineStr">
-        <is>
-          <t>字→読みを4択(認識テスト)。全字が対象。訓読みを優先し送り仮名を補って提示(強→つよ（い）)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="57.6" customHeight="1" s="82">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>形の弁別(漢字)</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>336</v>
-      </c>
-      <c r="D34" t="n">
-        <v>367</v>
-      </c>
-      <c r="E34" s="62" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>336</v>
-      </c>
-      <c r="G34" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H34" s="81" t="inlineStr">
-        <is>
-          <t>見かけ92%だが真の100%＝差8ptは"作れない天井"。似た字4択→正しい字を選ぶ(形の弁別)。見た目が紛らわしい字が3つ揃う字(formMakeable)だけが対象。※書き取り(手書き産出)は練習ゆえ面に非計上。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28.8" customHeight="1" s="82">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>漢字</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>聞き取り(漢字)</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>367</v>
-      </c>
-      <c r="D35" t="n">
-        <v>367</v>
-      </c>
-      <c r="E35" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>367</v>
-      </c>
-      <c r="G35" s="62" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H35" s="81" t="inlineStr">
-        <is>
-          <t>読みを聞いて漢字を選ぶ。drillレップを持つ当該級の漢字が対象。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>凡例：緑=問題なし(≥80%) ／ 黄=気になる(60-79%) ／ 赤=危険(&lt;60%)。カバー率が2つあるのは"天井"のあるドリル＝真のカバー率で判断。</t>
+      <c r="F67" s="120" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="117" t="inlineStr">
+        <is>
+          <t>産出パズル</t>
+        </is>
+      </c>
+      <c r="B68" s="118" t="inlineStr">
+        <is>
+          <t>例文の穴をタイルで組む</t>
+        </is>
+      </c>
+      <c r="C68" s="118" t="inlineStr">
+        <is>
+          <t>日本語のみ(翻訳不要)</t>
+        </is>
+      </c>
+      <c r="D68" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="113" t="inlineStr">
+        <is>
+          <t>※ ドリルは辞書データから自動生成。意味を見せる面は辞書の en/ne をそのまま使うので、辞書の翻訳率＝ドリルの翻訳率。専用の翻訳データは持たない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="114" t="inlineStr">
+        <is>
+          <t>まとめ</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="113" t="inlineStr">
+        <is>
+          <t>・完全対応は ja / en / ne の3言語。アプリのどこを開いても日本語・英語・ネパール語で読める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="113" t="inlineStr">
+        <is>
+          <t>・残り7言語(bn/id/ko/my/th/vi/zh)＝UIの約23%だけ。未訳部分は日本語で表示（フォールバック）。辞書・問題・例文は未着手。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="113" t="inlineStr">
+        <is>
+          <t>・7言語をフル対応にするなら、UIの残り約1081キー×7＋辞書の意味(語彙3540+漢字612+文法408)×7 の翻訳が必要（指示があれば一括で見積り→翻訳）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="16" customWidth="1" style="82" min="1" max="1"/>
-    <col width="12" customWidth="1" style="82" min="2" max="8"/>
-    <col width="66" customWidth="1" style="82" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="17.4" customHeight="1" s="82">
-      <c r="A1" s="60" t="inlineStr">
-        <is>
-          <t>用法(語の使い方) × 語彙idカバー×バランス</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="216" customHeight="1" s="82">
-      <c r="A3" s="51" t="inlineStr">
-        <is>
-          <t>最終目標＝可能な限り語彙をカバー(breadth%を100%へ)。番人=src/data/usageCoverage.test.ts が「①未紐づけ0(測定可能) ②大問内で1語1問まで(集中させず広く) ③カバー数は後退させない(ラチェット)」を担保。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="158.4" customHeight="1" s="82">
-      <c r="A4" s="51" t="inlineStr">
-        <is>
-          <t>級跨ぎ重複(同語をN4とN3の両大問で出題=冗長)＝0語。冗長は禁止せず記録のみ(復習として妥当な場合あり)＝新規作問は未カバー語を優先すると breadth が伸びる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="59" t="inlineStr">
-        <is>
-          <t>■ 級別サマリ</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="61" t="inlineStr">
-        <is>
-          <t>級</t>
-        </is>
-      </c>
-      <c r="B7" s="61" t="inlineStr">
-        <is>
-          <t>問題数</t>
-        </is>
-      </c>
-      <c r="C7" s="61" t="inlineStr">
-        <is>
-          <t>リンク</t>
-        </is>
-      </c>
-      <c r="D7" s="61" t="inlineStr">
-        <is>
-          <t>未紐づけ</t>
-        </is>
-      </c>
-      <c r="E7" s="61" t="inlineStr">
-        <is>
-          <t>カバー語</t>
-        </is>
-      </c>
-      <c r="F7" s="61" t="inlineStr">
-        <is>
-          <t>母数</t>
-        </is>
-      </c>
-      <c r="G7" s="61" t="inlineStr">
-        <is>
-          <t>breadth%</t>
-        </is>
-      </c>
-      <c r="H7" s="61" t="inlineStr">
-        <is>
-          <t>未カバー(backlog)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>571</v>
-      </c>
-      <c r="C8" t="n">
-        <v>571</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>573</v>
-      </c>
-      <c r="F8" t="n">
-        <v>673</v>
-      </c>
-      <c r="G8" s="62" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>100</v>
-      </c>
-      <c r="I8" s="51" t="inlineStr">
-        <is>
-          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=571</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>600</v>
-      </c>
-      <c r="C9" t="n">
-        <v>600</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>595</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2145</v>
-      </c>
-      <c r="G9" s="63" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1550</v>
-      </c>
-      <c r="I9" s="51" t="inlineStr">
-        <is>
-          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=595 / 下級流出=N5:3, N4:2</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A63:I63"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A72:I72"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② カバー率" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 品質・攻略耐性" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥ 翻訳状況" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解攻略耐性分析" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大問別まとめ'!$A$1:$L$1</definedName>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="37">
+  <fonts count="40">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -239,8 +240,17 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <color rgb="009C6500"/>
+    </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <color rgb="009C0006"/>
+    </font>
   </fonts>
-  <fills count="47">
+  <fills count="49">
     <fill>
       <patternFill/>
     </fill>
@@ -474,6 +484,16 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -604,7 +624,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -887,6 +907,12 @@
     <xf numFmtId="0" fontId="0" fillId="46" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="47" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="46" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="44" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="48" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2056,17 +2082,15 @@
         </is>
       </c>
       <c r="D16" s="98" t="n">
-        <v>211</v>
+        <v>398</v>
       </c>
       <c r="E16" s="98" t="inlineStr">
         <is>
           <t>×1</t>
         </is>
       </c>
-      <c r="F16" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F16" s="98" t="n">
+        <v>160</v>
       </c>
       <c r="G16" s="97" t="inlineStr"/>
       <c r="H16" s="98" t="inlineStr">
@@ -2077,12 +2101,12 @@
       <c r="I16" s="98" t="n">
         <v>16</v>
       </c>
-      <c r="J16" s="103" t="n">
-        <v>13</v>
+      <c r="J16" s="100" t="n">
+        <v>24</v>
       </c>
       <c r="K16" s="97" t="inlineStr">
         <is>
-          <t>3:210 / 4:1</t>
+          <t>3:397 / 4:1</t>
         </is>
       </c>
       <c r="L16" s="98" t="inlineStr">
@@ -2115,10 +2139,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F17" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F17" s="98" t="n">
+        <v>150</v>
       </c>
       <c r="G17" s="97" t="inlineStr"/>
       <c r="H17" s="98" t="inlineStr">
@@ -2167,10 +2189,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F18" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F18" s="98" t="n">
+        <v>130</v>
       </c>
       <c r="G18" s="97" t="inlineStr"/>
       <c r="H18" s="98" t="inlineStr">
@@ -3730,8 +3750,8 @@
           <t>文法</t>
         </is>
       </c>
-      <c r="B6" s="109" t="n">
-        <v>13</v>
+      <c r="B6" s="108" t="n">
+        <v>24</v>
       </c>
       <c r="C6" s="108" t="n">
         <v>24</v>
@@ -3807,8 +3827,8 @@
           <t>フル模試</t>
         </is>
       </c>
-      <c r="B12" s="103" t="n">
-        <v>13</v>
+      <c r="B12" s="100" t="n">
+        <v>21</v>
       </c>
       <c r="C12" s="100" t="n">
         <v>18</v>
@@ -11254,4 +11274,1212 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="82" min="1" max="1"/>
+    <col width="6" customWidth="1" style="82" min="2" max="2"/>
+    <col width="6" customWidth="1" style="82" min="3" max="3"/>
+    <col width="6" customWidth="1" style="82" min="4" max="4"/>
+    <col width="16" customWidth="1" style="82" min="5" max="5"/>
+    <col width="15" customWidth="1" style="82" min="6" max="6"/>
+    <col width="8" customWidth="1" style="82" min="7" max="7"/>
+    <col width="8" customWidth="1" style="82" min="8" max="8"/>
+    <col width="12" customWidth="1" style="82" min="9" max="9"/>
+    <col width="6" customWidth="1" style="82" min="10" max="10"/>
+    <col width="12" customWidth="1" style="82" min="11" max="11"/>
+    <col width="14" customWidth="1" style="82" min="12" max="12"/>
+    <col width="12" customWidth="1" style="82" min="13" max="13"/>
+    <col width="12" customWidth="1" style="82" min="14" max="14"/>
+    <col width="14" customWidth="1" style="82" min="15" max="15"/>
+    <col width="12" customWidth="1" style="82" min="16" max="16"/>
+    <col width="12" customWidth="1" style="82" min="17" max="17"/>
+    <col width="5" customWidth="1" style="82" min="18" max="18"/>
+    <col width="5" customWidth="1" style="82" min="19" max="19"/>
+    <col width="8" customWidth="1" style="82" min="20" max="20"/>
+    <col width="8" customWidth="1" style="82" min="21" max="21"/>
+    <col width="8" customWidth="1" style="82" min="22" max="22"/>
+    <col width="9" customWidth="1" style="82" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>聴解 攻略耐性・モーラ・ワンパターン 分析（2026-08-16 自動集計｜daimon_solvability.py）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>★セル色＝信号：緑=合格／黄=境界・注意／赤=要改善。しきい値＝最長≤基準+15・語彙マッチ≤基準+10・正誤差≤+1.0・設問テンプレ≤30%・台本/選択肢重複=0・帯外=0が理想・係/留守=0・(発話)依頼形≤35%/形分離≤65%・位置最大≤基準+7。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>本質3観点→ ①答えが本文/設問から予測できる ②誤答が弱い ③大問×レベル内でワンパターン/重複。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>語彙マッチ的中%=「本文と最も語が重なる選択肢」を選ぶと正解になる割合(基準=1/選択肢数)。高い=正解だけ本文語→聞かず語マッチで解ける(①②)。良い設計は正解を言い換え本文語は誤答へ罠として置く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>正解−誤答 本文一致差=正解の本文一致語数−誤答平均。+大=正解だけ本文語(①②)。最長を選ぶ的中=正解が最長選択肢の割合(②)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>選択肢方式「表示時ランダム」(課題/ポイント/概要=テキスト4択)はアプリが並べ替え→正解位置は無関係(正本①固定でOK)。「音声焼込み」(発話/即時)は位置固定→位置偏りが有効。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>台本重複/選択肢セット重複=同一大問×レベル内の近似(③)。設問テンプレ最大=同一設問文の最大シェア(③)。設計帯:課題/ポイント/概要/発話=公式中央値±20%、即時=公式実測再センタリング。既存問の帯外は帯導入前の据え置き。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="122" t="inlineStr">
+        <is>
+          <t>大問</t>
+        </is>
+      </c>
+      <c r="B8" s="122" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="C8" s="122" t="inlineStr">
+        <is>
+          <t>問題数</t>
+        </is>
+      </c>
+      <c r="D8" s="122" t="inlineStr">
+        <is>
+          <t>選択肢数</t>
+        </is>
+      </c>
+      <c r="E8" s="122" t="inlineStr">
+        <is>
+          <t>選択肢方式</t>
+        </is>
+      </c>
+      <c r="F8" s="122" t="inlineStr">
+        <is>
+          <t>台本モーラ min/中/max</t>
+        </is>
+      </c>
+      <c r="G8" s="122" t="inlineStr">
+        <is>
+          <t>設計帯</t>
+        </is>
+      </c>
+      <c r="H8" s="122" t="inlineStr">
+        <is>
+          <t>帯外 短/長</t>
+        </is>
+      </c>
+      <c r="I8" s="122" t="inlineStr">
+        <is>
+          <t>最長を選ぶ的中%</t>
+        </is>
+      </c>
+      <c r="J8" s="122" t="inlineStr">
+        <is>
+          <t>基準%</t>
+        </is>
+      </c>
+      <c r="K8" s="122" t="inlineStr">
+        <is>
+          <t>語彙マッチ的中%</t>
+        </is>
+      </c>
+      <c r="L8" s="122" t="inlineStr">
+        <is>
+          <t>正解−誤答 本文一致差</t>
+        </is>
+      </c>
+      <c r="M8" s="122" t="inlineStr">
+        <is>
+          <t>設問テンプレ最大%</t>
+        </is>
+      </c>
+      <c r="N8" s="122" t="inlineStr">
+        <is>
+          <t>台本重複(≥.60)</t>
+        </is>
+      </c>
+      <c r="O8" s="122" t="inlineStr">
+        <is>
+          <t>選択肢セット重複(≥.70)</t>
+        </is>
+      </c>
+      <c r="P8" s="122" t="inlineStr">
+        <is>
+          <t>正解位置(正本)</t>
+        </is>
+      </c>
+      <c r="Q8" s="122" t="inlineStr">
+        <is>
+          <t>位置最大%(有効時)</t>
+        </is>
+      </c>
+      <c r="R8" s="122" t="inlineStr">
+        <is>
+          <t>係</t>
+        </is>
+      </c>
+      <c r="S8" s="122" t="inlineStr">
+        <is>
+          <t>留守</t>
+        </is>
+      </c>
+      <c r="T8" s="122" t="inlineStr">
+        <is>
+          <t>依頼形%</t>
+        </is>
+      </c>
+      <c r="U8" s="122" t="inlineStr">
+        <is>
+          <t>形分離%</t>
+        </is>
+      </c>
+      <c r="V8" s="122" t="inlineStr">
+        <is>
+          <t>機能max%</t>
+        </is>
+      </c>
+      <c r="W8" s="122" t="inlineStr">
+        <is>
+          <t>弁別軸max%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>課題理解</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>150</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>表示時ランダム</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>183/306/384</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>258-386</t>
+        </is>
+      </c>
+      <c r="H9" s="123" t="inlineStr">
+        <is>
+          <t>19/0</t>
+        </is>
+      </c>
+      <c r="I9" s="124" t="n">
+        <v>36</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25</v>
+      </c>
+      <c r="K9" s="124" t="n">
+        <v>29</v>
+      </c>
+      <c r="L9" s="124" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" s="124" t="n">
+        <v>9</v>
+      </c>
+      <c r="N9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>150/0/0/0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>課題理解</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>150</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>表示時ランダム</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>163/241/311</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>209-313</t>
+        </is>
+      </c>
+      <c r="H10" s="123" t="inlineStr">
+        <is>
+          <t>20/0</t>
+        </is>
+      </c>
+      <c r="I10" s="124" t="n">
+        <v>34</v>
+      </c>
+      <c r="J10" t="n">
+        <v>25</v>
+      </c>
+      <c r="K10" s="124" t="n">
+        <v>19</v>
+      </c>
+      <c r="L10" s="124" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M10" s="124" t="n">
+        <v>8</v>
+      </c>
+      <c r="N10" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="125" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>150/0/0/0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R10" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>課題理解</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>150</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>表示時ランダム</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>73/115/154</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>105-157</t>
+        </is>
+      </c>
+      <c r="H11" s="123" t="inlineStr">
+        <is>
+          <t>18/0</t>
+        </is>
+      </c>
+      <c r="I11" s="124" t="n">
+        <v>38</v>
+      </c>
+      <c r="J11" t="n">
+        <v>25</v>
+      </c>
+      <c r="K11" s="124" t="n">
+        <v>13</v>
+      </c>
+      <c r="L11" s="124" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M11" s="124" t="n">
+        <v>16</v>
+      </c>
+      <c r="N11" s="125" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>150/0/0/0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R11" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ポイント理解</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>150</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>表示時ランダム</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>183/239/290</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>179-269</t>
+        </is>
+      </c>
+      <c r="H12" s="123" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="I12" s="123" t="n">
+        <v>45</v>
+      </c>
+      <c r="J12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K12" s="124" t="n">
+        <v>17</v>
+      </c>
+      <c r="L12" s="124" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M12" s="124" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="125" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>150/0/0/0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R12" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ポイント理解</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>150</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>表示時ランダム</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>124/196/263</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>175-263</t>
+        </is>
+      </c>
+      <c r="H13" s="123" t="inlineStr">
+        <is>
+          <t>21/0</t>
+        </is>
+      </c>
+      <c r="I13" s="124" t="n">
+        <v>20</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25</v>
+      </c>
+      <c r="K13" s="124" t="n">
+        <v>19</v>
+      </c>
+      <c r="L13" s="124" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M13" s="124" t="n">
+        <v>6</v>
+      </c>
+      <c r="N13" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>150/0/0/0</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R13" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ポイント理解</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>150</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>表示時ランダム</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>84/168/216</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>149-223</t>
+        </is>
+      </c>
+      <c r="H14" s="123" t="inlineStr">
+        <is>
+          <t>29/0</t>
+        </is>
+      </c>
+      <c r="I14" s="124" t="n">
+        <v>23</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K14" s="124" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" s="124" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M14" s="124" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>150/0/0/0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R14" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>概要理解</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>80</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>表示時ランダム</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>203/234/272</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>190-284</t>
+        </is>
+      </c>
+      <c r="H15" s="124" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="I15" s="124" t="n">
+        <v>18</v>
+      </c>
+      <c r="J15" t="n">
+        <v>25</v>
+      </c>
+      <c r="K15" s="124" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" s="124" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="M15" s="124" t="n">
+        <v>12</v>
+      </c>
+      <c r="N15" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>20/20/20/20</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R15" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>発話表現</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>200</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>音声焼込み(位置固定)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>29/40/47</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>27-41</t>
+        </is>
+      </c>
+      <c r="H16" s="123" t="inlineStr">
+        <is>
+          <t>0/71</t>
+        </is>
+      </c>
+      <c r="I16" s="124" t="n">
+        <v>28</v>
+      </c>
+      <c r="J16" t="n">
+        <v>33</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>60/74/66</t>
+        </is>
+      </c>
+      <c r="Q16" s="124" t="n">
+        <v>37</v>
+      </c>
+      <c r="R16" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="124" t="n">
+        <v>12</v>
+      </c>
+      <c r="U16" s="124" t="n">
+        <v>56</v>
+      </c>
+      <c r="V16" t="n">
+        <v>33</v>
+      </c>
+      <c r="W16" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>発話表現</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>200</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>音声焼込み(位置固定)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>24/38/47</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>20-30</t>
+        </is>
+      </c>
+      <c r="H17" s="123" t="inlineStr">
+        <is>
+          <t>0/183</t>
+        </is>
+      </c>
+      <c r="I17" s="124" t="n">
+        <v>28</v>
+      </c>
+      <c r="J17" t="n">
+        <v>33</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>58/74/68</t>
+        </is>
+      </c>
+      <c r="Q17" s="124" t="n">
+        <v>37</v>
+      </c>
+      <c r="R17" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="124" t="n">
+        <v>7</v>
+      </c>
+      <c r="U17" s="124" t="n">
+        <v>54</v>
+      </c>
+      <c r="V17" t="n">
+        <v>28</v>
+      </c>
+      <c r="W17" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>発話表現</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>200</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>音声焼込み(位置固定)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>24/36/47</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>20-30</t>
+        </is>
+      </c>
+      <c r="H18" s="123" t="inlineStr">
+        <is>
+          <t>0/168</t>
+        </is>
+      </c>
+      <c r="I18" s="124" t="n">
+        <v>32</v>
+      </c>
+      <c r="J18" t="n">
+        <v>33</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>59/77/64</t>
+        </is>
+      </c>
+      <c r="Q18" s="124" t="n">
+        <v>38</v>
+      </c>
+      <c r="R18" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="124" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="V18" t="n">
+        <v>26</v>
+      </c>
+      <c r="W18" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>240</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>音声焼込み(位置固定)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>13/26/46</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>18-32</t>
+        </is>
+      </c>
+      <c r="H19" s="123" t="inlineStr">
+        <is>
+          <t>5/2</t>
+        </is>
+      </c>
+      <c r="I19" s="124" t="n">
+        <v>46</v>
+      </c>
+      <c r="J19" t="n">
+        <v>33</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="125" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>94/74/72</t>
+        </is>
+      </c>
+      <c r="Q19" s="124" t="n">
+        <v>39</v>
+      </c>
+      <c r="R19" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>240</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>音声焼込み(位置固定)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>12/25/33</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>18-33</t>
+        </is>
+      </c>
+      <c r="H20" s="123" t="inlineStr">
+        <is>
+          <t>9/0</t>
+        </is>
+      </c>
+      <c r="I20" s="124" t="n">
+        <v>40</v>
+      </c>
+      <c r="J20" t="n">
+        <v>33</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>94/74/72</t>
+        </is>
+      </c>
+      <c r="Q20" s="124" t="n">
+        <v>39</v>
+      </c>
+      <c r="R20" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>240</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>音声焼込み(位置固定)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8/24/30</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>14-27</t>
+        </is>
+      </c>
+      <c r="H21" s="123" t="inlineStr">
+        <is>
+          <t>13/21</t>
+        </is>
+      </c>
+      <c r="I21" s="124" t="n">
+        <v>38</v>
+      </c>
+      <c r="J21" t="n">
+        <v>33</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="125" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>94/74/72</t>
+        </is>
+      </c>
+      <c r="Q21" s="124" t="n">
+        <v>39</v>
+      </c>
+      <c r="R21" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -1530,9 +1530,9 @@
       <c r="D5" s="98" t="n">
         <v>474</v>
       </c>
-      <c r="E5" s="98" t="inlineStr">
-        <is>
-          <t>×1</t>
+      <c r="E5" s="99" t="inlineStr">
+        <is>
+          <t>×3</t>
         </is>
       </c>
       <c r="F5" s="98" t="n">
@@ -2084,9 +2084,9 @@
       <c r="D16" s="98" t="n">
         <v>398</v>
       </c>
-      <c r="E16" s="98" t="inlineStr">
-        <is>
-          <t>×1</t>
+      <c r="E16" s="99" t="inlineStr">
+        <is>
+          <t>×4</t>
         </is>
       </c>
       <c r="F16" s="98" t="n">
@@ -2134,9 +2134,9 @@
       <c r="D17" s="98" t="n">
         <v>361</v>
       </c>
-      <c r="E17" s="98" t="inlineStr">
-        <is>
-          <t>×1</t>
+      <c r="E17" s="99" t="inlineStr">
+        <is>
+          <t>×3</t>
         </is>
       </c>
       <c r="F17" s="98" t="n">
@@ -2184,9 +2184,9 @@
       <c r="D18" s="98" t="n">
         <v>448</v>
       </c>
-      <c r="E18" s="98" t="inlineStr">
-        <is>
-          <t>×1</t>
+      <c r="E18" s="99" t="inlineStr">
+        <is>
+          <t>×2</t>
         </is>
       </c>
       <c r="F18" s="98" t="n">

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -2234,15 +2234,13 @@
       <c r="D19" s="98" t="n">
         <v>146</v>
       </c>
-      <c r="E19" s="98" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F19" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E19" s="99" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="F19" s="98" t="n">
+        <v>50</v>
       </c>
       <c r="G19" s="97" t="inlineStr"/>
       <c r="H19" s="98" t="inlineStr">
@@ -2286,15 +2284,13 @@
       <c r="D20" s="98" t="n">
         <v>216</v>
       </c>
-      <c r="E20" s="98" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F20" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E20" s="99" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="F20" s="98" t="n">
+        <v>50</v>
       </c>
       <c r="G20" s="97" t="inlineStr"/>
       <c r="H20" s="98" t="inlineStr">
@@ -2338,15 +2334,13 @@
       <c r="D21" s="98" t="n">
         <v>311</v>
       </c>
-      <c r="E21" s="98" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F21" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E21" s="99" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="F21" s="98" t="n">
+        <v>50</v>
       </c>
       <c r="G21" s="97" t="inlineStr"/>
       <c r="H21" s="98" t="inlineStr">
@@ -2390,15 +2384,13 @@
       <c r="D22" s="98" t="n">
         <v>400</v>
       </c>
-      <c r="E22" s="98" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F22" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E22" s="99" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="F22" s="98" t="n">
+        <v>50</v>
       </c>
       <c r="G22" s="97" t="inlineStr"/>
       <c r="H22" s="98" t="n">
@@ -2440,15 +2432,13 @@
       <c r="D23" s="98" t="n">
         <v>300</v>
       </c>
-      <c r="E23" s="98" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F23" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E23" s="99" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="F23" s="98" t="n">
+        <v>50</v>
       </c>
       <c r="G23" s="97" t="inlineStr"/>
       <c r="H23" s="98" t="n">
@@ -2490,15 +2480,13 @@
       <c r="D24" s="98" t="n">
         <v>350</v>
       </c>
-      <c r="E24" s="98" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F24" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E24" s="99" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="F24" s="98" t="n">
+        <v>50</v>
       </c>
       <c r="G24" s="97" t="inlineStr"/>
       <c r="H24" s="98" t="n">
@@ -11550,10 +11538,6 @@
       <c r="S9" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11629,10 +11613,6 @@
       <c r="S10" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11708,10 +11688,6 @@
       <c r="S11" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11787,10 +11763,6 @@
       <c r="S12" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11866,10 +11838,6 @@
       <c r="S13" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11945,10 +11913,6 @@
       <c r="S14" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12024,10 +11988,6 @@
       <c r="S15" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12072,9 +12032,6 @@
       <c r="J16" t="n">
         <v>33</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" s="124" t="n">
         <v>0</v>
       </c>
@@ -12151,9 +12108,6 @@
       <c r="J17" t="n">
         <v>33</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" s="124" t="n">
         <v>0</v>
       </c>
@@ -12230,9 +12184,6 @@
       <c r="J18" t="n">
         <v>33</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" s="124" t="n">
         <v>0</v>
       </c>
@@ -12309,9 +12260,6 @@
       <c r="J19" t="n">
         <v>33</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" s="124" t="n">
         <v>0</v>
       </c>
@@ -12332,10 +12280,6 @@
       <c r="S19" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -12380,9 +12324,6 @@
       <c r="J20" t="n">
         <v>33</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" s="124" t="n">
         <v>0</v>
       </c>
@@ -12403,10 +12344,6 @@
       <c r="S20" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12451,9 +12388,6 @@
       <c r="J21" t="n">
         <v>33</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" s="124" t="n">
         <v>0</v>
       </c>
@@ -12474,10 +12408,6 @@
       <c r="S21" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -2533,10 +2533,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F25" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F25" s="98" t="n">
+        <v>30</v>
       </c>
       <c r="G25" s="97" t="inlineStr"/>
       <c r="H25" s="98" t="n">
@@ -2583,10 +2581,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F26" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F26" s="98" t="n">
+        <v>40</v>
       </c>
       <c r="G26" s="97" t="inlineStr"/>
       <c r="H26" s="98" t="n">
@@ -2633,10 +2629,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F27" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F27" s="98" t="n">
+        <v>40</v>
       </c>
       <c r="G27" s="97" t="inlineStr"/>
       <c r="H27" s="98" t="n">
@@ -2683,10 +2677,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F28" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F28" s="98" t="n">
+        <v>20</v>
       </c>
       <c r="G28" s="97" t="inlineStr"/>
       <c r="H28" s="98" t="n">
@@ -2733,10 +2725,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F29" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F29" s="98" t="n">
+        <v>40</v>
       </c>
       <c r="G29" s="97" t="inlineStr"/>
       <c r="H29" s="98" t="n">
@@ -2783,10 +2773,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F30" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F30" s="98" t="n">
+        <v>60</v>
       </c>
       <c r="G30" s="97" t="inlineStr"/>
       <c r="H30" s="98" t="n">
@@ -2833,10 +2821,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F31" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F31" s="98" t="n">
+        <v>40</v>
       </c>
       <c r="G31" s="97" t="inlineStr"/>
       <c r="H31" s="98" t="n">
@@ -2883,10 +2869,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F32" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F32" s="98" t="n">
+        <v>10</v>
       </c>
       <c r="G32" s="97" t="inlineStr"/>
       <c r="H32" s="98" t="n">
@@ -2933,10 +2917,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F33" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F33" s="98" t="n">
+        <v>20</v>
       </c>
       <c r="G33" s="97" t="inlineStr"/>
       <c r="H33" s="98" t="n">
@@ -2983,10 +2965,8 @@
           <t>×1</t>
         </is>
       </c>
-      <c r="F34" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F34" s="98" t="n">
+        <v>20</v>
       </c>
       <c r="G34" s="97" t="inlineStr"/>
       <c r="H34" s="98" t="n">

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -10754,17 +10754,17 @@
       </c>
       <c r="D54" s="94" t="inlineStr">
         <is>
-          <t>音声台本(スクリプト)の訳</t>
+          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-02）</t>
         </is>
       </c>
       <c r="E54" s="110" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F54" s="110" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G54" s="109" t="inlineStr">
@@ -10940,7 +10940,7 @@
     <row r="61">
       <c r="A61" s="90" t="inlineStr">
         <is>
-          <t>※ 聴解は音声台本(スクリプト)の対訳の有無を記載。全大問=台本は日本語のみで en/ne 対訳は0件(現状なし)。</t>
+          <t>※ 聴解は音声台本(スクリプト)＋設問＋選択肢の対訳の有無を記載。課題理解=en/ne 100%完了(2026-09-02・660問・回答後表示)。他4大問(ポイント/概要/発話/即時)は未着手。</t>
         </is>
       </c>
     </row>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="32">
+  <fonts count="41">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -213,8 +213,49 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF808080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <color rgb="FF808080"/>
+    </font>
   </fonts>
-  <fills count="42">
+  <fills count="43">
     <fill>
       <patternFill/>
     </fill>
@@ -423,6 +464,11 @@
         <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -525,7 +571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -784,6 +830,129 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="42" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="42" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="32" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="42" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="42" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="32" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="42" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="32" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="42" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="32" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="42" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1167,62 +1336,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="50" t="inlineStr">
+      <c r="A1" s="155" t="inlineStr">
         <is>
           <t>セクション</t>
         </is>
       </c>
-      <c r="B1" s="50" t="inlineStr">
+      <c r="B1" s="155" t="inlineStr">
         <is>
           <t>大問</t>
         </is>
       </c>
-      <c r="C1" s="50" t="inlineStr">
+      <c r="C1" s="155" t="inlineStr">
         <is>
           <t>レベル</t>
         </is>
       </c>
-      <c r="D1" s="50" t="inlineStr">
+      <c r="D1" s="155" t="inlineStr">
         <is>
           <t>在庫問題数</t>
         </is>
       </c>
-      <c r="E1" s="50" t="inlineStr">
+      <c r="E1" s="155" t="inlineStr">
         <is>
           <t>割増し倍数</t>
         </is>
       </c>
-      <c r="F1" s="50" t="inlineStr">
+      <c r="F1" s="155" t="inlineStr">
         <is>
           <t>模試問題数</t>
         </is>
       </c>
-      <c r="G1" s="50" t="inlineStr">
+      <c r="G1" s="155" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
       </c>
-      <c r="H1" s="50" t="inlineStr">
+      <c r="H1" s="155" t="inlineStr">
         <is>
           <t>セット数</t>
         </is>
       </c>
-      <c r="I1" s="50" t="inlineStr">
+      <c r="I1" s="155" t="inlineStr">
         <is>
           <t>本番出題数</t>
         </is>
       </c>
-      <c r="J1" s="50" t="inlineStr">
+      <c r="J1" s="155" t="inlineStr">
         <is>
           <t>模試換算(何回分)</t>
         </is>
       </c>
-      <c r="K1" s="50" t="inlineStr">
+      <c r="K1" s="155" t="inlineStr">
         <is>
           <t>誤答数の内訳</t>
         </is>
       </c>
-      <c r="L1" s="50" t="inlineStr">
+      <c r="L1" s="155" t="inlineStr">
         <is>
           <t>シャッフル</t>
         </is>
@@ -3518,22 +3687,22 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="50" t="inlineStr">
+      <c r="A4" s="155" t="inlineStr">
         <is>
           <t>セクション</t>
         </is>
       </c>
-      <c r="B4" s="50" t="inlineStr">
+      <c r="B4" s="155" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="C4" s="50" t="inlineStr">
+      <c r="C4" s="155" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="D4" s="50" t="inlineStr">
+      <c r="D4" s="155" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -3611,22 +3780,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="50" t="inlineStr">
+      <c r="A11" s="155" t="inlineStr">
         <is>
           <t>セクション</t>
         </is>
       </c>
-      <c r="B11" s="50" t="inlineStr">
+      <c r="B11" s="155" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="C11" s="50" t="inlineStr">
+      <c r="C11" s="155" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="D11" s="50" t="inlineStr">
+      <c r="D11" s="155" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -3700,7 +3869,7 @@
       <c r="I3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="156" t="inlineStr">
         <is>
           <t>①単語マスタ数（学習項目）</t>
         </is>
@@ -3708,27 +3877,27 @@
       <c r="I4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="157" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="157" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="157" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="157" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="157" t="inlineStr">
         <is>
           <t>計</t>
         </is>
@@ -3796,7 +3965,7 @@
       <c r="I8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="156" t="inlineStr">
         <is>
           <t>②紐づく大問と問題数　総数 ／ verified在庫</t>
         </is>
@@ -3804,54 +3973,54 @@
       <c r="I9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="157" t="inlineStr">
         <is>
           <t>グループ</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="157" t="inlineStr">
         <is>
           <t>大問</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="157" t="inlineStr">
         <is>
           <t>N5 総数</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="157" t="inlineStr">
         <is>
           <t>N5 在庫</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="157" t="inlineStr">
         <is>
           <t>N4 総数</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="157" t="inlineStr">
         <is>
           <t>N4 在庫</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="157" t="inlineStr">
         <is>
           <t>N3 総数</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="157" t="inlineStr">
         <is>
           <t>N3 在庫</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="158" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="159" t="inlineStr">
         <is>
           <t>語彙</t>
         </is>
@@ -3942,7 +4111,7 @@
       <c r="I13" s="12" t="n"/>
     </row>
     <row r="14" ht="28.8" customHeight="1" s="75">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="159" t="inlineStr">
         <is>
           <t>文法</t>
         </is>
@@ -4043,26 +4212,26 @@
       <c r="I16" s="12" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="159" t="inlineStr">
         <is>
           <t>漢字</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="159" t="inlineStr">
         <is>
           <t>読み/意味/聞き取り/形＋書き(練習)</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="159" t="n">
         <v>79</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="159" t="n">
         <v>166</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="159" t="n">
         <v>367</v>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I17" s="159" t="inlineStr">
         <is>
           <t>漢字ID=字。面の内訳・字数は下の◆漢字面数分布を参照。書き取りは練習(面外)。</t>
         </is>
@@ -4103,42 +4272,42 @@
       <c r="G23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="160" t="inlineStr">
         <is>
           <t>単語種別</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="160" t="inlineStr">
         <is>
           <t>大問</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="160" t="inlineStr">
         <is>
           <t>問題数</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="160" t="inlineStr">
         <is>
           <t>カバー数</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="160" t="inlineStr">
         <is>
           <t>母数</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F24" s="160" t="inlineStr">
         <is>
           <t>カバー率</t>
         </is>
       </c>
-      <c r="G24" s="15" t="inlineStr">
+      <c r="G24" s="161" t="inlineStr">
         <is>
           <t>1単語が紐づく大問数の分布</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H24" s="162" t="inlineStr">
         <is>
           <t>点検メモ</t>
         </is>
@@ -4155,7 +4324,7 @@
       </c>
     </row>
     <row r="25" ht="28.8" customHeight="1" s="75">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="163" t="inlineStr">
         <is>
           <t>語彙単語(716)</t>
         </is>
@@ -4216,7 +4385,7 @@
       <c r="E27" s="9" t="n">
         <v>716</v>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="164" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -4305,7 +4474,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="163" t="inlineStr">
         <is>
           <t>文法単語(91)</t>
         </is>
@@ -4324,7 +4493,7 @@
       <c r="E30" s="9" t="n">
         <v>91</v>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="164" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -4380,7 +4549,7 @@
       <c r="E32" s="9" t="n">
         <v>91</v>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="164" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4404,42 +4573,42 @@
       <c r="G34" s="7" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="160" t="inlineStr">
         <is>
           <t>単語種別</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B35" s="160" t="inlineStr">
         <is>
           <t>大問</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="160" t="inlineStr">
         <is>
           <t>問題数</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D35" s="160" t="inlineStr">
         <is>
           <t>カバー数</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E35" s="160" t="inlineStr">
         <is>
           <t>母数</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="F35" s="160" t="inlineStr">
         <is>
           <t>カバー率</t>
         </is>
       </c>
-      <c r="G35" s="15" t="inlineStr">
+      <c r="G35" s="161" t="inlineStr">
         <is>
           <t>1単語が紐づく大問数の分布</t>
         </is>
       </c>
-      <c r="H35" s="16" t="inlineStr">
+      <c r="H35" s="162" t="inlineStr">
         <is>
           <t>点検メモ</t>
         </is>
@@ -4456,7 +4625,7 @@
       </c>
     </row>
     <row r="36" ht="28.8" customHeight="1" s="75">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="163" t="inlineStr">
         <is>
           <t>語彙単語(666)</t>
         </is>
@@ -4517,7 +4686,7 @@
       <c r="E38" s="9" t="n">
         <v>666</v>
       </c>
-      <c r="F38" s="21" t="inlineStr">
+      <c r="F38" s="164" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -4606,7 +4775,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="163" t="inlineStr">
         <is>
           <t>文法単語(131)</t>
         </is>
@@ -4625,7 +4794,7 @@
       <c r="E41" s="9" t="n">
         <v>131</v>
       </c>
-      <c r="F41" s="21" t="inlineStr">
+      <c r="F41" s="164" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -4653,7 +4822,7 @@
       <c r="E42" s="9" t="n">
         <v>131</v>
       </c>
-      <c r="F42" s="21" t="inlineStr">
+      <c r="F42" s="164" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -4677,7 +4846,7 @@
       <c r="E43" s="9" t="n">
         <v>131</v>
       </c>
-      <c r="F43" s="21" t="inlineStr">
+      <c r="F43" s="164" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4701,42 +4870,42 @@
       <c r="G45" s="7" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="A46" s="160" t="inlineStr">
         <is>
           <t>単語種別</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B46" s="160" t="inlineStr">
         <is>
           <t>大問</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C46" s="160" t="inlineStr">
         <is>
           <t>問題数</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D46" s="160" t="inlineStr">
         <is>
           <t>カバー数</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
+      <c r="E46" s="160" t="inlineStr">
         <is>
           <t>母数</t>
         </is>
       </c>
-      <c r="F46" s="14" t="inlineStr">
+      <c r="F46" s="160" t="inlineStr">
         <is>
           <t>カバー率</t>
         </is>
       </c>
-      <c r="G46" s="15" t="inlineStr">
+      <c r="G46" s="161" t="inlineStr">
         <is>
           <t>1単語が紐づく大問数の分布</t>
         </is>
       </c>
-      <c r="H46" s="16" t="inlineStr">
+      <c r="H46" s="162" t="inlineStr">
         <is>
           <t>点検メモ</t>
         </is>
@@ -4753,7 +4922,7 @@
       </c>
     </row>
     <row r="47" ht="28.8" customHeight="1" s="75">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A47" s="163" t="inlineStr">
         <is>
           <t>語彙単語(2145)</t>
         </is>
@@ -4814,7 +4983,7 @@
       <c r="E49" s="9" t="n">
         <v>2144</v>
       </c>
-      <c r="F49" s="21" t="inlineStr">
+      <c r="F49" s="164" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -4903,7 +5072,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="A52" s="163" t="inlineStr">
         <is>
           <t>文法単語(186)</t>
         </is>
@@ -4922,7 +5091,7 @@
       <c r="E52" s="9" t="n">
         <v>186</v>
       </c>
-      <c r="F52" s="21" t="inlineStr">
+      <c r="F52" s="164" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -4950,7 +5119,7 @@
       <c r="E53" s="9" t="n">
         <v>186</v>
       </c>
-      <c r="F53" s="21" t="inlineStr">
+      <c r="F53" s="164" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -4974,7 +5143,7 @@
       <c r="E54" s="9" t="n">
         <v>186</v>
       </c>
-      <c r="F54" s="21" t="inlineStr">
+      <c r="F54" s="164" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4990,7 +5159,7 @@
       <c r="G55" s="7" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="62" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
@@ -5004,7 +5173,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="156" t="inlineStr">
         <is>
           <t>学習ドリル×カバー率（学習タブ・各ドリルがID紐づけで対象にできる項目の広さ）</t>
         </is>
@@ -5018,49 +5187,49 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="156" t="inlineStr">
         <is>
           <t>■ N5</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="16" t="inlineStr">
+      <c r="A77" s="162" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B77" s="16" t="inlineStr">
+      <c r="B77" s="162" t="inlineStr">
         <is>
           <t>ドリル</t>
         </is>
       </c>
-      <c r="C77" s="16" t="inlineStr">
+      <c r="C77" s="162" t="inlineStr">
         <is>
           <t>対象</t>
         </is>
       </c>
-      <c r="D77" s="16" t="inlineStr">
+      <c r="D77" s="162" t="inlineStr">
         <is>
           <t>全ID母数</t>
         </is>
       </c>
-      <c r="E77" s="16" t="inlineStr">
+      <c r="E77" s="162" t="inlineStr">
         <is>
           <t>全IDカバー率</t>
         </is>
       </c>
-      <c r="F77" s="16" t="inlineStr">
+      <c r="F77" s="162" t="inlineStr">
         <is>
           <t>真の母数</t>
         </is>
       </c>
-      <c r="G77" s="16" t="inlineStr">
+      <c r="G77" s="162" t="inlineStr">
         <is>
           <t>真のカバー率</t>
         </is>
       </c>
-      <c r="H77" s="16" t="inlineStr">
+      <c r="H77" s="162" t="inlineStr">
         <is>
           <t>点検メモ</t>
         </is>
@@ -5083,7 +5252,7 @@
       <c r="D78" t="n">
         <v>723</v>
       </c>
-      <c r="E78" s="20" t="inlineStr">
+      <c r="E78" s="165" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -5091,7 +5260,7 @@
       <c r="F78" t="n">
         <v>705</v>
       </c>
-      <c r="G78" s="20" t="inlineStr">
+      <c r="G78" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5119,7 +5288,7 @@
       <c r="D79" t="n">
         <v>723</v>
       </c>
-      <c r="E79" s="20" t="inlineStr">
+      <c r="E79" s="165" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -5127,7 +5296,7 @@
       <c r="F79" t="n">
         <v>681</v>
       </c>
-      <c r="G79" s="20" t="inlineStr">
+      <c r="G79" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5155,7 +5324,7 @@
       <c r="D80" t="n">
         <v>91</v>
       </c>
-      <c r="E80" s="20" t="inlineStr">
+      <c r="E80" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5163,7 +5332,7 @@
       <c r="F80" t="n">
         <v>91</v>
       </c>
-      <c r="G80" s="20" t="inlineStr">
+      <c r="G80" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5199,7 +5368,7 @@
       <c r="F81" t="n">
         <v>67</v>
       </c>
-      <c r="G81" s="20" t="inlineStr">
+      <c r="G81" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5227,7 +5396,7 @@
       <c r="D82" t="n">
         <v>79</v>
       </c>
-      <c r="E82" s="20" t="inlineStr">
+      <c r="E82" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5235,7 +5404,7 @@
       <c r="F82" t="n">
         <v>79</v>
       </c>
-      <c r="G82" s="20" t="inlineStr">
+      <c r="G82" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5247,49 +5416,49 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="156" t="inlineStr">
         <is>
           <t>■ N4</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="inlineStr">
+      <c r="A85" s="162" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B85" s="16" t="inlineStr">
+      <c r="B85" s="162" t="inlineStr">
         <is>
           <t>ドリル</t>
         </is>
       </c>
-      <c r="C85" s="16" t="inlineStr">
+      <c r="C85" s="162" t="inlineStr">
         <is>
           <t>対象</t>
         </is>
       </c>
-      <c r="D85" s="16" t="inlineStr">
+      <c r="D85" s="162" t="inlineStr">
         <is>
           <t>全ID母数</t>
         </is>
       </c>
-      <c r="E85" s="16" t="inlineStr">
+      <c r="E85" s="162" t="inlineStr">
         <is>
           <t>全IDカバー率</t>
         </is>
       </c>
-      <c r="F85" s="16" t="inlineStr">
+      <c r="F85" s="162" t="inlineStr">
         <is>
           <t>真の母数</t>
         </is>
       </c>
-      <c r="G85" s="16" t="inlineStr">
+      <c r="G85" s="162" t="inlineStr">
         <is>
           <t>真のカバー率</t>
         </is>
       </c>
-      <c r="H85" s="16" t="inlineStr">
+      <c r="H85" s="162" t="inlineStr">
         <is>
           <t>点検メモ</t>
         </is>
@@ -5312,7 +5481,7 @@
       <c r="D86" t="n">
         <v>673</v>
       </c>
-      <c r="E86" s="20" t="inlineStr">
+      <c r="E86" s="165" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
@@ -5320,7 +5489,7 @@
       <c r="F86" t="n">
         <v>646</v>
       </c>
-      <c r="G86" s="20" t="inlineStr">
+      <c r="G86" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5348,7 +5517,7 @@
       <c r="D87" t="n">
         <v>673</v>
       </c>
-      <c r="E87" s="20" t="inlineStr">
+      <c r="E87" s="165" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
@@ -5356,7 +5525,7 @@
       <c r="F87" t="n">
         <v>643</v>
       </c>
-      <c r="G87" s="20" t="inlineStr">
+      <c r="G87" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5384,7 +5553,7 @@
       <c r="D88" t="n">
         <v>131</v>
       </c>
-      <c r="E88" s="20" t="inlineStr">
+      <c r="E88" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5392,7 +5561,7 @@
       <c r="F88" t="n">
         <v>131</v>
       </c>
-      <c r="G88" s="20" t="inlineStr">
+      <c r="G88" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5420,7 +5589,7 @@
       <c r="D89" t="n">
         <v>131</v>
       </c>
-      <c r="E89" s="20" t="inlineStr">
+      <c r="E89" s="165" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -5428,7 +5597,7 @@
       <c r="F89" t="n">
         <v>114</v>
       </c>
-      <c r="G89" s="20" t="inlineStr">
+      <c r="G89" s="165" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -5456,7 +5625,7 @@
       <c r="D90" t="n">
         <v>166</v>
       </c>
-      <c r="E90" s="20" t="inlineStr">
+      <c r="E90" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5464,7 +5633,7 @@
       <c r="F90" t="n">
         <v>166</v>
       </c>
-      <c r="G90" s="20" t="inlineStr">
+      <c r="G90" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5476,49 +5645,49 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" s="156" t="inlineStr">
         <is>
           <t>■ N3</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="16" t="inlineStr">
+      <c r="A93" s="162" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B93" s="16" t="inlineStr">
+      <c r="B93" s="162" t="inlineStr">
         <is>
           <t>ドリル</t>
         </is>
       </c>
-      <c r="C93" s="16" t="inlineStr">
+      <c r="C93" s="162" t="inlineStr">
         <is>
           <t>対象</t>
         </is>
       </c>
-      <c r="D93" s="16" t="inlineStr">
+      <c r="D93" s="162" t="inlineStr">
         <is>
           <t>全ID母数</t>
         </is>
       </c>
-      <c r="E93" s="16" t="inlineStr">
+      <c r="E93" s="162" t="inlineStr">
         <is>
           <t>全IDカバー率</t>
         </is>
       </c>
-      <c r="F93" s="16" t="inlineStr">
+      <c r="F93" s="162" t="inlineStr">
         <is>
           <t>真の母数</t>
         </is>
       </c>
-      <c r="G93" s="16" t="inlineStr">
+      <c r="G93" s="162" t="inlineStr">
         <is>
           <t>真のカバー率</t>
         </is>
       </c>
-      <c r="H93" s="16" t="inlineStr">
+      <c r="H93" s="162" t="inlineStr">
         <is>
           <t>点検メモ</t>
         </is>
@@ -5541,7 +5710,7 @@
       <c r="D94" t="n">
         <v>2144</v>
       </c>
-      <c r="E94" s="20" t="inlineStr">
+      <c r="E94" s="165" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -5549,7 +5718,7 @@
       <c r="F94" t="n">
         <v>2092</v>
       </c>
-      <c r="G94" s="20" t="inlineStr">
+      <c r="G94" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5577,7 +5746,7 @@
       <c r="D95" t="n">
         <v>2144</v>
       </c>
-      <c r="E95" s="20" t="inlineStr">
+      <c r="E95" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5585,7 +5754,7 @@
       <c r="F95" t="n">
         <v>2143</v>
       </c>
-      <c r="G95" s="20" t="inlineStr">
+      <c r="G95" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5613,7 +5782,7 @@
       <c r="D96" t="n">
         <v>186</v>
       </c>
-      <c r="E96" s="20" t="inlineStr">
+      <c r="E96" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5621,7 +5790,7 @@
       <c r="F96" t="n">
         <v>186</v>
       </c>
-      <c r="G96" s="20" t="inlineStr">
+      <c r="G96" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5649,7 +5818,7 @@
       <c r="D97" t="n">
         <v>186</v>
       </c>
-      <c r="E97" s="20" t="inlineStr">
+      <c r="E97" s="165" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -5657,7 +5826,7 @@
       <c r="F97" t="n">
         <v>169</v>
       </c>
-      <c r="G97" s="20" t="inlineStr">
+      <c r="G97" s="165" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -5685,7 +5854,7 @@
       <c r="D98" t="n">
         <v>367</v>
       </c>
-      <c r="E98" s="20" t="inlineStr">
+      <c r="E98" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5693,7 +5862,7 @@
       <c r="F98" t="n">
         <v>367</v>
       </c>
-      <c r="G98" s="20" t="inlineStr">
+      <c r="G98" s="165" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5726,37 +5895,37 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="26" t="inlineStr">
+      <c r="A106" s="166" t="inlineStr">
         <is>
           <t>面数</t>
         </is>
       </c>
-      <c r="B106" s="26" t="inlineStr">
+      <c r="B106" s="166" t="inlineStr">
         <is>
           <t>N5 語数</t>
         </is>
       </c>
-      <c r="C106" s="26" t="inlineStr">
+      <c r="C106" s="166" t="inlineStr">
         <is>
           <t>N4 語数</t>
         </is>
       </c>
-      <c r="D106" s="26" t="inlineStr">
+      <c r="D106" s="166" t="inlineStr">
         <is>
           <t>N3 語数</t>
         </is>
       </c>
-      <c r="E106" s="26" t="inlineStr">
+      <c r="E106" s="166" t="inlineStr">
         <is>
           <t>（参考）N5%</t>
         </is>
       </c>
-      <c r="F106" s="26" t="inlineStr">
+      <c r="F106" s="166" t="inlineStr">
         <is>
           <t>N4%</t>
         </is>
       </c>
-      <c r="G106" s="26" t="inlineStr">
+      <c r="G106" s="166" t="inlineStr">
         <is>
           <t>N3%</t>
         </is>
@@ -6104,31 +6273,31 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="28" t="inlineStr">
+      <c r="A118" s="167" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B118" s="28" t="n">
+      <c r="B118" s="167" t="n">
         <v>716</v>
       </c>
-      <c r="C118" s="28" t="n">
+      <c r="C118" s="167" t="n">
         <v>666</v>
       </c>
-      <c r="D118" s="28" t="n">
+      <c r="D118" s="167" t="n">
         <v>2144</v>
       </c>
-      <c r="E118" s="28" t="inlineStr">
+      <c r="E118" s="167" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F118" s="28" t="inlineStr">
+      <c r="F118" s="167" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G118" s="28" t="inlineStr">
+      <c r="G118" s="167" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6156,37 +6325,37 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="26" t="inlineStr">
+      <c r="A125" s="166" t="inlineStr">
         <is>
           <t>面数</t>
         </is>
       </c>
-      <c r="B125" s="26" t="inlineStr">
+      <c r="B125" s="166" t="inlineStr">
         <is>
           <t>N5 点数</t>
         </is>
       </c>
-      <c r="C125" s="26" t="inlineStr">
+      <c r="C125" s="166" t="inlineStr">
         <is>
           <t>N4 点数</t>
         </is>
       </c>
-      <c r="D125" s="26" t="inlineStr">
+      <c r="D125" s="166" t="inlineStr">
         <is>
           <t>N3 点数</t>
         </is>
       </c>
-      <c r="E125" s="26" t="inlineStr">
+      <c r="E125" s="166" t="inlineStr">
         <is>
           <t>（参考）N5%</t>
         </is>
       </c>
-      <c r="F125" s="26" t="inlineStr">
+      <c r="F125" s="166" t="inlineStr">
         <is>
           <t>N4%</t>
         </is>
       </c>
-      <c r="G125" s="26" t="inlineStr">
+      <c r="G125" s="166" t="inlineStr">
         <is>
           <t>N3%</t>
         </is>
@@ -6379,31 +6548,31 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="28" t="inlineStr">
+      <c r="A132" s="167" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B132" s="28" t="n">
+      <c r="B132" s="167" t="n">
         <v>90</v>
       </c>
-      <c r="C132" s="28" t="n">
+      <c r="C132" s="167" t="n">
         <v>131</v>
       </c>
-      <c r="D132" s="28" t="n">
+      <c r="D132" s="167" t="n">
         <v>186</v>
       </c>
-      <c r="E132" s="28" t="inlineStr">
+      <c r="E132" s="167" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F132" s="28" t="inlineStr">
+      <c r="F132" s="167" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G132" s="28" t="inlineStr">
+      <c r="G132" s="167" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6431,37 +6600,37 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="26" t="inlineStr">
+      <c r="A139" s="166" t="inlineStr">
         <is>
           <t>面数</t>
         </is>
       </c>
-      <c r="B139" s="26" t="inlineStr">
+      <c r="B139" s="166" t="inlineStr">
         <is>
           <t>N5 字数</t>
         </is>
       </c>
-      <c r="C139" s="26" t="inlineStr">
+      <c r="C139" s="166" t="inlineStr">
         <is>
           <t>N4 字数</t>
         </is>
       </c>
-      <c r="D139" s="26" t="inlineStr">
+      <c r="D139" s="166" t="inlineStr">
         <is>
           <t>N3 字数</t>
         </is>
       </c>
-      <c r="E139" s="26" t="inlineStr">
+      <c r="E139" s="166" t="inlineStr">
         <is>
           <t>（参考）N5%</t>
         </is>
       </c>
-      <c r="F139" s="26" t="inlineStr">
+      <c r="F139" s="166" t="inlineStr">
         <is>
           <t>N4%</t>
         </is>
       </c>
-      <c r="G139" s="26" t="inlineStr">
+      <c r="G139" s="166" t="inlineStr">
         <is>
           <t>N3%</t>
         </is>
@@ -6623,31 +6792,31 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="28" t="inlineStr">
+      <c r="A145" s="167" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B145" s="28" t="n">
+      <c r="B145" s="167" t="n">
         <v>79</v>
       </c>
-      <c r="C145" s="28" t="n">
+      <c r="C145" s="167" t="n">
         <v>166</v>
       </c>
-      <c r="D145" s="28" t="n">
+      <c r="D145" s="167" t="n">
         <v>367</v>
       </c>
-      <c r="E145" s="28" t="inlineStr">
+      <c r="E145" s="167" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F145" s="28" t="inlineStr">
+      <c r="F145" s="167" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G145" s="28" t="inlineStr">
+      <c r="G145" s="167" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6675,27 +6844,27 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="26" t="inlineStr">
+      <c r="A152" s="166" t="inlineStr">
         <is>
           <t>面（ドリル）</t>
         </is>
       </c>
-      <c r="B152" s="26" t="inlineStr">
+      <c r="B152" s="166" t="inlineStr">
         <is>
           <t>N5 字数</t>
         </is>
       </c>
-      <c r="C152" s="26" t="inlineStr">
+      <c r="C152" s="166" t="inlineStr">
         <is>
           <t>N4 字数</t>
         </is>
       </c>
-      <c r="D152" s="26" t="inlineStr">
+      <c r="D152" s="166" t="inlineStr">
         <is>
           <t>N3 字数</t>
         </is>
       </c>
-      <c r="E152" s="26" t="inlineStr">
+      <c r="E152" s="166" t="inlineStr">
         <is>
           <t>扱い</t>
         </is>
@@ -6868,84 +7037,84 @@
       </c>
     </row>
     <row r="4" ht="28.8" customHeight="1" s="75">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="168" t="inlineStr">
         <is>
           <t>①内容理解（短/中/長）　本体JSONの現在値（旧「現行」比較行は削除済み）</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28.8" customHeight="1" s="75">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="169" t="inlineStr">
         <is>
           <t>大問</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="169" t="inlineStr">
         <is>
           <t>級</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="169" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="D5" s="30" t="inlineStr">
+      <c r="D5" s="169" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="E5" s="30" t="inlineStr">
+      <c r="E5" s="169" t="inlineStr">
         <is>
           <t>設問</t>
         </is>
       </c>
-      <c r="F5" s="30" t="inlineStr">
+      <c r="F5" s="169" t="inlineStr">
         <is>
           <t>設問/本文(公式)</t>
         </is>
       </c>
-      <c r="G5" s="30" t="inlineStr">
+      <c r="G5" s="169" t="inlineStr">
         <is>
           <t>字数中央(最小/最大)</t>
         </is>
       </c>
-      <c r="H5" s="30" t="inlineStr">
+      <c r="H5" s="169" t="inlineStr">
         <is>
           <t>目標[許容]</t>
         </is>
       </c>
-      <c r="I5" s="30" t="inlineStr">
+      <c r="I5" s="169" t="inlineStr">
         <is>
           <t>帯外短/長</t>
         </is>
       </c>
-      <c r="J5" s="30" t="inlineStr">
+      <c r="J5" s="169" t="inlineStr">
         <is>
           <t>最長%(≤35)</t>
         </is>
       </c>
-      <c r="K5" s="30" t="inlineStr">
+      <c r="K5" s="169" t="inlineStr">
         <is>
           <t>丸写%</t>
         </is>
       </c>
-      <c r="L5" s="30" t="inlineStr">
+      <c r="L5" s="169" t="inlineStr">
         <is>
           <t>語彙%(≤45)</t>
         </is>
       </c>
-      <c r="M5" s="30" t="inlineStr">
+      <c r="M5" s="169" t="inlineStr">
         <is>
           <t>指示語本</t>
         </is>
       </c>
-      <c r="N5" s="30" t="inlineStr">
+      <c r="N5" s="169" t="inlineStr">
         <is>
           <t>指示語率</t>
         </is>
       </c>
-      <c r="O5" s="30" t="inlineStr">
+      <c r="O5" s="169" t="inlineStr">
         <is>
           <t>設問型</t>
         </is>
@@ -6988,22 +7157,22 @@
           <t>80[48-120]</t>
         </is>
       </c>
-      <c r="I6" s="32" t="inlineStr">
+      <c r="I6" s="170" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="J6" s="32" t="inlineStr">
+      <c r="J6" s="170" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="K6" s="32" t="inlineStr">
+      <c r="K6" s="170" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="L6" s="32" t="inlineStr">
+      <c r="L6" s="170" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
@@ -7066,17 +7235,17 @@
           <t>2/0</t>
         </is>
       </c>
-      <c r="J7" s="32" t="inlineStr">
+      <c r="J7" s="170" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="K7" s="32" t="inlineStr">
+      <c r="K7" s="170" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="L7" s="32" t="inlineStr">
+      <c r="L7" s="170" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -7134,22 +7303,22 @@
           <t>175[105-262]</t>
         </is>
       </c>
-      <c r="I8" s="32" t="inlineStr">
+      <c r="I8" s="170" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="J8" s="32" t="inlineStr">
+      <c r="J8" s="170" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K8" s="32" t="inlineStr">
+      <c r="K8" s="170" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="L8" s="32" t="inlineStr">
+      <c r="L8" s="170" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -7207,22 +7376,22 @@
           <t>250[150-375]</t>
         </is>
       </c>
-      <c r="I9" s="32" t="inlineStr">
+      <c r="I9" s="170" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="J9" s="32" t="inlineStr">
+      <c r="J9" s="170" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
       </c>
-      <c r="K9" s="32" t="inlineStr">
+      <c r="K9" s="170" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="L9" s="32" t="inlineStr">
+      <c r="L9" s="170" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -7280,22 +7449,22 @@
           <t>450[270-675]</t>
         </is>
       </c>
-      <c r="I10" s="32" t="inlineStr">
+      <c r="I10" s="170" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="J10" s="32" t="inlineStr">
+      <c r="J10" s="170" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="K10" s="32" t="inlineStr">
+      <c r="K10" s="170" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="L10" s="32" t="inlineStr">
+      <c r="L10" s="170" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -7353,22 +7522,22 @@
           <t>350[210-525]</t>
         </is>
       </c>
-      <c r="I11" s="32" t="inlineStr">
+      <c r="I11" s="170" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="J11" s="32" t="inlineStr">
+      <c r="J11" s="170" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="K11" s="32" t="inlineStr">
+      <c r="K11" s="170" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="L11" s="32" t="inlineStr">
+      <c r="L11" s="170" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -7426,22 +7595,22 @@
           <t>550[330-825]</t>
         </is>
       </c>
-      <c r="I12" s="32" t="inlineStr">
+      <c r="I12" s="170" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="J12" s="32" t="inlineStr">
+      <c r="J12" s="170" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="K12" s="32" t="inlineStr">
+      <c r="K12" s="170" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="L12" s="32" t="inlineStr">
+      <c r="L12" s="170" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -7463,54 +7632,54 @@
       </c>
     </row>
     <row r="14" ht="273.6" customHeight="1" s="75">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="171" t="inlineStr">
         <is>
           <t>②情報検索（図版込み・掲示物1枚＝1問）　実効字数＝ルビ除き本文＋図版の全文字（目標±15%）。figure比率＝全文字に占める図版の割合／図版依存%＝答えの根拠が図版側にある設問の割合／本文自足%＝本文だけで解ける設問の割合（低いほど図版を走査させる＝良い）。J列＝場面（全8種）の出題内訳%。走査S＝正解に必要な参照箇所（表/注記/カード）が何か所か＝多いほど掲示物全体を見る必要。走査C＝誘惑肢＝図版に実在して正解に見える紛らわしい選択肢（「選ぶ」型で必須。金額/時刻等は計算や言い換えの誘惑肢のため別枠）。全体走査＝正解に必要な情報源数(answer_sources)の分布（1源/2源/3源の問題数）。表の最有力行が罠で決め手が注記/別表/条件にあり、源数が多いほど掲示物の複数箇所を突き合わせないと解けない＝走査が重い。N5は走査S/Cのハード判定は対象外（易しく）だが数値は参考表示。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="57.6" customHeight="1" s="75">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="169" t="inlineStr">
         <is>
           <t>級</t>
         </is>
       </c>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B15" s="169" t="inlineStr">
         <is>
           <t>掲示</t>
         </is>
       </c>
-      <c r="C15" s="30" t="inlineStr">
+      <c r="C15" s="169" t="inlineStr">
         <is>
           <t>設問</t>
         </is>
       </c>
-      <c r="D15" s="30" t="inlineStr">
+      <c r="D15" s="169" t="inlineStr">
         <is>
           <t>実効字数中央(最小/最大)</t>
         </is>
       </c>
-      <c r="E15" s="30" t="inlineStr">
+      <c r="E15" s="169" t="inlineStr">
         <is>
           <t>目標[許容]</t>
         </is>
       </c>
-      <c r="F15" s="30" t="inlineStr">
+      <c r="F15" s="169" t="inlineStr">
         <is>
           <t>帯外短/長</t>
         </is>
       </c>
-      <c r="G15" s="30" t="inlineStr">
+      <c r="G15" s="169" t="inlineStr">
         <is>
           <t>figure比率</t>
         </is>
       </c>
-      <c r="H15" s="30" t="inlineStr">
+      <c r="H15" s="169" t="inlineStr">
         <is>
           <t>図版依存%</t>
         </is>
       </c>
-      <c r="I15" s="30" t="inlineStr">
+      <c r="I15" s="169" t="inlineStr">
         <is>
           <t>本文自足%</t>
         </is>
@@ -7548,7 +7717,7 @@
       <c r="C16" s="36" t="n">
         <v>60</v>
       </c>
-      <c r="D16" s="32" t="inlineStr">
+      <c r="D16" s="170" t="inlineStr">
         <is>
           <t>271(204/313)</t>
         </is>
@@ -7558,7 +7727,7 @@
           <t>250[200-375]</t>
         </is>
       </c>
-      <c r="F16" s="32" t="inlineStr">
+      <c r="F16" s="170" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
@@ -7573,27 +7742,27 @@
           <t>71%</t>
         </is>
       </c>
-      <c r="I16" s="32" t="inlineStr">
+      <c r="I16" s="170" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="J16" s="37" t="inlineStr">
+      <c r="J16" s="172" t="inlineStr">
         <is>
           <t>習い事13% ／ ツアー見学15% ／ 施設案内13% ／ カタログ12% ／ カレンダー回覧12% ／ イベント12% ／ 窓口受付12% ／ 募集12%</t>
         </is>
       </c>
-      <c r="K16" s="37" t="inlineStr">
+      <c r="K16" s="172" t="inlineStr">
         <is>
           <t>4源:9問／3源:1問／2源:24問／1源(密):26問（N5は走査ハード対象外＝参考値）</t>
         </is>
       </c>
-      <c r="L16" s="37" t="inlineStr">
+      <c r="L16" s="172" t="inlineStr">
         <is>
           <t>「選ぶ」型12問中 図版に実在する誘惑肢≥3＝8問（全型では24問が図版由来の紛らわしい肢）（N5は対象外）</t>
         </is>
       </c>
-      <c r="M16" s="37" t="inlineStr">
+      <c r="M16" s="172" t="inlineStr">
         <is>
           <t>1源=41問　2源=18問　3源=1問（正解に必要な情報源数。2源以上=19/60問=32%）</t>
         </is>
@@ -7611,7 +7780,7 @@
       <c r="C17" s="36" t="n">
         <v>60</v>
       </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="D17" s="170" t="inlineStr">
         <is>
           <t>386(341/459)</t>
         </is>
@@ -7621,7 +7790,7 @@
           <t>400[340-460]</t>
         </is>
       </c>
-      <c r="F17" s="32" t="inlineStr">
+      <c r="F17" s="170" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
@@ -7636,27 +7805,27 @@
           <t>68%</t>
         </is>
       </c>
-      <c r="I17" s="32" t="inlineStr">
+      <c r="I17" s="170" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J17" s="37" t="inlineStr">
+      <c r="J17" s="172" t="inlineStr">
         <is>
           <t>習い事13% ／ ツアー見学13% ／ 施設案内13% ／ カタログ13% ／ カレンダー回覧12% ／ イベント12% ／ 窓口受付12% ／ 募集12%</t>
         </is>
       </c>
-      <c r="K17" s="37" t="inlineStr">
+      <c r="K17" s="172" t="inlineStr">
         <is>
           <t>3源:22問／2源:38問／全60問が「表1行だけでは解けない」基準クリア</t>
         </is>
       </c>
-      <c r="L17" s="37" t="inlineStr">
+      <c r="L17" s="172" t="inlineStr">
         <is>
           <t>「選ぶ」型11問中 図版に実在する誘惑肢≥3＝11問（全型では24問が図版由来の紛らわしい肢）</t>
         </is>
       </c>
-      <c r="M17" s="37" t="inlineStr">
+      <c r="M17" s="172" t="inlineStr">
         <is>
           <t>1源=20問　2源=39問　3源=1問（正解に必要な情報源数。2源以上=40/60問=67%）</t>
         </is>
@@ -7674,7 +7843,7 @@
       <c r="C18" s="36" t="n">
         <v>60</v>
       </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="D18" s="170" t="inlineStr">
         <is>
           <t>550(516/679)</t>
         </is>
@@ -7684,7 +7853,7 @@
           <t>600[510-690]</t>
         </is>
       </c>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="F18" s="170" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
@@ -7699,27 +7868,27 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="I18" s="32" t="inlineStr">
+      <c r="I18" s="170" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="J18" s="37" t="inlineStr">
+      <c r="J18" s="172" t="inlineStr">
         <is>
           <t>習い事15% ／ ツアー見学12% ／ 施設案内13% ／ カタログ13% ／ カレンダー回覧12% ／ イベント12% ／ 窓口受付12% ／ 募集12%</t>
         </is>
       </c>
-      <c r="K18" s="37" t="inlineStr">
+      <c r="K18" s="172" t="inlineStr">
         <is>
           <t>4源:16問／3源:18問／2源:26問／全60問が「表1行だけでは解けない」基準クリア</t>
         </is>
       </c>
-      <c r="L18" s="37" t="inlineStr">
+      <c r="L18" s="172" t="inlineStr">
         <is>
           <t>「選ぶ」型11問中 図版に実在する誘惑肢≥3＝11問（全型では30問が図版由来の紛らわしい肢）</t>
         </is>
       </c>
-      <c r="M18" s="37" t="inlineStr">
+      <c r="M18" s="172" t="inlineStr">
         <is>
           <t>2源=30問　3源=30問（正解に必要な情報源数。2源以上=60/60問=100%）</t>
         </is>
@@ -7747,7 +7916,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="62" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
@@ -7789,57 +7958,57 @@
       </c>
     </row>
     <row r="44" ht="28.8" customHeight="1" s="75">
-      <c r="A44" s="39" t="inlineStr">
+      <c r="A44" s="70" t="inlineStr">
         <is>
           <t>大問</t>
         </is>
       </c>
-      <c r="B44" s="39" t="inlineStr">
+      <c r="B44" s="70" t="inlineStr">
         <is>
           <t>レベル</t>
         </is>
       </c>
-      <c r="C44" s="39" t="inlineStr">
+      <c r="C44" s="70" t="inlineStr">
         <is>
           <t>パラメータ</t>
         </is>
       </c>
-      <c r="D44" s="39" t="inlineStr">
+      <c r="D44" s="70" t="inlineStr">
         <is>
           <t>問題数</t>
         </is>
       </c>
-      <c r="E44" s="39" t="inlineStr">
+      <c r="E44" s="70" t="inlineStr">
         <is>
           <t>型の数</t>
         </is>
       </c>
-      <c r="F44" s="39" t="inlineStr">
+      <c r="F44" s="70" t="inlineStr">
         <is>
           <t>目安/型</t>
         </is>
       </c>
-      <c r="G44" s="39" t="inlineStr">
+      <c r="G44" s="70" t="inlineStr">
         <is>
           <t>最も多い型</t>
         </is>
       </c>
-      <c r="H44" s="39" t="inlineStr">
+      <c r="H44" s="70" t="inlineStr">
         <is>
           <t>最大%</t>
         </is>
       </c>
-      <c r="I44" s="39" t="inlineStr">
+      <c r="I44" s="70" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="J44" s="39" t="inlineStr">
+      <c r="J44" s="70" t="inlineStr">
         <is>
           <t>薄い型＝ここを増やして薄める</t>
         </is>
       </c>
-      <c r="K44" s="39" t="inlineStr">
+      <c r="K44" s="70" t="inlineStr">
         <is>
           <t>全分布</t>
         </is>
@@ -7875,12 +8044,12 @@
           <t>条件順序</t>
         </is>
       </c>
-      <c r="H45" s="20" t="inlineStr">
+      <c r="H45" s="165" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="I45" s="20" t="inlineStr">
+      <c r="I45" s="165" t="inlineStr">
         <is>
           <t>✅良好</t>
         </is>
@@ -7926,12 +8095,12 @@
           <t>消去</t>
         </is>
       </c>
-      <c r="H46" s="20" t="inlineStr">
+      <c r="H46" s="165" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="I46" s="20" t="inlineStr">
+      <c r="I46" s="165" t="inlineStr">
         <is>
           <t>✅良好</t>
         </is>
@@ -7977,12 +8146,12 @@
           <t>消去</t>
         </is>
       </c>
-      <c r="H47" s="20" t="inlineStr">
+      <c r="H47" s="165" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="I47" s="20" t="inlineStr">
+      <c r="I47" s="165" t="inlineStr">
         <is>
           <t>✅良好</t>
         </is>
@@ -8028,12 +8197,12 @@
           <t>いつ</t>
         </is>
       </c>
-      <c r="H48" s="20" t="inlineStr">
+      <c r="H48" s="165" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="I48" s="20" t="inlineStr">
+      <c r="I48" s="165" t="inlineStr">
         <is>
           <t>✅良好</t>
         </is>
@@ -8079,12 +8248,12 @@
           <t>どれ</t>
         </is>
       </c>
-      <c r="H49" s="20" t="inlineStr">
+      <c r="H49" s="165" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="I49" s="20" t="inlineStr">
+      <c r="I49" s="165" t="inlineStr">
         <is>
           <t>✅良好</t>
         </is>
@@ -8130,12 +8299,12 @@
           <t>なぜ</t>
         </is>
       </c>
-      <c r="H50" s="20" t="inlineStr">
+      <c r="H50" s="165" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="I50" s="20" t="inlineStr">
+      <c r="I50" s="165" t="inlineStr">
         <is>
           <t>✅良好</t>
         </is>
@@ -8181,12 +8350,12 @@
           <t>社会自然</t>
         </is>
       </c>
-      <c r="H51" s="20" t="inlineStr">
+      <c r="H51" s="165" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="I51" s="20" t="inlineStr">
+      <c r="I51" s="165" t="inlineStr">
         <is>
           <t>✅良好</t>
         </is>
@@ -8254,7 +8423,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="62" t="inlineStr">
         <is>
           <t>凡例：緑=問題なし ／ 黄=気になる ／ 赤=危険 ／ 灰=対象外・履歴</t>
         </is>
@@ -8317,117 +8486,117 @@
       </c>
     </row>
     <row r="77" ht="28.8" customHeight="1" s="75">
-      <c r="A77" s="39" t="inlineStr">
+      <c r="A77" s="70" t="inlineStr">
         <is>
           <t>大問</t>
         </is>
       </c>
-      <c r="B77" s="39" t="inlineStr">
+      <c r="B77" s="70" t="inlineStr">
         <is>
           <t>レベル</t>
         </is>
       </c>
-      <c r="C77" s="39" t="inlineStr">
+      <c r="C77" s="70" t="inlineStr">
         <is>
           <t>問題数</t>
         </is>
       </c>
-      <c r="D77" s="39" t="inlineStr">
+      <c r="D77" s="70" t="inlineStr">
         <is>
           <t>選択肢数</t>
         </is>
       </c>
-      <c r="E77" s="39" t="inlineStr">
+      <c r="E77" s="70" t="inlineStr">
         <is>
           <t>選択肢方式</t>
         </is>
       </c>
-      <c r="F77" s="39" t="inlineStr">
+      <c r="F77" s="70" t="inlineStr">
         <is>
           <t>台本モーラ min/中/max</t>
         </is>
       </c>
-      <c r="G77" s="39" t="inlineStr">
+      <c r="G77" s="70" t="inlineStr">
         <is>
           <t>設計帯</t>
         </is>
       </c>
-      <c r="H77" s="39" t="inlineStr">
+      <c r="H77" s="70" t="inlineStr">
         <is>
           <t>帯外 短/長</t>
         </is>
       </c>
-      <c r="I77" s="39" t="inlineStr">
+      <c r="I77" s="70" t="inlineStr">
         <is>
           <t>最長を選ぶ的中%</t>
         </is>
       </c>
-      <c r="J77" s="39" t="inlineStr">
+      <c r="J77" s="70" t="inlineStr">
         <is>
           <t>基準%</t>
         </is>
       </c>
-      <c r="K77" s="39" t="inlineStr">
+      <c r="K77" s="70" t="inlineStr">
         <is>
           <t>語彙マッチ的中%</t>
         </is>
       </c>
-      <c r="L77" s="39" t="inlineStr">
+      <c r="L77" s="70" t="inlineStr">
         <is>
           <t>正解−誤答 本文一致差</t>
         </is>
       </c>
-      <c r="M77" s="39" t="inlineStr">
+      <c r="M77" s="70" t="inlineStr">
         <is>
           <t>設問テンプレ最大%</t>
         </is>
       </c>
-      <c r="N77" s="39" t="inlineStr">
+      <c r="N77" s="70" t="inlineStr">
         <is>
           <t>台本重複(≥.60)</t>
         </is>
       </c>
-      <c r="O77" s="39" t="inlineStr">
+      <c r="O77" s="70" t="inlineStr">
         <is>
           <t>選択肢セット重複(≥.70)</t>
         </is>
       </c>
-      <c r="P77" s="39" t="inlineStr">
+      <c r="P77" s="70" t="inlineStr">
         <is>
           <t>正解位置(正本)</t>
         </is>
       </c>
-      <c r="Q77" s="39" t="inlineStr">
+      <c r="Q77" s="70" t="inlineStr">
         <is>
           <t>位置最大%(有効時)</t>
         </is>
       </c>
-      <c r="R77" s="39" t="inlineStr">
+      <c r="R77" s="70" t="inlineStr">
         <is>
           <t>係</t>
         </is>
       </c>
-      <c r="S77" s="39" t="inlineStr">
+      <c r="S77" s="70" t="inlineStr">
         <is>
           <t>留守</t>
         </is>
       </c>
-      <c r="T77" s="39" t="inlineStr">
+      <c r="T77" s="70" t="inlineStr">
         <is>
           <t>依頼形%</t>
         </is>
       </c>
-      <c r="U77" s="39" t="inlineStr">
+      <c r="U77" s="70" t="inlineStr">
         <is>
           <t>形分離%</t>
         </is>
       </c>
-      <c r="V77" s="39" t="inlineStr">
+      <c r="V77" s="70" t="inlineStr">
         <is>
           <t>機能max%</t>
         </is>
       </c>
-      <c r="W77" s="39" t="inlineStr">
+      <c r="W77" s="70" t="inlineStr">
         <is>
           <t>弁別軸max%</t>
         </is>
@@ -8465,30 +8634,30 @@
           <t>258-386</t>
         </is>
       </c>
-      <c r="H78" s="40" t="inlineStr">
+      <c r="H78" s="71" t="inlineStr">
         <is>
           <t>19/0</t>
         </is>
       </c>
-      <c r="I78" s="41" t="n">
+      <c r="I78" s="72" t="n">
         <v>36</v>
       </c>
       <c r="J78" t="n">
         <v>25</v>
       </c>
-      <c r="K78" s="41" t="n">
+      <c r="K78" s="72" t="n">
         <v>29</v>
       </c>
-      <c r="L78" s="41" t="n">
+      <c r="L78" s="72" t="n">
         <v>0.5</v>
       </c>
-      <c r="M78" s="41" t="n">
+      <c r="M78" s="72" t="n">
         <v>9</v>
       </c>
-      <c r="N78" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="41" t="n">
+      <c r="N78" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="72" t="n">
         <v>0</v>
       </c>
       <c r="P78" t="inlineStr">
@@ -8501,10 +8670,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R78" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="41" t="n">
+      <c r="R78" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8540,30 +8709,30 @@
           <t>209-313</t>
         </is>
       </c>
-      <c r="H79" s="40" t="inlineStr">
+      <c r="H79" s="71" t="inlineStr">
         <is>
           <t>20/0</t>
         </is>
       </c>
-      <c r="I79" s="41" t="n">
+      <c r="I79" s="72" t="n">
         <v>34</v>
       </c>
       <c r="J79" t="n">
         <v>25</v>
       </c>
-      <c r="K79" s="41" t="n">
+      <c r="K79" s="72" t="n">
         <v>19</v>
       </c>
-      <c r="L79" s="41" t="n">
+      <c r="L79" s="72" t="n">
         <v>0.3</v>
       </c>
-      <c r="M79" s="41" t="n">
+      <c r="M79" s="72" t="n">
         <v>8</v>
       </c>
-      <c r="N79" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="42" t="n">
+      <c r="N79" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="73" t="n">
         <v>2</v>
       </c>
       <c r="P79" t="inlineStr">
@@ -8576,10 +8745,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R79" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" s="41" t="n">
+      <c r="R79" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8615,30 +8784,30 @@
           <t>105-157</t>
         </is>
       </c>
-      <c r="H80" s="40" t="inlineStr">
+      <c r="H80" s="71" t="inlineStr">
         <is>
           <t>18/0</t>
         </is>
       </c>
-      <c r="I80" s="41" t="n">
+      <c r="I80" s="72" t="n">
         <v>38</v>
       </c>
       <c r="J80" t="n">
         <v>25</v>
       </c>
-      <c r="K80" s="41" t="n">
+      <c r="K80" s="72" t="n">
         <v>13</v>
       </c>
-      <c r="L80" s="41" t="n">
+      <c r="L80" s="72" t="n">
         <v>0.3</v>
       </c>
-      <c r="M80" s="41" t="n">
+      <c r="M80" s="72" t="n">
         <v>16</v>
       </c>
-      <c r="N80" s="42" t="n">
+      <c r="N80" s="73" t="n">
         <v>2</v>
       </c>
-      <c r="O80" s="41" t="n">
+      <c r="O80" s="72" t="n">
         <v>0</v>
       </c>
       <c r="P80" t="inlineStr">
@@ -8651,10 +8820,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R80" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" s="41" t="n">
+      <c r="R80" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8690,30 +8859,30 @@
           <t>179-269</t>
         </is>
       </c>
-      <c r="H81" s="40" t="inlineStr">
+      <c r="H81" s="71" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>
       </c>
-      <c r="I81" s="40" t="n">
+      <c r="I81" s="71" t="n">
         <v>45</v>
       </c>
       <c r="J81" t="n">
         <v>25</v>
       </c>
-      <c r="K81" s="41" t="n">
+      <c r="K81" s="72" t="n">
         <v>17</v>
       </c>
-      <c r="L81" s="41" t="n">
+      <c r="L81" s="72" t="n">
         <v>0.3</v>
       </c>
-      <c r="M81" s="41" t="n">
+      <c r="M81" s="72" t="n">
         <v>7</v>
       </c>
-      <c r="N81" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="42" t="n">
+      <c r="N81" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="73" t="n">
         <v>2</v>
       </c>
       <c r="P81" t="inlineStr">
@@ -8726,10 +8895,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R81" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" s="41" t="n">
+      <c r="R81" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8765,30 +8934,30 @@
           <t>175-263</t>
         </is>
       </c>
-      <c r="H82" s="40" t="inlineStr">
+      <c r="H82" s="71" t="inlineStr">
         <is>
           <t>21/0</t>
         </is>
       </c>
-      <c r="I82" s="41" t="n">
+      <c r="I82" s="72" t="n">
         <v>20</v>
       </c>
       <c r="J82" t="n">
         <v>25</v>
       </c>
-      <c r="K82" s="41" t="n">
+      <c r="K82" s="72" t="n">
         <v>19</v>
       </c>
-      <c r="L82" s="41" t="n">
+      <c r="L82" s="72" t="n">
         <v>0.1</v>
       </c>
-      <c r="M82" s="41" t="n">
+      <c r="M82" s="72" t="n">
         <v>6</v>
       </c>
-      <c r="N82" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="41" t="n">
+      <c r="N82" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="72" t="n">
         <v>0</v>
       </c>
       <c r="P82" t="inlineStr">
@@ -8801,10 +8970,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R82" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" s="41" t="n">
+      <c r="R82" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8840,30 +9009,30 @@
           <t>149-223</t>
         </is>
       </c>
-      <c r="H83" s="40" t="inlineStr">
+      <c r="H83" s="71" t="inlineStr">
         <is>
           <t>29/0</t>
         </is>
       </c>
-      <c r="I83" s="41" t="n">
+      <c r="I83" s="72" t="n">
         <v>23</v>
       </c>
       <c r="J83" t="n">
         <v>25</v>
       </c>
-      <c r="K83" s="41" t="n">
+      <c r="K83" s="72" t="n">
         <v>10</v>
       </c>
-      <c r="L83" s="41" t="n">
+      <c r="L83" s="72" t="n">
         <v>0.2</v>
       </c>
-      <c r="M83" s="41" t="n">
+      <c r="M83" s="72" t="n">
         <v>6</v>
       </c>
-      <c r="N83" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="41" t="n">
+      <c r="N83" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="72" t="n">
         <v>0</v>
       </c>
       <c r="P83" t="inlineStr">
@@ -8876,10 +9045,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R83" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" s="41" t="n">
+      <c r="R83" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8915,30 +9084,30 @@
           <t>190-284</t>
         </is>
       </c>
-      <c r="H84" s="41" t="inlineStr">
+      <c r="H84" s="72" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I84" s="41" t="n">
+      <c r="I84" s="72" t="n">
         <v>18</v>
       </c>
       <c r="J84" t="n">
         <v>25</v>
       </c>
-      <c r="K84" s="41" t="n">
+      <c r="K84" s="72" t="n">
         <v>10</v>
       </c>
-      <c r="L84" s="41" t="n">
+      <c r="L84" s="72" t="n">
         <v>-0.4</v>
       </c>
-      <c r="M84" s="41" t="n">
+      <c r="M84" s="72" t="n">
         <v>12</v>
       </c>
-      <c r="N84" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="41" t="n">
+      <c r="N84" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="72" t="n">
         <v>0</v>
       </c>
       <c r="P84" t="inlineStr">
@@ -8951,10 +9120,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R84" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" s="41" t="n">
+      <c r="R84" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8990,21 +9159,21 @@
           <t>27-41</t>
         </is>
       </c>
-      <c r="H85" s="40" t="inlineStr">
+      <c r="H85" s="71" t="inlineStr">
         <is>
           <t>0/71</t>
         </is>
       </c>
-      <c r="I85" s="41" t="n">
+      <c r="I85" s="72" t="n">
         <v>28</v>
       </c>
       <c r="J85" t="n">
         <v>33</v>
       </c>
-      <c r="N85" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="41" t="n">
+      <c r="N85" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="72" t="n">
         <v>0</v>
       </c>
       <c r="P85" t="inlineStr">
@@ -9012,19 +9181,19 @@
           <t>60/74/66</t>
         </is>
       </c>
-      <c r="Q85" s="41" t="n">
+      <c r="Q85" s="72" t="n">
         <v>37</v>
       </c>
-      <c r="R85" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" s="41" t="n">
+      <c r="R85" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" s="72" t="n">
         <v>12</v>
       </c>
-      <c r="U85" s="41" t="n">
+      <c r="U85" s="72" t="n">
         <v>56</v>
       </c>
       <c r="V85" t="n">
@@ -9066,21 +9235,21 @@
           <t>20-30</t>
         </is>
       </c>
-      <c r="H86" s="40" t="inlineStr">
+      <c r="H86" s="71" t="inlineStr">
         <is>
           <t>0/183</t>
         </is>
       </c>
-      <c r="I86" s="41" t="n">
+      <c r="I86" s="72" t="n">
         <v>28</v>
       </c>
       <c r="J86" t="n">
         <v>33</v>
       </c>
-      <c r="N86" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="41" t="n">
+      <c r="N86" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="72" t="n">
         <v>0</v>
       </c>
       <c r="P86" t="inlineStr">
@@ -9088,19 +9257,19 @@
           <t>58/74/68</t>
         </is>
       </c>
-      <c r="Q86" s="41" t="n">
+      <c r="Q86" s="72" t="n">
         <v>37</v>
       </c>
-      <c r="R86" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T86" s="41" t="n">
+      <c r="R86" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" s="72" t="n">
         <v>7</v>
       </c>
-      <c r="U86" s="41" t="n">
+      <c r="U86" s="72" t="n">
         <v>54</v>
       </c>
       <c r="V86" t="n">
@@ -9142,21 +9311,21 @@
           <t>20-30</t>
         </is>
       </c>
-      <c r="H87" s="40" t="inlineStr">
+      <c r="H87" s="71" t="inlineStr">
         <is>
           <t>0/168</t>
         </is>
       </c>
-      <c r="I87" s="41" t="n">
+      <c r="I87" s="72" t="n">
         <v>32</v>
       </c>
       <c r="J87" t="n">
         <v>33</v>
       </c>
-      <c r="N87" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="41" t="n">
+      <c r="N87" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="72" t="n">
         <v>0</v>
       </c>
       <c r="P87" t="inlineStr">
@@ -9164,19 +9333,19 @@
           <t>59/77/64</t>
         </is>
       </c>
-      <c r="Q87" s="41" t="n">
+      <c r="Q87" s="72" t="n">
         <v>38</v>
       </c>
-      <c r="R87" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" s="41" t="n">
+      <c r="R87" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" s="72" t="n">
         <v>6</v>
       </c>
-      <c r="U87" s="41" t="n">
+      <c r="U87" s="72" t="n">
         <v>50</v>
       </c>
       <c r="V87" t="n">
@@ -9218,21 +9387,21 @@
           <t>18-32</t>
         </is>
       </c>
-      <c r="H88" s="40" t="inlineStr">
+      <c r="H88" s="71" t="inlineStr">
         <is>
           <t>5/2</t>
         </is>
       </c>
-      <c r="I88" s="41" t="n">
+      <c r="I88" s="72" t="n">
         <v>46</v>
       </c>
       <c r="J88" t="n">
         <v>33</v>
       </c>
-      <c r="N88" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="42" t="n">
+      <c r="N88" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="73" t="n">
         <v>2</v>
       </c>
       <c r="P88" t="inlineStr">
@@ -9240,13 +9409,13 @@
           <t>94/74/72</t>
         </is>
       </c>
-      <c r="Q88" s="41" t="n">
+      <c r="Q88" s="72" t="n">
         <v>39</v>
       </c>
-      <c r="R88" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" s="41" t="n">
+      <c r="R88" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9282,21 +9451,21 @@
           <t>18-33</t>
         </is>
       </c>
-      <c r="H89" s="40" t="inlineStr">
+      <c r="H89" s="71" t="inlineStr">
         <is>
           <t>9/0</t>
         </is>
       </c>
-      <c r="I89" s="41" t="n">
+      <c r="I89" s="72" t="n">
         <v>40</v>
       </c>
       <c r="J89" t="n">
         <v>33</v>
       </c>
-      <c r="N89" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="41" t="n">
+      <c r="N89" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="72" t="n">
         <v>0</v>
       </c>
       <c r="P89" t="inlineStr">
@@ -9304,13 +9473,13 @@
           <t>94/74/72</t>
         </is>
       </c>
-      <c r="Q89" s="41" t="n">
+      <c r="Q89" s="72" t="n">
         <v>39</v>
       </c>
-      <c r="R89" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" s="41" t="n">
+      <c r="R89" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9346,21 +9515,21 @@
           <t>14-27</t>
         </is>
       </c>
-      <c r="H90" s="40" t="inlineStr">
+      <c r="H90" s="71" t="inlineStr">
         <is>
           <t>13/21</t>
         </is>
       </c>
-      <c r="I90" s="41" t="n">
+      <c r="I90" s="72" t="n">
         <v>38</v>
       </c>
       <c r="J90" t="n">
         <v>33</v>
       </c>
-      <c r="N90" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="42" t="n">
+      <c r="N90" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="73" t="n">
         <v>2</v>
       </c>
       <c r="P90" t="inlineStr">
@@ -9368,13 +9537,13 @@
           <t>94/74/72</t>
         </is>
       </c>
-      <c r="Q90" s="41" t="n">
+      <c r="Q90" s="72" t="n">
         <v>39</v>
       </c>
-      <c r="R90" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" s="41" t="n">
+      <c r="R90" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9396,16 +9565,16 @@
     <col width="20" customWidth="1" style="75" min="2" max="3"/>
     <col width="16" customWidth="1" style="75" min="4" max="4"/>
     <col width="22" customWidth="1" style="75" min="5" max="5"/>
-    <col width="16" customWidth="1" style="75" min="6" max="6"/>
-    <col width="14" customWidth="1" style="75" min="7" max="7"/>
-    <col width="12" customWidth="1" style="75" min="8" max="8"/>
+    <col width="15" customWidth="1" style="75" min="6" max="6"/>
+    <col width="15" customWidth="1" style="75" min="7" max="7"/>
+    <col width="24" customWidth="1" style="75" min="8" max="8"/>
     <col width="10" customWidth="1" style="75" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="75">
       <c r="A1" s="63" t="inlineStr">
         <is>
-          <t>アプリ全体の翻訳状況  (2026-09-02 時点)</t>
+          <t>アプリ全体の翻訳状況  (2026-09-03 時点)</t>
         </is>
       </c>
     </row>
@@ -9423,6 +9592,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="77" t="inlineStr">
         <is>
@@ -9458,10 +9628,15 @@
       </c>
       <c r="F6" s="64" t="inlineStr">
         <is>
-          <t>問題の翻訳</t>
+          <t>問題の翻訳（大問）</t>
         </is>
       </c>
       <c r="G6" s="64" t="inlineStr">
+        <is>
+          <t>問題の翻訳（ドリル）</t>
+        </is>
+      </c>
+      <c r="H6" s="64" t="inlineStr">
         <is>
           <t>総合</t>
         </is>
@@ -9478,27 +9653,32 @@
           <t>元(すべての元)</t>
         </is>
       </c>
-      <c r="C7" s="67" t="inlineStr">
+      <c r="C7" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D7" s="67" t="inlineStr">
+      <c r="D7" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E7" s="68" t="inlineStr">
+      <c r="E7" s="138" t="inlineStr">
         <is>
           <t>元</t>
         </is>
       </c>
-      <c r="F7" s="66" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G7" s="67" t="inlineStr">
+      <c r="F7" s="138" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="G7" s="138" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="H7" s="138" t="inlineStr">
         <is>
           <t>フル</t>
         </is>
@@ -9515,27 +9695,32 @@
           <t>表示言語(常時)</t>
         </is>
       </c>
-      <c r="C8" s="67" t="inlineStr">
+      <c r="C8" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D8" s="67" t="inlineStr">
+      <c r="D8" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E8" s="67" t="inlineStr">
+      <c r="E8" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F8" s="66" t="inlineStr">
-        <is>
-          <t>読解本文＋α</t>
-        </is>
-      </c>
-      <c r="G8" s="67" t="inlineStr">
+      <c r="F8" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G8" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="138" t="inlineStr">
         <is>
           <t>フル</t>
         </is>
@@ -9552,27 +9737,32 @@
           <t>母語＋表示言語</t>
         </is>
       </c>
-      <c r="C9" s="67" t="inlineStr">
+      <c r="C9" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D9" s="67" t="inlineStr">
+      <c r="D9" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E9" s="67" t="inlineStr">
+      <c r="E9" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F9" s="66" t="inlineStr">
-        <is>
-          <t>読解本文＋解説一部</t>
-        </is>
-      </c>
-      <c r="G9" s="67" t="inlineStr">
+      <c r="F9" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G9" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="138" t="inlineStr">
         <is>
           <t>フル</t>
         </is>
@@ -9589,27 +9779,32 @@
           <t>母語</t>
         </is>
       </c>
-      <c r="C10" s="67" t="inlineStr">
+      <c r="C10" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D10" s="68" t="inlineStr">
+      <c r="D10" s="139" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E10" s="68" t="inlineStr">
+      <c r="E10" s="139" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="68" t="inlineStr">
+      <c r="F10" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="G10" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H10" s="68" t="inlineStr">
         <is>
           <t>UI完全（辞書・問題は未）</t>
         </is>
@@ -9626,27 +9821,32 @@
           <t>母語</t>
         </is>
       </c>
-      <c r="C11" s="67" t="inlineStr">
+      <c r="C11" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D11" s="68" t="inlineStr">
+      <c r="D11" s="139" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="68" t="inlineStr">
+      <c r="E11" s="139" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="68" t="inlineStr">
+      <c r="F11" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="G11" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H11" s="68" t="inlineStr">
         <is>
           <t>UI完全（辞書・問題は未）</t>
         </is>
@@ -9663,27 +9863,32 @@
           <t>母語</t>
         </is>
       </c>
-      <c r="C12" s="67" t="inlineStr">
+      <c r="C12" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D12" s="68" t="inlineStr">
+      <c r="D12" s="139" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E12" s="68" t="inlineStr">
+      <c r="E12" s="139" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="68" t="inlineStr">
+      <c r="F12" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="G12" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H12" s="68" t="inlineStr">
         <is>
           <t>UI完全（辞書・問題は未）</t>
         </is>
@@ -9700,27 +9905,32 @@
           <t>母語</t>
         </is>
       </c>
-      <c r="C13" s="67" t="inlineStr">
+      <c r="C13" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D13" s="68" t="inlineStr">
+      <c r="D13" s="139" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="68" t="inlineStr">
+      <c r="E13" s="139" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="68" t="inlineStr">
+      <c r="F13" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="G13" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H13" s="68" t="inlineStr">
         <is>
           <t>UI完全（辞書・問題は未）</t>
         </is>
@@ -9737,27 +9947,32 @@
           <t>母語</t>
         </is>
       </c>
-      <c r="C14" s="67" t="inlineStr">
+      <c r="C14" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D14" s="68" t="inlineStr">
+      <c r="D14" s="139" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E14" s="68" t="inlineStr">
+      <c r="E14" s="139" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="68" t="inlineStr">
+      <c r="F14" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="G14" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H14" s="68" t="inlineStr">
         <is>
           <t>UI完全（辞書・問題は未）</t>
         </is>
@@ -9774,27 +9989,32 @@
           <t>母語</t>
         </is>
       </c>
-      <c r="C15" s="67" t="inlineStr">
+      <c r="C15" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D15" s="68" t="inlineStr">
+      <c r="D15" s="139" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="68" t="inlineStr">
+      <c r="E15" s="139" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="68" t="inlineStr">
+      <c r="F15" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="G15" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H15" s="68" t="inlineStr">
         <is>
           <t>UI完全（辞書・問題は未）</t>
         </is>
@@ -9811,32 +10031,38 @@
           <t>母語</t>
         </is>
       </c>
-      <c r="C16" s="67" t="inlineStr">
+      <c r="C16" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D16" s="68" t="inlineStr">
+      <c r="D16" s="139" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="68" t="inlineStr">
+      <c r="E16" s="139" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="68" t="inlineStr">
+      <c r="F16" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="G16" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H16" s="68" t="inlineStr">
         <is>
           <t>UI完全（辞書・問題は未）</t>
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="77" t="inlineStr">
         <is>
@@ -9883,12 +10109,12 @@
       <c r="C20" s="66" t="n">
         <v>1405</v>
       </c>
-      <c r="D20" s="67" t="inlineStr">
+      <c r="D20" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E20" s="66" t="inlineStr">
+      <c r="E20" s="138" t="inlineStr">
         <is>
           <t>元</t>
         </is>
@@ -9906,12 +10132,12 @@
       <c r="C21" s="66" t="n">
         <v>1405</v>
       </c>
-      <c r="D21" s="67" t="inlineStr">
+      <c r="D21" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E21" s="66" t="inlineStr">
+      <c r="E21" s="138" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
@@ -9929,12 +10155,12 @@
       <c r="C22" s="66" t="n">
         <v>1405</v>
       </c>
-      <c r="D22" s="67" t="inlineStr">
+      <c r="D22" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E22" s="66" t="inlineStr">
+      <c r="E22" s="138" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
@@ -9952,14 +10178,14 @@
       <c r="C23" s="66" t="n">
         <v>1405</v>
       </c>
-      <c r="D23" s="67" t="inlineStr">
+      <c r="D23" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E23" s="66" t="inlineStr">
-        <is>
-          <t>完了(UI全訳・2026-09)</t>
+      <c r="E23" s="138" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
     </row>
@@ -9975,14 +10201,14 @@
       <c r="C24" s="66" t="n">
         <v>1405</v>
       </c>
-      <c r="D24" s="67" t="inlineStr">
+      <c r="D24" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E24" s="66" t="inlineStr">
-        <is>
-          <t>完了(UI全訳・2026-09)</t>
+      <c r="E24" s="138" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
     </row>
@@ -9998,14 +10224,14 @@
       <c r="C25" s="66" t="n">
         <v>1405</v>
       </c>
-      <c r="D25" s="67" t="inlineStr">
+      <c r="D25" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E25" s="66" t="inlineStr">
-        <is>
-          <t>完了(UI全訳・2026-09)</t>
+      <c r="E25" s="138" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
     </row>
@@ -10021,14 +10247,14 @@
       <c r="C26" s="66" t="n">
         <v>1405</v>
       </c>
-      <c r="D26" s="67" t="inlineStr">
+      <c r="D26" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E26" s="66" t="inlineStr">
-        <is>
-          <t>完了(UI全訳・2026-09)</t>
+      <c r="E26" s="138" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
     </row>
@@ -10044,14 +10270,14 @@
       <c r="C27" s="66" t="n">
         <v>1405</v>
       </c>
-      <c r="D27" s="67" t="inlineStr">
+      <c r="D27" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E27" s="66" t="inlineStr">
-        <is>
-          <t>完了(UI全訳・2026-09)</t>
+      <c r="E27" s="138" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
     </row>
@@ -10067,14 +10293,14 @@
       <c r="C28" s="66" t="n">
         <v>1405</v>
       </c>
-      <c r="D28" s="67" t="inlineStr">
+      <c r="D28" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E28" s="66" t="inlineStr">
-        <is>
-          <t>完了(UI全訳・2026-09)</t>
+      <c r="E28" s="138" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
     </row>
@@ -10090,14 +10316,14 @@
       <c r="C29" s="66" t="n">
         <v>1405</v>
       </c>
-      <c r="D29" s="67" t="inlineStr">
+      <c r="D29" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E29" s="66" t="inlineStr">
-        <is>
-          <t>完了(UI全訳・2026-09)</t>
+      <c r="E29" s="138" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
     </row>
@@ -10108,6 +10334,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="77" t="inlineStr">
         <is>
@@ -10143,7 +10370,7 @@
       </c>
       <c r="F33" s="64" t="inlineStr">
         <is>
-          <t>他7言語</t>
+          <t>bn/id/ko/my/th/vi/zh</t>
         </is>
       </c>
     </row>
@@ -10156,22 +10383,22 @@
       <c r="B34" s="66" t="n">
         <v>3540</v>
       </c>
-      <c r="C34" s="67" t="inlineStr">
+      <c r="C34" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D34" s="67" t="inlineStr">
+      <c r="D34" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E34" s="67" t="inlineStr">
+      <c r="E34" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F34" s="68" t="inlineStr">
+      <c r="F34" s="140" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10186,22 +10413,22 @@
       <c r="B35" s="66" t="n">
         <v>612</v>
       </c>
-      <c r="C35" s="67" t="inlineStr">
+      <c r="C35" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D35" s="67" t="inlineStr">
+      <c r="D35" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E35" s="67" t="inlineStr">
+      <c r="E35" s="138" t="inlineStr">
         <is>
           <t>100%（語義1182）</t>
         </is>
       </c>
-      <c r="F35" s="68" t="inlineStr">
+      <c r="F35" s="140" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10216,22 +10443,22 @@
       <c r="B36" s="66" t="n">
         <v>408</v>
       </c>
-      <c r="C36" s="67" t="inlineStr">
+      <c r="C36" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D36" s="67" t="inlineStr">
+      <c r="D36" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E36" s="67" t="inlineStr">
+      <c r="E36" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F36" s="68" t="inlineStr">
+      <c r="F36" s="140" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10246,22 +10473,22 @@
       <c r="B37" s="66" t="n">
         <v>3524</v>
       </c>
-      <c r="C37" s="67" t="inlineStr">
+      <c r="C37" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D37" s="67" t="inlineStr">
+      <c r="D37" s="138" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E37" s="67" t="inlineStr">
+      <c r="E37" s="138" t="inlineStr">
         <is>
           <t>100%（3844）</t>
         </is>
       </c>
-      <c r="F37" s="68" t="inlineStr">
+      <c r="F37" s="140" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10274,6 +10501,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="105" t="inlineStr">
         <is>
@@ -10314,7 +10542,7 @@
       </c>
       <c r="G41" s="107" t="inlineStr">
         <is>
-          <t>他7言語</t>
+          <t>bn/id/ko/my/th/vi/zh</t>
         </is>
       </c>
       <c r="H41" s="82" t="n"/>
@@ -10337,17 +10565,17 @@
           <t>本文の対訳</t>
         </is>
       </c>
-      <c r="E42" s="108" t="inlineStr">
+      <c r="E42" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F42" s="108" t="inlineStr">
+      <c r="F42" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G42" s="109" t="inlineStr">
+      <c r="G42" s="142" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10372,17 +10600,17 @@
           <t>訳なし（下線語の解読課題・意味は問わず不要）</t>
         </is>
       </c>
-      <c r="E43" s="110" t="inlineStr">
+      <c r="E43" s="143" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F43" s="110" t="inlineStr">
+      <c r="F43" s="143" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="109" t="inlineStr">
+      <c r="G43" s="144" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10407,17 +10635,17 @@
           <t>訳なし（下線語の解読課題・意味は問わず不要）</t>
         </is>
       </c>
-      <c r="E44" s="110" t="inlineStr">
+      <c r="E44" s="143" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F44" s="110" t="inlineStr">
+      <c r="F44" s="143" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G44" s="109" t="inlineStr">
+      <c r="G44" s="144" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10442,17 +10670,17 @@
           <t>本文＋選択肢の対訳（回答後表示・誤答も正当な語ゆえ訳す・2026-09）</t>
         </is>
       </c>
-      <c r="E45" s="108" t="inlineStr">
+      <c r="E45" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F45" s="108" t="inlineStr">
+      <c r="F45" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G45" s="109" t="inlineStr">
+      <c r="G45" s="142" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10477,17 +10705,17 @@
           <t>正解の文の対訳（回答後表示・誤答は不自然文ゆえ訳さず・2026-09）</t>
         </is>
       </c>
-      <c r="E46" s="108" t="inlineStr">
+      <c r="E46" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F46" s="108" t="inlineStr">
+      <c r="F46" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G46" s="109" t="inlineStr">
+      <c r="G46" s="142" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10512,17 +10740,17 @@
           <t>完成文の対訳（回答後表示・選択肢=文法パーツは訳さず・2026-09）</t>
         </is>
       </c>
-      <c r="E47" s="108" t="inlineStr">
+      <c r="E47" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F47" s="108" t="inlineStr">
+      <c r="F47" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G47" s="109" t="inlineStr">
+      <c r="G47" s="142" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10547,17 +10775,17 @@
           <t>正しい文＋母語訳（回答後表示・2026-09再翻訳）</t>
         </is>
       </c>
-      <c r="E48" s="108" t="inlineStr">
+      <c r="E48" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F48" s="108" t="inlineStr">
+      <c r="F48" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G48" s="109" t="inlineStr">
+      <c r="G48" s="142" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10582,17 +10810,17 @@
           <t>本文の対訳</t>
         </is>
       </c>
-      <c r="E49" s="108" t="inlineStr">
+      <c r="E49" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F49" s="108" t="inlineStr">
+      <c r="F49" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G49" s="109" t="inlineStr">
+      <c r="G49" s="142" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10617,17 +10845,17 @@
           <t>本文の対訳（設問解説は廃止・本文訳は維持）</t>
         </is>
       </c>
-      <c r="E50" s="108" t="inlineStr">
+      <c r="E50" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F50" s="108" t="inlineStr">
+      <c r="F50" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G50" s="109" t="inlineStr">
+      <c r="G50" s="142" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10652,17 +10880,17 @@
           <t>本文の対訳</t>
         </is>
       </c>
-      <c r="E51" s="108" t="inlineStr">
+      <c r="E51" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F51" s="108" t="inlineStr">
+      <c r="F51" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G51" s="109" t="inlineStr">
+      <c r="G51" s="142" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10687,17 +10915,17 @@
           <t>本文の対訳</t>
         </is>
       </c>
-      <c r="E52" s="108" t="inlineStr">
+      <c r="E52" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F52" s="108" t="inlineStr">
+      <c r="F52" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G52" s="109" t="inlineStr">
+      <c r="G52" s="142" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10722,17 +10950,17 @@
           <t>訳なし（機械式・不要）</t>
         </is>
       </c>
-      <c r="E53" s="110" t="inlineStr">
+      <c r="E53" s="143" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F53" s="110" t="inlineStr">
+      <c r="F53" s="143" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="109" t="inlineStr">
+      <c r="G53" s="144" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10757,17 +10985,17 @@
           <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-02）</t>
         </is>
       </c>
-      <c r="E54" s="110" t="inlineStr">
+      <c r="E54" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F54" s="110" t="inlineStr">
+      <c r="F54" s="141" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G54" s="109" t="inlineStr">
+      <c r="G54" s="142" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
@@ -10789,20 +11017,20 @@
       </c>
       <c r="D55" s="94" t="inlineStr">
         <is>
-          <t>音声台本(スクリプト)の訳</t>
-        </is>
-      </c>
-      <c r="E55" s="110" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="F55" s="110" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="G55" s="109" t="inlineStr">
+          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-03）</t>
+        </is>
+      </c>
+      <c r="E55" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F55" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G55" s="142" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
@@ -10824,20 +11052,20 @@
       </c>
       <c r="D56" s="94" t="inlineStr">
         <is>
-          <t>音声台本(スクリプト)の訳</t>
-        </is>
-      </c>
-      <c r="E56" s="110" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="F56" s="110" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="G56" s="109" t="inlineStr">
+          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-03・N3のみ）</t>
+        </is>
+      </c>
+      <c r="E56" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F56" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G56" s="142" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
@@ -10859,20 +11087,20 @@
       </c>
       <c r="D57" s="94" t="inlineStr">
         <is>
-          <t>音声台本(スクリプト)の訳</t>
-        </is>
-      </c>
-      <c r="E57" s="110" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="F57" s="110" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="G57" s="109" t="inlineStr">
+          <t>場面文(台本)＋選択肢の対訳（回答後表示・2026-09-03・設問文なし＝場面に合う一言を選ぶ）</t>
+        </is>
+      </c>
+      <c r="E57" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F57" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G57" s="142" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
@@ -10894,20 +11122,20 @@
       </c>
       <c r="D58" s="94" t="inlineStr">
         <is>
-          <t>音声台本(スクリプト)の訳</t>
-        </is>
-      </c>
-      <c r="E58" s="110" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="F58" s="110" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="G58" s="109" t="inlineStr">
+          <t>場面文(台本)＋選択肢の対訳（回答後表示・2026-09-03・設問文なし＝相手の一言への返しを選ぶ）</t>
+        </is>
+      </c>
+      <c r="E58" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F58" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G58" s="142" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
@@ -10940,7 +11168,7 @@
     <row r="61">
       <c r="A61" s="90" t="inlineStr">
         <is>
-          <t>※ 聴解は音声台本(スクリプト)＋設問＋選択肢の対訳の有無を記載。課題理解=en/ne 100%完了(2026-09-02・660問・回答後表示)。他4大問(ポイント/概要/発話/即時)は未着手。</t>
+          <t>※ 聴解は音声台本(スクリプト)＋設問＋選択肢の対訳の有無を記載。全5大問=en/ne 100%完了・回答後表示（課題理解2026-09-02／ポイント理解・概要理解・発話表現・即時応答2026-09-03）。</t>
         </is>
       </c>
     </row>
@@ -10994,7 +11222,7 @@
       </c>
       <c r="F64" s="111" t="inlineStr">
         <is>
-          <t>他7言語</t>
+          <t>bn/id/ko/my/th/vi/zh</t>
         </is>
       </c>
       <c r="G64" s="82" t="n"/>
@@ -11032,17 +11260,17 @@
           <t>日本語のみ（かな・字／翻訳不要）</t>
         </is>
       </c>
-      <c r="D66" s="113" t="inlineStr">
+      <c r="D66" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E66" s="113" t="inlineStr">
+      <c r="E66" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F66" s="113" t="inlineStr">
+      <c r="F66" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11067,17 +11295,17 @@
           <t>辞書の意味を流用</t>
         </is>
       </c>
-      <c r="D67" s="114" t="inlineStr">
+      <c r="D67" s="147" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E67" s="114" t="inlineStr">
+      <c r="E67" s="147" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F67" s="113" t="inlineStr">
+      <c r="F67" s="148" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -11102,17 +11330,17 @@
           <t>日本語のみ（かな／翻訳不要）</t>
         </is>
       </c>
-      <c r="D68" s="113" t="inlineStr">
+      <c r="D68" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E68" s="113" t="inlineStr">
+      <c r="E68" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F68" s="113" t="inlineStr">
+      <c r="F68" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11137,17 +11365,17 @@
           <t>日本語のみ（字／翻訳不要）</t>
         </is>
       </c>
-      <c r="D69" s="115" t="inlineStr">
+      <c r="D69" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E69" s="115" t="inlineStr">
+      <c r="E69" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F69" s="115" t="inlineStr">
+      <c r="F69" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11172,17 +11400,17 @@
           <t>日本語のみ（音声・字／翻訳不要）</t>
         </is>
       </c>
-      <c r="D70" s="115" t="inlineStr">
+      <c r="D70" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E70" s="115" t="inlineStr">
+      <c r="E70" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F70" s="115" t="inlineStr">
+      <c r="F70" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11222,17 +11450,17 @@
           <t>辞書の意味を流用</t>
         </is>
       </c>
-      <c r="D72" s="117" t="inlineStr">
+      <c r="D72" s="150" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E72" s="117" t="inlineStr">
+      <c r="E72" s="150" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F72" s="115" t="inlineStr">
+      <c r="F72" s="151" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -11257,17 +11485,17 @@
           <t>日本語のみ（かな／翻訳不要）</t>
         </is>
       </c>
-      <c r="D73" s="115" t="inlineStr">
+      <c r="D73" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E73" s="115" t="inlineStr">
+      <c r="E73" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F73" s="115" t="inlineStr">
+      <c r="F73" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11292,17 +11520,17 @@
           <t>辞書の意味を流用</t>
         </is>
       </c>
-      <c r="D74" s="117" t="inlineStr">
+      <c r="D74" s="150" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E74" s="117" t="inlineStr">
+      <c r="E74" s="150" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F74" s="115" t="inlineStr">
+      <c r="F74" s="151" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -11327,17 +11555,17 @@
           <t>辞書の意味を流用</t>
         </is>
       </c>
-      <c r="D75" s="117" t="inlineStr">
+      <c r="D75" s="150" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E75" s="117" t="inlineStr">
+      <c r="E75" s="150" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F75" s="115" t="inlineStr">
+      <c r="F75" s="151" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -11362,17 +11590,17 @@
           <t>辞書の意味を流用（意味を提示）</t>
         </is>
       </c>
-      <c r="D76" s="117" t="inlineStr">
+      <c r="D76" s="150" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E76" s="117" t="inlineStr">
+      <c r="E76" s="150" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F76" s="115" t="inlineStr">
+      <c r="F76" s="151" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -11412,17 +11640,17 @@
           <t>辞書の意味を流用</t>
         </is>
       </c>
-      <c r="D78" s="117" t="inlineStr">
+      <c r="D78" s="150" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E78" s="117" t="inlineStr">
+      <c r="E78" s="150" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F78" s="115" t="inlineStr">
+      <c r="F78" s="151" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -11447,17 +11675,17 @@
           <t>辞書の意味を流用（ヒントに意味）</t>
         </is>
       </c>
-      <c r="D79" s="117" t="inlineStr">
+      <c r="D79" s="150" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E79" s="117" t="inlineStr">
+      <c r="E79" s="150" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F79" s="115" t="inlineStr">
+      <c r="F79" s="151" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -11496,6 +11724,7 @@
       <c r="H81" s="82" t="n"/>
       <c r="I81" s="82" t="n"/>
     </row>
+    <row r="82"/>
     <row r="83">
       <c r="A83" s="91" t="inlineStr">
         <is>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -9558,17 +9558,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="26" customWidth="1" style="75" min="1" max="1"/>
     <col width="20" customWidth="1" style="75" min="2" max="3"/>
     <col width="16" customWidth="1" style="75" min="4" max="4"/>
     <col width="22" customWidth="1" style="75" min="5" max="5"/>
-    <col width="15" customWidth="1" style="75" min="6" max="6"/>
-    <col width="15" customWidth="1" style="75" min="7" max="7"/>
-    <col width="24" customWidth="1" style="75" min="8" max="8"/>
-    <col width="10" customWidth="1" style="75" min="9" max="9"/>
+    <col width="11" customWidth="1" style="75" min="6" max="6"/>
+    <col width="11" customWidth="1" style="75" min="7" max="7"/>
+    <col width="22" customWidth="1" style="75" min="8" max="8"/>
+    <col width="11" customWidth="1" style="75" min="9" max="9"/>
+    <col width="11" customWidth="1" style="75" min="10" max="10"/>
+    <col width="11" customWidth="1" style="75" min="11" max="11"/>
+    <col width="11" customWidth="1" style="75" min="12" max="12"/>
+    <col width="11" customWidth="1" style="75" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="75">
@@ -10370,7 +10374,37 @@
       </c>
       <c r="F33" s="64" t="inlineStr">
         <is>
-          <t>bn/id/ko/my/th/vi/zh</t>
+          <t>ベンガル語</t>
+        </is>
+      </c>
+      <c r="G33" s="64" t="inlineStr">
+        <is>
+          <t>インドネシア語</t>
+        </is>
+      </c>
+      <c r="H33" s="64" t="inlineStr">
+        <is>
+          <t>韓国語</t>
+        </is>
+      </c>
+      <c r="I33" s="64" t="inlineStr">
+        <is>
+          <t>ミャンマー語</t>
+        </is>
+      </c>
+      <c r="J33" s="64" t="inlineStr">
+        <is>
+          <t>タイ語</t>
+        </is>
+      </c>
+      <c r="K33" s="64" t="inlineStr">
+        <is>
+          <t>ベトナム語</t>
+        </is>
+      </c>
+      <c r="L33" s="64" t="inlineStr">
+        <is>
+          <t>中国語</t>
         </is>
       </c>
     </row>
@@ -10403,6 +10437,36 @@
           <t>未着手</t>
         </is>
       </c>
+      <c r="G34" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H34" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I34" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J34" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K34" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L34" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="65" t="inlineStr">
@@ -10425,10 +10489,40 @@
       </c>
       <c r="E35" s="138" t="inlineStr">
         <is>
-          <t>100%（語義1182）</t>
+          <t>100%（語義1859）</t>
         </is>
       </c>
       <c r="F35" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="G35" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H35" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I35" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J35" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K35" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L35" s="140" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10463,6 +10557,36 @@
           <t>未着手</t>
         </is>
       </c>
+      <c r="G36" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H36" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I36" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J36" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K36" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L36" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="65" t="inlineStr">
@@ -10485,10 +10609,40 @@
       </c>
       <c r="E37" s="138" t="inlineStr">
         <is>
-          <t>100%（3844）</t>
+          <t>100%（3524）</t>
         </is>
       </c>
       <c r="F37" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="G37" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H37" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I37" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J37" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K37" s="140" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L37" s="140" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10542,11 +10696,39 @@
       </c>
       <c r="G41" s="107" t="inlineStr">
         <is>
-          <t>bn/id/ko/my/th/vi/zh</t>
-        </is>
-      </c>
-      <c r="H41" s="82" t="n"/>
-      <c r="I41" s="82" t="n"/>
+          <t>ベンガル語</t>
+        </is>
+      </c>
+      <c r="H41" s="107" t="inlineStr">
+        <is>
+          <t>インドネシア語</t>
+        </is>
+      </c>
+      <c r="I41" s="107" t="inlineStr">
+        <is>
+          <t>韓国語</t>
+        </is>
+      </c>
+      <c r="J41" s="107" t="inlineStr">
+        <is>
+          <t>ミャンマー語</t>
+        </is>
+      </c>
+      <c r="K41" s="107" t="inlineStr">
+        <is>
+          <t>タイ語</t>
+        </is>
+      </c>
+      <c r="L41" s="107" t="inlineStr">
+        <is>
+          <t>ベトナム語</t>
+        </is>
+      </c>
+      <c r="M41" s="107" t="inlineStr">
+        <is>
+          <t>中国語</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="94" t="inlineStr">
@@ -10580,8 +10762,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H42" s="82" t="n"/>
-      <c r="I42" s="82" t="n"/>
+      <c r="H42" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I42" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J42" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K42" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L42" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="M42" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="94" t="inlineStr">
@@ -10615,8 +10825,36 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H43" s="82" t="n"/>
-      <c r="I43" s="82" t="n"/>
+      <c r="H43" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K43" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="94" t="inlineStr">
@@ -10650,8 +10888,36 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H44" s="82" t="n"/>
-      <c r="I44" s="82" t="n"/>
+      <c r="H44" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="94" t="inlineStr">
@@ -10685,8 +10951,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H45" s="82" t="n"/>
-      <c r="I45" s="82" t="n"/>
+      <c r="H45" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I45" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J45" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K45" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L45" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="M45" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="94" t="inlineStr">
@@ -10720,8 +11014,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H46" s="82" t="n"/>
-      <c r="I46" s="82" t="n"/>
+      <c r="H46" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I46" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J46" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K46" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L46" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="M46" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="94" t="inlineStr">
@@ -10755,8 +11077,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H47" s="82" t="n"/>
-      <c r="I47" s="82" t="n"/>
+      <c r="H47" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I47" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J47" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K47" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L47" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="M47" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="94" t="inlineStr">
@@ -10790,8 +11140,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H48" s="82" t="n"/>
-      <c r="I48" s="82" t="n"/>
+      <c r="H48" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I48" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J48" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K48" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L48" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="M48" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="94" t="inlineStr">
@@ -10825,8 +11203,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H49" s="82" t="n"/>
-      <c r="I49" s="82" t="n"/>
+      <c r="H49" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I49" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J49" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K49" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L49" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="M49" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="94" t="inlineStr">
@@ -10860,8 +11266,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H50" s="82" t="n"/>
-      <c r="I50" s="82" t="n"/>
+      <c r="H50" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I50" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J50" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K50" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L50" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="M50" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="94" t="inlineStr">
@@ -10895,8 +11329,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H51" s="82" t="n"/>
-      <c r="I51" s="82" t="n"/>
+      <c r="H51" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I51" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J51" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K51" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L51" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="M51" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="94" t="inlineStr">
@@ -10930,8 +11392,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H52" s="82" t="n"/>
-      <c r="I52" s="82" t="n"/>
+      <c r="H52" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I52" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J52" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K52" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L52" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="M52" s="142" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="94" t="inlineStr">
@@ -10965,8 +11455,36 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H53" s="82" t="n"/>
-      <c r="I53" s="82" t="n"/>
+      <c r="H53" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J53" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K53" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L53" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M53" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="94" t="inlineStr">
@@ -11000,8 +11518,36 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="H54" s="82" t="n"/>
-      <c r="I54" s="82" t="n"/>
+      <c r="H54" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="I54" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="J54" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="K54" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="L54" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="M54" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="94" t="inlineStr">
@@ -11035,8 +11581,36 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="H55" s="82" t="n"/>
-      <c r="I55" s="82" t="n"/>
+      <c r="H55" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="I55" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="J55" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="K55" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="L55" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="M55" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="94" t="inlineStr">
@@ -11070,8 +11644,36 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="H56" s="82" t="n"/>
-      <c r="I56" s="82" t="n"/>
+      <c r="H56" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="I56" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="J56" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="K56" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="L56" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="M56" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="94" t="inlineStr">
@@ -11105,8 +11707,36 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="H57" s="82" t="n"/>
-      <c r="I57" s="82" t="n"/>
+      <c r="H57" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="I57" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="J57" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="K57" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="L57" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="M57" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="94" t="inlineStr">
@@ -11140,8 +11770,36 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="H58" s="82" t="n"/>
-      <c r="I58" s="82" t="n"/>
+      <c r="H58" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="I58" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="J58" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="K58" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="L58" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="M58" s="142" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="102" t="inlineStr">
@@ -11222,12 +11880,39 @@
       </c>
       <c r="F64" s="111" t="inlineStr">
         <is>
-          <t>bn/id/ko/my/th/vi/zh</t>
-        </is>
-      </c>
-      <c r="G64" s="82" t="n"/>
-      <c r="H64" s="82" t="n"/>
-      <c r="I64" s="82" t="n"/>
+          <t>ベンガル語</t>
+        </is>
+      </c>
+      <c r="G64" s="111" t="inlineStr">
+        <is>
+          <t>インドネシア語</t>
+        </is>
+      </c>
+      <c r="H64" s="111" t="inlineStr">
+        <is>
+          <t>韓国語</t>
+        </is>
+      </c>
+      <c r="I64" s="111" t="inlineStr">
+        <is>
+          <t>ミャンマー語</t>
+        </is>
+      </c>
+      <c r="J64" s="111" t="inlineStr">
+        <is>
+          <t>タイ語</t>
+        </is>
+      </c>
+      <c r="K64" s="111" t="inlineStr">
+        <is>
+          <t>ベトナム語</t>
+        </is>
+      </c>
+      <c r="L64" s="111" t="inlineStr">
+        <is>
+          <t>中国語</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="112" t="inlineStr">
@@ -11240,9 +11925,12 @@
       <c r="D65" s="85" t="n"/>
       <c r="E65" s="85" t="n"/>
       <c r="F65" s="85" t="n"/>
-      <c r="G65" s="82" t="n"/>
-      <c r="H65" s="82" t="n"/>
-      <c r="I65" s="82" t="n"/>
+      <c r="G65" s="85" t="n"/>
+      <c r="H65" s="85" t="n"/>
+      <c r="I65" s="85" t="n"/>
+      <c r="J65" s="85" t="n"/>
+      <c r="K65" s="85" t="n"/>
+      <c r="L65" s="85" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="86" t="inlineStr">
@@ -11275,9 +11963,36 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G66" s="82" t="n"/>
-      <c r="H66" s="82" t="n"/>
-      <c r="I66" s="82" t="n"/>
+      <c r="G66" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J66" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L66" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="86" t="inlineStr">
@@ -11310,9 +12025,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="G67" s="82" t="n"/>
-      <c r="H67" s="82" t="n"/>
-      <c r="I67" s="82" t="n"/>
+      <c r="G67" s="148" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H67" s="148" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I67" s="148" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J67" s="148" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K67" s="148" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L67" s="148" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="86" t="inlineStr">
@@ -11345,9 +12087,36 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G68" s="82" t="n"/>
-      <c r="H68" s="82" t="n"/>
-      <c r="I68" s="82" t="n"/>
+      <c r="G68" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J68" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="82" t="inlineStr">
@@ -11380,9 +12149,36 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G69" s="82" t="n"/>
-      <c r="H69" s="82" t="n"/>
-      <c r="I69" s="82" t="n"/>
+      <c r="G69" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J69" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="82" t="inlineStr">
@@ -11415,9 +12211,36 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G70" s="82" t="n"/>
-      <c r="H70" s="82" t="n"/>
-      <c r="I70" s="82" t="n"/>
+      <c r="G70" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J70" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="116" t="inlineStr">
@@ -11433,6 +12256,9 @@
       <c r="G71" s="82" t="n"/>
       <c r="H71" s="82" t="n"/>
       <c r="I71" s="82" t="n"/>
+      <c r="J71" s="82" t="n"/>
+      <c r="K71" s="82" t="n"/>
+      <c r="L71" s="82" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="82" t="inlineStr">
@@ -11465,9 +12291,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="G72" s="82" t="n"/>
-      <c r="H72" s="82" t="n"/>
-      <c r="I72" s="82" t="n"/>
+      <c r="G72" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H72" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I72" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J72" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K72" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L72" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="82" t="inlineStr">
@@ -11500,9 +12353,36 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G73" s="82" t="n"/>
-      <c r="H73" s="82" t="n"/>
-      <c r="I73" s="82" t="n"/>
+      <c r="G73" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J73" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="82" t="inlineStr">
@@ -11535,9 +12415,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="G74" s="82" t="n"/>
-      <c r="H74" s="82" t="n"/>
-      <c r="I74" s="82" t="n"/>
+      <c r="G74" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H74" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I74" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J74" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K74" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L74" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="82" t="inlineStr">
@@ -11570,9 +12477,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="G75" s="82" t="n"/>
-      <c r="H75" s="82" t="n"/>
-      <c r="I75" s="82" t="n"/>
+      <c r="G75" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H75" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I75" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J75" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K75" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L75" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="82" t="inlineStr">
@@ -11605,9 +12539,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="G76" s="82" t="n"/>
-      <c r="H76" s="82" t="n"/>
-      <c r="I76" s="82" t="n"/>
+      <c r="G76" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H76" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I76" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J76" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K76" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L76" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="116" t="inlineStr">
@@ -11623,6 +12584,9 @@
       <c r="G77" s="82" t="n"/>
       <c r="H77" s="82" t="n"/>
       <c r="I77" s="82" t="n"/>
+      <c r="J77" s="82" t="n"/>
+      <c r="K77" s="82" t="n"/>
+      <c r="L77" s="82" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="82" t="inlineStr">
@@ -11655,9 +12619,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="G78" s="82" t="n"/>
-      <c r="H78" s="82" t="n"/>
-      <c r="I78" s="82" t="n"/>
+      <c r="G78" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H78" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I78" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J78" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K78" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L78" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="82" t="inlineStr">
@@ -11690,9 +12681,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="G79" s="82" t="n"/>
-      <c r="H79" s="82" t="n"/>
-      <c r="I79" s="82" t="n"/>
+      <c r="G79" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H79" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I79" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J79" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K79" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="L79" s="151" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="90" t="inlineStr">
@@ -11708,6 +12726,9 @@
       <c r="G80" s="82" t="n"/>
       <c r="H80" s="82" t="n"/>
       <c r="I80" s="82" t="n"/>
+      <c r="J80" s="82" t="n"/>
+      <c r="K80" s="82" t="n"/>
+      <c r="L80" s="82" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="90" t="inlineStr">
@@ -11723,6 +12744,9 @@
       <c r="G81" s="82" t="n"/>
       <c r="H81" s="82" t="n"/>
       <c r="I81" s="82" t="n"/>
+      <c r="J81" s="82" t="n"/>
+      <c r="K81" s="82" t="n"/>
+      <c r="L81" s="82" t="n"/>
     </row>
     <row r="82"/>
     <row r="83">

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -9578,7 +9578,7 @@
     <row r="1" ht="18" customHeight="1" s="75">
       <c r="A1" s="63" t="inlineStr">
         <is>
-          <t>アプリ全体の翻訳状況  (2026-09-03 時点)</t>
+          <t>アプリ全体の翻訳状況  (2026-09-05 時点)</t>
         </is>
       </c>
     </row>
@@ -9788,14 +9788,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D10" s="139" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="139" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="D10" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E10" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="F10" s="140" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="H10" s="68" t="inlineStr">
         <is>
-          <t>UI完全（辞書・問題は未）</t>
+          <t>UI＋辞書完全（問題は未）</t>
         </is>
       </c>
     </row>
@@ -9830,14 +9830,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D11" s="139" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="139" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="D11" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E11" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="F11" s="140" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="H11" s="68" t="inlineStr">
         <is>
-          <t>UI完全（辞書・問題は未）</t>
+          <t>UI＋辞書完全（問題は未）</t>
         </is>
       </c>
     </row>
@@ -9872,14 +9872,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D12" s="139" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="139" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="D12" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E12" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="F12" s="140" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="H12" s="68" t="inlineStr">
         <is>
-          <t>UI完全（辞書・問題は未）</t>
+          <t>UI＋辞書完全（問題は未）</t>
         </is>
       </c>
     </row>
@@ -9914,14 +9914,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D13" s="139" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="139" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="D13" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E13" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="F13" s="140" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="H13" s="68" t="inlineStr">
         <is>
-          <t>UI完全（辞書・問題は未）</t>
+          <t>UI＋辞書完全（問題は未）</t>
         </is>
       </c>
     </row>
@@ -9956,14 +9956,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D14" s="139" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="139" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="D14" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E14" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="F14" s="140" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="H14" s="68" t="inlineStr">
         <is>
-          <t>UI完全（辞書・問題は未）</t>
+          <t>UI＋辞書完全（問題は未）</t>
         </is>
       </c>
     </row>
@@ -9998,14 +9998,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D15" s="139" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="139" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="D15" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E15" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="F15" s="140" t="inlineStr">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="H15" s="68" t="inlineStr">
         <is>
-          <t>UI完全（辞書・問題は未）</t>
+          <t>UI＋辞書完全（問題は未）</t>
         </is>
       </c>
     </row>
@@ -10040,14 +10040,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="D16" s="139" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="139" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="D16" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E16" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="F16" s="140" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="H16" s="68" t="inlineStr">
         <is>
-          <t>UI完全（辞書・問題は未）</t>
+          <t>UI＋辞書完全（問題は未）</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
     <row r="18">
       <c r="A18" s="77" t="inlineStr">
         <is>
-          <t>② UI（画面の文字）　ja=1405 キーが元</t>
+          <t>② UI（画面の文字）　ja=1422 キーが元</t>
         </is>
       </c>
     </row>
@@ -10108,10 +10108,10 @@
         </is>
       </c>
       <c r="B20" s="67" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="C20" s="66" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="D20" s="138" t="inlineStr">
         <is>
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="B21" s="67" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="C21" s="66" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="D21" s="138" t="inlineStr">
         <is>
@@ -10154,10 +10154,10 @@
         </is>
       </c>
       <c r="B22" s="67" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="C22" s="66" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="D22" s="138" t="inlineStr">
         <is>
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="B23" s="67" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="C23" s="66" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="D23" s="138" t="inlineStr">
         <is>
@@ -10200,10 +10200,10 @@
         </is>
       </c>
       <c r="B24" s="67" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="C24" s="66" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="D24" s="138" t="inlineStr">
         <is>
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="B25" s="67" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="C25" s="66" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="D25" s="138" t="inlineStr">
         <is>
@@ -10246,10 +10246,10 @@
         </is>
       </c>
       <c r="B26" s="67" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="C26" s="66" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="D26" s="138" t="inlineStr">
         <is>
@@ -10269,10 +10269,10 @@
         </is>
       </c>
       <c r="B27" s="67" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="C27" s="66" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="D27" s="138" t="inlineStr">
         <is>
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="B28" s="67" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="C28" s="66" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="D28" s="138" t="inlineStr">
         <is>
@@ -10315,10 +10315,10 @@
         </is>
       </c>
       <c r="B29" s="67" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="C29" s="66" t="n">
-        <v>1405</v>
+        <v>1422</v>
       </c>
       <c r="D29" s="138" t="inlineStr">
         <is>
@@ -10432,39 +10432,39 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F34" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G34" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H34" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I34" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J34" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K34" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L34" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="F34" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G34" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H34" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I34" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J34" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K34" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L34" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10492,39 +10492,39 @@
           <t>100%（語義1859）</t>
         </is>
       </c>
-      <c r="F35" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G35" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H35" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I35" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J35" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K35" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L35" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="F35" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G35" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H35" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I35" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J35" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K35" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L35" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10552,39 +10552,39 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F36" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G36" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H36" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I36" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J36" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K36" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L36" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="F36" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G36" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H36" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I36" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J36" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K36" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L36" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10612,46 +10612,46 @@
           <t>100%（3524）</t>
         </is>
       </c>
-      <c r="F37" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G37" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H37" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I37" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J37" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K37" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L37" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="F37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="76" t="inlineStr">
         <is>
-          <t>※ 英語＝同梱データに最初から入っている意味。ネパール語＝配信(OTA)の上書き層 content/lexicon で全件対応済（meaning=4561件＝語彙+漢字+文法の全意味）。</t>
+          <t>※ 英語＝同梱データに最初から入っている意味。ネパール語＝配信(OTA)の上書き層 content/lexicon で全件対応済（meaning=4561件＝語彙+漢字+文法の全意味）。 ／ インドネシア語(id)＝辞書全4種(意味4560+漢字グロス1859+例文3524+文法例文408)を2026-09-05に翻訳(Gemini・content/lexicon に id 追記・app改修不要)。</t>
         </is>
       </c>
     </row>
@@ -12020,39 +12020,39 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F67" s="148" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G67" s="148" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H67" s="148" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I67" s="148" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J67" s="148" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K67" s="148" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L67" s="148" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="F67" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G67" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H67" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I67" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J67" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K67" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L67" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -12286,39 +12286,39 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F72" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G72" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H72" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I72" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J72" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K72" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L72" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="F72" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G72" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H72" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I72" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J72" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K72" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L72" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -12410,39 +12410,39 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F74" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G74" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H74" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I74" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J74" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K74" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L74" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="F74" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G74" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H74" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I74" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J74" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K74" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L74" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -12472,39 +12472,39 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F75" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G75" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H75" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I75" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J75" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K75" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L75" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="F75" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G75" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H75" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I75" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J75" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K75" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L75" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -12534,39 +12534,39 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F76" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G76" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H76" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I76" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J76" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K76" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L76" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="F76" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G76" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H76" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I76" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J76" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K76" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L76" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -12614,39 +12614,39 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F78" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G78" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H78" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I78" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J78" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K78" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L78" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="F78" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G78" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H78" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I78" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J78" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K78" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L78" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -12676,39 +12676,39 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F79" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G79" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H79" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I79" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J79" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K79" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L79" s="151" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="F79" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G79" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H79" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I79" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J79" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K79" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L79" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -12766,14 +12766,14 @@
     <row r="85">
       <c r="A85" s="90" t="inlineStr">
         <is>
-          <t>・残り7言語(bn/id/ko/my/th/vi/zh)＝UIは全キー翻訳済(2026-09・100%)。辞書・問題・例文は未着手。</t>
+          <t>・残り7言語(bn/id/ko/my/th/vi/zh)＝UIは全キー翻訳済(100%)。辞書は7言語すべて完了(id 2026-09-05／bn/ko/my/th/vi/zh 2026-09-05)。全7言語の問題訳は未着手。</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="90" t="inlineStr">
         <is>
-          <t>・7言語をフル対応にするなら、辞書の意味(語彙3540+漢字612+文法408)×7＋各問題の対訳 の翻訳が必要（指示があれば一括で見積り→翻訳）。UIは対応済。</t>
+          <t>・7言語フル対応には 各問題の対訳 が必要（辞書は全7言語完了済）。UIは全言語対応済。</t>
         </is>
       </c>
     </row>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="41">
+  <fonts count="43">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -254,6 +254,13 @@
     <font>
       <color rgb="FF808080"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="43">
     <fill>
@@ -470,7 +477,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -567,11 +574,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -952,6 +973,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="13" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="42" fillId="13" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="13" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9558,7 +9593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="26" customWidth="1" style="75" min="1" max="1"/>
@@ -9798,19 +9833,19 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F10" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G10" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H10" s="68" t="inlineStr">
-        <is>
-          <t>UI＋辞書完全（問題は未）</t>
+      <c r="F10" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G10" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="138" t="inlineStr">
+        <is>
+          <t>フル</t>
         </is>
       </c>
     </row>
@@ -9840,19 +9875,19 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F11" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G11" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H11" s="68" t="inlineStr">
-        <is>
-          <t>UI＋辞書完全（問題は未）</t>
+      <c r="F11" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G11" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="138" t="inlineStr">
+        <is>
+          <t>フル</t>
         </is>
       </c>
     </row>
@@ -9882,19 +9917,19 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F12" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G12" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H12" s="68" t="inlineStr">
-        <is>
-          <t>UI＋辞書完全（問題は未）</t>
+      <c r="F12" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G12" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="138" t="inlineStr">
+        <is>
+          <t>フル</t>
         </is>
       </c>
     </row>
@@ -9924,19 +9959,19 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F13" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G13" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H13" s="68" t="inlineStr">
-        <is>
-          <t>UI＋辞書完全（問題は未）</t>
+      <c r="F13" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G13" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="138" t="inlineStr">
+        <is>
+          <t>フル</t>
         </is>
       </c>
     </row>
@@ -9966,19 +10001,19 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F14" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G14" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H14" s="68" t="inlineStr">
-        <is>
-          <t>UI＋辞書完全（問題は未）</t>
+      <c r="F14" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G14" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H14" s="138" t="inlineStr">
+        <is>
+          <t>フル</t>
         </is>
       </c>
     </row>
@@ -10008,19 +10043,19 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F15" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G15" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H15" s="68" t="inlineStr">
-        <is>
-          <t>UI＋辞書完全（問題は未）</t>
+      <c r="F15" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G15" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="138" t="inlineStr">
+        <is>
+          <t>フル</t>
         </is>
       </c>
     </row>
@@ -10050,19 +10085,19 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F16" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G16" s="140" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H16" s="68" t="inlineStr">
-        <is>
-          <t>UI＋辞書完全（問題は未）</t>
+      <c r="F16" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G16" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H16" s="138" t="inlineStr">
+        <is>
+          <t>フル</t>
         </is>
       </c>
     </row>
@@ -10649,417 +10684,372 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="76" t="inlineStr">
+      <c r="A38" s="173" t="inlineStr">
+        <is>
+          <t>辞書訳 出力字数(参考)</t>
+        </is>
+      </c>
+      <c r="B38" s="174" t="n"/>
+      <c r="C38" s="174" t="n"/>
+      <c r="E38" s="174" t="n"/>
+      <c r="F38" s="175" t="n">
+        <v>344226</v>
+      </c>
+      <c r="G38" s="175" t="n">
+        <v>388928</v>
+      </c>
+      <c r="H38" s="175" t="n">
+        <v>151711</v>
+      </c>
+      <c r="I38" s="175" t="n">
+        <v>375205</v>
+      </c>
+      <c r="J38" s="175" t="n">
+        <v>303788</v>
+      </c>
+      <c r="K38" s="175" t="n">
+        <v>351959</v>
+      </c>
+      <c r="L38" s="175" t="n">
+        <v>102244</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="173" t="inlineStr">
+        <is>
+          <t>辞書訳 概算実費(参考・Gemini2.5Flash・6言語計≈¥327/通算≈¥405)</t>
+        </is>
+      </c>
+      <c r="B39" s="174" t="n"/>
+      <c r="C39" s="174" t="n"/>
+      <c r="D39" s="176" t="inlineStr">
+        <is>
+          <t>¥0(元)</t>
+        </is>
+      </c>
+      <c r="E39" s="174" t="n"/>
+      <c r="F39" s="176" t="inlineStr">
+        <is>
+          <t>≈¥69</t>
+        </is>
+      </c>
+      <c r="G39" s="176" t="inlineStr">
+        <is>
+          <t>¥78</t>
+        </is>
+      </c>
+      <c r="H39" s="176" t="inlineStr">
+        <is>
+          <t>≈¥30</t>
+        </is>
+      </c>
+      <c r="I39" s="176" t="inlineStr">
+        <is>
+          <t>≈¥75</t>
+        </is>
+      </c>
+      <c r="J39" s="176" t="inlineStr">
+        <is>
+          <t>≈¥61</t>
+        </is>
+      </c>
+      <c r="K39" s="176" t="inlineStr">
+        <is>
+          <t>≈¥71</t>
+        </is>
+      </c>
+      <c r="L39" s="176" t="inlineStr">
+        <is>
+          <t>≈¥21</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="76" t="inlineStr">
         <is>
           <t>※ 英語＝同梱データに最初から入っている意味。ネパール語＝配信(OTA)の上書き層 content/lexicon で全件対応済（meaning=4561件＝語彙+漢字+文法の全意味）。 ／ インドネシア語(id)＝辞書全4種(意味4560+漢字グロス1859+例文3524+文法例文408)を2026-09-05に翻訳(Gemini・content/lexicon に id 追記・app改修不要)。</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="105" t="inlineStr">
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="105" t="inlineStr">
         <is>
           <t>④ 各大問（問題）の翻訳　※問題文は日本語。ここは『読解本文』などの対訳と、解説の翻訳の話</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="106" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="106" t="inlineStr">
         <is>
           <t>大問</t>
         </is>
       </c>
-      <c r="B41" s="106" t="inlineStr">
+      <c r="B43" s="106" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="C41" s="106" t="inlineStr">
+      <c r="C43" s="106" t="inlineStr">
         <is>
           <t>模試</t>
         </is>
       </c>
-      <c r="D41" s="106" t="inlineStr">
+      <c r="D43" s="106" t="inlineStr">
         <is>
           <t>翻訳の種類</t>
         </is>
       </c>
-      <c r="E41" s="106" t="inlineStr">
+      <c r="E43" s="106" t="inlineStr">
         <is>
           <t>英語(en)</t>
         </is>
       </c>
-      <c r="F41" s="106" t="inlineStr">
+      <c r="F43" s="106" t="inlineStr">
         <is>
           <t>ネパール語(ne)</t>
         </is>
       </c>
-      <c r="G41" s="107" t="inlineStr">
+      <c r="G43" s="107" t="inlineStr">
         <is>
           <t>ベンガル語</t>
         </is>
       </c>
-      <c r="H41" s="107" t="inlineStr">
+      <c r="H43" s="107" t="inlineStr">
         <is>
           <t>インドネシア語</t>
         </is>
       </c>
-      <c r="I41" s="107" t="inlineStr">
+      <c r="I43" s="107" t="inlineStr">
         <is>
           <t>韓国語</t>
         </is>
       </c>
-      <c r="J41" s="107" t="inlineStr">
+      <c r="J43" s="107" t="inlineStr">
         <is>
           <t>ミャンマー語</t>
         </is>
       </c>
-      <c r="K41" s="107" t="inlineStr">
+      <c r="K43" s="107" t="inlineStr">
         <is>
           <t>タイ語</t>
         </is>
       </c>
-      <c r="L41" s="107" t="inlineStr">
+      <c r="L43" s="107" t="inlineStr">
         <is>
           <t>ベトナム語</t>
         </is>
       </c>
-      <c r="M41" s="107" t="inlineStr">
+      <c r="M43" s="107" t="inlineStr">
         <is>
           <t>中国語</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="94" t="inlineStr">
-        <is>
-          <t>文字語彙・文脈規定</t>
-        </is>
-      </c>
-      <c r="B42" s="95" t="n">
-        <v>3464</v>
-      </c>
-      <c r="C42" s="95" t="n">
-        <v>310</v>
-      </c>
-      <c r="D42" s="94" t="inlineStr">
-        <is>
-          <t>本文の対訳</t>
-        </is>
-      </c>
-      <c r="E42" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F42" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G42" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H42" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I42" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J42" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K42" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L42" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="M42" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="94" t="inlineStr">
-        <is>
-          <t>文字語彙・漢字読み</t>
-        </is>
-      </c>
-      <c r="B43" s="95" t="n">
-        <v>3204</v>
-      </c>
-      <c r="C43" s="95" t="n">
-        <v>274</v>
-      </c>
-      <c r="D43" s="94" t="inlineStr">
-        <is>
-          <t>訳なし（下線語の解読課題・意味は問わず不要）</t>
-        </is>
-      </c>
-      <c r="E43" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J43" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K43" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L43" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="94" t="inlineStr">
         <is>
-          <t>文字語彙・表記</t>
+          <t>文字語彙・文脈規定</t>
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>3350</v>
+        <v>3464</v>
       </c>
       <c r="C44" s="95" t="n">
-        <v>200</v>
+        <v>310</v>
       </c>
       <c r="D44" s="94" t="inlineStr">
         <is>
-          <t>訳なし（下線語の解読課題・意味は問わず不要）</t>
-        </is>
-      </c>
-      <c r="E44" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F44" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J44" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K44" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L44" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>本文の対訳</t>
+        </is>
+      </c>
+      <c r="E44" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F44" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G44" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H44" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I44" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J44" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K44" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L44" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M44" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="94" t="inlineStr">
         <is>
-          <t>文字語彙・言い換え</t>
+          <t>文字語彙・漢字読み</t>
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>2255</v>
+        <v>3204</v>
       </c>
       <c r="C45" s="95" t="n">
-        <v>150</v>
+        <v>274</v>
       </c>
       <c r="D45" s="94" t="inlineStr">
         <is>
-          <t>本文＋選択肢の対訳（回答後表示・誤答も正当な語ゆえ訳す・2026-09）</t>
-        </is>
-      </c>
-      <c r="E45" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F45" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G45" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H45" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I45" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J45" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K45" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L45" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="M45" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>訳なし（下線語の解読課題・意味は問わず不要）</t>
+        </is>
+      </c>
+      <c r="E45" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K45" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L45" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M45" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="94" t="inlineStr">
         <is>
-          <t>文字語彙・用法</t>
+          <t>文字語彙・表記</t>
         </is>
       </c>
       <c r="B46" s="95" t="n">
-        <v>1171</v>
+        <v>3350</v>
       </c>
       <c r="C46" s="95" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D46" s="94" t="inlineStr">
         <is>
-          <t>正解の文の対訳（回答後表示・誤答は不自然文ゆえ訳さず・2026-09）</t>
-        </is>
-      </c>
-      <c r="E46" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F46" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G46" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H46" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I46" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J46" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K46" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L46" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="M46" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>訳なし（下線語の解読課題・意味は問わず不要）</t>
+        </is>
+      </c>
+      <c r="E46" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K46" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L46" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M46" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="94" t="inlineStr">
         <is>
-          <t>文法・穴埋め</t>
+          <t>文字語彙・言い換え</t>
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>1207</v>
+        <v>2255</v>
       </c>
       <c r="C47" s="95" t="n">
-        <v>440</v>
+        <v>150</v>
       </c>
       <c r="D47" s="94" t="inlineStr">
         <is>
-          <t>完成文の対訳（回答後表示・選択肢=文法パーツは訳さず・2026-09）</t>
+          <t>本文＋選択肢の対訳（回答後表示・誤答も正当な語ゆえ訳す・2026-09）</t>
         </is>
       </c>
       <c r="E47" s="141" t="inlineStr">
@@ -11072,57 +11062,57 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="G47" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H47" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I47" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J47" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K47" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L47" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="M47" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G47" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H47" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I47" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J47" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K47" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L47" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M47" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="94" t="inlineStr">
         <is>
-          <t>文法・並べ替え</t>
+          <t>文字語彙・用法</t>
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>673</v>
+        <v>1171</v>
       </c>
       <c r="C48" s="95" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D48" s="94" t="inlineStr">
         <is>
-          <t>正しい文＋母語訳（回答後表示・2026-09再翻訳）</t>
+          <t>正解の文の対訳（回答後表示・誤答は不自然文ゆえ訳さず・2026-09）</t>
         </is>
       </c>
       <c r="E48" s="141" t="inlineStr">
@@ -11135,57 +11125,57 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="G48" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H48" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I48" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J48" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K48" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L48" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="M48" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G48" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H48" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I48" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J48" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K48" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L48" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M48" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="94" t="inlineStr">
         <is>
-          <t>文法・文章の文法</t>
+          <t>文法・穴埋め</t>
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>210</v>
+        <v>1207</v>
       </c>
       <c r="C49" s="95" t="n">
-        <v>30</v>
+        <v>440</v>
       </c>
       <c r="D49" s="94" t="inlineStr">
         <is>
-          <t>本文の対訳</t>
+          <t>完成文の対訳（回答後表示・選択肢=文法パーツは訳さず・2026-09）</t>
         </is>
       </c>
       <c r="E49" s="141" t="inlineStr">
@@ -11198,57 +11188,57 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="G49" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H49" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I49" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J49" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K49" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L49" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="M49" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G49" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H49" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I49" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J49" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K49" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L49" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M49" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="94" t="inlineStr">
         <is>
-          <t>読解・内容理解(短)</t>
+          <t>文法・並べ替え</t>
         </is>
       </c>
       <c r="B50" s="95" t="n">
-        <v>330</v>
+        <v>673</v>
       </c>
       <c r="C50" s="95" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="D50" s="94" t="inlineStr">
         <is>
-          <t>本文の対訳（設問解説は廃止・本文訳は維持）</t>
+          <t>正しい文＋母語訳（回答後表示・2026-09再翻訳）</t>
         </is>
       </c>
       <c r="E50" s="141" t="inlineStr">
@@ -11261,53 +11251,53 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="G50" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H50" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I50" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J50" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K50" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L50" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="M50" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G50" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H50" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I50" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J50" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K50" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L50" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M50" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="94" t="inlineStr">
         <is>
-          <t>読解・内容理解(中)</t>
+          <t>文法・文章の文法</t>
         </is>
       </c>
       <c r="B51" s="95" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="C51" s="95" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D51" s="94" t="inlineStr">
         <is>
@@ -11324,57 +11314,57 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="G51" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H51" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I51" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J51" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K51" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L51" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="M51" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G51" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K51" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L51" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M51" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="94" t="inlineStr">
         <is>
-          <t>読解・長文</t>
+          <t>読解・内容理解(短)</t>
         </is>
       </c>
       <c r="B52" s="95" t="n">
-        <v>40</v>
+        <v>330</v>
       </c>
       <c r="C52" s="95" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="D52" s="94" t="inlineStr">
         <is>
-          <t>本文の対訳</t>
+          <t>本文の対訳（設問解説は廃止・本文訳は維持）</t>
         </is>
       </c>
       <c r="E52" s="141" t="inlineStr">
@@ -11387,120 +11377,120 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="G52" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H52" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I52" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J52" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="K52" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="L52" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="M52" s="142" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G52" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H52" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I52" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J52" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K52" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L52" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M52" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="94" t="inlineStr">
         <is>
-          <t>読解・情報検索</t>
+          <t>読解・内容理解(中)</t>
         </is>
       </c>
       <c r="B53" s="95" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="C53" s="95" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D53" s="94" t="inlineStr">
         <is>
-          <t>訳なし（機械式・不要）</t>
-        </is>
-      </c>
-      <c r="E53" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I53" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J53" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K53" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L53" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M53" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>本文の対訳</t>
+        </is>
+      </c>
+      <c r="E53" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F53" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G53" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H53" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I53" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J53" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K53" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L53" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M53" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="94" t="inlineStr">
         <is>
-          <t>聴解・課題理解</t>
+          <t>読解・長文</t>
         </is>
       </c>
       <c r="B54" s="95" t="n">
-        <v>450</v>
+        <v>40</v>
       </c>
       <c r="C54" s="95" t="n">
-        <v>210</v>
+        <v>10</v>
       </c>
       <c r="D54" s="94" t="inlineStr">
         <is>
-          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-02）</t>
+          <t>本文の対訳</t>
         </is>
       </c>
       <c r="E54" s="141" t="inlineStr">
@@ -11513,120 +11503,120 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="G54" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="H54" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="I54" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="J54" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="K54" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="L54" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="M54" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
+      <c r="G54" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H54" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I54" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J54" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K54" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L54" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M54" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="94" t="inlineStr">
         <is>
-          <t>聴解・ポイント理解</t>
+          <t>読解・情報検索</t>
         </is>
       </c>
       <c r="B55" s="95" t="n">
-        <v>450</v>
+        <v>180</v>
       </c>
       <c r="C55" s="95" t="n">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="D55" s="94" t="inlineStr">
         <is>
-          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-03）</t>
-        </is>
-      </c>
-      <c r="E55" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F55" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G55" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="H55" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="I55" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="J55" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="K55" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="L55" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="M55" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
+          <t>訳なし（機械式・不要）</t>
+        </is>
+      </c>
+      <c r="E55" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J55" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K55" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L55" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M55" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="94" t="inlineStr">
         <is>
-          <t>聴解・概要理解</t>
+          <t>聴解・課題理解</t>
         </is>
       </c>
       <c r="B56" s="95" t="n">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="C56" s="95" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="D56" s="94" t="inlineStr">
         <is>
-          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-03・N3のみ）</t>
+          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-02）</t>
         </is>
       </c>
       <c r="E56" s="141" t="inlineStr">
@@ -11639,57 +11629,57 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="G56" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="H56" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="I56" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="J56" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="K56" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="L56" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="M56" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
+      <c r="G56" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H56" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I56" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J56" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K56" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L56" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M56" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="94" t="inlineStr">
         <is>
-          <t>聴解・発話表現</t>
+          <t>聴解・ポイント理解</t>
         </is>
       </c>
       <c r="B57" s="95" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="C57" s="95" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="D57" s="94" t="inlineStr">
         <is>
-          <t>場面文(台本)＋選択肢の対訳（回答後表示・2026-09-03・設問文なし＝場面に合う一言を選ぶ）</t>
+          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-03）</t>
         </is>
       </c>
       <c r="E57" s="141" t="inlineStr">
@@ -11702,640 +11692,632 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="G57" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="H57" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="I57" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="J57" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="K57" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="L57" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="M57" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
+      <c r="G57" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K57" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L57" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M57" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="94" t="inlineStr">
         <is>
+          <t>聴解・概要理解</t>
+        </is>
+      </c>
+      <c r="B58" s="95" t="n">
+        <v>80</v>
+      </c>
+      <c r="C58" s="95" t="n">
+        <v>30</v>
+      </c>
+      <c r="D58" s="94" t="inlineStr">
+        <is>
+          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-03・N3のみ）</t>
+        </is>
+      </c>
+      <c r="E58" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F58" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G58" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H58" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I58" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J58" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K58" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L58" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M58" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="94" t="inlineStr">
+        <is>
+          <t>聴解・発話表現</t>
+        </is>
+      </c>
+      <c r="B59" s="95" t="n">
+        <v>600</v>
+      </c>
+      <c r="C59" s="95" t="n">
+        <v>140</v>
+      </c>
+      <c r="D59" s="94" t="inlineStr">
+        <is>
+          <t>場面文(台本)＋選択肢の対訳（回答後表示・2026-09-03・設問文なし＝場面に合う一言を選ぶ）</t>
+        </is>
+      </c>
+      <c r="E59" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F59" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G59" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H59" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I59" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J59" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K59" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L59" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M59" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="94" t="inlineStr">
+        <is>
           <t>聴解・即時応答</t>
         </is>
       </c>
-      <c r="B58" s="95" t="n">
+      <c r="B60" s="95" t="n">
         <v>720</v>
       </c>
-      <c r="C58" s="95" t="n">
+      <c r="C60" s="95" t="n">
         <v>230</v>
       </c>
-      <c r="D58" s="94" t="inlineStr">
+      <c r="D60" s="94" t="inlineStr">
         <is>
           <t>場面文(台本)＋選択肢の対訳（回答後表示・2026-09-03・設問文なし＝相手の一言への返しを選ぶ）</t>
         </is>
       </c>
-      <c r="E58" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F58" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G58" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="H58" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="I58" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="J58" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="K58" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="L58" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="M58" s="142" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="102" t="inlineStr">
+      <c r="E60" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F60" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G60" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H60" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I60" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J60" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K60" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L60" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M60" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="177" t="inlineStr">
+        <is>
+          <t>◇大問訳 出力字数(参考)</t>
+        </is>
+      </c>
+      <c r="G61" s="175" t="n">
+        <v>2785247</v>
+      </c>
+      <c r="H61" s="175" t="n">
+        <v>3401751</v>
+      </c>
+      <c r="I61" s="175" t="n">
+        <v>1447703</v>
+      </c>
+      <c r="J61" s="175" t="n">
+        <v>3294974</v>
+      </c>
+      <c r="K61" s="175" t="n">
+        <v>2646058</v>
+      </c>
+      <c r="L61" s="175" t="n">
+        <v>3046533</v>
+      </c>
+      <c r="M61" s="175" t="n">
+        <v>905106</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="177" t="inlineStr">
+        <is>
+          <t>◇大問訳 概算実費(参考・Gemini2.5Flash)</t>
+        </is>
+      </c>
+      <c r="G62" s="176" t="inlineStr">
+        <is>
+          <t>¥481</t>
+        </is>
+      </c>
+      <c r="H62" s="176" t="inlineStr">
+        <is>
+          <t>¥494</t>
+        </is>
+      </c>
+      <c r="I62" s="176" t="inlineStr">
+        <is>
+          <t>¥504</t>
+        </is>
+      </c>
+      <c r="J62" s="176" t="inlineStr">
+        <is>
+          <t>¥719</t>
+        </is>
+      </c>
+      <c r="K62" s="176" t="inlineStr">
+        <is>
+          <t>¥544</t>
+        </is>
+      </c>
+      <c r="L62" s="176" t="inlineStr">
+        <is>
+          <t>¥532</t>
+        </is>
+      </c>
+      <c r="M62" s="176" t="inlineStr">
+        <is>
+          <t>¥432</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="102" t="inlineStr">
         <is>
           <t>※ 通常＝学習プール、模試＝模試専用プール(初見)。旧「└ 漢字読み(模試プール)」サブ行は廃止し、全大問に模試列を新設。</t>
         </is>
       </c>
-      <c r="B59" s="103" t="n"/>
-      <c r="C59" s="103" t="n"/>
-      <c r="D59" s="103" t="n"/>
-      <c r="E59" s="103" t="n"/>
-      <c r="F59" s="103" t="n"/>
-      <c r="G59" s="103" t="n"/>
-      <c r="H59" s="103" t="n"/>
-      <c r="I59" s="104" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="90" t="inlineStr">
+      <c r="B63" s="103" t="n"/>
+      <c r="C63" s="103" t="n"/>
+      <c r="D63" s="103" t="n"/>
+      <c r="E63" s="103" t="n"/>
+      <c r="F63" s="103" t="n"/>
+      <c r="G63" s="103" t="n"/>
+      <c r="H63" s="103" t="n"/>
+      <c r="I63" s="104" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="90" t="inlineStr">
         <is>
           <t>※ 文脈規定は「解説の翻訳(旧ne38%)」を廃止し、本文の対訳(空所を答えで埋めた完成文の en/ne)へ移行済。表示＝回答後に本文の下。2026-09-02 完了(3774問)。</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="90" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="90" t="inlineStr">
         <is>
           <t>※ 聴解は音声台本(スクリプト)＋設問＋選択肢の対訳の有無を記載。全5大問=en/ne 100%完了・回答後表示（課題理解2026-09-02／ポイント理解・概要理解・発話表現・即時応答2026-09-03）。</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>※ 表記・漢字読みは『下線語を読む／漢字で書く』の解読問題で本文の意味は問わない（意味は辞書・意味ドリルで担保）。解説・母語訳は不要と判断し、表記の解説(en/ne 旧ne77%)を全削除。2026-09-02。</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="105" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="105" t="inlineStr">
         <is>
           <t>⑤ 各ドリル（単語タブの全ドリル｜漢字5・語彙5・文法2＝計12種）</t>
         </is>
       </c>
-      <c r="B63" s="82" t="n"/>
-      <c r="C63" s="82" t="n"/>
-      <c r="D63" s="82" t="n"/>
-      <c r="E63" s="82" t="n"/>
-      <c r="F63" s="82" t="n"/>
-      <c r="G63" s="82" t="n"/>
-      <c r="H63" s="82" t="n"/>
-      <c r="I63" s="82" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="111" t="inlineStr">
+      <c r="B67" s="82" t="n"/>
+      <c r="C67" s="82" t="n"/>
+      <c r="D67" s="82" t="n"/>
+      <c r="E67" s="82" t="n"/>
+      <c r="F67" s="82" t="n"/>
+      <c r="G67" s="82" t="n"/>
+      <c r="H67" s="82" t="n"/>
+      <c r="I67" s="82" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="111" t="inlineStr">
         <is>
           <t>ドリル</t>
         </is>
       </c>
-      <c r="B64" s="111" t="inlineStr">
+      <c r="B68" s="111" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C64" s="111" t="inlineStr">
+      <c r="C68" s="111" t="inlineStr">
         <is>
           <t>翻訳の出どころ</t>
         </is>
       </c>
-      <c r="D64" s="111" t="inlineStr">
+      <c r="D68" s="111" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="E64" s="111" t="inlineStr">
+      <c r="E68" s="111" t="inlineStr">
         <is>
           <t>ne</t>
         </is>
       </c>
-      <c r="F64" s="111" t="inlineStr">
+      <c r="F68" s="111" t="inlineStr">
         <is>
           <t>ベンガル語</t>
         </is>
       </c>
-      <c r="G64" s="111" t="inlineStr">
+      <c r="G68" s="111" t="inlineStr">
         <is>
           <t>インドネシア語</t>
         </is>
       </c>
-      <c r="H64" s="111" t="inlineStr">
+      <c r="H68" s="111" t="inlineStr">
         <is>
           <t>韓国語</t>
         </is>
       </c>
-      <c r="I64" s="111" t="inlineStr">
+      <c r="I68" s="111" t="inlineStr">
         <is>
           <t>ミャンマー語</t>
         </is>
       </c>
-      <c r="J64" s="111" t="inlineStr">
+      <c r="J68" s="111" t="inlineStr">
         <is>
           <t>タイ語</t>
         </is>
       </c>
-      <c r="K64" s="111" t="inlineStr">
+      <c r="K68" s="111" t="inlineStr">
         <is>
           <t>ベトナム語</t>
         </is>
       </c>
-      <c r="L64" s="111" t="inlineStr">
+      <c r="L68" s="111" t="inlineStr">
         <is>
           <t>中国語</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="112" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="112" t="inlineStr">
         <is>
           <t>■ 漢字（5種）</t>
         </is>
       </c>
-      <c r="B65" s="85" t="n"/>
-      <c r="C65" s="85" t="n"/>
-      <c r="D65" s="85" t="n"/>
-      <c r="E65" s="85" t="n"/>
-      <c r="F65" s="85" t="n"/>
-      <c r="G65" s="85" t="n"/>
-      <c r="H65" s="85" t="n"/>
-      <c r="I65" s="85" t="n"/>
-      <c r="J65" s="85" t="n"/>
-      <c r="K65" s="85" t="n"/>
-      <c r="L65" s="85" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="86" t="inlineStr">
+      <c r="B69" s="85" t="n"/>
+      <c r="C69" s="85" t="n"/>
+      <c r="D69" s="85" t="n"/>
+      <c r="E69" s="85" t="n"/>
+      <c r="F69" s="85" t="n"/>
+      <c r="G69" s="85" t="n"/>
+      <c r="H69" s="85" t="n"/>
+      <c r="I69" s="85" t="n"/>
+      <c r="J69" s="85" t="n"/>
+      <c r="K69" s="85" t="n"/>
+      <c r="L69" s="85" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="86" t="inlineStr">
         <is>
           <t>書き取り</t>
         </is>
       </c>
-      <c r="B66" s="85" t="inlineStr">
+      <c r="B70" s="85" t="inlineStr">
         <is>
           <t>字をなぞって手書き</t>
         </is>
       </c>
-      <c r="C66" s="85" t="inlineStr">
+      <c r="C70" s="85" t="inlineStr">
         <is>
           <t>日本語のみ（かな・字／翻訳不要）</t>
         </is>
       </c>
-      <c r="D66" s="146" t="inlineStr">
+      <c r="D70" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E66" s="146" t="inlineStr">
+      <c r="E70" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F66" s="146" t="inlineStr">
+      <c r="F70" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G66" s="146" t="inlineStr">
+      <c r="G70" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H66" s="146" t="inlineStr">
+      <c r="H70" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I66" s="146" t="inlineStr">
+      <c r="I70" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J66" s="146" t="inlineStr">
+      <c r="J70" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K66" s="146" t="inlineStr">
+      <c r="K70" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L66" s="146" t="inlineStr">
+      <c r="L70" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="86" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="86" t="inlineStr">
         <is>
           <t>意味</t>
         </is>
       </c>
-      <c r="B67" s="85" t="inlineStr">
+      <c r="B71" s="85" t="inlineStr">
         <is>
           <t>字→意味を4択</t>
         </is>
       </c>
-      <c r="C67" s="85" t="inlineStr">
+      <c r="C71" s="85" t="inlineStr">
         <is>
           <t>辞書の意味を流用</t>
         </is>
       </c>
-      <c r="D67" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E67" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F67" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G67" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H67" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I67" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J67" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K67" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L67" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="86" t="inlineStr">
+      <c r="D71" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E71" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F71" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G71" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H71" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I71" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J71" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K71" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L71" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="86" t="inlineStr">
         <is>
           <t>読み</t>
         </is>
       </c>
-      <c r="B68" s="85" t="inlineStr">
+      <c r="B72" s="85" t="inlineStr">
         <is>
           <t>字→読みを4択</t>
         </is>
       </c>
-      <c r="C68" s="85" t="inlineStr">
+      <c r="C72" s="85" t="inlineStr">
         <is>
           <t>日本語のみ（かな／翻訳不要）</t>
         </is>
       </c>
-      <c r="D68" s="146" t="inlineStr">
+      <c r="D72" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E68" s="146" t="inlineStr">
+      <c r="E72" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F68" s="146" t="inlineStr">
+      <c r="F72" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G68" s="146" t="inlineStr">
+      <c r="G72" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H68" s="146" t="inlineStr">
+      <c r="H72" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I68" s="146" t="inlineStr">
+      <c r="I72" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J68" s="146" t="inlineStr">
+      <c r="J72" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K68" s="146" t="inlineStr">
+      <c r="K72" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L68" s="146" t="inlineStr">
+      <c r="L72" s="146" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="82" t="inlineStr">
-        <is>
-          <t>似た字の見分け</t>
-        </is>
-      </c>
-      <c r="B69" s="82" t="inlineStr">
-        <is>
-          <t>似た字4択→正しい字</t>
-        </is>
-      </c>
-      <c r="C69" s="82" t="inlineStr">
-        <is>
-          <t>日本語のみ（字／翻訳不要）</t>
-        </is>
-      </c>
-      <c r="D69" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J69" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="82" t="inlineStr">
-        <is>
-          <t>聞き取り</t>
-        </is>
-      </c>
-      <c r="B70" s="82" t="inlineStr">
-        <is>
-          <t>🔊読み→字を4択</t>
-        </is>
-      </c>
-      <c r="C70" s="82" t="inlineStr">
-        <is>
-          <t>日本語のみ（音声・字／翻訳不要）</t>
-        </is>
-      </c>
-      <c r="D70" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J70" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="116" t="inlineStr">
-        <is>
-          <t>■ 語彙（5種）</t>
-        </is>
-      </c>
-      <c r="B71" s="82" t="n"/>
-      <c r="C71" s="82" t="n"/>
-      <c r="D71" s="82" t="n"/>
-      <c r="E71" s="82" t="n"/>
-      <c r="F71" s="82" t="n"/>
-      <c r="G71" s="82" t="n"/>
-      <c r="H71" s="82" t="n"/>
-      <c r="I71" s="82" t="n"/>
-      <c r="J71" s="82" t="n"/>
-      <c r="K71" s="82" t="n"/>
-      <c r="L71" s="82" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="82" t="inlineStr">
-        <is>
-          <t>意味</t>
-        </is>
-      </c>
-      <c r="B72" s="82" t="inlineStr">
-        <is>
-          <t>語→意味を4択</t>
-        </is>
-      </c>
-      <c r="C72" s="82" t="inlineStr">
-        <is>
-          <t>辞書の意味を流用</t>
-        </is>
-      </c>
-      <c r="D72" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E72" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F72" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G72" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H72" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I72" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J72" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K72" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L72" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="82" t="inlineStr">
         <is>
-          <t>読み</t>
+          <t>似た字の見分け</t>
         </is>
       </c>
       <c r="B73" s="82" t="inlineStr">
         <is>
-          <t>語→読みを4択</t>
+          <t>似た字4択→正しい字</t>
         </is>
       </c>
       <c r="C73" s="82" t="inlineStr">
         <is>
-          <t>日本語のみ（かな／翻訳不要）</t>
+          <t>日本語のみ（字／翻訳不要）</t>
         </is>
       </c>
       <c r="D73" s="149" t="inlineStr">
@@ -12387,141 +12369,97 @@
     <row r="74">
       <c r="A74" s="82" t="inlineStr">
         <is>
-          <t>表記</t>
+          <t>聞き取り</t>
         </is>
       </c>
       <c r="B74" s="82" t="inlineStr">
         <is>
-          <t>意味→漢字表記を4択</t>
+          <t>🔊読み→字を4択</t>
         </is>
       </c>
       <c r="C74" s="82" t="inlineStr">
         <is>
-          <t>辞書の意味を流用</t>
-        </is>
-      </c>
-      <c r="D74" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E74" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F74" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G74" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H74" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I74" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J74" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K74" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L74" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>日本語のみ（音声・字／翻訳不要）</t>
+        </is>
+      </c>
+      <c r="D74" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J74" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="82" t="inlineStr">
-        <is>
-          <t>聞き取り</t>
-        </is>
-      </c>
-      <c r="B75" s="82" t="inlineStr">
-        <is>
-          <t>🔊読み→意味を4択</t>
-        </is>
-      </c>
-      <c r="C75" s="82" t="inlineStr">
-        <is>
-          <t>辞書の意味を流用</t>
-        </is>
-      </c>
-      <c r="D75" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E75" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F75" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G75" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H75" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I75" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J75" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K75" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L75" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
+      <c r="A75" s="116" t="inlineStr">
+        <is>
+          <t>■ 語彙（5種）</t>
+        </is>
+      </c>
+      <c r="B75" s="82" t="n"/>
+      <c r="C75" s="82" t="n"/>
+      <c r="D75" s="82" t="n"/>
+      <c r="E75" s="82" t="n"/>
+      <c r="F75" s="82" t="n"/>
+      <c r="G75" s="82" t="n"/>
+      <c r="H75" s="82" t="n"/>
+      <c r="I75" s="82" t="n"/>
+      <c r="J75" s="82" t="n"/>
+      <c r="K75" s="82" t="n"/>
+      <c r="L75" s="82" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="82" t="inlineStr">
         <is>
-          <t>語彙パズル</t>
+          <t>意味</t>
         </is>
       </c>
       <c r="B76" s="82" t="inlineStr">
         <is>
-          <t>意味→かなタイルで語を作る</t>
+          <t>語→意味を4択</t>
         </is>
       </c>
       <c r="C76" s="82" t="inlineStr">
         <is>
-          <t>辞書の意味を流用（意味を提示）</t>
+          <t>辞書の意味を流用</t>
         </is>
       </c>
       <c r="D76" s="150" t="inlineStr">
@@ -12571,32 +12509,76 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="116" t="inlineStr">
-        <is>
-          <t>■ 文法（2種）</t>
-        </is>
-      </c>
-      <c r="B77" s="82" t="n"/>
-      <c r="C77" s="82" t="n"/>
-      <c r="D77" s="82" t="n"/>
-      <c r="E77" s="82" t="n"/>
-      <c r="F77" s="82" t="n"/>
-      <c r="G77" s="82" t="n"/>
-      <c r="H77" s="82" t="n"/>
-      <c r="I77" s="82" t="n"/>
-      <c r="J77" s="82" t="n"/>
-      <c r="K77" s="82" t="n"/>
-      <c r="L77" s="82" t="n"/>
+      <c r="A77" s="82" t="inlineStr">
+        <is>
+          <t>読み</t>
+        </is>
+      </c>
+      <c r="B77" s="82" t="inlineStr">
+        <is>
+          <t>語→読みを4択</t>
+        </is>
+      </c>
+      <c r="C77" s="82" t="inlineStr">
+        <is>
+          <t>日本語のみ（かな／翻訳不要）</t>
+        </is>
+      </c>
+      <c r="D77" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J77" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="82" t="inlineStr">
         <is>
-          <t>意味</t>
+          <t>表記</t>
         </is>
       </c>
       <c r="B78" s="82" t="inlineStr">
         <is>
-          <t>文法点→意味を4択</t>
+          <t>意味→漢字表記を4択</t>
         </is>
       </c>
       <c r="C78" s="82" t="inlineStr">
@@ -12653,17 +12635,17 @@
     <row r="79">
       <c r="A79" s="82" t="inlineStr">
         <is>
-          <t>パズル</t>
+          <t>聞き取り</t>
         </is>
       </c>
       <c r="B79" s="82" t="inlineStr">
         <is>
-          <t>例文の穴に文法語をタイルで作る</t>
+          <t>🔊読み→意味を4択</t>
         </is>
       </c>
       <c r="C79" s="82" t="inlineStr">
         <is>
-          <t>辞書の意味を流用（ヒントに意味）</t>
+          <t>辞書の意味を流用</t>
         </is>
       </c>
       <c r="D79" s="150" t="inlineStr">
@@ -12713,27 +12695,71 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="90" t="inlineStr">
-        <is>
-          <t>※ ドリルは辞書データから自動生成。意味を見せる面（意味／表記／聞き取り〈語彙〉／各パズル）は辞書の en/ne をそのまま使うので、辞書の翻訳率＝ドリルの翻訳率（＝100%）。専用の翻訳データは持たない。</t>
-        </is>
-      </c>
-      <c r="B80" s="82" t="n"/>
-      <c r="C80" s="82" t="n"/>
-      <c r="D80" s="82" t="n"/>
-      <c r="E80" s="82" t="n"/>
-      <c r="F80" s="82" t="n"/>
-      <c r="G80" s="82" t="n"/>
-      <c r="H80" s="82" t="n"/>
-      <c r="I80" s="82" t="n"/>
-      <c r="J80" s="82" t="n"/>
-      <c r="K80" s="82" t="n"/>
-      <c r="L80" s="82" t="n"/>
+      <c r="A80" s="82" t="inlineStr">
+        <is>
+          <t>語彙パズル</t>
+        </is>
+      </c>
+      <c r="B80" s="82" t="inlineStr">
+        <is>
+          <t>意味→かなタイルで語を作る</t>
+        </is>
+      </c>
+      <c r="C80" s="82" t="inlineStr">
+        <is>
+          <t>辞書の意味を流用（意味を提示）</t>
+        </is>
+      </c>
+      <c r="D80" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E80" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F80" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G80" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H80" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I80" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J80" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K80" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L80" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="90" t="inlineStr">
-        <is>
-          <t>※ 読み・書き取り・似た字の見分け・聞き取り〈漢字〉は かな／字／音声だけで解くため翻訳不要。旧版で「産出パズルは翻訳不要」としていたのは誤り＝意味を提示するため辞書流用100%。</t>
+      <c r="A81" s="116" t="inlineStr">
+        <is>
+          <t>■ 文法（2種）</t>
         </is>
       </c>
       <c r="B81" s="82" t="n"/>
@@ -12748,30 +12774,189 @@
       <c r="K81" s="82" t="n"/>
       <c r="L81" s="82" t="n"/>
     </row>
-    <row r="82"/>
+    <row r="82">
+      <c r="A82" s="82" t="inlineStr">
+        <is>
+          <t>意味</t>
+        </is>
+      </c>
+      <c r="B82" s="82" t="inlineStr">
+        <is>
+          <t>文法点→意味を4択</t>
+        </is>
+      </c>
+      <c r="C82" s="82" t="inlineStr">
+        <is>
+          <t>辞書の意味を流用</t>
+        </is>
+      </c>
+      <c r="D82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
     <row r="83">
-      <c r="A83" s="91" t="inlineStr">
-        <is>
-          <t>まとめ</t>
+      <c r="A83" s="82" t="inlineStr">
+        <is>
+          <t>パズル</t>
+        </is>
+      </c>
+      <c r="B83" s="82" t="inlineStr">
+        <is>
+          <t>例文の穴に文法語をタイルで作る</t>
+        </is>
+      </c>
+      <c r="C83" s="82" t="inlineStr">
+        <is>
+          <t>辞書の意味を流用（ヒントに意味）</t>
+        </is>
+      </c>
+      <c r="D83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="90" t="inlineStr">
         <is>
-          <t>・完全対応は ja / en / ne の3言語。アプリのどこを開いても日本語・英語・ネパール語で読める。</t>
-        </is>
-      </c>
+          <t>※ ドリルは辞書データから自動生成。意味を見せる面（意味／表記／聞き取り〈語彙〉／各パズル）は辞書の en/ne をそのまま使うので、辞書の翻訳率＝ドリルの翻訳率（＝100%）。専用の翻訳データは持たない。</t>
+        </is>
+      </c>
+      <c r="B84" s="82" t="n"/>
+      <c r="C84" s="82" t="n"/>
+      <c r="D84" s="82" t="n"/>
+      <c r="E84" s="82" t="n"/>
+      <c r="F84" s="82" t="n"/>
+      <c r="G84" s="82" t="n"/>
+      <c r="H84" s="82" t="n"/>
+      <c r="I84" s="82" t="n"/>
+      <c r="J84" s="82" t="n"/>
+      <c r="K84" s="82" t="n"/>
+      <c r="L84" s="82" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="90" t="inlineStr">
         <is>
+          <t>※ 読み・書き取り・似た字の見分け・聞き取り〈漢字〉は かな／字／音声だけで解くため翻訳不要。旧版で「産出パズルは翻訳不要」としていたのは誤り＝意味を提示するため辞書流用100%。</t>
+        </is>
+      </c>
+      <c r="B85" s="82" t="n"/>
+      <c r="C85" s="82" t="n"/>
+      <c r="D85" s="82" t="n"/>
+      <c r="E85" s="82" t="n"/>
+      <c r="F85" s="82" t="n"/>
+      <c r="G85" s="82" t="n"/>
+      <c r="H85" s="82" t="n"/>
+      <c r="I85" s="82" t="n"/>
+      <c r="J85" s="82" t="n"/>
+      <c r="K85" s="82" t="n"/>
+      <c r="L85" s="82" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="91" t="inlineStr">
+        <is>
+          <t>まとめ</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="90" t="inlineStr">
+        <is>
+          <t>・完全対応は ja / en / ne の3言語。アプリのどこを開いても日本語・英語・ネパール語で読める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="90" t="inlineStr">
+        <is>
           <t>・残り7言語(bn/id/ko/my/th/vi/zh)＝UIは全キー翻訳済(100%)。辞書は7言語すべて完了(id 2026-09-05／bn/ko/my/th/vi/zh 2026-09-05)。全7言語の問題訳は未着手。</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="90" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="90" t="inlineStr">
         <is>
           <t>・7言語フル対応には 各問題の対訳 が必要（辞書は全7言語完了済）。UIは全言語対応済。</t>
         </is>
@@ -12779,17 +12964,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A65:I65"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A63:I63"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A42:I42"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A40:I40"/>
     <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A61:I61"/>
-    <mergeCell ref="A38:I38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -12934,6 +12934,7 @@
       <c r="K85" s="82" t="n"/>
       <c r="L85" s="82" t="n"/>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" s="91" t="inlineStr">
         <is>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -9593,7 +9593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="26" customWidth="1" style="75" min="1" max="1"/>
@@ -9620,7 +9620,7 @@
     <row r="2">
       <c r="A2" s="76" t="inlineStr">
         <is>
-          <t>フル対応＝日本語(ja)・英語(en)・ネパール語(ne) の3言語。残り7言語(bn/id/ko/my/th/vi/zh)はUIを全キー翻訳済(2026-09)。辞書・問題・例文は未着手。※UIは番人が無く今後の追加分は陳腐化しうる。</t>
+          <t>フル対応＝全11言語(ja/en/ne/bn/id/ko/my/th/vi/zh/zh2)。UIは全キー翻訳済み。新規UIキーは番人(parity.test.ts・全11言語)＋build時の自動翻訳(trans_i18n.py --fill)で常時同期。辞書・問題・例文は下記。</t>
         </is>
       </c>
     </row>
@@ -9635,7 +9635,7 @@
     <row r="5">
       <c r="A5" s="77" t="inlineStr">
         <is>
-          <t>① 表示言語 10種の対応ぐあい（ざっくり）</t>
+          <t>① 表示言語 11種の対応ぐあい（ざっくり）</t>
         </is>
       </c>
     </row>
@@ -10101,75 +10101,94 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="77" t="inlineStr">
-        <is>
-          <t>② UI（画面の文字）　ja=1422 キーが元</t>
-        </is>
-      </c>
-    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>zh2（中国語・繁体）</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>母語</t>
+        </is>
+      </c>
+      <c r="C17" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D17" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E17" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F17" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G17" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="124" t="inlineStr">
+        <is>
+          <t>フル</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
-      <c r="A19" s="64" t="inlineStr">
+      <c r="A19" s="77" t="inlineStr">
+        <is>
+          <t>② UI（画面の文字）　ja=1432 キーが元（全11言語=番人＋自動翻訳で常時100%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="64" t="inlineStr">
         <is>
           <t>言語</t>
         </is>
       </c>
-      <c r="B19" s="64" t="inlineStr">
+      <c r="B20" s="64" t="inlineStr">
         <is>
           <t>訳済みキー数</t>
         </is>
       </c>
-      <c r="C19" s="64" t="inlineStr">
+      <c r="C20" s="64" t="inlineStr">
         <is>
           <t>総キー</t>
         </is>
       </c>
-      <c r="D19" s="64" t="inlineStr">
+      <c r="D20" s="64" t="inlineStr">
         <is>
           <t>カバー率</t>
         </is>
       </c>
-      <c r="E19" s="64" t="inlineStr">
+      <c r="E20" s="64" t="inlineStr">
         <is>
           <t>状態</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="65" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="B20" s="67" t="n">
-        <v>1422</v>
-      </c>
-      <c r="C20" s="66" t="n">
-        <v>1422</v>
-      </c>
-      <c r="D20" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E20" s="138" t="inlineStr">
-        <is>
-          <t>元</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="65" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="B21" s="67" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="C21" s="66" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="D21" s="138" t="inlineStr">
         <is>
@@ -10178,21 +10197,21 @@
       </c>
       <c r="E21" s="138" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>元</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="65" t="inlineStr">
         <is>
-          <t>ne</t>
+          <t>en</t>
         </is>
       </c>
       <c r="B22" s="67" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="C22" s="66" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="D22" s="138" t="inlineStr">
         <is>
@@ -10208,14 +10227,14 @@
     <row r="23">
       <c r="A23" s="65" t="inlineStr">
         <is>
-          <t>bn</t>
+          <t>ne</t>
         </is>
       </c>
       <c r="B23" s="67" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="C23" s="66" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="D23" s="138" t="inlineStr">
         <is>
@@ -10231,14 +10250,14 @@
     <row r="24">
       <c r="A24" s="65" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>bn</t>
         </is>
       </c>
       <c r="B24" s="67" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="C24" s="66" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="D24" s="138" t="inlineStr">
         <is>
@@ -10254,14 +10273,14 @@
     <row r="25">
       <c r="A25" s="65" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B25" s="67" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="C25" s="66" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="D25" s="138" t="inlineStr">
         <is>
@@ -10277,14 +10296,14 @@
     <row r="26">
       <c r="A26" s="65" t="inlineStr">
         <is>
-          <t>my</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="B26" s="67" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="C26" s="66" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="D26" s="138" t="inlineStr">
         <is>
@@ -10300,14 +10319,14 @@
     <row r="27">
       <c r="A27" s="65" t="inlineStr">
         <is>
-          <t>th</t>
+          <t>my</t>
         </is>
       </c>
       <c r="B27" s="67" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="C27" s="66" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="D27" s="138" t="inlineStr">
         <is>
@@ -10323,14 +10342,14 @@
     <row r="28">
       <c r="A28" s="65" t="inlineStr">
         <is>
-          <t>vi</t>
+          <t>th</t>
         </is>
       </c>
       <c r="B28" s="67" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="C28" s="66" t="n">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="D28" s="138" t="inlineStr">
         <is>
@@ -10346,231 +10365,157 @@
     <row r="29">
       <c r="A29" s="65" t="inlineStr">
         <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="B29" s="67" t="n">
+        <v>1432</v>
+      </c>
+      <c r="C29" s="66" t="n">
+        <v>1432</v>
+      </c>
+      <c r="D29" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E29" s="138" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="65" t="inlineStr">
+        <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="B29" s="67" t="n">
-        <v>1422</v>
-      </c>
-      <c r="C29" s="66" t="n">
-        <v>1422</v>
-      </c>
-      <c r="D29" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E29" s="138" t="inlineStr">
+      <c r="B30" s="67" t="n">
+        <v>1432</v>
+      </c>
+      <c r="C30" s="66" t="n">
+        <v>1432</v>
+      </c>
+      <c r="D30" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E30" s="138" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="76" t="inlineStr">
-        <is>
-          <t>※ en/ne は新規UIを作るたび必ず同時に訳す(番人 parity.test.ts)。他7言語は2026-09に全キー一括翻訳(23%→100%)。ただし番人が無いため今後の追加UIは未訳で陳腐化しうる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>zh2</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1432</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1432</v>
+      </c>
+      <c r="D31" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E31" s="124" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
-      <c r="A32" s="77" t="inlineStr">
+      <c r="A32" s="76" t="inlineStr">
+        <is>
+          <t>※ 新規UIキーは全11言語を同時に用意(2026-09-07変更)。en/neは手書き、他8言語(zh2=OpenCC)はtrans_i18n.py --fillが差分翻訳。番人parity.test.tsが全11言語を強制＋build.ps1が検証前に--fillを自動実行するため、未訳のまま出荷されない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="77" t="inlineStr">
         <is>
           <t>③ 辞書（語彙・漢字・文法・例文）</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="64" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="64" t="inlineStr">
         <is>
           <t>種類</t>
         </is>
       </c>
-      <c r="B33" s="64" t="inlineStr">
+      <c r="B35" s="64" t="inlineStr">
         <is>
           <t>総数</t>
         </is>
       </c>
-      <c r="C33" s="64" t="inlineStr">
+      <c r="C35" s="64" t="inlineStr">
         <is>
           <t>日本語(語/読み)</t>
         </is>
       </c>
-      <c r="D33" s="64" t="inlineStr">
+      <c r="D35" s="64" t="inlineStr">
         <is>
           <t>英語(意味)</t>
         </is>
       </c>
-      <c r="E33" s="64" t="inlineStr">
+      <c r="E35" s="64" t="inlineStr">
         <is>
           <t>ネパール語(意味)</t>
         </is>
       </c>
-      <c r="F33" s="64" t="inlineStr">
+      <c r="F35" s="64" t="inlineStr">
         <is>
           <t>ベンガル語</t>
         </is>
       </c>
-      <c r="G33" s="64" t="inlineStr">
+      <c r="G35" s="64" t="inlineStr">
         <is>
           <t>インドネシア語</t>
         </is>
       </c>
-      <c r="H33" s="64" t="inlineStr">
+      <c r="H35" s="64" t="inlineStr">
         <is>
           <t>韓国語</t>
         </is>
       </c>
-      <c r="I33" s="64" t="inlineStr">
+      <c r="I35" s="64" t="inlineStr">
         <is>
           <t>ミャンマー語</t>
         </is>
       </c>
-      <c r="J33" s="64" t="inlineStr">
+      <c r="J35" s="64" t="inlineStr">
         <is>
           <t>タイ語</t>
         </is>
       </c>
-      <c r="K33" s="64" t="inlineStr">
+      <c r="K35" s="64" t="inlineStr">
         <is>
           <t>ベトナム語</t>
         </is>
       </c>
-      <c r="L33" s="64" t="inlineStr">
+      <c r="L35" s="64" t="inlineStr">
         <is>
           <t>中国語</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="65" t="inlineStr">
-        <is>
-          <t>語彙（意味）</t>
-        </is>
-      </c>
-      <c r="B34" s="66" t="n">
-        <v>3540</v>
-      </c>
-      <c r="C34" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D34" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E34" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F34" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G34" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H34" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I34" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J34" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K34" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L34" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="65" t="inlineStr">
-        <is>
-          <t>漢字（意味・音訓）</t>
-        </is>
-      </c>
-      <c r="B35" s="66" t="n">
-        <v>612</v>
-      </c>
-      <c r="C35" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D35" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E35" s="138" t="inlineStr">
-        <is>
-          <t>100%（語義1859）</t>
-        </is>
-      </c>
-      <c r="F35" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G35" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H35" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I35" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J35" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K35" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L35" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="65" t="inlineStr">
         <is>
-          <t>文法（意味・例文）</t>
+          <t>語彙（意味）</t>
         </is>
       </c>
       <c r="B36" s="66" t="n">
-        <v>408</v>
+        <v>3540</v>
       </c>
       <c r="C36" s="138" t="inlineStr">
         <is>
@@ -10626,556 +10571,550 @@
     <row r="37">
       <c r="A37" s="65" t="inlineStr">
         <is>
+          <t>漢字（意味・音訓）</t>
+        </is>
+      </c>
+      <c r="B37" s="66" t="n">
+        <v>612</v>
+      </c>
+      <c r="C37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E37" s="138" t="inlineStr">
+        <is>
+          <t>100%（語義1859）</t>
+        </is>
+      </c>
+      <c r="F37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L37" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="65" t="inlineStr">
+        <is>
+          <t>文法（意味・例文）</t>
+        </is>
+      </c>
+      <c r="B38" s="66" t="n">
+        <v>408</v>
+      </c>
+      <c r="C38" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D38" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E38" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F38" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G38" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K38" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L38" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="65" t="inlineStr">
+        <is>
           <t>例文（辞書タブ）</t>
         </is>
       </c>
-      <c r="B37" s="66" t="n">
+      <c r="B39" s="66" t="n">
         <v>3524</v>
       </c>
-      <c r="C37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E37" s="138" t="inlineStr">
+      <c r="C39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E39" s="138" t="inlineStr">
         <is>
           <t>100%（3524）</t>
         </is>
       </c>
-      <c r="F37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="173" t="inlineStr">
+      <c r="F39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="173" t="inlineStr">
         <is>
           <t>辞書訳 出力字数(参考)</t>
         </is>
       </c>
-      <c r="B38" s="174" t="n"/>
-      <c r="C38" s="174" t="n"/>
-      <c r="E38" s="174" t="n"/>
-      <c r="F38" s="175" t="n">
+      <c r="B40" s="174" t="n"/>
+      <c r="C40" s="174" t="n"/>
+      <c r="E40" s="174" t="n"/>
+      <c r="F40" s="175" t="n">
         <v>344226</v>
       </c>
-      <c r="G38" s="175" t="n">
+      <c r="G40" s="175" t="n">
         <v>388928</v>
       </c>
-      <c r="H38" s="175" t="n">
+      <c r="H40" s="175" t="n">
         <v>151711</v>
       </c>
-      <c r="I38" s="175" t="n">
+      <c r="I40" s="175" t="n">
         <v>375205</v>
       </c>
-      <c r="J38" s="175" t="n">
+      <c r="J40" s="175" t="n">
         <v>303788</v>
       </c>
-      <c r="K38" s="175" t="n">
+      <c r="K40" s="175" t="n">
         <v>351959</v>
       </c>
-      <c r="L38" s="175" t="n">
+      <c r="L40" s="175" t="n">
         <v>102244</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="173" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="173" t="inlineStr">
         <is>
           <t>辞書訳 概算実費(参考・Gemini2.5Flash・6言語計≈¥327/通算≈¥405)</t>
         </is>
       </c>
-      <c r="B39" s="174" t="n"/>
-      <c r="C39" s="174" t="n"/>
-      <c r="D39" s="176" t="inlineStr">
+      <c r="B41" s="174" t="n"/>
+      <c r="C41" s="174" t="n"/>
+      <c r="D41" s="176" t="inlineStr">
         <is>
           <t>¥0(元)</t>
         </is>
       </c>
-      <c r="E39" s="174" t="n"/>
-      <c r="F39" s="176" t="inlineStr">
+      <c r="E41" s="174" t="n"/>
+      <c r="F41" s="176" t="inlineStr">
         <is>
           <t>≈¥69</t>
         </is>
       </c>
-      <c r="G39" s="176" t="inlineStr">
+      <c r="G41" s="176" t="inlineStr">
         <is>
           <t>¥78</t>
         </is>
       </c>
-      <c r="H39" s="176" t="inlineStr">
+      <c r="H41" s="176" t="inlineStr">
         <is>
           <t>≈¥30</t>
         </is>
       </c>
-      <c r="I39" s="176" t="inlineStr">
+      <c r="I41" s="176" t="inlineStr">
         <is>
           <t>≈¥75</t>
         </is>
       </c>
-      <c r="J39" s="176" t="inlineStr">
+      <c r="J41" s="176" t="inlineStr">
         <is>
           <t>≈¥61</t>
         </is>
       </c>
-      <c r="K39" s="176" t="inlineStr">
+      <c r="K41" s="176" t="inlineStr">
         <is>
           <t>≈¥71</t>
         </is>
       </c>
-      <c r="L39" s="176" t="inlineStr">
+      <c r="L41" s="176" t="inlineStr">
         <is>
           <t>≈¥21</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="76" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="76" t="inlineStr">
         <is>
           <t>※ 英語＝同梱データに最初から入っている意味。ネパール語＝配信(OTA)の上書き層 content/lexicon で全件対応済（meaning=4561件＝語彙+漢字+文法の全意味）。 ／ インドネシア語(id)＝辞書全4種(意味4560+漢字グロス1859+例文3524+文法例文408)を2026-09-05に翻訳(Gemini・content/lexicon に id 追記・app改修不要)。</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="105" t="inlineStr">
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="105" t="inlineStr">
         <is>
           <t>④ 各大問（問題）の翻訳　※問題文は日本語。ここは『読解本文』などの対訳と、解説の翻訳の話</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="106" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="106" t="inlineStr">
         <is>
           <t>大問</t>
         </is>
       </c>
-      <c r="B43" s="106" t="inlineStr">
+      <c r="B45" s="106" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="C43" s="106" t="inlineStr">
+      <c r="C45" s="106" t="inlineStr">
         <is>
           <t>模試</t>
         </is>
       </c>
-      <c r="D43" s="106" t="inlineStr">
+      <c r="D45" s="106" t="inlineStr">
         <is>
           <t>翻訳の種類</t>
         </is>
       </c>
-      <c r="E43" s="106" t="inlineStr">
+      <c r="E45" s="106" t="inlineStr">
         <is>
           <t>英語(en)</t>
         </is>
       </c>
-      <c r="F43" s="106" t="inlineStr">
+      <c r="F45" s="106" t="inlineStr">
         <is>
           <t>ネパール語(ne)</t>
         </is>
       </c>
-      <c r="G43" s="107" t="inlineStr">
+      <c r="G45" s="107" t="inlineStr">
         <is>
           <t>ベンガル語</t>
         </is>
       </c>
-      <c r="H43" s="107" t="inlineStr">
+      <c r="H45" s="107" t="inlineStr">
         <is>
           <t>インドネシア語</t>
         </is>
       </c>
-      <c r="I43" s="107" t="inlineStr">
+      <c r="I45" s="107" t="inlineStr">
         <is>
           <t>韓国語</t>
         </is>
       </c>
-      <c r="J43" s="107" t="inlineStr">
+      <c r="J45" s="107" t="inlineStr">
         <is>
           <t>ミャンマー語</t>
         </is>
       </c>
-      <c r="K43" s="107" t="inlineStr">
+      <c r="K45" s="107" t="inlineStr">
         <is>
           <t>タイ語</t>
         </is>
       </c>
-      <c r="L43" s="107" t="inlineStr">
+      <c r="L45" s="107" t="inlineStr">
         <is>
           <t>ベトナム語</t>
         </is>
       </c>
-      <c r="M43" s="107" t="inlineStr">
+      <c r="M45" s="107" t="inlineStr">
         <is>
           <t>中国語</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="94" t="inlineStr">
-        <is>
-          <t>文字語彙・文脈規定</t>
-        </is>
-      </c>
-      <c r="B44" s="95" t="n">
-        <v>3464</v>
-      </c>
-      <c r="C44" s="95" t="n">
-        <v>310</v>
-      </c>
-      <c r="D44" s="94" t="inlineStr">
-        <is>
-          <t>本文の対訳</t>
-        </is>
-      </c>
-      <c r="E44" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F44" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G44" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H44" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I44" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J44" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K44" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L44" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M44" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="94" t="inlineStr">
-        <is>
-          <t>文字語彙・漢字読み</t>
-        </is>
-      </c>
-      <c r="B45" s="95" t="n">
-        <v>3204</v>
-      </c>
-      <c r="C45" s="95" t="n">
-        <v>274</v>
-      </c>
-      <c r="D45" s="94" t="inlineStr">
-        <is>
-          <t>訳なし（下線語の解読課題・意味は問わず不要）</t>
-        </is>
-      </c>
-      <c r="E45" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J45" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K45" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L45" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M45" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="94" t="inlineStr">
         <is>
-          <t>文字語彙・表記</t>
+          <t>文字語彙・文脈規定</t>
         </is>
       </c>
       <c r="B46" s="95" t="n">
-        <v>3350</v>
+        <v>3464</v>
       </c>
       <c r="C46" s="95" t="n">
-        <v>200</v>
+        <v>310</v>
       </c>
       <c r="D46" s="94" t="inlineStr">
         <is>
-          <t>訳なし（下線語の解読課題・意味は問わず不要）</t>
-        </is>
-      </c>
-      <c r="E46" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F46" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J46" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K46" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L46" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M46" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>本文の対訳</t>
+        </is>
+      </c>
+      <c r="E46" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F46" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G46" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H46" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I46" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J46" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K46" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L46" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M46" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="94" t="inlineStr">
         <is>
-          <t>文字語彙・言い換え</t>
+          <t>文字語彙・漢字読み</t>
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>2255</v>
+        <v>3204</v>
       </c>
       <c r="C47" s="95" t="n">
-        <v>150</v>
+        <v>274</v>
       </c>
       <c r="D47" s="94" t="inlineStr">
         <is>
-          <t>本文＋選択肢の対訳（回答後表示・誤答も正当な語ゆえ訳す・2026-09）</t>
-        </is>
-      </c>
-      <c r="E47" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F47" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G47" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H47" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I47" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J47" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K47" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L47" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M47" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>訳なし（下線語の解読課題・意味は問わず不要）</t>
+        </is>
+      </c>
+      <c r="E47" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K47" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L47" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M47" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="94" t="inlineStr">
         <is>
-          <t>文字語彙・用法</t>
+          <t>文字語彙・表記</t>
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>1171</v>
+        <v>3350</v>
       </c>
       <c r="C48" s="95" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D48" s="94" t="inlineStr">
         <is>
-          <t>正解の文の対訳（回答後表示・誤答は不自然文ゆえ訳さず・2026-09）</t>
-        </is>
-      </c>
-      <c r="E48" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F48" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G48" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H48" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I48" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J48" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K48" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L48" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M48" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>訳なし（下線語の解読課題・意味は問わず不要）</t>
+        </is>
+      </c>
+      <c r="E48" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J48" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K48" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L48" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M48" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="94" t="inlineStr">
         <is>
-          <t>文法・穴埋め</t>
+          <t>文字語彙・言い換え</t>
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>1207</v>
+        <v>2255</v>
       </c>
       <c r="C49" s="95" t="n">
-        <v>440</v>
+        <v>150</v>
       </c>
       <c r="D49" s="94" t="inlineStr">
         <is>
-          <t>完成文の対訳（回答後表示・選択肢=文法パーツは訳さず・2026-09）</t>
+          <t>本文＋選択肢の対訳（回答後表示・誤答も正当な語ゆえ訳す・2026-09）</t>
         </is>
       </c>
       <c r="E49" s="141" t="inlineStr">
@@ -11227,18 +11166,18 @@
     <row r="50">
       <c r="A50" s="94" t="inlineStr">
         <is>
-          <t>文法・並べ替え</t>
+          <t>文字語彙・用法</t>
         </is>
       </c>
       <c r="B50" s="95" t="n">
-        <v>673</v>
+        <v>1171</v>
       </c>
       <c r="C50" s="95" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D50" s="94" t="inlineStr">
         <is>
-          <t>正しい文＋母語訳（回答後表示・2026-09再翻訳）</t>
+          <t>正解の文の対訳（回答後表示・誤答は不自然文ゆえ訳さず・2026-09）</t>
         </is>
       </c>
       <c r="E50" s="141" t="inlineStr">
@@ -11290,18 +11229,18 @@
     <row r="51">
       <c r="A51" s="94" t="inlineStr">
         <is>
-          <t>文法・文章の文法</t>
+          <t>文法・穴埋め</t>
         </is>
       </c>
       <c r="B51" s="95" t="n">
-        <v>210</v>
+        <v>1207</v>
       </c>
       <c r="C51" s="95" t="n">
-        <v>30</v>
+        <v>440</v>
       </c>
       <c r="D51" s="94" t="inlineStr">
         <is>
-          <t>本文の対訳</t>
+          <t>完成文の対訳（回答後表示・選択肢=文法パーツは訳さず・2026-09）</t>
         </is>
       </c>
       <c r="E51" s="141" t="inlineStr">
@@ -11353,18 +11292,18 @@
     <row r="52">
       <c r="A52" s="94" t="inlineStr">
         <is>
-          <t>読解・内容理解(短)</t>
+          <t>文法・並べ替え</t>
         </is>
       </c>
       <c r="B52" s="95" t="n">
-        <v>330</v>
+        <v>673</v>
       </c>
       <c r="C52" s="95" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="D52" s="94" t="inlineStr">
         <is>
-          <t>本文の対訳（設問解説は廃止・本文訳は維持）</t>
+          <t>正しい文＋母語訳（回答後表示・2026-09再翻訳）</t>
         </is>
       </c>
       <c r="E52" s="141" t="inlineStr">
@@ -11416,14 +11355,14 @@
     <row r="53">
       <c r="A53" s="94" t="inlineStr">
         <is>
-          <t>読解・内容理解(中)</t>
+          <t>文法・文章の文法</t>
         </is>
       </c>
       <c r="B53" s="95" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="C53" s="95" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D53" s="94" t="inlineStr">
         <is>
@@ -11479,18 +11418,18 @@
     <row r="54">
       <c r="A54" s="94" t="inlineStr">
         <is>
-          <t>読解・長文</t>
+          <t>読解・内容理解(短)</t>
         </is>
       </c>
       <c r="B54" s="95" t="n">
-        <v>40</v>
+        <v>330</v>
       </c>
       <c r="C54" s="95" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="D54" s="94" t="inlineStr">
         <is>
-          <t>本文の対訳</t>
+          <t>本文の対訳（設問解説は廃止・本文訳は維持）</t>
         </is>
       </c>
       <c r="E54" s="141" t="inlineStr">
@@ -11542,81 +11481,81 @@
     <row r="55">
       <c r="A55" s="94" t="inlineStr">
         <is>
-          <t>読解・情報検索</t>
+          <t>読解・内容理解(中)</t>
         </is>
       </c>
       <c r="B55" s="95" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="C55" s="95" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D55" s="94" t="inlineStr">
         <is>
-          <t>訳なし（機械式・不要）</t>
-        </is>
-      </c>
-      <c r="E55" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I55" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J55" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K55" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L55" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M55" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>本文の対訳</t>
+        </is>
+      </c>
+      <c r="E55" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F55" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G55" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H55" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I55" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J55" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K55" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L55" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M55" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="94" t="inlineStr">
         <is>
-          <t>聴解・課題理解</t>
+          <t>読解・長文</t>
         </is>
       </c>
       <c r="B56" s="95" t="n">
-        <v>450</v>
+        <v>40</v>
       </c>
       <c r="C56" s="95" t="n">
-        <v>210</v>
+        <v>10</v>
       </c>
       <c r="D56" s="94" t="inlineStr">
         <is>
-          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-02）</t>
+          <t>本文の対訳</t>
         </is>
       </c>
       <c r="E56" s="141" t="inlineStr">
@@ -11668,81 +11607,81 @@
     <row r="57">
       <c r="A57" s="94" t="inlineStr">
         <is>
-          <t>聴解・ポイント理解</t>
+          <t>読解・情報検索</t>
         </is>
       </c>
       <c r="B57" s="95" t="n">
-        <v>450</v>
+        <v>180</v>
       </c>
       <c r="C57" s="95" t="n">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="D57" s="94" t="inlineStr">
         <is>
-          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-03）</t>
-        </is>
-      </c>
-      <c r="E57" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F57" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G57" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K57" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L57" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M57" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>訳なし（機械式・不要）</t>
+        </is>
+      </c>
+      <c r="E57" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J57" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K57" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L57" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M57" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="94" t="inlineStr">
         <is>
-          <t>聴解・概要理解</t>
+          <t>聴解・課題理解</t>
         </is>
       </c>
       <c r="B58" s="95" t="n">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="C58" s="95" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="D58" s="94" t="inlineStr">
         <is>
-          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-03・N3のみ）</t>
+          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-02）</t>
         </is>
       </c>
       <c r="E58" s="141" t="inlineStr">
@@ -11794,18 +11733,18 @@
     <row r="59">
       <c r="A59" s="94" t="inlineStr">
         <is>
-          <t>聴解・発話表現</t>
+          <t>聴解・ポイント理解</t>
         </is>
       </c>
       <c r="B59" s="95" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="C59" s="95" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="D59" s="94" t="inlineStr">
         <is>
-          <t>場面文(台本)＋選択肢の対訳（回答後表示・2026-09-03・設問文なし＝場面に合う一言を選ぶ）</t>
+          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-03）</t>
         </is>
       </c>
       <c r="E59" s="141" t="inlineStr">
@@ -11857,728 +11796,730 @@
     <row r="60">
       <c r="A60" s="94" t="inlineStr">
         <is>
+          <t>聴解・概要理解</t>
+        </is>
+      </c>
+      <c r="B60" s="95" t="n">
+        <v>80</v>
+      </c>
+      <c r="C60" s="95" t="n">
+        <v>30</v>
+      </c>
+      <c r="D60" s="94" t="inlineStr">
+        <is>
+          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-03・N3のみ）</t>
+        </is>
+      </c>
+      <c r="E60" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F60" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G60" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H60" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I60" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J60" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K60" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L60" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M60" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="94" t="inlineStr">
+        <is>
+          <t>聴解・発話表現</t>
+        </is>
+      </c>
+      <c r="B61" s="95" t="n">
+        <v>600</v>
+      </c>
+      <c r="C61" s="95" t="n">
+        <v>140</v>
+      </c>
+      <c r="D61" s="94" t="inlineStr">
+        <is>
+          <t>場面文(台本)＋選択肢の対訳（回答後表示・2026-09-03・設問文なし＝場面に合う一言を選ぶ）</t>
+        </is>
+      </c>
+      <c r="E61" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F61" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G61" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H61" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I61" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J61" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K61" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L61" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M61" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="94" t="inlineStr">
+        <is>
           <t>聴解・即時応答</t>
         </is>
       </c>
-      <c r="B60" s="95" t="n">
+      <c r="B62" s="95" t="n">
         <v>720</v>
       </c>
-      <c r="C60" s="95" t="n">
+      <c r="C62" s="95" t="n">
         <v>230</v>
       </c>
-      <c r="D60" s="94" t="inlineStr">
+      <c r="D62" s="94" t="inlineStr">
         <is>
           <t>場面文(台本)＋選択肢の対訳（回答後表示・2026-09-03・設問文なし＝相手の一言への返しを選ぶ）</t>
         </is>
       </c>
-      <c r="E60" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F60" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G60" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H60" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I60" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J60" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K60" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L60" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M60" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="177" t="inlineStr">
+      <c r="E62" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F62" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G62" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H62" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I62" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J62" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K62" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L62" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M62" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="177" t="inlineStr">
         <is>
           <t>◇大問訳 出力字数(参考)</t>
         </is>
       </c>
-      <c r="G61" s="175" t="n">
+      <c r="G63" s="175" t="n">
         <v>2785247</v>
       </c>
-      <c r="H61" s="175" t="n">
+      <c r="H63" s="175" t="n">
         <v>3401751</v>
       </c>
-      <c r="I61" s="175" t="n">
+      <c r="I63" s="175" t="n">
         <v>1447703</v>
       </c>
-      <c r="J61" s="175" t="n">
+      <c r="J63" s="175" t="n">
         <v>3294974</v>
       </c>
-      <c r="K61" s="175" t="n">
+      <c r="K63" s="175" t="n">
         <v>2646058</v>
       </c>
-      <c r="L61" s="175" t="n">
+      <c r="L63" s="175" t="n">
         <v>3046533</v>
       </c>
-      <c r="M61" s="175" t="n">
+      <c r="M63" s="175" t="n">
         <v>905106</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="177" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="177" t="inlineStr">
         <is>
           <t>◇大問訳 概算実費(参考・Gemini2.5Flash)</t>
         </is>
       </c>
-      <c r="G62" s="176" t="inlineStr">
+      <c r="G64" s="176" t="inlineStr">
         <is>
           <t>¥481</t>
         </is>
       </c>
-      <c r="H62" s="176" t="inlineStr">
+      <c r="H64" s="176" t="inlineStr">
         <is>
           <t>¥494</t>
         </is>
       </c>
-      <c r="I62" s="176" t="inlineStr">
+      <c r="I64" s="176" t="inlineStr">
         <is>
           <t>¥504</t>
         </is>
       </c>
-      <c r="J62" s="176" t="inlineStr">
+      <c r="J64" s="176" t="inlineStr">
         <is>
           <t>¥719</t>
         </is>
       </c>
-      <c r="K62" s="176" t="inlineStr">
+      <c r="K64" s="176" t="inlineStr">
         <is>
           <t>¥544</t>
         </is>
       </c>
-      <c r="L62" s="176" t="inlineStr">
+      <c r="L64" s="176" t="inlineStr">
         <is>
           <t>¥532</t>
         </is>
       </c>
-      <c r="M62" s="176" t="inlineStr">
+      <c r="M64" s="176" t="inlineStr">
         <is>
           <t>¥432</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="102" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="102" t="inlineStr">
         <is>
           <t>※ 通常＝学習プール、模試＝模試専用プール(初見)。旧「└ 漢字読み(模試プール)」サブ行は廃止し、全大問に模試列を新設。</t>
         </is>
       </c>
-      <c r="B63" s="103" t="n"/>
-      <c r="C63" s="103" t="n"/>
-      <c r="D63" s="103" t="n"/>
-      <c r="E63" s="103" t="n"/>
-      <c r="F63" s="103" t="n"/>
-      <c r="G63" s="103" t="n"/>
-      <c r="H63" s="103" t="n"/>
-      <c r="I63" s="104" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="90" t="inlineStr">
+      <c r="B65" s="103" t="n"/>
+      <c r="C65" s="103" t="n"/>
+      <c r="D65" s="103" t="n"/>
+      <c r="E65" s="103" t="n"/>
+      <c r="F65" s="103" t="n"/>
+      <c r="G65" s="103" t="n"/>
+      <c r="H65" s="103" t="n"/>
+      <c r="I65" s="104" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="90" t="inlineStr">
         <is>
           <t>※ 文脈規定は「解説の翻訳(旧ne38%)」を廃止し、本文の対訳(空所を答えで埋めた完成文の en/ne)へ移行済。表示＝回答後に本文の下。2026-09-02 完了(3774問)。</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="90" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="90" t="inlineStr">
         <is>
           <t>※ 聴解は音声台本(スクリプト)＋設問＋選択肢の対訳の有無を記載。全5大問=en/ne 100%完了・回答後表示（課題理解2026-09-02／ポイント理解・概要理解・発話表現・即時応答2026-09-03）。</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>※ 表記・漢字読みは『下線語を読む／漢字で書く』の解読問題で本文の意味は問わない（意味は辞書・意味ドリルで担保）。解説・母語訳は不要と判断し、表記の解説(en/ne 旧ne77%)を全削除。2026-09-02。</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="105" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="105" t="inlineStr">
         <is>
           <t>⑤ 各ドリル（単語タブの全ドリル｜漢字5・語彙5・文法2＝計12種）</t>
         </is>
       </c>
-      <c r="B67" s="82" t="n"/>
-      <c r="C67" s="82" t="n"/>
-      <c r="D67" s="82" t="n"/>
-      <c r="E67" s="82" t="n"/>
-      <c r="F67" s="82" t="n"/>
-      <c r="G67" s="82" t="n"/>
-      <c r="H67" s="82" t="n"/>
-      <c r="I67" s="82" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="111" t="inlineStr">
+      <c r="B69" s="82" t="n"/>
+      <c r="C69" s="82" t="n"/>
+      <c r="D69" s="82" t="n"/>
+      <c r="E69" s="82" t="n"/>
+      <c r="F69" s="82" t="n"/>
+      <c r="G69" s="82" t="n"/>
+      <c r="H69" s="82" t="n"/>
+      <c r="I69" s="82" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="111" t="inlineStr">
         <is>
           <t>ドリル</t>
         </is>
       </c>
-      <c r="B68" s="111" t="inlineStr">
+      <c r="B70" s="111" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C68" s="111" t="inlineStr">
+      <c r="C70" s="111" t="inlineStr">
         <is>
           <t>翻訳の出どころ</t>
         </is>
       </c>
-      <c r="D68" s="111" t="inlineStr">
+      <c r="D70" s="111" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="E68" s="111" t="inlineStr">
+      <c r="E70" s="111" t="inlineStr">
         <is>
           <t>ne</t>
         </is>
       </c>
-      <c r="F68" s="111" t="inlineStr">
+      <c r="F70" s="111" t="inlineStr">
         <is>
           <t>ベンガル語</t>
         </is>
       </c>
-      <c r="G68" s="111" t="inlineStr">
+      <c r="G70" s="111" t="inlineStr">
         <is>
           <t>インドネシア語</t>
         </is>
       </c>
-      <c r="H68" s="111" t="inlineStr">
+      <c r="H70" s="111" t="inlineStr">
         <is>
           <t>韓国語</t>
         </is>
       </c>
-      <c r="I68" s="111" t="inlineStr">
+      <c r="I70" s="111" t="inlineStr">
         <is>
           <t>ミャンマー語</t>
         </is>
       </c>
-      <c r="J68" s="111" t="inlineStr">
+      <c r="J70" s="111" t="inlineStr">
         <is>
           <t>タイ語</t>
         </is>
       </c>
-      <c r="K68" s="111" t="inlineStr">
+      <c r="K70" s="111" t="inlineStr">
         <is>
           <t>ベトナム語</t>
         </is>
       </c>
-      <c r="L68" s="111" t="inlineStr">
+      <c r="L70" s="111" t="inlineStr">
         <is>
           <t>中国語</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="112" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="112" t="inlineStr">
         <is>
           <t>■ 漢字（5種）</t>
         </is>
       </c>
-      <c r="B69" s="85" t="n"/>
-      <c r="C69" s="85" t="n"/>
-      <c r="D69" s="85" t="n"/>
-      <c r="E69" s="85" t="n"/>
-      <c r="F69" s="85" t="n"/>
-      <c r="G69" s="85" t="n"/>
-      <c r="H69" s="85" t="n"/>
-      <c r="I69" s="85" t="n"/>
-      <c r="J69" s="85" t="n"/>
-      <c r="K69" s="85" t="n"/>
-      <c r="L69" s="85" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="86" t="inlineStr">
-        <is>
-          <t>書き取り</t>
-        </is>
-      </c>
-      <c r="B70" s="85" t="inlineStr">
-        <is>
-          <t>字をなぞって手書き</t>
-        </is>
-      </c>
-      <c r="C70" s="85" t="inlineStr">
-        <is>
-          <t>日本語のみ（かな・字／翻訳不要）</t>
-        </is>
-      </c>
-      <c r="D70" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J70" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="86" t="inlineStr">
-        <is>
-          <t>意味</t>
-        </is>
-      </c>
-      <c r="B71" s="85" t="inlineStr">
-        <is>
-          <t>字→意味を4択</t>
-        </is>
-      </c>
-      <c r="C71" s="85" t="inlineStr">
-        <is>
-          <t>辞書の意味を流用</t>
-        </is>
-      </c>
-      <c r="D71" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E71" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F71" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G71" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H71" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I71" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J71" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K71" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L71" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
+      <c r="B71" s="85" t="n"/>
+      <c r="C71" s="85" t="n"/>
+      <c r="D71" s="85" t="n"/>
+      <c r="E71" s="85" t="n"/>
+      <c r="F71" s="85" t="n"/>
+      <c r="G71" s="85" t="n"/>
+      <c r="H71" s="85" t="n"/>
+      <c r="I71" s="85" t="n"/>
+      <c r="J71" s="85" t="n"/>
+      <c r="K71" s="85" t="n"/>
+      <c r="L71" s="85" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="86" t="inlineStr">
         <is>
+          <t>書き取り</t>
+        </is>
+      </c>
+      <c r="B72" s="85" t="inlineStr">
+        <is>
+          <t>字をなぞって手書き</t>
+        </is>
+      </c>
+      <c r="C72" s="85" t="inlineStr">
+        <is>
+          <t>日本語のみ（かな・字／翻訳不要）</t>
+        </is>
+      </c>
+      <c r="D72" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J72" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="86" t="inlineStr">
+        <is>
+          <t>意味</t>
+        </is>
+      </c>
+      <c r="B73" s="85" t="inlineStr">
+        <is>
+          <t>字→意味を4択</t>
+        </is>
+      </c>
+      <c r="C73" s="85" t="inlineStr">
+        <is>
+          <t>辞書の意味を流用</t>
+        </is>
+      </c>
+      <c r="D73" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E73" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F73" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G73" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H73" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I73" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J73" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K73" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L73" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="86" t="inlineStr">
+        <is>
           <t>読み</t>
         </is>
       </c>
-      <c r="B72" s="85" t="inlineStr">
+      <c r="B74" s="85" t="inlineStr">
         <is>
           <t>字→読みを4択</t>
         </is>
       </c>
-      <c r="C72" s="85" t="inlineStr">
+      <c r="C74" s="85" t="inlineStr">
         <is>
           <t>日本語のみ（かな／翻訳不要）</t>
         </is>
       </c>
-      <c r="D72" s="146" t="inlineStr">
+      <c r="D74" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E72" s="146" t="inlineStr">
+      <c r="E74" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F72" s="146" t="inlineStr">
+      <c r="F74" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G72" s="146" t="inlineStr">
+      <c r="G74" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H72" s="146" t="inlineStr">
+      <c r="H74" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I72" s="146" t="inlineStr">
+      <c r="I74" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J72" s="146" t="inlineStr">
+      <c r="J74" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K72" s="146" t="inlineStr">
+      <c r="K74" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L72" s="146" t="inlineStr">
+      <c r="L74" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="82" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="82" t="inlineStr">
         <is>
           <t>似た字の見分け</t>
         </is>
       </c>
-      <c r="B73" s="82" t="inlineStr">
+      <c r="B75" s="82" t="inlineStr">
         <is>
           <t>似た字4択→正しい字</t>
         </is>
       </c>
-      <c r="C73" s="82" t="inlineStr">
+      <c r="C75" s="82" t="inlineStr">
         <is>
           <t>日本語のみ（字／翻訳不要）</t>
         </is>
       </c>
-      <c r="D73" s="149" t="inlineStr">
+      <c r="D75" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E73" s="149" t="inlineStr">
+      <c r="E75" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F73" s="149" t="inlineStr">
+      <c r="F75" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G73" s="149" t="inlineStr">
+      <c r="G75" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H73" s="149" t="inlineStr">
+      <c r="H75" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I73" s="149" t="inlineStr">
+      <c r="I75" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J73" s="149" t="inlineStr">
+      <c r="J75" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K73" s="149" t="inlineStr">
+      <c r="K75" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L73" s="149" t="inlineStr">
+      <c r="L75" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="82" t="inlineStr">
-        <is>
-          <t>聞き取り</t>
-        </is>
-      </c>
-      <c r="B74" s="82" t="inlineStr">
-        <is>
-          <t>🔊読み→字を4択</t>
-        </is>
-      </c>
-      <c r="C74" s="82" t="inlineStr">
-        <is>
-          <t>日本語のみ（音声・字／翻訳不要）</t>
-        </is>
-      </c>
-      <c r="D74" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J74" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="116" t="inlineStr">
-        <is>
-          <t>■ 語彙（5種）</t>
-        </is>
-      </c>
-      <c r="B75" s="82" t="n"/>
-      <c r="C75" s="82" t="n"/>
-      <c r="D75" s="82" t="n"/>
-      <c r="E75" s="82" t="n"/>
-      <c r="F75" s="82" t="n"/>
-      <c r="G75" s="82" t="n"/>
-      <c r="H75" s="82" t="n"/>
-      <c r="I75" s="82" t="n"/>
-      <c r="J75" s="82" t="n"/>
-      <c r="K75" s="82" t="n"/>
-      <c r="L75" s="82" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="82" t="inlineStr">
         <is>
-          <t>意味</t>
+          <t>聞き取り</t>
         </is>
       </c>
       <c r="B76" s="82" t="inlineStr">
         <is>
-          <t>語→意味を4択</t>
+          <t>🔊読み→字を4択</t>
         </is>
       </c>
       <c r="C76" s="82" t="inlineStr">
         <is>
-          <t>辞書の意味を流用</t>
-        </is>
-      </c>
-      <c r="D76" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E76" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F76" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G76" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H76" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I76" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J76" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K76" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L76" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>日本語のみ（音声・字／翻訳不要）</t>
+        </is>
+      </c>
+      <c r="D76" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J76" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="82" t="inlineStr">
-        <is>
-          <t>読み</t>
-        </is>
-      </c>
-      <c r="B77" s="82" t="inlineStr">
-        <is>
-          <t>語→読みを4択</t>
-        </is>
-      </c>
-      <c r="C77" s="82" t="inlineStr">
-        <is>
-          <t>日本語のみ（かな／翻訳不要）</t>
-        </is>
-      </c>
-      <c r="D77" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J77" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A77" s="116" t="inlineStr">
+        <is>
+          <t>■ 語彙（5種）</t>
+        </is>
+      </c>
+      <c r="B77" s="82" t="n"/>
+      <c r="C77" s="82" t="n"/>
+      <c r="D77" s="82" t="n"/>
+      <c r="E77" s="82" t="n"/>
+      <c r="F77" s="82" t="n"/>
+      <c r="G77" s="82" t="n"/>
+      <c r="H77" s="82" t="n"/>
+      <c r="I77" s="82" t="n"/>
+      <c r="J77" s="82" t="n"/>
+      <c r="K77" s="82" t="n"/>
+      <c r="L77" s="82" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="82" t="inlineStr">
         <is>
-          <t>表記</t>
+          <t>意味</t>
         </is>
       </c>
       <c r="B78" s="82" t="inlineStr">
         <is>
-          <t>意味→漢字表記を4択</t>
+          <t>語→意味を4択</t>
         </is>
       </c>
       <c r="C78" s="82" t="inlineStr">
@@ -12635,79 +12576,79 @@
     <row r="79">
       <c r="A79" s="82" t="inlineStr">
         <is>
-          <t>聞き取り</t>
+          <t>読み</t>
         </is>
       </c>
       <c r="B79" s="82" t="inlineStr">
         <is>
-          <t>🔊読み→意味を4択</t>
+          <t>語→読みを4択</t>
         </is>
       </c>
       <c r="C79" s="82" t="inlineStr">
         <is>
-          <t>辞書の意味を流用</t>
-        </is>
-      </c>
-      <c r="D79" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E79" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F79" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G79" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H79" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I79" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J79" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K79" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L79" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>日本語のみ（かな／翻訳不要）</t>
+        </is>
+      </c>
+      <c r="D79" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J79" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="82" t="inlineStr">
         <is>
-          <t>語彙パズル</t>
+          <t>表記</t>
         </is>
       </c>
       <c r="B80" s="82" t="inlineStr">
         <is>
-          <t>意味→かなタイルで語を作る</t>
+          <t>意味→漢字表記を4択</t>
         </is>
       </c>
       <c r="C80" s="82" t="inlineStr">
         <is>
-          <t>辞書の意味を流用（意味を提示）</t>
+          <t>辞書の意味を流用</t>
         </is>
       </c>
       <c r="D80" s="150" t="inlineStr">
@@ -12757,225 +12698,349 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="116" t="inlineStr">
-        <is>
-          <t>■ 文法（2種）</t>
-        </is>
-      </c>
-      <c r="B81" s="82" t="n"/>
-      <c r="C81" s="82" t="n"/>
-      <c r="D81" s="82" t="n"/>
-      <c r="E81" s="82" t="n"/>
-      <c r="F81" s="82" t="n"/>
-      <c r="G81" s="82" t="n"/>
-      <c r="H81" s="82" t="n"/>
-      <c r="I81" s="82" t="n"/>
-      <c r="J81" s="82" t="n"/>
-      <c r="K81" s="82" t="n"/>
-      <c r="L81" s="82" t="n"/>
+      <c r="A81" s="82" t="inlineStr">
+        <is>
+          <t>聞き取り</t>
+        </is>
+      </c>
+      <c r="B81" s="82" t="inlineStr">
+        <is>
+          <t>🔊読み→意味を4択</t>
+        </is>
+      </c>
+      <c r="C81" s="82" t="inlineStr">
+        <is>
+          <t>辞書の意味を流用</t>
+        </is>
+      </c>
+      <c r="D81" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E81" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F81" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G81" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H81" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I81" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J81" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K81" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L81" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="82" t="inlineStr">
         <is>
+          <t>語彙パズル</t>
+        </is>
+      </c>
+      <c r="B82" s="82" t="inlineStr">
+        <is>
+          <t>意味→かなタイルで語を作る</t>
+        </is>
+      </c>
+      <c r="C82" s="82" t="inlineStr">
+        <is>
+          <t>辞書の意味を流用（意味を提示）</t>
+        </is>
+      </c>
+      <c r="D82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L82" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="116" t="inlineStr">
+        <is>
+          <t>■ 文法（2種）</t>
+        </is>
+      </c>
+      <c r="B83" s="82" t="n"/>
+      <c r="C83" s="82" t="n"/>
+      <c r="D83" s="82" t="n"/>
+      <c r="E83" s="82" t="n"/>
+      <c r="F83" s="82" t="n"/>
+      <c r="G83" s="82" t="n"/>
+      <c r="H83" s="82" t="n"/>
+      <c r="I83" s="82" t="n"/>
+      <c r="J83" s="82" t="n"/>
+      <c r="K83" s="82" t="n"/>
+      <c r="L83" s="82" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="82" t="inlineStr">
+        <is>
           <t>意味</t>
         </is>
       </c>
-      <c r="B82" s="82" t="inlineStr">
+      <c r="B84" s="82" t="inlineStr">
         <is>
           <t>文法点→意味を4択</t>
         </is>
       </c>
-      <c r="C82" s="82" t="inlineStr">
+      <c r="C84" s="82" t="inlineStr">
         <is>
           <t>辞書の意味を流用</t>
         </is>
       </c>
-      <c r="D82" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E82" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F82" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G82" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H82" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I82" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J82" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K82" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L82" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="82" t="inlineStr">
+      <c r="D84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="82" t="inlineStr">
         <is>
           <t>パズル</t>
         </is>
       </c>
-      <c r="B83" s="82" t="inlineStr">
+      <c r="B85" s="82" t="inlineStr">
         <is>
           <t>例文の穴に文法語をタイルで作る</t>
         </is>
       </c>
-      <c r="C83" s="82" t="inlineStr">
+      <c r="C85" s="82" t="inlineStr">
         <is>
           <t>辞書の意味を流用（ヒントに意味）</t>
         </is>
       </c>
-      <c r="D83" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E83" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F83" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G83" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H83" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I83" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J83" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K83" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L83" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="90" t="inlineStr">
+      <c r="D85" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E85" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F85" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G85" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H85" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I85" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J85" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K85" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L85" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="90" t="inlineStr">
         <is>
           <t>※ ドリルは辞書データから自動生成。意味を見せる面（意味／表記／聞き取り〈語彙〉／各パズル）は辞書の en/ne をそのまま使うので、辞書の翻訳率＝ドリルの翻訳率（＝100%）。専用の翻訳データは持たない。</t>
         </is>
       </c>
-      <c r="B84" s="82" t="n"/>
-      <c r="C84" s="82" t="n"/>
-      <c r="D84" s="82" t="n"/>
-      <c r="E84" s="82" t="n"/>
-      <c r="F84" s="82" t="n"/>
-      <c r="G84" s="82" t="n"/>
-      <c r="H84" s="82" t="n"/>
-      <c r="I84" s="82" t="n"/>
-      <c r="J84" s="82" t="n"/>
-      <c r="K84" s="82" t="n"/>
-      <c r="L84" s="82" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="90" t="inlineStr">
+      <c r="B86" s="82" t="n"/>
+      <c r="C86" s="82" t="n"/>
+      <c r="D86" s="82" t="n"/>
+      <c r="E86" s="82" t="n"/>
+      <c r="F86" s="82" t="n"/>
+      <c r="G86" s="82" t="n"/>
+      <c r="H86" s="82" t="n"/>
+      <c r="I86" s="82" t="n"/>
+      <c r="J86" s="82" t="n"/>
+      <c r="K86" s="82" t="n"/>
+      <c r="L86" s="82" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="90" t="inlineStr">
         <is>
           <t>※ 読み・書き取り・似た字の見分け・聞き取り〈漢字〉は かな／字／音声だけで解くため翻訳不要。旧版で「産出パズルは翻訳不要」としていたのは誤り＝意味を提示するため辞書流用100%。</t>
         </is>
       </c>
-      <c r="B85" s="82" t="n"/>
-      <c r="C85" s="82" t="n"/>
-      <c r="D85" s="82" t="n"/>
-      <c r="E85" s="82" t="n"/>
-      <c r="F85" s="82" t="n"/>
-      <c r="G85" s="82" t="n"/>
-      <c r="H85" s="82" t="n"/>
-      <c r="I85" s="82" t="n"/>
-      <c r="J85" s="82" t="n"/>
-      <c r="K85" s="82" t="n"/>
-      <c r="L85" s="82" t="n"/>
-    </row>
-    <row r="86"/>
-    <row r="87">
-      <c r="A87" s="91" t="inlineStr">
+      <c r="B87" s="82" t="n"/>
+      <c r="C87" s="82" t="n"/>
+      <c r="D87" s="82" t="n"/>
+      <c r="E87" s="82" t="n"/>
+      <c r="F87" s="82" t="n"/>
+      <c r="G87" s="82" t="n"/>
+      <c r="H87" s="82" t="n"/>
+      <c r="I87" s="82" t="n"/>
+      <c r="J87" s="82" t="n"/>
+      <c r="K87" s="82" t="n"/>
+      <c r="L87" s="82" t="n"/>
+    </row>
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" s="91" t="inlineStr">
         <is>
           <t>まとめ</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="90" t="inlineStr">
-        <is>
-          <t>・完全対応は ja / en / ne の3言語。アプリのどこを開いても日本語・英語・ネパール語で読める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="90" t="inlineStr">
-        <is>
-          <t>・残り7言語(bn/id/ko/my/th/vi/zh)＝UIは全キー翻訳済(100%)。辞書は7言語すべて完了(id 2026-09-05／bn/ko/my/th/vi/zh 2026-09-05)。全7言語の問題訳は未着手。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="90" t="inlineStr">
         <is>
+          <t>・完全対応は ja / en / ne の3言語。アプリのどこを開いても日本語・英語・ネパール語で読める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="90" t="inlineStr">
+        <is>
+          <t>・残り7言語(bn/id/ko/my/th/vi/zh)＝UIは全キー翻訳済(100%)。辞書は7言語すべて完了(id 2026-09-05／bn/ko/my/th/vi/zh 2026-09-05)。全7言語の問題訳は未着手。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="90" t="inlineStr">
+        <is>
           <t>・7言語フル対応には 各問題の対訳 が必要（辞書は全7言語完了済）。UIは全言語対応済。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A64:I64"/>
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A63:I63"/>
+    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A42:I42"/>
     <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A66:I66"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A67:I67"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A34:I34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 品質・攻略耐性" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥ 翻訳状況" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聴解攻略耐性分析" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ 用法カバー×バランス" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大問別まとめ'!$A$1:$L$1</definedName>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="43">
+  <fonts count="49">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -261,8 +262,34 @@
     <font>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F7A3D"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3B57"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3B57"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="007A756C"/>
+    </font>
   </fonts>
-  <fills count="43">
+  <fills count="49">
     <fill>
       <patternFill/>
     </fill>
@@ -476,8 +503,38 @@
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E5A88"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDF2E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF0FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EAF3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -588,11 +645,25 @@
         <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3DE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D3DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -988,6 +1059,48 @@
     <xf numFmtId="0" fontId="38" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="44" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1354,7 +1467,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="75" min="1" max="1"/>
     <col width="16" customWidth="1" style="75" min="2" max="2"/>
@@ -1371,2318 +1484,2318 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="155" t="inlineStr">
+      <c r="A1" s="184" t="inlineStr">
         <is>
           <t>セクション</t>
         </is>
       </c>
-      <c r="B1" s="155" t="inlineStr">
+      <c r="B1" s="184" t="inlineStr">
         <is>
           <t>大問</t>
         </is>
       </c>
-      <c r="C1" s="155" t="inlineStr">
+      <c r="C1" s="184" t="inlineStr">
         <is>
           <t>レベル</t>
         </is>
       </c>
-      <c r="D1" s="155" t="inlineStr">
+      <c r="D1" s="184" t="inlineStr">
         <is>
           <t>在庫問題数</t>
         </is>
       </c>
-      <c r="E1" s="155" t="inlineStr">
+      <c r="E1" s="184" t="inlineStr">
         <is>
           <t>割増し倍数</t>
         </is>
       </c>
-      <c r="F1" s="155" t="inlineStr">
+      <c r="F1" s="184" t="inlineStr">
         <is>
           <t>模試問題数</t>
         </is>
       </c>
-      <c r="G1" s="155" t="inlineStr">
+      <c r="G1" s="184" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
       </c>
-      <c r="H1" s="155" t="inlineStr">
+      <c r="H1" s="184" t="inlineStr">
         <is>
           <t>セット数</t>
         </is>
       </c>
-      <c r="I1" s="155" t="inlineStr">
+      <c r="I1" s="184" t="inlineStr">
         <is>
           <t>本番出題数</t>
         </is>
       </c>
-      <c r="J1" s="155" t="inlineStr">
+      <c r="J1" s="184" t="inlineStr">
         <is>
           <t>模試換算(何回分)</t>
         </is>
       </c>
-      <c r="K1" s="155" t="inlineStr">
+      <c r="K1" s="184" t="inlineStr">
         <is>
           <t>誤答数の内訳</t>
         </is>
       </c>
-      <c r="L1" s="155" t="inlineStr">
+      <c r="L1" s="184" t="inlineStr">
         <is>
           <t>シャッフル</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="51" t="inlineStr">
+      <c r="A2" s="185" t="inlineStr">
         <is>
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B2" s="52" t="inlineStr">
+      <c r="B2" s="186" t="inlineStr">
         <is>
           <t>漢字読み</t>
         </is>
       </c>
-      <c r="C2" s="53" t="inlineStr">
+      <c r="C2" s="187" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="D2" s="53" t="n">
+      <c r="D2" s="187" t="n">
         <v>410</v>
       </c>
-      <c r="E2" s="54" t="inlineStr">
+      <c r="E2" s="188" t="inlineStr">
         <is>
           <t>×3</t>
         </is>
       </c>
-      <c r="F2" s="53" t="n">
+      <c r="F2" s="187" t="n">
         <v>104</v>
       </c>
-      <c r="G2" s="52" t="inlineStr">
+      <c r="G2" s="186" t="inlineStr">
         <is>
           <t>N5の質の高い漢字語（数字・接尾辞を除く）は実質104語＝N5は漢字自体が少ないため上限。模試プールは120でなく104問が自然な上限。</t>
         </is>
       </c>
-      <c r="H2" s="53" t="inlineStr">
+      <c r="H2" s="187" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I2" s="53" t="n">
+      <c r="I2" s="187" t="n">
         <v>12</v>
       </c>
-      <c r="J2" s="55" t="n">
+      <c r="J2" s="189" t="n">
         <v>34</v>
       </c>
-      <c r="K2" s="52" t="inlineStr">
+      <c r="K2" s="186" t="inlineStr">
         <is>
           <t>3:785</t>
         </is>
       </c>
-      <c r="L2" s="53" t="inlineStr">
+      <c r="L2" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="51" t="inlineStr">
+      <c r="A3" s="185" t="inlineStr">
         <is>
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="186" t="inlineStr">
         <is>
           <t>漢字読み</t>
         </is>
       </c>
-      <c r="C3" s="53" t="inlineStr">
+      <c r="C3" s="187" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="D3" s="53" t="n">
+      <c r="D3" s="187" t="n">
         <v>331</v>
       </c>
-      <c r="E3" s="53" t="inlineStr">
+      <c r="E3" s="187" t="inlineStr">
         <is>
           <t>×1</t>
         </is>
       </c>
-      <c r="F3" s="53" t="n">
+      <c r="F3" s="187" t="n">
         <v>90</v>
       </c>
-      <c r="G3" s="52" t="n"/>
-      <c r="H3" s="53" t="inlineStr">
+      <c r="G3" s="186" t="inlineStr"/>
+      <c r="H3" s="187" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I3" s="53" t="n">
+      <c r="I3" s="187" t="n">
         <v>9</v>
       </c>
-      <c r="J3" s="55" t="n">
+      <c r="J3" s="189" t="n">
         <v>36</v>
       </c>
-      <c r="K3" s="52" t="inlineStr">
+      <c r="K3" s="186" t="inlineStr">
         <is>
           <t>3:537</t>
         </is>
       </c>
-      <c r="L3" s="53" t="inlineStr">
+      <c r="L3" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="185" t="inlineStr">
         <is>
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="186" t="inlineStr">
         <is>
           <t>漢字読み</t>
         </is>
       </c>
-      <c r="C4" s="53" t="inlineStr">
+      <c r="C4" s="187" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="D4" s="53" t="n">
+      <c r="D4" s="187" t="n">
         <v>1944</v>
       </c>
-      <c r="E4" s="53" t="inlineStr">
+      <c r="E4" s="187" t="inlineStr">
         <is>
           <t>×1</t>
         </is>
       </c>
-      <c r="F4" s="53" t="n">
+      <c r="F4" s="187" t="n">
         <v>80</v>
       </c>
-      <c r="G4" s="52" t="n"/>
-      <c r="H4" s="53" t="inlineStr">
+      <c r="G4" s="186" t="inlineStr"/>
+      <c r="H4" s="187" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I4" s="53" t="n">
+      <c r="I4" s="187" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="55" t="n">
+      <c r="J4" s="189" t="n">
         <v>243</v>
       </c>
-      <c r="K4" s="52" t="inlineStr">
+      <c r="K4" s="186" t="inlineStr">
         <is>
           <t>3:1882</t>
         </is>
       </c>
-      <c r="L4" s="53" t="inlineStr">
+      <c r="L4" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="51" t="inlineStr">
+      <c r="A5" s="185" t="inlineStr">
         <is>
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="B5" s="186" t="inlineStr">
         <is>
           <t>表記</t>
         </is>
       </c>
-      <c r="C5" s="53" t="inlineStr">
+      <c r="C5" s="187" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="D5" s="53" t="n">
+      <c r="D5" s="187" t="n">
         <v>474</v>
       </c>
-      <c r="E5" s="54" t="inlineStr">
+      <c r="E5" s="188" t="inlineStr">
         <is>
           <t>×3</t>
         </is>
       </c>
-      <c r="F5" s="53" t="n">
+      <c r="F5" s="187" t="n">
         <v>80</v>
       </c>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="G5" s="186" t="inlineStr">
         <is>
           <t>漢字読みN5の104×2の例題を流用</t>
         </is>
       </c>
-      <c r="H5" s="53" t="inlineStr">
+      <c r="H5" s="187" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="53" t="n">
+      <c r="I5" s="187" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="55" t="n">
+      <c r="J5" s="189" t="n">
         <v>59</v>
       </c>
-      <c r="K5" s="52" t="inlineStr">
+      <c r="K5" s="186" t="inlineStr">
         <is>
           <t>3:849</t>
         </is>
       </c>
-      <c r="L5" s="53" t="inlineStr">
+      <c r="L5" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="51" t="inlineStr">
+      <c r="A6" s="185" t="inlineStr">
         <is>
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B6" s="52" t="inlineStr">
+      <c r="B6" s="186" t="inlineStr">
         <is>
           <t>表記</t>
         </is>
       </c>
-      <c r="C6" s="53" t="inlineStr">
+      <c r="C6" s="187" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="D6" s="53" t="n">
+      <c r="D6" s="187" t="n">
         <v>365</v>
       </c>
-      <c r="E6" s="53" t="inlineStr">
+      <c r="E6" s="187" t="inlineStr">
         <is>
           <t>×1</t>
         </is>
       </c>
-      <c r="F6" s="53" t="n">
+      <c r="F6" s="187" t="n">
         <v>60</v>
       </c>
-      <c r="G6" s="52" t="n"/>
-      <c r="H6" s="53" t="inlineStr">
+      <c r="G6" s="186" t="inlineStr"/>
+      <c r="H6" s="187" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="53" t="n">
+      <c r="I6" s="187" t="n">
         <v>6</v>
       </c>
-      <c r="J6" s="55" t="n">
+      <c r="J6" s="189" t="n">
         <v>60</v>
       </c>
-      <c r="K6" s="52" t="inlineStr">
+      <c r="K6" s="186" t="inlineStr">
         <is>
           <t>3:571</t>
         </is>
       </c>
-      <c r="L6" s="53" t="inlineStr">
+      <c r="L6" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="51" t="inlineStr">
+      <c r="A7" s="185" t="inlineStr">
         <is>
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B7" s="52" t="inlineStr">
+      <c r="B7" s="186" t="inlineStr">
         <is>
           <t>表記</t>
         </is>
       </c>
-      <c r="C7" s="53" t="inlineStr">
+      <c r="C7" s="187" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="D7" s="53" t="n">
+      <c r="D7" s="187" t="n">
         <v>1992</v>
       </c>
-      <c r="E7" s="53" t="inlineStr">
+      <c r="E7" s="187" t="inlineStr">
         <is>
           <t>×1</t>
         </is>
       </c>
-      <c r="F7" s="53" t="n">
+      <c r="F7" s="187" t="n">
         <v>60</v>
       </c>
-      <c r="G7" s="52" t="n"/>
-      <c r="H7" s="53" t="inlineStr">
+      <c r="G7" s="186" t="inlineStr"/>
+      <c r="H7" s="187" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I7" s="53" t="n">
+      <c r="I7" s="187" t="n">
         <v>6</v>
       </c>
-      <c r="J7" s="55" t="n">
+      <c r="J7" s="189" t="n">
         <v>332</v>
       </c>
-      <c r="K7" s="52" t="inlineStr">
+      <c r="K7" s="186" t="inlineStr">
         <is>
           <t>3:1930</t>
         </is>
       </c>
-      <c r="L7" s="53" t="inlineStr">
+      <c r="L7" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="51" t="inlineStr">
+      <c r="A8" s="185" t="inlineStr">
         <is>
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B8" s="52" t="inlineStr">
+      <c r="B8" s="186" t="inlineStr">
         <is>
           <t>文脈規定</t>
         </is>
       </c>
-      <c r="C8" s="53" t="inlineStr">
+      <c r="C8" s="187" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="D8" s="53" t="n">
+      <c r="D8" s="187" t="n">
         <v>687</v>
       </c>
-      <c r="E8" s="53" t="inlineStr">
+      <c r="E8" s="187" t="inlineStr">
         <is>
           <t>×1</t>
         </is>
       </c>
-      <c r="F8" s="53" t="n">
+      <c r="F8" s="187" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="52" t="n"/>
-      <c r="H8" s="53" t="inlineStr">
+      <c r="G8" s="186" t="inlineStr"/>
+      <c r="H8" s="187" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I8" s="53" t="n">
+      <c r="I8" s="187" t="n">
         <v>10</v>
       </c>
-      <c r="J8" s="55" t="n">
+      <c r="J8" s="189" t="n">
         <v>68</v>
       </c>
-      <c r="K8" s="52" t="inlineStr">
+      <c r="K8" s="186" t="inlineStr">
         <is>
           <t>3:197 / 4:222 / 5:268</t>
         </is>
       </c>
-      <c r="L8" s="53" t="inlineStr">
+      <c r="L8" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="51" t="inlineStr">
+      <c r="A9" s="185" t="inlineStr">
         <is>
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B9" s="52" t="inlineStr">
+      <c r="B9" s="186" t="inlineStr">
         <is>
           <t>文脈規定</t>
         </is>
       </c>
-      <c r="C9" s="53" t="inlineStr">
+      <c r="C9" s="187" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="D9" s="53" t="n">
+      <c r="D9" s="187" t="n">
         <v>655</v>
       </c>
-      <c r="E9" s="53" t="inlineStr">
+      <c r="E9" s="187" t="inlineStr">
         <is>
           <t>×1</t>
         </is>
       </c>
-      <c r="F9" s="53" t="n">
+      <c r="F9" s="187" t="n">
         <v>100</v>
       </c>
-      <c r="G9" s="52" t="n"/>
-      <c r="H9" s="53" t="inlineStr">
+      <c r="G9" s="186" t="inlineStr"/>
+      <c r="H9" s="187" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="53" t="n">
+      <c r="I9" s="187" t="n">
         <v>10</v>
       </c>
-      <c r="J9" s="55" t="n">
+      <c r="J9" s="189" t="n">
         <v>65</v>
       </c>
-      <c r="K9" s="52" t="inlineStr">
+      <c r="K9" s="186" t="inlineStr">
         <is>
           <t>3:243 / 4:231 / 5:181</t>
         </is>
       </c>
-      <c r="L9" s="53" t="inlineStr">
+      <c r="L9" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="inlineStr">
+      <c r="A10" s="185" t="inlineStr">
         <is>
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B10" s="52" t="inlineStr">
+      <c r="B10" s="186" t="inlineStr">
         <is>
           <t>文脈規定</t>
         </is>
       </c>
-      <c r="C10" s="53" t="inlineStr">
+      <c r="C10" s="187" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="D10" s="53" t="n">
+      <c r="D10" s="187" t="n">
         <v>2105</v>
       </c>
-      <c r="E10" s="53" t="inlineStr">
+      <c r="E10" s="187" t="inlineStr">
         <is>
           <t>×1</t>
         </is>
       </c>
-      <c r="F10" s="53" t="n">
+      <c r="F10" s="187" t="n">
         <v>110</v>
       </c>
-      <c r="G10" s="52" t="n"/>
-      <c r="H10" s="53" t="inlineStr">
+      <c r="G10" s="186" t="inlineStr"/>
+      <c r="H10" s="187" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I10" s="53" t="n">
+      <c r="I10" s="187" t="n">
         <v>11</v>
       </c>
-      <c r="J10" s="55" t="n">
+      <c r="J10" s="189" t="n">
         <v>191</v>
       </c>
-      <c r="K10" s="52" t="inlineStr">
+      <c r="K10" s="186" t="inlineStr">
         <is>
           <t>3:1397 / 4:450 / 5:258</t>
         </is>
       </c>
-      <c r="L10" s="53" t="inlineStr">
+      <c r="L10" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="185" t="inlineStr">
         <is>
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B11" s="52" t="inlineStr">
+      <c r="B11" s="186" t="inlineStr">
         <is>
           <t>言い換え類義</t>
         </is>
       </c>
-      <c r="C11" s="53" t="inlineStr">
+      <c r="C11" s="187" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="D11" s="53" t="n">
+      <c r="D11" s="187" t="n">
         <v>236</v>
       </c>
-      <c r="E11" s="53" t="inlineStr">
+      <c r="E11" s="187" t="inlineStr">
         <is>
           <t>×1</t>
         </is>
       </c>
-      <c r="F11" s="53" t="n">
+      <c r="F11" s="187" t="n">
         <v>50</v>
       </c>
-      <c r="G11" s="52" t="n"/>
-      <c r="H11" s="53" t="inlineStr">
+      <c r="G11" s="186" t="inlineStr"/>
+      <c r="H11" s="187" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I11" s="53" t="n">
+      <c r="I11" s="187" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="55" t="n">
+      <c r="J11" s="189" t="n">
         <v>47</v>
       </c>
-      <c r="K11" s="52" t="inlineStr">
+      <c r="K11" s="186" t="inlineStr">
         <is>
           <t>3:205 / 4:13 / 5:18</t>
         </is>
       </c>
-      <c r="L11" s="53" t="inlineStr">
+      <c r="L11" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="A12" s="185" t="inlineStr">
         <is>
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B12" s="52" t="inlineStr">
+      <c r="B12" s="186" t="inlineStr">
         <is>
           <t>言い換え類義</t>
         </is>
       </c>
-      <c r="C12" s="53" t="inlineStr">
+      <c r="C12" s="187" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="D12" s="53" t="n">
+      <c r="D12" s="187" t="n">
         <v>407</v>
       </c>
-      <c r="E12" s="53" t="inlineStr">
+      <c r="E12" s="187" t="inlineStr">
         <is>
           <t>×1</t>
         </is>
       </c>
-      <c r="F12" s="53" t="n">
+      <c r="F12" s="187" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="52" t="n"/>
-      <c r="H12" s="53" t="inlineStr">
+      <c r="G12" s="186" t="inlineStr"/>
+      <c r="H12" s="187" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I12" s="53" t="n">
+      <c r="I12" s="187" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="55" t="n">
+      <c r="J12" s="189" t="n">
         <v>81</v>
       </c>
-      <c r="K12" s="52" t="inlineStr">
+      <c r="K12" s="186" t="inlineStr">
         <is>
           <t>3:183 / 4:8 / 5:40 / 6:176</t>
         </is>
       </c>
-      <c r="L12" s="53" t="inlineStr">
+      <c r="L12" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="51" t="inlineStr">
+      <c r="A13" s="185" t="inlineStr">
         <is>
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B13" s="52" t="inlineStr">
+      <c r="B13" s="186" t="inlineStr">
         <is>
           <t>言い換え類義</t>
         </is>
       </c>
-      <c r="C13" s="53" t="inlineStr">
+      <c r="C13" s="187" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="D13" s="53" t="n">
+      <c r="D13" s="187" t="n">
         <v>1612</v>
       </c>
-      <c r="E13" s="53" t="inlineStr">
+      <c r="E13" s="187" t="inlineStr">
         <is>
           <t>×1</t>
         </is>
       </c>
-      <c r="F13" s="53" t="n">
+      <c r="F13" s="187" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="52" t="n"/>
-      <c r="H13" s="53" t="inlineStr">
+      <c r="G13" s="186" t="inlineStr"/>
+      <c r="H13" s="187" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I13" s="53" t="n">
+      <c r="I13" s="187" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="55" t="n">
+      <c r="J13" s="189" t="n">
         <v>322</v>
       </c>
-      <c r="K13" s="52" t="inlineStr">
-        <is>
-          <t>3:601 / 4:14 / 5:100 / 6:897</t>
-        </is>
-      </c>
-      <c r="L13" s="53" t="inlineStr">
+      <c r="K13" s="186" t="inlineStr">
+        <is>
+          <t>3:1612</t>
+        </is>
+      </c>
+      <c r="L13" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="51" t="inlineStr">
+      <c r="A14" s="185" t="inlineStr">
         <is>
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B14" s="52" t="inlineStr">
+      <c r="B14" s="186" t="inlineStr">
         <is>
           <t>用法</t>
         </is>
       </c>
-      <c r="C14" s="53" t="inlineStr">
+      <c r="C14" s="187" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="D14" s="53" t="n">
+      <c r="D14" s="187" t="n">
         <v>571</v>
       </c>
-      <c r="E14" s="53" t="inlineStr">
+      <c r="E14" s="187" t="inlineStr">
         <is>
           <t>×1</t>
         </is>
       </c>
-      <c r="F14" s="53" t="n">
+      <c r="F14" s="187" t="n">
         <v>50</v>
       </c>
-      <c r="G14" s="52" t="n"/>
-      <c r="H14" s="53" t="inlineStr">
+      <c r="G14" s="186" t="inlineStr"/>
+      <c r="H14" s="187" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I14" s="53" t="n">
+      <c r="I14" s="187" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="55" t="n">
+      <c r="J14" s="189" t="n">
         <v>114</v>
       </c>
-      <c r="K14" s="52" t="inlineStr">
+      <c r="K14" s="186" t="inlineStr">
         <is>
           <t>3:571</t>
         </is>
       </c>
-      <c r="L14" s="53" t="inlineStr">
+      <c r="L14" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="A15" s="185" t="inlineStr">
         <is>
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B15" s="52" t="inlineStr">
+      <c r="B15" s="186" t="inlineStr">
         <is>
           <t>用法</t>
         </is>
       </c>
-      <c r="C15" s="53" t="inlineStr">
+      <c r="C15" s="187" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="D15" s="53" t="n">
-        <v>600</v>
-      </c>
-      <c r="E15" s="53" t="inlineStr">
+      <c r="D15" s="187" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E15" s="187" t="inlineStr">
         <is>
           <t>×1</t>
         </is>
       </c>
-      <c r="F15" s="53" t="n">
+      <c r="F15" s="187" t="n">
         <v>50</v>
       </c>
-      <c r="G15" s="52" t="n"/>
-      <c r="H15" s="53" t="inlineStr">
+      <c r="G15" s="186" t="inlineStr"/>
+      <c r="H15" s="187" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I15" s="53" t="n">
+      <c r="I15" s="187" t="n">
         <v>5</v>
       </c>
-      <c r="J15" s="55" t="n">
+      <c r="J15" s="189" t="n">
+        <v>240</v>
+      </c>
+      <c r="K15" s="186" t="inlineStr">
+        <is>
+          <t>3:1131 / 4:28 / 5:27 / 6:14</t>
+        </is>
+      </c>
+      <c r="L15" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="190" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B16" s="186" t="inlineStr">
+        <is>
+          <t>文法形式</t>
+        </is>
+      </c>
+      <c r="C16" s="187" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D16" s="187" t="n">
+        <v>398</v>
+      </c>
+      <c r="E16" s="188" t="inlineStr">
+        <is>
+          <t>×4</t>
+        </is>
+      </c>
+      <c r="F16" s="187" t="n">
+        <v>160</v>
+      </c>
+      <c r="G16" s="186" t="inlineStr"/>
+      <c r="H16" s="187" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="187" t="n">
+        <v>16</v>
+      </c>
+      <c r="J16" s="189" t="n">
+        <v>24</v>
+      </c>
+      <c r="K16" s="186" t="inlineStr">
+        <is>
+          <t>3:397 / 4:1</t>
+        </is>
+      </c>
+      <c r="L16" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="190" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B17" s="186" t="inlineStr">
+        <is>
+          <t>文法形式</t>
+        </is>
+      </c>
+      <c r="C17" s="187" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D17" s="187" t="n">
+        <v>361</v>
+      </c>
+      <c r="E17" s="188" t="inlineStr">
+        <is>
+          <t>×3</t>
+        </is>
+      </c>
+      <c r="F17" s="187" t="n">
+        <v>150</v>
+      </c>
+      <c r="G17" s="186" t="inlineStr"/>
+      <c r="H17" s="187" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="187" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" s="189" t="n">
+        <v>24</v>
+      </c>
+      <c r="K17" s="186" t="inlineStr">
+        <is>
+          <t>3:361</t>
+        </is>
+      </c>
+      <c r="L17" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="190" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B18" s="186" t="inlineStr">
+        <is>
+          <t>文法形式</t>
+        </is>
+      </c>
+      <c r="C18" s="187" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D18" s="187" t="n">
+        <v>448</v>
+      </c>
+      <c r="E18" s="188" t="inlineStr">
+        <is>
+          <t>×2</t>
+        </is>
+      </c>
+      <c r="F18" s="187" t="n">
+        <v>130</v>
+      </c>
+      <c r="G18" s="186" t="inlineStr"/>
+      <c r="H18" s="187" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="187" t="n">
+        <v>13</v>
+      </c>
+      <c r="J18" s="189" t="n">
+        <v>34</v>
+      </c>
+      <c r="K18" s="186" t="inlineStr">
+        <is>
+          <t>3:446 / 4:2</t>
+        </is>
+      </c>
+      <c r="L18" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="190" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B19" s="186" t="inlineStr">
+        <is>
+          <t>組み立て</t>
+        </is>
+      </c>
+      <c r="C19" s="187" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D19" s="187" t="n">
+        <v>146</v>
+      </c>
+      <c r="E19" s="188" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="F19" s="187" t="n">
+        <v>50</v>
+      </c>
+      <c r="G19" s="186" t="inlineStr"/>
+      <c r="H19" s="187" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="187" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" s="189" t="n">
+        <v>29</v>
+      </c>
+      <c r="K19" s="186" t="inlineStr">
+        <is>
+          <t>3:146</t>
+        </is>
+      </c>
+      <c r="L19" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="190" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B20" s="186" t="inlineStr">
+        <is>
+          <t>組み立て</t>
+        </is>
+      </c>
+      <c r="C20" s="187" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D20" s="187" t="n">
+        <v>216</v>
+      </c>
+      <c r="E20" s="188" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="F20" s="187" t="n">
+        <v>50</v>
+      </c>
+      <c r="G20" s="186" t="inlineStr"/>
+      <c r="H20" s="187" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="187" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" s="189" t="n">
+        <v>43</v>
+      </c>
+      <c r="K20" s="186" t="inlineStr">
+        <is>
+          <t>3:216</t>
+        </is>
+      </c>
+      <c r="L20" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="190" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B21" s="186" t="inlineStr">
+        <is>
+          <t>組み立て</t>
+        </is>
+      </c>
+      <c r="C21" s="187" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D21" s="187" t="n">
+        <v>311</v>
+      </c>
+      <c r="E21" s="188" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="F21" s="187" t="n">
+        <v>50</v>
+      </c>
+      <c r="G21" s="186" t="inlineStr"/>
+      <c r="H21" s="187" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="187" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" s="189" t="n">
+        <v>62</v>
+      </c>
+      <c r="K21" s="186" t="inlineStr">
+        <is>
+          <t>3:311</t>
+        </is>
+      </c>
+      <c r="L21" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="190" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B22" s="186" t="inlineStr">
+        <is>
+          <t>文章の文法</t>
+        </is>
+      </c>
+      <c r="C22" s="187" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D22" s="187" t="n">
+        <v>400</v>
+      </c>
+      <c r="E22" s="188" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="F22" s="187" t="n">
+        <v>50</v>
+      </c>
+      <c r="G22" s="186" t="inlineStr"/>
+      <c r="H22" s="187" t="n">
+        <v>80</v>
+      </c>
+      <c r="I22" s="187" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" s="189" t="n">
+        <v>80</v>
+      </c>
+      <c r="K22" s="186" t="inlineStr">
+        <is>
+          <t>3:400</t>
+        </is>
+      </c>
+      <c r="L22" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="190" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B23" s="186" t="inlineStr">
+        <is>
+          <t>文章の文法</t>
+        </is>
+      </c>
+      <c r="C23" s="187" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D23" s="187" t="n">
+        <v>300</v>
+      </c>
+      <c r="E23" s="188" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="F23" s="187" t="n">
+        <v>50</v>
+      </c>
+      <c r="G23" s="186" t="inlineStr"/>
+      <c r="H23" s="187" t="n">
+        <v>60</v>
+      </c>
+      <c r="I23" s="187" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" s="189" t="n">
+        <v>60</v>
+      </c>
+      <c r="K23" s="186" t="inlineStr">
+        <is>
+          <t>3:300</t>
+        </is>
+      </c>
+      <c r="L23" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="190" t="inlineStr">
+        <is>
+          <t>文法</t>
+        </is>
+      </c>
+      <c r="B24" s="186" t="inlineStr">
+        <is>
+          <t>文章の文法</t>
+        </is>
+      </c>
+      <c r="C24" s="187" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D24" s="187" t="n">
+        <v>350</v>
+      </c>
+      <c r="E24" s="188" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="F24" s="187" t="n">
+        <v>50</v>
+      </c>
+      <c r="G24" s="186" t="inlineStr"/>
+      <c r="H24" s="187" t="n">
+        <v>70</v>
+      </c>
+      <c r="I24" s="187" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" s="189" t="n">
+        <v>70</v>
+      </c>
+      <c r="K24" s="186" t="inlineStr">
+        <is>
+          <t>3:350</t>
+        </is>
+      </c>
+      <c r="L24" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="191" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B25" s="186" t="inlineStr">
+        <is>
+          <t>内容理解(短文)</t>
+        </is>
+      </c>
+      <c r="C25" s="187" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D25" s="187" t="n">
+        <v>90</v>
+      </c>
+      <c r="E25" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F25" s="187" t="n">
+        <v>30</v>
+      </c>
+      <c r="G25" s="186" t="inlineStr"/>
+      <c r="H25" s="187" t="n">
+        <v>90</v>
+      </c>
+      <c r="I25" s="187" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" s="189" t="n">
+        <v>30</v>
+      </c>
+      <c r="K25" s="186" t="inlineStr">
+        <is>
+          <t>3:90</t>
+        </is>
+      </c>
+      <c r="L25" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="191" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B26" s="186" t="inlineStr">
+        <is>
+          <t>内容理解(短文)</t>
+        </is>
+      </c>
+      <c r="C26" s="187" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D26" s="187" t="n">
         <v>120</v>
       </c>
-      <c r="K15" s="52" t="inlineStr">
-        <is>
-          <t>3:531 / 4:28 / 5:27 / 6:14</t>
-        </is>
-      </c>
-      <c r="L15" s="53" t="inlineStr">
+      <c r="E26" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F26" s="187" t="n">
+        <v>40</v>
+      </c>
+      <c r="G26" s="186" t="inlineStr"/>
+      <c r="H26" s="187" t="n">
+        <v>120</v>
+      </c>
+      <c r="I26" s="187" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" s="189" t="n">
+        <v>30</v>
+      </c>
+      <c r="K26" s="186" t="inlineStr">
+        <is>
+          <t>3:120</t>
+        </is>
+      </c>
+      <c r="L26" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="56" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B16" s="52" t="inlineStr">
-        <is>
-          <t>文法形式</t>
-        </is>
-      </c>
-      <c r="C16" s="53" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="191" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B27" s="186" t="inlineStr">
+        <is>
+          <t>内容理解(短文)</t>
+        </is>
+      </c>
+      <c r="C27" s="187" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D27" s="187" t="n">
+        <v>120</v>
+      </c>
+      <c r="E27" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F27" s="187" t="n">
+        <v>40</v>
+      </c>
+      <c r="G27" s="186" t="inlineStr"/>
+      <c r="H27" s="187" t="n">
+        <v>120</v>
+      </c>
+      <c r="I27" s="187" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" s="189" t="n">
+        <v>30</v>
+      </c>
+      <c r="K27" s="186" t="inlineStr">
+        <is>
+          <t>3:120</t>
+        </is>
+      </c>
+      <c r="L27" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="191" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B28" s="186" t="inlineStr">
+        <is>
+          <t>内容理解(中文)</t>
+        </is>
+      </c>
+      <c r="C28" s="187" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="D16" s="53" t="n">
-        <v>398</v>
-      </c>
-      <c r="E16" s="54" t="inlineStr">
-        <is>
-          <t>×4</t>
-        </is>
-      </c>
-      <c r="F16" s="53" t="n">
+      <c r="D28" s="187" t="n">
+        <v>80</v>
+      </c>
+      <c r="E28" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F28" s="187" t="n">
+        <v>20</v>
+      </c>
+      <c r="G28" s="186" t="inlineStr"/>
+      <c r="H28" s="187" t="n">
+        <v>40</v>
+      </c>
+      <c r="I28" s="187" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="189" t="n">
+        <v>40</v>
+      </c>
+      <c r="K28" s="186" t="inlineStr">
+        <is>
+          <t>3:80</t>
+        </is>
+      </c>
+      <c r="L28" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="191" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B29" s="186" t="inlineStr">
+        <is>
+          <t>内容理解(中文)</t>
+        </is>
+      </c>
+      <c r="C29" s="187" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D29" s="187" t="n">
         <v>160</v>
       </c>
-      <c r="G16" s="52" t="n"/>
-      <c r="H16" s="53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" s="53" t="n">
-        <v>16</v>
-      </c>
-      <c r="J16" s="55" t="n">
-        <v>24</v>
-      </c>
-      <c r="K16" s="52" t="inlineStr">
-        <is>
-          <t>3:397 / 4:1</t>
-        </is>
-      </c>
-      <c r="L16" s="53" t="inlineStr">
+      <c r="E29" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F29" s="187" t="n">
+        <v>40</v>
+      </c>
+      <c r="G29" s="186" t="inlineStr"/>
+      <c r="H29" s="187" t="n">
+        <v>40</v>
+      </c>
+      <c r="I29" s="187" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" s="189" t="n">
+        <v>40</v>
+      </c>
+      <c r="K29" s="186" t="inlineStr">
+        <is>
+          <t>3:160</t>
+        </is>
+      </c>
+      <c r="L29" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="56" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B17" s="52" t="inlineStr">
-        <is>
-          <t>文法形式</t>
-        </is>
-      </c>
-      <c r="C17" s="53" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="191" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B30" s="186" t="inlineStr">
+        <is>
+          <t>内容理解(中文)</t>
+        </is>
+      </c>
+      <c r="C30" s="187" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D30" s="187" t="n">
+        <v>240</v>
+      </c>
+      <c r="E30" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F30" s="187" t="n">
+        <v>60</v>
+      </c>
+      <c r="G30" s="186" t="inlineStr"/>
+      <c r="H30" s="187" t="n">
+        <v>80</v>
+      </c>
+      <c r="I30" s="187" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" s="189" t="n">
+        <v>40</v>
+      </c>
+      <c r="K30" s="186" t="inlineStr">
+        <is>
+          <t>3:240</t>
+        </is>
+      </c>
+      <c r="L30" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="191" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B31" s="186" t="inlineStr">
+        <is>
+          <t>内容理解(長文)</t>
+        </is>
+      </c>
+      <c r="C31" s="187" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D31" s="187" t="n">
+        <v>160</v>
+      </c>
+      <c r="E31" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F31" s="187" t="n">
+        <v>40</v>
+      </c>
+      <c r="G31" s="186" t="inlineStr"/>
+      <c r="H31" s="187" t="n">
+        <v>40</v>
+      </c>
+      <c r="I31" s="187" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" s="189" t="n">
+        <v>40</v>
+      </c>
+      <c r="K31" s="186" t="inlineStr">
+        <is>
+          <t>3:160</t>
+        </is>
+      </c>
+      <c r="L31" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="191" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B32" s="186" t="inlineStr">
+        <is>
+          <t>情報検索</t>
+        </is>
+      </c>
+      <c r="C32" s="187" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D32" s="187" t="n">
+        <v>60</v>
+      </c>
+      <c r="E32" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F32" s="187" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="186" t="inlineStr"/>
+      <c r="H32" s="187" t="n">
+        <v>60</v>
+      </c>
+      <c r="I32" s="187" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="189" t="n">
+        <v>60</v>
+      </c>
+      <c r="K32" s="186" t="inlineStr">
+        <is>
+          <t>3:60</t>
+        </is>
+      </c>
+      <c r="L32" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="191" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B33" s="186" t="inlineStr">
+        <is>
+          <t>情報検索</t>
+        </is>
+      </c>
+      <c r="C33" s="187" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="D17" s="53" t="n">
-        <v>361</v>
-      </c>
-      <c r="E17" s="54" t="inlineStr">
-        <is>
-          <t>×3</t>
-        </is>
-      </c>
-      <c r="F17" s="53" t="n">
+      <c r="D33" s="187" t="n">
+        <v>60</v>
+      </c>
+      <c r="E33" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F33" s="187" t="n">
+        <v>20</v>
+      </c>
+      <c r="G33" s="186" t="inlineStr"/>
+      <c r="H33" s="187" t="n">
+        <v>60</v>
+      </c>
+      <c r="I33" s="187" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" s="189" t="n">
+        <v>30</v>
+      </c>
+      <c r="K33" s="186" t="inlineStr">
+        <is>
+          <t>3:60</t>
+        </is>
+      </c>
+      <c r="L33" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="191" t="inlineStr">
+        <is>
+          <t>読解</t>
+        </is>
+      </c>
+      <c r="B34" s="186" t="inlineStr">
+        <is>
+          <t>情報検索</t>
+        </is>
+      </c>
+      <c r="C34" s="187" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D34" s="187" t="n">
+        <v>60</v>
+      </c>
+      <c r="E34" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F34" s="187" t="n">
+        <v>20</v>
+      </c>
+      <c r="G34" s="186" t="inlineStr"/>
+      <c r="H34" s="187" t="n">
+        <v>60</v>
+      </c>
+      <c r="I34" s="187" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" s="189" t="n">
+        <v>30</v>
+      </c>
+      <c r="K34" s="186" t="inlineStr">
+        <is>
+          <t>3:60</t>
+        </is>
+      </c>
+      <c r="L34" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="192" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B35" s="186" t="inlineStr">
+        <is>
+          <t>課題理解</t>
+        </is>
+      </c>
+      <c r="C35" s="187" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D35" s="187" t="n">
         <v>150</v>
       </c>
-      <c r="G17" s="52" t="n"/>
-      <c r="H17" s="53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" s="53" t="n">
-        <v>15</v>
-      </c>
-      <c r="J17" s="55" t="n">
-        <v>24</v>
-      </c>
-      <c r="K17" s="52" t="inlineStr">
-        <is>
-          <t>3:361</t>
-        </is>
-      </c>
-      <c r="L17" s="53" t="inlineStr">
+      <c r="E35" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F35" s="187" t="n">
+        <v>70</v>
+      </c>
+      <c r="G35" s="186" t="inlineStr"/>
+      <c r="H35" s="187" t="n">
+        <v>150</v>
+      </c>
+      <c r="I35" s="187" t="n">
+        <v>7</v>
+      </c>
+      <c r="J35" s="189" t="n">
+        <v>21</v>
+      </c>
+      <c r="K35" s="186" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="L35" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="56" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B18" s="52" t="inlineStr">
-        <is>
-          <t>文法形式</t>
-        </is>
-      </c>
-      <c r="C18" s="53" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="192" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B36" s="186" t="inlineStr">
+        <is>
+          <t>課題理解</t>
+        </is>
+      </c>
+      <c r="C36" s="187" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D36" s="187" t="n">
+        <v>150</v>
+      </c>
+      <c r="E36" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F36" s="187" t="n">
+        <v>80</v>
+      </c>
+      <c r="G36" s="186" t="inlineStr"/>
+      <c r="H36" s="187" t="n">
+        <v>150</v>
+      </c>
+      <c r="I36" s="187" t="n">
+        <v>8</v>
+      </c>
+      <c r="J36" s="189" t="n">
+        <v>18</v>
+      </c>
+      <c r="K36" s="186" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="L36" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="192" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B37" s="186" t="inlineStr">
+        <is>
+          <t>課題理解</t>
+        </is>
+      </c>
+      <c r="C37" s="187" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="D18" s="53" t="n">
-        <v>448</v>
-      </c>
-      <c r="E18" s="54" t="inlineStr">
-        <is>
-          <t>×2</t>
-        </is>
-      </c>
-      <c r="F18" s="53" t="n">
-        <v>130</v>
-      </c>
-      <c r="G18" s="52" t="n"/>
-      <c r="H18" s="53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I18" s="53" t="n">
-        <v>13</v>
-      </c>
-      <c r="J18" s="55" t="n">
-        <v>34</v>
-      </c>
-      <c r="K18" s="52" t="inlineStr">
-        <is>
-          <t>3:446 / 4:2</t>
-        </is>
-      </c>
-      <c r="L18" s="53" t="inlineStr">
+      <c r="D37" s="187" t="n">
+        <v>150</v>
+      </c>
+      <c r="E37" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F37" s="187" t="n">
+        <v>60</v>
+      </c>
+      <c r="G37" s="186" t="inlineStr"/>
+      <c r="H37" s="187" t="n">
+        <v>150</v>
+      </c>
+      <c r="I37" s="187" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" s="189" t="n">
+        <v>25</v>
+      </c>
+      <c r="K37" s="186" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="L37" s="187" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="56" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B19" s="52" t="inlineStr">
-        <is>
-          <t>組み立て</t>
-        </is>
-      </c>
-      <c r="C19" s="53" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="192" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B38" s="186" t="inlineStr">
+        <is>
+          <t>ポイント理解</t>
+        </is>
+      </c>
+      <c r="C38" s="187" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="D19" s="53" t="n">
-        <v>146</v>
-      </c>
-      <c r="E19" s="54" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="F19" s="53" t="n">
+      <c r="D38" s="187" t="n">
+        <v>150</v>
+      </c>
+      <c r="E38" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F38" s="187" t="n">
+        <v>60</v>
+      </c>
+      <c r="G38" s="186" t="inlineStr"/>
+      <c r="H38" s="187" t="n">
+        <v>150</v>
+      </c>
+      <c r="I38" s="187" t="n">
+        <v>6</v>
+      </c>
+      <c r="J38" s="189" t="n">
+        <v>25</v>
+      </c>
+      <c r="K38" s="186" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="L38" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="192" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B39" s="186" t="inlineStr">
+        <is>
+          <t>ポイント理解</t>
+        </is>
+      </c>
+      <c r="C39" s="187" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D39" s="187" t="n">
+        <v>150</v>
+      </c>
+      <c r="E39" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F39" s="187" t="n">
+        <v>70</v>
+      </c>
+      <c r="G39" s="186" t="inlineStr"/>
+      <c r="H39" s="187" t="n">
+        <v>150</v>
+      </c>
+      <c r="I39" s="187" t="n">
+        <v>7</v>
+      </c>
+      <c r="J39" s="189" t="n">
+        <v>21</v>
+      </c>
+      <c r="K39" s="186" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="L39" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="192" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B40" s="186" t="inlineStr">
+        <is>
+          <t>ポイント理解</t>
+        </is>
+      </c>
+      <c r="C40" s="187" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D40" s="187" t="n">
+        <v>150</v>
+      </c>
+      <c r="E40" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F40" s="187" t="n">
+        <v>60</v>
+      </c>
+      <c r="G40" s="186" t="inlineStr"/>
+      <c r="H40" s="187" t="n">
+        <v>150</v>
+      </c>
+      <c r="I40" s="187" t="n">
+        <v>6</v>
+      </c>
+      <c r="J40" s="189" t="n">
+        <v>25</v>
+      </c>
+      <c r="K40" s="186" t="inlineStr">
+        <is>
+          <t>3:150</t>
+        </is>
+      </c>
+      <c r="L40" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="192" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B41" s="186" t="inlineStr">
+        <is>
+          <t>概要理解</t>
+        </is>
+      </c>
+      <c r="C41" s="187" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="D41" s="187" t="n">
+        <v>80</v>
+      </c>
+      <c r="E41" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F41" s="187" t="n">
+        <v>30</v>
+      </c>
+      <c r="G41" s="186" t="inlineStr"/>
+      <c r="H41" s="187" t="n">
+        <v>80</v>
+      </c>
+      <c r="I41" s="187" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" s="189" t="n">
+        <v>26</v>
+      </c>
+      <c r="K41" s="186" t="inlineStr">
+        <is>
+          <t>3:80</t>
+        </is>
+      </c>
+      <c r="L41" s="187" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="192" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B42" s="186" t="inlineStr">
+        <is>
+          <t>発話表現</t>
+        </is>
+      </c>
+      <c r="C42" s="187" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="D42" s="187" t="n">
+        <v>200</v>
+      </c>
+      <c r="E42" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F42" s="187" t="n">
         <v>50</v>
       </c>
-      <c r="G19" s="52" t="n"/>
-      <c r="H19" s="53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I19" s="53" t="n">
+      <c r="G42" s="186" t="inlineStr"/>
+      <c r="H42" s="187" t="n">
+        <v>200</v>
+      </c>
+      <c r="I42" s="187" t="n">
         <v>5</v>
       </c>
-      <c r="J19" s="55" t="n">
-        <v>29</v>
-      </c>
-      <c r="K19" s="52" t="inlineStr">
-        <is>
-          <t>3:146</t>
-        </is>
-      </c>
-      <c r="L19" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="56" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B20" s="52" t="inlineStr">
-        <is>
-          <t>組み立て</t>
-        </is>
-      </c>
-      <c r="C20" s="53" t="inlineStr">
+      <c r="J42" s="189" t="n">
+        <v>40</v>
+      </c>
+      <c r="K42" s="186" t="inlineStr">
+        <is>
+          <t>2:200</t>
+        </is>
+      </c>
+      <c r="L42" s="187" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="192" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B43" s="186" t="inlineStr">
+        <is>
+          <t>発話表現</t>
+        </is>
+      </c>
+      <c r="C43" s="187" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="D20" s="53" t="n">
-        <v>216</v>
-      </c>
-      <c r="E20" s="54" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="F20" s="53" t="n">
+      <c r="D43" s="187" t="n">
+        <v>200</v>
+      </c>
+      <c r="E43" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F43" s="187" t="n">
         <v>50</v>
       </c>
-      <c r="G20" s="52" t="n"/>
-      <c r="H20" s="53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" s="53" t="n">
+      <c r="G43" s="186" t="inlineStr"/>
+      <c r="H43" s="187" t="n">
+        <v>200</v>
+      </c>
+      <c r="I43" s="187" t="n">
         <v>5</v>
       </c>
-      <c r="J20" s="55" t="n">
-        <v>43</v>
-      </c>
-      <c r="K20" s="52" t="inlineStr">
-        <is>
-          <t>3:216</t>
-        </is>
-      </c>
-      <c r="L20" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="56" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B21" s="52" t="inlineStr">
-        <is>
-          <t>組み立て</t>
-        </is>
-      </c>
-      <c r="C21" s="53" t="inlineStr">
+      <c r="J43" s="189" t="n">
+        <v>40</v>
+      </c>
+      <c r="K43" s="186" t="inlineStr">
+        <is>
+          <t>2:200</t>
+        </is>
+      </c>
+      <c r="L43" s="187" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="192" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B44" s="186" t="inlineStr">
+        <is>
+          <t>発話表現</t>
+        </is>
+      </c>
+      <c r="C44" s="187" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="D21" s="53" t="n">
-        <v>311</v>
-      </c>
-      <c r="E21" s="54" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="F21" s="53" t="n">
+      <c r="D44" s="187" t="n">
+        <v>200</v>
+      </c>
+      <c r="E44" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F44" s="187" t="n">
+        <v>40</v>
+      </c>
+      <c r="G44" s="186" t="inlineStr"/>
+      <c r="H44" s="187" t="n">
+        <v>200</v>
+      </c>
+      <c r="I44" s="187" t="n">
+        <v>4</v>
+      </c>
+      <c r="J44" s="189" t="n">
         <v>50</v>
       </c>
-      <c r="G21" s="52" t="n"/>
-      <c r="H21" s="53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I21" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" s="55" t="n">
-        <v>62</v>
-      </c>
-      <c r="K21" s="52" t="inlineStr">
-        <is>
-          <t>3:311</t>
-        </is>
-      </c>
-      <c r="L21" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="56" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B22" s="52" t="inlineStr">
-        <is>
-          <t>文章の文法</t>
-        </is>
-      </c>
-      <c r="C22" s="53" t="inlineStr">
+      <c r="K44" s="186" t="inlineStr">
+        <is>
+          <t>2:200</t>
+        </is>
+      </c>
+      <c r="L44" s="187" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="192" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B45" s="186" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="C45" s="187" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="D22" s="53" t="n">
-        <v>400</v>
-      </c>
-      <c r="E22" s="54" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
-      <c r="F22" s="53" t="n">
-        <v>50</v>
-      </c>
-      <c r="G22" s="52" t="n"/>
-      <c r="H22" s="53" t="n">
+      <c r="D45" s="187" t="n">
+        <v>240</v>
+      </c>
+      <c r="E45" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F45" s="187" t="n">
+        <v>60</v>
+      </c>
+      <c r="G45" s="186" t="inlineStr"/>
+      <c r="H45" s="187" t="n">
+        <v>240</v>
+      </c>
+      <c r="I45" s="187" t="n">
+        <v>6</v>
+      </c>
+      <c r="J45" s="189" t="n">
+        <v>40</v>
+      </c>
+      <c r="K45" s="186" t="inlineStr">
+        <is>
+          <t>2:240</t>
+        </is>
+      </c>
+      <c r="L45" s="187" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="192" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B46" s="186" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="C46" s="187" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="D46" s="187" t="n">
+        <v>240</v>
+      </c>
+      <c r="E46" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F46" s="187" t="n">
         <v>80</v>
       </c>
-      <c r="I22" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" s="55" t="n">
-        <v>80</v>
-      </c>
-      <c r="K22" s="52" t="inlineStr">
-        <is>
-          <t>3:400</t>
-        </is>
-      </c>
-      <c r="L22" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="56" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B23" s="52" t="inlineStr">
-        <is>
-          <t>文章の文法</t>
-        </is>
-      </c>
-      <c r="C23" s="53" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D23" s="53" t="n">
-        <v>300</v>
-      </c>
-      <c r="E23" s="54" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
-      <c r="F23" s="53" t="n">
-        <v>50</v>
-      </c>
-      <c r="G23" s="52" t="n"/>
-      <c r="H23" s="53" t="n">
-        <v>60</v>
-      </c>
-      <c r="I23" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="J23" s="55" t="n">
-        <v>60</v>
-      </c>
-      <c r="K23" s="52" t="inlineStr">
-        <is>
-          <t>3:300</t>
-        </is>
-      </c>
-      <c r="L23" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="56" t="inlineStr">
-        <is>
-          <t>文法</t>
-        </is>
-      </c>
-      <c r="B24" s="52" t="inlineStr">
-        <is>
-          <t>文章の文法</t>
-        </is>
-      </c>
-      <c r="C24" s="53" t="inlineStr">
+      <c r="G46" s="186" t="inlineStr"/>
+      <c r="H46" s="187" t="n">
+        <v>240</v>
+      </c>
+      <c r="I46" s="187" t="n">
+        <v>8</v>
+      </c>
+      <c r="J46" s="189" t="n">
+        <v>30</v>
+      </c>
+      <c r="K46" s="186" t="inlineStr">
+        <is>
+          <t>2:240</t>
+        </is>
+      </c>
+      <c r="L46" s="187" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="192" t="inlineStr">
+        <is>
+          <t>聴解</t>
+        </is>
+      </c>
+      <c r="B47" s="186" t="inlineStr">
+        <is>
+          <t>即時応答</t>
+        </is>
+      </c>
+      <c r="C47" s="187" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="D24" s="53" t="n">
-        <v>350</v>
-      </c>
-      <c r="E24" s="54" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="F24" s="53" t="n">
-        <v>50</v>
-      </c>
-      <c r="G24" s="52" t="n"/>
-      <c r="H24" s="53" t="n">
-        <v>70</v>
-      </c>
-      <c r="I24" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" s="55" t="n">
-        <v>70</v>
-      </c>
-      <c r="K24" s="52" t="inlineStr">
-        <is>
-          <t>3:350</t>
-        </is>
-      </c>
-      <c r="L24" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="57" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B25" s="52" t="inlineStr">
-        <is>
-          <t>内容理解(短文)</t>
-        </is>
-      </c>
-      <c r="C25" s="53" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D25" s="53" t="n">
+      <c r="D47" s="187" t="n">
+        <v>240</v>
+      </c>
+      <c r="E47" s="187" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+      <c r="F47" s="187" t="n">
         <v>90</v>
       </c>
-      <c r="E25" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F25" s="53" t="n">
-        <v>30</v>
-      </c>
-      <c r="G25" s="52" t="n"/>
-      <c r="H25" s="53" t="n">
-        <v>90</v>
-      </c>
-      <c r="I25" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" s="55" t="n">
-        <v>30</v>
-      </c>
-      <c r="K25" s="52" t="inlineStr">
-        <is>
-          <t>3:90</t>
-        </is>
-      </c>
-      <c r="L25" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="57" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B26" s="52" t="inlineStr">
-        <is>
-          <t>内容理解(短文)</t>
-        </is>
-      </c>
-      <c r="C26" s="53" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D26" s="53" t="n">
-        <v>120</v>
-      </c>
-      <c r="E26" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F26" s="53" t="n">
-        <v>40</v>
-      </c>
-      <c r="G26" s="52" t="n"/>
-      <c r="H26" s="53" t="n">
-        <v>120</v>
-      </c>
-      <c r="I26" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="J26" s="55" t="n">
-        <v>30</v>
-      </c>
-      <c r="K26" s="52" t="inlineStr">
-        <is>
-          <t>3:120</t>
-        </is>
-      </c>
-      <c r="L26" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="57" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B27" s="52" t="inlineStr">
-        <is>
-          <t>内容理解(短文)</t>
-        </is>
-      </c>
-      <c r="C27" s="53" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D27" s="53" t="n">
-        <v>120</v>
-      </c>
-      <c r="E27" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F27" s="53" t="n">
-        <v>40</v>
-      </c>
-      <c r="G27" s="52" t="n"/>
-      <c r="H27" s="53" t="n">
-        <v>120</v>
-      </c>
-      <c r="I27" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="J27" s="55" t="n">
-        <v>30</v>
-      </c>
-      <c r="K27" s="52" t="inlineStr">
-        <is>
-          <t>3:120</t>
-        </is>
-      </c>
-      <c r="L27" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="57" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B28" s="52" t="inlineStr">
-        <is>
-          <t>内容理解(中文)</t>
-        </is>
-      </c>
-      <c r="C28" s="53" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D28" s="53" t="n">
-        <v>80</v>
-      </c>
-      <c r="E28" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F28" s="53" t="n">
-        <v>20</v>
-      </c>
-      <c r="G28" s="52" t="n"/>
-      <c r="H28" s="53" t="n">
-        <v>40</v>
-      </c>
-      <c r="I28" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="55" t="n">
-        <v>40</v>
-      </c>
-      <c r="K28" s="52" t="inlineStr">
-        <is>
-          <t>3:80</t>
-        </is>
-      </c>
-      <c r="L28" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="57" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B29" s="52" t="inlineStr">
-        <is>
-          <t>内容理解(中文)</t>
-        </is>
-      </c>
-      <c r="C29" s="53" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D29" s="53" t="n">
-        <v>160</v>
-      </c>
-      <c r="E29" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F29" s="53" t="n">
-        <v>40</v>
-      </c>
-      <c r="G29" s="52" t="n"/>
-      <c r="H29" s="53" t="n">
-        <v>40</v>
-      </c>
-      <c r="I29" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="J29" s="55" t="n">
-        <v>40</v>
-      </c>
-      <c r="K29" s="52" t="inlineStr">
-        <is>
-          <t>3:160</t>
-        </is>
-      </c>
-      <c r="L29" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="57" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B30" s="52" t="inlineStr">
-        <is>
-          <t>内容理解(中文)</t>
-        </is>
-      </c>
-      <c r="C30" s="53" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D30" s="53" t="n">
+      <c r="G47" s="186" t="inlineStr"/>
+      <c r="H47" s="187" t="n">
         <v>240</v>
       </c>
-      <c r="E30" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F30" s="53" t="n">
-        <v>60</v>
-      </c>
-      <c r="G30" s="52" t="n"/>
-      <c r="H30" s="53" t="n">
-        <v>80</v>
-      </c>
-      <c r="I30" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="J30" s="55" t="n">
-        <v>40</v>
-      </c>
-      <c r="K30" s="52" t="inlineStr">
-        <is>
-          <t>3:240</t>
-        </is>
-      </c>
-      <c r="L30" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="57" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B31" s="52" t="inlineStr">
-        <is>
-          <t>内容理解(長文)</t>
-        </is>
-      </c>
-      <c r="C31" s="53" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D31" s="53" t="n">
-        <v>160</v>
-      </c>
-      <c r="E31" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F31" s="53" t="n">
-        <v>40</v>
-      </c>
-      <c r="G31" s="52" t="n"/>
-      <c r="H31" s="53" t="n">
-        <v>40</v>
-      </c>
-      <c r="I31" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="J31" s="55" t="n">
-        <v>40</v>
-      </c>
-      <c r="K31" s="52" t="inlineStr">
-        <is>
-          <t>3:160</t>
-        </is>
-      </c>
-      <c r="L31" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="57" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B32" s="52" t="inlineStr">
-        <is>
-          <t>情報検索</t>
-        </is>
-      </c>
-      <c r="C32" s="53" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D32" s="53" t="n">
-        <v>60</v>
-      </c>
-      <c r="E32" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F32" s="53" t="n">
-        <v>10</v>
-      </c>
-      <c r="G32" s="52" t="n"/>
-      <c r="H32" s="53" t="n">
-        <v>60</v>
-      </c>
-      <c r="I32" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="55" t="n">
-        <v>60</v>
-      </c>
-      <c r="K32" s="52" t="inlineStr">
-        <is>
-          <t>3:60</t>
-        </is>
-      </c>
-      <c r="L32" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="57" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B33" s="52" t="inlineStr">
-        <is>
-          <t>情報検索</t>
-        </is>
-      </c>
-      <c r="C33" s="53" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D33" s="53" t="n">
-        <v>60</v>
-      </c>
-      <c r="E33" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F33" s="53" t="n">
-        <v>20</v>
-      </c>
-      <c r="G33" s="52" t="n"/>
-      <c r="H33" s="53" t="n">
-        <v>60</v>
-      </c>
-      <c r="I33" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" s="55" t="n">
-        <v>30</v>
-      </c>
-      <c r="K33" s="52" t="inlineStr">
-        <is>
-          <t>3:60</t>
-        </is>
-      </c>
-      <c r="L33" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="57" t="inlineStr">
-        <is>
-          <t>読解</t>
-        </is>
-      </c>
-      <c r="B34" s="52" t="inlineStr">
-        <is>
-          <t>情報検索</t>
-        </is>
-      </c>
-      <c r="C34" s="53" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D34" s="53" t="n">
-        <v>60</v>
-      </c>
-      <c r="E34" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F34" s="53" t="n">
-        <v>20</v>
-      </c>
-      <c r="G34" s="52" t="n"/>
-      <c r="H34" s="53" t="n">
-        <v>60</v>
-      </c>
-      <c r="I34" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="55" t="n">
-        <v>30</v>
-      </c>
-      <c r="K34" s="52" t="inlineStr">
-        <is>
-          <t>3:60</t>
-        </is>
-      </c>
-      <c r="L34" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="58" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B35" s="52" t="inlineStr">
-        <is>
-          <t>課題理解</t>
-        </is>
-      </c>
-      <c r="C35" s="53" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D35" s="53" t="n">
-        <v>150</v>
-      </c>
-      <c r="E35" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F35" s="53" t="n">
-        <v>70</v>
-      </c>
-      <c r="G35" s="52" t="n"/>
-      <c r="H35" s="53" t="n">
-        <v>150</v>
-      </c>
-      <c r="I35" s="53" t="n">
-        <v>7</v>
-      </c>
-      <c r="J35" s="55" t="n">
-        <v>21</v>
-      </c>
-      <c r="K35" s="52" t="inlineStr">
-        <is>
-          <t>3:150</t>
-        </is>
-      </c>
-      <c r="L35" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="58" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B36" s="52" t="inlineStr">
-        <is>
-          <t>課題理解</t>
-        </is>
-      </c>
-      <c r="C36" s="53" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D36" s="53" t="n">
-        <v>150</v>
-      </c>
-      <c r="E36" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F36" s="53" t="n">
-        <v>80</v>
-      </c>
-      <c r="G36" s="52" t="n"/>
-      <c r="H36" s="53" t="n">
-        <v>150</v>
-      </c>
-      <c r="I36" s="53" t="n">
-        <v>8</v>
-      </c>
-      <c r="J36" s="55" t="n">
-        <v>18</v>
-      </c>
-      <c r="K36" s="52" t="inlineStr">
-        <is>
-          <t>3:150</t>
-        </is>
-      </c>
-      <c r="L36" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="58" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B37" s="52" t="inlineStr">
-        <is>
-          <t>課題理解</t>
-        </is>
-      </c>
-      <c r="C37" s="53" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D37" s="53" t="n">
-        <v>150</v>
-      </c>
-      <c r="E37" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F37" s="53" t="n">
-        <v>60</v>
-      </c>
-      <c r="G37" s="52" t="n"/>
-      <c r="H37" s="53" t="n">
-        <v>150</v>
-      </c>
-      <c r="I37" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="J37" s="55" t="n">
-        <v>25</v>
-      </c>
-      <c r="K37" s="52" t="inlineStr">
-        <is>
-          <t>3:150</t>
-        </is>
-      </c>
-      <c r="L37" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="58" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B38" s="52" t="inlineStr">
-        <is>
-          <t>ポイント理解</t>
-        </is>
-      </c>
-      <c r="C38" s="53" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D38" s="53" t="n">
-        <v>150</v>
-      </c>
-      <c r="E38" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F38" s="53" t="n">
-        <v>60</v>
-      </c>
-      <c r="G38" s="52" t="n"/>
-      <c r="H38" s="53" t="n">
-        <v>150</v>
-      </c>
-      <c r="I38" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="J38" s="55" t="n">
-        <v>25</v>
-      </c>
-      <c r="K38" s="52" t="inlineStr">
-        <is>
-          <t>3:150</t>
-        </is>
-      </c>
-      <c r="L38" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="58" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B39" s="52" t="inlineStr">
-        <is>
-          <t>ポイント理解</t>
-        </is>
-      </c>
-      <c r="C39" s="53" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D39" s="53" t="n">
-        <v>150</v>
-      </c>
-      <c r="E39" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F39" s="53" t="n">
-        <v>70</v>
-      </c>
-      <c r="G39" s="52" t="n"/>
-      <c r="H39" s="53" t="n">
-        <v>150</v>
-      </c>
-      <c r="I39" s="53" t="n">
-        <v>7</v>
-      </c>
-      <c r="J39" s="55" t="n">
-        <v>21</v>
-      </c>
-      <c r="K39" s="52" t="inlineStr">
-        <is>
-          <t>3:150</t>
-        </is>
-      </c>
-      <c r="L39" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="58" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B40" s="52" t="inlineStr">
-        <is>
-          <t>ポイント理解</t>
-        </is>
-      </c>
-      <c r="C40" s="53" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D40" s="53" t="n">
-        <v>150</v>
-      </c>
-      <c r="E40" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F40" s="53" t="n">
-        <v>60</v>
-      </c>
-      <c r="G40" s="52" t="n"/>
-      <c r="H40" s="53" t="n">
-        <v>150</v>
-      </c>
-      <c r="I40" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="J40" s="55" t="n">
-        <v>25</v>
-      </c>
-      <c r="K40" s="52" t="inlineStr">
-        <is>
-          <t>3:150</t>
-        </is>
-      </c>
-      <c r="L40" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="58" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B41" s="52" t="inlineStr">
-        <is>
-          <t>概要理解</t>
-        </is>
-      </c>
-      <c r="C41" s="53" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D41" s="53" t="n">
-        <v>80</v>
-      </c>
-      <c r="E41" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F41" s="53" t="n">
-        <v>30</v>
-      </c>
-      <c r="G41" s="52" t="n"/>
-      <c r="H41" s="53" t="n">
-        <v>80</v>
-      </c>
-      <c r="I41" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="J41" s="55" t="n">
+      <c r="I47" s="187" t="n">
+        <v>9</v>
+      </c>
+      <c r="J47" s="189" t="n">
         <v>26</v>
       </c>
-      <c r="K41" s="52" t="inlineStr">
-        <is>
-          <t>3:80</t>
-        </is>
-      </c>
-      <c r="L41" s="53" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="58" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B42" s="52" t="inlineStr">
-        <is>
-          <t>発話表現</t>
-        </is>
-      </c>
-      <c r="C42" s="53" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D42" s="53" t="n">
-        <v>200</v>
-      </c>
-      <c r="E42" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F42" s="53" t="n">
-        <v>50</v>
-      </c>
-      <c r="G42" s="52" t="n"/>
-      <c r="H42" s="53" t="n">
-        <v>200</v>
-      </c>
-      <c r="I42" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="J42" s="55" t="n">
-        <v>40</v>
-      </c>
-      <c r="K42" s="52" t="inlineStr">
-        <is>
-          <t>2:200</t>
-        </is>
-      </c>
-      <c r="L42" s="53" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="58" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B43" s="52" t="inlineStr">
-        <is>
-          <t>発話表現</t>
-        </is>
-      </c>
-      <c r="C43" s="53" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D43" s="53" t="n">
-        <v>200</v>
-      </c>
-      <c r="E43" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F43" s="53" t="n">
-        <v>50</v>
-      </c>
-      <c r="G43" s="52" t="n"/>
-      <c r="H43" s="53" t="n">
-        <v>200</v>
-      </c>
-      <c r="I43" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="J43" s="55" t="n">
-        <v>40</v>
-      </c>
-      <c r="K43" s="52" t="inlineStr">
-        <is>
-          <t>2:200</t>
-        </is>
-      </c>
-      <c r="L43" s="53" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="58" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B44" s="52" t="inlineStr">
-        <is>
-          <t>発話表現</t>
-        </is>
-      </c>
-      <c r="C44" s="53" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D44" s="53" t="n">
-        <v>200</v>
-      </c>
-      <c r="E44" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F44" s="53" t="n">
-        <v>40</v>
-      </c>
-      <c r="G44" s="52" t="n"/>
-      <c r="H44" s="53" t="n">
-        <v>200</v>
-      </c>
-      <c r="I44" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="J44" s="55" t="n">
-        <v>50</v>
-      </c>
-      <c r="K44" s="52" t="inlineStr">
-        <is>
-          <t>2:200</t>
-        </is>
-      </c>
-      <c r="L44" s="53" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="58" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B45" s="52" t="inlineStr">
-        <is>
-          <t>即時応答</t>
-        </is>
-      </c>
-      <c r="C45" s="53" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="D45" s="53" t="n">
-        <v>240</v>
-      </c>
-      <c r="E45" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F45" s="53" t="n">
-        <v>60</v>
-      </c>
-      <c r="G45" s="52" t="n"/>
-      <c r="H45" s="53" t="n">
-        <v>240</v>
-      </c>
-      <c r="I45" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="J45" s="55" t="n">
-        <v>40</v>
-      </c>
-      <c r="K45" s="52" t="inlineStr">
+      <c r="K47" s="186" t="inlineStr">
         <is>
           <t>2:240</t>
         </is>
       </c>
-      <c r="L45" s="53" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="58" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B46" s="52" t="inlineStr">
-        <is>
-          <t>即時応答</t>
-        </is>
-      </c>
-      <c r="C46" s="53" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="D46" s="53" t="n">
-        <v>240</v>
-      </c>
-      <c r="E46" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F46" s="53" t="n">
-        <v>80</v>
-      </c>
-      <c r="G46" s="52" t="n"/>
-      <c r="H46" s="53" t="n">
-        <v>240</v>
-      </c>
-      <c r="I46" s="53" t="n">
-        <v>8</v>
-      </c>
-      <c r="J46" s="55" t="n">
-        <v>30</v>
-      </c>
-      <c r="K46" s="52" t="inlineStr">
-        <is>
-          <t>2:240</t>
-        </is>
-      </c>
-      <c r="L46" s="53" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="58" t="inlineStr">
-        <is>
-          <t>聴解</t>
-        </is>
-      </c>
-      <c r="B47" s="52" t="inlineStr">
-        <is>
-          <t>即時応答</t>
-        </is>
-      </c>
-      <c r="C47" s="53" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="D47" s="53" t="n">
-        <v>240</v>
-      </c>
-      <c r="E47" s="53" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-      <c r="F47" s="53" t="n">
-        <v>90</v>
-      </c>
-      <c r="G47" s="52" t="n"/>
-      <c r="H47" s="53" t="n">
-        <v>240</v>
-      </c>
-      <c r="I47" s="53" t="n">
-        <v>9</v>
-      </c>
-      <c r="J47" s="55" t="n">
-        <v>26</v>
-      </c>
-      <c r="K47" s="52" t="inlineStr">
-        <is>
-          <t>2:240</t>
-        </is>
-      </c>
-      <c r="L47" s="53" t="inlineStr">
+      <c r="L47" s="187" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
@@ -3701,159 +3814,161 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="75" min="1" max="1"/>
-    <col width="8" customWidth="1" style="75" min="2" max="4"/>
+    <col width="8" customWidth="1" style="75" min="2" max="2"/>
+    <col width="8" customWidth="1" style="75" min="3" max="3"/>
+    <col width="8" customWidth="1" style="75" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" customHeight="1" s="75">
-      <c r="A1" s="59" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="193" t="inlineStr">
         <is>
           <t>◆ 模試換算 = 在庫 ÷ 本番出題数 = その大問だけで組めるフル模試の回数（floor）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="194" t="inlineStr">
         <is>
           <t>セクション別 律速（そのセクションで最も少ない大問の回数＝そのセクションを何回組めるか）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="155" t="inlineStr">
+      <c r="A4" s="184" t="inlineStr">
         <is>
           <t>セクション</t>
         </is>
       </c>
-      <c r="B4" s="155" t="inlineStr">
+      <c r="B4" s="184" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="C4" s="155" t="inlineStr">
+      <c r="C4" s="184" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="D4" s="155" t="inlineStr">
+      <c r="D4" s="184" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="51" t="inlineStr">
+      <c r="A5" s="185" t="inlineStr">
         <is>
           <t>文字・語彙</t>
         </is>
       </c>
-      <c r="B5" s="61" t="n">
+      <c r="B5" s="195" t="n">
         <v>34</v>
       </c>
-      <c r="C5" s="61" t="n">
+      <c r="C5" s="195" t="n">
         <v>36</v>
       </c>
-      <c r="D5" s="61" t="n">
-        <v>120</v>
+      <c r="D5" s="195" t="n">
+        <v>191</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="56" t="inlineStr">
+      <c r="A6" s="190" t="inlineStr">
         <is>
           <t>文法</t>
         </is>
       </c>
-      <c r="B6" s="61" t="n">
+      <c r="B6" s="195" t="n">
         <v>24</v>
       </c>
-      <c r="C6" s="61" t="n">
+      <c r="C6" s="195" t="n">
         <v>24</v>
       </c>
-      <c r="D6" s="61" t="n">
+      <c r="D6" s="195" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="57" t="inlineStr">
+      <c r="A7" s="191" t="inlineStr">
         <is>
           <t>読解</t>
         </is>
       </c>
-      <c r="B7" s="61" t="n">
+      <c r="B7" s="195" t="n">
         <v>30</v>
       </c>
-      <c r="C7" s="61" t="n">
+      <c r="C7" s="195" t="n">
         <v>30</v>
       </c>
-      <c r="D7" s="61" t="n">
+      <c r="D7" s="195" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="A8" s="192" t="inlineStr">
         <is>
           <t>聴解</t>
         </is>
       </c>
-      <c r="B8" s="61" t="n">
+      <c r="B8" s="195" t="n">
         <v>21</v>
       </c>
-      <c r="C8" s="61" t="n">
+      <c r="C8" s="195" t="n">
         <v>18</v>
       </c>
-      <c r="D8" s="61" t="n">
+      <c r="D8" s="195" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="60" t="inlineStr">
+      <c r="A10" s="194" t="inlineStr">
         <is>
           <t>級ごとの「フル模試」完成可能回数（全大問の最小＝律速大問で決まる）</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="155" t="inlineStr">
+      <c r="A11" s="184" t="inlineStr">
         <is>
           <t>セクション</t>
         </is>
       </c>
-      <c r="B11" s="155" t="inlineStr">
+      <c r="B11" s="184" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="C11" s="155" t="inlineStr">
+      <c r="C11" s="184" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="D11" s="155" t="inlineStr">
+      <c r="D11" s="184" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="52" t="inlineStr">
+      <c r="A12" s="186" t="inlineStr">
         <is>
           <t>フル模試</t>
         </is>
       </c>
-      <c r="B12" s="55" t="n">
+      <c r="B12" s="189" t="n">
         <v>21</v>
       </c>
-      <c r="C12" s="55" t="n">
+      <c r="C12" s="189" t="n">
         <v>18</v>
       </c>
-      <c r="D12" s="55" t="n">
+      <c r="D12" s="189" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="62" t="inlineStr">
+      <c r="A14" s="196" t="inlineStr">
         <is>
           <t>凡例：赤=5回以下(不足) / 橙=15回以下(要増産) / 緑=16回以上(十分)</t>
         </is>
@@ -5078,27 +5193,27 @@
         </is>
       </c>
       <c r="C51" s="9" t="n">
-        <v>595</v>
+        <v>1195</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>595</v>
+        <v>1195</v>
       </c>
       <c r="E51" s="9" t="n">
         <v>2145</v>
       </c>
       <c r="F51" s="80" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="G51" s="12" t="n"/>
       <c r="H51" s="74" t="inlineStr">
         <is>
-          <t>この級の語を対象にした用法問題は595問（＝カバー語595）。母数は級内の全語彙2145語。用法は語を選ばず作れる（構造的な天井なし）＝作問した語自体が母数＝真のカバー率100%。</t>
+          <t>この級の語を対象にした用法問題は1195問（＝カバー語1195）。母数は級内の全語彙2145語。用法は語を選ばず作れる（構造的な天井なし）＝作問した語自体が母数＝真のカバー率100%。</t>
         </is>
       </c>
       <c r="I51" s="17" t="n">
-        <v>595</v>
+        <v>1195</v>
       </c>
       <c r="J51" s="43" t="inlineStr">
         <is>
@@ -9631,7 +9746,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="77" t="inlineStr">
         <is>
@@ -10143,11 +10257,10 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="77" t="inlineStr">
         <is>
-          <t>② UI（画面の文字）　ja=1432 キーが元（全11言語=番人＋自動翻訳で常時100%）</t>
+          <t>② UI（画面の文字）　ja=1433 キーが元（全11言語=番人＋自動翻訳で常時100%）</t>
         </is>
       </c>
     </row>
@@ -10185,10 +10298,10 @@
         </is>
       </c>
       <c r="B21" s="67" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C21" s="66" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D21" s="138" t="inlineStr">
         <is>
@@ -10208,10 +10321,10 @@
         </is>
       </c>
       <c r="B22" s="67" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C22" s="66" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D22" s="138" t="inlineStr">
         <is>
@@ -10231,10 +10344,10 @@
         </is>
       </c>
       <c r="B23" s="67" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C23" s="66" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D23" s="138" t="inlineStr">
         <is>
@@ -10254,10 +10367,10 @@
         </is>
       </c>
       <c r="B24" s="67" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C24" s="66" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D24" s="138" t="inlineStr">
         <is>
@@ -10277,10 +10390,10 @@
         </is>
       </c>
       <c r="B25" s="67" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C25" s="66" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D25" s="138" t="inlineStr">
         <is>
@@ -10300,10 +10413,10 @@
         </is>
       </c>
       <c r="B26" s="67" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C26" s="66" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D26" s="138" t="inlineStr">
         <is>
@@ -10323,10 +10436,10 @@
         </is>
       </c>
       <c r="B27" s="67" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C27" s="66" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D27" s="138" t="inlineStr">
         <is>
@@ -10346,10 +10459,10 @@
         </is>
       </c>
       <c r="B28" s="67" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C28" s="66" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D28" s="138" t="inlineStr">
         <is>
@@ -10369,10 +10482,10 @@
         </is>
       </c>
       <c r="B29" s="67" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C29" s="66" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D29" s="138" t="inlineStr">
         <is>
@@ -10392,10 +10505,10 @@
         </is>
       </c>
       <c r="B30" s="67" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C30" s="66" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D30" s="138" t="inlineStr">
         <is>
@@ -10415,10 +10528,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C31" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D31" s="124" t="inlineStr">
         <is>
@@ -10438,7 +10551,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="77" t="inlineStr">
         <is>
@@ -10836,7 +10948,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="105" t="inlineStr">
         <is>
@@ -12999,7 +13110,6 @@
       <c r="K87" s="82" t="n"/>
       <c r="L87" s="82" t="n"/>
     </row>
-    <row r="88"/>
     <row r="89">
       <c r="A89" s="91" t="inlineStr">
         <is>
@@ -14186,4 +14296,169 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="75" min="1" max="1"/>
+    <col width="12" customWidth="1" style="75" min="2" max="2"/>
+    <col width="12" customWidth="1" style="75" min="3" max="3"/>
+    <col width="12" customWidth="1" style="75" min="4" max="4"/>
+    <col width="12" customWidth="1" style="75" min="5" max="5"/>
+    <col width="12" customWidth="1" style="75" min="6" max="6"/>
+    <col width="12" customWidth="1" style="75" min="7" max="7"/>
+    <col width="12" customWidth="1" style="75" min="8" max="8"/>
+    <col width="66" customWidth="1" style="75" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="179" t="inlineStr">
+        <is>
+          <t>用法(語の使い方) × 語彙idカバー×バランス</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="180" t="inlineStr">
+        <is>
+          <t>最終目標＝可能な限り語彙をカバー(breadth%を100%へ)。番人=src/data/usageCoverage.test.ts が「①未紐づけ0(測定可能) ②大問内で1語1問まで(集中させず広く) ③カバー数は後退させない(ラチェット)」を担保。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="180" t="inlineStr">
+        <is>
+          <t>級跨ぎ重複(同語をN4とN3の両大問で出題=冗長)＝0語。冗長は禁止せず記録のみ(復習として妥当な場合あり)＝新規作問は未カバー語を優先すると breadth が伸びる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="91" t="inlineStr">
+        <is>
+          <t>■ 級別サマリ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="181" t="inlineStr">
+        <is>
+          <t>級</t>
+        </is>
+      </c>
+      <c r="B7" s="181" t="inlineStr">
+        <is>
+          <t>問題数</t>
+        </is>
+      </c>
+      <c r="C7" s="181" t="inlineStr">
+        <is>
+          <t>リンク</t>
+        </is>
+      </c>
+      <c r="D7" s="181" t="inlineStr">
+        <is>
+          <t>未紐づけ</t>
+        </is>
+      </c>
+      <c r="E7" s="181" t="inlineStr">
+        <is>
+          <t>カバー語</t>
+        </is>
+      </c>
+      <c r="F7" s="181" t="inlineStr">
+        <is>
+          <t>母数</t>
+        </is>
+      </c>
+      <c r="G7" s="181" t="inlineStr">
+        <is>
+          <t>breadth%</t>
+        </is>
+      </c>
+      <c r="H7" s="181" t="inlineStr">
+        <is>
+          <t>未カバー(backlog)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>571</v>
+      </c>
+      <c r="C8" t="n">
+        <v>571</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>573</v>
+      </c>
+      <c r="F8" t="n">
+        <v>673</v>
+      </c>
+      <c r="G8" s="182" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>100</v>
+      </c>
+      <c r="I8" s="180" t="inlineStr">
+        <is>
+          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=571</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1195</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2145</v>
+      </c>
+      <c r="G9" s="183" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>950</v>
+      </c>
+      <c r="I9" s="180" t="inlineStr">
+        <is>
+          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=1195 / 下級流出=N5:3, N4:2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/memory/在庫・模試ストックまとめ.xlsx
+++ b/memory/在庫・模試ストックまとめ.xlsx
@@ -289,7 +289,7 @@
       <color rgb="007A756C"/>
     </font>
   </fonts>
-  <fills count="49">
+  <fills count="50">
     <fill>
       <patternFill/>
     </fill>
@@ -533,6 +533,11 @@
         <fgColor rgb="00F3EAF3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE7C0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -663,7 +668,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="197">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1101,6 +1106,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2220,7 +2226,7 @@
         </is>
       </c>
       <c r="D15" s="187" t="n">
-        <v>1200</v>
+        <v>1494</v>
       </c>
       <c r="E15" s="187" t="inlineStr">
         <is>
@@ -2240,11 +2246,11 @@
         <v>5</v>
       </c>
       <c r="J15" s="189" t="n">
-        <v>240</v>
+        <v>298</v>
       </c>
       <c r="K15" s="186" t="inlineStr">
         <is>
-          <t>3:1131 / 4:28 / 5:27 / 6:14</t>
+          <t>3:1425 / 4:28 / 5:27 / 6:14</t>
         </is>
       </c>
       <c r="L15" s="187" t="inlineStr">
@@ -5193,27 +5199,27 @@
         </is>
       </c>
       <c r="C51" s="9" t="n">
-        <v>1195</v>
+        <v>1495</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1195</v>
+        <v>1495</v>
       </c>
       <c r="E51" s="9" t="n">
         <v>2145</v>
       </c>
       <c r="F51" s="80" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="G51" s="12" t="n"/>
       <c r="H51" s="74" t="inlineStr">
         <is>
-          <t>この級の語を対象にした用法問題は1195問（＝カバー語1195）。母数は級内の全語彙2145語。用法は語を選ばず作れる（構造的な天井なし）＝作問した語自体が母数＝真のカバー率100%。</t>
+          <t>この級の語を対象にした用法問題は1495問（＝カバー語1495）。母数は級内の全語彙2145語。用法は語を選ばず作れる（構造的な天井なし）＝作問した語自体が母数＝真のカバー率100%。2026-09-12 新規300問追加(1195→1495・全IDカバー率56→70%)。</t>
         </is>
       </c>
       <c r="I51" s="17" t="n">
-        <v>1195</v>
+        <v>1495</v>
       </c>
       <c r="J51" s="43" t="inlineStr">
         <is>
@@ -9708,7 +9714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M92"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="26" customWidth="1" style="75" min="1" max="1"/>
@@ -9746,6 +9752,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="77" t="inlineStr">
         <is>
@@ -10215,109 +10222,129 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" s="75">
       <c r="A17" t="inlineStr">
         <is>
+          <t>hi（ヒンディー語）</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>母語</t>
+        </is>
+      </c>
+      <c r="C17" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D17" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E17" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F17" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G17" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="124" t="inlineStr">
+        <is>
+          <t>フル</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" s="75">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>zh2（中国語・繁体）</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>母語</t>
         </is>
       </c>
-      <c r="C17" s="124" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D17" s="124" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E17" s="124" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F17" s="124" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G17" s="124" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="124" t="inlineStr">
+      <c r="C18" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D18" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E18" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F18" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G18" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="124" t="inlineStr">
         <is>
           <t>フル</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="77" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="77" t="inlineStr">
         <is>
           <t>② UI（画面の文字）　ja=1433 キーが元（全11言語=番人＋自動翻訳で常時100%）</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="64" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="64" t="inlineStr">
         <is>
           <t>言語</t>
         </is>
       </c>
-      <c r="B20" s="64" t="inlineStr">
+      <c r="B21" s="64" t="inlineStr">
         <is>
           <t>訳済みキー数</t>
         </is>
       </c>
-      <c r="C20" s="64" t="inlineStr">
+      <c r="C21" s="64" t="inlineStr">
         <is>
           <t>総キー</t>
         </is>
       </c>
-      <c r="D20" s="64" t="inlineStr">
+      <c r="D21" s="64" t="inlineStr">
         <is>
           <t>カバー率</t>
         </is>
       </c>
-      <c r="E20" s="64" t="inlineStr">
+      <c r="E21" s="64" t="inlineStr">
         <is>
           <t>状態</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="65" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="B21" s="67" t="n">
-        <v>1433</v>
-      </c>
-      <c r="C21" s="66" t="n">
-        <v>1433</v>
-      </c>
-      <c r="D21" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E21" s="138" t="inlineStr">
-        <is>
-          <t>元</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="65" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="B22" s="67" t="n">
@@ -10333,14 +10360,14 @@
       </c>
       <c r="E22" s="138" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>元</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="65" t="inlineStr">
         <is>
-          <t>ne</t>
+          <t>en</t>
         </is>
       </c>
       <c r="B23" s="67" t="n">
@@ -10363,7 +10390,7 @@
     <row r="24">
       <c r="A24" s="65" t="inlineStr">
         <is>
-          <t>bn</t>
+          <t>ne</t>
         </is>
       </c>
       <c r="B24" s="67" t="n">
@@ -10386,7 +10413,7 @@
     <row r="25">
       <c r="A25" s="65" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>bn</t>
         </is>
       </c>
       <c r="B25" s="67" t="n">
@@ -10409,7 +10436,7 @@
     <row r="26">
       <c r="A26" s="65" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B26" s="67" t="n">
@@ -10432,7 +10459,7 @@
     <row r="27">
       <c r="A27" s="65" t="inlineStr">
         <is>
-          <t>my</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="B27" s="67" t="n">
@@ -10455,7 +10482,7 @@
     <row r="28">
       <c r="A28" s="65" t="inlineStr">
         <is>
-          <t>th</t>
+          <t>my</t>
         </is>
       </c>
       <c r="B28" s="67" t="n">
@@ -10478,7 +10505,7 @@
     <row r="29">
       <c r="A29" s="65" t="inlineStr">
         <is>
-          <t>vi</t>
+          <t>th</t>
         </is>
       </c>
       <c r="B29" s="67" t="n">
@@ -10501,7 +10528,7 @@
     <row r="30">
       <c r="A30" s="65" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>vi</t>
         </is>
       </c>
       <c r="B30" s="67" t="n">
@@ -10522,232 +10549,159 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="65" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="B31" s="67" t="n">
+        <v>1433</v>
+      </c>
+      <c r="C31" s="66" t="n">
+        <v>1433</v>
+      </c>
+      <c r="D31" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E31" s="138" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" s="75">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1433</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1433</v>
+      </c>
+      <c r="D32" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E32" s="124" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" s="75">
+      <c r="A33" t="inlineStr">
         <is>
           <t>zh2</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B33" t="n">
         <v>1433</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C33" t="n">
         <v>1433</v>
       </c>
-      <c r="D31" s="124" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E31" s="124" t="inlineStr">
+      <c r="D33" s="124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E33" s="124" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="76" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="76" t="inlineStr">
         <is>
           <t>※ 新規UIキーは全11言語を同時に用意(2026-09-07変更)。en/neは手書き、他8言語(zh2=OpenCC)はtrans_i18n.py --fillが差分翻訳。番人parity.test.tsが全11言語を強制＋build.ps1が検証前に--fillを自動実行するため、未訳のまま出荷されない。</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="77" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="77" t="inlineStr">
         <is>
           <t>③ 辞書（語彙・漢字・文法・例文）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="64" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="64" t="inlineStr">
         <is>
           <t>種類</t>
         </is>
       </c>
-      <c r="B35" s="64" t="inlineStr">
+      <c r="B37" s="64" t="inlineStr">
         <is>
           <t>総数</t>
         </is>
       </c>
-      <c r="C35" s="64" t="inlineStr">
+      <c r="C37" s="64" t="inlineStr">
         <is>
           <t>日本語(語/読み)</t>
         </is>
       </c>
-      <c r="D35" s="64" t="inlineStr">
+      <c r="D37" s="64" t="inlineStr">
         <is>
           <t>英語(意味)</t>
         </is>
       </c>
-      <c r="E35" s="64" t="inlineStr">
+      <c r="E37" s="64" t="inlineStr">
         <is>
           <t>ネパール語(意味)</t>
         </is>
       </c>
-      <c r="F35" s="64" t="inlineStr">
+      <c r="F37" s="64" t="inlineStr">
         <is>
           <t>ベンガル語</t>
         </is>
       </c>
-      <c r="G35" s="64" t="inlineStr">
+      <c r="G37" s="64" t="inlineStr">
         <is>
           <t>インドネシア語</t>
         </is>
       </c>
-      <c r="H35" s="64" t="inlineStr">
+      <c r="H37" s="64" t="inlineStr">
         <is>
           <t>韓国語</t>
         </is>
       </c>
-      <c r="I35" s="64" t="inlineStr">
+      <c r="I37" s="64" t="inlineStr">
         <is>
           <t>ミャンマー語</t>
         </is>
       </c>
-      <c r="J35" s="64" t="inlineStr">
+      <c r="J37" s="64" t="inlineStr">
         <is>
           <t>タイ語</t>
         </is>
       </c>
-      <c r="K35" s="64" t="inlineStr">
+      <c r="K37" s="64" t="inlineStr">
         <is>
           <t>ベトナム語</t>
         </is>
       </c>
-      <c r="L35" s="64" t="inlineStr">
+      <c r="L37" s="64" t="inlineStr">
         <is>
           <t>中国語</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="65" t="inlineStr">
-        <is>
-          <t>語彙（意味）</t>
-        </is>
-      </c>
-      <c r="B36" s="66" t="n">
-        <v>3540</v>
-      </c>
-      <c r="C36" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D36" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E36" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F36" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G36" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H36" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I36" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J36" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K36" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L36" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="65" t="inlineStr">
-        <is>
-          <t>漢字（意味・音訓）</t>
-        </is>
-      </c>
-      <c r="B37" s="66" t="n">
-        <v>612</v>
-      </c>
-      <c r="C37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E37" s="138" t="inlineStr">
-        <is>
-          <t>100%（語義1859）</t>
-        </is>
-      </c>
-      <c r="F37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L37" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="65" t="inlineStr">
         <is>
-          <t>文法（意味・例文）</t>
+          <t>語彙（意味）</t>
         </is>
       </c>
       <c r="B38" s="66" t="n">
-        <v>408</v>
+        <v>3540</v>
       </c>
       <c r="C38" s="138" t="inlineStr">
         <is>
@@ -10803,555 +10757,543 @@
     <row r="39">
       <c r="A39" s="65" t="inlineStr">
         <is>
+          <t>漢字（意味・音訓）</t>
+        </is>
+      </c>
+      <c r="B39" s="66" t="n">
+        <v>612</v>
+      </c>
+      <c r="C39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E39" s="138" t="inlineStr">
+        <is>
+          <t>100%（語義1859）</t>
+        </is>
+      </c>
+      <c r="F39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L39" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="65" t="inlineStr">
+        <is>
+          <t>文法（意味・例文）</t>
+        </is>
+      </c>
+      <c r="B40" s="66" t="n">
+        <v>408</v>
+      </c>
+      <c r="C40" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D40" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E40" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F40" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G40" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H40" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I40" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J40" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K40" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L40" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="65" t="inlineStr">
+        <is>
           <t>例文（辞書タブ）</t>
         </is>
       </c>
-      <c r="B39" s="66" t="n">
+      <c r="B41" s="66" t="n">
         <v>3524</v>
       </c>
-      <c r="C39" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D39" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E39" s="138" t="inlineStr">
+      <c r="C41" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D41" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E41" s="138" t="inlineStr">
         <is>
           <t>100%（3524）</t>
         </is>
       </c>
-      <c r="F39" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G39" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K39" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L39" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="173" t="inlineStr">
+      <c r="F41" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G41" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H41" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I41" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J41" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K41" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L41" s="138" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="173" t="inlineStr">
         <is>
           <t>辞書訳 出力字数(参考)</t>
         </is>
       </c>
-      <c r="B40" s="174" t="n"/>
-      <c r="C40" s="174" t="n"/>
-      <c r="E40" s="174" t="n"/>
-      <c r="F40" s="175" t="n">
-        <v>344226</v>
-      </c>
-      <c r="G40" s="175" t="n">
-        <v>388928</v>
-      </c>
-      <c r="H40" s="175" t="n">
-        <v>151711</v>
-      </c>
-      <c r="I40" s="175" t="n">
-        <v>375205</v>
-      </c>
-      <c r="J40" s="175" t="n">
+      <c r="B42" s="103" t="n"/>
+      <c r="C42" s="103" t="n"/>
+      <c r="D42" s="103" t="n"/>
+      <c r="E42" s="103" t="n"/>
+      <c r="F42" s="103" t="n"/>
+      <c r="G42" s="103" t="n"/>
+      <c r="H42" s="103" t="n"/>
+      <c r="I42" s="104" t="n"/>
+      <c r="J42" s="175" t="n">
         <v>303788</v>
       </c>
-      <c r="K40" s="175" t="n">
+      <c r="K42" s="175" t="n">
         <v>351959</v>
       </c>
-      <c r="L40" s="175" t="n">
+      <c r="L42" s="175" t="n">
         <v>102244</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="173" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="173" t="inlineStr">
         <is>
           <t>辞書訳 概算実費(参考・Gemini2.5Flash・6言語計≈¥327/通算≈¥405)</t>
         </is>
       </c>
-      <c r="B41" s="174" t="n"/>
-      <c r="C41" s="174" t="n"/>
-      <c r="D41" s="176" t="inlineStr">
+      <c r="B43" s="174" t="n"/>
+      <c r="C43" s="174" t="n"/>
+      <c r="D43" s="176" t="inlineStr">
         <is>
           <t>¥0(元)</t>
         </is>
       </c>
-      <c r="E41" s="174" t="n"/>
-      <c r="F41" s="176" t="inlineStr">
+      <c r="E43" s="174" t="n"/>
+      <c r="F43" s="176" t="inlineStr">
         <is>
           <t>≈¥69</t>
         </is>
       </c>
-      <c r="G41" s="176" t="inlineStr">
+      <c r="G43" s="176" t="inlineStr">
         <is>
           <t>¥78</t>
         </is>
       </c>
-      <c r="H41" s="176" t="inlineStr">
+      <c r="H43" s="176" t="inlineStr">
         <is>
           <t>≈¥30</t>
         </is>
       </c>
-      <c r="I41" s="176" t="inlineStr">
+      <c r="I43" s="176" t="inlineStr">
         <is>
           <t>≈¥75</t>
         </is>
       </c>
-      <c r="J41" s="176" t="inlineStr">
+      <c r="J43" s="176" t="inlineStr">
         <is>
           <t>≈¥61</t>
         </is>
       </c>
-      <c r="K41" s="176" t="inlineStr">
+      <c r="K43" s="176" t="inlineStr">
         <is>
           <t>≈¥71</t>
         </is>
       </c>
-      <c r="L41" s="176" t="inlineStr">
+      <c r="L43" s="176" t="inlineStr">
         <is>
           <t>≈¥21</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="76" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="76" t="inlineStr">
         <is>
           <t>※ 英語＝同梱データに最初から入っている意味。ネパール語＝配信(OTA)の上書き層 content/lexicon で全件対応済（meaning=4561件＝語彙+漢字+文法の全意味）。 ／ インドネシア語(id)＝辞書全4種(意味4560+漢字グロス1859+例文3524+文法例文408)を2026-09-05に翻訳(Gemini・content/lexicon に id 追記・app改修不要)。</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="105" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="105" t="inlineStr">
         <is>
           <t>④ 各大問（問題）の翻訳　※問題文は日本語。ここは『読解本文』などの対訳と、解説の翻訳の話</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="106" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="106" t="inlineStr">
         <is>
           <t>大問</t>
         </is>
       </c>
-      <c r="B45" s="106" t="inlineStr">
+      <c r="B47" s="106" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="C45" s="106" t="inlineStr">
+      <c r="C47" s="106" t="inlineStr">
         <is>
           <t>模試</t>
         </is>
       </c>
-      <c r="D45" s="106" t="inlineStr">
+      <c r="D47" s="106" t="inlineStr">
         <is>
           <t>翻訳の種類</t>
         </is>
       </c>
-      <c r="E45" s="106" t="inlineStr">
+      <c r="E47" s="106" t="inlineStr">
         <is>
           <t>英語(en)</t>
         </is>
       </c>
-      <c r="F45" s="106" t="inlineStr">
+      <c r="F47" s="106" t="inlineStr">
         <is>
           <t>ネパール語(ne)</t>
         </is>
       </c>
-      <c r="G45" s="107" t="inlineStr">
+      <c r="G47" s="107" t="inlineStr">
         <is>
           <t>ベンガル語</t>
         </is>
       </c>
-      <c r="H45" s="107" t="inlineStr">
+      <c r="H47" s="107" t="inlineStr">
         <is>
           <t>インドネシア語</t>
         </is>
       </c>
-      <c r="I45" s="107" t="inlineStr">
+      <c r="I47" s="107" t="inlineStr">
         <is>
           <t>韓国語</t>
         </is>
       </c>
-      <c r="J45" s="107" t="inlineStr">
+      <c r="J47" s="107" t="inlineStr">
         <is>
           <t>ミャンマー語</t>
         </is>
       </c>
-      <c r="K45" s="107" t="inlineStr">
+      <c r="K47" s="107" t="inlineStr">
         <is>
           <t>タイ語</t>
         </is>
       </c>
-      <c r="L45" s="107" t="inlineStr">
+      <c r="L47" s="107" t="inlineStr">
         <is>
           <t>ベトナム語</t>
         </is>
       </c>
-      <c r="M45" s="107" t="inlineStr">
+      <c r="M47" s="107" t="inlineStr">
         <is>
           <t>中国語</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="94" t="inlineStr">
-        <is>
-          <t>文字語彙・文脈規定</t>
-        </is>
-      </c>
-      <c r="B46" s="95" t="n">
-        <v>3464</v>
-      </c>
-      <c r="C46" s="95" t="n">
-        <v>310</v>
-      </c>
-      <c r="D46" s="94" t="inlineStr">
-        <is>
-          <t>本文の対訳</t>
-        </is>
-      </c>
-      <c r="E46" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F46" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G46" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H46" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I46" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J46" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K46" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L46" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M46" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="94" t="inlineStr">
-        <is>
-          <t>文字語彙・漢字読み</t>
-        </is>
-      </c>
-      <c r="B47" s="95" t="n">
-        <v>3204</v>
-      </c>
-      <c r="C47" s="95" t="n">
-        <v>274</v>
-      </c>
-      <c r="D47" s="94" t="inlineStr">
-        <is>
-          <t>訳なし（下線語の解読課題・意味は問わず不要）</t>
-        </is>
-      </c>
-      <c r="E47" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F47" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I47" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J47" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K47" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L47" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M47" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="94" t="inlineStr">
         <is>
-          <t>文字語彙・表記</t>
+          <t>文字語彙・文脈規定</t>
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>3350</v>
+        <v>3464</v>
       </c>
       <c r="C48" s="95" t="n">
-        <v>200</v>
+        <v>310</v>
       </c>
       <c r="D48" s="94" t="inlineStr">
         <is>
-          <t>訳なし（下線語の解読課題・意味は問わず不要）</t>
-        </is>
-      </c>
-      <c r="E48" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F48" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J48" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K48" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L48" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M48" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>本文の対訳</t>
+        </is>
+      </c>
+      <c r="E48" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F48" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G48" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H48" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I48" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J48" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K48" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L48" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M48" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="94" t="inlineStr">
         <is>
-          <t>文字語彙・言い換え</t>
+          <t>文字語彙・漢字読み</t>
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>2255</v>
+        <v>3204</v>
       </c>
       <c r="C49" s="95" t="n">
-        <v>150</v>
+        <v>274</v>
       </c>
       <c r="D49" s="94" t="inlineStr">
         <is>
-          <t>本文＋選択肢の対訳（回答後表示・誤答も正当な語ゆえ訳す・2026-09）</t>
-        </is>
-      </c>
-      <c r="E49" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F49" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G49" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H49" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I49" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J49" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K49" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L49" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M49" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>訳なし（下線語の解読課題・意味は問わず不要）</t>
+        </is>
+      </c>
+      <c r="E49" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J49" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K49" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L49" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M49" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="94" t="inlineStr">
         <is>
-          <t>文字語彙・用法</t>
+          <t>文字語彙・表記</t>
         </is>
       </c>
       <c r="B50" s="95" t="n">
-        <v>1171</v>
+        <v>3350</v>
       </c>
       <c r="C50" s="95" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D50" s="94" t="inlineStr">
         <is>
-          <t>正解の文の対訳（回答後表示・誤答は不自然文ゆえ訳さず・2026-09）</t>
-        </is>
-      </c>
-      <c r="E50" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F50" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G50" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H50" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I50" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J50" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K50" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L50" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M50" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>訳なし（下線語の解読課題・意味は問わず不要）</t>
+        </is>
+      </c>
+      <c r="E50" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J50" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K50" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L50" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M50" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="94" t="inlineStr">
         <is>
-          <t>文法・穴埋め</t>
+          <t>文字語彙・言い換え</t>
         </is>
       </c>
       <c r="B51" s="95" t="n">
-        <v>1207</v>
+        <v>2255</v>
       </c>
       <c r="C51" s="95" t="n">
-        <v>440</v>
+        <v>150</v>
       </c>
       <c r="D51" s="94" t="inlineStr">
         <is>
-          <t>完成文の対訳（回答後表示・選択肢=文法パーツは訳さず・2026-09）</t>
+          <t>本文＋選択肢の対訳（回答後表示・誤答も正当な語ゆえ訳す・2026-09）</t>
         </is>
       </c>
       <c r="E51" s="141" t="inlineStr">
@@ -11403,18 +11345,18 @@
     <row r="52">
       <c r="A52" s="94" t="inlineStr">
         <is>
-          <t>文法・並べ替え</t>
+          <t>文字語彙・用法</t>
         </is>
       </c>
       <c r="B52" s="95" t="n">
-        <v>673</v>
+        <v>1171</v>
       </c>
       <c r="C52" s="95" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D52" s="94" t="inlineStr">
         <is>
-          <t>正しい文＋母語訳（回答後表示・2026-09再翻訳）</t>
+          <t>正解の文の対訳（回答後表示・誤答は不自然文ゆえ訳さず・2026-09）</t>
         </is>
       </c>
       <c r="E52" s="141" t="inlineStr">
@@ -11466,18 +11408,18 @@
     <row r="53">
       <c r="A53" s="94" t="inlineStr">
         <is>
-          <t>文法・文章の文法</t>
+          <t>文法・穴埋め</t>
         </is>
       </c>
       <c r="B53" s="95" t="n">
-        <v>210</v>
+        <v>1207</v>
       </c>
       <c r="C53" s="95" t="n">
-        <v>30</v>
+        <v>440</v>
       </c>
       <c r="D53" s="94" t="inlineStr">
         <is>
-          <t>本文の対訳</t>
+          <t>完成文の対訳（回答後表示・選択肢=文法パーツは訳さず・2026-09）</t>
         </is>
       </c>
       <c r="E53" s="141" t="inlineStr">
@@ -11529,18 +11471,18 @@
     <row r="54">
       <c r="A54" s="94" t="inlineStr">
         <is>
-          <t>読解・内容理解(短)</t>
+          <t>文法・並べ替え</t>
         </is>
       </c>
       <c r="B54" s="95" t="n">
-        <v>330</v>
+        <v>673</v>
       </c>
       <c r="C54" s="95" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="D54" s="94" t="inlineStr">
         <is>
-          <t>本文の対訳（設問解説は廃止・本文訳は維持）</t>
+          <t>正しい文＋母語訳（回答後表示・2026-09再翻訳）</t>
         </is>
       </c>
       <c r="E54" s="141" t="inlineStr">
@@ -11592,14 +11534,14 @@
     <row r="55">
       <c r="A55" s="94" t="inlineStr">
         <is>
-          <t>読解・内容理解(中)</t>
+          <t>文法・文章の文法</t>
         </is>
       </c>
       <c r="B55" s="95" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="C55" s="95" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D55" s="94" t="inlineStr">
         <is>
@@ -11655,18 +11597,18 @@
     <row r="56">
       <c r="A56" s="94" t="inlineStr">
         <is>
-          <t>読解・長文</t>
+          <t>読解・内容理解(短)</t>
         </is>
       </c>
       <c r="B56" s="95" t="n">
-        <v>40</v>
+        <v>330</v>
       </c>
       <c r="C56" s="95" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="D56" s="94" t="inlineStr">
         <is>
-          <t>本文の対訳</t>
+          <t>本文の対訳（設問解説は廃止・本文訳は維持）</t>
         </is>
       </c>
       <c r="E56" s="141" t="inlineStr">
@@ -11718,81 +11660,81 @@
     <row r="57">
       <c r="A57" s="94" t="inlineStr">
         <is>
-          <t>読解・情報検索</t>
+          <t>読解・内容理解(中)</t>
         </is>
       </c>
       <c r="B57" s="95" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="C57" s="95" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D57" s="94" t="inlineStr">
         <is>
-          <t>訳なし（機械式・不要）</t>
-        </is>
-      </c>
-      <c r="E57" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="143" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I57" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J57" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K57" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L57" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M57" s="144" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>本文の対訳</t>
+        </is>
+      </c>
+      <c r="E57" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F57" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G57" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K57" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L57" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M57" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="94" t="inlineStr">
         <is>
-          <t>聴解・課題理解</t>
+          <t>読解・長文</t>
         </is>
       </c>
       <c r="B58" s="95" t="n">
-        <v>450</v>
+        <v>40</v>
       </c>
       <c r="C58" s="95" t="n">
-        <v>210</v>
+        <v>10</v>
       </c>
       <c r="D58" s="94" t="inlineStr">
         <is>
-          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-02）</t>
+          <t>本文の対訳</t>
         </is>
       </c>
       <c r="E58" s="141" t="inlineStr">
@@ -11844,81 +11786,81 @@
     <row r="59">
       <c r="A59" s="94" t="inlineStr">
         <is>
-          <t>聴解・ポイント理解</t>
+          <t>読解・情報検索</t>
         </is>
       </c>
       <c r="B59" s="95" t="n">
-        <v>450</v>
+        <v>180</v>
       </c>
       <c r="C59" s="95" t="n">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="D59" s="94" t="inlineStr">
         <is>
-          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-03）</t>
-        </is>
-      </c>
-      <c r="E59" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F59" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G59" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H59" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I59" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J59" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K59" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L59" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M59" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>訳なし（機械式・不要）</t>
+        </is>
+      </c>
+      <c r="E59" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I59" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J59" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K59" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L59" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M59" s="144" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="94" t="inlineStr">
         <is>
-          <t>聴解・概要理解</t>
+          <t>聴解・課題理解</t>
         </is>
       </c>
       <c r="B60" s="95" t="n">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="C60" s="95" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="D60" s="94" t="inlineStr">
         <is>
-          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-03・N3のみ）</t>
+          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-02）</t>
         </is>
       </c>
       <c r="E60" s="141" t="inlineStr">
@@ -11970,18 +11912,18 @@
     <row r="61">
       <c r="A61" s="94" t="inlineStr">
         <is>
-          <t>聴解・発話表現</t>
+          <t>聴解・ポイント理解</t>
         </is>
       </c>
       <c r="B61" s="95" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="C61" s="95" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="D61" s="94" t="inlineStr">
         <is>
-          <t>場面文(台本)＋選択肢の対訳（回答後表示・2026-09-03・設問文なし＝場面に合う一言を選ぶ）</t>
+          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-03）</t>
         </is>
       </c>
       <c r="E61" s="141" t="inlineStr">
@@ -12033,140 +11975,196 @@
     <row r="62">
       <c r="A62" s="94" t="inlineStr">
         <is>
+          <t>聴解・概要理解</t>
+        </is>
+      </c>
+      <c r="B62" s="95" t="n">
+        <v>80</v>
+      </c>
+      <c r="C62" s="95" t="n">
+        <v>30</v>
+      </c>
+      <c r="D62" s="94" t="inlineStr">
+        <is>
+          <t>台本＋設問＋選択肢の対訳（回答後表示・2026-09-03・N3のみ）</t>
+        </is>
+      </c>
+      <c r="E62" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F62" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G62" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H62" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I62" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J62" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K62" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L62" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M62" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="94" t="inlineStr">
+        <is>
+          <t>聴解・発話表現</t>
+        </is>
+      </c>
+      <c r="B63" s="95" t="n">
+        <v>600</v>
+      </c>
+      <c r="C63" s="95" t="n">
+        <v>140</v>
+      </c>
+      <c r="D63" s="94" t="inlineStr">
+        <is>
+          <t>場面文(台本)＋選択肢の対訳（回答後表示・2026-09-03・設問文なし＝場面に合う一言を選ぶ）</t>
+        </is>
+      </c>
+      <c r="E63" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F63" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G63" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H63" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I63" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J63" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K63" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L63" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M63" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="94" t="inlineStr">
+        <is>
           <t>聴解・即時応答</t>
         </is>
       </c>
-      <c r="B62" s="95" t="n">
+      <c r="B64" s="95" t="n">
         <v>720</v>
       </c>
-      <c r="C62" s="95" t="n">
+      <c r="C64" s="95" t="n">
         <v>230</v>
       </c>
-      <c r="D62" s="94" t="inlineStr">
+      <c r="D64" s="94" t="inlineStr">
         <is>
           <t>場面文(台本)＋選択肢の対訳（回答後表示・2026-09-03・設問文なし＝相手の一言への返しを選ぶ）</t>
         </is>
       </c>
-      <c r="E62" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F62" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G62" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H62" s="141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I62" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J62" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K62" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L62" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M62" s="178" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="177" t="inlineStr">
+      <c r="E64" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F64" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G64" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H64" s="141" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I64" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J64" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K64" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L64" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M64" s="178" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="177" t="inlineStr">
         <is>
           <t>◇大問訳 出力字数(参考)</t>
-        </is>
-      </c>
-      <c r="G63" s="175" t="n">
-        <v>2785247</v>
-      </c>
-      <c r="H63" s="175" t="n">
-        <v>3401751</v>
-      </c>
-      <c r="I63" s="175" t="n">
-        <v>1447703</v>
-      </c>
-      <c r="J63" s="175" t="n">
-        <v>3294974</v>
-      </c>
-      <c r="K63" s="175" t="n">
-        <v>2646058</v>
-      </c>
-      <c r="L63" s="175" t="n">
-        <v>3046533</v>
-      </c>
-      <c r="M63" s="175" t="n">
-        <v>905106</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="177" t="inlineStr">
-        <is>
-          <t>◇大問訳 概算実費(参考・Gemini2.5Flash)</t>
-        </is>
-      </c>
-      <c r="G64" s="176" t="inlineStr">
-        <is>
-          <t>¥481</t>
-        </is>
-      </c>
-      <c r="H64" s="176" t="inlineStr">
-        <is>
-          <t>¥494</t>
-        </is>
-      </c>
-      <c r="I64" s="176" t="inlineStr">
-        <is>
-          <t>¥504</t>
-        </is>
-      </c>
-      <c r="J64" s="176" t="inlineStr">
-        <is>
-          <t>¥719</t>
-        </is>
-      </c>
-      <c r="K64" s="176" t="inlineStr">
-        <is>
-          <t>¥544</t>
-        </is>
-      </c>
-      <c r="L64" s="176" t="inlineStr">
-        <is>
-          <t>¥532</t>
-        </is>
-      </c>
-      <c r="M64" s="176" t="inlineStr">
-        <is>
-          <t>¥432</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="102" t="inlineStr">
-        <is>
-          <t>※ 通常＝学習プール、模試＝模試専用プール(初見)。旧「└ 漢字読み(模試プール)」サブ行は廃止し、全大問に模試列を新設。</t>
         </is>
       </c>
       <c r="B65" s="103" t="n"/>
@@ -12177,584 +12175,522 @@
       <c r="G65" s="103" t="n"/>
       <c r="H65" s="103" t="n"/>
       <c r="I65" s="104" t="n"/>
+      <c r="J65" s="175" t="n">
+        <v>3294974</v>
+      </c>
+      <c r="K65" s="175" t="n">
+        <v>2646058</v>
+      </c>
+      <c r="L65" s="175" t="n">
+        <v>3046533</v>
+      </c>
+      <c r="M65" s="175" t="n">
+        <v>905106</v>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="90" t="inlineStr">
+      <c r="A66" s="177" t="inlineStr">
+        <is>
+          <t>◇大問訳 概算実費(参考・Gemini2.5Flash)</t>
+        </is>
+      </c>
+      <c r="B66" s="103" t="n"/>
+      <c r="C66" s="103" t="n"/>
+      <c r="D66" s="103" t="n"/>
+      <c r="E66" s="103" t="n"/>
+      <c r="F66" s="103" t="n"/>
+      <c r="G66" s="103" t="n"/>
+      <c r="H66" s="103" t="n"/>
+      <c r="I66" s="104" t="n"/>
+      <c r="J66" s="176" t="inlineStr">
+        <is>
+          <t>¥719</t>
+        </is>
+      </c>
+      <c r="K66" s="176" t="inlineStr">
+        <is>
+          <t>¥544</t>
+        </is>
+      </c>
+      <c r="L66" s="176" t="inlineStr">
+        <is>
+          <t>¥532</t>
+        </is>
+      </c>
+      <c r="M66" s="176" t="inlineStr">
+        <is>
+          <t>¥432</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="102" t="inlineStr">
+        <is>
+          <t>※ 通常＝学習プール、模試＝模試専用プール(初見)。旧「└ 漢字読み(模試プール)」サブ行は廃止し、全大問に模試列を新設。</t>
+        </is>
+      </c>
+      <c r="B67" s="103" t="n"/>
+      <c r="C67" s="103" t="n"/>
+      <c r="D67" s="103" t="n"/>
+      <c r="E67" s="103" t="n"/>
+      <c r="F67" s="103" t="n"/>
+      <c r="G67" s="103" t="n"/>
+      <c r="H67" s="103" t="n"/>
+      <c r="I67" s="104" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="90" t="inlineStr">
         <is>
           <t>※ 文脈規定は「解説の翻訳(旧ne38%)」を廃止し、本文の対訳(空所を答えで埋めた完成文の en/ne)へ移行済。表示＝回答後に本文の下。2026-09-02 完了(3774問)。</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="90" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="90" t="inlineStr">
         <is>
           <t>※ 聴解は音声台本(スクリプト)＋設問＋選択肢の対訳の有無を記載。全5大問=en/ne 100%完了・回答後表示（課題理解2026-09-02／ポイント理解・概要理解・発話表現・即時応答2026-09-03）。</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>※ 表記・漢字読みは『下線語を読む／漢字で書く』の解読問題で本文の意味は問わない（意味は辞書・意味ドリルで担保）。解説・母語訳は不要と判断し、表記の解説(en/ne 旧ne77%)を全削除。2026-09-02。</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="105" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="105" t="inlineStr">
         <is>
           <t>⑤ 各ドリル（単語タブの全ドリル｜漢字5・語彙5・文法2＝計12種）</t>
         </is>
       </c>
-      <c r="B69" s="82" t="n"/>
-      <c r="C69" s="82" t="n"/>
-      <c r="D69" s="82" t="n"/>
-      <c r="E69" s="82" t="n"/>
-      <c r="F69" s="82" t="n"/>
-      <c r="G69" s="82" t="n"/>
-      <c r="H69" s="82" t="n"/>
-      <c r="I69" s="82" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="111" t="inlineStr">
+      <c r="B71" s="82" t="n"/>
+      <c r="C71" s="82" t="n"/>
+      <c r="D71" s="82" t="n"/>
+      <c r="E71" s="82" t="n"/>
+      <c r="F71" s="82" t="n"/>
+      <c r="G71" s="82" t="n"/>
+      <c r="H71" s="82" t="n"/>
+      <c r="I71" s="82" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="111" t="inlineStr">
         <is>
           <t>ドリル</t>
         </is>
       </c>
-      <c r="B70" s="111" t="inlineStr">
+      <c r="B72" s="111" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C70" s="111" t="inlineStr">
+      <c r="C72" s="111" t="inlineStr">
         <is>
           <t>翻訳の出どころ</t>
         </is>
       </c>
-      <c r="D70" s="111" t="inlineStr">
+      <c r="D72" s="111" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="E70" s="111" t="inlineStr">
+      <c r="E72" s="111" t="inlineStr">
         <is>
           <t>ne</t>
         </is>
       </c>
-      <c r="F70" s="111" t="inlineStr">
+      <c r="F72" s="111" t="inlineStr">
         <is>
           <t>ベンガル語</t>
         </is>
       </c>
-      <c r="G70" s="111" t="inlineStr">
+      <c r="G72" s="111" t="inlineStr">
         <is>
           <t>インドネシア語</t>
         </is>
       </c>
-      <c r="H70" s="111" t="inlineStr">
+      <c r="H72" s="111" t="inlineStr">
         <is>
           <t>韓国語</t>
         </is>
       </c>
-      <c r="I70" s="111" t="inlineStr">
+      <c r="I72" s="111" t="inlineStr">
         <is>
           <t>ミャンマー語</t>
         </is>
       </c>
-      <c r="J70" s="111" t="inlineStr">
+      <c r="J72" s="111" t="inlineStr">
         <is>
           <t>タイ語</t>
         </is>
       </c>
-      <c r="K70" s="111" t="inlineStr">
+      <c r="K72" s="111" t="inlineStr">
         <is>
           <t>ベトナム語</t>
         </is>
       </c>
-      <c r="L70" s="111" t="inlineStr">
+      <c r="L72" s="111" t="inlineStr">
         <is>
           <t>中国語</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="112" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="112" t="inlineStr">
         <is>
           <t>■ 漢字（5種）</t>
         </is>
       </c>
-      <c r="B71" s="85" t="n"/>
-      <c r="C71" s="85" t="n"/>
-      <c r="D71" s="85" t="n"/>
-      <c r="E71" s="85" t="n"/>
-      <c r="F71" s="85" t="n"/>
-      <c r="G71" s="85" t="n"/>
-      <c r="H71" s="85" t="n"/>
-      <c r="I71" s="85" t="n"/>
-      <c r="J71" s="85" t="n"/>
-      <c r="K71" s="85" t="n"/>
-      <c r="L71" s="85" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="86" t="inlineStr">
-        <is>
-          <t>書き取り</t>
-        </is>
-      </c>
-      <c r="B72" s="85" t="inlineStr">
-        <is>
-          <t>字をなぞって手書き</t>
-        </is>
-      </c>
-      <c r="C72" s="85" t="inlineStr">
-        <is>
-          <t>日本語のみ（かな・字／翻訳不要）</t>
-        </is>
-      </c>
-      <c r="D72" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J72" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="146" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="86" t="inlineStr">
-        <is>
-          <t>意味</t>
-        </is>
-      </c>
-      <c r="B73" s="85" t="inlineStr">
-        <is>
-          <t>字→意味を4択</t>
-        </is>
-      </c>
-      <c r="C73" s="85" t="inlineStr">
-        <is>
-          <t>辞書の意味を流用</t>
-        </is>
-      </c>
-      <c r="D73" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E73" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F73" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G73" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H73" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I73" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J73" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K73" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L73" s="147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
+      <c r="B73" s="85" t="n"/>
+      <c r="C73" s="85" t="n"/>
+      <c r="D73" s="85" t="n"/>
+      <c r="E73" s="85" t="n"/>
+      <c r="F73" s="85" t="n"/>
+      <c r="G73" s="85" t="n"/>
+      <c r="H73" s="85" t="n"/>
+      <c r="I73" s="85" t="n"/>
+      <c r="J73" s="85" t="n"/>
+      <c r="K73" s="85" t="n"/>
+      <c r="L73" s="85" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="86" t="inlineStr">
         <is>
+          <t>書き取り</t>
+        </is>
+      </c>
+      <c r="B74" s="85" t="inlineStr">
+        <is>
+          <t>字をなぞって手書き</t>
+        </is>
+      </c>
+      <c r="C74" s="85" t="inlineStr">
+        <is>
+          <t>日本語のみ（かな・字／翻訳不要）</t>
+        </is>
+      </c>
+      <c r="D74" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J74" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="86" t="inlineStr">
+        <is>
+          <t>意味</t>
+        </is>
+      </c>
+      <c r="B75" s="85" t="inlineStr">
+        <is>
+          <t>字→意味を4択</t>
+        </is>
+      </c>
+      <c r="C75" s="85" t="inlineStr">
+        <is>
+          <t>辞書の意味を流用</t>
+        </is>
+      </c>
+      <c r="D75" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E75" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F75" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G75" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H75" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I75" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J75" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K75" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L75" s="147" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="86" t="inlineStr">
+        <is>
           <t>読み</t>
         </is>
       </c>
-      <c r="B74" s="85" t="inlineStr">
+      <c r="B76" s="85" t="inlineStr">
         <is>
           <t>字→読みを4択</t>
         </is>
       </c>
-      <c r="C74" s="85" t="inlineStr">
+      <c r="C76" s="85" t="inlineStr">
         <is>
           <t>日本語のみ（かな／翻訳不要）</t>
         </is>
       </c>
-      <c r="D74" s="146" t="inlineStr">
+      <c r="D76" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E74" s="146" t="inlineStr">
+      <c r="E76" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F74" s="146" t="inlineStr">
+      <c r="F76" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G74" s="146" t="inlineStr">
+      <c r="G76" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H74" s="146" t="inlineStr">
+      <c r="H76" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I74" s="146" t="inlineStr">
+      <c r="I76" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J74" s="146" t="inlineStr">
+      <c r="J76" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K74" s="146" t="inlineStr">
+      <c r="K76" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L74" s="146" t="inlineStr">
+      <c r="L76" s="146" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="82" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="82" t="inlineStr">
         <is>
           <t>似た字の見分け</t>
         </is>
       </c>
-      <c r="B75" s="82" t="inlineStr">
+      <c r="B77" s="82" t="inlineStr">
         <is>
           <t>似た字4択→正しい字</t>
         </is>
       </c>
-      <c r="C75" s="82" t="inlineStr">
+      <c r="C77" s="82" t="inlineStr">
         <is>
           <t>日本語のみ（字／翻訳不要）</t>
         </is>
       </c>
-      <c r="D75" s="149" t="inlineStr">
+      <c r="D77" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E75" s="149" t="inlineStr">
+      <c r="E77" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F75" s="149" t="inlineStr">
+      <c r="F77" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G75" s="149" t="inlineStr">
+      <c r="G77" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H75" s="149" t="inlineStr">
+      <c r="H77" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I75" s="149" t="inlineStr">
+      <c r="I77" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J75" s="149" t="inlineStr">
+      <c r="J77" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K75" s="149" t="inlineStr">
+      <c r="K77" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L75" s="149" t="inlineStr">
+      <c r="L77" s="149" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="82" t="inlineStr">
-        <is>
-          <t>聞き取り</t>
-        </is>
-      </c>
-      <c r="B76" s="82" t="inlineStr">
-        <is>
-          <t>🔊読み→字を4択</t>
-        </is>
-      </c>
-      <c r="C76" s="82" t="inlineStr">
-        <is>
-          <t>日本語のみ（音声・字／翻訳不要）</t>
-        </is>
-      </c>
-      <c r="D76" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J76" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="116" t="inlineStr">
-        <is>
-          <t>■ 語彙（5種）</t>
-        </is>
-      </c>
-      <c r="B77" s="82" t="n"/>
-      <c r="C77" s="82" t="n"/>
-      <c r="D77" s="82" t="n"/>
-      <c r="E77" s="82" t="n"/>
-      <c r="F77" s="82" t="n"/>
-      <c r="G77" s="82" t="n"/>
-      <c r="H77" s="82" t="n"/>
-      <c r="I77" s="82" t="n"/>
-      <c r="J77" s="82" t="n"/>
-      <c r="K77" s="82" t="n"/>
-      <c r="L77" s="82" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="82" t="inlineStr">
         <is>
-          <t>意味</t>
+          <t>聞き取り</t>
         </is>
       </c>
       <c r="B78" s="82" t="inlineStr">
         <is>
-          <t>語→意味を4択</t>
+          <t>🔊読み→字を4択</t>
         </is>
       </c>
       <c r="C78" s="82" t="inlineStr">
         <is>
-          <t>辞書の意味を流用</t>
-        </is>
-      </c>
-      <c r="D78" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E78" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F78" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G78" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H78" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I78" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J78" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K78" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L78" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>日本語のみ（音声・字／翻訳不要）</t>
+        </is>
+      </c>
+      <c r="D78" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J78" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="82" t="inlineStr">
-        <is>
-          <t>読み</t>
-        </is>
-      </c>
-      <c r="B79" s="82" t="inlineStr">
-        <is>
-          <t>語→読みを4択</t>
-        </is>
-      </c>
-      <c r="C79" s="82" t="inlineStr">
-        <is>
-          <t>日本語のみ（かな／翻訳不要）</t>
-        </is>
-      </c>
-      <c r="D79" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J79" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="149" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A79" s="116" t="inlineStr">
+        <is>
+          <t>■ 語彙（5種）</t>
+        </is>
+      </c>
+      <c r="B79" s="82" t="n"/>
+      <c r="C79" s="82" t="n"/>
+      <c r="D79" s="82" t="n"/>
+      <c r="E79" s="82" t="n"/>
+      <c r="F79" s="82" t="n"/>
+      <c r="G79" s="82" t="n"/>
+      <c r="H79" s="82" t="n"/>
+      <c r="I79" s="82" t="n"/>
+      <c r="J79" s="82" t="n"/>
+      <c r="K79" s="82" t="n"/>
+      <c r="L79" s="82" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="82" t="inlineStr">
         <is>
-          <t>表記</t>
+          <t>意味</t>
         </is>
       </c>
       <c r="B80" s="82" t="inlineStr">
         <is>
-          <t>意味→漢字表記を4択</t>
+          <t>語→意味を4択</t>
         </is>
       </c>
       <c r="C80" s="82" t="inlineStr">
@@ -12811,79 +12747,79 @@
     <row r="81">
       <c r="A81" s="82" t="inlineStr">
         <is>
-          <t>聞き取り</t>
+          <t>読み</t>
         </is>
       </c>
       <c r="B81" s="82" t="inlineStr">
         <is>
-          <t>🔊読み→意味を4択</t>
+          <t>語→読みを4択</t>
         </is>
       </c>
       <c r="C81" s="82" t="inlineStr">
         <is>
-          <t>辞書の意味を流用</t>
-        </is>
-      </c>
-      <c r="D81" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E81" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F81" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G81" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H81" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I81" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J81" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K81" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L81" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>日本語のみ（かな／翻訳不要）</t>
+        </is>
+      </c>
+      <c r="D81" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J81" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="149" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="82" t="inlineStr">
         <is>
-          <t>語彙パズル</t>
+          <t>表記</t>
         </is>
       </c>
       <c r="B82" s="82" t="inlineStr">
         <is>
-          <t>意味→かなタイルで語を作る</t>
+          <t>意味→漢字表記を4択</t>
         </is>
       </c>
       <c r="C82" s="82" t="inlineStr">
         <is>
-          <t>辞書の意味を流用（意味を提示）</t>
+          <t>辞書の意味を流用</t>
         </is>
       </c>
       <c r="D82" s="150" t="inlineStr">
@@ -12933,219 +12869,343 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="116" t="inlineStr">
-        <is>
-          <t>■ 文法（2種）</t>
-        </is>
-      </c>
-      <c r="B83" s="82" t="n"/>
-      <c r="C83" s="82" t="n"/>
-      <c r="D83" s="82" t="n"/>
-      <c r="E83" s="82" t="n"/>
-      <c r="F83" s="82" t="n"/>
-      <c r="G83" s="82" t="n"/>
-      <c r="H83" s="82" t="n"/>
-      <c r="I83" s="82" t="n"/>
-      <c r="J83" s="82" t="n"/>
-      <c r="K83" s="82" t="n"/>
-      <c r="L83" s="82" t="n"/>
+      <c r="A83" s="82" t="inlineStr">
+        <is>
+          <t>聞き取り</t>
+        </is>
+      </c>
+      <c r="B83" s="82" t="inlineStr">
+        <is>
+          <t>🔊読み→意味を4択</t>
+        </is>
+      </c>
+      <c r="C83" s="82" t="inlineStr">
+        <is>
+          <t>辞書の意味を流用</t>
+        </is>
+      </c>
+      <c r="D83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L83" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="82" t="inlineStr">
         <is>
+          <t>語彙パズル</t>
+        </is>
+      </c>
+      <c r="B84" s="82" t="inlineStr">
+        <is>
+          <t>意味→かなタイルで語を作る</t>
+        </is>
+      </c>
+      <c r="C84" s="82" t="inlineStr">
+        <is>
+          <t>辞書の意味を流用（意味を提示）</t>
+        </is>
+      </c>
+      <c r="D84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L84" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="116" t="inlineStr">
+        <is>
+          <t>■ 文法（2種）</t>
+        </is>
+      </c>
+      <c r="B85" s="82" t="n"/>
+      <c r="C85" s="82" t="n"/>
+      <c r="D85" s="82" t="n"/>
+      <c r="E85" s="82" t="n"/>
+      <c r="F85" s="82" t="n"/>
+      <c r="G85" s="82" t="n"/>
+      <c r="H85" s="82" t="n"/>
+      <c r="I85" s="82" t="n"/>
+      <c r="J85" s="82" t="n"/>
+      <c r="K85" s="82" t="n"/>
+      <c r="L85" s="82" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="82" t="inlineStr">
+        <is>
           <t>意味</t>
         </is>
       </c>
-      <c r="B84" s="82" t="inlineStr">
+      <c r="B86" s="82" t="inlineStr">
         <is>
           <t>文法点→意味を4択</t>
         </is>
       </c>
-      <c r="C84" s="82" t="inlineStr">
+      <c r="C86" s="82" t="inlineStr">
         <is>
           <t>辞書の意味を流用</t>
         </is>
       </c>
-      <c r="D84" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E84" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F84" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G84" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H84" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I84" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J84" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K84" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L84" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="82" t="inlineStr">
+      <c r="D86" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E86" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F86" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G86" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H86" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I86" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J86" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K86" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L86" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="82" t="inlineStr">
         <is>
           <t>パズル</t>
         </is>
       </c>
-      <c r="B85" s="82" t="inlineStr">
+      <c r="B87" s="82" t="inlineStr">
         <is>
           <t>例文の穴に文法語をタイルで作る</t>
         </is>
       </c>
-      <c r="C85" s="82" t="inlineStr">
+      <c r="C87" s="82" t="inlineStr">
         <is>
           <t>辞書の意味を流用（ヒントに意味）</t>
         </is>
       </c>
-      <c r="D85" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E85" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F85" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G85" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H85" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I85" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J85" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K85" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L85" s="150" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="90" t="inlineStr">
+      <c r="D87" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E87" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F87" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G87" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H87" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I87" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J87" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K87" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L87" s="150" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="90" t="inlineStr">
         <is>
           <t>※ ドリルは辞書データから自動生成。意味を見せる面（意味／表記／聞き取り〈語彙〉／各パズル）は辞書の en/ne をそのまま使うので、辞書の翻訳率＝ドリルの翻訳率（＝100%）。専用の翻訳データは持たない。</t>
         </is>
       </c>
-      <c r="B86" s="82" t="n"/>
-      <c r="C86" s="82" t="n"/>
-      <c r="D86" s="82" t="n"/>
-      <c r="E86" s="82" t="n"/>
-      <c r="F86" s="82" t="n"/>
-      <c r="G86" s="82" t="n"/>
-      <c r="H86" s="82" t="n"/>
-      <c r="I86" s="82" t="n"/>
-      <c r="J86" s="82" t="n"/>
-      <c r="K86" s="82" t="n"/>
-      <c r="L86" s="82" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="90" t="inlineStr">
+      <c r="B88" s="82" t="n"/>
+      <c r="C88" s="82" t="n"/>
+      <c r="D88" s="82" t="n"/>
+      <c r="E88" s="82" t="n"/>
+      <c r="F88" s="82" t="n"/>
+      <c r="G88" s="82" t="n"/>
+      <c r="H88" s="82" t="n"/>
+      <c r="I88" s="82" t="n"/>
+      <c r="J88" s="82" t="n"/>
+      <c r="K88" s="82" t="n"/>
+      <c r="L88" s="82" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="90" t="inlineStr">
         <is>
           <t>※ 読み・書き取り・似た字の見分け・聞き取り〈漢字〉は かな／字／音声だけで解くため翻訳不要。旧版で「産出パズルは翻訳不要」としていたのは誤り＝意味を提示するため辞書流用100%。</t>
         </is>
       </c>
-      <c r="B87" s="82" t="n"/>
-      <c r="C87" s="82" t="n"/>
-      <c r="D87" s="82" t="n"/>
-      <c r="E87" s="82" t="n"/>
-      <c r="F87" s="82" t="n"/>
-      <c r="G87" s="82" t="n"/>
-      <c r="H87" s="82" t="n"/>
-      <c r="I87" s="82" t="n"/>
-      <c r="J87" s="82" t="n"/>
-      <c r="K87" s="82" t="n"/>
-      <c r="L87" s="82" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="91" t="inlineStr">
+      <c r="B89" s="82" t="n"/>
+      <c r="C89" s="82" t="n"/>
+      <c r="D89" s="82" t="n"/>
+      <c r="E89" s="82" t="n"/>
+      <c r="F89" s="82" t="n"/>
+      <c r="G89" s="82" t="n"/>
+      <c r="H89" s="82" t="n"/>
+      <c r="I89" s="82" t="n"/>
+      <c r="J89" s="82" t="n"/>
+      <c r="K89" s="82" t="n"/>
+      <c r="L89" s="82" t="n"/>
+    </row>
+    <row r="90"/>
+    <row r="91">
+      <c r="A91" s="91" t="inlineStr">
         <is>
           <t>まとめ</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="90" t="inlineStr">
-        <is>
-          <t>・完全対応は ja / en / ne の3言語。アプリのどこを開いても日本語・英語・ネパール語で読める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="90" t="inlineStr">
-        <is>
-          <t>・残り7言語(bn/id/ko/my/th/vi/zh)＝UIは全キー翻訳済(100%)。辞書は7言語すべて完了(id 2026-09-05／bn/ko/my/th/vi/zh 2026-09-05)。全7言語の問題訳は未着手。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="90" t="inlineStr">
         <is>
+          <t>・完全対応は ja / en / ne の3言語。アプリのどこを開いても日本語・英語・ネパール語で読める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="90" t="inlineStr">
+        <is>
+          <t>・残り7言語(bn/id/ko/my/th/vi/zh)＝UIは全キー翻訳済(100%)。辞書は7言語すべて完了(id 2026-09-05／bn/ko/my/th/vi/zh 2026-09-05)。全7言語の問題訳は未着手。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="90" t="inlineStr">
+        <is>
           <t>・7言語フル対応には 各問題の対訳 が必要（辞書は全7言語完了済）。UIは全言語対応済。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A32:I32"/>
     <mergeCell ref="A66:I66"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A67:I67"/>
@@ -14430,31 +14490,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="C9" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1195</v>
+        <v>1495</v>
       </c>
       <c r="F9" t="n">
         <v>2145</v>
       </c>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>56%</t>
+      <c r="G9" s="197" t="inlineStr">
+        <is>
+          <t>70%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>950</v>
+        <v>650</v>
       </c>
       <c r="I9" s="180" t="inlineStr">
         <is>
-          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=1195 / 下級流出=N5:3, N4:2</t>
+          <t>集中: 重複語0・最大1問/語 ｜ level-fit: 級内=1495 / 下級流出=N5:3, N4:2</t>
         </is>
       </c>
     </row>
